--- a/SubRES_TMPL/SubRES_NewTechs.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC46D044-FF80-4E7D-939E-67DEFF2C5F35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89AF23C2-FF22-44C2-A52E-B0D62AF925BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PRI_Sector_Fuels" sheetId="6" r:id="rId1"/>
@@ -1554,7 +1554,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="148">
   <si>
     <t>~FI_T</t>
   </si>
@@ -1823,15 +1823,6 @@
     <t>DayNite</t>
   </si>
   <si>
-    <t>GW per annum</t>
-  </si>
-  <si>
-    <t>Annual energy consumption devided by the product of annual hours*effficiency</t>
-  </si>
-  <si>
-    <t>Annual operating hours</t>
-  </si>
-  <si>
     <t>Natural Gas/Domestic</t>
   </si>
   <si>
@@ -1910,9 +1901,6 @@
     <t>CEMENTHEAT</t>
   </si>
   <si>
-    <t>Attribute</t>
-  </si>
-  <si>
     <t>TH2024USD/GWh</t>
   </si>
   <si>
@@ -1923,24 +1911,6 @@
   </si>
   <si>
     <t>Share-I~UP~2030</t>
-  </si>
-  <si>
-    <t>~TFM_UPD</t>
-  </si>
-  <si>
-    <t>REG</t>
-  </si>
-  <si>
-    <t>PROCESS</t>
-  </si>
-  <si>
-    <t>BioBoiler</t>
-  </si>
-  <si>
-    <t>UP</t>
-  </si>
-  <si>
-    <t>NCAP_BND</t>
   </si>
   <si>
     <t>START</t>
@@ -2656,189 +2626,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>516548</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>65943</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>3771674</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>142143</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="TextBox 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{90E0A094-A986-4947-A6ED-3B5001361863}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10026308" y="6299103"/>
-          <a:ext cx="5952606" cy="914400"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent6">
-            <a:lumMod val="20000"/>
-            <a:lumOff val="80000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr lvl="0"/>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>Declare  demand industry sector</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t> a demand commodity and an industry carbon dioxide</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>  environmental commodity (FI_COMM table) and define demand</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t> technology</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t> option (FI_Process table).</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr lvl="0"/>
-          <a:endParaRPr lang="en-GB" sz="1100">
-            <a:solidFill>
-              <a:schemeClr val="dk1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr lvl="0"/>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>Construct a demand</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t> technology to deliver the  industrial demand commodity.</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-GB" sz="1100">
-            <a:solidFill>
-              <a:schemeClr val="dk1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -3180,7 +2967,7 @@
         <v>58</v>
       </c>
       <c r="F2" s="73" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G2" s="14"/>
       <c r="N2" s="6" t="s">
@@ -3206,7 +2993,7 @@
         <v>58</v>
       </c>
       <c r="F3" s="73" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G3" s="14"/>
       <c r="N3" s="8" t="s">
@@ -3248,7 +3035,7 @@
         <v>58</v>
       </c>
       <c r="F4" s="73" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G4" s="14"/>
       <c r="N4" s="13" t="s">
@@ -3290,7 +3077,7 @@
         <v>58</v>
       </c>
       <c r="F5" s="73" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G5" s="14"/>
       <c r="N5" s="39" t="s">
@@ -3327,7 +3114,7 @@
         <v>67</v>
       </c>
       <c r="Q6" s="39" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="R6" s="39" t="s">
         <v>58</v>
@@ -3353,7 +3140,7 @@
         <v>72</v>
       </c>
       <c r="Q7" s="12" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="R7" s="12" t="s">
         <v>58</v>
@@ -3377,10 +3164,10 @@
       </c>
       <c r="O8" s="37"/>
       <c r="P8" s="37" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="Q8" s="37" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="R8" s="37" t="s">
         <v>58</v>
@@ -3718,7 +3505,7 @@
         <v>54</v>
       </c>
       <c r="I25" s="20" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="J25" s="20" t="s">
         <v>58</v>
@@ -3728,7 +3515,7 @@
         <v>81</v>
       </c>
       <c r="O25" s="22" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="P25" s="22"/>
       <c r="Q25" s="22"/>
@@ -3772,7 +3559,7 @@
       </c>
       <c r="O26" s="38"/>
       <c r="P26" s="39" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="Q26" s="40" t="str">
         <f>"Domestic Supply of "&amp;$D$4&amp;" "</f>
@@ -3820,7 +3607,7 @@
       </c>
       <c r="O27" s="38"/>
       <c r="P27" s="39" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="Q27" s="40" t="str">
         <f>"Domestic Supply of "&amp;$D$5&amp;" "</f>
@@ -3864,10 +3651,10 @@
         <v>64</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="Q28" s="1" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="R28" s="38" t="s">
         <v>58</v>
@@ -3908,10 +3695,10 @@
       </c>
       <c r="O29" s="14"/>
       <c r="P29" s="14" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="Q29" s="14" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="R29" s="38" t="s">
         <v>58</v>
@@ -4340,10 +4127,10 @@
     </row>
     <row r="2" spans="2:31" ht="31.2" x14ac:dyDescent="0.3">
       <c r="B2" s="48" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C2" s="48" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D2" s="49" t="str">
         <f>"Demand Technologies"</f>
@@ -4353,11 +4140,11 @@
         <v>58</v>
       </c>
       <c r="F2" s="48" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="G2" s="48"/>
       <c r="H2" s="48" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="V2" s="50" t="s">
         <v>7</v>
@@ -4446,10 +4233,10 @@
         <v>69</v>
       </c>
       <c r="X5" s="46" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="Y5" s="79" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="Z5" s="79" t="s">
         <v>58</v>
@@ -4469,10 +4256,10 @@
         <v>69</v>
       </c>
       <c r="X6" s="46" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="Y6" s="79" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="Z6" s="79" t="s">
         <v>58</v>
@@ -4492,10 +4279,10 @@
         <v>69</v>
       </c>
       <c r="X7" s="46" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="Y7" s="46" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="Z7" s="79" t="s">
         <v>58</v>
@@ -4738,7 +4525,7 @@
         <v>4</v>
       </c>
       <c r="E24" s="58" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="F24" s="58" t="s">
         <v>16</v>
@@ -4756,31 +4543,31 @@
         <v>5</v>
       </c>
       <c r="K24" s="60" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="L24" s="58" t="s">
         <v>56</v>
       </c>
       <c r="M24" s="60" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="N24" s="59" t="s">
+        <v>118</v>
+      </c>
+      <c r="O24" s="60" t="s">
+        <v>121</v>
+      </c>
+      <c r="P24" s="60" t="s">
         <v>122</v>
       </c>
-      <c r="O24" s="60" t="s">
-        <v>131</v>
-      </c>
-      <c r="P24" s="60" t="s">
+      <c r="Q24" s="60" t="s">
+        <v>123</v>
+      </c>
+      <c r="R24" s="60" t="s">
+        <v>124</v>
+      </c>
+      <c r="S24" s="60" t="s">
         <v>132</v>
-      </c>
-      <c r="Q24" s="60" t="s">
-        <v>133</v>
-      </c>
-      <c r="R24" s="60" t="s">
-        <v>134</v>
-      </c>
-      <c r="S24" s="60" t="s">
-        <v>142</v>
       </c>
       <c r="V24" s="31" t="s">
         <v>50</v>
@@ -4855,31 +4642,31 @@
         <v>37</v>
       </c>
       <c r="K25" s="33" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="L25" s="33" t="s">
         <v>80</v>
       </c>
       <c r="M25" s="33" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="N25" s="32" t="s">
         <v>85</v>
       </c>
       <c r="O25" s="33" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="P25" s="33" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="Q25" s="33" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="R25" s="76" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="S25" s="76" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="V25" s="31" t="s">
         <v>81</v>
@@ -4909,17 +4696,17 @@
         <v>54</v>
       </c>
       <c r="I26" s="35" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="J26" s="35" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="K26" s="35" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="L26" s="36"/>
       <c r="M26" s="36" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="N26" s="35"/>
       <c r="O26" s="36"/>
@@ -4928,14 +4715,14 @@
       <c r="R26" s="35"/>
       <c r="S26" s="77"/>
       <c r="V26" s="61" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="W26" s="61"/>
       <c r="X26" s="62" t="s">
         <v>66</v>
       </c>
       <c r="Y26" s="63" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="Z26" s="46" t="s">
         <v>58</v>
@@ -4961,7 +4748,7 @@
         <v>69</v>
       </c>
       <c r="D27" s="51" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E27" s="44">
         <v>2030</v>
@@ -5005,14 +4792,14 @@
       </c>
       <c r="S27" s="44"/>
       <c r="V27" s="61" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="W27" s="61"/>
       <c r="X27" s="62" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="Y27" s="63" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Z27" s="46" t="s">
         <v>58</v>
@@ -5052,7 +4839,7 @@
         <v>MANBIOMIN</v>
       </c>
       <c r="D28" s="51" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E28" s="44">
         <v>2030</v>
@@ -5086,14 +4873,14 @@
       <c r="R28" s="44"/>
       <c r="S28" s="44"/>
       <c r="V28" s="61" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="W28" s="61"/>
       <c r="X28" s="62" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="Y28" s="63" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="Z28" s="46" t="s">
         <v>58</v>
@@ -5132,7 +4919,7 @@
         <v>69</v>
       </c>
       <c r="D29" s="51" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E29" s="44">
         <v>2030</v>
@@ -5176,14 +4963,14 @@
       </c>
       <c r="S29" s="44"/>
       <c r="V29" s="61" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="W29" s="61"/>
       <c r="X29" s="62" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="Y29" s="63" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="Z29" s="46" t="s">
         <v>58</v>
@@ -5210,7 +4997,7 @@
         <v>MANBIOMIN</v>
       </c>
       <c r="D30" s="51" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E30" s="44">
         <v>2030</v>
@@ -5244,14 +5031,14 @@
       <c r="R30" s="44"/>
       <c r="S30" s="44"/>
       <c r="V30" s="61" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="W30" s="61"/>
       <c r="X30" s="62" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="Y30" s="63" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="Z30" s="46" t="s">
         <v>58</v>
@@ -5288,7 +5075,7 @@
         <v>MANGASMIN</v>
       </c>
       <c r="D31" s="51" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E31" s="44">
         <v>2030</v>
@@ -5322,14 +5109,14 @@
       <c r="R31" s="44"/>
       <c r="S31" s="44"/>
       <c r="V31" s="61" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="W31" s="61"/>
       <c r="X31" s="62" t="s">
         <v>65</v>
       </c>
       <c r="Y31" s="63" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="Z31" s="46" t="s">
         <v>58</v>
@@ -5366,7 +5153,7 @@
         <v>WIND</v>
       </c>
       <c r="D32" s="51" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="E32" s="44">
         <v>2030</v>
@@ -5406,10 +5193,10 @@
       </c>
       <c r="W32" s="61"/>
       <c r="X32" s="62" t="s">
+        <v>90</v>
+      </c>
+      <c r="Y32" s="63" t="s">
         <v>93</v>
-      </c>
-      <c r="Y32" s="63" t="s">
-        <v>96</v>
       </c>
       <c r="Z32" s="46" t="s">
         <v>58</v>
@@ -5446,7 +5233,7 @@
         <v>SOLAR</v>
       </c>
       <c r="D33" s="51" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="E33" s="44">
         <v>2030</v>
@@ -5486,10 +5273,10 @@
       </c>
       <c r="W33" s="61"/>
       <c r="X33" s="62" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="Y33" s="63" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="Z33" s="46" t="s">
         <v>58</v>
@@ -5526,7 +5313,7 @@
         <v>SOLAR</v>
       </c>
       <c r="D34" s="51" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E34" s="44">
         <v>2030</v>
@@ -5564,10 +5351,10 @@
       </c>
       <c r="W34" s="61"/>
       <c r="X34" s="62" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="Y34" s="63" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="Z34" s="46" t="s">
         <v>58</v>
@@ -5601,7 +5388,7 @@
       </c>
       <c r="C35" s="46"/>
       <c r="D35" s="51" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E35" s="44">
         <v>2030</v>
@@ -5639,10 +5426,10 @@
       </c>
       <c r="W35" s="61"/>
       <c r="X35" s="62" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="Y35" s="63" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="Z35" s="46" t="s">
         <v>58</v>
@@ -5675,7 +5462,7 @@
         <v>DECELC</v>
       </c>
       <c r="C36" s="51" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="D36" s="51" t="s">
         <v>69</v>
@@ -5739,7 +5526,7 @@
         <v>DECELC</v>
       </c>
       <c r="C37" s="51" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="D37" s="51" t="s">
         <v>69</v>
@@ -5806,7 +5593,7 @@
         <v>68</v>
       </c>
       <c r="D38" s="51" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="E38" s="44">
         <v>2030</v>
@@ -5865,10 +5652,10 @@
     </row>
     <row r="39" spans="2:49" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B39" s="51" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="C39" s="46" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="D39" s="51" t="s">
         <v>69</v>
@@ -6375,12 +6162,6 @@
       <c r="AT53" s="39"/>
     </row>
     <row r="54" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="E54" s="46" t="s">
-        <v>89</v>
-      </c>
-      <c r="F54" s="46" t="s">
-        <v>90</v>
-      </c>
       <c r="H54" s="70"/>
       <c r="AI54"/>
       <c r="AJ54"/>
@@ -6402,13 +6183,6 @@
       <c r="AT55" s="39"/>
     </row>
     <row r="56" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="E56" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="F56" s="46">
-        <f>24*365</f>
-        <v>8760</v>
-      </c>
       <c r="AI56"/>
       <c r="AJ56"/>
       <c r="AK56" s="39"/>
@@ -6490,9 +6264,7 @@
       <c r="AT63" s="39"/>
     </row>
     <row r="64" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="B64" s="74" t="s">
-        <v>123</v>
-      </c>
+      <c r="B64" s="74"/>
       <c r="C64" s="74"/>
       <c r="D64"/>
       <c r="E64"/>
@@ -6513,39 +6285,17 @@
       <c r="AT64" s="39"/>
     </row>
     <row r="65" spans="1:48" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B65" s="75" t="s">
-        <v>124</v>
-      </c>
-      <c r="C65" s="75" t="s">
-        <v>125</v>
-      </c>
-      <c r="D65" s="75" t="s">
-        <v>11</v>
-      </c>
-      <c r="E65" s="75" t="s">
-        <v>118</v>
-      </c>
-      <c r="F65" s="75">
-        <v>2022</v>
-      </c>
-      <c r="G65" s="75">
-        <v>2025</v>
-      </c>
-      <c r="H65" s="75">
-        <v>2030</v>
-      </c>
-      <c r="I65" s="75">
-        <v>2035</v>
-      </c>
-      <c r="J65" s="75">
-        <v>2040</v>
-      </c>
-      <c r="K65" s="75">
-        <v>2045</v>
-      </c>
-      <c r="L65" s="75">
-        <v>2050</v>
-      </c>
+      <c r="B65" s="75"/>
+      <c r="C65" s="75"/>
+      <c r="D65" s="75"/>
+      <c r="E65" s="75"/>
+      <c r="F65" s="75"/>
+      <c r="G65" s="75"/>
+      <c r="H65" s="75"/>
+      <c r="I65" s="75"/>
+      <c r="J65" s="75"/>
+      <c r="K65" s="75"/>
+      <c r="L65" s="75"/>
       <c r="AI65"/>
       <c r="AJ65"/>
       <c r="AK65" s="39"/>
@@ -6556,24 +6306,12 @@
       <c r="AT65" s="39"/>
     </row>
     <row r="66" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="B66" t="s">
-        <v>111</v>
-      </c>
-      <c r="C66" t="s">
-        <v>94</v>
-      </c>
-      <c r="D66" t="s">
-        <v>127</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F66">
-        <v>0</v>
-      </c>
-      <c r="G66">
-        <v>0</v>
-      </c>
+      <c r="B66"/>
+      <c r="C66"/>
+      <c r="D66"/>
+      <c r="E66" s="1"/>
+      <c r="F66"/>
+      <c r="G66"/>
       <c r="H66"/>
       <c r="I66"/>
       <c r="J66"/>
@@ -6589,24 +6327,12 @@
       <c r="AT66" s="39"/>
     </row>
     <row r="67" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="B67" t="s">
-        <v>111</v>
-      </c>
-      <c r="C67" t="s">
-        <v>93</v>
-      </c>
-      <c r="D67" t="s">
-        <v>127</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F67">
-        <v>0</v>
-      </c>
-      <c r="G67">
-        <v>0</v>
-      </c>
+      <c r="B67"/>
+      <c r="C67"/>
+      <c r="D67"/>
+      <c r="E67" s="1"/>
+      <c r="F67"/>
+      <c r="G67"/>
       <c r="H67"/>
       <c r="I67"/>
       <c r="J67"/>
@@ -6622,24 +6348,12 @@
       <c r="AT67" s="39"/>
     </row>
     <row r="68" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="B68" t="s">
-        <v>111</v>
-      </c>
-      <c r="C68" t="s">
-        <v>65</v>
-      </c>
-      <c r="D68" t="s">
-        <v>127</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F68">
-        <v>0</v>
-      </c>
-      <c r="G68">
-        <v>0</v>
-      </c>
+      <c r="B68"/>
+      <c r="C68"/>
+      <c r="D68"/>
+      <c r="E68" s="1"/>
+      <c r="F68"/>
+      <c r="G68"/>
       <c r="H68"/>
       <c r="I68"/>
       <c r="J68"/>
@@ -6655,24 +6369,12 @@
       <c r="AT68" s="39"/>
     </row>
     <row r="69" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="B69" t="s">
-        <v>111</v>
-      </c>
-      <c r="C69" t="s">
-        <v>126</v>
-      </c>
-      <c r="D69" t="s">
-        <v>127</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F69">
-        <v>0</v>
-      </c>
-      <c r="G69">
-        <v>0</v>
-      </c>
+      <c r="B69"/>
+      <c r="C69"/>
+      <c r="D69"/>
+      <c r="E69" s="1"/>
+      <c r="F69"/>
+      <c r="G69"/>
       <c r="H69"/>
       <c r="I69"/>
       <c r="J69"/>
@@ -6688,24 +6390,12 @@
       <c r="AT69" s="39"/>
     </row>
     <row r="70" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="B70" t="s">
-        <v>111</v>
-      </c>
-      <c r="C70" t="s">
-        <v>102</v>
-      </c>
-      <c r="D70" t="s">
-        <v>127</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F70">
-        <v>0</v>
-      </c>
-      <c r="G70">
-        <v>0</v>
-      </c>
+      <c r="B70"/>
+      <c r="C70"/>
+      <c r="D70"/>
+      <c r="E70" s="1"/>
+      <c r="F70"/>
+      <c r="G70"/>
       <c r="H70"/>
       <c r="I70"/>
       <c r="J70"/>
@@ -6721,24 +6411,12 @@
       <c r="AT70" s="39"/>
     </row>
     <row r="71" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="B71" t="s">
-        <v>111</v>
-      </c>
-      <c r="C71" t="s">
-        <v>105</v>
-      </c>
-      <c r="D71" t="s">
-        <v>127</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F71">
-        <v>0</v>
-      </c>
-      <c r="G71">
-        <v>0</v>
-      </c>
+      <c r="B71"/>
+      <c r="C71"/>
+      <c r="D71"/>
+      <c r="E71" s="1"/>
+      <c r="F71"/>
+      <c r="G71"/>
       <c r="H71"/>
       <c r="I71"/>
       <c r="J71"/>
@@ -6754,24 +6432,12 @@
       <c r="AT71" s="39"/>
     </row>
     <row r="72" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="B72" t="s">
-        <v>111</v>
-      </c>
-      <c r="C72" t="s">
-        <v>66</v>
-      </c>
-      <c r="D72" t="s">
-        <v>127</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F72">
-        <v>0</v>
-      </c>
-      <c r="G72">
-        <v>0</v>
-      </c>
+      <c r="B72"/>
+      <c r="C72"/>
+      <c r="D72"/>
+      <c r="E72" s="1"/>
+      <c r="F72"/>
+      <c r="G72"/>
       <c r="H72"/>
       <c r="I72"/>
       <c r="J72"/>
@@ -6787,24 +6453,12 @@
       <c r="AT72" s="39"/>
     </row>
     <row r="73" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="B73" t="s">
-        <v>111</v>
-      </c>
-      <c r="C73" t="s">
-        <v>103</v>
-      </c>
-      <c r="D73" t="s">
-        <v>127</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F73">
-        <v>0</v>
-      </c>
-      <c r="G73">
-        <v>0</v>
-      </c>
+      <c r="B73"/>
+      <c r="C73"/>
+      <c r="D73"/>
+      <c r="E73" s="1"/>
+      <c r="F73"/>
+      <c r="G73"/>
       <c r="H73"/>
       <c r="I73"/>
       <c r="J73"/>
@@ -7810,7 +7464,6 @@
   <phoneticPr fontId="24" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/SubRES_TMPL/SubRES_NewTechs.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89AF23C2-FF22-44C2-A52E-B0D62AF925BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C62061C-1AE3-4F1E-8A7E-5B49CEE382C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PRI_Sector_Fuels" sheetId="6" r:id="rId1"/>
@@ -1125,7 +1125,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB23" authorId="2" shapeId="0" xr:uid="{5EE58488-723F-4683-9026-2F0EE70F8071}">
+    <comment ref="AB13" authorId="2" shapeId="0" xr:uid="{5EE58488-723F-4683-9026-2F0EE70F8071}">
       <text>
         <r>
           <rPr>
@@ -1218,7 +1218,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC23" authorId="1" shapeId="0" xr:uid="{308E9284-8F99-498B-A3DD-262799AF67EB}">
+    <comment ref="AC13" authorId="1" shapeId="0" xr:uid="{308E9284-8F99-498B-A3DD-262799AF67EB}">
       <text>
         <r>
           <rPr>
@@ -1243,7 +1243,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AD23" authorId="2" shapeId="0" xr:uid="{FD29F772-15B8-47C4-8D7A-88CCF8F71647}">
+    <comment ref="AD13" authorId="2" shapeId="0" xr:uid="{FD29F772-15B8-47C4-8D7A-88CCF8F71647}">
       <text>
         <r>
           <rPr>
@@ -1306,7 +1306,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V24" authorId="2" shapeId="0" xr:uid="{BAA0F8AB-741B-4302-9E54-000CB5DC4ACF}">
+    <comment ref="V14" authorId="2" shapeId="0" xr:uid="{BAA0F8AB-741B-4302-9E54-000CB5DC4ACF}">
       <text>
         <r>
           <rPr>
@@ -2309,7 +2309,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
@@ -2395,9 +2395,6 @@
     <xf numFmtId="165" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="8" borderId="0" xfId="20" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="21" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="21" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="21" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
@@ -2456,9 +2453,7 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="20" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="4" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" xfId="4" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2963,10 +2958,10 @@
       <c r="D2" s="38" t="s">
         <v>73</v>
       </c>
-      <c r="E2" s="73" t="s">
+      <c r="E2" s="72" t="s">
         <v>58</v>
       </c>
-      <c r="F2" s="73" t="s">
+      <c r="F2" s="72" t="s">
         <v>115</v>
       </c>
       <c r="G2" s="14"/>
@@ -2989,10 +2984,10 @@
       <c r="D3" s="38" t="s">
         <v>74</v>
       </c>
-      <c r="E3" s="73" t="s">
+      <c r="E3" s="72" t="s">
         <v>58</v>
       </c>
-      <c r="F3" s="73" t="s">
+      <c r="F3" s="72" t="s">
         <v>115</v>
       </c>
       <c r="G3" s="14"/>
@@ -3031,10 +3026,10 @@
       <c r="D4" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="E4" s="73" t="s">
+      <c r="E4" s="72" t="s">
         <v>58</v>
       </c>
-      <c r="F4" s="73" t="s">
+      <c r="F4" s="72" t="s">
         <v>115</v>
       </c>
       <c r="G4" s="14"/>
@@ -3073,10 +3068,10 @@
       <c r="D5" s="38" t="s">
         <v>75</v>
       </c>
-      <c r="E5" s="73" t="s">
+      <c r="E5" s="72" t="s">
         <v>58</v>
       </c>
-      <c r="F5" s="73" t="s">
+      <c r="F5" s="72" t="s">
         <v>115</v>
       </c>
       <c r="G5" s="14"/>
@@ -4068,132 +4063,132 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3360854E-4C4D-467D-BD8A-32231E61C6CE}">
-  <dimension ref="A1:AY156"/>
+  <dimension ref="A1:AY146"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3" style="46" customWidth="1"/>
-    <col min="2" max="2" width="12.21875" style="46" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.77734375" style="46" customWidth="1"/>
-    <col min="4" max="4" width="13.77734375" style="46" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20" style="46" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.21875" style="46" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.5546875" style="46" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.77734375" style="46" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.21875" style="46" customWidth="1"/>
-    <col min="10" max="10" width="12.77734375" style="46" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="8.21875" style="46" customWidth="1"/>
-    <col min="13" max="13" width="10.21875" style="46" bestFit="1" customWidth="1"/>
-    <col min="14" max="19" width="8.21875" style="46" customWidth="1"/>
-    <col min="20" max="21" width="8.21875" style="47" customWidth="1"/>
-    <col min="22" max="22" width="12.77734375" style="46" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.21875" style="46" customWidth="1"/>
-    <col min="24" max="24" width="11.44140625" style="46" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="63.77734375" style="46" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="8.21875" style="46" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.77734375" style="46" customWidth="1"/>
-    <col min="28" max="28" width="13.44140625" style="46" customWidth="1"/>
-    <col min="29" max="29" width="13.77734375" style="46" customWidth="1"/>
-    <col min="30" max="30" width="8.44140625" style="46" customWidth="1"/>
-    <col min="31" max="35" width="8.77734375" style="46"/>
-    <col min="36" max="36" width="25.21875" style="46" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="16" style="46" bestFit="1" customWidth="1"/>
-    <col min="38" max="40" width="8.77734375" style="46"/>
-    <col min="41" max="41" width="13.21875" style="46" bestFit="1" customWidth="1"/>
-    <col min="42" max="43" width="8.77734375" style="46"/>
-    <col min="44" max="44" width="25.21875" style="46" bestFit="1" customWidth="1"/>
-    <col min="45" max="16384" width="8.77734375" style="46"/>
+    <col min="1" max="1" width="3" style="45" customWidth="1"/>
+    <col min="2" max="2" width="12.21875" style="45" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.77734375" style="45" customWidth="1"/>
+    <col min="4" max="4" width="13.77734375" style="45" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20" style="45" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.21875" style="45" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5546875" style="45" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.77734375" style="45" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.21875" style="45" customWidth="1"/>
+    <col min="10" max="10" width="12.77734375" style="45" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="8.21875" style="45" customWidth="1"/>
+    <col min="13" max="13" width="10.21875" style="45" bestFit="1" customWidth="1"/>
+    <col min="14" max="19" width="8.21875" style="45" customWidth="1"/>
+    <col min="20" max="21" width="8.21875" style="46" customWidth="1"/>
+    <col min="22" max="22" width="12.77734375" style="45" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.21875" style="45" customWidth="1"/>
+    <col min="24" max="24" width="11.44140625" style="45" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="63.77734375" style="45" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="8.21875" style="45" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.77734375" style="45" customWidth="1"/>
+    <col min="28" max="28" width="13.44140625" style="45" customWidth="1"/>
+    <col min="29" max="29" width="13.77734375" style="45" customWidth="1"/>
+    <col min="30" max="30" width="8.44140625" style="45" customWidth="1"/>
+    <col min="31" max="35" width="8.77734375" style="45"/>
+    <col min="36" max="36" width="25.21875" style="45" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="16" style="45" bestFit="1" customWidth="1"/>
+    <col min="38" max="40" width="8.77734375" style="45"/>
+    <col min="41" max="41" width="13.21875" style="45" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="8.77734375" style="45"/>
+    <col min="44" max="44" width="25.21875" style="45" bestFit="1" customWidth="1"/>
+    <col min="45" max="16384" width="8.77734375" style="45"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:31" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B1" s="45" t="s">
+    <row r="1" spans="2:51" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B1" s="44" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="45" t="s">
+      <c r="C1" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="45" t="s">
+      <c r="D1" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="45" t="s">
+      <c r="E1" s="44" t="s">
         <v>71</v>
       </c>
-      <c r="F1" s="45" t="s">
+      <c r="F1" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45" t="s">
+      <c r="G1" s="44"/>
+      <c r="H1" s="44" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="2:31" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="B2" s="48" t="s">
+    <row r="2" spans="2:51" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="B2" s="47" t="s">
         <v>95</v>
       </c>
-      <c r="C2" s="48" t="s">
+      <c r="C2" s="47" t="s">
         <v>96</v>
       </c>
-      <c r="D2" s="49" t="str">
+      <c r="D2" s="48" t="str">
         <f>"Demand Technologies"</f>
         <v>Demand Technologies</v>
       </c>
-      <c r="E2" s="48" t="s">
+      <c r="E2" s="47" t="s">
         <v>58</v>
       </c>
-      <c r="F2" s="48" t="s">
+      <c r="F2" s="47" t="s">
         <v>116</v>
       </c>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48" t="s">
+      <c r="G2" s="47"/>
+      <c r="H2" s="47" t="s">
         <v>94</v>
       </c>
-      <c r="V2" s="50" t="s">
+      <c r="V2" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="W2" s="50"/>
-      <c r="X2" s="51"/>
-      <c r="Y2" s="51"/>
-      <c r="Z2" s="51"/>
-      <c r="AA2" s="51"/>
-      <c r="AB2" s="51"/>
-      <c r="AC2" s="51"/>
-      <c r="AD2" s="51"/>
-    </row>
-    <row r="3" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="V3" s="52" t="s">
+      <c r="W2" s="49"/>
+      <c r="X2" s="50"/>
+      <c r="Y2" s="50"/>
+      <c r="Z2" s="50"/>
+      <c r="AA2" s="50"/>
+      <c r="AB2" s="50"/>
+      <c r="AC2" s="50"/>
+      <c r="AD2" s="50"/>
+    </row>
+    <row r="3" spans="2:51" x14ac:dyDescent="0.25">
+      <c r="V3" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="W3" s="53" t="s">
+      <c r="W3" s="52" t="s">
         <v>42</v>
       </c>
-      <c r="X3" s="52" t="s">
+      <c r="X3" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="Y3" s="52" t="s">
+      <c r="Y3" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="Z3" s="52" t="s">
+      <c r="Z3" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="AA3" s="52" t="s">
+      <c r="AA3" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="AB3" s="52" t="s">
+      <c r="AB3" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="AC3" s="52" t="s">
+      <c r="AC3" s="51" t="s">
         <v>13</v>
       </c>
-      <c r="AD3" s="52" t="s">
+      <c r="AD3" s="51" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="2:31" ht="22.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="54"/>
-      <c r="C4" s="54"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54"/>
+    <row r="4" spans="2:51" ht="22.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="53"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
       <c r="V4" s="31" t="s">
         <v>43</v>
       </c>
@@ -4222,1921 +4217,1893 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="2:31" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B5" s="54"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="V5" s="79" t="s">
+    <row r="5" spans="2:51" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B5" s="53"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="53"/>
+      <c r="E5" s="53"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="53"/>
+      <c r="V5" s="77" t="s">
         <v>69</v>
       </c>
-      <c r="X5" s="46" t="s">
+      <c r="X5" s="45" t="s">
         <v>140</v>
       </c>
-      <c r="Y5" s="79" t="s">
+      <c r="Y5" s="77" t="s">
         <v>141</v>
       </c>
-      <c r="Z5" s="79" t="s">
+      <c r="Z5" s="77" t="s">
         <v>58</v>
       </c>
-      <c r="AB5" s="79" t="s">
+      <c r="AB5" s="77" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="6" spans="2:31" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B6" s="54"/>
-      <c r="C6" s="54"/>
-      <c r="D6" s="54"/>
-      <c r="E6" s="54"/>
-      <c r="F6" s="54"/>
-      <c r="G6" s="54"/>
-      <c r="V6" s="79" t="s">
+    <row r="6" spans="2:51" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B6" s="53"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="53"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="53"/>
+      <c r="V6" s="77" t="s">
         <v>69</v>
       </c>
-      <c r="X6" s="46" t="s">
+      <c r="X6" s="45" t="s">
         <v>139</v>
       </c>
-      <c r="Y6" s="79" t="s">
+      <c r="Y6" s="77" t="s">
         <v>142</v>
       </c>
-      <c r="Z6" s="79" t="s">
+      <c r="Z6" s="77" t="s">
         <v>58</v>
       </c>
-      <c r="AB6" s="79" t="s">
+      <c r="AB6" s="77" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="2:31" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B7" s="54"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="54"/>
-      <c r="F7" s="54"/>
-      <c r="G7" s="54"/>
-      <c r="V7" s="46" t="s">
+    <row r="7" spans="2:51" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B7" s="53"/>
+      <c r="C7" s="53"/>
+      <c r="D7" s="53"/>
+      <c r="E7" s="53"/>
+      <c r="F7" s="53"/>
+      <c r="G7" s="53"/>
+      <c r="V7" s="45" t="s">
         <v>69</v>
       </c>
-      <c r="X7" s="46" t="s">
+      <c r="X7" s="45" t="s">
         <v>145</v>
       </c>
-      <c r="Y7" s="46" t="s">
+      <c r="Y7" s="45" t="s">
         <v>146</v>
       </c>
-      <c r="Z7" s="79" t="s">
+      <c r="Z7" s="77" t="s">
         <v>58</v>
       </c>
-      <c r="AB7" s="79" t="s">
+      <c r="AB7" s="77" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="2:31" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B8" s="54"/>
-      <c r="C8" s="54"/>
-      <c r="D8" s="54"/>
-      <c r="E8" s="54"/>
-      <c r="F8" s="54"/>
-      <c r="G8" s="54"/>
-    </row>
-    <row r="9" spans="2:31" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B9" s="54"/>
-      <c r="C9" s="54"/>
-      <c r="D9" s="54"/>
-      <c r="E9" s="54"/>
-      <c r="F9" s="54"/>
-      <c r="G9" s="54"/>
-    </row>
-    <row r="10" spans="2:31" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B10" s="54"/>
-      <c r="C10" s="54"/>
-      <c r="D10" s="54"/>
-      <c r="E10" s="54"/>
-      <c r="F10" s="54"/>
-      <c r="G10" s="54"/>
-    </row>
-    <row r="11" spans="2:31" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B11" s="54"/>
-      <c r="C11" s="54"/>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="54"/>
-      <c r="V11" s="42"/>
-      <c r="W11" s="42"/>
-      <c r="X11" s="42"/>
-      <c r="Y11" s="42"/>
-      <c r="Z11" s="42"/>
-      <c r="AA11" s="41"/>
-      <c r="AB11" s="64"/>
-      <c r="AC11" s="41"/>
-      <c r="AD11" s="41"/>
-    </row>
-    <row r="12" spans="2:31" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B12" s="54"/>
-      <c r="C12" s="54"/>
-      <c r="D12" s="54"/>
-      <c r="E12" s="54"/>
-      <c r="F12" s="54"/>
-      <c r="G12" s="54"/>
-      <c r="V12" s="42"/>
-      <c r="W12" s="42"/>
-      <c r="X12" s="42"/>
-      <c r="Y12" s="42"/>
-      <c r="Z12" s="42"/>
-      <c r="AA12" s="55"/>
-      <c r="AB12" s="64"/>
-      <c r="AC12" s="55"/>
-      <c r="AD12" s="55"/>
-      <c r="AE12" s="47"/>
-    </row>
-    <row r="13" spans="2:31" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B13" s="54"/>
-      <c r="C13" s="54"/>
-      <c r="D13" s="54"/>
-      <c r="E13" s="54"/>
-      <c r="F13" s="54"/>
-      <c r="G13" s="54"/>
-      <c r="V13" s="43"/>
-      <c r="W13" s="43"/>
-      <c r="X13" s="43"/>
-      <c r="Y13" s="43"/>
-      <c r="Z13" s="43"/>
-      <c r="AA13" s="55"/>
-      <c r="AB13" s="64"/>
-      <c r="AC13" s="55"/>
-      <c r="AD13" s="55"/>
-      <c r="AE13" s="47"/>
-    </row>
-    <row r="14" spans="2:31" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B14" s="54"/>
-      <c r="C14" s="54"/>
-      <c r="D14" s="54"/>
-      <c r="E14" s="54"/>
-      <c r="F14" s="54"/>
-      <c r="G14" s="54"/>
-      <c r="V14" s="79"/>
-      <c r="W14" s="79"/>
-      <c r="X14" s="79"/>
-      <c r="Y14" s="79"/>
-      <c r="Z14" s="79"/>
-      <c r="AA14" s="79"/>
-      <c r="AB14" s="79"/>
-      <c r="AC14" s="79"/>
-      <c r="AD14" s="79"/>
-      <c r="AE14" s="47"/>
-    </row>
-    <row r="15" spans="2:31" s="79" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B15" s="78"/>
-      <c r="C15" s="78"/>
-      <c r="D15" s="78"/>
-      <c r="E15" s="78"/>
-      <c r="F15" s="78"/>
-      <c r="G15" s="78"/>
-      <c r="T15" s="80"/>
-      <c r="U15" s="80"/>
-      <c r="AE15" s="80"/>
-    </row>
-    <row r="16" spans="2:31" s="79" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B16" s="78"/>
-      <c r="C16" s="78"/>
-      <c r="D16" s="78"/>
-      <c r="E16" s="78"/>
-      <c r="F16" s="78"/>
-      <c r="G16" s="78"/>
-      <c r="T16" s="80"/>
-      <c r="U16" s="80"/>
-      <c r="V16" s="46"/>
-      <c r="W16" s="46"/>
-      <c r="X16" s="46"/>
-      <c r="Y16" s="46"/>
-      <c r="Z16" s="46"/>
-      <c r="AA16" s="46"/>
-      <c r="AB16" s="46"/>
+    <row r="8" spans="2:51" x14ac:dyDescent="0.25">
+      <c r="AE8" s="46"/>
+    </row>
+    <row r="9" spans="2:51" x14ac:dyDescent="0.25">
+      <c r="V9" s="50"/>
+      <c r="W9" s="50"/>
+      <c r="X9" s="50"/>
+      <c r="Y9" s="50"/>
+      <c r="Z9" s="50"/>
+      <c r="AA9" s="50"/>
+      <c r="AB9" s="50"/>
+      <c r="AC9" s="50"/>
+      <c r="AD9" s="50"/>
+    </row>
+    <row r="10" spans="2:51" x14ac:dyDescent="0.25">
+      <c r="V10" s="50"/>
+      <c r="W10" s="50"/>
+      <c r="X10" s="50"/>
+      <c r="Y10" s="50"/>
+      <c r="Z10" s="50"/>
+      <c r="AA10" s="50"/>
+      <c r="AB10" s="50"/>
+      <c r="AC10" s="50"/>
+      <c r="AD10" s="50"/>
+    </row>
+    <row r="12" spans="2:51" x14ac:dyDescent="0.25">
+      <c r="V12" s="49" t="s">
+        <v>17</v>
+      </c>
+      <c r="W12" s="49"/>
+      <c r="X12" s="50"/>
+      <c r="Y12" s="50"/>
+      <c r="Z12" s="50"/>
+      <c r="AA12" s="50"/>
+      <c r="AB12" s="50"/>
+      <c r="AC12" s="50"/>
+      <c r="AD12" s="50"/>
+    </row>
+    <row r="13" spans="2:51" x14ac:dyDescent="0.25">
+      <c r="D13" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="E13" s="55"/>
+      <c r="F13" s="55"/>
+      <c r="H13" s="55"/>
+      <c r="V13" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="W13" s="52" t="s">
+        <v>42</v>
+      </c>
+      <c r="X13" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y13" s="51" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z13" s="51" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA13" s="51" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB13" s="51" t="s">
+        <v>20</v>
+      </c>
+      <c r="AC13" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="AD13" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="AI13"/>
+      <c r="AJ13" s="39"/>
+      <c r="AK13" s="77"/>
+      <c r="AL13" s="77"/>
+      <c r="AM13" s="77"/>
+      <c r="AN13" s="77"/>
+      <c r="AO13" s="77"/>
+      <c r="AP13" s="77"/>
+      <c r="AQ13" s="77"/>
+      <c r="AR13" s="77"/>
+      <c r="AS13" s="77"/>
+      <c r="AT13" s="77"/>
+      <c r="AU13" s="77"/>
+      <c r="AV13" s="77"/>
+      <c r="AW13" s="77"/>
+    </row>
+    <row r="14" spans="2:51" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="56" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="57" t="s">
+        <v>119</v>
+      </c>
+      <c r="F14" s="57" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14" s="57" t="s">
+        <v>34</v>
+      </c>
+      <c r="H14" s="57" t="s">
+        <v>47</v>
+      </c>
+      <c r="I14" s="57" t="s">
+        <v>36</v>
+      </c>
+      <c r="J14" s="59" t="s">
+        <v>5</v>
+      </c>
+      <c r="K14" s="59" t="s">
+        <v>104</v>
+      </c>
+      <c r="L14" s="57" t="s">
+        <v>56</v>
+      </c>
+      <c r="M14" s="59" t="s">
+        <v>109</v>
+      </c>
+      <c r="N14" s="58" t="s">
+        <v>118</v>
+      </c>
+      <c r="O14" s="59" t="s">
+        <v>121</v>
+      </c>
+      <c r="P14" s="59" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q14" s="59" t="s">
+        <v>123</v>
+      </c>
+      <c r="R14" s="59" t="s">
+        <v>124</v>
+      </c>
+      <c r="S14" s="59" t="s">
+        <v>132</v>
+      </c>
+      <c r="V14" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="W14" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="X14" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y14" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z14" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA14" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB14" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="AC14" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD14" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI14"/>
+      <c r="AJ14" s="39"/>
+      <c r="AK14" s="77"/>
+      <c r="AL14" s="77"/>
+      <c r="AM14" s="77"/>
+      <c r="AN14" s="77"/>
+      <c r="AO14" s="77"/>
+      <c r="AP14" s="77"/>
+      <c r="AQ14" s="77"/>
+      <c r="AR14" s="77"/>
+      <c r="AS14" s="77"/>
+      <c r="AT14" s="77"/>
+      <c r="AU14" s="77"/>
+      <c r="AV14" s="77"/>
+      <c r="AW14" s="77"/>
+      <c r="AY14" s="46"/>
+    </row>
+    <row r="15" spans="2:51" ht="31.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="E15" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="F15" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="G15" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="H15" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="I15" s="32" t="s">
+        <v>86</v>
+      </c>
+      <c r="J15" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="K15" s="33" t="s">
+        <v>105</v>
+      </c>
+      <c r="L15" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="M15" s="33" t="s">
+        <v>110</v>
+      </c>
+      <c r="N15" s="32" t="s">
+        <v>85</v>
+      </c>
+      <c r="O15" s="33" t="s">
+        <v>120</v>
+      </c>
+      <c r="P15" s="33" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q15" s="33" t="s">
+        <v>120</v>
+      </c>
+      <c r="R15" s="75" t="s">
+        <v>120</v>
+      </c>
+      <c r="S15" s="75" t="s">
+        <v>133</v>
+      </c>
+      <c r="V15" s="31" t="s">
+        <v>81</v>
+      </c>
+      <c r="W15" s="31"/>
+      <c r="X15" s="31"/>
+      <c r="Y15" s="31"/>
+      <c r="Z15" s="31"/>
+      <c r="AA15" s="31"/>
+      <c r="AB15" s="31"/>
+      <c r="AC15" s="31"/>
+      <c r="AD15" s="31"/>
+      <c r="AI15"/>
+      <c r="AJ15" s="39"/>
+      <c r="AY15" s="46"/>
+    </row>
+    <row r="16" spans="2:51" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="35"/>
+      <c r="G16" s="36"/>
+      <c r="H16" s="35" t="s">
+        <v>54</v>
+      </c>
+      <c r="I16" s="35" t="s">
+        <v>117</v>
+      </c>
+      <c r="J16" s="35" t="s">
+        <v>117</v>
+      </c>
+      <c r="K16" s="35" t="s">
+        <v>144</v>
+      </c>
+      <c r="L16" s="36"/>
+      <c r="M16" s="36" t="s">
+        <v>111</v>
+      </c>
+      <c r="N16" s="35"/>
+      <c r="O16" s="36"/>
+      <c r="P16" s="36"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="35"/>
+      <c r="S16" s="76"/>
+      <c r="V16" s="60" t="s">
+        <v>135</v>
+      </c>
+      <c r="W16" s="60"/>
+      <c r="X16" s="61" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y16" s="62" t="s">
+        <v>134</v>
+      </c>
+      <c r="Z16" s="45" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA16" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB16" s="63" t="s">
+        <v>88</v>
+      </c>
       <c r="AC16" s="46"/>
       <c r="AD16" s="46"/>
-      <c r="AE16" s="80"/>
-    </row>
-    <row r="17" spans="2:51" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B17" s="54"/>
-      <c r="C17" s="54"/>
-      <c r="D17" s="54"/>
-      <c r="E17" s="54"/>
-      <c r="F17" s="54"/>
-      <c r="G17" s="54"/>
-      <c r="AE17" s="47"/>
+      <c r="AI16"/>
+      <c r="AJ16" s="39"/>
+      <c r="AY16" s="46"/>
+    </row>
+    <row r="17" spans="2:51" x14ac:dyDescent="0.25">
+      <c r="B17" s="45" t="str">
+        <f>X16</f>
+        <v>Furnace</v>
+      </c>
+      <c r="C17" s="45" t="s">
+        <v>69</v>
+      </c>
+      <c r="D17" s="50" t="s">
+        <v>113</v>
+      </c>
+      <c r="E17" s="43">
+        <v>2030</v>
+      </c>
+      <c r="F17" s="64">
+        <v>1</v>
+      </c>
+      <c r="G17" s="64">
+        <v>1</v>
+      </c>
+      <c r="H17" s="43">
+        <v>25</v>
+      </c>
+      <c r="I17" s="64">
+        <v>81</v>
+      </c>
+      <c r="J17" s="64">
+        <v>0</v>
+      </c>
+      <c r="K17" s="64">
+        <v>0.24</v>
+      </c>
+      <c r="L17" s="64">
+        <v>8.76</v>
+      </c>
+      <c r="M17" s="43"/>
+      <c r="N17" s="64">
+        <v>0.1</v>
+      </c>
+      <c r="O17" s="64">
+        <v>0.15</v>
+      </c>
+      <c r="P17" s="64">
+        <v>0.2</v>
+      </c>
+      <c r="Q17" s="64">
+        <v>0.25</v>
+      </c>
+      <c r="R17" s="64">
+        <v>0.35</v>
+      </c>
+      <c r="S17" s="43"/>
+      <c r="V17" s="60" t="s">
+        <v>135</v>
+      </c>
+      <c r="W17" s="60"/>
+      <c r="X17" s="61" t="s">
+        <v>98</v>
+      </c>
+      <c r="Y17" s="62" t="s">
+        <v>97</v>
+      </c>
+      <c r="Z17" s="45" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA17" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB17" s="63" t="s">
+        <v>88</v>
+      </c>
+      <c r="AC17" s="46"/>
+      <c r="AD17" s="46"/>
+      <c r="AI17"/>
+      <c r="AJ17" s="39"/>
+      <c r="AK17" s="77"/>
+      <c r="AL17" s="77"/>
+      <c r="AM17" s="77"/>
+      <c r="AN17" s="77"/>
+      <c r="AO17" s="77"/>
+      <c r="AP17" s="77"/>
+      <c r="AQ17" s="77"/>
+      <c r="AR17" s="77"/>
+      <c r="AS17" s="77"/>
+      <c r="AT17" s="77"/>
+      <c r="AU17" s="77"/>
+      <c r="AV17" s="77"/>
+      <c r="AW17" s="77"/>
+      <c r="AY17" s="46"/>
     </row>
     <row r="18" spans="2:51" x14ac:dyDescent="0.25">
-      <c r="AE18" s="47"/>
-    </row>
-    <row r="19" spans="2:51" x14ac:dyDescent="0.25">
-      <c r="V19" s="51"/>
-      <c r="W19" s="51"/>
-      <c r="X19" s="51"/>
-      <c r="Y19" s="51"/>
-      <c r="Z19" s="51"/>
-      <c r="AA19" s="51"/>
-      <c r="AB19" s="51"/>
-      <c r="AC19" s="51"/>
-      <c r="AD19" s="51"/>
-    </row>
-    <row r="20" spans="2:51" x14ac:dyDescent="0.25">
-      <c r="V20" s="51"/>
-      <c r="W20" s="51"/>
-      <c r="X20" s="51"/>
-      <c r="Y20" s="51"/>
-      <c r="Z20" s="51"/>
-      <c r="AA20" s="51"/>
-      <c r="AB20" s="51"/>
-      <c r="AC20" s="51"/>
-      <c r="AD20" s="51"/>
-    </row>
-    <row r="22" spans="2:51" x14ac:dyDescent="0.25">
-      <c r="V22" s="50" t="s">
-        <v>17</v>
-      </c>
-      <c r="W22" s="50"/>
-      <c r="X22" s="51"/>
-      <c r="Y22" s="51"/>
-      <c r="Z22" s="51"/>
-      <c r="AA22" s="51"/>
-      <c r="AB22" s="51"/>
-      <c r="AC22" s="51"/>
-      <c r="AD22" s="51"/>
-    </row>
-    <row r="23" spans="2:51" x14ac:dyDescent="0.25">
-      <c r="D23" s="56" t="s">
-        <v>0</v>
-      </c>
-      <c r="E23" s="56"/>
-      <c r="F23" s="56"/>
-      <c r="H23" s="56"/>
-      <c r="V23" s="52" t="s">
-        <v>15</v>
-      </c>
-      <c r="W23" s="53" t="s">
-        <v>42</v>
-      </c>
-      <c r="X23" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y23" s="52" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z23" s="52" t="s">
-        <v>18</v>
-      </c>
-      <c r="AA23" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="AB23" s="52" t="s">
-        <v>20</v>
-      </c>
-      <c r="AC23" s="52" t="s">
-        <v>21</v>
-      </c>
-      <c r="AD23" s="52" t="s">
-        <v>22</v>
-      </c>
-      <c r="AI23"/>
-      <c r="AJ23" s="39"/>
-      <c r="AK23" s="79"/>
-      <c r="AL23" s="79"/>
-      <c r="AM23" s="79"/>
-      <c r="AN23" s="79"/>
-      <c r="AO23" s="79"/>
-      <c r="AP23" s="79"/>
-      <c r="AQ23" s="79"/>
-      <c r="AR23" s="79"/>
-      <c r="AS23" s="79"/>
-      <c r="AT23" s="79"/>
-      <c r="AU23" s="79"/>
-      <c r="AV23" s="79"/>
-      <c r="AW23" s="79"/>
-    </row>
-    <row r="24" spans="2:51" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" s="57" t="s">
-        <v>3</v>
-      </c>
-      <c r="D24" s="57" t="s">
-        <v>4</v>
-      </c>
-      <c r="E24" s="58" t="s">
-        <v>119</v>
-      </c>
-      <c r="F24" s="58" t="s">
-        <v>16</v>
-      </c>
-      <c r="G24" s="58" t="s">
-        <v>34</v>
-      </c>
-      <c r="H24" s="58" t="s">
-        <v>47</v>
-      </c>
-      <c r="I24" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="J24" s="60" t="s">
-        <v>5</v>
-      </c>
-      <c r="K24" s="60" t="s">
-        <v>104</v>
-      </c>
-      <c r="L24" s="58" t="s">
-        <v>56</v>
-      </c>
-      <c r="M24" s="60" t="s">
-        <v>109</v>
-      </c>
-      <c r="N24" s="59" t="s">
-        <v>118</v>
-      </c>
-      <c r="O24" s="60" t="s">
-        <v>121</v>
-      </c>
-      <c r="P24" s="60" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q24" s="60" t="s">
-        <v>123</v>
-      </c>
-      <c r="R24" s="60" t="s">
-        <v>124</v>
-      </c>
-      <c r="S24" s="60" t="s">
-        <v>132</v>
-      </c>
-      <c r="V24" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="W24" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="X24" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y24" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z24" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="AA24" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB24" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="AC24" s="31" t="s">
-        <v>52</v>
-      </c>
-      <c r="AD24" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="AI24"/>
-      <c r="AJ24" s="39"/>
-      <c r="AK24" s="79"/>
-      <c r="AL24" s="79"/>
-      <c r="AM24" s="79"/>
-      <c r="AN24" s="79"/>
-      <c r="AO24" s="79"/>
-      <c r="AP24" s="79"/>
-      <c r="AQ24" s="79"/>
-      <c r="AR24" s="79"/>
-      <c r="AS24" s="79"/>
-      <c r="AT24" s="79"/>
-      <c r="AU24" s="79"/>
-      <c r="AV24" s="79"/>
-      <c r="AW24" s="79"/>
-      <c r="AY24" s="47"/>
-    </row>
-    <row r="25" spans="2:51" ht="31.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="32" t="s">
-        <v>48</v>
-      </c>
-      <c r="C25" s="32" t="s">
-        <v>32</v>
-      </c>
-      <c r="D25" s="32" t="s">
-        <v>33</v>
-      </c>
-      <c r="E25" s="32" t="s">
-        <v>54</v>
-      </c>
-      <c r="F25" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="G25" s="33" t="s">
-        <v>49</v>
-      </c>
-      <c r="H25" s="32" t="s">
-        <v>57</v>
-      </c>
-      <c r="I25" s="32" t="s">
-        <v>86</v>
-      </c>
-      <c r="J25" s="33" t="s">
-        <v>37</v>
-      </c>
-      <c r="K25" s="33" t="s">
-        <v>105</v>
-      </c>
-      <c r="L25" s="33" t="s">
-        <v>80</v>
-      </c>
-      <c r="M25" s="33" t="s">
-        <v>110</v>
-      </c>
-      <c r="N25" s="32" t="s">
-        <v>85</v>
-      </c>
-      <c r="O25" s="33" t="s">
-        <v>120</v>
-      </c>
-      <c r="P25" s="33" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q25" s="33" t="s">
-        <v>120</v>
-      </c>
-      <c r="R25" s="76" t="s">
-        <v>120</v>
-      </c>
-      <c r="S25" s="76" t="s">
-        <v>133</v>
-      </c>
-      <c r="V25" s="31" t="s">
-        <v>81</v>
-      </c>
-      <c r="W25" s="31"/>
-      <c r="X25" s="31"/>
-      <c r="Y25" s="31"/>
-      <c r="Z25" s="31"/>
-      <c r="AA25" s="31"/>
-      <c r="AB25" s="31"/>
-      <c r="AC25" s="31"/>
-      <c r="AD25" s="31"/>
-      <c r="AI25"/>
-      <c r="AJ25" s="39"/>
-      <c r="AY25" s="47"/>
-    </row>
-    <row r="26" spans="2:51" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="C26" s="34"/>
-      <c r="D26" s="34"/>
-      <c r="E26" s="35"/>
-      <c r="F26" s="35"/>
-      <c r="G26" s="36"/>
-      <c r="H26" s="35" t="s">
-        <v>54</v>
-      </c>
-      <c r="I26" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="J26" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="K26" s="35" t="s">
-        <v>144</v>
-      </c>
-      <c r="L26" s="36"/>
-      <c r="M26" s="36" t="s">
-        <v>111</v>
-      </c>
-      <c r="N26" s="35"/>
-      <c r="O26" s="36"/>
-      <c r="P26" s="36"/>
-      <c r="Q26" s="36"/>
-      <c r="R26" s="35"/>
-      <c r="S26" s="77"/>
-      <c r="V26" s="61" t="s">
-        <v>135</v>
-      </c>
-      <c r="W26" s="61"/>
-      <c r="X26" s="62" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y26" s="63" t="s">
-        <v>134</v>
-      </c>
-      <c r="Z26" s="46" t="s">
-        <v>58</v>
-      </c>
-      <c r="AA26" s="46" t="s">
-        <v>87</v>
-      </c>
-      <c r="AB26" s="64" t="s">
-        <v>88</v>
-      </c>
-      <c r="AC26" s="47"/>
-      <c r="AD26" s="47"/>
-      <c r="AI26"/>
-      <c r="AJ26" s="39"/>
-      <c r="AY26" s="47"/>
-    </row>
-    <row r="27" spans="2:51" x14ac:dyDescent="0.25">
-      <c r="B27" s="46" t="str">
-        <f>X26</f>
-        <v>Furnace</v>
-      </c>
-      <c r="C27" s="46" t="s">
-        <v>69</v>
-      </c>
-      <c r="D27" s="51" t="s">
-        <v>113</v>
-      </c>
-      <c r="E27" s="44">
-        <v>2030</v>
-      </c>
-      <c r="F27" s="65">
-        <v>1</v>
-      </c>
-      <c r="G27" s="65">
-        <v>1</v>
-      </c>
-      <c r="H27" s="44">
-        <v>25</v>
-      </c>
-      <c r="I27" s="65">
-        <v>81</v>
-      </c>
-      <c r="J27" s="65">
-        <v>0</v>
-      </c>
-      <c r="K27" s="65">
-        <v>0.24</v>
-      </c>
-      <c r="L27" s="65">
-        <v>8.76</v>
-      </c>
-      <c r="M27" s="44"/>
-      <c r="N27" s="65">
-        <v>0.1</v>
-      </c>
-      <c r="O27" s="65">
-        <v>0.15</v>
-      </c>
-      <c r="P27" s="65">
-        <v>0.2</v>
-      </c>
-      <c r="Q27" s="65">
-        <v>0.25</v>
-      </c>
-      <c r="R27" s="65">
-        <v>0.35</v>
-      </c>
-      <c r="S27" s="44"/>
-      <c r="V27" s="61" t="s">
-        <v>135</v>
-      </c>
-      <c r="W27" s="61"/>
-      <c r="X27" s="62" t="s">
-        <v>98</v>
-      </c>
-      <c r="Y27" s="63" t="s">
-        <v>97</v>
-      </c>
-      <c r="Z27" s="46" t="s">
-        <v>58</v>
-      </c>
-      <c r="AA27" s="46" t="s">
-        <v>87</v>
-      </c>
-      <c r="AB27" s="64" t="s">
-        <v>88</v>
-      </c>
-      <c r="AC27" s="47"/>
-      <c r="AD27" s="47"/>
-      <c r="AI27"/>
-      <c r="AJ27" s="39"/>
-      <c r="AK27" s="79"/>
-      <c r="AL27" s="79"/>
-      <c r="AM27" s="79"/>
-      <c r="AN27" s="79"/>
-      <c r="AO27" s="79"/>
-      <c r="AP27" s="79"/>
-      <c r="AQ27" s="79"/>
-      <c r="AR27" s="79"/>
-      <c r="AS27" s="79"/>
-      <c r="AT27" s="79"/>
-      <c r="AU27" s="79"/>
-      <c r="AV27" s="79"/>
-      <c r="AW27" s="79"/>
-      <c r="AY27" s="47"/>
-    </row>
-    <row r="28" spans="2:51" x14ac:dyDescent="0.25">
-      <c r="B28" s="46" t="str">
-        <f>X$27</f>
+      <c r="B18" s="45" t="str">
+        <f>X$17</f>
         <v>BIOBoiler</v>
       </c>
-      <c r="C28" s="46" t="str">
+      <c r="C18" s="45" t="str">
         <f>PRI_Sector_Fuels!P5</f>
         <v>MANBIOMIN</v>
       </c>
-      <c r="D28" s="51" t="s">
+      <c r="D18" s="50" t="s">
         <v>113</v>
       </c>
-      <c r="E28" s="44">
+      <c r="E18" s="43">
         <v>2030</v>
       </c>
-      <c r="F28" s="65">
+      <c r="F18" s="64">
         <v>0.7</v>
       </c>
-      <c r="G28" s="65">
+      <c r="G18" s="64">
         <v>0.98</v>
       </c>
-      <c r="H28" s="44">
+      <c r="H18" s="43">
         <v>25</v>
       </c>
-      <c r="I28" s="65">
+      <c r="I18" s="64">
         <v>797.9</v>
       </c>
-      <c r="J28" s="65">
+      <c r="J18" s="64">
         <v>48.48</v>
       </c>
-      <c r="K28" s="65">
+      <c r="K18" s="64">
         <v>3.75</v>
       </c>
-      <c r="L28" s="65">
+      <c r="L18" s="64">
         <v>8.76</v>
       </c>
-      <c r="M28" s="44"/>
-      <c r="N28" s="69"/>
-      <c r="O28" s="44"/>
-      <c r="P28" s="44"/>
-      <c r="Q28" s="44"/>
-      <c r="R28" s="44"/>
-      <c r="S28" s="44"/>
-      <c r="V28" s="61" t="s">
+      <c r="M18" s="43"/>
+      <c r="N18" s="68"/>
+      <c r="O18" s="43"/>
+      <c r="P18" s="43"/>
+      <c r="Q18" s="43"/>
+      <c r="R18" s="43"/>
+      <c r="S18" s="43"/>
+      <c r="V18" s="60" t="s">
         <v>135</v>
       </c>
-      <c r="W28" s="61"/>
-      <c r="X28" s="62" t="s">
+      <c r="W18" s="60"/>
+      <c r="X18" s="61" t="s">
         <v>99</v>
       </c>
-      <c r="Y28" s="63" t="s">
+      <c r="Y18" s="62" t="s">
         <v>138</v>
       </c>
-      <c r="Z28" s="46" t="s">
+      <c r="Z18" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="AA28" s="46" t="s">
+      <c r="AA18" s="45" t="s">
         <v>87</v>
       </c>
-      <c r="AB28" s="64" t="s">
+      <c r="AB18" s="63" t="s">
         <v>88</v>
       </c>
-      <c r="AC28" s="47"/>
-      <c r="AD28" s="47"/>
-      <c r="AI28"/>
-      <c r="AJ28" s="39"/>
-      <c r="AK28" s="79"/>
-      <c r="AL28" s="79"/>
-      <c r="AM28" s="79"/>
-      <c r="AN28" s="79"/>
-      <c r="AO28" s="79"/>
-      <c r="AP28" s="79"/>
-      <c r="AQ28" s="79"/>
-      <c r="AR28" s="79"/>
-      <c r="AS28" s="79"/>
-      <c r="AT28" s="79"/>
-      <c r="AU28" s="79"/>
-      <c r="AV28" s="79"/>
-      <c r="AW28" s="79"/>
-      <c r="AY28" s="47"/>
-    </row>
-    <row r="29" spans="2:51" x14ac:dyDescent="0.25">
-      <c r="B29" s="46" t="str">
-        <f>X30</f>
+      <c r="AC18" s="46"/>
+      <c r="AD18" s="46"/>
+      <c r="AI18"/>
+      <c r="AJ18" s="39"/>
+      <c r="AK18" s="77"/>
+      <c r="AL18" s="77"/>
+      <c r="AM18" s="77"/>
+      <c r="AN18" s="77"/>
+      <c r="AO18" s="77"/>
+      <c r="AP18" s="77"/>
+      <c r="AQ18" s="77"/>
+      <c r="AR18" s="77"/>
+      <c r="AS18" s="77"/>
+      <c r="AT18" s="77"/>
+      <c r="AU18" s="77"/>
+      <c r="AV18" s="77"/>
+      <c r="AW18" s="77"/>
+      <c r="AY18" s="46"/>
+    </row>
+    <row r="19" spans="2:51" x14ac:dyDescent="0.25">
+      <c r="B19" s="45" t="str">
+        <f>X20</f>
         <v>ELCBoiler</v>
       </c>
-      <c r="C29" s="46" t="s">
+      <c r="C19" s="45" t="s">
         <v>69</v>
       </c>
-      <c r="D29" s="51" t="s">
+      <c r="D19" s="50" t="s">
         <v>113</v>
       </c>
-      <c r="E29" s="44">
+      <c r="E19" s="43">
         <v>2030</v>
       </c>
-      <c r="F29" s="65">
+      <c r="F19" s="64">
         <v>0.99</v>
       </c>
-      <c r="G29" s="65">
+      <c r="G19" s="64">
         <v>1</v>
       </c>
-      <c r="H29" s="44">
+      <c r="H19" s="43">
         <v>25</v>
       </c>
-      <c r="I29" s="65">
+      <c r="I19" s="64">
         <v>112.9</v>
       </c>
-      <c r="J29" s="65">
+      <c r="J19" s="64">
         <v>14.26</v>
       </c>
-      <c r="K29" s="65">
+      <c r="K19" s="64">
         <v>1.22</v>
       </c>
-      <c r="L29" s="65">
+      <c r="L19" s="64">
         <v>8.76</v>
       </c>
-      <c r="M29" s="44"/>
-      <c r="N29" s="46">
+      <c r="M19" s="43"/>
+      <c r="N19" s="45">
         <v>0.2</v>
       </c>
-      <c r="O29" s="46">
+      <c r="O19" s="45">
         <v>0.25</v>
       </c>
-      <c r="P29" s="46">
+      <c r="P19" s="45">
         <v>0.3</v>
       </c>
-      <c r="Q29" s="46">
+      <c r="Q19" s="45">
         <v>0.35</v>
       </c>
-      <c r="R29" s="46">
+      <c r="R19" s="45">
         <v>0.4</v>
       </c>
-      <c r="S29" s="44"/>
-      <c r="V29" s="61" t="s">
+      <c r="S19" s="43"/>
+      <c r="V19" s="60" t="s">
         <v>135</v>
       </c>
-      <c r="W29" s="61"/>
-      <c r="X29" s="62" t="s">
+      <c r="W19" s="60"/>
+      <c r="X19" s="61" t="s">
         <v>100</v>
       </c>
-      <c r="Y29" s="63" t="s">
+      <c r="Y19" s="62" t="s">
         <v>101</v>
       </c>
-      <c r="Z29" s="46" t="s">
+      <c r="Z19" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="AA29" s="46" t="s">
+      <c r="AA19" s="45" t="s">
         <v>87</v>
       </c>
-      <c r="AB29" s="64" t="s">
+      <c r="AB19" s="63" t="s">
         <v>88</v>
       </c>
-      <c r="AC29" s="47"/>
-      <c r="AD29" s="47"/>
-      <c r="AI29"/>
-      <c r="AJ29" s="39"/>
-      <c r="AY29" s="47"/>
-    </row>
-    <row r="30" spans="2:51" s="47" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="46" t="str">
-        <f>X28</f>
+      <c r="AC19" s="46"/>
+      <c r="AD19" s="46"/>
+      <c r="AI19"/>
+      <c r="AJ19" s="39"/>
+      <c r="AY19" s="46"/>
+    </row>
+    <row r="20" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="45" t="str">
+        <f>X18</f>
         <v>BIOKiln</v>
       </c>
-      <c r="C30" s="46" t="str">
+      <c r="C20" s="45" t="str">
         <f>PRI_Sector_Fuels!P5</f>
         <v>MANBIOMIN</v>
       </c>
-      <c r="D30" s="51" t="s">
+      <c r="D20" s="50" t="s">
         <v>114</v>
       </c>
-      <c r="E30" s="44">
+      <c r="E20" s="43">
         <v>2030</v>
       </c>
-      <c r="F30" s="65">
+      <c r="F20" s="64">
         <v>0.55600000000000005</v>
       </c>
-      <c r="G30" s="65">
+      <c r="G20" s="64">
         <v>0.98</v>
       </c>
-      <c r="H30" s="44">
+      <c r="H20" s="43">
         <v>25</v>
       </c>
-      <c r="I30" s="65">
+      <c r="I20" s="64">
         <v>297.10000000000002</v>
       </c>
-      <c r="J30" s="65">
+      <c r="J20" s="64">
         <v>4.46</v>
       </c>
-      <c r="K30" s="65">
+      <c r="K20" s="64">
         <v>0.45</v>
       </c>
-      <c r="L30" s="65">
+      <c r="L20" s="64">
         <v>8.76</v>
       </c>
-      <c r="M30" s="44"/>
-      <c r="N30" s="69"/>
-      <c r="O30" s="44"/>
-      <c r="P30" s="44"/>
-      <c r="Q30" s="44"/>
-      <c r="R30" s="44"/>
-      <c r="S30" s="44"/>
-      <c r="V30" s="61" t="s">
+      <c r="M20" s="43"/>
+      <c r="N20" s="68"/>
+      <c r="O20" s="43"/>
+      <c r="P20" s="43"/>
+      <c r="Q20" s="43"/>
+      <c r="R20" s="43"/>
+      <c r="S20" s="43"/>
+      <c r="V20" s="60" t="s">
         <v>135</v>
       </c>
-      <c r="W30" s="61"/>
-      <c r="X30" s="62" t="s">
+      <c r="W20" s="60"/>
+      <c r="X20" s="61" t="s">
         <v>102</v>
       </c>
-      <c r="Y30" s="63" t="s">
+      <c r="Y20" s="62" t="s">
         <v>137</v>
       </c>
-      <c r="Z30" s="46" t="s">
+      <c r="Z20" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="AA30" s="46" t="s">
+      <c r="AA20" s="45" t="s">
         <v>87</v>
       </c>
-      <c r="AB30" s="64" t="s">
+      <c r="AB20" s="63" t="s">
         <v>88</v>
       </c>
+      <c r="AI20"/>
+      <c r="AJ20"/>
+      <c r="AK20" s="45"/>
+      <c r="AL20" s="45"/>
+      <c r="AM20" s="45"/>
+      <c r="AN20" s="45"/>
+      <c r="AO20" s="45"/>
+      <c r="AP20" s="45"/>
+      <c r="AQ20" s="45"/>
+      <c r="AR20" s="45"/>
+      <c r="AS20" s="45"/>
+      <c r="AT20" s="45"/>
+      <c r="AU20" s="45"/>
+      <c r="AV20" s="45"/>
+      <c r="AW20" s="45"/>
+    </row>
+    <row r="21" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="50" t="str">
+        <f>X19</f>
+        <v>GASBoiler</v>
+      </c>
+      <c r="C21" s="45" t="str">
+        <f>PRI_Sector_Fuels!P6</f>
+        <v>MANGASMIN</v>
+      </c>
+      <c r="D21" s="50" t="s">
+        <v>113</v>
+      </c>
+      <c r="E21" s="43">
+        <v>2030</v>
+      </c>
+      <c r="F21" s="64">
+        <v>0.75</v>
+      </c>
+      <c r="G21" s="64">
+        <v>0.99</v>
+      </c>
+      <c r="H21" s="43">
+        <v>25</v>
+      </c>
+      <c r="I21" s="64">
+        <v>61.4</v>
+      </c>
+      <c r="J21" s="64">
+        <v>2.57</v>
+      </c>
+      <c r="K21" s="64">
+        <v>1.35</v>
+      </c>
+      <c r="L21" s="64">
+        <v>8.76</v>
+      </c>
+      <c r="M21" s="43"/>
+      <c r="N21" s="68"/>
+      <c r="O21" s="43"/>
+      <c r="P21" s="43"/>
+      <c r="Q21" s="43"/>
+      <c r="R21" s="43"/>
+      <c r="S21" s="43"/>
+      <c r="V21" s="60" t="s">
+        <v>135</v>
+      </c>
+      <c r="W21" s="60"/>
+      <c r="X21" s="61" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y21" s="62" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z21" s="45" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA21" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB21" s="46" t="s">
+        <v>88</v>
+      </c>
+      <c r="AI21"/>
+      <c r="AJ21"/>
+      <c r="AK21" s="77"/>
+      <c r="AL21" s="77"/>
+      <c r="AM21" s="77"/>
+      <c r="AN21" s="77"/>
+      <c r="AO21" s="77"/>
+      <c r="AP21" s="77"/>
+      <c r="AQ21" s="77"/>
+      <c r="AR21" s="77"/>
+      <c r="AS21" s="77"/>
+      <c r="AT21" s="77"/>
+      <c r="AU21" s="77"/>
+      <c r="AV21" s="77"/>
+      <c r="AW21" s="77"/>
+    </row>
+    <row r="22" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="50" t="str">
+        <f>X22</f>
+        <v>WNDTRBN</v>
+      </c>
+      <c r="C22" s="45" t="str">
+        <f>PRI_Sector_Fuels!D28</f>
+        <v>WIND</v>
+      </c>
+      <c r="D22" s="50" t="s">
+        <v>139</v>
+      </c>
+      <c r="E22" s="43">
+        <v>2030</v>
+      </c>
+      <c r="F22" s="83">
+        <v>1</v>
+      </c>
+      <c r="G22" s="64">
+        <v>0.97</v>
+      </c>
+      <c r="H22" s="43">
+        <v>25</v>
+      </c>
+      <c r="I22" s="64">
+        <v>1041</v>
+      </c>
+      <c r="J22" s="64">
+        <v>38</v>
+      </c>
+      <c r="K22" s="64">
+        <v>0</v>
+      </c>
+      <c r="L22" s="64">
+        <v>8.76</v>
+      </c>
+      <c r="M22" s="68"/>
+      <c r="N22" s="68"/>
+      <c r="O22" s="64"/>
+      <c r="P22" s="64"/>
+      <c r="Q22" s="64"/>
+      <c r="R22" s="68"/>
+      <c r="S22" s="43">
+        <v>0.2</v>
+      </c>
+      <c r="V22" s="60" t="s">
+        <v>69</v>
+      </c>
+      <c r="W22" s="60"/>
+      <c r="X22" s="61" t="s">
+        <v>90</v>
+      </c>
+      <c r="Y22" s="62" t="s">
+        <v>93</v>
+      </c>
+      <c r="Z22" s="45" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA22" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB22" s="46" t="s">
+        <v>88</v>
+      </c>
+      <c r="AI22"/>
+      <c r="AJ22"/>
+      <c r="AK22" s="77"/>
+      <c r="AL22" s="77"/>
+      <c r="AM22" s="77"/>
+      <c r="AN22" s="77"/>
+      <c r="AO22" s="77"/>
+      <c r="AP22" s="77"/>
+      <c r="AQ22" s="77"/>
+      <c r="AR22" s="77"/>
+      <c r="AS22" s="77"/>
+      <c r="AT22" s="77"/>
+      <c r="AU22" s="77"/>
+      <c r="AV22" s="77"/>
+      <c r="AW22" s="77"/>
+    </row>
+    <row r="23" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="50" t="str">
+        <f>X23</f>
+        <v>SOLPV</v>
+      </c>
+      <c r="C23" s="45" t="str">
+        <f>PRI_Sector_Fuels!D29</f>
+        <v>SOLAR</v>
+      </c>
+      <c r="D23" s="50" t="s">
+        <v>140</v>
+      </c>
+      <c r="E23" s="43">
+        <v>2030</v>
+      </c>
+      <c r="F23" s="83">
+        <v>1</v>
+      </c>
+      <c r="G23" s="64">
+        <v>0.99</v>
+      </c>
+      <c r="H23" s="43">
+        <v>25</v>
+      </c>
+      <c r="I23" s="64">
+        <v>691</v>
+      </c>
+      <c r="J23" s="64">
+        <v>6.99</v>
+      </c>
+      <c r="K23" s="64">
+        <v>0</v>
+      </c>
+      <c r="L23" s="64">
+        <v>8.76</v>
+      </c>
+      <c r="M23" s="68"/>
+      <c r="N23" s="68"/>
+      <c r="O23" s="64"/>
+      <c r="P23" s="64"/>
+      <c r="Q23" s="64"/>
+      <c r="R23" s="68"/>
+      <c r="S23" s="43">
+        <v>0.3</v>
+      </c>
+      <c r="V23" s="60" t="s">
+        <v>69</v>
+      </c>
+      <c r="W23" s="60"/>
+      <c r="X23" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="Y23" s="62" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z23" s="45" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA23" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB23" s="46" t="s">
+        <v>88</v>
+      </c>
+      <c r="AI23"/>
+      <c r="AJ23"/>
+      <c r="AK23" s="45"/>
+      <c r="AL23" s="45"/>
+      <c r="AM23" s="45"/>
+      <c r="AN23" s="45"/>
+      <c r="AO23" s="45"/>
+      <c r="AP23" s="45"/>
+      <c r="AQ23" s="45"/>
+      <c r="AR23" s="45"/>
+      <c r="AS23" s="45"/>
+      <c r="AT23" s="45"/>
+      <c r="AU23" s="45"/>
+      <c r="AV23" s="45"/>
+      <c r="AW23" s="45"/>
+    </row>
+    <row r="24" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="50" t="str">
+        <f>X21</f>
+        <v>CSP</v>
+      </c>
+      <c r="C24" s="45" t="str">
+        <f>PRI_Sector_Fuels!D29</f>
+        <v>SOLAR</v>
+      </c>
+      <c r="D24" s="50" t="s">
+        <v>113</v>
+      </c>
+      <c r="E24" s="43">
+        <v>2030</v>
+      </c>
+      <c r="F24" s="83">
+        <v>1</v>
+      </c>
+      <c r="G24" s="64">
+        <v>1</v>
+      </c>
+      <c r="H24" s="43">
+        <v>25</v>
+      </c>
+      <c r="I24" s="64">
+        <v>3677</v>
+      </c>
+      <c r="J24" s="64">
+        <v>0</v>
+      </c>
+      <c r="K24" s="64">
+        <v>14</v>
+      </c>
+      <c r="L24" s="64">
+        <v>8.76</v>
+      </c>
+      <c r="M24" s="68"/>
+      <c r="N24" s="68"/>
+      <c r="O24" s="64"/>
+      <c r="P24" s="64"/>
+      <c r="Q24" s="64"/>
+      <c r="R24" s="68"/>
+      <c r="S24" s="43"/>
+      <c r="V24" s="60" t="s">
+        <v>69</v>
+      </c>
+      <c r="W24" s="60"/>
+      <c r="X24" s="61" t="s">
+        <v>136</v>
+      </c>
+      <c r="Y24" s="62" t="s">
+        <v>143</v>
+      </c>
+      <c r="Z24" s="45" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA24" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB24" s="46" t="s">
+        <v>88</v>
+      </c>
+      <c r="AI24"/>
+      <c r="AJ24"/>
+      <c r="AK24" s="45"/>
+      <c r="AL24" s="45"/>
+      <c r="AM24" s="45"/>
+      <c r="AN24" s="45"/>
+      <c r="AO24" s="45"/>
+      <c r="AP24" s="45"/>
+      <c r="AQ24" s="45"/>
+      <c r="AR24" s="45"/>
+      <c r="AS24" s="45"/>
+      <c r="AT24" s="45"/>
+      <c r="AU24" s="45"/>
+      <c r="AV24" s="45"/>
+      <c r="AW24" s="45"/>
+    </row>
+    <row r="25" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="50" t="str">
+        <f>X19</f>
+        <v>GASBoiler</v>
+      </c>
+      <c r="C25" s="45"/>
+      <c r="D25" s="50" t="s">
+        <v>112</v>
+      </c>
+      <c r="E25" s="43">
+        <v>2030</v>
+      </c>
+      <c r="F25" s="83">
+        <v>1</v>
+      </c>
+      <c r="G25" s="64">
+        <v>1</v>
+      </c>
+      <c r="H25" s="43">
+        <v>25</v>
+      </c>
+      <c r="I25" s="64">
+        <v>0</v>
+      </c>
+      <c r="J25" s="64">
+        <v>0</v>
+      </c>
+      <c r="K25" s="64">
+        <v>0</v>
+      </c>
+      <c r="L25" s="64">
+        <v>8.76</v>
+      </c>
+      <c r="M25" s="68"/>
+      <c r="N25" s="68"/>
+      <c r="O25" s="64"/>
+      <c r="P25" s="64"/>
+      <c r="Q25" s="64"/>
+      <c r="R25" s="68"/>
+      <c r="S25" s="43"/>
+      <c r="V25" s="60" t="s">
+        <v>69</v>
+      </c>
+      <c r="W25" s="60"/>
+      <c r="X25" s="61" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y25" s="62" t="s">
+        <v>146</v>
+      </c>
+      <c r="Z25" s="45" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA25" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB25" s="46" t="s">
+        <v>88</v>
+      </c>
+      <c r="AI25"/>
+      <c r="AJ25"/>
+      <c r="AK25" s="45"/>
+      <c r="AL25" s="45"/>
+      <c r="AM25" s="45"/>
+      <c r="AN25" s="45"/>
+      <c r="AO25" s="45"/>
+      <c r="AP25" s="45"/>
+      <c r="AQ25" s="45"/>
+      <c r="AR25" s="45"/>
+      <c r="AS25" s="45"/>
+      <c r="AT25" s="45"/>
+      <c r="AU25" s="45"/>
+      <c r="AV25" s="45"/>
+      <c r="AW25" s="45"/>
+    </row>
+    <row r="26" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="85" t="str">
+        <f>X24</f>
+        <v>DECELC</v>
+      </c>
+      <c r="C26" s="50" t="s">
+        <v>139</v>
+      </c>
+      <c r="D26" s="50" t="s">
+        <v>69</v>
+      </c>
+      <c r="E26" s="43">
+        <v>2030</v>
+      </c>
+      <c r="F26" s="46">
+        <v>1</v>
+      </c>
+      <c r="G26" s="46">
+        <v>1</v>
+      </c>
+      <c r="H26" s="43">
+        <v>100</v>
+      </c>
+      <c r="I26" s="64">
+        <v>0</v>
+      </c>
+      <c r="J26" s="45">
+        <v>0</v>
+      </c>
+      <c r="K26" s="46">
+        <v>0</v>
+      </c>
+      <c r="L26" s="64">
+        <v>8.76</v>
+      </c>
+      <c r="M26" s="68"/>
+      <c r="N26" s="68"/>
+      <c r="O26" s="64"/>
+      <c r="P26" s="64"/>
+      <c r="Q26" s="64"/>
+      <c r="R26" s="68"/>
+      <c r="S26" s="43"/>
+      <c r="V26" s="60"/>
+      <c r="W26" s="60"/>
+      <c r="X26" s="61"/>
+      <c r="Y26" s="62"/>
+      <c r="Z26" s="45"/>
+      <c r="AA26" s="45"/>
+      <c r="AI26"/>
+      <c r="AJ26"/>
+      <c r="AK26" s="45"/>
+      <c r="AL26" s="45"/>
+      <c r="AM26" s="45"/>
+      <c r="AN26" s="45"/>
+      <c r="AO26" s="45"/>
+      <c r="AP26" s="45"/>
+      <c r="AQ26" s="45"/>
+      <c r="AR26" s="45"/>
+      <c r="AS26" s="45"/>
+      <c r="AT26" s="45"/>
+      <c r="AU26" s="45"/>
+      <c r="AV26" s="45"/>
+      <c r="AW26" s="45"/>
+    </row>
+    <row r="27" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="85" t="str">
+        <f>X24</f>
+        <v>DECELC</v>
+      </c>
+      <c r="C27" s="50" t="s">
+        <v>140</v>
+      </c>
+      <c r="D27" s="50" t="s">
+        <v>69</v>
+      </c>
+      <c r="E27" s="43">
+        <v>2030</v>
+      </c>
+      <c r="F27" s="46">
+        <v>1</v>
+      </c>
+      <c r="G27" s="46">
+        <v>1</v>
+      </c>
+      <c r="H27" s="43">
+        <v>100</v>
+      </c>
+      <c r="I27" s="64">
+        <v>0</v>
+      </c>
+      <c r="J27" s="45">
+        <v>0</v>
+      </c>
+      <c r="K27" s="46">
+        <v>0</v>
+      </c>
+      <c r="L27" s="64">
+        <v>8.76</v>
+      </c>
+      <c r="M27" s="68"/>
+      <c r="N27" s="68"/>
+      <c r="O27" s="64"/>
+      <c r="P27" s="64"/>
+      <c r="Q27" s="64"/>
+      <c r="R27" s="68"/>
+      <c r="S27" s="43"/>
+      <c r="V27" s="60"/>
+      <c r="W27" s="60"/>
+      <c r="X27" s="61"/>
+      <c r="Y27" s="62"/>
+      <c r="Z27" s="45"/>
+      <c r="AA27" s="45"/>
+      <c r="AI27"/>
+      <c r="AJ27"/>
+      <c r="AK27" s="45"/>
+      <c r="AL27" s="45"/>
+      <c r="AM27" s="45"/>
+      <c r="AN27" s="45"/>
+      <c r="AO27" s="45"/>
+      <c r="AP27" s="45"/>
+      <c r="AQ27" s="45"/>
+      <c r="AR27" s="45"/>
+      <c r="AS27" s="45"/>
+      <c r="AT27" s="45"/>
+      <c r="AU27" s="45"/>
+      <c r="AV27" s="45"/>
+      <c r="AW27" s="45"/>
+    </row>
+    <row r="28" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="50" t="str">
+        <f>X25</f>
+        <v>BIOPOWER</v>
+      </c>
+      <c r="C28" s="50" t="s">
+        <v>68</v>
+      </c>
+      <c r="D28" s="50" t="s">
+        <v>145</v>
+      </c>
+      <c r="E28" s="43">
+        <v>2030</v>
+      </c>
+      <c r="F28" s="46">
+        <v>0.35</v>
+      </c>
+      <c r="G28" s="46">
+        <v>0.98</v>
+      </c>
+      <c r="H28" s="43">
+        <v>20</v>
+      </c>
+      <c r="I28" s="86">
+        <v>3242</v>
+      </c>
+      <c r="J28" s="64">
+        <v>129.68</v>
+      </c>
+      <c r="K28" s="64">
+        <v>0</v>
+      </c>
+      <c r="L28" s="64">
+        <v>8.76</v>
+      </c>
+      <c r="M28" s="68"/>
+      <c r="N28" s="68"/>
+      <c r="O28" s="64"/>
+      <c r="P28" s="64"/>
+      <c r="Q28" s="64"/>
+      <c r="R28" s="68"/>
+      <c r="S28" s="43"/>
+      <c r="V28" s="45"/>
+      <c r="W28" s="45"/>
+      <c r="X28" s="45"/>
+      <c r="Y28" s="45"/>
+      <c r="Z28" s="45"/>
+      <c r="AA28" s="45"/>
+      <c r="AC28" s="45"/>
+      <c r="AD28" s="45"/>
+      <c r="AI28"/>
+      <c r="AJ28"/>
+      <c r="AK28" s="45"/>
+      <c r="AL28" s="45"/>
+      <c r="AM28" s="45"/>
+      <c r="AN28" s="45"/>
+      <c r="AO28" s="45"/>
+      <c r="AP28" s="45"/>
+      <c r="AQ28" s="45"/>
+      <c r="AR28" s="45"/>
+      <c r="AS28" s="45"/>
+      <c r="AT28" s="45"/>
+      <c r="AU28" s="45"/>
+      <c r="AV28" s="45"/>
+      <c r="AW28" s="45"/>
+    </row>
+    <row r="29" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="50" t="s">
+        <v>136</v>
+      </c>
+      <c r="C29" s="45" t="s">
+        <v>145</v>
+      </c>
+      <c r="D29" s="50" t="s">
+        <v>69</v>
+      </c>
+      <c r="E29" s="43">
+        <v>2030</v>
+      </c>
+      <c r="F29" s="83">
+        <v>1</v>
+      </c>
+      <c r="G29" s="64">
+        <v>1</v>
+      </c>
+      <c r="H29" s="46">
+        <v>100</v>
+      </c>
+      <c r="I29" s="46">
+        <v>0</v>
+      </c>
+      <c r="J29" s="46">
+        <v>0</v>
+      </c>
+      <c r="K29" s="46">
+        <v>0</v>
+      </c>
+      <c r="L29" s="46">
+        <v>0</v>
+      </c>
+      <c r="M29" s="68"/>
+      <c r="N29" s="68"/>
+      <c r="O29" s="64"/>
+      <c r="P29" s="64"/>
+      <c r="Q29" s="64"/>
+      <c r="R29" s="68"/>
+      <c r="S29" s="43"/>
+      <c r="AI29"/>
+      <c r="AJ29"/>
+      <c r="AK29" s="45"/>
+      <c r="AL29" s="45"/>
+      <c r="AM29" s="45"/>
+      <c r="AN29" s="45"/>
+      <c r="AO29" s="45"/>
+      <c r="AP29" s="45"/>
+      <c r="AQ29" s="45"/>
+      <c r="AR29" s="45"/>
+      <c r="AS29" s="45"/>
+      <c r="AT29" s="45"/>
+      <c r="AU29" s="45"/>
+      <c r="AV29" s="45"/>
+      <c r="AW29" s="45"/>
+    </row>
+    <row r="30" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="45"/>
+      <c r="C30" s="50"/>
+      <c r="D30" s="84"/>
+      <c r="E30" s="43"/>
+      <c r="F30" s="64"/>
+      <c r="G30" s="64"/>
+      <c r="H30" s="43"/>
+      <c r="I30" s="64"/>
+      <c r="J30" s="64"/>
+      <c r="K30" s="64"/>
+      <c r="L30" s="64"/>
+      <c r="M30" s="68"/>
+      <c r="N30" s="68"/>
+      <c r="O30" s="64"/>
+      <c r="P30" s="64"/>
+      <c r="Q30" s="64"/>
+      <c r="R30" s="68"/>
+      <c r="S30" s="43"/>
+      <c r="V30" s="45"/>
+      <c r="W30" s="45"/>
+      <c r="X30" s="45"/>
+      <c r="Y30" s="45"/>
+      <c r="Z30" s="45"/>
+      <c r="AA30" s="45"/>
+      <c r="AB30" s="45"/>
+      <c r="AC30" s="45"/>
+      <c r="AD30" s="45"/>
       <c r="AI30"/>
       <c r="AJ30"/>
-      <c r="AK30" s="46"/>
-      <c r="AL30" s="46"/>
-      <c r="AM30" s="46"/>
-      <c r="AN30" s="46"/>
-      <c r="AO30" s="46"/>
-      <c r="AP30" s="46"/>
-      <c r="AQ30" s="46"/>
-      <c r="AR30" s="46"/>
-      <c r="AS30" s="46"/>
-      <c r="AT30" s="46"/>
-      <c r="AU30" s="46"/>
-      <c r="AV30" s="46"/>
-      <c r="AW30" s="46"/>
-    </row>
-    <row r="31" spans="2:51" s="47" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="51" t="str">
-        <f>X29</f>
-        <v>GASBoiler</v>
-      </c>
-      <c r="C31" s="46" t="str">
-        <f>PRI_Sector_Fuels!P6</f>
-        <v>MANGASMIN</v>
-      </c>
-      <c r="D31" s="51" t="s">
-        <v>113</v>
-      </c>
-      <c r="E31" s="44">
-        <v>2030</v>
-      </c>
-      <c r="F31" s="65">
-        <v>0.75</v>
-      </c>
-      <c r="G31" s="65">
-        <v>0.99</v>
-      </c>
-      <c r="H31" s="44">
-        <v>25</v>
-      </c>
-      <c r="I31" s="65">
-        <v>61.4</v>
-      </c>
-      <c r="J31" s="65">
-        <v>2.57</v>
-      </c>
-      <c r="K31" s="65">
-        <v>1.35</v>
-      </c>
-      <c r="L31" s="65">
-        <v>8.76</v>
-      </c>
-      <c r="M31" s="44"/>
-      <c r="N31" s="69"/>
-      <c r="O31" s="44"/>
-      <c r="P31" s="44"/>
-      <c r="Q31" s="44"/>
-      <c r="R31" s="44"/>
-      <c r="S31" s="44"/>
-      <c r="V31" s="61" t="s">
-        <v>135</v>
-      </c>
-      <c r="W31" s="61"/>
-      <c r="X31" s="62" t="s">
-        <v>65</v>
-      </c>
-      <c r="Y31" s="63" t="s">
-        <v>103</v>
-      </c>
-      <c r="Z31" s="46" t="s">
-        <v>58</v>
-      </c>
-      <c r="AA31" s="46" t="s">
-        <v>87</v>
-      </c>
-      <c r="AB31" s="47" t="s">
-        <v>88</v>
-      </c>
+      <c r="AK30" s="77"/>
+      <c r="AL30" s="77"/>
+      <c r="AM30" s="77"/>
+      <c r="AN30" s="77"/>
+      <c r="AO30" s="77"/>
+      <c r="AP30" s="77"/>
+      <c r="AQ30" s="77"/>
+      <c r="AR30" s="77"/>
+      <c r="AS30" s="77"/>
+      <c r="AT30" s="77"/>
+      <c r="AU30" s="77"/>
+      <c r="AV30" s="77"/>
+      <c r="AW30" s="77"/>
+    </row>
+    <row r="31" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="45"/>
+      <c r="C31" s="50"/>
+      <c r="D31" s="84"/>
+      <c r="E31" s="43"/>
+      <c r="F31" s="64"/>
+      <c r="G31" s="64"/>
+      <c r="H31" s="43"/>
+      <c r="I31" s="64"/>
+      <c r="J31" s="64"/>
+      <c r="K31" s="64"/>
+      <c r="L31" s="64"/>
+      <c r="M31" s="68"/>
+      <c r="N31" s="68"/>
+      <c r="O31" s="64"/>
+      <c r="P31" s="64"/>
+      <c r="Q31" s="64"/>
+      <c r="R31" s="68"/>
+      <c r="S31" s="43"/>
+      <c r="V31" s="45"/>
+      <c r="W31" s="45"/>
+      <c r="X31" s="45"/>
+      <c r="Y31" s="45"/>
+      <c r="Z31" s="45"/>
+      <c r="AA31" s="45"/>
+      <c r="AB31" s="45"/>
+      <c r="AC31" s="45"/>
+      <c r="AD31" s="45"/>
       <c r="AI31"/>
       <c r="AJ31"/>
-      <c r="AK31" s="79"/>
-      <c r="AL31" s="79"/>
-      <c r="AM31" s="79"/>
-      <c r="AN31" s="79"/>
-      <c r="AO31" s="79"/>
-      <c r="AP31" s="79"/>
-      <c r="AQ31" s="79"/>
-      <c r="AR31" s="79"/>
-      <c r="AS31" s="79"/>
-      <c r="AT31" s="79"/>
-      <c r="AU31" s="79"/>
-      <c r="AV31" s="79"/>
-      <c r="AW31" s="79"/>
-    </row>
-    <row r="32" spans="2:51" s="47" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="51" t="str">
-        <f>X32</f>
-        <v>WNDTRBN</v>
-      </c>
-      <c r="C32" s="46" t="str">
-        <f>PRI_Sector_Fuels!D28</f>
-        <v>WIND</v>
-      </c>
-      <c r="D32" s="51" t="s">
-        <v>139</v>
-      </c>
-      <c r="E32" s="44">
-        <v>2030</v>
-      </c>
-      <c r="F32" s="86">
-        <v>1</v>
-      </c>
-      <c r="G32" s="65">
-        <v>0.97</v>
-      </c>
-      <c r="H32" s="44">
-        <v>25</v>
-      </c>
-      <c r="I32" s="65">
-        <v>1041</v>
-      </c>
-      <c r="J32" s="65">
-        <v>38</v>
-      </c>
-      <c r="K32" s="65">
-        <v>0</v>
-      </c>
-      <c r="L32" s="65">
-        <v>8.76</v>
-      </c>
-      <c r="M32" s="69"/>
-      <c r="N32" s="69"/>
-      <c r="O32" s="65"/>
-      <c r="P32" s="65"/>
-      <c r="Q32" s="65"/>
-      <c r="R32" s="69"/>
-      <c r="S32" s="44">
-        <v>0.2</v>
-      </c>
-      <c r="V32" s="61" t="s">
-        <v>69</v>
-      </c>
-      <c r="W32" s="61"/>
-      <c r="X32" s="62" t="s">
-        <v>90</v>
-      </c>
-      <c r="Y32" s="63" t="s">
-        <v>93</v>
-      </c>
-      <c r="Z32" s="46" t="s">
-        <v>58</v>
-      </c>
-      <c r="AA32" s="46" t="s">
-        <v>87</v>
-      </c>
-      <c r="AB32" s="47" t="s">
-        <v>88</v>
-      </c>
+      <c r="AK31" s="77"/>
+      <c r="AL31" s="77"/>
+      <c r="AM31" s="77"/>
+      <c r="AN31" s="77"/>
+      <c r="AO31" s="77"/>
+      <c r="AP31" s="77"/>
+      <c r="AQ31" s="77"/>
+      <c r="AR31" s="77"/>
+      <c r="AS31" s="77"/>
+      <c r="AT31" s="77"/>
+      <c r="AU31" s="77"/>
+      <c r="AV31" s="77"/>
+      <c r="AW31" s="77"/>
+    </row>
+    <row r="32" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="45"/>
+      <c r="C32" s="50"/>
+      <c r="D32" s="84"/>
+      <c r="E32" s="43"/>
+      <c r="F32" s="64"/>
+      <c r="G32" s="64"/>
+      <c r="H32" s="43"/>
+      <c r="I32" s="64"/>
+      <c r="J32" s="64"/>
+      <c r="K32" s="64"/>
+      <c r="L32" s="64"/>
+      <c r="M32" s="68"/>
+      <c r="N32" s="68"/>
+      <c r="O32" s="64"/>
+      <c r="P32" s="64"/>
+      <c r="Q32" s="64"/>
+      <c r="R32" s="68"/>
+      <c r="S32" s="43"/>
+      <c r="V32" s="45"/>
+      <c r="W32" s="45"/>
+      <c r="X32" s="45"/>
+      <c r="Y32" s="45"/>
+      <c r="Z32" s="45"/>
+      <c r="AA32" s="45"/>
+      <c r="AB32" s="45"/>
+      <c r="AC32" s="45"/>
+      <c r="AD32" s="45"/>
       <c r="AI32"/>
       <c r="AJ32"/>
-      <c r="AK32" s="79"/>
-      <c r="AL32" s="79"/>
-      <c r="AM32" s="79"/>
-      <c r="AN32" s="79"/>
-      <c r="AO32" s="79"/>
-      <c r="AP32" s="79"/>
-      <c r="AQ32" s="79"/>
-      <c r="AR32" s="79"/>
-      <c r="AS32" s="79"/>
-      <c r="AT32" s="79"/>
-      <c r="AU32" s="79"/>
-      <c r="AV32" s="79"/>
-      <c r="AW32" s="79"/>
-    </row>
-    <row r="33" spans="2:49" s="47" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="51" t="str">
-        <f>X33</f>
-        <v>SOLPV</v>
-      </c>
-      <c r="C33" s="46" t="str">
-        <f>PRI_Sector_Fuels!D29</f>
-        <v>SOLAR</v>
-      </c>
-      <c r="D33" s="51" t="s">
-        <v>140</v>
-      </c>
-      <c r="E33" s="44">
-        <v>2030</v>
-      </c>
-      <c r="F33" s="86">
-        <v>1</v>
-      </c>
-      <c r="G33" s="65">
-        <v>0.99</v>
-      </c>
-      <c r="H33" s="44">
-        <v>25</v>
-      </c>
-      <c r="I33" s="65">
-        <v>691</v>
-      </c>
-      <c r="J33" s="65">
-        <v>6.99</v>
-      </c>
-      <c r="K33" s="65">
-        <v>0</v>
-      </c>
-      <c r="L33" s="65">
-        <v>8.76</v>
-      </c>
-      <c r="M33" s="69"/>
-      <c r="N33" s="69"/>
-      <c r="O33" s="65"/>
-      <c r="P33" s="65"/>
-      <c r="Q33" s="65"/>
-      <c r="R33" s="69"/>
-      <c r="S33" s="44">
-        <v>0.3</v>
-      </c>
-      <c r="V33" s="61" t="s">
-        <v>69</v>
-      </c>
-      <c r="W33" s="61"/>
-      <c r="X33" s="62" t="s">
-        <v>91</v>
-      </c>
-      <c r="Y33" s="63" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z33" s="46" t="s">
-        <v>58</v>
-      </c>
-      <c r="AA33" s="46" t="s">
-        <v>87</v>
-      </c>
-      <c r="AB33" s="47" t="s">
-        <v>88</v>
-      </c>
+      <c r="AK32" s="45"/>
+      <c r="AL32" s="45"/>
+      <c r="AM32" s="45"/>
+      <c r="AN32" s="45"/>
+      <c r="AO32" s="45"/>
+      <c r="AP32" s="45"/>
+      <c r="AQ32" s="45"/>
+      <c r="AR32" s="45"/>
+      <c r="AS32" s="45"/>
+      <c r="AT32" s="45"/>
+      <c r="AU32" s="45"/>
+      <c r="AV32" s="45"/>
+      <c r="AW32" s="45"/>
+    </row>
+    <row r="33" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="50"/>
+      <c r="C33" s="50"/>
+      <c r="D33" s="50"/>
+      <c r="E33" s="43"/>
+      <c r="F33" s="64"/>
+      <c r="G33" s="64"/>
+      <c r="H33" s="43"/>
+      <c r="I33" s="64"/>
+      <c r="J33" s="64"/>
+      <c r="K33" s="64"/>
+      <c r="L33" s="64"/>
+      <c r="M33" s="68"/>
+      <c r="N33" s="68"/>
+      <c r="O33" s="64"/>
+      <c r="P33" s="64"/>
+      <c r="Q33" s="64"/>
+      <c r="R33" s="68"/>
+      <c r="S33" s="43"/>
+      <c r="V33" s="45"/>
+      <c r="W33" s="45"/>
+      <c r="X33" s="45"/>
+      <c r="Y33" s="45"/>
+      <c r="Z33" s="45"/>
+      <c r="AA33" s="45"/>
+      <c r="AB33" s="45"/>
+      <c r="AC33" s="45"/>
+      <c r="AD33" s="45"/>
       <c r="AI33"/>
       <c r="AJ33"/>
-      <c r="AK33" s="46"/>
-      <c r="AL33" s="46"/>
-      <c r="AM33" s="46"/>
-      <c r="AN33" s="46"/>
-      <c r="AO33" s="46"/>
-      <c r="AP33" s="46"/>
-      <c r="AQ33" s="46"/>
-      <c r="AR33" s="46"/>
-      <c r="AS33" s="46"/>
-      <c r="AT33" s="46"/>
-      <c r="AU33" s="46"/>
-      <c r="AV33" s="46"/>
-      <c r="AW33" s="46"/>
-    </row>
-    <row r="34" spans="2:49" s="47" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="51" t="str">
-        <f>X31</f>
-        <v>CSP</v>
-      </c>
-      <c r="C34" s="46" t="str">
-        <f>PRI_Sector_Fuels!D29</f>
-        <v>SOLAR</v>
-      </c>
-      <c r="D34" s="51" t="s">
-        <v>113</v>
-      </c>
-      <c r="E34" s="44">
-        <v>2030</v>
-      </c>
-      <c r="F34" s="86">
-        <v>1</v>
-      </c>
-      <c r="G34" s="65">
-        <v>1</v>
-      </c>
-      <c r="H34" s="44">
-        <v>25</v>
-      </c>
-      <c r="I34" s="65">
-        <v>3677</v>
-      </c>
-      <c r="J34" s="65">
-        <v>0</v>
-      </c>
-      <c r="K34" s="65">
-        <v>14</v>
-      </c>
-      <c r="L34" s="65">
-        <v>8.76</v>
-      </c>
-      <c r="M34" s="69"/>
-      <c r="N34" s="69"/>
-      <c r="O34" s="65"/>
-      <c r="P34" s="65"/>
-      <c r="Q34" s="65"/>
-      <c r="R34" s="69"/>
-      <c r="S34" s="44"/>
-      <c r="V34" s="61" t="s">
-        <v>69</v>
-      </c>
-      <c r="W34" s="61"/>
-      <c r="X34" s="62" t="s">
-        <v>136</v>
-      </c>
-      <c r="Y34" s="63" t="s">
-        <v>143</v>
-      </c>
-      <c r="Z34" s="46" t="s">
-        <v>58</v>
-      </c>
-      <c r="AA34" s="46" t="s">
-        <v>87</v>
-      </c>
-      <c r="AB34" s="47" t="s">
-        <v>88</v>
-      </c>
+      <c r="AK33" s="39"/>
+      <c r="AL33" s="39"/>
+      <c r="AM33" s="45"/>
+      <c r="AN33" s="45"/>
+      <c r="AO33" s="45"/>
+      <c r="AQ33"/>
+      <c r="AR33"/>
+      <c r="AS33" s="39"/>
+      <c r="AT33" s="39"/>
+      <c r="AU33" s="45"/>
+      <c r="AV33" s="45"/>
+    </row>
+    <row r="34" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="50"/>
+      <c r="C34" s="50"/>
+      <c r="D34" s="50"/>
+      <c r="E34" s="43"/>
+      <c r="H34" s="43"/>
+      <c r="I34" s="64"/>
+      <c r="J34" s="45"/>
+      <c r="L34" s="64"/>
+      <c r="M34" s="68"/>
+      <c r="N34" s="68"/>
+      <c r="O34" s="64"/>
+      <c r="P34" s="64"/>
+      <c r="Q34" s="64"/>
+      <c r="R34" s="68"/>
+      <c r="S34" s="43"/>
+      <c r="V34" s="45"/>
+      <c r="W34" s="45"/>
+      <c r="X34" s="45"/>
+      <c r="Y34" s="45"/>
+      <c r="Z34" s="45"/>
+      <c r="AA34" s="45"/>
+      <c r="AB34" s="45"/>
+      <c r="AC34" s="45"/>
+      <c r="AD34" s="45"/>
       <c r="AI34"/>
       <c r="AJ34"/>
-      <c r="AK34" s="46"/>
-      <c r="AL34" s="46"/>
-      <c r="AM34" s="46"/>
-      <c r="AN34" s="46"/>
-      <c r="AO34" s="46"/>
-      <c r="AP34" s="46"/>
-      <c r="AQ34" s="46"/>
-      <c r="AR34" s="46"/>
-      <c r="AS34" s="46"/>
-      <c r="AT34" s="46"/>
-      <c r="AU34" s="46"/>
-      <c r="AV34" s="46"/>
-      <c r="AW34" s="46"/>
-    </row>
-    <row r="35" spans="2:49" s="47" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="51" t="str">
-        <f>X29</f>
-        <v>GASBoiler</v>
-      </c>
-      <c r="C35" s="46"/>
-      <c r="D35" s="51" t="s">
-        <v>112</v>
-      </c>
-      <c r="E35" s="44">
-        <v>2030</v>
-      </c>
-      <c r="F35" s="86">
-        <v>1</v>
-      </c>
-      <c r="G35" s="65">
-        <v>1</v>
-      </c>
-      <c r="H35" s="44">
-        <v>25</v>
-      </c>
-      <c r="I35" s="65">
-        <v>0</v>
-      </c>
-      <c r="J35" s="65">
-        <v>0</v>
-      </c>
-      <c r="K35" s="65">
-        <v>0</v>
-      </c>
-      <c r="L35" s="65">
-        <v>8.76</v>
-      </c>
-      <c r="M35" s="69"/>
-      <c r="N35" s="69"/>
-      <c r="O35" s="65"/>
-      <c r="P35" s="65"/>
-      <c r="Q35" s="65"/>
-      <c r="R35" s="69"/>
-      <c r="S35" s="44"/>
-      <c r="V35" s="61" t="s">
-        <v>69</v>
-      </c>
-      <c r="W35" s="61"/>
-      <c r="X35" s="62" t="s">
-        <v>147</v>
-      </c>
-      <c r="Y35" s="63" t="s">
-        <v>146</v>
-      </c>
-      <c r="Z35" s="46" t="s">
-        <v>58</v>
-      </c>
-      <c r="AA35" s="46" t="s">
-        <v>87</v>
-      </c>
-      <c r="AB35" s="47" t="s">
-        <v>88</v>
-      </c>
+      <c r="AK34" s="39"/>
+      <c r="AL34" s="39"/>
+      <c r="AM34" s="45"/>
+      <c r="AN34" s="45"/>
+      <c r="AO34" s="45"/>
+      <c r="AQ34"/>
+      <c r="AR34"/>
+      <c r="AS34" s="39"/>
+      <c r="AT34" s="39"/>
+      <c r="AU34" s="45"/>
+      <c r="AV34" s="45"/>
+    </row>
+    <row r="35" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="50"/>
+      <c r="C35" s="50"/>
+      <c r="D35" s="50"/>
+      <c r="E35" s="43"/>
+      <c r="H35" s="43"/>
+      <c r="I35" s="64"/>
+      <c r="J35" s="45"/>
+      <c r="L35" s="64"/>
+      <c r="M35" s="43"/>
+      <c r="N35" s="68"/>
+      <c r="O35" s="43"/>
+      <c r="P35" s="43"/>
+      <c r="Q35" s="43"/>
+      <c r="R35" s="43"/>
+      <c r="S35" s="43"/>
+      <c r="V35" s="38"/>
+      <c r="W35" s="38"/>
+      <c r="X35" s="39"/>
+      <c r="Y35" s="40"/>
+      <c r="Z35" s="38"/>
+      <c r="AA35" s="38"/>
+      <c r="AB35" s="38"/>
+      <c r="AC35" s="45"/>
+      <c r="AD35" s="45"/>
       <c r="AI35"/>
       <c r="AJ35"/>
-      <c r="AK35" s="46"/>
-      <c r="AL35" s="46"/>
-      <c r="AM35" s="46"/>
-      <c r="AN35" s="46"/>
-      <c r="AO35" s="46"/>
-      <c r="AP35" s="46"/>
-      <c r="AQ35" s="46"/>
-      <c r="AR35" s="46"/>
-      <c r="AS35" s="46"/>
-      <c r="AT35" s="46"/>
-      <c r="AU35" s="46"/>
-      <c r="AV35" s="46"/>
-      <c r="AW35" s="46"/>
-    </row>
-    <row r="36" spans="2:49" s="47" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="88" t="str">
-        <f>X34</f>
-        <v>DECELC</v>
-      </c>
-      <c r="C36" s="51" t="s">
-        <v>139</v>
-      </c>
-      <c r="D36" s="51" t="s">
-        <v>69</v>
-      </c>
-      <c r="E36" s="44">
-        <v>2030</v>
-      </c>
-      <c r="F36" s="47">
-        <v>1</v>
-      </c>
-      <c r="G36" s="47">
-        <v>1</v>
-      </c>
-      <c r="H36" s="44">
-        <v>100</v>
-      </c>
-      <c r="I36" s="65">
-        <v>0</v>
-      </c>
-      <c r="J36" s="46">
-        <v>0</v>
-      </c>
-      <c r="K36" s="47">
-        <v>0</v>
-      </c>
-      <c r="L36" s="65">
-        <v>8.76</v>
-      </c>
-      <c r="M36" s="69"/>
-      <c r="N36" s="69"/>
-      <c r="O36" s="65"/>
-      <c r="P36" s="65"/>
-      <c r="Q36" s="65"/>
-      <c r="R36" s="69"/>
-      <c r="S36" s="44"/>
-      <c r="V36" s="61"/>
-      <c r="W36" s="61"/>
-      <c r="X36" s="62"/>
-      <c r="Y36" s="63"/>
-      <c r="Z36" s="46"/>
-      <c r="AA36" s="46"/>
+      <c r="AK35" s="39"/>
+      <c r="AL35" s="39"/>
+      <c r="AM35" s="45"/>
+      <c r="AN35" s="45"/>
+      <c r="AO35" s="45"/>
+      <c r="AQ35"/>
+      <c r="AR35"/>
+      <c r="AS35" s="39"/>
+      <c r="AT35" s="39"/>
+      <c r="AU35" s="45"/>
+      <c r="AV35" s="45"/>
+    </row>
+    <row r="36" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="45"/>
+      <c r="C36" s="50"/>
+      <c r="D36" s="50"/>
+      <c r="E36" s="64"/>
+      <c r="F36" s="65"/>
+      <c r="K36" s="45"/>
+      <c r="N36" s="65"/>
+      <c r="V36" s="38"/>
+      <c r="W36" s="38"/>
+      <c r="X36" s="39"/>
+      <c r="Y36" s="40"/>
+      <c r="Z36" s="38"/>
+      <c r="AA36" s="38"/>
+      <c r="AB36" s="38"/>
+      <c r="AC36" s="45"/>
+      <c r="AD36" s="45"/>
       <c r="AI36"/>
       <c r="AJ36"/>
-      <c r="AK36" s="46"/>
-      <c r="AL36" s="46"/>
-      <c r="AM36" s="46"/>
-      <c r="AN36" s="46"/>
-      <c r="AO36" s="46"/>
-      <c r="AP36" s="46"/>
-      <c r="AQ36" s="46"/>
-      <c r="AR36" s="46"/>
-      <c r="AS36" s="46"/>
-      <c r="AT36" s="46"/>
-      <c r="AU36" s="46"/>
-      <c r="AV36" s="46"/>
-      <c r="AW36" s="46"/>
-    </row>
-    <row r="37" spans="2:49" s="47" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="88" t="str">
-        <f>X34</f>
-        <v>DECELC</v>
-      </c>
-      <c r="C37" s="51" t="s">
-        <v>140</v>
-      </c>
-      <c r="D37" s="51" t="s">
-        <v>69</v>
-      </c>
-      <c r="E37" s="44">
-        <v>2030</v>
-      </c>
-      <c r="F37" s="47">
-        <v>1</v>
-      </c>
-      <c r="G37" s="47">
-        <v>1</v>
-      </c>
-      <c r="H37" s="44">
-        <v>100</v>
-      </c>
-      <c r="I37" s="65">
-        <v>0</v>
-      </c>
-      <c r="J37" s="46">
-        <v>0</v>
-      </c>
-      <c r="K37" s="47">
-        <v>0</v>
-      </c>
-      <c r="L37" s="65">
-        <v>8.76</v>
-      </c>
-      <c r="M37" s="69"/>
-      <c r="N37" s="69"/>
-      <c r="O37" s="65"/>
-      <c r="P37" s="65"/>
-      <c r="Q37" s="65"/>
-      <c r="R37" s="69"/>
-      <c r="S37" s="44"/>
-      <c r="V37" s="61"/>
-      <c r="W37" s="61"/>
-      <c r="X37" s="62"/>
-      <c r="Y37" s="63"/>
-      <c r="Z37" s="46"/>
-      <c r="AA37" s="46"/>
+      <c r="AK36" s="39"/>
+      <c r="AL36" s="39"/>
+      <c r="AM36" s="45"/>
+      <c r="AN36" s="45"/>
+      <c r="AO36" s="45"/>
+      <c r="AQ36"/>
+      <c r="AR36"/>
+      <c r="AS36" s="39"/>
+      <c r="AT36" s="39"/>
+      <c r="AU36" s="45"/>
+      <c r="AV36" s="45"/>
+    </row>
+    <row r="37" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="50"/>
+      <c r="C37" s="50"/>
+      <c r="D37" s="50"/>
+      <c r="E37" s="64"/>
+      <c r="F37" s="65"/>
+      <c r="J37" s="66"/>
+      <c r="K37" s="45"/>
+      <c r="N37" s="65"/>
+      <c r="V37" s="45"/>
+      <c r="W37" s="45"/>
+      <c r="X37" s="45"/>
+      <c r="Y37" s="45"/>
+      <c r="Z37" s="50"/>
+      <c r="AA37" s="50"/>
+      <c r="AB37" s="63"/>
+      <c r="AC37" s="45"/>
+      <c r="AD37" s="45"/>
       <c r="AI37"/>
       <c r="AJ37"/>
-      <c r="AK37" s="46"/>
-      <c r="AL37" s="46"/>
-      <c r="AM37" s="46"/>
-      <c r="AN37" s="46"/>
-      <c r="AO37" s="46"/>
-      <c r="AP37" s="46"/>
-      <c r="AQ37" s="46"/>
-      <c r="AR37" s="46"/>
-      <c r="AS37" s="46"/>
-      <c r="AT37" s="46"/>
-      <c r="AU37" s="46"/>
-      <c r="AV37" s="46"/>
-      <c r="AW37" s="46"/>
-    </row>
-    <row r="38" spans="2:49" s="47" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="51" t="str">
-        <f>X35</f>
-        <v>BIOPOWER</v>
-      </c>
-      <c r="C38" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="D38" s="51" t="s">
-        <v>145</v>
-      </c>
-      <c r="E38" s="44">
-        <v>2030</v>
-      </c>
-      <c r="F38" s="47">
-        <v>0.35</v>
-      </c>
-      <c r="G38" s="47">
-        <v>0.98</v>
-      </c>
-      <c r="H38" s="44">
-        <v>20</v>
-      </c>
-      <c r="I38" s="89">
-        <v>3242</v>
-      </c>
-      <c r="J38" s="65">
-        <v>129.68</v>
-      </c>
-      <c r="K38" s="65">
-        <v>0</v>
-      </c>
-      <c r="L38" s="65">
-        <v>8.76</v>
-      </c>
-      <c r="M38" s="69"/>
-      <c r="N38" s="69"/>
-      <c r="O38" s="65"/>
-      <c r="P38" s="65"/>
-      <c r="Q38" s="65"/>
-      <c r="R38" s="69"/>
-      <c r="S38" s="44"/>
-      <c r="V38" s="46"/>
-      <c r="W38" s="46"/>
-      <c r="X38" s="46"/>
-      <c r="Y38" s="46"/>
-      <c r="Z38" s="46"/>
-      <c r="AA38" s="46"/>
-      <c r="AC38" s="46"/>
-      <c r="AD38" s="46"/>
+      <c r="AK37" s="39"/>
+      <c r="AL37" s="39"/>
+      <c r="AM37" s="45"/>
+      <c r="AN37" s="45"/>
+      <c r="AO37" s="45"/>
+      <c r="AQ37"/>
+      <c r="AR37"/>
+      <c r="AS37" s="39"/>
+      <c r="AT37" s="39"/>
+      <c r="AU37" s="45"/>
+      <c r="AV37" s="45"/>
+    </row>
+    <row r="38" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="50"/>
+      <c r="C38" s="45"/>
+      <c r="D38" s="50"/>
+      <c r="E38" s="64"/>
+      <c r="F38" s="67"/>
+      <c r="G38" s="45"/>
+      <c r="H38" s="45"/>
+      <c r="I38" s="45"/>
+      <c r="J38" s="68"/>
+      <c r="K38" s="45"/>
+      <c r="V38" s="45"/>
+      <c r="X38" s="45"/>
+      <c r="Z38" s="54"/>
+      <c r="AA38" s="54"/>
+      <c r="AB38" s="45"/>
+      <c r="AC38" s="45"/>
+      <c r="AD38" s="45"/>
       <c r="AI38"/>
       <c r="AJ38"/>
-      <c r="AK38" s="46"/>
-      <c r="AL38" s="46"/>
-      <c r="AM38" s="46"/>
-      <c r="AN38" s="46"/>
-      <c r="AO38" s="46"/>
-      <c r="AP38" s="46"/>
-      <c r="AQ38" s="46"/>
-      <c r="AR38" s="46"/>
-      <c r="AS38" s="46"/>
-      <c r="AT38" s="46"/>
-      <c r="AU38" s="46"/>
-      <c r="AV38" s="46"/>
-      <c r="AW38" s="46"/>
-    </row>
-    <row r="39" spans="2:49" s="47" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="51" t="s">
-        <v>136</v>
-      </c>
-      <c r="C39" s="46" t="s">
-        <v>145</v>
-      </c>
-      <c r="D39" s="51" t="s">
-        <v>69</v>
-      </c>
-      <c r="E39" s="44">
-        <v>2030</v>
-      </c>
-      <c r="F39" s="86">
-        <v>1</v>
-      </c>
-      <c r="G39" s="65">
-        <v>1</v>
-      </c>
-      <c r="H39" s="47">
-        <v>100</v>
-      </c>
-      <c r="I39" s="47">
-        <v>0</v>
-      </c>
-      <c r="J39" s="47">
-        <v>0</v>
-      </c>
-      <c r="K39" s="47">
-        <v>0</v>
-      </c>
-      <c r="L39" s="47">
-        <v>0</v>
-      </c>
-      <c r="M39" s="69"/>
-      <c r="N39" s="69"/>
-      <c r="O39" s="65"/>
-      <c r="P39" s="65"/>
-      <c r="Q39" s="65"/>
-      <c r="R39" s="69"/>
-      <c r="S39" s="44"/>
+      <c r="AK38" s="39"/>
+      <c r="AL38" s="39"/>
+      <c r="AM38" s="45"/>
+      <c r="AN38" s="45"/>
+      <c r="AO38" s="45"/>
+      <c r="AQ38"/>
+      <c r="AR38"/>
+      <c r="AS38" s="39"/>
+      <c r="AT38" s="39"/>
+      <c r="AU38" s="45"/>
+      <c r="AV38" s="45"/>
+    </row>
+    <row r="39" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="45"/>
+      <c r="C39" s="45"/>
+      <c r="D39" s="45"/>
+      <c r="E39" s="64"/>
+      <c r="F39" s="67"/>
+      <c r="G39" s="45"/>
+      <c r="H39" s="45"/>
+      <c r="I39" s="45"/>
+      <c r="J39" s="68"/>
+      <c r="K39" s="45"/>
+      <c r="V39" s="45"/>
+      <c r="W39" s="45"/>
+      <c r="X39" s="45"/>
+      <c r="Y39" s="45"/>
+      <c r="Z39" s="45"/>
+      <c r="AA39" s="45"/>
+      <c r="AB39" s="45"/>
+      <c r="AC39" s="45"/>
+      <c r="AD39" s="45"/>
+      <c r="AE39" s="45"/>
       <c r="AI39"/>
       <c r="AJ39"/>
-      <c r="AK39" s="46"/>
-      <c r="AL39" s="46"/>
-      <c r="AM39" s="46"/>
-      <c r="AN39" s="46"/>
-      <c r="AO39" s="46"/>
-      <c r="AP39" s="46"/>
-      <c r="AQ39" s="46"/>
-      <c r="AR39" s="46"/>
-      <c r="AS39" s="46"/>
-      <c r="AT39" s="46"/>
-      <c r="AU39" s="46"/>
-      <c r="AV39" s="46"/>
-      <c r="AW39" s="46"/>
-    </row>
-    <row r="40" spans="2:49" s="47" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="46"/>
-      <c r="C40" s="51"/>
-      <c r="D40" s="87"/>
-      <c r="E40" s="44"/>
-      <c r="F40" s="65"/>
-      <c r="G40" s="65"/>
-      <c r="H40" s="44"/>
-      <c r="I40" s="65"/>
-      <c r="J40" s="65"/>
-      <c r="K40" s="65"/>
-      <c r="L40" s="65"/>
-      <c r="M40" s="69"/>
-      <c r="N40" s="69"/>
-      <c r="O40" s="65"/>
-      <c r="P40" s="65"/>
-      <c r="Q40" s="65"/>
-      <c r="R40" s="69"/>
-      <c r="S40" s="44"/>
-      <c r="V40" s="46"/>
-      <c r="W40" s="46"/>
-      <c r="X40" s="46"/>
-      <c r="Y40" s="46"/>
-      <c r="Z40" s="46"/>
-      <c r="AA40" s="46"/>
-      <c r="AB40" s="46"/>
-      <c r="AC40" s="46"/>
-      <c r="AD40" s="46"/>
+      <c r="AK39" s="39"/>
+      <c r="AL39" s="39"/>
+      <c r="AM39" s="45"/>
+      <c r="AN39" s="45"/>
+      <c r="AO39" s="45"/>
+      <c r="AQ39"/>
+      <c r="AR39"/>
+      <c r="AS39" s="39"/>
+      <c r="AT39" s="39"/>
+      <c r="AU39" s="45"/>
+      <c r="AV39" s="45"/>
+    </row>
+    <row r="40" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A40" s="46"/>
+      <c r="F40" s="67"/>
+      <c r="G40" s="43"/>
+      <c r="H40" s="69"/>
+      <c r="M40" s="46"/>
+      <c r="N40" s="46"/>
+      <c r="O40" s="46"/>
+      <c r="P40" s="46"/>
+      <c r="Q40" s="46"/>
+      <c r="R40" s="46"/>
+      <c r="S40" s="46"/>
       <c r="AI40"/>
       <c r="AJ40"/>
-      <c r="AK40" s="79"/>
-      <c r="AL40" s="79"/>
-      <c r="AM40" s="79"/>
-      <c r="AN40" s="79"/>
-      <c r="AO40" s="79"/>
-      <c r="AP40" s="79"/>
-      <c r="AQ40" s="79"/>
-      <c r="AR40" s="79"/>
-      <c r="AS40" s="79"/>
-      <c r="AT40" s="79"/>
-      <c r="AU40" s="79"/>
-      <c r="AV40" s="79"/>
-      <c r="AW40" s="79"/>
-    </row>
-    <row r="41" spans="2:49" s="47" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="46"/>
-      <c r="C41" s="51"/>
-      <c r="D41" s="87"/>
-      <c r="E41" s="44"/>
-      <c r="F41" s="65"/>
-      <c r="G41" s="65"/>
-      <c r="H41" s="44"/>
-      <c r="I41" s="65"/>
-      <c r="J41" s="65"/>
-      <c r="K41" s="65"/>
-      <c r="L41" s="65"/>
-      <c r="M41" s="69"/>
-      <c r="N41" s="69"/>
-      <c r="O41" s="65"/>
-      <c r="P41" s="65"/>
-      <c r="Q41" s="65"/>
-      <c r="R41" s="69"/>
-      <c r="S41" s="44"/>
-      <c r="V41" s="46"/>
-      <c r="W41" s="46"/>
-      <c r="X41" s="46"/>
-      <c r="Y41" s="46"/>
-      <c r="Z41" s="46"/>
-      <c r="AA41" s="46"/>
-      <c r="AB41" s="46"/>
-      <c r="AC41" s="46"/>
-      <c r="AD41" s="46"/>
+      <c r="AK40" s="39"/>
+      <c r="AL40" s="39"/>
+      <c r="AP40" s="46"/>
+      <c r="AQ40"/>
+      <c r="AR40"/>
+      <c r="AS40" s="39"/>
+      <c r="AT40" s="39"/>
+    </row>
+    <row r="41" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A41" s="46"/>
+      <c r="H41" s="69"/>
+      <c r="M41" s="46"/>
+      <c r="N41" s="46"/>
+      <c r="O41" s="46"/>
+      <c r="P41" s="46"/>
+      <c r="Q41" s="46"/>
+      <c r="R41" s="46"/>
+      <c r="S41" s="46"/>
       <c r="AI41"/>
       <c r="AJ41"/>
-      <c r="AK41" s="79"/>
-      <c r="AL41" s="79"/>
-      <c r="AM41" s="79"/>
-      <c r="AN41" s="79"/>
-      <c r="AO41" s="79"/>
-      <c r="AP41" s="79"/>
-      <c r="AQ41" s="79"/>
-      <c r="AR41" s="79"/>
-      <c r="AS41" s="79"/>
-      <c r="AT41" s="79"/>
-      <c r="AU41" s="79"/>
-      <c r="AV41" s="79"/>
-      <c r="AW41" s="79"/>
-    </row>
-    <row r="42" spans="2:49" s="47" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="46"/>
-      <c r="C42" s="51"/>
-      <c r="D42" s="87"/>
-      <c r="E42" s="44"/>
-      <c r="F42" s="65"/>
-      <c r="G42" s="65"/>
-      <c r="H42" s="44"/>
-      <c r="I42" s="65"/>
-      <c r="J42" s="65"/>
-      <c r="K42" s="65"/>
-      <c r="L42" s="65"/>
-      <c r="M42" s="69"/>
-      <c r="N42" s="69"/>
-      <c r="O42" s="65"/>
-      <c r="P42" s="65"/>
-      <c r="Q42" s="65"/>
-      <c r="R42" s="69"/>
-      <c r="S42" s="44"/>
-      <c r="V42" s="46"/>
-      <c r="W42" s="46"/>
-      <c r="X42" s="46"/>
-      <c r="Y42" s="46"/>
-      <c r="Z42" s="46"/>
-      <c r="AA42" s="46"/>
-      <c r="AB42" s="46"/>
-      <c r="AC42" s="46"/>
-      <c r="AD42" s="46"/>
+      <c r="AK41" s="39"/>
+      <c r="AL41" s="39"/>
+      <c r="AP41" s="46"/>
+      <c r="AQ41"/>
+      <c r="AR41"/>
+      <c r="AS41" s="39"/>
+      <c r="AT41" s="39"/>
+    </row>
+    <row r="42" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="B42" s="70"/>
+      <c r="C42" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="H42" s="69"/>
       <c r="AI42"/>
       <c r="AJ42"/>
-      <c r="AK42" s="46"/>
-      <c r="AL42" s="46"/>
-      <c r="AM42" s="46"/>
-      <c r="AN42" s="46"/>
-      <c r="AO42" s="46"/>
-      <c r="AP42" s="46"/>
-      <c r="AQ42" s="46"/>
-      <c r="AR42" s="46"/>
-      <c r="AS42" s="46"/>
-      <c r="AT42" s="46"/>
-      <c r="AU42" s="46"/>
-      <c r="AV42" s="46"/>
-      <c r="AW42" s="46"/>
-    </row>
-    <row r="43" spans="2:49" s="47" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="51"/>
-      <c r="C43" s="51"/>
-      <c r="D43" s="51"/>
-      <c r="E43" s="44"/>
-      <c r="F43" s="65"/>
-      <c r="G43" s="65"/>
-      <c r="H43" s="44"/>
-      <c r="I43" s="65"/>
-      <c r="J43" s="65"/>
-      <c r="K43" s="65"/>
-      <c r="L43" s="65"/>
-      <c r="M43" s="69"/>
-      <c r="N43" s="69"/>
-      <c r="O43" s="65"/>
-      <c r="P43" s="65"/>
-      <c r="Q43" s="65"/>
-      <c r="R43" s="69"/>
-      <c r="S43" s="44"/>
-      <c r="V43" s="46"/>
-      <c r="W43" s="46"/>
-      <c r="X43" s="46"/>
-      <c r="Y43" s="46"/>
-      <c r="Z43" s="46"/>
-      <c r="AA43" s="46"/>
-      <c r="AB43" s="46"/>
-      <c r="AC43" s="46"/>
-      <c r="AD43" s="46"/>
+      <c r="AK42" s="39"/>
+      <c r="AL42" s="39"/>
+      <c r="AQ42"/>
+      <c r="AR42"/>
+      <c r="AS42" s="39"/>
+      <c r="AT42" s="39"/>
+    </row>
+    <row r="43" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="B43" s="71"/>
+      <c r="C43" s="45" t="s">
+        <v>83</v>
+      </c>
+      <c r="H43" s="69"/>
       <c r="AI43"/>
       <c r="AJ43"/>
       <c r="AK43" s="39"/>
       <c r="AL43" s="39"/>
-      <c r="AM43" s="46"/>
-      <c r="AN43" s="46"/>
-      <c r="AO43" s="46"/>
       <c r="AQ43"/>
       <c r="AR43"/>
       <c r="AS43" s="39"/>
       <c r="AT43" s="39"/>
-      <c r="AU43" s="46"/>
-      <c r="AV43" s="46"/>
-    </row>
-    <row r="44" spans="2:49" s="47" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="51"/>
-      <c r="C44" s="51"/>
-      <c r="D44" s="51"/>
-      <c r="E44" s="44"/>
-      <c r="H44" s="44"/>
-      <c r="I44" s="65"/>
-      <c r="J44" s="46"/>
-      <c r="L44" s="65"/>
-      <c r="M44" s="69"/>
-      <c r="N44" s="69"/>
-      <c r="O44" s="65"/>
-      <c r="P44" s="65"/>
-      <c r="Q44" s="65"/>
-      <c r="R44" s="69"/>
-      <c r="S44" s="44"/>
-      <c r="V44" s="46"/>
-      <c r="W44" s="46"/>
-      <c r="X44" s="46"/>
-      <c r="Y44" s="46"/>
-      <c r="Z44" s="46"/>
-      <c r="AA44" s="46"/>
-      <c r="AB44" s="46"/>
-      <c r="AC44" s="46"/>
-      <c r="AD44" s="46"/>
+    </row>
+    <row r="44" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="H44" s="69"/>
       <c r="AI44"/>
       <c r="AJ44"/>
       <c r="AK44" s="39"/>
       <c r="AL44" s="39"/>
-      <c r="AM44" s="46"/>
-      <c r="AN44" s="46"/>
-      <c r="AO44" s="46"/>
       <c r="AQ44"/>
       <c r="AR44"/>
       <c r="AS44" s="39"/>
       <c r="AT44" s="39"/>
-      <c r="AU44" s="46"/>
-      <c r="AV44" s="46"/>
-    </row>
-    <row r="45" spans="2:49" s="47" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="51"/>
-      <c r="C45" s="51"/>
-      <c r="D45" s="51"/>
-      <c r="E45" s="44"/>
-      <c r="H45" s="44"/>
-      <c r="I45" s="65"/>
-      <c r="J45" s="46"/>
-      <c r="L45" s="65"/>
-      <c r="M45" s="44"/>
-      <c r="N45" s="69"/>
-      <c r="O45" s="44"/>
-      <c r="P45" s="44"/>
-      <c r="Q45" s="44"/>
-      <c r="R45" s="44"/>
-      <c r="S45" s="44"/>
-      <c r="V45" s="38"/>
-      <c r="W45" s="38"/>
-      <c r="X45" s="39"/>
-      <c r="Y45" s="40"/>
-      <c r="Z45" s="38"/>
-      <c r="AA45" s="38"/>
-      <c r="AB45" s="38"/>
-      <c r="AC45" s="46"/>
-      <c r="AD45" s="46"/>
+    </row>
+    <row r="45" spans="1:48" x14ac:dyDescent="0.25">
       <c r="AI45"/>
       <c r="AJ45"/>
       <c r="AK45" s="39"/>
       <c r="AL45" s="39"/>
-      <c r="AM45" s="46"/>
-      <c r="AN45" s="46"/>
-      <c r="AO45" s="46"/>
       <c r="AQ45"/>
       <c r="AR45"/>
       <c r="AS45" s="39"/>
       <c r="AT45" s="39"/>
-      <c r="AU45" s="46"/>
-      <c r="AV45" s="46"/>
-    </row>
-    <row r="46" spans="2:49" s="47" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="46"/>
-      <c r="C46" s="51"/>
-      <c r="D46" s="51"/>
-      <c r="E46" s="65"/>
-      <c r="F46" s="66"/>
-      <c r="K46" s="46"/>
-      <c r="N46" s="66"/>
-      <c r="V46" s="38"/>
-      <c r="W46" s="38"/>
-      <c r="X46" s="39"/>
-      <c r="Y46" s="40"/>
-      <c r="Z46" s="38"/>
-      <c r="AA46" s="38"/>
-      <c r="AB46" s="38"/>
-      <c r="AC46" s="46"/>
-      <c r="AD46" s="46"/>
+    </row>
+    <row r="46" spans="1:48" x14ac:dyDescent="0.25">
       <c r="AI46"/>
       <c r="AJ46"/>
       <c r="AK46" s="39"/>
       <c r="AL46" s="39"/>
-      <c r="AM46" s="46"/>
-      <c r="AN46" s="46"/>
-      <c r="AO46" s="46"/>
       <c r="AQ46"/>
       <c r="AR46"/>
       <c r="AS46" s="39"/>
       <c r="AT46" s="39"/>
-      <c r="AU46" s="46"/>
-      <c r="AV46" s="46"/>
-    </row>
-    <row r="47" spans="2:49" s="47" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="51"/>
-      <c r="C47" s="51"/>
-      <c r="D47" s="51"/>
-      <c r="E47" s="65"/>
-      <c r="F47" s="66"/>
-      <c r="J47" s="67"/>
-      <c r="K47" s="46"/>
-      <c r="N47" s="66"/>
-      <c r="V47" s="46"/>
-      <c r="W47" s="46"/>
-      <c r="X47" s="46"/>
-      <c r="Y47" s="46"/>
-      <c r="Z47" s="51"/>
-      <c r="AA47" s="51"/>
-      <c r="AB47" s="64"/>
-      <c r="AC47" s="46"/>
-      <c r="AD47" s="46"/>
+    </row>
+    <row r="47" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="E47" s="43"/>
       <c r="AI47"/>
       <c r="AJ47"/>
       <c r="AK47" s="39"/>
       <c r="AL47" s="39"/>
-      <c r="AM47" s="46"/>
-      <c r="AN47" s="46"/>
-      <c r="AO47" s="46"/>
       <c r="AQ47"/>
       <c r="AR47"/>
       <c r="AS47" s="39"/>
       <c r="AT47" s="39"/>
-      <c r="AU47" s="46"/>
-      <c r="AV47" s="46"/>
-    </row>
-    <row r="48" spans="2:49" s="47" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="51"/>
-      <c r="C48" s="46"/>
-      <c r="D48" s="51"/>
-      <c r="E48" s="65"/>
-      <c r="F48" s="68"/>
-      <c r="G48" s="46"/>
-      <c r="H48" s="46"/>
-      <c r="I48" s="46"/>
-      <c r="J48" s="69"/>
-      <c r="K48" s="46"/>
-      <c r="V48" s="46"/>
-      <c r="X48" s="46"/>
-      <c r="Z48" s="55"/>
-      <c r="AA48" s="55"/>
-      <c r="AB48" s="46"/>
-      <c r="AC48" s="46"/>
-      <c r="AD48" s="46"/>
+    </row>
+    <row r="48" spans="1:48" x14ac:dyDescent="0.25">
       <c r="AI48"/>
       <c r="AJ48"/>
       <c r="AK48" s="39"/>
       <c r="AL48" s="39"/>
-      <c r="AM48" s="46"/>
-      <c r="AN48" s="46"/>
-      <c r="AO48" s="46"/>
       <c r="AQ48"/>
       <c r="AR48"/>
       <c r="AS48" s="39"/>
       <c r="AT48" s="39"/>
-      <c r="AU48" s="46"/>
-      <c r="AV48" s="46"/>
-    </row>
-    <row r="49" spans="1:48" s="47" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="46"/>
-      <c r="C49" s="46"/>
-      <c r="D49" s="46"/>
-      <c r="E49" s="65"/>
-      <c r="F49" s="68"/>
-      <c r="G49" s="46"/>
-      <c r="H49" s="46"/>
-      <c r="I49" s="46"/>
-      <c r="J49" s="69"/>
-      <c r="K49" s="46"/>
-      <c r="V49" s="46"/>
-      <c r="W49" s="46"/>
-      <c r="X49" s="46"/>
-      <c r="Y49" s="46"/>
-      <c r="Z49" s="46"/>
-      <c r="AA49" s="46"/>
-      <c r="AB49" s="46"/>
-      <c r="AC49" s="46"/>
-      <c r="AD49" s="46"/>
-      <c r="AE49" s="46"/>
+    </row>
+    <row r="49" spans="2:46" x14ac:dyDescent="0.25">
       <c r="AI49"/>
       <c r="AJ49"/>
       <c r="AK49" s="39"/>
       <c r="AL49" s="39"/>
-      <c r="AM49" s="46"/>
-      <c r="AN49" s="46"/>
-      <c r="AO49" s="46"/>
       <c r="AQ49"/>
       <c r="AR49"/>
       <c r="AS49" s="39"/>
       <c r="AT49" s="39"/>
-      <c r="AU49" s="46"/>
-      <c r="AV49" s="46"/>
-    </row>
-    <row r="50" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A50" s="47"/>
-      <c r="F50" s="68"/>
-      <c r="G50" s="44"/>
-      <c r="H50" s="70"/>
-      <c r="M50" s="47"/>
-      <c r="N50" s="47"/>
-      <c r="O50" s="47"/>
-      <c r="P50" s="47"/>
-      <c r="Q50" s="47"/>
-      <c r="R50" s="47"/>
-      <c r="S50" s="47"/>
+    </row>
+    <row r="50" spans="2:46" x14ac:dyDescent="0.25">
       <c r="AI50"/>
       <c r="AJ50"/>
       <c r="AK50" s="39"/>
       <c r="AL50" s="39"/>
-      <c r="AP50" s="47"/>
       <c r="AQ50"/>
       <c r="AR50"/>
       <c r="AS50" s="39"/>
       <c r="AT50" s="39"/>
     </row>
-    <row r="51" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A51" s="47"/>
-      <c r="H51" s="70"/>
-      <c r="M51" s="47"/>
-      <c r="N51" s="47"/>
-      <c r="O51" s="47"/>
-      <c r="P51" s="47"/>
-      <c r="Q51" s="47"/>
-      <c r="R51" s="47"/>
-      <c r="S51" s="47"/>
+    <row r="51" spans="2:46" x14ac:dyDescent="0.25">
       <c r="AI51"/>
       <c r="AJ51"/>
       <c r="AK51" s="39"/>
       <c r="AL51" s="39"/>
-      <c r="AP51" s="47"/>
       <c r="AQ51"/>
       <c r="AR51"/>
       <c r="AS51" s="39"/>
       <c r="AT51" s="39"/>
     </row>
-    <row r="52" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="B52" s="71"/>
-      <c r="C52" s="46" t="s">
-        <v>82</v>
-      </c>
-      <c r="H52" s="70"/>
+    <row r="52" spans="2:46" x14ac:dyDescent="0.25">
       <c r="AI52"/>
       <c r="AJ52"/>
       <c r="AK52" s="39"/>
@@ -6146,12 +6113,7 @@
       <c r="AS52" s="39"/>
       <c r="AT52" s="39"/>
     </row>
-    <row r="53" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="B53" s="72"/>
-      <c r="C53" s="46" t="s">
-        <v>83</v>
-      </c>
-      <c r="H53" s="70"/>
+    <row r="53" spans="2:46" x14ac:dyDescent="0.25">
       <c r="AI53"/>
       <c r="AJ53"/>
       <c r="AK53" s="39"/>
@@ -6161,8 +6123,18 @@
       <c r="AS53" s="39"/>
       <c r="AT53" s="39"/>
     </row>
-    <row r="54" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="H54" s="70"/>
+    <row r="54" spans="2:46" x14ac:dyDescent="0.25">
+      <c r="B54" s="73"/>
+      <c r="C54" s="73"/>
+      <c r="D54"/>
+      <c r="E54"/>
+      <c r="F54"/>
+      <c r="G54"/>
+      <c r="H54"/>
+      <c r="I54"/>
+      <c r="J54"/>
+      <c r="K54"/>
+      <c r="L54"/>
       <c r="AI54"/>
       <c r="AJ54"/>
       <c r="AK54" s="39"/>
@@ -6172,7 +6144,18 @@
       <c r="AS54" s="39"/>
       <c r="AT54" s="39"/>
     </row>
-    <row r="55" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:46" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B55" s="74"/>
+      <c r="C55" s="74"/>
+      <c r="D55" s="74"/>
+      <c r="E55" s="74"/>
+      <c r="F55" s="74"/>
+      <c r="G55" s="74"/>
+      <c r="H55" s="74"/>
+      <c r="I55" s="74"/>
+      <c r="J55" s="74"/>
+      <c r="K55" s="74"/>
+      <c r="L55" s="74"/>
       <c r="AI55"/>
       <c r="AJ55"/>
       <c r="AK55" s="39"/>
@@ -6182,7 +6165,18 @@
       <c r="AS55" s="39"/>
       <c r="AT55" s="39"/>
     </row>
-    <row r="56" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:46" x14ac:dyDescent="0.25">
+      <c r="B56"/>
+      <c r="C56"/>
+      <c r="D56"/>
+      <c r="E56" s="1"/>
+      <c r="F56"/>
+      <c r="G56"/>
+      <c r="H56"/>
+      <c r="I56"/>
+      <c r="J56"/>
+      <c r="K56"/>
+      <c r="L56"/>
       <c r="AI56"/>
       <c r="AJ56"/>
       <c r="AK56" s="39"/>
@@ -6192,8 +6186,18 @@
       <c r="AS56" s="39"/>
       <c r="AT56" s="39"/>
     </row>
-    <row r="57" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="E57" s="44"/>
+    <row r="57" spans="2:46" x14ac:dyDescent="0.25">
+      <c r="B57"/>
+      <c r="C57"/>
+      <c r="D57"/>
+      <c r="E57" s="1"/>
+      <c r="F57"/>
+      <c r="G57"/>
+      <c r="H57"/>
+      <c r="I57"/>
+      <c r="J57"/>
+      <c r="K57"/>
+      <c r="L57"/>
       <c r="AI57"/>
       <c r="AJ57"/>
       <c r="AK57" s="39"/>
@@ -6203,7 +6207,18 @@
       <c r="AS57" s="39"/>
       <c r="AT57" s="39"/>
     </row>
-    <row r="58" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:46" x14ac:dyDescent="0.25">
+      <c r="B58"/>
+      <c r="C58"/>
+      <c r="D58"/>
+      <c r="E58" s="1"/>
+      <c r="F58"/>
+      <c r="G58"/>
+      <c r="H58"/>
+      <c r="I58"/>
+      <c r="J58"/>
+      <c r="K58"/>
+      <c r="L58"/>
       <c r="AI58"/>
       <c r="AJ58"/>
       <c r="AK58" s="39"/>
@@ -6213,7 +6228,18 @@
       <c r="AS58" s="39"/>
       <c r="AT58" s="39"/>
     </row>
-    <row r="59" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:46" x14ac:dyDescent="0.25">
+      <c r="B59"/>
+      <c r="C59"/>
+      <c r="D59"/>
+      <c r="E59" s="1"/>
+      <c r="F59"/>
+      <c r="G59"/>
+      <c r="H59"/>
+      <c r="I59"/>
+      <c r="J59"/>
+      <c r="K59"/>
+      <c r="L59"/>
       <c r="AI59"/>
       <c r="AJ59"/>
       <c r="AK59" s="39"/>
@@ -6223,7 +6249,18 @@
       <c r="AS59" s="39"/>
       <c r="AT59" s="39"/>
     </row>
-    <row r="60" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:46" x14ac:dyDescent="0.25">
+      <c r="B60"/>
+      <c r="C60"/>
+      <c r="D60"/>
+      <c r="E60" s="1"/>
+      <c r="F60"/>
+      <c r="G60"/>
+      <c r="H60"/>
+      <c r="I60"/>
+      <c r="J60"/>
+      <c r="K60"/>
+      <c r="L60"/>
       <c r="AI60"/>
       <c r="AJ60"/>
       <c r="AK60" s="39"/>
@@ -6233,7 +6270,18 @@
       <c r="AS60" s="39"/>
       <c r="AT60" s="39"/>
     </row>
-    <row r="61" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:46" x14ac:dyDescent="0.25">
+      <c r="B61"/>
+      <c r="C61"/>
+      <c r="D61"/>
+      <c r="E61" s="1"/>
+      <c r="F61"/>
+      <c r="G61"/>
+      <c r="H61"/>
+      <c r="I61"/>
+      <c r="J61"/>
+      <c r="K61"/>
+      <c r="L61"/>
       <c r="AI61"/>
       <c r="AJ61"/>
       <c r="AK61" s="39"/>
@@ -6243,7 +6291,18 @@
       <c r="AS61" s="39"/>
       <c r="AT61" s="39"/>
     </row>
-    <row r="62" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:46" x14ac:dyDescent="0.25">
+      <c r="B62"/>
+      <c r="C62"/>
+      <c r="D62"/>
+      <c r="E62" s="1"/>
+      <c r="F62"/>
+      <c r="G62"/>
+      <c r="H62"/>
+      <c r="I62"/>
+      <c r="J62"/>
+      <c r="K62"/>
+      <c r="L62"/>
       <c r="AI62"/>
       <c r="AJ62"/>
       <c r="AK62" s="39"/>
@@ -6253,7 +6312,18 @@
       <c r="AS62" s="39"/>
       <c r="AT62" s="39"/>
     </row>
-    <row r="63" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:46" x14ac:dyDescent="0.25">
+      <c r="B63"/>
+      <c r="C63"/>
+      <c r="D63"/>
+      <c r="E63" s="1"/>
+      <c r="F63"/>
+      <c r="G63"/>
+      <c r="H63"/>
+      <c r="I63"/>
+      <c r="J63"/>
+      <c r="K63"/>
+      <c r="L63"/>
       <c r="AI63"/>
       <c r="AJ63"/>
       <c r="AK63" s="39"/>
@@ -6263,18 +6333,7 @@
       <c r="AS63" s="39"/>
       <c r="AT63" s="39"/>
     </row>
-    <row r="64" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="B64" s="74"/>
-      <c r="C64" s="74"/>
-      <c r="D64"/>
-      <c r="E64"/>
-      <c r="F64"/>
-      <c r="G64"/>
-      <c r="H64"/>
-      <c r="I64"/>
-      <c r="J64"/>
-      <c r="K64"/>
-      <c r="L64"/>
+    <row r="64" spans="2:46" x14ac:dyDescent="0.25">
       <c r="AI64"/>
       <c r="AJ64"/>
       <c r="AK64" s="39"/>
@@ -6284,18 +6343,7 @@
       <c r="AS64" s="39"/>
       <c r="AT64" s="39"/>
     </row>
-    <row r="65" spans="1:48" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B65" s="75"/>
-      <c r="C65" s="75"/>
-      <c r="D65" s="75"/>
-      <c r="E65" s="75"/>
-      <c r="F65" s="75"/>
-      <c r="G65" s="75"/>
-      <c r="H65" s="75"/>
-      <c r="I65" s="75"/>
-      <c r="J65" s="75"/>
-      <c r="K65" s="75"/>
-      <c r="L65" s="75"/>
+    <row r="65" spans="1:48" x14ac:dyDescent="0.25">
       <c r="AI65"/>
       <c r="AJ65"/>
       <c r="AK65" s="39"/>
@@ -6306,17 +6354,6 @@
       <c r="AT65" s="39"/>
     </row>
     <row r="66" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="B66"/>
-      <c r="C66"/>
-      <c r="D66"/>
-      <c r="E66" s="1"/>
-      <c r="F66"/>
-      <c r="G66"/>
-      <c r="H66"/>
-      <c r="I66"/>
-      <c r="J66"/>
-      <c r="K66"/>
-      <c r="L66"/>
       <c r="AI66"/>
       <c r="AJ66"/>
       <c r="AK66" s="39"/>
@@ -6327,17 +6364,6 @@
       <c r="AT66" s="39"/>
     </row>
     <row r="67" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="B67"/>
-      <c r="C67"/>
-      <c r="D67"/>
-      <c r="E67" s="1"/>
-      <c r="F67"/>
-      <c r="G67"/>
-      <c r="H67"/>
-      <c r="I67"/>
-      <c r="J67"/>
-      <c r="K67"/>
-      <c r="L67"/>
       <c r="AI67"/>
       <c r="AJ67"/>
       <c r="AK67" s="39"/>
@@ -6348,17 +6374,15 @@
       <c r="AT67" s="39"/>
     </row>
     <row r="68" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="B68"/>
-      <c r="C68"/>
-      <c r="D68"/>
-      <c r="E68" s="1"/>
-      <c r="F68"/>
-      <c r="G68"/>
-      <c r="H68"/>
-      <c r="I68"/>
-      <c r="J68"/>
-      <c r="K68"/>
-      <c r="L68"/>
+      <c r="V68" s="46"/>
+      <c r="W68" s="46"/>
+      <c r="X68" s="46"/>
+      <c r="Y68" s="46"/>
+      <c r="Z68" s="46"/>
+      <c r="AA68" s="46"/>
+      <c r="AB68" s="46"/>
+      <c r="AC68" s="46"/>
+      <c r="AD68" s="46"/>
       <c r="AI68"/>
       <c r="AJ68"/>
       <c r="AK68" s="39"/>
@@ -6371,15 +6395,24 @@
     <row r="69" spans="1:48" x14ac:dyDescent="0.25">
       <c r="B69"/>
       <c r="C69"/>
-      <c r="D69"/>
-      <c r="E69" s="1"/>
-      <c r="F69"/>
-      <c r="G69"/>
+      <c r="E69" s="73"/>
+      <c r="F69" s="73"/>
+      <c r="G69" s="1"/>
       <c r="H69"/>
-      <c r="I69"/>
+      <c r="I69" s="73"/>
       <c r="J69"/>
       <c r="K69"/>
-      <c r="L69"/>
+      <c r="L69" s="73"/>
+      <c r="V69" s="46"/>
+      <c r="W69" s="46"/>
+      <c r="X69" s="46"/>
+      <c r="Y69" s="46"/>
+      <c r="Z69" s="46"/>
+      <c r="AA69" s="46"/>
+      <c r="AB69" s="46"/>
+      <c r="AC69" s="46"/>
+      <c r="AD69" s="46"/>
+      <c r="AE69" s="46"/>
       <c r="AI69"/>
       <c r="AJ69"/>
       <c r="AK69" s="39"/>
@@ -6389,567 +6422,524 @@
       <c r="AS69" s="39"/>
       <c r="AT69" s="39"/>
     </row>
-    <row r="70" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="B70"/>
-      <c r="C70"/>
-      <c r="D70"/>
-      <c r="E70" s="1"/>
-      <c r="F70"/>
-      <c r="G70"/>
-      <c r="H70"/>
-      <c r="I70"/>
-      <c r="J70"/>
-      <c r="K70"/>
-      <c r="L70"/>
+    <row r="70" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="45"/>
+      <c r="B70" s="79"/>
+      <c r="C70" s="79"/>
+      <c r="D70" s="79"/>
+      <c r="E70" s="79"/>
+      <c r="F70" s="79"/>
+      <c r="G70" s="79"/>
+      <c r="H70" s="80"/>
+      <c r="I70" s="79"/>
+      <c r="J70" s="79"/>
+      <c r="K70" s="79"/>
+      <c r="L70" s="79"/>
+      <c r="M70" s="45"/>
+      <c r="N70" s="45"/>
+      <c r="O70" s="45"/>
+      <c r="P70" s="45"/>
+      <c r="Q70" s="45"/>
+      <c r="R70" s="45"/>
+      <c r="S70" s="45"/>
       <c r="AI70"/>
-      <c r="AJ70"/>
+      <c r="AJ70" s="80"/>
       <c r="AK70" s="39"/>
-      <c r="AL70" s="39"/>
+      <c r="AL70" s="41"/>
+      <c r="AM70" s="45"/>
+      <c r="AN70" s="45"/>
       <c r="AQ70"/>
-      <c r="AR70"/>
+      <c r="AR70" s="80"/>
       <c r="AS70" s="39"/>
-      <c r="AT70" s="39"/>
-    </row>
-    <row r="71" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="B71"/>
-      <c r="C71"/>
-      <c r="D71"/>
-      <c r="E71" s="1"/>
-      <c r="F71"/>
-      <c r="G71"/>
-      <c r="H71"/>
-      <c r="I71"/>
-      <c r="J71"/>
-      <c r="K71"/>
-      <c r="L71"/>
-      <c r="AI71"/>
-      <c r="AJ71"/>
-      <c r="AK71" s="39"/>
-      <c r="AL71" s="39"/>
-      <c r="AQ71"/>
-      <c r="AR71"/>
-      <c r="AS71" s="39"/>
-      <c r="AT71" s="39"/>
-    </row>
-    <row r="72" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="B72"/>
-      <c r="C72"/>
-      <c r="D72"/>
-      <c r="E72" s="1"/>
-      <c r="F72"/>
-      <c r="G72"/>
-      <c r="H72"/>
-      <c r="I72"/>
-      <c r="J72"/>
-      <c r="K72"/>
-      <c r="L72"/>
-      <c r="AI72"/>
-      <c r="AJ72"/>
-      <c r="AK72" s="39"/>
-      <c r="AL72" s="39"/>
-      <c r="AQ72"/>
-      <c r="AR72"/>
-      <c r="AS72" s="39"/>
-      <c r="AT72" s="39"/>
+      <c r="AT70" s="41"/>
+      <c r="AU70" s="45"/>
+      <c r="AV70" s="45"/>
+    </row>
+    <row r="71" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="73"/>
+      <c r="B71" s="81"/>
+      <c r="C71" s="82"/>
+      <c r="D71" s="81"/>
+      <c r="E71" s="81"/>
+      <c r="F71" s="81"/>
+      <c r="G71" s="81"/>
+      <c r="H71" s="80"/>
+      <c r="I71" s="81"/>
+      <c r="J71" s="81"/>
+      <c r="K71" s="82"/>
+      <c r="L71" s="82"/>
+      <c r="M71" s="73"/>
+      <c r="N71" s="73"/>
+      <c r="O71" s="1"/>
+      <c r="P71" s="45"/>
+      <c r="Q71" s="45"/>
+      <c r="R71" s="45"/>
+      <c r="S71" s="45"/>
+      <c r="V71" s="45"/>
+      <c r="W71" s="45"/>
+      <c r="X71" s="45"/>
+      <c r="Y71" s="45"/>
+      <c r="Z71" s="45"/>
+      <c r="AA71" s="45"/>
+      <c r="AB71" s="45"/>
+      <c r="AC71" s="45"/>
+      <c r="AD71" s="45"/>
+      <c r="AI71" s="42"/>
+      <c r="AJ71" s="42"/>
+      <c r="AK71" s="54"/>
+    </row>
+    <row r="72" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="79"/>
+      <c r="B72" s="81"/>
+      <c r="C72" s="81"/>
+      <c r="D72" s="81"/>
+      <c r="E72" s="81"/>
+      <c r="F72" s="81"/>
+      <c r="G72" s="81"/>
+      <c r="H72" s="80"/>
+      <c r="I72" s="81"/>
+      <c r="J72" s="81"/>
+      <c r="K72" s="81"/>
+      <c r="L72" s="81"/>
+      <c r="M72" s="79"/>
+      <c r="N72" s="79"/>
+      <c r="O72" s="79"/>
+      <c r="V72" s="45"/>
+      <c r="W72" s="45"/>
+      <c r="X72" s="45"/>
+      <c r="Y72" s="45"/>
+      <c r="Z72" s="45"/>
+      <c r="AA72" s="45"/>
+      <c r="AB72" s="45"/>
+      <c r="AC72" s="45"/>
+      <c r="AD72" s="45"/>
+      <c r="AE72" s="45"/>
+      <c r="AI72" s="42"/>
+      <c r="AJ72" s="42"/>
+      <c r="AK72" s="54"/>
     </row>
     <row r="73" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A73" s="81"/>
       <c r="B73"/>
-      <c r="C73"/>
-      <c r="D73"/>
-      <c r="E73" s="1"/>
-      <c r="F73"/>
-      <c r="G73"/>
+      <c r="C73" s="39"/>
+      <c r="D73" s="39"/>
       <c r="H73"/>
       <c r="I73"/>
       <c r="J73"/>
-      <c r="K73"/>
-      <c r="L73"/>
-      <c r="AI73"/>
-      <c r="AJ73"/>
-      <c r="AK73" s="39"/>
-      <c r="AL73" s="39"/>
-      <c r="AQ73"/>
-      <c r="AR73"/>
-      <c r="AS73" s="39"/>
-      <c r="AT73" s="39"/>
+      <c r="K73" s="39"/>
+      <c r="L73" s="39"/>
+      <c r="M73" s="82"/>
+      <c r="N73" s="82"/>
+      <c r="O73" s="81"/>
+      <c r="P73" s="46"/>
+      <c r="Q73" s="46"/>
+      <c r="R73" s="46"/>
+      <c r="S73" s="46"/>
+      <c r="AI73" s="38"/>
+      <c r="AJ73" s="38"/>
+      <c r="AK73" s="50"/>
     </row>
     <row r="74" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="AI74"/>
-      <c r="AJ74"/>
-      <c r="AK74" s="39"/>
-      <c r="AL74" s="39"/>
-      <c r="AQ74"/>
-      <c r="AR74"/>
-      <c r="AS74" s="39"/>
-      <c r="AT74" s="39"/>
+      <c r="A74" s="81"/>
+      <c r="B74"/>
+      <c r="C74" s="39"/>
+      <c r="D74" s="39"/>
+      <c r="H74" s="78"/>
+      <c r="I74"/>
+      <c r="J74"/>
+      <c r="K74" s="39"/>
+      <c r="L74" s="39"/>
+      <c r="M74" s="81"/>
+      <c r="N74" s="81"/>
+      <c r="O74" s="81"/>
+      <c r="P74" s="46"/>
+      <c r="Q74" s="46"/>
+      <c r="R74" s="46"/>
+      <c r="S74" s="46"/>
+      <c r="AI74" s="38"/>
+      <c r="AJ74" s="38"/>
+      <c r="AK74" s="50"/>
     </row>
     <row r="75" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="AI75"/>
-      <c r="AJ75"/>
-      <c r="AK75" s="39"/>
-      <c r="AL75" s="39"/>
-      <c r="AQ75"/>
-      <c r="AR75"/>
-      <c r="AS75" s="39"/>
-      <c r="AT75" s="39"/>
+      <c r="A75"/>
+      <c r="B75"/>
+      <c r="C75" s="39"/>
+      <c r="D75" s="39"/>
+      <c r="I75"/>
+      <c r="J75"/>
+      <c r="K75" s="39"/>
+      <c r="L75" s="39"/>
+      <c r="AI75" s="38"/>
+      <c r="AJ75" s="38"/>
+      <c r="AK75" s="50"/>
     </row>
     <row r="76" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="AI76"/>
-      <c r="AJ76"/>
-      <c r="AK76" s="39"/>
-      <c r="AL76" s="39"/>
-      <c r="AQ76"/>
-      <c r="AR76"/>
-      <c r="AS76" s="39"/>
-      <c r="AT76" s="39"/>
+      <c r="A76"/>
+      <c r="B76"/>
+      <c r="C76" s="39"/>
+      <c r="D76" s="39"/>
+      <c r="I76"/>
+      <c r="J76"/>
+      <c r="K76" s="39"/>
+      <c r="L76" s="39"/>
+      <c r="AI76" s="38"/>
+      <c r="AJ76" s="38"/>
+      <c r="AK76" s="50"/>
     </row>
     <row r="77" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="AI77"/>
-      <c r="AJ77"/>
-      <c r="AK77" s="39"/>
-      <c r="AL77" s="39"/>
-      <c r="AQ77"/>
-      <c r="AR77"/>
-      <c r="AS77" s="39"/>
-      <c r="AT77" s="39"/>
+      <c r="A77"/>
+      <c r="B77"/>
+      <c r="C77" s="39"/>
+      <c r="D77" s="39"/>
+      <c r="H77" s="46"/>
+      <c r="I77"/>
+      <c r="J77"/>
+      <c r="K77" s="39"/>
+      <c r="L77" s="39"/>
+      <c r="O77" s="46"/>
+      <c r="AI77" s="38"/>
+      <c r="AJ77" s="38"/>
+      <c r="AK77" s="50"/>
     </row>
     <row r="78" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="V78" s="47"/>
-      <c r="W78" s="47"/>
-      <c r="X78" s="47"/>
-      <c r="Y78" s="47"/>
-      <c r="Z78" s="47"/>
-      <c r="AA78" s="47"/>
-      <c r="AB78" s="47"/>
-      <c r="AC78" s="47"/>
-      <c r="AD78" s="47"/>
-      <c r="AI78"/>
-      <c r="AJ78"/>
-      <c r="AK78" s="39"/>
-      <c r="AL78" s="39"/>
-      <c r="AQ78"/>
-      <c r="AR78"/>
-      <c r="AS78" s="39"/>
-      <c r="AT78" s="39"/>
+      <c r="A78"/>
+      <c r="B78"/>
+      <c r="C78" s="39"/>
+      <c r="D78" s="39"/>
+      <c r="H78" s="46"/>
+      <c r="I78"/>
+      <c r="J78"/>
+      <c r="K78" s="39"/>
+      <c r="L78" s="39"/>
+      <c r="O78" s="46"/>
+      <c r="AI78" s="38"/>
+      <c r="AJ78" s="38"/>
+      <c r="AK78" s="50"/>
     </row>
     <row r="79" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A79"/>
       <c r="B79"/>
-      <c r="C79"/>
-      <c r="E79" s="74"/>
-      <c r="F79" s="74"/>
-      <c r="G79" s="1"/>
-      <c r="H79"/>
-      <c r="I79" s="74"/>
+      <c r="C79" s="39"/>
+      <c r="D79" s="39"/>
+      <c r="H79" s="46"/>
+      <c r="I79"/>
       <c r="J79"/>
-      <c r="K79"/>
-      <c r="L79" s="74"/>
-      <c r="V79" s="47"/>
-      <c r="W79" s="47"/>
-      <c r="X79" s="47"/>
-      <c r="Y79" s="47"/>
-      <c r="Z79" s="47"/>
-      <c r="AA79" s="47"/>
-      <c r="AB79" s="47"/>
-      <c r="AC79" s="47"/>
-      <c r="AD79" s="47"/>
-      <c r="AE79" s="47"/>
-      <c r="AI79"/>
-      <c r="AJ79"/>
-      <c r="AK79" s="39"/>
-      <c r="AL79" s="39"/>
-      <c r="AQ79"/>
-      <c r="AR79"/>
-      <c r="AS79" s="39"/>
-      <c r="AT79" s="39"/>
-    </row>
-    <row r="80" spans="1:48" s="47" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="46"/>
-      <c r="B80" s="82"/>
-      <c r="C80" s="82"/>
-      <c r="D80" s="82"/>
-      <c r="E80" s="82"/>
-      <c r="F80" s="82"/>
-      <c r="G80" s="82"/>
-      <c r="H80" s="83"/>
-      <c r="I80" s="82"/>
-      <c r="J80" s="82"/>
-      <c r="K80" s="82"/>
-      <c r="L80" s="82"/>
-      <c r="M80" s="46"/>
-      <c r="N80" s="46"/>
+      <c r="K79" s="39"/>
+      <c r="L79" s="39"/>
+      <c r="O79" s="46"/>
+      <c r="AI79" s="38"/>
+      <c r="AJ79" s="38"/>
+      <c r="AK79" s="50"/>
+    </row>
+    <row r="80" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A80"/>
+      <c r="B80"/>
+      <c r="C80" s="39"/>
+      <c r="D80" s="39"/>
+      <c r="H80" s="46"/>
+      <c r="I80"/>
+      <c r="J80"/>
+      <c r="K80" s="39"/>
+      <c r="L80" s="39"/>
       <c r="O80" s="46"/>
-      <c r="P80" s="46"/>
-      <c r="Q80" s="46"/>
-      <c r="R80" s="46"/>
-      <c r="S80" s="46"/>
-      <c r="AI80"/>
-      <c r="AJ80" s="83"/>
-      <c r="AK80" s="39"/>
-      <c r="AL80" s="42"/>
-      <c r="AM80" s="46"/>
-      <c r="AN80" s="46"/>
-      <c r="AQ80"/>
-      <c r="AR80" s="83"/>
-      <c r="AS80" s="39"/>
-      <c r="AT80" s="42"/>
-      <c r="AU80" s="46"/>
-      <c r="AV80" s="46"/>
-    </row>
-    <row r="81" spans="1:37" s="47" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="74"/>
-      <c r="B81" s="84"/>
-      <c r="C81" s="85"/>
-      <c r="D81" s="84"/>
-      <c r="E81" s="84"/>
-      <c r="F81" s="84"/>
-      <c r="G81" s="84"/>
-      <c r="H81" s="83"/>
-      <c r="I81" s="84"/>
-      <c r="J81" s="84"/>
-      <c r="K81" s="85"/>
-      <c r="L81" s="85"/>
-      <c r="M81" s="74"/>
-      <c r="N81" s="74"/>
-      <c r="O81" s="1"/>
-      <c r="P81" s="46"/>
-      <c r="Q81" s="46"/>
-      <c r="R81" s="46"/>
-      <c r="S81" s="46"/>
-      <c r="V81" s="46"/>
-      <c r="W81" s="46"/>
-      <c r="X81" s="46"/>
-      <c r="Y81" s="46"/>
-      <c r="Z81" s="46"/>
-      <c r="AA81" s="46"/>
-      <c r="AB81" s="46"/>
-      <c r="AC81" s="46"/>
-      <c r="AD81" s="46"/>
-      <c r="AI81" s="43"/>
-      <c r="AJ81" s="43"/>
-      <c r="AK81" s="55"/>
-    </row>
-    <row r="82" spans="1:37" s="47" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="82"/>
-      <c r="B82" s="84"/>
-      <c r="C82" s="84"/>
-      <c r="D82" s="84"/>
-      <c r="E82" s="84"/>
-      <c r="F82" s="84"/>
-      <c r="G82" s="84"/>
-      <c r="H82" s="83"/>
-      <c r="I82" s="84"/>
-      <c r="J82" s="84"/>
-      <c r="K82" s="84"/>
-      <c r="L82" s="84"/>
-      <c r="M82" s="82"/>
-      <c r="N82" s="82"/>
-      <c r="O82" s="82"/>
-      <c r="V82" s="46"/>
-      <c r="W82" s="46"/>
-      <c r="X82" s="46"/>
-      <c r="Y82" s="46"/>
-      <c r="Z82" s="46"/>
-      <c r="AA82" s="46"/>
-      <c r="AB82" s="46"/>
-      <c r="AC82" s="46"/>
-      <c r="AD82" s="46"/>
-      <c r="AE82" s="46"/>
-      <c r="AI82" s="43"/>
-      <c r="AJ82" s="43"/>
-      <c r="AK82" s="55"/>
+      <c r="AI80" s="38"/>
+      <c r="AJ80" s="38"/>
+      <c r="AK80" s="50"/>
+    </row>
+    <row r="81" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A81"/>
+      <c r="B81"/>
+      <c r="C81" s="39"/>
+      <c r="D81" s="39"/>
+      <c r="H81" s="46"/>
+      <c r="I81"/>
+      <c r="J81"/>
+      <c r="K81" s="39"/>
+      <c r="L81" s="39"/>
+      <c r="O81" s="46"/>
+      <c r="AI81" s="38"/>
+      <c r="AJ81" s="38"/>
+      <c r="AK81" s="50"/>
+    </row>
+    <row r="82" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A82"/>
+      <c r="B82"/>
+      <c r="C82" s="39"/>
+      <c r="D82" s="39"/>
+      <c r="H82" s="46"/>
+      <c r="I82"/>
+      <c r="J82"/>
+      <c r="K82" s="39"/>
+      <c r="L82" s="39"/>
+      <c r="O82" s="46"/>
+      <c r="AI82" s="38"/>
+      <c r="AJ82" s="38"/>
+      <c r="AK82" s="50"/>
     </row>
     <row r="83" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A83" s="84"/>
+      <c r="A83"/>
       <c r="B83"/>
       <c r="C83" s="39"/>
       <c r="D83" s="39"/>
-      <c r="H83"/>
+      <c r="H83" s="46"/>
       <c r="I83"/>
       <c r="J83"/>
       <c r="K83" s="39"/>
       <c r="L83" s="39"/>
-      <c r="M83" s="85"/>
-      <c r="N83" s="85"/>
-      <c r="O83" s="84"/>
-      <c r="P83" s="47"/>
-      <c r="Q83" s="47"/>
-      <c r="R83" s="47"/>
-      <c r="S83" s="47"/>
+      <c r="O83" s="46"/>
       <c r="AI83" s="38"/>
       <c r="AJ83" s="38"/>
-      <c r="AK83" s="51"/>
+      <c r="AK83" s="50"/>
     </row>
     <row r="84" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A84" s="84"/>
+      <c r="A84"/>
       <c r="B84"/>
       <c r="C84" s="39"/>
       <c r="D84" s="39"/>
-      <c r="H84" s="81"/>
+      <c r="H84" s="46"/>
       <c r="I84"/>
       <c r="J84"/>
       <c r="K84" s="39"/>
       <c r="L84" s="39"/>
-      <c r="M84" s="84"/>
-      <c r="N84" s="84"/>
-      <c r="O84" s="84"/>
-      <c r="P84" s="47"/>
-      <c r="Q84" s="47"/>
-      <c r="R84" s="47"/>
-      <c r="S84" s="47"/>
+      <c r="O84" s="46"/>
       <c r="AI84" s="38"/>
       <c r="AJ84" s="38"/>
-      <c r="AK84" s="51"/>
+      <c r="AK84" s="50"/>
     </row>
     <row r="85" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A85"/>
       <c r="B85"/>
       <c r="C85" s="39"/>
       <c r="D85" s="39"/>
+      <c r="H85" s="46"/>
       <c r="I85"/>
       <c r="J85"/>
       <c r="K85" s="39"/>
       <c r="L85" s="39"/>
+      <c r="O85" s="46"/>
       <c r="AI85" s="38"/>
       <c r="AJ85" s="38"/>
-      <c r="AK85" s="51"/>
+      <c r="AK85" s="50"/>
     </row>
     <row r="86" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A86"/>
       <c r="B86"/>
       <c r="C86" s="39"/>
       <c r="D86" s="39"/>
+      <c r="H86" s="46"/>
       <c r="I86"/>
       <c r="J86"/>
       <c r="K86" s="39"/>
       <c r="L86" s="39"/>
+      <c r="O86" s="46"/>
       <c r="AI86" s="38"/>
       <c r="AJ86" s="38"/>
-      <c r="AK86" s="51"/>
+      <c r="AK86" s="50"/>
     </row>
     <row r="87" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A87"/>
       <c r="B87"/>
       <c r="C87" s="39"/>
       <c r="D87" s="39"/>
-      <c r="H87" s="47"/>
+      <c r="H87" s="46"/>
       <c r="I87"/>
       <c r="J87"/>
       <c r="K87" s="39"/>
       <c r="L87" s="39"/>
-      <c r="O87" s="47"/>
+      <c r="O87" s="46"/>
       <c r="AI87" s="38"/>
       <c r="AJ87" s="38"/>
-      <c r="AK87" s="51"/>
+      <c r="AK87" s="50"/>
     </row>
     <row r="88" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A88"/>
       <c r="B88"/>
       <c r="C88" s="39"/>
       <c r="D88" s="39"/>
-      <c r="H88" s="47"/>
+      <c r="H88" s="46"/>
       <c r="I88"/>
       <c r="J88"/>
       <c r="K88" s="39"/>
       <c r="L88" s="39"/>
-      <c r="O88" s="47"/>
+      <c r="O88" s="46"/>
       <c r="AI88" s="38"/>
       <c r="AJ88" s="38"/>
-      <c r="AK88" s="51"/>
+      <c r="AK88" s="50"/>
     </row>
     <row r="89" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A89"/>
       <c r="B89"/>
       <c r="C89" s="39"/>
       <c r="D89" s="39"/>
-      <c r="H89" s="47"/>
+      <c r="H89" s="46"/>
       <c r="I89"/>
       <c r="J89"/>
       <c r="K89" s="39"/>
       <c r="L89" s="39"/>
-      <c r="O89" s="47"/>
+      <c r="O89" s="46"/>
       <c r="AI89" s="38"/>
       <c r="AJ89" s="38"/>
-      <c r="AK89" s="51"/>
+      <c r="AK89" s="50"/>
     </row>
     <row r="90" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A90"/>
       <c r="B90"/>
       <c r="C90" s="39"/>
       <c r="D90" s="39"/>
-      <c r="H90" s="47"/>
+      <c r="H90" s="46"/>
       <c r="I90"/>
       <c r="J90"/>
       <c r="K90" s="39"/>
       <c r="L90" s="39"/>
-      <c r="O90" s="47"/>
+      <c r="O90" s="46"/>
       <c r="AI90" s="38"/>
       <c r="AJ90" s="38"/>
-      <c r="AK90" s="51"/>
+      <c r="AK90" s="50"/>
     </row>
     <row r="91" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A91"/>
       <c r="B91"/>
       <c r="C91" s="39"/>
       <c r="D91" s="39"/>
-      <c r="H91" s="47"/>
+      <c r="H91" s="46"/>
       <c r="I91"/>
       <c r="J91"/>
       <c r="K91" s="39"/>
       <c r="L91" s="39"/>
-      <c r="O91" s="47"/>
+      <c r="O91" s="46"/>
       <c r="AI91" s="38"/>
       <c r="AJ91" s="38"/>
-      <c r="AK91" s="51"/>
+      <c r="AK91" s="50"/>
     </row>
     <row r="92" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A92"/>
       <c r="B92"/>
       <c r="C92" s="39"/>
       <c r="D92" s="39"/>
-      <c r="H92" s="47"/>
       <c r="I92"/>
       <c r="J92"/>
       <c r="K92" s="39"/>
       <c r="L92" s="39"/>
-      <c r="O92" s="47"/>
       <c r="AI92" s="38"/>
       <c r="AJ92" s="38"/>
-      <c r="AK92" s="51"/>
+      <c r="AK92" s="50"/>
     </row>
     <row r="93" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A93"/>
       <c r="B93"/>
       <c r="C93" s="39"/>
       <c r="D93" s="39"/>
-      <c r="H93" s="47"/>
       <c r="I93"/>
       <c r="J93"/>
       <c r="K93" s="39"/>
       <c r="L93" s="39"/>
-      <c r="O93" s="47"/>
       <c r="AI93" s="38"/>
       <c r="AJ93" s="38"/>
-      <c r="AK93" s="51"/>
+      <c r="AK93" s="50"/>
     </row>
     <row r="94" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A94"/>
       <c r="B94"/>
       <c r="C94" s="39"/>
       <c r="D94" s="39"/>
-      <c r="H94" s="47"/>
       <c r="I94"/>
       <c r="J94"/>
       <c r="K94" s="39"/>
       <c r="L94" s="39"/>
-      <c r="O94" s="47"/>
       <c r="AI94" s="38"/>
       <c r="AJ94" s="38"/>
-      <c r="AK94" s="51"/>
+      <c r="AK94" s="50"/>
     </row>
     <row r="95" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A95"/>
       <c r="B95"/>
       <c r="C95" s="39"/>
       <c r="D95" s="39"/>
-      <c r="H95" s="47"/>
       <c r="I95"/>
       <c r="J95"/>
       <c r="K95" s="39"/>
       <c r="L95" s="39"/>
-      <c r="O95" s="47"/>
       <c r="AI95" s="38"/>
       <c r="AJ95" s="38"/>
-      <c r="AK95" s="51"/>
+      <c r="AK95" s="50"/>
     </row>
     <row r="96" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A96"/>
       <c r="B96"/>
       <c r="C96" s="39"/>
       <c r="D96" s="39"/>
-      <c r="H96" s="47"/>
       <c r="I96"/>
       <c r="J96"/>
       <c r="K96" s="39"/>
       <c r="L96" s="39"/>
-      <c r="O96" s="47"/>
       <c r="AI96" s="38"/>
       <c r="AJ96" s="38"/>
-      <c r="AK96" s="51"/>
+      <c r="AK96" s="50"/>
     </row>
     <row r="97" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A97"/>
       <c r="B97"/>
       <c r="C97" s="39"/>
       <c r="D97" s="39"/>
-      <c r="H97" s="47"/>
       <c r="I97"/>
       <c r="J97"/>
       <c r="K97" s="39"/>
       <c r="L97" s="39"/>
-      <c r="O97" s="47"/>
       <c r="AI97" s="38"/>
       <c r="AJ97" s="38"/>
-      <c r="AK97" s="51"/>
+      <c r="AK97" s="50"/>
     </row>
     <row r="98" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A98"/>
       <c r="B98"/>
       <c r="C98" s="39"/>
       <c r="D98" s="39"/>
-      <c r="H98" s="47"/>
       <c r="I98"/>
       <c r="J98"/>
       <c r="K98" s="39"/>
       <c r="L98" s="39"/>
-      <c r="O98" s="47"/>
       <c r="AI98" s="38"/>
       <c r="AJ98" s="38"/>
-      <c r="AK98" s="51"/>
+      <c r="AK98" s="50"/>
     </row>
     <row r="99" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A99"/>
       <c r="B99"/>
       <c r="C99" s="39"/>
       <c r="D99" s="39"/>
-      <c r="H99" s="47"/>
       <c r="I99"/>
       <c r="J99"/>
       <c r="K99" s="39"/>
       <c r="L99" s="39"/>
-      <c r="O99" s="47"/>
       <c r="AI99" s="38"/>
       <c r="AJ99" s="38"/>
-      <c r="AK99" s="51"/>
+      <c r="AK99" s="50"/>
     </row>
     <row r="100" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A100"/>
       <c r="B100"/>
       <c r="C100" s="39"/>
       <c r="D100" s="39"/>
-      <c r="H100" s="47"/>
       <c r="I100"/>
       <c r="J100"/>
       <c r="K100" s="39"/>
       <c r="L100" s="39"/>
-      <c r="O100" s="47"/>
       <c r="AI100" s="38"/>
       <c r="AJ100" s="38"/>
-      <c r="AK100" s="51"/>
+      <c r="AK100" s="50"/>
     </row>
     <row r="101" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A101"/>
       <c r="B101"/>
       <c r="C101" s="39"/>
       <c r="D101" s="39"/>
-      <c r="H101" s="47"/>
       <c r="I101"/>
       <c r="J101"/>
       <c r="K101" s="39"/>
       <c r="L101" s="39"/>
-      <c r="O101" s="47"/>
       <c r="AI101" s="38"/>
       <c r="AJ101" s="38"/>
-      <c r="AK101" s="51"/>
+      <c r="AK101" s="50"/>
     </row>
     <row r="102" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A102"/>
@@ -6962,7 +6952,7 @@
       <c r="L102" s="39"/>
       <c r="AI102" s="38"/>
       <c r="AJ102" s="38"/>
-      <c r="AK102" s="51"/>
+      <c r="AK102" s="50"/>
     </row>
     <row r="103" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A103"/>
@@ -6975,7 +6965,7 @@
       <c r="L103" s="39"/>
       <c r="AI103" s="38"/>
       <c r="AJ103" s="38"/>
-      <c r="AK103" s="51"/>
+      <c r="AK103" s="50"/>
     </row>
     <row r="104" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A104"/>
@@ -6988,7 +6978,7 @@
       <c r="L104" s="39"/>
       <c r="AI104" s="38"/>
       <c r="AJ104" s="38"/>
-      <c r="AK104" s="51"/>
+      <c r="AK104" s="50"/>
     </row>
     <row r="105" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A105"/>
@@ -7001,7 +6991,7 @@
       <c r="L105" s="39"/>
       <c r="AI105" s="38"/>
       <c r="AJ105" s="38"/>
-      <c r="AK105" s="51"/>
+      <c r="AK105" s="50"/>
     </row>
     <row r="106" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A106"/>
@@ -7014,7 +7004,7 @@
       <c r="L106" s="39"/>
       <c r="AI106" s="38"/>
       <c r="AJ106" s="38"/>
-      <c r="AK106" s="51"/>
+      <c r="AK106" s="50"/>
     </row>
     <row r="107" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A107"/>
@@ -7027,7 +7017,7 @@
       <c r="L107" s="39"/>
       <c r="AI107" s="38"/>
       <c r="AJ107" s="38"/>
-      <c r="AK107" s="51"/>
+      <c r="AK107" s="50"/>
     </row>
     <row r="108" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A108"/>
@@ -7040,7 +7030,7 @@
       <c r="L108" s="39"/>
       <c r="AI108" s="38"/>
       <c r="AJ108" s="38"/>
-      <c r="AK108" s="51"/>
+      <c r="AK108" s="50"/>
     </row>
     <row r="109" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A109"/>
@@ -7053,7 +7043,7 @@
       <c r="L109" s="39"/>
       <c r="AI109" s="38"/>
       <c r="AJ109" s="38"/>
-      <c r="AK109" s="51"/>
+      <c r="AK109" s="50"/>
     </row>
     <row r="110" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A110"/>
@@ -7066,7 +7056,7 @@
       <c r="L110" s="39"/>
       <c r="AI110" s="38"/>
       <c r="AJ110" s="38"/>
-      <c r="AK110" s="51"/>
+      <c r="AK110" s="50"/>
     </row>
     <row r="111" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A111"/>
@@ -7079,7 +7069,7 @@
       <c r="L111" s="39"/>
       <c r="AI111" s="38"/>
       <c r="AJ111" s="38"/>
-      <c r="AK111" s="51"/>
+      <c r="AK111" s="50"/>
     </row>
     <row r="112" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A112"/>
@@ -7092,7 +7082,7 @@
       <c r="L112" s="39"/>
       <c r="AI112" s="38"/>
       <c r="AJ112" s="38"/>
-      <c r="AK112" s="51"/>
+      <c r="AK112" s="50"/>
     </row>
     <row r="113" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A113"/>
@@ -7105,7 +7095,7 @@
       <c r="L113" s="39"/>
       <c r="AI113" s="38"/>
       <c r="AJ113" s="38"/>
-      <c r="AK113" s="51"/>
+      <c r="AK113" s="50"/>
     </row>
     <row r="114" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A114"/>
@@ -7118,7 +7108,7 @@
       <c r="L114" s="39"/>
       <c r="AI114" s="38"/>
       <c r="AJ114" s="38"/>
-      <c r="AK114" s="51"/>
+      <c r="AK114" s="50"/>
     </row>
     <row r="115" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A115"/>
@@ -7131,7 +7121,7 @@
       <c r="L115" s="39"/>
       <c r="AI115" s="38"/>
       <c r="AJ115" s="38"/>
-      <c r="AK115" s="51"/>
+      <c r="AK115" s="50"/>
     </row>
     <row r="116" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A116"/>
@@ -7144,7 +7134,7 @@
       <c r="L116" s="39"/>
       <c r="AI116" s="38"/>
       <c r="AJ116" s="38"/>
-      <c r="AK116" s="51"/>
+      <c r="AK116" s="50"/>
     </row>
     <row r="117" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A117"/>
@@ -7157,7 +7147,7 @@
       <c r="L117" s="39"/>
       <c r="AI117" s="38"/>
       <c r="AJ117" s="38"/>
-      <c r="AK117" s="51"/>
+      <c r="AK117" s="50"/>
     </row>
     <row r="118" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A118"/>
@@ -7170,7 +7160,7 @@
       <c r="L118" s="39"/>
       <c r="AI118" s="38"/>
       <c r="AJ118" s="38"/>
-      <c r="AK118" s="51"/>
+      <c r="AK118" s="50"/>
     </row>
     <row r="119" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A119"/>
@@ -7183,7 +7173,7 @@
       <c r="L119" s="39"/>
       <c r="AI119" s="38"/>
       <c r="AJ119" s="38"/>
-      <c r="AK119" s="51"/>
+      <c r="AK119" s="50"/>
     </row>
     <row r="120" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A120"/>
@@ -7196,269 +7186,139 @@
       <c r="L120" s="39"/>
       <c r="AI120" s="38"/>
       <c r="AJ120" s="38"/>
-      <c r="AK120" s="51"/>
+      <c r="AK120" s="50"/>
     </row>
     <row r="121" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A121"/>
-      <c r="B121"/>
-      <c r="C121" s="39"/>
-      <c r="D121" s="39"/>
-      <c r="I121"/>
-      <c r="J121"/>
-      <c r="K121" s="39"/>
-      <c r="L121" s="39"/>
       <c r="AI121" s="38"/>
       <c r="AJ121" s="38"/>
-      <c r="AK121" s="51"/>
+      <c r="AK121" s="50"/>
     </row>
     <row r="122" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A122"/>
-      <c r="B122"/>
-      <c r="C122" s="39"/>
-      <c r="D122" s="39"/>
-      <c r="I122"/>
-      <c r="J122"/>
-      <c r="K122" s="39"/>
-      <c r="L122" s="39"/>
       <c r="AI122" s="38"/>
       <c r="AJ122" s="38"/>
-      <c r="AK122" s="51"/>
+      <c r="AK122" s="50"/>
     </row>
     <row r="123" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A123"/>
-      <c r="B123"/>
-      <c r="C123" s="39"/>
-      <c r="D123" s="39"/>
-      <c r="I123"/>
-      <c r="J123"/>
-      <c r="K123" s="39"/>
-      <c r="L123" s="39"/>
       <c r="AI123" s="38"/>
       <c r="AJ123" s="38"/>
-      <c r="AK123" s="51"/>
+      <c r="AK123" s="50"/>
     </row>
     <row r="124" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A124"/>
-      <c r="B124"/>
-      <c r="C124" s="39"/>
-      <c r="D124" s="39"/>
-      <c r="I124"/>
-      <c r="J124"/>
-      <c r="K124" s="39"/>
-      <c r="L124" s="39"/>
       <c r="AI124" s="38"/>
       <c r="AJ124" s="38"/>
-      <c r="AK124" s="51"/>
+      <c r="AK124" s="50"/>
     </row>
     <row r="125" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A125"/>
-      <c r="B125"/>
-      <c r="C125" s="39"/>
-      <c r="D125" s="39"/>
-      <c r="I125"/>
-      <c r="J125"/>
-      <c r="K125" s="39"/>
-      <c r="L125" s="39"/>
       <c r="AI125" s="38"/>
       <c r="AJ125" s="38"/>
-      <c r="AK125" s="51"/>
+      <c r="AK125" s="50"/>
     </row>
     <row r="126" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A126"/>
-      <c r="B126"/>
-      <c r="C126" s="39"/>
-      <c r="D126" s="39"/>
-      <c r="I126"/>
-      <c r="J126"/>
-      <c r="K126" s="39"/>
-      <c r="L126" s="39"/>
       <c r="AI126" s="38"/>
       <c r="AJ126" s="38"/>
-      <c r="AK126" s="51"/>
+      <c r="AK126" s="50"/>
     </row>
     <row r="127" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A127"/>
-      <c r="B127"/>
-      <c r="C127" s="39"/>
-      <c r="D127" s="39"/>
-      <c r="I127"/>
-      <c r="J127"/>
-      <c r="K127" s="39"/>
-      <c r="L127" s="39"/>
       <c r="AI127" s="38"/>
       <c r="AJ127" s="38"/>
-      <c r="AK127" s="51"/>
+      <c r="AK127" s="50"/>
     </row>
     <row r="128" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A128"/>
-      <c r="B128"/>
-      <c r="C128" s="39"/>
-      <c r="D128" s="39"/>
-      <c r="I128"/>
-      <c r="J128"/>
-      <c r="K128" s="39"/>
-      <c r="L128" s="39"/>
       <c r="AI128" s="38"/>
       <c r="AJ128" s="38"/>
-      <c r="AK128" s="51"/>
-    </row>
-    <row r="129" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A129"/>
-      <c r="B129"/>
-      <c r="C129" s="39"/>
-      <c r="D129" s="39"/>
-      <c r="I129"/>
-      <c r="J129"/>
-      <c r="K129" s="39"/>
-      <c r="L129" s="39"/>
+      <c r="AK128" s="50"/>
+    </row>
+    <row r="129" spans="35:37" x14ac:dyDescent="0.25">
       <c r="AI129" s="38"/>
       <c r="AJ129" s="38"/>
-      <c r="AK129" s="51"/>
-    </row>
-    <row r="130" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A130"/>
-      <c r="B130"/>
-      <c r="C130" s="39"/>
-      <c r="D130" s="39"/>
-      <c r="I130"/>
-      <c r="J130"/>
-      <c r="K130" s="39"/>
-      <c r="L130" s="39"/>
+      <c r="AK129" s="50"/>
+    </row>
+    <row r="130" spans="35:37" x14ac:dyDescent="0.25">
       <c r="AI130" s="38"/>
       <c r="AJ130" s="38"/>
-      <c r="AK130" s="51"/>
-    </row>
-    <row r="131" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A131"/>
+      <c r="AK130" s="50"/>
+    </row>
+    <row r="131" spans="35:37" x14ac:dyDescent="0.25">
       <c r="AI131" s="38"/>
       <c r="AJ131" s="38"/>
-      <c r="AK131" s="51"/>
-    </row>
-    <row r="132" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A132"/>
+      <c r="AK131" s="50"/>
+    </row>
+    <row r="132" spans="35:37" x14ac:dyDescent="0.25">
       <c r="AI132" s="38"/>
       <c r="AJ132" s="38"/>
-      <c r="AK132" s="51"/>
-    </row>
-    <row r="133" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK132" s="50"/>
+    </row>
+    <row r="133" spans="35:37" x14ac:dyDescent="0.25">
       <c r="AI133" s="38"/>
       <c r="AJ133" s="38"/>
-      <c r="AK133" s="51"/>
-    </row>
-    <row r="134" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK133" s="50"/>
+    </row>
+    <row r="134" spans="35:37" x14ac:dyDescent="0.25">
       <c r="AI134" s="38"/>
       <c r="AJ134" s="38"/>
-      <c r="AK134" s="51"/>
-    </row>
-    <row r="135" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK134" s="50"/>
+    </row>
+    <row r="135" spans="35:37" x14ac:dyDescent="0.25">
       <c r="AI135" s="38"/>
       <c r="AJ135" s="38"/>
-      <c r="AK135" s="51"/>
-    </row>
-    <row r="136" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK135" s="50"/>
+    </row>
+    <row r="136" spans="35:37" x14ac:dyDescent="0.25">
       <c r="AI136" s="38"/>
       <c r="AJ136" s="38"/>
-      <c r="AK136" s="51"/>
-    </row>
-    <row r="137" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK136" s="50"/>
+    </row>
+    <row r="137" spans="35:37" x14ac:dyDescent="0.25">
       <c r="AI137" s="38"/>
       <c r="AJ137" s="38"/>
-      <c r="AK137" s="51"/>
-    </row>
-    <row r="138" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK137" s="50"/>
+    </row>
+    <row r="138" spans="35:37" x14ac:dyDescent="0.25">
       <c r="AI138" s="38"/>
       <c r="AJ138" s="38"/>
-      <c r="AK138" s="51"/>
-    </row>
-    <row r="139" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK138" s="50"/>
+    </row>
+    <row r="139" spans="35:37" x14ac:dyDescent="0.25">
       <c r="AI139" s="38"/>
       <c r="AJ139" s="38"/>
-      <c r="AK139" s="51"/>
-    </row>
-    <row r="140" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK139" s="50"/>
+    </row>
+    <row r="140" spans="35:37" x14ac:dyDescent="0.25">
       <c r="AI140" s="38"/>
       <c r="AJ140" s="38"/>
-      <c r="AK140" s="51"/>
-    </row>
-    <row r="141" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK140" s="50"/>
+    </row>
+    <row r="141" spans="35:37" x14ac:dyDescent="0.25">
       <c r="AI141" s="38"/>
       <c r="AJ141" s="38"/>
-      <c r="AK141" s="51"/>
-    </row>
-    <row r="142" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK141" s="50"/>
+    </row>
+    <row r="142" spans="35:37" x14ac:dyDescent="0.25">
       <c r="AI142" s="38"/>
       <c r="AJ142" s="38"/>
-      <c r="AK142" s="51"/>
-    </row>
-    <row r="143" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK142" s="50"/>
+    </row>
+    <row r="143" spans="35:37" x14ac:dyDescent="0.25">
       <c r="AI143" s="38"/>
       <c r="AJ143" s="38"/>
-      <c r="AK143" s="51"/>
-    </row>
-    <row r="144" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK143" s="50"/>
+    </row>
+    <row r="144" spans="35:37" x14ac:dyDescent="0.25">
       <c r="AI144" s="38"/>
       <c r="AJ144" s="38"/>
-      <c r="AK144" s="51"/>
+      <c r="AK144" s="50"/>
     </row>
     <row r="145" spans="35:37" x14ac:dyDescent="0.25">
       <c r="AI145" s="38"/>
       <c r="AJ145" s="38"/>
-      <c r="AK145" s="51"/>
+      <c r="AK145" s="50"/>
     </row>
     <row r="146" spans="35:37" x14ac:dyDescent="0.25">
       <c r="AI146" s="38"/>
       <c r="AJ146" s="38"/>
-      <c r="AK146" s="51"/>
-    </row>
-    <row r="147" spans="35:37" x14ac:dyDescent="0.25">
-      <c r="AI147" s="38"/>
-      <c r="AJ147" s="38"/>
-      <c r="AK147" s="51"/>
-    </row>
-    <row r="148" spans="35:37" x14ac:dyDescent="0.25">
-      <c r="AI148" s="38"/>
-      <c r="AJ148" s="38"/>
-      <c r="AK148" s="51"/>
-    </row>
-    <row r="149" spans="35:37" x14ac:dyDescent="0.25">
-      <c r="AI149" s="38"/>
-      <c r="AJ149" s="38"/>
-      <c r="AK149" s="51"/>
-    </row>
-    <row r="150" spans="35:37" x14ac:dyDescent="0.25">
-      <c r="AI150" s="38"/>
-      <c r="AJ150" s="38"/>
-      <c r="AK150" s="51"/>
-    </row>
-    <row r="151" spans="35:37" x14ac:dyDescent="0.25">
-      <c r="AI151" s="38"/>
-      <c r="AJ151" s="38"/>
-      <c r="AK151" s="51"/>
-    </row>
-    <row r="152" spans="35:37" x14ac:dyDescent="0.25">
-      <c r="AI152" s="38"/>
-      <c r="AJ152" s="38"/>
-      <c r="AK152" s="51"/>
-    </row>
-    <row r="153" spans="35:37" x14ac:dyDescent="0.25">
-      <c r="AI153" s="38"/>
-      <c r="AJ153" s="38"/>
-      <c r="AK153" s="51"/>
-    </row>
-    <row r="154" spans="35:37" x14ac:dyDescent="0.25">
-      <c r="AI154" s="38"/>
-      <c r="AJ154" s="38"/>
-      <c r="AK154" s="51"/>
-    </row>
-    <row r="155" spans="35:37" x14ac:dyDescent="0.25">
-      <c r="AI155" s="38"/>
-      <c r="AJ155" s="38"/>
-      <c r="AK155" s="51"/>
-    </row>
-    <row r="156" spans="35:37" x14ac:dyDescent="0.25">
-      <c r="AI156" s="38"/>
-      <c r="AJ156" s="38"/>
-      <c r="AK156" s="51"/>
+      <c r="AK146" s="50"/>
     </row>
   </sheetData>
   <phoneticPr fontId="24" type="noConversion"/>

--- a/SubRES_TMPL/SubRES_NewTechs.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C62061C-1AE3-4F1E-8A7E-5B49CEE382C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E782074-86D5-4F0F-9E00-D8D4BDACB17E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PRI_Sector_Fuels" sheetId="6" r:id="rId1"/>
@@ -343,7 +343,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J23" authorId="2" shapeId="0" xr:uid="{08A0A247-5B70-4F6A-BE7F-DF9684B12478}">
+    <comment ref="J14" authorId="2" shapeId="0" xr:uid="{08A0A247-5B70-4F6A-BE7F-DF9684B12478}">
       <text>
         <r>
           <rPr>
@@ -390,7 +390,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T23" authorId="2" shapeId="0" xr:uid="{89F66F35-9E7D-4CFE-82E2-FED540200A65}">
+    <comment ref="T14" authorId="2" shapeId="0" xr:uid="{89F66F35-9E7D-4CFE-82E2-FED540200A65}">
       <text>
         <r>
           <rPr>
@@ -483,7 +483,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U23" authorId="1" shapeId="0" xr:uid="{BFBE1E56-B2CF-4342-9D18-7A5625043F27}">
+    <comment ref="U14" authorId="1" shapeId="0" xr:uid="{BFBE1E56-B2CF-4342-9D18-7A5625043F27}">
       <text>
         <r>
           <rPr>
@@ -508,7 +508,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V23" authorId="2" shapeId="0" xr:uid="{32A4C634-AF1C-4AC8-8B25-E2B72657AC1B}">
+    <comment ref="V14" authorId="2" shapeId="0" xr:uid="{32A4C634-AF1C-4AC8-8B25-E2B72657AC1B}">
       <text>
         <r>
           <rPr>
@@ -571,7 +571,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N24" authorId="2" shapeId="0" xr:uid="{CC49012E-D54F-4799-8BAE-EA97B5C3A29A}">
+    <comment ref="N15" authorId="2" shapeId="0" xr:uid="{CC49012E-D54F-4799-8BAE-EA97B5C3A29A}">
       <text>
         <r>
           <rPr>
@@ -1125,7 +1125,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB13" authorId="2" shapeId="0" xr:uid="{5EE58488-723F-4683-9026-2F0EE70F8071}">
+    <comment ref="AB14" authorId="2" shapeId="0" xr:uid="{5EE58488-723F-4683-9026-2F0EE70F8071}">
       <text>
         <r>
           <rPr>
@@ -1218,7 +1218,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC13" authorId="1" shapeId="0" xr:uid="{308E9284-8F99-498B-A3DD-262799AF67EB}">
+    <comment ref="AC14" authorId="1" shapeId="0" xr:uid="{308E9284-8F99-498B-A3DD-262799AF67EB}">
       <text>
         <r>
           <rPr>
@@ -1243,7 +1243,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AD13" authorId="2" shapeId="0" xr:uid="{FD29F772-15B8-47C4-8D7A-88CCF8F71647}">
+    <comment ref="AD14" authorId="2" shapeId="0" xr:uid="{FD29F772-15B8-47C4-8D7A-88CCF8F71647}">
       <text>
         <r>
           <rPr>
@@ -1306,7 +1306,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V14" authorId="2" shapeId="0" xr:uid="{BAA0F8AB-741B-4302-9E54-000CB5DC4ACF}">
+    <comment ref="V15" authorId="2" shapeId="0" xr:uid="{BAA0F8AB-741B-4302-9E54-000CB5DC4ACF}">
       <text>
         <r>
           <rPr>
@@ -1823,9 +1823,6 @@
     <t>DayNite</t>
   </si>
   <si>
-    <t>Natural Gas/Domestic</t>
-  </si>
-  <si>
     <t>WNDTRBN</t>
   </si>
   <si>
@@ -1998,6 +1995,9 @@
   </si>
   <si>
     <t>BIOPOWER</t>
+  </si>
+  <si>
+    <t>Natural Gas-Domestic</t>
   </si>
 </sst>
 </file>
@@ -2513,13 +2513,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>129540</xdr:colOff>
-      <xdr:row>55</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>137160</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
       <xdr:colOff>133299</xdr:colOff>
-      <xdr:row>64</xdr:row>
+      <xdr:row>55</xdr:row>
       <xdr:rowOff>45720</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2908,7 +2908,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F289C8C-2E2A-4CC1-9EB1-31AFA36FA445}">
-  <dimension ref="A1:W67"/>
+  <dimension ref="A1:W58"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" bestFit="1" customWidth="1"/>
@@ -2962,7 +2962,7 @@
         <v>58</v>
       </c>
       <c r="F2" s="72" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G2" s="14"/>
       <c r="N2" s="6" t="s">
@@ -2988,7 +2988,7 @@
         <v>58</v>
       </c>
       <c r="F3" s="72" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G3" s="14"/>
       <c r="N3" s="8" t="s">
@@ -3030,7 +3030,7 @@
         <v>58</v>
       </c>
       <c r="F4" s="72" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G4" s="14"/>
       <c r="N4" s="13" t="s">
@@ -3072,7 +3072,7 @@
         <v>58</v>
       </c>
       <c r="F5" s="72" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G5" s="14"/>
       <c r="N5" s="39" t="s">
@@ -3109,7 +3109,7 @@
         <v>67</v>
       </c>
       <c r="Q6" s="39" t="s">
-        <v>89</v>
+        <v>147</v>
       </c>
       <c r="R6" s="39" t="s">
         <v>58</v>
@@ -3135,7 +3135,7 @@
         <v>72</v>
       </c>
       <c r="Q7" s="12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="R7" s="12" t="s">
         <v>58</v>
@@ -3159,10 +3159,10 @@
       </c>
       <c r="O8" s="37"/>
       <c r="P8" s="37" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q8" s="37" t="s">
         <v>126</v>
-      </c>
-      <c r="Q8" s="37" t="s">
-        <v>127</v>
       </c>
       <c r="R8" s="37" t="s">
         <v>58</v>
@@ -3193,579 +3193,576 @@
       <c r="V9" s="12"/>
     </row>
     <row r="10" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="N10" s="14"/>
-      <c r="O10" s="14"/>
-      <c r="P10" s="14"/>
-      <c r="Q10" s="14"/>
-      <c r="R10" s="14"/>
-      <c r="S10" s="12"/>
-      <c r="T10" s="12"/>
-      <c r="U10" s="12"/>
-      <c r="V10" s="12"/>
-    </row>
-    <row r="11" spans="2:22" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="L11"/>
-      <c r="M11"/>
-      <c r="N11"/>
-      <c r="O11"/>
-      <c r="P11"/>
-      <c r="Q11"/>
-      <c r="R11"/>
-      <c r="S11" s="12"/>
-      <c r="T11" s="12"/>
-      <c r="U11" s="12"/>
-      <c r="V11" s="12"/>
-    </row>
-    <row r="12" spans="2:22" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="L12"/>
-      <c r="M12"/>
-      <c r="N12"/>
-      <c r="O12"/>
-      <c r="P12"/>
-      <c r="Q12"/>
-      <c r="R12"/>
-      <c r="S12" s="12"/>
-      <c r="T12" s="7"/>
-      <c r="U12" s="7"/>
-      <c r="V12" s="7"/>
-    </row>
-    <row r="13" spans="2:22" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B13"/>
-      <c r="C13"/>
-      <c r="D13"/>
-      <c r="E13"/>
-      <c r="F13"/>
-      <c r="G13"/>
-      <c r="H13"/>
-      <c r="L13"/>
-      <c r="M13"/>
-      <c r="N13"/>
-      <c r="O13"/>
-      <c r="P13"/>
-      <c r="Q13"/>
-      <c r="R13"/>
-      <c r="S13"/>
-      <c r="T13"/>
-      <c r="U13"/>
-      <c r="V13"/>
-    </row>
-    <row r="14" spans="2:22" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B14"/>
-      <c r="C14"/>
-      <c r="D14"/>
-      <c r="E14"/>
-      <c r="F14"/>
-      <c r="G14"/>
-      <c r="H14"/>
-      <c r="L14"/>
-      <c r="M14"/>
-      <c r="N14" s="7"/>
-      <c r="O14" s="10"/>
-      <c r="P14" s="7"/>
-      <c r="Q14" s="7"/>
-      <c r="R14" s="7"/>
-      <c r="S14" s="7"/>
-      <c r="T14" s="7"/>
-      <c r="U14" s="7"/>
-      <c r="V14" s="7"/>
-    </row>
-    <row r="15" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="N15" s="7"/>
-      <c r="O15" s="10"/>
-      <c r="P15" s="7"/>
-      <c r="Q15" s="7"/>
-      <c r="R15" s="7"/>
-      <c r="S15" s="7"/>
-      <c r="T15" s="7"/>
-      <c r="U15" s="7"/>
-      <c r="V15" s="7"/>
-    </row>
-    <row r="16" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="N16" s="7"/>
-      <c r="O16" s="10"/>
-      <c r="P16" s="7"/>
-      <c r="Q16" s="7"/>
-      <c r="R16" s="7"/>
-      <c r="S16" s="7"/>
-      <c r="T16" s="7"/>
-      <c r="U16" s="7"/>
-      <c r="V16" s="7"/>
-    </row>
-    <row r="17" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="N17" s="7"/>
-      <c r="O17" s="10"/>
-      <c r="P17" s="7"/>
-      <c r="Q17" s="7"/>
-      <c r="R17" s="7"/>
-      <c r="S17" s="7"/>
-      <c r="T17" s="7"/>
-      <c r="U17" s="7"/>
-      <c r="V17" s="7"/>
-    </row>
-    <row r="18" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="N18" s="7"/>
-      <c r="O18" s="10"/>
-      <c r="P18" s="7"/>
-      <c r="Q18" s="7"/>
-      <c r="R18" s="7"/>
-      <c r="S18" s="7"/>
-      <c r="T18" s="7"/>
-      <c r="U18" s="7"/>
-      <c r="V18" s="7"/>
-    </row>
-    <row r="19" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="N19" s="7"/>
-      <c r="O19" s="10"/>
-      <c r="P19" s="7"/>
-      <c r="Q19" s="7"/>
-      <c r="R19" s="7"/>
-      <c r="S19" s="7"/>
-      <c r="T19" s="7"/>
-      <c r="U19" s="7"/>
-      <c r="V19" s="7"/>
-    </row>
-    <row r="20" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="N20" s="7"/>
-      <c r="O20" s="10"/>
-      <c r="P20" s="7"/>
-      <c r="Q20" s="7"/>
-      <c r="R20" s="7"/>
-      <c r="S20" s="7"/>
-      <c r="T20" s="7"/>
-      <c r="U20" s="7"/>
-      <c r="V20" s="7"/>
-    </row>
-    <row r="21" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="N21" s="1"/>
-      <c r="P21" s="1"/>
-      <c r="Q21" s="1"/>
-      <c r="R21" s="1"/>
-      <c r="S21" s="1"/>
-      <c r="T21" s="1"/>
-      <c r="U21" s="1"/>
-      <c r="V21" s="1"/>
-    </row>
-    <row r="22" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="F22" s="2" t="s">
+      <c r="N10" s="7"/>
+      <c r="O10" s="10"/>
+      <c r="P10" s="7"/>
+      <c r="Q10" s="7"/>
+      <c r="R10" s="7"/>
+      <c r="S10" s="7"/>
+      <c r="T10" s="7"/>
+      <c r="U10" s="7"/>
+      <c r="V10" s="7"/>
+    </row>
+    <row r="11" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="N11" s="7"/>
+      <c r="O11" s="10"/>
+      <c r="P11" s="7"/>
+      <c r="Q11" s="7"/>
+      <c r="R11" s="7"/>
+      <c r="S11" s="7"/>
+      <c r="T11" s="7"/>
+      <c r="U11" s="7"/>
+      <c r="V11" s="7"/>
+    </row>
+    <row r="12" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="N12" s="1"/>
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1"/>
+      <c r="R12" s="1"/>
+      <c r="S12" s="1"/>
+      <c r="T12" s="1"/>
+      <c r="U12" s="1"/>
+      <c r="V12" s="1"/>
+    </row>
+    <row r="13" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="F13" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="G22" s="2"/>
-      <c r="N22" s="6" t="s">
+      <c r="G13" s="2"/>
+      <c r="N13" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="O22" s="6"/>
-      <c r="P22" s="10"/>
-      <c r="Q22" s="10"/>
-      <c r="R22" s="10"/>
-      <c r="S22" s="10"/>
-      <c r="T22" s="10"/>
-      <c r="U22" s="10"/>
-      <c r="V22" s="10"/>
-    </row>
-    <row r="23" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B23" s="15" t="s">
+      <c r="O13" s="6"/>
+      <c r="P13" s="10"/>
+      <c r="Q13" s="10"/>
+      <c r="R13" s="10"/>
+      <c r="S13" s="10"/>
+      <c r="T13" s="10"/>
+      <c r="U13" s="10"/>
+      <c r="V13" s="10"/>
+    </row>
+    <row r="14" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B14" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C23" s="16" t="s">
+      <c r="C14" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D23" s="15" t="s">
+      <c r="D14" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E23" s="15" t="s">
+      <c r="E14" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="F23" s="15" t="s">
+      <c r="F14" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="G23" s="15" t="s">
+      <c r="G14" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="H23" s="17" t="s">
+      <c r="H14" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="I23" s="17" t="s">
+      <c r="I14" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="J23" s="17" t="s">
+      <c r="J14" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="K23" s="17" t="s">
+      <c r="K14" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="N23" s="8" t="s">
+      <c r="N14" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="O23" s="9" t="s">
+      <c r="O14" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="P23" s="8" t="s">
+      <c r="P14" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="Q23" s="8" t="s">
+      <c r="Q14" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="R23" s="8" t="s">
+      <c r="R14" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="S23" s="8" t="s">
+      <c r="S14" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="T23" s="8" t="s">
+      <c r="T14" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="U23" s="8" t="s">
+      <c r="U14" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="V23" s="8" t="s">
+      <c r="V14" s="8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="2:22" ht="21.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="18" t="s">
+    <row r="15" spans="2:22" ht="21.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="C24" s="18" t="s">
+      <c r="C15" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="D24" s="18" t="s">
+      <c r="D15" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="E24" s="18" t="s">
+      <c r="E15" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="F24" s="18" t="s">
+      <c r="F15" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="G24" s="18" t="s">
+      <c r="G15" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="H24" s="18" t="s">
+      <c r="H15" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="I24" s="18" t="s">
+      <c r="I15" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="J24" s="18" t="s">
+      <c r="J15" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="K24" s="19" t="s">
+      <c r="K15" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="N24" s="13" t="s">
+      <c r="N15" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="O24" s="13" t="s">
+      <c r="O15" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="P24" s="13" t="s">
+      <c r="P15" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="Q24" s="13" t="s">
+      <c r="Q15" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="R24" s="13" t="s">
+      <c r="R15" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="S24" s="13" t="s">
+      <c r="S15" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="T24" s="13" t="s">
+      <c r="T15" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="U24" s="13" t="s">
+      <c r="U15" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="V24" s="13" t="s">
+      <c r="V15" s="13" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="2:22" ht="21.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="18" t="s">
+    <row r="16" spans="2:22" ht="21.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="C25" s="20"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="20" t="s">
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="I25" s="20" t="s">
-        <v>115</v>
-      </c>
-      <c r="J25" s="20" t="s">
+      <c r="I16" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="J16" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="K25" s="21"/>
-      <c r="N25" s="13" t="s">
+      <c r="K16" s="21"/>
+      <c r="N16" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="O25" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="P25" s="22"/>
-      <c r="Q25" s="22"/>
-      <c r="R25" s="22"/>
-      <c r="S25" s="22"/>
-      <c r="T25" s="22"/>
-      <c r="U25" s="22"/>
-      <c r="V25" s="22"/>
-    </row>
-    <row r="26" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B26" s="7" t="str">
-        <f>P26</f>
+      <c r="O16" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="P16" s="22"/>
+      <c r="Q16" s="22"/>
+      <c r="R16" s="22"/>
+      <c r="S16" s="22"/>
+      <c r="T16" s="22"/>
+      <c r="U16" s="22"/>
+      <c r="V16" s="22"/>
+    </row>
+    <row r="17" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B17" s="7" t="str">
+        <f>P17</f>
         <v>MINBIO</v>
       </c>
-      <c r="C26" s="10"/>
-      <c r="D26" s="7" t="str">
+      <c r="C17" s="10"/>
+      <c r="D17" s="7" t="str">
         <f>P5</f>
         <v>MANBIOMIN</v>
       </c>
-      <c r="E26" s="1">
+      <c r="E17" s="1">
         <v>2030</v>
       </c>
-      <c r="F26" s="1">
+      <c r="F17" s="1">
         <v>1</v>
       </c>
-      <c r="G26" s="1">
+      <c r="G17" s="1">
         <v>1</v>
       </c>
-      <c r="H26" s="1">
+      <c r="H17" s="1">
         <v>50</v>
       </c>
-      <c r="I26" s="24">
+      <c r="I17" s="24">
         <v>17.166319999999999</v>
       </c>
-      <c r="J26" s="25"/>
-      <c r="K26" s="26">
+      <c r="J17" s="25"/>
+      <c r="K17" s="26">
         <v>8.76</v>
       </c>
-      <c r="N26" s="38" t="s">
+      <c r="N17" s="38" t="s">
         <v>64</v>
       </c>
-      <c r="O26" s="38"/>
-      <c r="P26" s="39" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q26" s="40" t="str">
+      <c r="O17" s="38"/>
+      <c r="P17" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q17" s="40" t="str">
         <f>"Domestic Supply of "&amp;$D$4&amp;" "</f>
         <v xml:space="preserve">Domestic Supply of Biomass </v>
       </c>
-      <c r="R26" s="38" t="s">
+      <c r="R17" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="S26" s="38"/>
-      <c r="T26" s="12" t="s">
+      <c r="S17" s="38"/>
+      <c r="T17" s="12" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="27" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B27" s="7" t="str">
-        <f>P27</f>
+    <row r="18" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B18" s="7" t="str">
+        <f>P18</f>
         <v>MINGAS</v>
       </c>
-      <c r="C27" s="10"/>
-      <c r="D27" s="7" t="str">
+      <c r="C18" s="10"/>
+      <c r="D18" s="7" t="str">
         <f>P6</f>
         <v>MANGASMIN</v>
       </c>
-      <c r="E27" s="1">
+      <c r="E18" s="1">
         <v>2030</v>
       </c>
-      <c r="F27" s="1">
+      <c r="F18" s="1">
         <v>1</v>
       </c>
-      <c r="G27" s="1">
+      <c r="G18" s="1">
         <v>1</v>
       </c>
-      <c r="H27" s="1">
+      <c r="H18" s="1">
         <v>50</v>
       </c>
-      <c r="I27" s="28">
+      <c r="I18" s="28">
         <v>33.817659999999997</v>
       </c>
-      <c r="J27" s="29"/>
-      <c r="K27" s="26">
+      <c r="J18" s="29"/>
+      <c r="K18" s="26">
         <v>8.76</v>
       </c>
-      <c r="N27" s="38" t="s">
+      <c r="N18" s="38" t="s">
         <v>64</v>
       </c>
-      <c r="O27" s="38"/>
-      <c r="P27" s="39" t="s">
-        <v>107</v>
-      </c>
-      <c r="Q27" s="40" t="str">
+      <c r="O18" s="38"/>
+      <c r="P18" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q18" s="40" t="str">
         <f>"Domestic Supply of "&amp;$D$5&amp;" "</f>
         <v xml:space="preserve">Domestic Supply of Ngas </v>
       </c>
-      <c r="R27" s="38" t="s">
+      <c r="R18" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="S27" s="38"/>
-      <c r="T27" s="12" t="s">
+      <c r="S18" s="38"/>
+      <c r="T18" s="12" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="28" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B28" s="7" t="str">
-        <f t="shared" ref="B28:B29" si="0">P28</f>
+    <row r="19" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B19" s="7" t="str">
+        <f t="shared" ref="B19:B20" si="0">P19</f>
         <v>MINWIND</v>
       </c>
-      <c r="C28" s="10"/>
-      <c r="D28" s="7" t="str">
-        <f t="shared" ref="D28:D29" si="1">P7</f>
+      <c r="C19" s="10"/>
+      <c r="D19" s="7" t="str">
+        <f t="shared" ref="D19:D20" si="1">P7</f>
         <v>WIND</v>
       </c>
-      <c r="E28" s="1">
+      <c r="E19" s="1">
         <v>2030</v>
       </c>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1">
+      <c r="F19" s="1"/>
+      <c r="G19" s="1">
         <v>1</v>
       </c>
-      <c r="H28" s="1">
+      <c r="H19" s="1">
         <v>100</v>
       </c>
-      <c r="I28" s="1">
+      <c r="I19" s="1">
         <v>0</v>
       </c>
-      <c r="K28" s="26">
+      <c r="K19" s="26">
         <v>8.76</v>
       </c>
-      <c r="N28" s="38" t="s">
+      <c r="N19" s="38" t="s">
         <v>64</v>
       </c>
-      <c r="P28" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="Q28" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="R28" s="38" t="s">
+      <c r="P19" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="R19" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="S28" s="38"/>
-      <c r="T28" s="12" t="s">
+      <c r="S19" s="38"/>
+      <c r="T19" s="12" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="29" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B29" s="7" t="str">
+    <row r="20" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B20" s="7" t="str">
         <f t="shared" si="0"/>
         <v>MINSOLAR</v>
       </c>
-      <c r="C29" s="10"/>
-      <c r="D29" s="7" t="str">
+      <c r="C20" s="10"/>
+      <c r="D20" s="7" t="str">
         <f t="shared" si="1"/>
         <v>SOLAR</v>
       </c>
-      <c r="E29" s="1">
+      <c r="E20" s="1">
         <v>2030</v>
       </c>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1">
+      <c r="F20" s="1"/>
+      <c r="G20" s="1">
         <v>1</v>
       </c>
-      <c r="H29" s="1">
+      <c r="H20" s="1">
         <v>100</v>
       </c>
-      <c r="I29" s="1">
+      <c r="I20" s="1">
         <v>0</v>
       </c>
-      <c r="K29" s="26">
+      <c r="K20" s="26">
         <v>8.76</v>
       </c>
-      <c r="N29" s="38" t="s">
+      <c r="N20" s="38" t="s">
         <v>64</v>
       </c>
-      <c r="O29" s="14"/>
-      <c r="P29" s="14" t="s">
+      <c r="O20" s="14"/>
+      <c r="P20" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q20" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="Q29" s="14" t="s">
-        <v>130</v>
-      </c>
-      <c r="R29" s="38" t="s">
+      <c r="R20" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="S29" s="38"/>
-      <c r="T29" s="12" t="s">
+      <c r="S20" s="38"/>
+      <c r="T20" s="12" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="30" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B30" s="7"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="N30" s="14"/>
-      <c r="O30" s="14"/>
-      <c r="P30" s="14"/>
-      <c r="Q30" s="14"/>
-      <c r="R30" s="38"/>
-      <c r="S30" s="38"/>
-      <c r="T30" s="38"/>
-    </row>
-    <row r="31" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B31" s="7"/>
-      <c r="C31" s="10"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="N31" s="14"/>
-      <c r="O31" s="14"/>
-      <c r="P31" s="14"/>
-      <c r="Q31" s="14"/>
-      <c r="R31" s="38"/>
-      <c r="S31" s="38"/>
-      <c r="T31" s="38"/>
-    </row>
-    <row r="32" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B32" s="7"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="N32" s="14"/>
-      <c r="O32" s="14"/>
-      <c r="P32" s="14"/>
-      <c r="Q32" s="14"/>
-      <c r="R32" s="38"/>
-      <c r="S32" s="38"/>
-      <c r="T32" s="38"/>
+    <row r="21" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B21" s="7"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="N21" s="14"/>
+      <c r="O21" s="14"/>
+      <c r="P21" s="14"/>
+      <c r="Q21" s="14"/>
+      <c r="R21" s="38"/>
+      <c r="S21" s="38"/>
+      <c r="T21" s="38"/>
+    </row>
+    <row r="22" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B22" s="7"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="N22" s="14"/>
+      <c r="O22" s="14"/>
+      <c r="P22" s="14"/>
+      <c r="Q22" s="14"/>
+      <c r="R22" s="38"/>
+      <c r="S22" s="38"/>
+      <c r="T22" s="38"/>
+    </row>
+    <row r="23" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B23" s="7"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="N23" s="14"/>
+      <c r="O23" s="14"/>
+      <c r="P23" s="14"/>
+      <c r="Q23" s="14"/>
+      <c r="R23" s="38"/>
+      <c r="S23" s="38"/>
+      <c r="T23" s="38"/>
+    </row>
+    <row r="24" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B24" s="7"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="N24" s="14"/>
+      <c r="O24" s="14"/>
+      <c r="P24" s="14"/>
+      <c r="Q24" s="14"/>
+      <c r="R24" s="38"/>
+      <c r="S24" s="38"/>
+      <c r="T24" s="38"/>
+    </row>
+    <row r="25" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B25" s="7"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="P25" s="1"/>
+      <c r="Q25" s="1"/>
+      <c r="R25" s="38"/>
+      <c r="S25" s="38"/>
+      <c r="T25" s="38"/>
+    </row>
+    <row r="26" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B26" s="7"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="P26" s="1"/>
+      <c r="Q26" s="1"/>
+      <c r="R26" s="38"/>
+      <c r="S26" s="38"/>
+      <c r="T26" s="38"/>
+    </row>
+    <row r="27" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B27" s="7"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="N27" s="1"/>
+      <c r="P27" s="1"/>
+      <c r="Q27" s="1"/>
+      <c r="R27" s="38"/>
+      <c r="S27" s="38"/>
+      <c r="T27" s="38"/>
+    </row>
+    <row r="28" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="N28" s="1"/>
+      <c r="P28" s="1"/>
+      <c r="Q28" s="1"/>
+    </row>
+    <row r="29" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
+      <c r="N29" s="1"/>
+      <c r="P29" s="1"/>
+      <c r="Q29" s="1"/>
+      <c r="R29" s="14"/>
+      <c r="S29" s="14"/>
+      <c r="T29" s="14"/>
+    </row>
+    <row r="30" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+      <c r="N30" s="1"/>
+      <c r="P30" s="1"/>
+      <c r="Q30" s="1"/>
+      <c r="R30" s="14"/>
+      <c r="S30" s="14"/>
+      <c r="T30" s="14"/>
+    </row>
+    <row r="31" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B31" s="12"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="14"/>
+      <c r="N31" s="1"/>
+      <c r="P31" s="1"/>
+      <c r="Q31" s="1"/>
+      <c r="R31" s="14"/>
+      <c r="S31" s="14"/>
+      <c r="T31" s="14"/>
+    </row>
+    <row r="32" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B32" s="12"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
+      <c r="H32" s="14"/>
+      <c r="N32" s="1"/>
+      <c r="P32" s="1"/>
+      <c r="Q32" s="1"/>
+      <c r="R32" s="14"/>
+      <c r="S32" s="14"/>
+      <c r="T32" s="14"/>
     </row>
     <row r="33" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B33" s="7"/>
-      <c r="C33" s="10"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
-      <c r="N33" s="14"/>
-      <c r="O33" s="14"/>
-      <c r="P33" s="14"/>
-      <c r="Q33" s="14"/>
-      <c r="R33" s="38"/>
-      <c r="S33" s="38"/>
-      <c r="T33" s="38"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
+      <c r="H33" s="14"/>
+      <c r="N33" s="1"/>
+      <c r="P33" s="1"/>
+      <c r="Q33" s="1"/>
+      <c r="R33" s="14"/>
+      <c r="S33" s="14"/>
+      <c r="T33" s="14"/>
     </row>
     <row r="34" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B34" s="7"/>
@@ -3774,13 +3771,9 @@
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
       <c r="N34" s="1"/>
       <c r="P34" s="1"/>
       <c r="Q34" s="1"/>
-      <c r="R34" s="38"/>
-      <c r="S34" s="38"/>
-      <c r="T34" s="38"/>
     </row>
     <row r="35" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B35" s="7"/>
@@ -3789,13 +3782,9 @@
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
       <c r="N35" s="1"/>
       <c r="P35" s="1"/>
       <c r="Q35" s="1"/>
-      <c r="R35" s="38"/>
-      <c r="S35" s="38"/>
-      <c r="T35" s="38"/>
     </row>
     <row r="36" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B36" s="7"/>
@@ -3804,253 +3793,136 @@
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-      <c r="N36" s="1"/>
-      <c r="P36" s="1"/>
-      <c r="Q36" s="1"/>
-      <c r="R36" s="38"/>
-      <c r="S36" s="38"/>
-      <c r="T36" s="38"/>
     </row>
     <row r="37" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="N37" s="1"/>
-      <c r="P37" s="1"/>
-      <c r="Q37" s="1"/>
+      <c r="B37" s="7"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
     </row>
     <row r="38" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B38" s="12"/>
-      <c r="C38" s="12"/>
-      <c r="D38" s="12"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="N38" s="1"/>
-      <c r="P38" s="1"/>
-      <c r="Q38" s="1"/>
-      <c r="R38" s="14"/>
-      <c r="S38" s="14"/>
-      <c r="T38" s="14"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
     </row>
     <row r="39" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B39" s="12"/>
-      <c r="C39" s="12"/>
-      <c r="D39" s="12"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="N39" s="1"/>
-      <c r="P39" s="1"/>
-      <c r="Q39" s="1"/>
-      <c r="R39" s="14"/>
-      <c r="S39" s="14"/>
-      <c r="T39" s="14"/>
+      <c r="B39" s="5"/>
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
     </row>
     <row r="40" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B40" s="12"/>
-      <c r="C40" s="12"/>
-      <c r="D40" s="12"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="N40" s="1"/>
-      <c r="P40" s="1"/>
-      <c r="Q40" s="1"/>
-      <c r="R40" s="14"/>
-      <c r="S40" s="14"/>
-      <c r="T40" s="14"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="7"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="N40" s="14"/>
+      <c r="O40" s="14"/>
+      <c r="P40" s="14"/>
+      <c r="Q40" s="14"/>
     </row>
     <row r="41" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B41" s="12"/>
-      <c r="C41" s="12"/>
-      <c r="D41" s="12"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="N41" s="1"/>
-      <c r="P41" s="1"/>
-      <c r="Q41" s="1"/>
-      <c r="R41" s="14"/>
-      <c r="S41" s="14"/>
-      <c r="T41" s="14"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="7"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="N41" s="14"/>
+      <c r="O41" s="14"/>
+      <c r="P41" s="14"/>
+      <c r="Q41" s="14"/>
     </row>
     <row r="42" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B42" s="12"/>
-      <c r="C42" s="12"/>
-      <c r="D42" s="12"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="N42" s="1"/>
-      <c r="P42" s="1"/>
-      <c r="Q42" s="1"/>
-      <c r="R42" s="14"/>
-      <c r="S42" s="14"/>
-      <c r="T42" s="14"/>
+      <c r="B42" s="7"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="N42" s="14"/>
+      <c r="O42" s="14"/>
+      <c r="P42" s="14"/>
+      <c r="Q42" s="14"/>
     </row>
     <row r="43" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B43" s="7"/>
-      <c r="C43" s="10"/>
+      <c r="C43" s="1"/>
       <c r="D43" s="7"/>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
-      <c r="N43" s="1"/>
-      <c r="P43" s="1"/>
-      <c r="Q43" s="1"/>
+      <c r="N43" s="14"/>
+      <c r="O43" s="14"/>
+      <c r="P43" s="14"/>
+      <c r="Q43" s="14"/>
     </row>
     <row r="44" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B44" s="7"/>
-      <c r="C44" s="10"/>
       <c r="D44" s="7"/>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
-      <c r="N44" s="1"/>
-      <c r="P44" s="1"/>
-      <c r="Q44" s="1"/>
+      <c r="N44" s="14"/>
+      <c r="O44" s="14"/>
+      <c r="P44" s="14"/>
+      <c r="Q44" s="14"/>
     </row>
     <row r="45" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B45" s="7"/>
-      <c r="C45" s="10"/>
-      <c r="D45" s="7"/>
-      <c r="E45" s="1"/>
-      <c r="F45" s="1"/>
-      <c r="G45" s="1"/>
+      <c r="P45" s="10"/>
+      <c r="Q45" s="27"/>
     </row>
     <row r="46" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B46" s="7"/>
-      <c r="C46" s="1"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="1"/>
-      <c r="F46" s="1"/>
-      <c r="G46" s="1"/>
+      <c r="B46" s="23"/>
+      <c r="C46" s="1" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="47" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B47" s="5"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="7"/>
-      <c r="E47" s="1"/>
-      <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B48" s="5"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="1"/>
-      <c r="F48" s="1"/>
-      <c r="G48" s="1"/>
-    </row>
-    <row r="49" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B49" s="5"/>
-      <c r="C49" s="7"/>
-      <c r="D49" s="7"/>
-      <c r="E49" s="1"/>
-      <c r="F49" s="1"/>
-      <c r="G49" s="1"/>
-      <c r="N49" s="14"/>
-      <c r="O49" s="14"/>
-      <c r="P49" s="14"/>
-      <c r="Q49" s="14"/>
-    </row>
-    <row r="50" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B50" s="5"/>
-      <c r="C50" s="1"/>
-      <c r="D50" s="7"/>
-      <c r="E50" s="1"/>
-      <c r="F50" s="1"/>
-      <c r="G50" s="1"/>
-      <c r="N50" s="14"/>
-      <c r="O50" s="14"/>
-      <c r="P50" s="14"/>
-      <c r="Q50" s="14"/>
-    </row>
-    <row r="51" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B51" s="7"/>
-      <c r="C51" s="1"/>
-      <c r="D51" s="7"/>
-      <c r="E51" s="1"/>
-      <c r="F51" s="1"/>
-      <c r="G51" s="1"/>
-      <c r="N51" s="14"/>
-      <c r="O51" s="14"/>
-      <c r="P51" s="14"/>
-      <c r="Q51" s="14"/>
-    </row>
-    <row r="52" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B52" s="7"/>
-      <c r="C52" s="1"/>
-      <c r="D52" s="7"/>
-      <c r="E52" s="1"/>
-      <c r="F52" s="1"/>
-      <c r="G52" s="1"/>
-      <c r="N52" s="14"/>
-      <c r="O52" s="14"/>
-      <c r="P52" s="14"/>
-      <c r="Q52" s="14"/>
-    </row>
-    <row r="53" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B53" s="7"/>
-      <c r="D53" s="7"/>
-      <c r="E53" s="1"/>
-      <c r="F53" s="1"/>
-      <c r="G53" s="1"/>
-      <c r="N53" s="14"/>
-      <c r="O53" s="14"/>
-      <c r="P53" s="14"/>
-      <c r="Q53" s="14"/>
-    </row>
-    <row r="54" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="P54" s="10"/>
-      <c r="Q54" s="27"/>
-    </row>
-    <row r="55" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B55" s="23"/>
-      <c r="C55" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="56" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B56" s="30"/>
-      <c r="C56" s="1" t="s">
+      <c r="B47" s="30"/>
+      <c r="C47" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="65" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A65"/>
-      <c r="B65"/>
-      <c r="C65"/>
-      <c r="D65"/>
-      <c r="E65"/>
-      <c r="F65"/>
-      <c r="G65"/>
-      <c r="H65"/>
-      <c r="I65"/>
-      <c r="J65"/>
-      <c r="K65"/>
-      <c r="L65"/>
-      <c r="M65"/>
-      <c r="N65"/>
-      <c r="O65"/>
-      <c r="P65"/>
-      <c r="Q65"/>
-      <c r="R65"/>
-      <c r="S65"/>
-      <c r="T65"/>
-      <c r="U65"/>
-      <c r="V65"/>
-      <c r="W65"/>
-    </row>
-    <row r="66" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="W66" s="1"/>
-    </row>
-    <row r="67" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A67" s="1"/>
+    <row r="56" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56"/>
+      <c r="B56"/>
+      <c r="C56"/>
+      <c r="D56"/>
+      <c r="E56"/>
+      <c r="F56"/>
+      <c r="G56"/>
+      <c r="H56"/>
+      <c r="I56"/>
+      <c r="J56"/>
+      <c r="K56"/>
+      <c r="L56"/>
+      <c r="M56"/>
+      <c r="N56"/>
+      <c r="O56"/>
+      <c r="P56"/>
+      <c r="Q56"/>
+      <c r="R56"/>
+      <c r="S56"/>
+      <c r="T56"/>
+      <c r="U56"/>
+      <c r="V56"/>
+      <c r="W56"/>
+    </row>
+    <row r="57" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W57" s="1"/>
+    </row>
+    <row r="58" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A58" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4122,10 +3994,10 @@
     </row>
     <row r="2" spans="2:51" ht="31.2" x14ac:dyDescent="0.3">
       <c r="B2" s="47" t="s">
+        <v>94</v>
+      </c>
+      <c r="C2" s="47" t="s">
         <v>95</v>
-      </c>
-      <c r="C2" s="47" t="s">
-        <v>96</v>
       </c>
       <c r="D2" s="48" t="str">
         <f>"Demand Technologies"</f>
@@ -4135,11 +4007,11 @@
         <v>58</v>
       </c>
       <c r="F2" s="47" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G2" s="47"/>
       <c r="H2" s="47" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V2" s="49" t="s">
         <v>7</v>
@@ -4228,10 +4100,10 @@
         <v>69</v>
       </c>
       <c r="X5" s="45" t="s">
+        <v>139</v>
+      </c>
+      <c r="Y5" s="77" t="s">
         <v>140</v>
-      </c>
-      <c r="Y5" s="77" t="s">
-        <v>141</v>
       </c>
       <c r="Z5" s="77" t="s">
         <v>58</v>
@@ -4251,10 +4123,10 @@
         <v>69</v>
       </c>
       <c r="X6" s="45" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="Y6" s="77" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="Z6" s="77" t="s">
         <v>58</v>
@@ -4274,10 +4146,10 @@
         <v>69</v>
       </c>
       <c r="X7" s="45" t="s">
+        <v>144</v>
+      </c>
+      <c r="Y7" s="45" t="s">
         <v>145</v>
-      </c>
-      <c r="Y7" s="45" t="s">
-        <v>146</v>
       </c>
       <c r="Z7" s="77" t="s">
         <v>58</v>
@@ -4311,19 +4183,6 @@
       <c r="AC10" s="50"/>
       <c r="AD10" s="50"/>
     </row>
-    <row r="12" spans="2:51" x14ac:dyDescent="0.25">
-      <c r="V12" s="49" t="s">
-        <v>17</v>
-      </c>
-      <c r="W12" s="49"/>
-      <c r="X12" s="50"/>
-      <c r="Y12" s="50"/>
-      <c r="Z12" s="50"/>
-      <c r="AA12" s="50"/>
-      <c r="AB12" s="50"/>
-      <c r="AC12" s="50"/>
-      <c r="AD12" s="50"/>
-    </row>
     <row r="13" spans="2:51" x14ac:dyDescent="0.25">
       <c r="D13" s="55" t="s">
         <v>0</v>
@@ -4331,33 +4190,17 @@
       <c r="E13" s="55"/>
       <c r="F13" s="55"/>
       <c r="H13" s="55"/>
-      <c r="V13" s="51" t="s">
-        <v>15</v>
-      </c>
-      <c r="W13" s="52" t="s">
-        <v>42</v>
-      </c>
-      <c r="X13" s="51" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y13" s="51" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z13" s="51" t="s">
-        <v>18</v>
-      </c>
-      <c r="AA13" s="51" t="s">
-        <v>19</v>
-      </c>
-      <c r="AB13" s="51" t="s">
-        <v>20</v>
-      </c>
-      <c r="AC13" s="51" t="s">
-        <v>21</v>
-      </c>
-      <c r="AD13" s="51" t="s">
-        <v>22</v>
-      </c>
+      <c r="V13" s="49" t="s">
+        <v>17</v>
+      </c>
+      <c r="W13" s="49"/>
+      <c r="X13" s="50"/>
+      <c r="Y13" s="50"/>
+      <c r="Z13" s="50"/>
+      <c r="AA13" s="50"/>
+      <c r="AB13" s="50"/>
+      <c r="AC13" s="50"/>
+      <c r="AD13" s="50"/>
       <c r="AI13"/>
       <c r="AJ13" s="39"/>
       <c r="AK13" s="77"/>
@@ -4374,7 +4217,7 @@
       <c r="AV13" s="77"/>
       <c r="AW13" s="77"/>
     </row>
-    <row r="14" spans="2:51" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="56" t="s">
         <v>1</v>
       </c>
@@ -4385,7 +4228,7 @@
         <v>4</v>
       </c>
       <c r="E14" s="57" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F14" s="57" t="s">
         <v>16</v>
@@ -4403,58 +4246,58 @@
         <v>5</v>
       </c>
       <c r="K14" s="59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L14" s="57" t="s">
         <v>56</v>
       </c>
       <c r="M14" s="59" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N14" s="58" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O14" s="59" t="s">
+        <v>120</v>
+      </c>
+      <c r="P14" s="59" t="s">
         <v>121</v>
       </c>
-      <c r="P14" s="59" t="s">
+      <c r="Q14" s="59" t="s">
         <v>122</v>
       </c>
-      <c r="Q14" s="59" t="s">
+      <c r="R14" s="59" t="s">
         <v>123</v>
       </c>
-      <c r="R14" s="59" t="s">
-        <v>124</v>
-      </c>
       <c r="S14" s="59" t="s">
-        <v>132</v>
-      </c>
-      <c r="V14" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="W14" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="X14" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y14" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z14" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="AA14" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB14" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="AC14" s="31" t="s">
-        <v>52</v>
-      </c>
-      <c r="AD14" s="31" t="s">
-        <v>31</v>
+        <v>131</v>
+      </c>
+      <c r="V14" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="W14" s="52" t="s">
+        <v>42</v>
+      </c>
+      <c r="X14" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y14" s="51" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z14" s="51" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA14" s="51" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB14" s="51" t="s">
+        <v>20</v>
+      </c>
+      <c r="AC14" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="AD14" s="51" t="s">
+        <v>22</v>
       </c>
       <c r="AI14"/>
       <c r="AJ14" s="39"/>
@@ -4502,43 +4345,59 @@
         <v>37</v>
       </c>
       <c r="K15" s="33" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L15" s="33" t="s">
         <v>80</v>
       </c>
       <c r="M15" s="33" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="N15" s="32" t="s">
         <v>85</v>
       </c>
       <c r="O15" s="33" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="P15" s="33" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q15" s="33" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="R15" s="75" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="S15" s="75" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="V15" s="31" t="s">
-        <v>81</v>
-      </c>
-      <c r="W15" s="31"/>
-      <c r="X15" s="31"/>
-      <c r="Y15" s="31"/>
-      <c r="Z15" s="31"/>
-      <c r="AA15" s="31"/>
-      <c r="AB15" s="31"/>
-      <c r="AC15" s="31"/>
-      <c r="AD15" s="31"/>
+        <v>50</v>
+      </c>
+      <c r="W15" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="X15" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y15" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z15" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA15" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB15" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="AC15" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD15" s="31" t="s">
+        <v>31</v>
+      </c>
       <c r="AI15"/>
       <c r="AJ15" s="39"/>
       <c r="AY15" s="46"/>
@@ -4556,17 +4415,17 @@
         <v>54</v>
       </c>
       <c r="I16" s="35" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J16" s="35" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K16" s="35" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L16" s="36"/>
       <c r="M16" s="36" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="N16" s="35"/>
       <c r="O16" s="36"/>
@@ -4574,41 +4433,31 @@
       <c r="Q16" s="36"/>
       <c r="R16" s="35"/>
       <c r="S16" s="76"/>
-      <c r="V16" s="60" t="s">
-        <v>135</v>
-      </c>
-      <c r="W16" s="60"/>
-      <c r="X16" s="61" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y16" s="62" t="s">
-        <v>134</v>
-      </c>
-      <c r="Z16" s="45" t="s">
-        <v>58</v>
-      </c>
-      <c r="AA16" s="45" t="s">
-        <v>87</v>
-      </c>
-      <c r="AB16" s="63" t="s">
-        <v>88</v>
-      </c>
-      <c r="AC16" s="46"/>
-      <c r="AD16" s="46"/>
+      <c r="V16" s="31" t="s">
+        <v>81</v>
+      </c>
+      <c r="W16" s="31"/>
+      <c r="X16" s="31"/>
+      <c r="Y16" s="31"/>
+      <c r="Z16" s="31"/>
+      <c r="AA16" s="31"/>
+      <c r="AB16" s="31"/>
+      <c r="AC16" s="31"/>
+      <c r="AD16" s="31"/>
       <c r="AI16"/>
       <c r="AJ16" s="39"/>
       <c r="AY16" s="46"/>
     </row>
     <row r="17" spans="2:51" x14ac:dyDescent="0.25">
       <c r="B17" s="45" t="str">
-        <f>X16</f>
+        <f>X17</f>
         <v>Furnace</v>
       </c>
       <c r="C17" s="45" t="s">
         <v>69</v>
       </c>
       <c r="D17" s="50" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E17" s="43">
         <v>2030</v>
@@ -4652,14 +4501,14 @@
       </c>
       <c r="S17" s="43"/>
       <c r="V17" s="60" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W17" s="60"/>
       <c r="X17" s="61" t="s">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="Y17" s="62" t="s">
-        <v>97</v>
+        <v>133</v>
       </c>
       <c r="Z17" s="45" t="s">
         <v>58</v>
@@ -4691,7 +4540,7 @@
     </row>
     <row r="18" spans="2:51" x14ac:dyDescent="0.25">
       <c r="B18" s="45" t="str">
-        <f>X$17</f>
+        <f>X$18</f>
         <v>BIOBoiler</v>
       </c>
       <c r="C18" s="45" t="str">
@@ -4699,7 +4548,7 @@
         <v>MANBIOMIN</v>
       </c>
       <c r="D18" s="50" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E18" s="43">
         <v>2030</v>
@@ -4733,14 +4582,14 @@
       <c r="R18" s="43"/>
       <c r="S18" s="43"/>
       <c r="V18" s="60" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W18" s="60"/>
       <c r="X18" s="61" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="Y18" s="62" t="s">
-        <v>138</v>
+        <v>96</v>
       </c>
       <c r="Z18" s="45" t="s">
         <v>58</v>
@@ -4772,14 +4621,14 @@
     </row>
     <row r="19" spans="2:51" x14ac:dyDescent="0.25">
       <c r="B19" s="45" t="str">
-        <f>X20</f>
+        <f>X21</f>
         <v>ELCBoiler</v>
       </c>
       <c r="C19" s="45" t="s">
         <v>69</v>
       </c>
       <c r="D19" s="50" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E19" s="43">
         <v>2030</v>
@@ -4823,14 +4672,14 @@
       </c>
       <c r="S19" s="43"/>
       <c r="V19" s="60" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W19" s="60"/>
       <c r="X19" s="61" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="Y19" s="62" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="Z19" s="45" t="s">
         <v>58</v>
@@ -4849,7 +4698,7 @@
     </row>
     <row r="20" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B20" s="45" t="str">
-        <f>X18</f>
+        <f>X19</f>
         <v>BIOKiln</v>
       </c>
       <c r="C20" s="45" t="str">
@@ -4857,7 +4706,7 @@
         <v>MANBIOMIN</v>
       </c>
       <c r="D20" s="50" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E20" s="43">
         <v>2030</v>
@@ -4891,14 +4740,14 @@
       <c r="R20" s="43"/>
       <c r="S20" s="43"/>
       <c r="V20" s="60" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W20" s="60"/>
       <c r="X20" s="61" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="Y20" s="62" t="s">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="Z20" s="45" t="s">
         <v>58</v>
@@ -4927,7 +4776,7 @@
     </row>
     <row r="21" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B21" s="50" t="str">
-        <f>X19</f>
+        <f>X20</f>
         <v>GASBoiler</v>
       </c>
       <c r="C21" s="45" t="str">
@@ -4935,7 +4784,7 @@
         <v>MANGASMIN</v>
       </c>
       <c r="D21" s="50" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E21" s="43">
         <v>2030</v>
@@ -4969,14 +4818,14 @@
       <c r="R21" s="43"/>
       <c r="S21" s="43"/>
       <c r="V21" s="60" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W21" s="60"/>
       <c r="X21" s="61" t="s">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="Y21" s="62" t="s">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="Z21" s="45" t="s">
         <v>58</v>
@@ -4984,7 +4833,7 @@
       <c r="AA21" s="45" t="s">
         <v>87</v>
       </c>
-      <c r="AB21" s="46" t="s">
+      <c r="AB21" s="63" t="s">
         <v>88</v>
       </c>
       <c r="AI21"/>
@@ -5005,15 +4854,15 @@
     </row>
     <row r="22" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B22" s="50" t="str">
-        <f>X22</f>
+        <f>X23</f>
         <v>WNDTRBN</v>
       </c>
       <c r="C22" s="45" t="str">
-        <f>PRI_Sector_Fuels!D28</f>
+        <f>PRI_Sector_Fuels!D19</f>
         <v>WIND</v>
       </c>
       <c r="D22" s="50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E22" s="43">
         <v>2030</v>
@@ -5049,14 +4898,14 @@
         <v>0.2</v>
       </c>
       <c r="V22" s="60" t="s">
-        <v>69</v>
+        <v>134</v>
       </c>
       <c r="W22" s="60"/>
       <c r="X22" s="61" t="s">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="Y22" s="62" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="Z22" s="45" t="s">
         <v>58</v>
@@ -5085,15 +4934,15 @@
     </row>
     <row r="23" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B23" s="50" t="str">
-        <f>X23</f>
+        <f>X24</f>
         <v>SOLPV</v>
       </c>
       <c r="C23" s="45" t="str">
-        <f>PRI_Sector_Fuels!D29</f>
+        <f>PRI_Sector_Fuels!D20</f>
         <v>SOLAR</v>
       </c>
       <c r="D23" s="50" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E23" s="43">
         <v>2030</v>
@@ -5133,7 +4982,7 @@
       </c>
       <c r="W23" s="60"/>
       <c r="X23" s="61" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="Y23" s="62" t="s">
         <v>92</v>
@@ -5165,15 +5014,15 @@
     </row>
     <row r="24" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B24" s="50" t="str">
-        <f>X21</f>
+        <f>X22</f>
         <v>CSP</v>
       </c>
       <c r="C24" s="45" t="str">
-        <f>PRI_Sector_Fuels!D29</f>
+        <f>PRI_Sector_Fuels!D20</f>
         <v>SOLAR</v>
       </c>
       <c r="D24" s="50" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E24" s="43">
         <v>2030</v>
@@ -5211,10 +5060,10 @@
       </c>
       <c r="W24" s="60"/>
       <c r="X24" s="61" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="Y24" s="62" t="s">
-        <v>143</v>
+        <v>91</v>
       </c>
       <c r="Z24" s="45" t="s">
         <v>58</v>
@@ -5243,12 +5092,12 @@
     </row>
     <row r="25" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B25" s="50" t="str">
-        <f>X19</f>
+        <f>X20</f>
         <v>GASBoiler</v>
       </c>
       <c r="C25" s="45"/>
       <c r="D25" s="50" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E25" s="43">
         <v>2030</v>
@@ -5286,10 +5135,10 @@
       </c>
       <c r="W25" s="60"/>
       <c r="X25" s="61" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="Y25" s="62" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="Z25" s="45" t="s">
         <v>58</v>
@@ -5318,11 +5167,11 @@
     </row>
     <row r="26" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B26" s="85" t="str">
-        <f>X24</f>
+        <f>X25</f>
         <v>DECELC</v>
       </c>
       <c r="C26" s="50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D26" s="50" t="s">
         <v>69</v>
@@ -5358,12 +5207,25 @@
       <c r="Q26" s="64"/>
       <c r="R26" s="68"/>
       <c r="S26" s="43"/>
-      <c r="V26" s="60"/>
+      <c r="V26" s="60" t="s">
+        <v>69</v>
+      </c>
       <c r="W26" s="60"/>
-      <c r="X26" s="61"/>
-      <c r="Y26" s="62"/>
-      <c r="Z26" s="45"/>
-      <c r="AA26" s="45"/>
+      <c r="X26" s="61" t="s">
+        <v>146</v>
+      </c>
+      <c r="Y26" s="62" t="s">
+        <v>145</v>
+      </c>
+      <c r="Z26" s="45" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA26" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB26" s="46" t="s">
+        <v>88</v>
+      </c>
       <c r="AI26"/>
       <c r="AJ26"/>
       <c r="AK26" s="45"/>
@@ -5382,11 +5244,11 @@
     </row>
     <row r="27" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B27" s="85" t="str">
-        <f>X24</f>
+        <f>X25</f>
         <v>DECELC</v>
       </c>
       <c r="C27" s="50" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D27" s="50" t="s">
         <v>69</v>
@@ -5446,14 +5308,14 @@
     </row>
     <row r="28" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B28" s="50" t="str">
-        <f>X25</f>
+        <f>X26</f>
         <v>BIOPOWER</v>
       </c>
       <c r="C28" s="50" t="s">
         <v>68</v>
       </c>
       <c r="D28" s="50" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E28" s="43">
         <v>2030</v>
@@ -5486,14 +5348,12 @@
       <c r="Q28" s="64"/>
       <c r="R28" s="68"/>
       <c r="S28" s="43"/>
-      <c r="V28" s="45"/>
-      <c r="W28" s="45"/>
-      <c r="X28" s="45"/>
-      <c r="Y28" s="45"/>
+      <c r="V28" s="60"/>
+      <c r="W28" s="60"/>
+      <c r="X28" s="61"/>
+      <c r="Y28" s="62"/>
       <c r="Z28" s="45"/>
       <c r="AA28" s="45"/>
-      <c r="AC28" s="45"/>
-      <c r="AD28" s="45"/>
       <c r="AI28"/>
       <c r="AJ28"/>
       <c r="AK28" s="45"/>
@@ -5512,10 +5372,10 @@
     </row>
     <row r="29" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B29" s="50" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C29" s="45" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D29" s="50" t="s">
         <v>69</v>

--- a/SubRES_TMPL/SubRES_NewTechs.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E782074-86D5-4F0F-9E00-D8D4BDACB17E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2E4E6D2-96C2-451D-B61F-BA1733016731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PRI_Sector_Fuels" sheetId="6" r:id="rId1"/>
@@ -4655,21 +4655,6 @@
         <v>8.76</v>
       </c>
       <c r="M19" s="43"/>
-      <c r="N19" s="45">
-        <v>0.2</v>
-      </c>
-      <c r="O19" s="45">
-        <v>0.25</v>
-      </c>
-      <c r="P19" s="45">
-        <v>0.3</v>
-      </c>
-      <c r="Q19" s="45">
-        <v>0.35</v>
-      </c>
-      <c r="R19" s="45">
-        <v>0.4</v>
-      </c>
       <c r="S19" s="43"/>
       <c r="V19" s="60" t="s">
         <v>134</v>
@@ -4733,11 +4718,21 @@
         <v>8.76</v>
       </c>
       <c r="M20" s="43"/>
-      <c r="N20" s="68"/>
-      <c r="O20" s="43"/>
-      <c r="P20" s="43"/>
-      <c r="Q20" s="43"/>
-      <c r="R20" s="43"/>
+      <c r="N20" s="64">
+        <v>0.1</v>
+      </c>
+      <c r="O20" s="64">
+        <v>0.15</v>
+      </c>
+      <c r="P20" s="64">
+        <v>0.2</v>
+      </c>
+      <c r="Q20" s="64">
+        <v>0.25</v>
+      </c>
+      <c r="R20" s="64">
+        <v>0.35</v>
+      </c>
       <c r="S20" s="43"/>
       <c r="V20" s="60" t="s">
         <v>134</v>

--- a/SubRES_TMPL/SubRES_NewTechs.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2E4E6D2-96C2-451D-B61F-BA1733016731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B770AF86-2F68-4ECA-A3A2-B2A22B62B02A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PRI_Sector_Fuels" sheetId="6" r:id="rId1"/>
@@ -5279,10 +5279,10 @@
       <c r="Q27" s="64"/>
       <c r="R27" s="68"/>
       <c r="S27" s="43"/>
-      <c r="V27" s="60"/>
-      <c r="W27" s="60"/>
-      <c r="X27" s="61"/>
-      <c r="Y27" s="62"/>
+      <c r="V27" s="45"/>
+      <c r="W27" s="45"/>
+      <c r="X27" s="45"/>
+      <c r="Y27" s="45"/>
       <c r="Z27" s="45"/>
       <c r="AA27" s="45"/>
       <c r="AI27"/>
@@ -5343,10 +5343,10 @@
       <c r="Q28" s="64"/>
       <c r="R28" s="68"/>
       <c r="S28" s="43"/>
-      <c r="V28" s="60"/>
-      <c r="W28" s="60"/>
-      <c r="X28" s="61"/>
-      <c r="Y28" s="62"/>
+      <c r="V28" s="45"/>
+      <c r="W28" s="45"/>
+      <c r="X28" s="45"/>
+      <c r="Y28" s="45"/>
       <c r="Z28" s="45"/>
       <c r="AA28" s="45"/>
       <c r="AI28"/>

--- a/SubRES_TMPL/SubRES_NewTechs.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B770AF86-2F68-4ECA-A3A2-B2A22B62B02A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{242AA50E-92F9-4A27-B564-FC860C526CE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4943,7 +4943,7 @@
         <v>2030</v>
       </c>
       <c r="F23" s="83">
-        <v>1</v>
+        <v>0.42</v>
       </c>
       <c r="G23" s="64">
         <v>0.99</v>
@@ -5023,7 +5023,7 @@
         <v>2030</v>
       </c>
       <c r="F24" s="83">
-        <v>1</v>
+        <v>0.41</v>
       </c>
       <c r="G24" s="64">
         <v>1</v>

--- a/SubRES_TMPL/SubRES_NewTechs.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{242AA50E-92F9-4A27-B564-FC860C526CE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31DB0006-6781-46B3-BB11-4A32DCAE830C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PRI_Sector_Fuels" sheetId="6" r:id="rId1"/>
@@ -3501,7 +3501,9 @@
       <c r="E19" s="1">
         <v>2030</v>
       </c>
-      <c r="F19" s="1"/>
+      <c r="F19" s="1">
+        <v>1</v>
+      </c>
       <c r="G19" s="1">
         <v>1</v>
       </c>
@@ -3544,7 +3546,9 @@
       <c r="E20" s="1">
         <v>2030</v>
       </c>
-      <c r="F20" s="1"/>
+      <c r="F20" s="1">
+        <v>1</v>
+      </c>
       <c r="G20" s="1">
         <v>1</v>
       </c>
@@ -4943,7 +4947,7 @@
         <v>2030</v>
       </c>
       <c r="F23" s="83">
-        <v>0.42</v>
+        <v>0.20499999999999999</v>
       </c>
       <c r="G23" s="64">
         <v>0.99</v>
@@ -5023,7 +5027,7 @@
         <v>2030</v>
       </c>
       <c r="F24" s="83">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="G24" s="64">
         <v>1</v>
@@ -5098,7 +5102,7 @@
         <v>2030</v>
       </c>
       <c r="F25" s="83">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="G25" s="64">
         <v>1</v>

--- a/SubRES_TMPL/SubRES_NewTechs.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31DB0006-6781-46B3-BB11-4A32DCAE830C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D5A8EF8-B65D-4300-9173-B16E2B826EAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PRI_Sector_Fuels" sheetId="6" r:id="rId1"/>

--- a/SubRES_TMPL/SubRES_NewTechs.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E782074-86D5-4F0F-9E00-D8D4BDACB17E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D5A8EF8-B65D-4300-9173-B16E2B826EAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PRI_Sector_Fuels" sheetId="6" r:id="rId1"/>
@@ -3501,7 +3501,9 @@
       <c r="E19" s="1">
         <v>2030</v>
       </c>
-      <c r="F19" s="1"/>
+      <c r="F19" s="1">
+        <v>1</v>
+      </c>
       <c r="G19" s="1">
         <v>1</v>
       </c>
@@ -3544,7 +3546,9 @@
       <c r="E20" s="1">
         <v>2030</v>
       </c>
-      <c r="F20" s="1"/>
+      <c r="F20" s="1">
+        <v>1</v>
+      </c>
       <c r="G20" s="1">
         <v>1</v>
       </c>
@@ -4655,21 +4659,6 @@
         <v>8.76</v>
       </c>
       <c r="M19" s="43"/>
-      <c r="N19" s="45">
-        <v>0.2</v>
-      </c>
-      <c r="O19" s="45">
-        <v>0.25</v>
-      </c>
-      <c r="P19" s="45">
-        <v>0.3</v>
-      </c>
-      <c r="Q19" s="45">
-        <v>0.35</v>
-      </c>
-      <c r="R19" s="45">
-        <v>0.4</v>
-      </c>
       <c r="S19" s="43"/>
       <c r="V19" s="60" t="s">
         <v>134</v>
@@ -4733,11 +4722,21 @@
         <v>8.76</v>
       </c>
       <c r="M20" s="43"/>
-      <c r="N20" s="68"/>
-      <c r="O20" s="43"/>
-      <c r="P20" s="43"/>
-      <c r="Q20" s="43"/>
-      <c r="R20" s="43"/>
+      <c r="N20" s="64">
+        <v>0.1</v>
+      </c>
+      <c r="O20" s="64">
+        <v>0.15</v>
+      </c>
+      <c r="P20" s="64">
+        <v>0.2</v>
+      </c>
+      <c r="Q20" s="64">
+        <v>0.25</v>
+      </c>
+      <c r="R20" s="64">
+        <v>0.35</v>
+      </c>
       <c r="S20" s="43"/>
       <c r="V20" s="60" t="s">
         <v>134</v>
@@ -4948,7 +4947,7 @@
         <v>2030</v>
       </c>
       <c r="F23" s="83">
-        <v>1</v>
+        <v>0.20499999999999999</v>
       </c>
       <c r="G23" s="64">
         <v>0.99</v>
@@ -5028,7 +5027,7 @@
         <v>2030</v>
       </c>
       <c r="F24" s="83">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="G24" s="64">
         <v>1</v>
@@ -5103,7 +5102,7 @@
         <v>2030</v>
       </c>
       <c r="F25" s="83">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="G25" s="64">
         <v>1</v>
@@ -5284,10 +5283,10 @@
       <c r="Q27" s="64"/>
       <c r="R27" s="68"/>
       <c r="S27" s="43"/>
-      <c r="V27" s="60"/>
-      <c r="W27" s="60"/>
-      <c r="X27" s="61"/>
-      <c r="Y27" s="62"/>
+      <c r="V27" s="45"/>
+      <c r="W27" s="45"/>
+      <c r="X27" s="45"/>
+      <c r="Y27" s="45"/>
       <c r="Z27" s="45"/>
       <c r="AA27" s="45"/>
       <c r="AI27"/>
@@ -5348,10 +5347,10 @@
       <c r="Q28" s="64"/>
       <c r="R28" s="68"/>
       <c r="S28" s="43"/>
-      <c r="V28" s="60"/>
-      <c r="W28" s="60"/>
-      <c r="X28" s="61"/>
-      <c r="Y28" s="62"/>
+      <c r="V28" s="45"/>
+      <c r="W28" s="45"/>
+      <c r="X28" s="45"/>
+      <c r="Y28" s="45"/>
       <c r="Z28" s="45"/>
       <c r="AA28" s="45"/>
       <c r="AI28"/>

--- a/SubRES_TMPL/SubRES_NewTechs.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D5A8EF8-B65D-4300-9173-B16E2B826EAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9440EED7-F3ED-4CB9-A8D9-C62D41FC9412}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1554,7 +1554,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="154">
   <si>
     <t>~FI_T</t>
   </si>
@@ -1829,12 +1829,6 @@
     <t>SOLPV</t>
   </si>
   <si>
-    <t>Electricity from Solar PV</t>
-  </si>
-  <si>
-    <t>Electricity from wind</t>
-  </si>
-  <si>
     <t>N</t>
   </si>
   <si>
@@ -1844,9 +1838,6 @@
     <t>Mamufacturing</t>
   </si>
   <si>
-    <t>Biomass boiler</t>
-  </si>
-  <si>
     <t>BIOBoiler</t>
   </si>
   <si>
@@ -1856,15 +1847,9 @@
     <t>GASBoiler</t>
   </si>
   <si>
-    <t>Gas boiler</t>
-  </si>
-  <si>
     <t>ELCBoiler</t>
   </si>
   <si>
-    <t>Manufacturing heat from Solar</t>
-  </si>
-  <si>
     <t>VAROM</t>
   </si>
   <si>
@@ -1955,21 +1940,12 @@
     <t>% Contribution</t>
   </si>
   <si>
-    <t>Manufacturing heat supplier using electricity</t>
-  </si>
-  <si>
     <t>DMD</t>
   </si>
   <si>
     <t>DECELC</t>
   </si>
   <si>
-    <t>Electric boiler</t>
-  </si>
-  <si>
-    <t>Biomass kiln</t>
-  </si>
-  <si>
     <t>WNDELC</t>
   </si>
   <si>
@@ -1982,9 +1958,6 @@
     <t>Electricity from Wind</t>
   </si>
   <si>
-    <t>Decenteralized electricity from wind and solar aggrigator</t>
-  </si>
-  <si>
     <t>TH2024USD/MWh</t>
   </si>
   <si>
@@ -1998,6 +1971,51 @@
   </si>
   <si>
     <t>Natural Gas-Domestic</t>
+  </si>
+  <si>
+    <t>HEAT</t>
+  </si>
+  <si>
+    <t>SOLTHERMAL</t>
+  </si>
+  <si>
+    <t>Process heat from Solar</t>
+  </si>
+  <si>
+    <t>SOLTHT</t>
+  </si>
+  <si>
+    <t>Electricity to Manufacturing Process Heat Conversion Technology</t>
+  </si>
+  <si>
+    <t>Biomass Boiler</t>
+  </si>
+  <si>
+    <t>Biomass Kiln</t>
+  </si>
+  <si>
+    <t>Gas Boiler</t>
+  </si>
+  <si>
+    <t>Electric Boiler</t>
+  </si>
+  <si>
+    <t>Solarthermal Technology</t>
+  </si>
+  <si>
+    <t>Wind Turbine</t>
+  </si>
+  <si>
+    <t>Solar PV</t>
+  </si>
+  <si>
+    <t>Decentralized Alectricity Aggrigator</t>
+  </si>
+  <si>
+    <t>Bio-Elctricity Generation Technology</t>
+  </si>
+  <si>
+    <t>Solar Thermal to Process Heat Technology</t>
   </si>
 </sst>
 </file>
@@ -2962,7 +2980,7 @@
         <v>58</v>
       </c>
       <c r="F2" s="72" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="G2" s="14"/>
       <c r="N2" s="6" t="s">
@@ -2988,7 +3006,7 @@
         <v>58</v>
       </c>
       <c r="F3" s="72" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="G3" s="14"/>
       <c r="N3" s="8" t="s">
@@ -3030,7 +3048,7 @@
         <v>58</v>
       </c>
       <c r="F4" s="72" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="G4" s="14"/>
       <c r="N4" s="13" t="s">
@@ -3072,7 +3090,7 @@
         <v>58</v>
       </c>
       <c r="F5" s="72" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="G5" s="14"/>
       <c r="N5" s="39" t="s">
@@ -3109,7 +3127,7 @@
         <v>67</v>
       </c>
       <c r="Q6" s="39" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="R6" s="39" t="s">
         <v>58</v>
@@ -3135,7 +3153,7 @@
         <v>72</v>
       </c>
       <c r="Q7" s="12" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="R7" s="12" t="s">
         <v>58</v>
@@ -3159,10 +3177,10 @@
       </c>
       <c r="O8" s="37"/>
       <c r="P8" s="37" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="Q8" s="37" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="R8" s="37" t="s">
         <v>58</v>
@@ -3372,7 +3390,7 @@
         <v>54</v>
       </c>
       <c r="I16" s="20" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="J16" s="20" t="s">
         <v>58</v>
@@ -3382,7 +3400,7 @@
         <v>81</v>
       </c>
       <c r="O16" s="22" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="P16" s="22"/>
       <c r="Q16" s="22"/>
@@ -3426,7 +3444,7 @@
       </c>
       <c r="O17" s="38"/>
       <c r="P17" s="39" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="Q17" s="40" t="str">
         <f>"Domestic Supply of "&amp;$D$4&amp;" "</f>
@@ -3474,7 +3492,7 @@
       </c>
       <c r="O18" s="38"/>
       <c r="P18" s="39" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="Q18" s="40" t="str">
         <f>"Domestic Supply of "&amp;$D$5&amp;" "</f>
@@ -3520,10 +3538,10 @@
         <v>64</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="R19" s="38" t="s">
         <v>58</v>
@@ -3566,10 +3584,10 @@
       </c>
       <c r="O20" s="14"/>
       <c r="P20" s="14" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="Q20" s="14" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="R20" s="38" t="s">
         <v>58</v>
@@ -3998,10 +4016,10 @@
     </row>
     <row r="2" spans="2:51" ht="31.2" x14ac:dyDescent="0.3">
       <c r="B2" s="47" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C2" s="47" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D2" s="48" t="str">
         <f>"Demand Technologies"</f>
@@ -4011,11 +4029,11 @@
         <v>58</v>
       </c>
       <c r="F2" s="47" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="G2" s="47"/>
       <c r="H2" s="47" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="V2" s="49" t="s">
         <v>7</v>
@@ -4104,10 +4122,10 @@
         <v>69</v>
       </c>
       <c r="X5" s="45" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="Y5" s="77" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="Z5" s="77" t="s">
         <v>58</v>
@@ -4127,10 +4145,10 @@
         <v>69</v>
       </c>
       <c r="X6" s="45" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="Y6" s="77" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="Z6" s="77" t="s">
         <v>58</v>
@@ -4150,10 +4168,10 @@
         <v>69</v>
       </c>
       <c r="X7" s="45" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="Y7" s="45" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="Z7" s="77" t="s">
         <v>58</v>
@@ -4163,6 +4181,15 @@
       </c>
     </row>
     <row r="8" spans="2:51" x14ac:dyDescent="0.25">
+      <c r="V8" s="45" t="s">
+        <v>139</v>
+      </c>
+      <c r="X8" s="45" t="s">
+        <v>140</v>
+      </c>
+      <c r="Y8" s="45" t="s">
+        <v>141</v>
+      </c>
       <c r="AE8" s="46"/>
     </row>
     <row r="9" spans="2:51" x14ac:dyDescent="0.25">
@@ -4232,7 +4259,7 @@
         <v>4</v>
       </c>
       <c r="E14" s="57" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="F14" s="57" t="s">
         <v>16</v>
@@ -4250,31 +4277,31 @@
         <v>5</v>
       </c>
       <c r="K14" s="59" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="L14" s="57" t="s">
         <v>56</v>
       </c>
       <c r="M14" s="59" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="N14" s="58" t="s">
+        <v>112</v>
+      </c>
+      <c r="O14" s="59" t="s">
+        <v>115</v>
+      </c>
+      <c r="P14" s="59" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q14" s="59" t="s">
         <v>117</v>
       </c>
-      <c r="O14" s="59" t="s">
-        <v>120</v>
-      </c>
-      <c r="P14" s="59" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q14" s="59" t="s">
-        <v>122</v>
-      </c>
       <c r="R14" s="59" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="S14" s="59" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="V14" s="51" t="s">
         <v>15</v>
@@ -4349,31 +4376,31 @@
         <v>37</v>
       </c>
       <c r="K15" s="33" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="L15" s="33" t="s">
         <v>80</v>
       </c>
       <c r="M15" s="33" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="N15" s="32" t="s">
         <v>85</v>
       </c>
       <c r="O15" s="33" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="P15" s="33" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="Q15" s="33" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="R15" s="75" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="S15" s="75" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="V15" s="31" t="s">
         <v>50</v>
@@ -4419,17 +4446,17 @@
         <v>54</v>
       </c>
       <c r="I16" s="35" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="J16" s="35" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="K16" s="35" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="L16" s="36"/>
       <c r="M16" s="36" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="N16" s="35"/>
       <c r="O16" s="36"/>
@@ -4461,7 +4488,7 @@
         <v>69</v>
       </c>
       <c r="D17" s="50" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E17" s="43">
         <v>2030</v>
@@ -4505,14 +4532,14 @@
       </c>
       <c r="S17" s="43"/>
       <c r="V17" s="60" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="W17" s="60"/>
       <c r="X17" s="61" t="s">
         <v>66</v>
       </c>
       <c r="Y17" s="62" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="Z17" s="45" t="s">
         <v>58</v>
@@ -4552,7 +4579,7 @@
         <v>MANBIOMIN</v>
       </c>
       <c r="D18" s="50" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E18" s="43">
         <v>2030</v>
@@ -4586,14 +4613,14 @@
       <c r="R18" s="43"/>
       <c r="S18" s="43"/>
       <c r="V18" s="60" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="W18" s="60"/>
       <c r="X18" s="61" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="Y18" s="62" t="s">
-        <v>96</v>
+        <v>144</v>
       </c>
       <c r="Z18" s="45" t="s">
         <v>58</v>
@@ -4632,7 +4659,7 @@
         <v>69</v>
       </c>
       <c r="D19" s="50" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E19" s="43">
         <v>2030</v>
@@ -4661,14 +4688,14 @@
       <c r="M19" s="43"/>
       <c r="S19" s="43"/>
       <c r="V19" s="60" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="W19" s="60"/>
       <c r="X19" s="61" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="Y19" s="62" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="Z19" s="45" t="s">
         <v>58</v>
@@ -4695,7 +4722,7 @@
         <v>MANBIOMIN</v>
       </c>
       <c r="D20" s="50" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="E20" s="43">
         <v>2030</v>
@@ -4739,14 +4766,14 @@
       </c>
       <c r="S20" s="43"/>
       <c r="V20" s="60" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="W20" s="60"/>
       <c r="X20" s="61" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="Y20" s="62" t="s">
-        <v>100</v>
+        <v>146</v>
       </c>
       <c r="Z20" s="45" t="s">
         <v>58</v>
@@ -4783,7 +4810,7 @@
         <v>MANGASMIN</v>
       </c>
       <c r="D21" s="50" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E21" s="43">
         <v>2030</v>
@@ -4817,14 +4844,14 @@
       <c r="R21" s="43"/>
       <c r="S21" s="43"/>
       <c r="V21" s="60" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="W21" s="60"/>
       <c r="X21" s="61" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="Y21" s="62" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="Z21" s="45" t="s">
         <v>58</v>
@@ -4861,7 +4888,7 @@
         <v>WIND</v>
       </c>
       <c r="D22" s="50" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="E22" s="43">
         <v>2030</v>
@@ -4897,14 +4924,14 @@
         <v>0.2</v>
       </c>
       <c r="V22" s="60" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="W22" s="60"/>
       <c r="X22" s="61" t="s">
         <v>65</v>
       </c>
       <c r="Y22" s="62" t="s">
-        <v>102</v>
+        <v>148</v>
       </c>
       <c r="Z22" s="45" t="s">
         <v>58</v>
@@ -4941,7 +4968,7 @@
         <v>SOLAR</v>
       </c>
       <c r="D23" s="50" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="E23" s="43">
         <v>2030</v>
@@ -4984,7 +5011,7 @@
         <v>89</v>
       </c>
       <c r="Y23" s="62" t="s">
-        <v>92</v>
+        <v>149</v>
       </c>
       <c r="Z23" s="45" t="s">
         <v>58</v>
@@ -5020,8 +5047,9 @@
         <f>PRI_Sector_Fuels!D20</f>
         <v>SOLAR</v>
       </c>
-      <c r="D24" s="50" t="s">
-        <v>112</v>
+      <c r="D24" s="50" t="str">
+        <f>X8</f>
+        <v>SOLTHERMAL</v>
       </c>
       <c r="E24" s="43">
         <v>2030</v>
@@ -5062,7 +5090,7 @@
         <v>90</v>
       </c>
       <c r="Y24" s="62" t="s">
-        <v>91</v>
+        <v>150</v>
       </c>
       <c r="Z24" s="45" t="s">
         <v>58</v>
@@ -5096,7 +5124,7 @@
       </c>
       <c r="C25" s="45"/>
       <c r="D25" s="50" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E25" s="43">
         <v>2030</v>
@@ -5134,10 +5162,10 @@
       </c>
       <c r="W25" s="60"/>
       <c r="X25" s="61" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="Y25" s="62" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="Z25" s="45" t="s">
         <v>58</v>
@@ -5170,7 +5198,7 @@
         <v>DECELC</v>
       </c>
       <c r="C26" s="50" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="D26" s="50" t="s">
         <v>69</v>
@@ -5211,10 +5239,10 @@
       </c>
       <c r="W26" s="60"/>
       <c r="X26" s="61" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="Y26" s="62" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="Z26" s="45" t="s">
         <v>58</v>
@@ -5247,7 +5275,7 @@
         <v>DECELC</v>
       </c>
       <c r="C27" s="50" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="D27" s="50" t="s">
         <v>69</v>
@@ -5283,12 +5311,25 @@
       <c r="Q27" s="64"/>
       <c r="R27" s="68"/>
       <c r="S27" s="43"/>
-      <c r="V27" s="45"/>
+      <c r="V27" s="45" t="s">
+        <v>128</v>
+      </c>
       <c r="W27" s="45"/>
-      <c r="X27" s="45"/>
-      <c r="Y27" s="45"/>
-      <c r="Z27" s="45"/>
-      <c r="AA27" s="45"/>
+      <c r="X27" s="45" t="s">
+        <v>142</v>
+      </c>
+      <c r="Y27" s="45" t="s">
+        <v>153</v>
+      </c>
+      <c r="Z27" s="45" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA27" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB27" s="46" t="s">
+        <v>88</v>
+      </c>
       <c r="AI27"/>
       <c r="AJ27"/>
       <c r="AK27" s="45"/>
@@ -5314,7 +5355,7 @@
         <v>68</v>
       </c>
       <c r="D28" s="50" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="E28" s="43">
         <v>2030</v>
@@ -5371,10 +5412,10 @@
     </row>
     <row r="29" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B29" s="50" t="s">
+        <v>129</v>
+      </c>
+      <c r="C29" s="45" t="s">
         <v>135</v>
-      </c>
-      <c r="C29" s="45" t="s">
-        <v>144</v>
       </c>
       <c r="D29" s="50" t="s">
         <v>69</v>
@@ -5427,17 +5468,41 @@
       <c r="AW29" s="45"/>
     </row>
     <row r="30" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="45"/>
-      <c r="C30" s="50"/>
-      <c r="D30" s="84"/>
-      <c r="E30" s="43"/>
-      <c r="F30" s="64"/>
-      <c r="G30" s="64"/>
-      <c r="H30" s="43"/>
-      <c r="I30" s="64"/>
-      <c r="J30" s="64"/>
-      <c r="K30" s="64"/>
-      <c r="L30" s="64"/>
+      <c r="B30" s="45" t="str">
+        <f>X27</f>
+        <v>SOLTHT</v>
+      </c>
+      <c r="C30" s="50" t="str">
+        <f>X8</f>
+        <v>SOLTHERMAL</v>
+      </c>
+      <c r="D30" s="84" t="s">
+        <v>107</v>
+      </c>
+      <c r="E30" s="43">
+        <v>2030</v>
+      </c>
+      <c r="F30" s="64">
+        <v>1</v>
+      </c>
+      <c r="G30" s="64">
+        <v>1</v>
+      </c>
+      <c r="H30" s="43">
+        <v>100</v>
+      </c>
+      <c r="I30" s="64">
+        <v>0</v>
+      </c>
+      <c r="J30" s="64">
+        <v>0</v>
+      </c>
+      <c r="K30" s="64">
+        <v>0</v>
+      </c>
+      <c r="L30" s="64">
+        <v>0</v>
+      </c>
       <c r="M30" s="68"/>
       <c r="N30" s="68"/>
       <c r="O30" s="64"/>

--- a/SubRES_TMPL/SubRES_NewTechs.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9440EED7-F3ED-4CB9-A8D9-C62D41FC9412}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF20CE3F-891C-406E-8ED6-5D189703483D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PRI_Sector_Fuels" sheetId="6" r:id="rId1"/>
@@ -1554,7 +1554,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="156">
   <si>
     <t>~FI_T</t>
   </si>
@@ -1982,9 +1982,6 @@
     <t>Process heat from Solar</t>
   </si>
   <si>
-    <t>SOLTHT</t>
-  </si>
-  <si>
     <t>Electricity to Manufacturing Process Heat Conversion Technology</t>
   </si>
   <si>
@@ -2015,7 +2012,16 @@
     <t>Bio-Elctricity Generation Technology</t>
   </si>
   <si>
-    <t>Solar Thermal to Process Heat Technology</t>
+    <t>Renewable Manufacturing Process Heat Aggregator</t>
+  </si>
+  <si>
+    <t>RENHEAT</t>
+  </si>
+  <si>
+    <t>Process heat from all renewables</t>
+  </si>
+  <si>
+    <t>RENTHT</t>
   </si>
 </sst>
 </file>
@@ -2327,7 +2333,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
@@ -2487,6 +2493,7 @@
     <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="4" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="22">
     <cellStyle name="20% - Accent5 2" xfId="18" xr:uid="{4C3A48E2-3C46-4D12-9A64-54698D8BF8EE}"/>
@@ -3957,7 +3964,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3360854E-4C4D-467D-BD8A-32231E61C6CE}">
-  <dimension ref="A1:AY146"/>
+  <dimension ref="A1:AY145"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" style="45" customWidth="1"/>
@@ -4190,16 +4197,32 @@
       <c r="Y8" s="45" t="s">
         <v>141</v>
       </c>
+      <c r="Z8" s="77" t="s">
+        <v>58</v>
+      </c>
+      <c r="AB8" s="77" t="s">
+        <v>88</v>
+      </c>
       <c r="AE8" s="46"/>
     </row>
     <row r="9" spans="2:51" x14ac:dyDescent="0.25">
-      <c r="V9" s="50"/>
+      <c r="V9" s="50" t="s">
+        <v>139</v>
+      </c>
       <c r="W9" s="50"/>
-      <c r="X9" s="50"/>
-      <c r="Y9" s="50"/>
-      <c r="Z9" s="50"/>
+      <c r="X9" s="50" t="s">
+        <v>153</v>
+      </c>
+      <c r="Y9" s="50" t="s">
+        <v>154</v>
+      </c>
+      <c r="Z9" s="77" t="s">
+        <v>58</v>
+      </c>
       <c r="AA9" s="50"/>
-      <c r="AB9" s="50"/>
+      <c r="AB9" s="77" t="s">
+        <v>88</v>
+      </c>
       <c r="AC9" s="50"/>
       <c r="AD9" s="50"/>
     </row>
@@ -4539,7 +4562,7 @@
         <v>66</v>
       </c>
       <c r="Y17" s="62" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="Z17" s="45" t="s">
         <v>58</v>
@@ -4578,8 +4601,9 @@
         <f>PRI_Sector_Fuels!P5</f>
         <v>MANBIOMIN</v>
       </c>
-      <c r="D18" s="50" t="s">
-        <v>107</v>
+      <c r="D18" s="50" t="str">
+        <f>X9</f>
+        <v>RENHEAT</v>
       </c>
       <c r="E18" s="43">
         <v>2030</v>
@@ -4612,15 +4636,15 @@
       <c r="Q18" s="43"/>
       <c r="R18" s="43"/>
       <c r="S18" s="43"/>
-      <c r="V18" s="60" t="s">
-        <v>128</v>
+      <c r="V18" s="87" t="s">
+        <v>139</v>
       </c>
       <c r="W18" s="60"/>
       <c r="X18" s="61" t="s">
         <v>94</v>
       </c>
       <c r="Y18" s="62" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="Z18" s="45" t="s">
         <v>58</v>
@@ -4695,7 +4719,7 @@
         <v>95</v>
       </c>
       <c r="Y19" s="62" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Z19" s="45" t="s">
         <v>58</v>
@@ -4773,7 +4797,7 @@
         <v>96</v>
       </c>
       <c r="Y20" s="62" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Z20" s="45" t="s">
         <v>58</v>
@@ -4851,7 +4875,7 @@
         <v>97</v>
       </c>
       <c r="Y21" s="62" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Z21" s="45" t="s">
         <v>58</v>
@@ -4931,7 +4955,7 @@
         <v>65</v>
       </c>
       <c r="Y22" s="62" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="Z22" s="45" t="s">
         <v>58</v>
@@ -5011,7 +5035,7 @@
         <v>89</v>
       </c>
       <c r="Y23" s="62" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="Z23" s="45" t="s">
         <v>58</v>
@@ -5048,8 +5072,8 @@
         <v>SOLAR</v>
       </c>
       <c r="D24" s="50" t="str">
-        <f>X8</f>
-        <v>SOLTHERMAL</v>
+        <f>X9</f>
+        <v>RENHEAT</v>
       </c>
       <c r="E24" s="43">
         <v>2030</v>
@@ -5090,7 +5114,7 @@
         <v>90</v>
       </c>
       <c r="Y24" s="62" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="Z24" s="45" t="s">
         <v>58</v>
@@ -5165,7 +5189,7 @@
         <v>129</v>
       </c>
       <c r="Y25" s="62" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Z25" s="45" t="s">
         <v>58</v>
@@ -5242,7 +5266,7 @@
         <v>137</v>
       </c>
       <c r="Y26" s="62" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Z26" s="45" t="s">
         <v>58</v>
@@ -5312,14 +5336,14 @@
       <c r="R27" s="68"/>
       <c r="S27" s="43"/>
       <c r="V27" s="45" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="W27" s="45"/>
       <c r="X27" s="45" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="Y27" s="45" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Z27" s="45" t="s">
         <v>58</v>
@@ -5388,12 +5412,6 @@
       <c r="Q28" s="64"/>
       <c r="R28" s="68"/>
       <c r="S28" s="43"/>
-      <c r="V28" s="45"/>
-      <c r="W28" s="45"/>
-      <c r="X28" s="45"/>
-      <c r="Y28" s="45"/>
-      <c r="Z28" s="45"/>
-      <c r="AA28" s="45"/>
       <c r="AI28"/>
       <c r="AJ28"/>
       <c r="AK28" s="45"/>
@@ -5451,6 +5469,15 @@
       <c r="Q29" s="64"/>
       <c r="R29" s="68"/>
       <c r="S29" s="43"/>
+      <c r="V29" s="45"/>
+      <c r="W29" s="45"/>
+      <c r="X29" s="45"/>
+      <c r="Y29" s="45"/>
+      <c r="Z29" s="45"/>
+      <c r="AA29" s="45"/>
+      <c r="AB29" s="45"/>
+      <c r="AC29" s="45"/>
+      <c r="AD29" s="45"/>
       <c r="AI29"/>
       <c r="AJ29"/>
       <c r="AK29" s="45"/>
@@ -5470,11 +5497,11 @@
     <row r="30" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B30" s="45" t="str">
         <f>X27</f>
-        <v>SOLTHT</v>
+        <v>RENTHT</v>
       </c>
       <c r="C30" s="50" t="str">
-        <f>X8</f>
-        <v>SOLTHERMAL</v>
+        <f>X9</f>
+        <v>RENHEAT</v>
       </c>
       <c r="D30" s="84" t="s">
         <v>107</v>
@@ -5565,24 +5592,24 @@
       <c r="AD31" s="45"/>
       <c r="AI31"/>
       <c r="AJ31"/>
-      <c r="AK31" s="77"/>
-      <c r="AL31" s="77"/>
-      <c r="AM31" s="77"/>
-      <c r="AN31" s="77"/>
-      <c r="AO31" s="77"/>
-      <c r="AP31" s="77"/>
-      <c r="AQ31" s="77"/>
-      <c r="AR31" s="77"/>
-      <c r="AS31" s="77"/>
-      <c r="AT31" s="77"/>
-      <c r="AU31" s="77"/>
-      <c r="AV31" s="77"/>
-      <c r="AW31" s="77"/>
+      <c r="AK31" s="45"/>
+      <c r="AL31" s="45"/>
+      <c r="AM31" s="45"/>
+      <c r="AN31" s="45"/>
+      <c r="AO31" s="45"/>
+      <c r="AP31" s="45"/>
+      <c r="AQ31" s="45"/>
+      <c r="AR31" s="45"/>
+      <c r="AS31" s="45"/>
+      <c r="AT31" s="45"/>
+      <c r="AU31" s="45"/>
+      <c r="AV31" s="45"/>
+      <c r="AW31" s="45"/>
     </row>
     <row r="32" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="45"/>
+      <c r="B32" s="50"/>
       <c r="C32" s="50"/>
-      <c r="D32" s="84"/>
+      <c r="D32" s="50"/>
       <c r="E32" s="43"/>
       <c r="F32" s="64"/>
       <c r="G32" s="64"/>
@@ -5609,31 +5636,26 @@
       <c r="AD32" s="45"/>
       <c r="AI32"/>
       <c r="AJ32"/>
-      <c r="AK32" s="45"/>
-      <c r="AL32" s="45"/>
+      <c r="AK32" s="39"/>
+      <c r="AL32" s="39"/>
       <c r="AM32" s="45"/>
       <c r="AN32" s="45"/>
       <c r="AO32" s="45"/>
-      <c r="AP32" s="45"/>
-      <c r="AQ32" s="45"/>
-      <c r="AR32" s="45"/>
-      <c r="AS32" s="45"/>
-      <c r="AT32" s="45"/>
+      <c r="AQ32"/>
+      <c r="AR32"/>
+      <c r="AS32" s="39"/>
+      <c r="AT32" s="39"/>
       <c r="AU32" s="45"/>
       <c r="AV32" s="45"/>
-      <c r="AW32" s="45"/>
     </row>
     <row r="33" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B33" s="50"/>
       <c r="C33" s="50"/>
       <c r="D33" s="50"/>
       <c r="E33" s="43"/>
-      <c r="F33" s="64"/>
-      <c r="G33" s="64"/>
       <c r="H33" s="43"/>
       <c r="I33" s="64"/>
-      <c r="J33" s="64"/>
-      <c r="K33" s="64"/>
+      <c r="J33" s="45"/>
       <c r="L33" s="64"/>
       <c r="M33" s="68"/>
       <c r="N33" s="68"/>
@@ -5642,13 +5664,13 @@
       <c r="Q33" s="64"/>
       <c r="R33" s="68"/>
       <c r="S33" s="43"/>
-      <c r="V33" s="45"/>
-      <c r="W33" s="45"/>
-      <c r="X33" s="45"/>
-      <c r="Y33" s="45"/>
-      <c r="Z33" s="45"/>
-      <c r="AA33" s="45"/>
-      <c r="AB33" s="45"/>
+      <c r="V33" s="38"/>
+      <c r="W33" s="38"/>
+      <c r="X33" s="39"/>
+      <c r="Y33" s="40"/>
+      <c r="Z33" s="38"/>
+      <c r="AA33" s="38"/>
+      <c r="AB33" s="38"/>
       <c r="AC33" s="45"/>
       <c r="AD33" s="45"/>
       <c r="AI33"/>
@@ -5674,20 +5696,20 @@
       <c r="I34" s="64"/>
       <c r="J34" s="45"/>
       <c r="L34" s="64"/>
-      <c r="M34" s="68"/>
+      <c r="M34" s="43"/>
       <c r="N34" s="68"/>
-      <c r="O34" s="64"/>
-      <c r="P34" s="64"/>
-      <c r="Q34" s="64"/>
-      <c r="R34" s="68"/>
+      <c r="O34" s="43"/>
+      <c r="P34" s="43"/>
+      <c r="Q34" s="43"/>
+      <c r="R34" s="43"/>
       <c r="S34" s="43"/>
-      <c r="V34" s="45"/>
-      <c r="W34" s="45"/>
-      <c r="X34" s="45"/>
-      <c r="Y34" s="45"/>
-      <c r="Z34" s="45"/>
-      <c r="AA34" s="45"/>
-      <c r="AB34" s="45"/>
+      <c r="V34" s="38"/>
+      <c r="W34" s="38"/>
+      <c r="X34" s="39"/>
+      <c r="Y34" s="40"/>
+      <c r="Z34" s="38"/>
+      <c r="AA34" s="38"/>
+      <c r="AB34" s="38"/>
       <c r="AC34" s="45"/>
       <c r="AD34" s="45"/>
       <c r="AI34"/>
@@ -5705,28 +5727,20 @@
       <c r="AV34" s="45"/>
     </row>
     <row r="35" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="50"/>
+      <c r="B35" s="45"/>
       <c r="C35" s="50"/>
       <c r="D35" s="50"/>
-      <c r="E35" s="43"/>
-      <c r="H35" s="43"/>
-      <c r="I35" s="64"/>
-      <c r="J35" s="45"/>
-      <c r="L35" s="64"/>
-      <c r="M35" s="43"/>
-      <c r="N35" s="68"/>
-      <c r="O35" s="43"/>
-      <c r="P35" s="43"/>
-      <c r="Q35" s="43"/>
-      <c r="R35" s="43"/>
-      <c r="S35" s="43"/>
-      <c r="V35" s="38"/>
-      <c r="W35" s="38"/>
-      <c r="X35" s="39"/>
-      <c r="Y35" s="40"/>
-      <c r="Z35" s="38"/>
-      <c r="AA35" s="38"/>
-      <c r="AB35" s="38"/>
+      <c r="E35" s="64"/>
+      <c r="F35" s="65"/>
+      <c r="K35" s="45"/>
+      <c r="N35" s="65"/>
+      <c r="V35" s="45"/>
+      <c r="W35" s="45"/>
+      <c r="X35" s="45"/>
+      <c r="Y35" s="45"/>
+      <c r="Z35" s="50"/>
+      <c r="AA35" s="50"/>
+      <c r="AB35" s="63"/>
       <c r="AC35" s="45"/>
       <c r="AD35" s="45"/>
       <c r="AI35"/>
@@ -5744,20 +5758,19 @@
       <c r="AV35" s="45"/>
     </row>
     <row r="36" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="45"/>
+      <c r="B36" s="50"/>
       <c r="C36" s="50"/>
       <c r="D36" s="50"/>
       <c r="E36" s="64"/>
       <c r="F36" s="65"/>
+      <c r="J36" s="66"/>
       <c r="K36" s="45"/>
       <c r="N36" s="65"/>
-      <c r="V36" s="38"/>
-      <c r="W36" s="38"/>
-      <c r="X36" s="39"/>
-      <c r="Y36" s="40"/>
-      <c r="Z36" s="38"/>
-      <c r="AA36" s="38"/>
-      <c r="AB36" s="38"/>
+      <c r="V36" s="45"/>
+      <c r="X36" s="45"/>
+      <c r="Z36" s="54"/>
+      <c r="AA36" s="54"/>
+      <c r="AB36" s="45"/>
       <c r="AC36" s="45"/>
       <c r="AD36" s="45"/>
       <c r="AI36"/>
@@ -5776,22 +5789,25 @@
     </row>
     <row r="37" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B37" s="50"/>
-      <c r="C37" s="50"/>
+      <c r="C37" s="45"/>
       <c r="D37" s="50"/>
       <c r="E37" s="64"/>
-      <c r="F37" s="65"/>
-      <c r="J37" s="66"/>
+      <c r="F37" s="67"/>
+      <c r="G37" s="45"/>
+      <c r="H37" s="45"/>
+      <c r="I37" s="45"/>
+      <c r="J37" s="68"/>
       <c r="K37" s="45"/>
-      <c r="N37" s="65"/>
       <c r="V37" s="45"/>
       <c r="W37" s="45"/>
       <c r="X37" s="45"/>
       <c r="Y37" s="45"/>
-      <c r="Z37" s="50"/>
-      <c r="AA37" s="50"/>
-      <c r="AB37" s="63"/>
+      <c r="Z37" s="45"/>
+      <c r="AA37" s="45"/>
+      <c r="AB37" s="45"/>
       <c r="AC37" s="45"/>
       <c r="AD37" s="45"/>
+      <c r="AE37" s="45"/>
       <c r="AI37"/>
       <c r="AJ37"/>
       <c r="AK37" s="39"/>
@@ -5807,9 +5823,9 @@
       <c r="AV37" s="45"/>
     </row>
     <row r="38" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="50"/>
+      <c r="B38" s="45"/>
       <c r="C38" s="45"/>
-      <c r="D38" s="50"/>
+      <c r="D38" s="45"/>
       <c r="E38" s="64"/>
       <c r="F38" s="67"/>
       <c r="G38" s="45"/>
@@ -5818,12 +5834,15 @@
       <c r="J38" s="68"/>
       <c r="K38" s="45"/>
       <c r="V38" s="45"/>
+      <c r="W38" s="45"/>
       <c r="X38" s="45"/>
-      <c r="Z38" s="54"/>
-      <c r="AA38" s="54"/>
+      <c r="Y38" s="45"/>
+      <c r="Z38" s="45"/>
+      <c r="AA38" s="45"/>
       <c r="AB38" s="45"/>
       <c r="AC38" s="45"/>
       <c r="AD38" s="45"/>
+      <c r="AE38" s="45"/>
       <c r="AI38"/>
       <c r="AJ38"/>
       <c r="AK38" s="39"/>
@@ -5838,45 +5857,30 @@
       <c r="AU38" s="45"/>
       <c r="AV38" s="45"/>
     </row>
-    <row r="39" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="45"/>
-      <c r="C39" s="45"/>
-      <c r="D39" s="45"/>
-      <c r="E39" s="64"/>
+    <row r="39" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A39" s="46"/>
       <c r="F39" s="67"/>
-      <c r="G39" s="45"/>
-      <c r="H39" s="45"/>
-      <c r="I39" s="45"/>
-      <c r="J39" s="68"/>
-      <c r="K39" s="45"/>
-      <c r="V39" s="45"/>
-      <c r="W39" s="45"/>
-      <c r="X39" s="45"/>
-      <c r="Y39" s="45"/>
-      <c r="Z39" s="45"/>
-      <c r="AA39" s="45"/>
-      <c r="AB39" s="45"/>
-      <c r="AC39" s="45"/>
-      <c r="AD39" s="45"/>
-      <c r="AE39" s="45"/>
+      <c r="G39" s="43"/>
+      <c r="H39" s="69"/>
+      <c r="M39" s="46"/>
+      <c r="N39" s="46"/>
+      <c r="O39" s="46"/>
+      <c r="P39" s="46"/>
+      <c r="Q39" s="46"/>
+      <c r="R39" s="46"/>
+      <c r="S39" s="46"/>
       <c r="AI39"/>
       <c r="AJ39"/>
       <c r="AK39" s="39"/>
       <c r="AL39" s="39"/>
-      <c r="AM39" s="45"/>
-      <c r="AN39" s="45"/>
-      <c r="AO39" s="45"/>
+      <c r="AP39" s="46"/>
       <c r="AQ39"/>
       <c r="AR39"/>
       <c r="AS39" s="39"/>
       <c r="AT39" s="39"/>
-      <c r="AU39" s="45"/>
-      <c r="AV39" s="45"/>
     </row>
     <row r="40" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A40" s="46"/>
-      <c r="F40" s="67"/>
-      <c r="G40" s="43"/>
       <c r="H40" s="69"/>
       <c r="M40" s="46"/>
       <c r="N40" s="46"/>
@@ -5896,29 +5900,24 @@
       <c r="AT40" s="39"/>
     </row>
     <row r="41" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A41" s="46"/>
+      <c r="B41" s="70"/>
+      <c r="C41" s="45" t="s">
+        <v>82</v>
+      </c>
       <c r="H41" s="69"/>
-      <c r="M41" s="46"/>
-      <c r="N41" s="46"/>
-      <c r="O41" s="46"/>
-      <c r="P41" s="46"/>
-      <c r="Q41" s="46"/>
-      <c r="R41" s="46"/>
-      <c r="S41" s="46"/>
       <c r="AI41"/>
       <c r="AJ41"/>
       <c r="AK41" s="39"/>
       <c r="AL41" s="39"/>
-      <c r="AP41" s="46"/>
       <c r="AQ41"/>
       <c r="AR41"/>
       <c r="AS41" s="39"/>
       <c r="AT41" s="39"/>
     </row>
     <row r="42" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="B42" s="70"/>
+      <c r="B42" s="71"/>
       <c r="C42" s="45" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H42" s="69"/>
       <c r="AI42"/>
@@ -5931,10 +5930,6 @@
       <c r="AT42" s="39"/>
     </row>
     <row r="43" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="B43" s="71"/>
-      <c r="C43" s="45" t="s">
-        <v>83</v>
-      </c>
       <c r="H43" s="69"/>
       <c r="AI43"/>
       <c r="AJ43"/>
@@ -5946,7 +5941,6 @@
       <c r="AT43" s="39"/>
     </row>
     <row r="44" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="H44" s="69"/>
       <c r="AI44"/>
       <c r="AJ44"/>
       <c r="AK44" s="39"/>
@@ -5967,6 +5961,7 @@
       <c r="AT45" s="39"/>
     </row>
     <row r="46" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="E46" s="43"/>
       <c r="AI46"/>
       <c r="AJ46"/>
       <c r="AK46" s="39"/>
@@ -5977,7 +5972,6 @@
       <c r="AT46" s="39"/>
     </row>
     <row r="47" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="E47" s="43"/>
       <c r="AI47"/>
       <c r="AJ47"/>
       <c r="AK47" s="39"/>
@@ -6038,6 +6032,17 @@
       <c r="AT52" s="39"/>
     </row>
     <row r="53" spans="2:46" x14ac:dyDescent="0.25">
+      <c r="B53" s="73"/>
+      <c r="C53" s="73"/>
+      <c r="D53"/>
+      <c r="E53"/>
+      <c r="F53"/>
+      <c r="G53"/>
+      <c r="H53"/>
+      <c r="I53"/>
+      <c r="J53"/>
+      <c r="K53"/>
+      <c r="L53"/>
       <c r="AI53"/>
       <c r="AJ53"/>
       <c r="AK53" s="39"/>
@@ -6047,18 +6052,18 @@
       <c r="AS53" s="39"/>
       <c r="AT53" s="39"/>
     </row>
-    <row r="54" spans="2:46" x14ac:dyDescent="0.25">
-      <c r="B54" s="73"/>
-      <c r="C54" s="73"/>
-      <c r="D54"/>
-      <c r="E54"/>
-      <c r="F54"/>
-      <c r="G54"/>
-      <c r="H54"/>
-      <c r="I54"/>
-      <c r="J54"/>
-      <c r="K54"/>
-      <c r="L54"/>
+    <row r="54" spans="2:46" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B54" s="74"/>
+      <c r="C54" s="74"/>
+      <c r="D54" s="74"/>
+      <c r="E54" s="74"/>
+      <c r="F54" s="74"/>
+      <c r="G54" s="74"/>
+      <c r="H54" s="74"/>
+      <c r="I54" s="74"/>
+      <c r="J54" s="74"/>
+      <c r="K54" s="74"/>
+      <c r="L54" s="74"/>
       <c r="AI54"/>
       <c r="AJ54"/>
       <c r="AK54" s="39"/>
@@ -6068,18 +6073,18 @@
       <c r="AS54" s="39"/>
       <c r="AT54" s="39"/>
     </row>
-    <row r="55" spans="2:46" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="74"/>
-      <c r="C55" s="74"/>
-      <c r="D55" s="74"/>
-      <c r="E55" s="74"/>
-      <c r="F55" s="74"/>
-      <c r="G55" s="74"/>
-      <c r="H55" s="74"/>
-      <c r="I55" s="74"/>
-      <c r="J55" s="74"/>
-      <c r="K55" s="74"/>
-      <c r="L55" s="74"/>
+    <row r="55" spans="2:46" x14ac:dyDescent="0.25">
+      <c r="B55"/>
+      <c r="C55"/>
+      <c r="D55"/>
+      <c r="E55" s="1"/>
+      <c r="F55"/>
+      <c r="G55"/>
+      <c r="H55"/>
+      <c r="I55"/>
+      <c r="J55"/>
+      <c r="K55"/>
+      <c r="L55"/>
       <c r="AI55"/>
       <c r="AJ55"/>
       <c r="AK55" s="39"/>
@@ -6237,17 +6242,6 @@
       <c r="AT62" s="39"/>
     </row>
     <row r="63" spans="2:46" x14ac:dyDescent="0.25">
-      <c r="B63"/>
-      <c r="C63"/>
-      <c r="D63"/>
-      <c r="E63" s="1"/>
-      <c r="F63"/>
-      <c r="G63"/>
-      <c r="H63"/>
-      <c r="I63"/>
-      <c r="J63"/>
-      <c r="K63"/>
-      <c r="L63"/>
       <c r="AI63"/>
       <c r="AJ63"/>
       <c r="AK63" s="39"/>
@@ -6278,6 +6272,15 @@
       <c r="AT65" s="39"/>
     </row>
     <row r="66" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="V66" s="46"/>
+      <c r="W66" s="46"/>
+      <c r="X66" s="46"/>
+      <c r="Y66" s="46"/>
+      <c r="Z66" s="46"/>
+      <c r="AA66" s="46"/>
+      <c r="AB66" s="46"/>
+      <c r="AC66" s="46"/>
+      <c r="AD66" s="46"/>
       <c r="AI66"/>
       <c r="AJ66"/>
       <c r="AK66" s="39"/>
@@ -6288,6 +6291,16 @@
       <c r="AT66" s="39"/>
     </row>
     <row r="67" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="V67" s="46"/>
+      <c r="W67" s="46"/>
+      <c r="X67" s="46"/>
+      <c r="Y67" s="46"/>
+      <c r="Z67" s="46"/>
+      <c r="AA67" s="46"/>
+      <c r="AB67" s="46"/>
+      <c r="AC67" s="46"/>
+      <c r="AD67" s="46"/>
+      <c r="AE67" s="46"/>
       <c r="AI67"/>
       <c r="AJ67"/>
       <c r="AK67" s="39"/>
@@ -6298,6 +6311,16 @@
       <c r="AT67" s="39"/>
     </row>
     <row r="68" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="B68"/>
+      <c r="C68"/>
+      <c r="E68" s="73"/>
+      <c r="F68" s="73"/>
+      <c r="G68" s="1"/>
+      <c r="H68"/>
+      <c r="I68" s="73"/>
+      <c r="J68"/>
+      <c r="K68"/>
+      <c r="L68" s="73"/>
       <c r="V68" s="46"/>
       <c r="W68" s="46"/>
       <c r="X68" s="46"/>
@@ -6307,6 +6330,7 @@
       <c r="AB68" s="46"/>
       <c r="AC68" s="46"/>
       <c r="AD68" s="46"/>
+      <c r="AE68" s="46"/>
       <c r="AI68"/>
       <c r="AJ68"/>
       <c r="AK68" s="39"/>
@@ -6316,73 +6340,86 @@
       <c r="AS68" s="39"/>
       <c r="AT68" s="39"/>
     </row>
-    <row r="69" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="B69"/>
-      <c r="C69"/>
-      <c r="E69" s="73"/>
-      <c r="F69" s="73"/>
-      <c r="G69" s="1"/>
-      <c r="H69"/>
-      <c r="I69" s="73"/>
-      <c r="J69"/>
-      <c r="K69"/>
-      <c r="L69" s="73"/>
-      <c r="V69" s="46"/>
-      <c r="W69" s="46"/>
-      <c r="X69" s="46"/>
-      <c r="Y69" s="46"/>
-      <c r="Z69" s="46"/>
-      <c r="AA69" s="46"/>
-      <c r="AB69" s="46"/>
-      <c r="AC69" s="46"/>
-      <c r="AD69" s="46"/>
-      <c r="AE69" s="46"/>
+    <row r="69" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="45"/>
+      <c r="B69" s="79"/>
+      <c r="C69" s="79"/>
+      <c r="D69" s="79"/>
+      <c r="E69" s="79"/>
+      <c r="F69" s="79"/>
+      <c r="G69" s="79"/>
+      <c r="H69" s="80"/>
+      <c r="I69" s="79"/>
+      <c r="J69" s="79"/>
+      <c r="K69" s="79"/>
+      <c r="L69" s="79"/>
+      <c r="M69" s="45"/>
+      <c r="N69" s="45"/>
+      <c r="O69" s="45"/>
+      <c r="P69" s="45"/>
+      <c r="Q69" s="45"/>
+      <c r="R69" s="45"/>
+      <c r="S69" s="45"/>
+      <c r="V69" s="45"/>
+      <c r="W69" s="45"/>
+      <c r="X69" s="45"/>
+      <c r="Y69" s="45"/>
+      <c r="Z69" s="45"/>
+      <c r="AA69" s="45"/>
+      <c r="AB69" s="45"/>
+      <c r="AC69" s="45"/>
+      <c r="AD69" s="45"/>
       <c r="AI69"/>
-      <c r="AJ69"/>
+      <c r="AJ69" s="80"/>
       <c r="AK69" s="39"/>
-      <c r="AL69" s="39"/>
+      <c r="AL69" s="41"/>
+      <c r="AM69" s="45"/>
+      <c r="AN69" s="45"/>
       <c r="AQ69"/>
-      <c r="AR69"/>
+      <c r="AR69" s="80"/>
       <c r="AS69" s="39"/>
-      <c r="AT69" s="39"/>
+      <c r="AT69" s="41"/>
+      <c r="AU69" s="45"/>
+      <c r="AV69" s="45"/>
     </row>
     <row r="70" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="45"/>
-      <c r="B70" s="79"/>
-      <c r="C70" s="79"/>
-      <c r="D70" s="79"/>
-      <c r="E70" s="79"/>
-      <c r="F70" s="79"/>
-      <c r="G70" s="79"/>
+      <c r="A70" s="73"/>
+      <c r="B70" s="81"/>
+      <c r="C70" s="82"/>
+      <c r="D70" s="81"/>
+      <c r="E70" s="81"/>
+      <c r="F70" s="81"/>
+      <c r="G70" s="81"/>
       <c r="H70" s="80"/>
-      <c r="I70" s="79"/>
-      <c r="J70" s="79"/>
-      <c r="K70" s="79"/>
-      <c r="L70" s="79"/>
-      <c r="M70" s="45"/>
-      <c r="N70" s="45"/>
-      <c r="O70" s="45"/>
+      <c r="I70" s="81"/>
+      <c r="J70" s="81"/>
+      <c r="K70" s="82"/>
+      <c r="L70" s="82"/>
+      <c r="M70" s="73"/>
+      <c r="N70" s="73"/>
+      <c r="O70" s="1"/>
       <c r="P70" s="45"/>
       <c r="Q70" s="45"/>
       <c r="R70" s="45"/>
       <c r="S70" s="45"/>
-      <c r="AI70"/>
-      <c r="AJ70" s="80"/>
-      <c r="AK70" s="39"/>
-      <c r="AL70" s="41"/>
-      <c r="AM70" s="45"/>
-      <c r="AN70" s="45"/>
-      <c r="AQ70"/>
-      <c r="AR70" s="80"/>
-      <c r="AS70" s="39"/>
-      <c r="AT70" s="41"/>
-      <c r="AU70" s="45"/>
-      <c r="AV70" s="45"/>
+      <c r="V70" s="45"/>
+      <c r="W70" s="45"/>
+      <c r="X70" s="45"/>
+      <c r="Y70" s="45"/>
+      <c r="Z70" s="45"/>
+      <c r="AA70" s="45"/>
+      <c r="AB70" s="45"/>
+      <c r="AC70" s="45"/>
+      <c r="AD70" s="45"/>
+      <c r="AE70" s="45"/>
+      <c r="AI70" s="42"/>
+      <c r="AJ70" s="42"/>
+      <c r="AK70" s="54"/>
     </row>
     <row r="71" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="73"/>
+      <c r="A71" s="79"/>
       <c r="B71" s="81"/>
-      <c r="C71" s="82"/>
+      <c r="C71" s="81"/>
       <c r="D71" s="81"/>
       <c r="E71" s="81"/>
       <c r="F71" s="81"/>
@@ -6390,15 +6427,11 @@
       <c r="H71" s="80"/>
       <c r="I71" s="81"/>
       <c r="J71" s="81"/>
-      <c r="K71" s="82"/>
-      <c r="L71" s="82"/>
-      <c r="M71" s="73"/>
-      <c r="N71" s="73"/>
-      <c r="O71" s="1"/>
-      <c r="P71" s="45"/>
-      <c r="Q71" s="45"/>
-      <c r="R71" s="45"/>
-      <c r="S71" s="45"/>
+      <c r="K71" s="81"/>
+      <c r="L71" s="81"/>
+      <c r="M71" s="79"/>
+      <c r="N71" s="79"/>
+      <c r="O71" s="79"/>
       <c r="V71" s="45"/>
       <c r="W71" s="45"/>
       <c r="X71" s="45"/>
@@ -6408,52 +6441,44 @@
       <c r="AB71" s="45"/>
       <c r="AC71" s="45"/>
       <c r="AD71" s="45"/>
+      <c r="AE71" s="45"/>
       <c r="AI71" s="42"/>
       <c r="AJ71" s="42"/>
       <c r="AK71" s="54"/>
     </row>
-    <row r="72" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="79"/>
-      <c r="B72" s="81"/>
-      <c r="C72" s="81"/>
-      <c r="D72" s="81"/>
-      <c r="E72" s="81"/>
-      <c r="F72" s="81"/>
-      <c r="G72" s="81"/>
-      <c r="H72" s="80"/>
-      <c r="I72" s="81"/>
-      <c r="J72" s="81"/>
-      <c r="K72" s="81"/>
-      <c r="L72" s="81"/>
-      <c r="M72" s="79"/>
-      <c r="N72" s="79"/>
-      <c r="O72" s="79"/>
-      <c r="V72" s="45"/>
-      <c r="W72" s="45"/>
-      <c r="X72" s="45"/>
-      <c r="Y72" s="45"/>
-      <c r="Z72" s="45"/>
-      <c r="AA72" s="45"/>
-      <c r="AB72" s="45"/>
-      <c r="AC72" s="45"/>
-      <c r="AD72" s="45"/>
-      <c r="AE72" s="45"/>
-      <c r="AI72" s="42"/>
-      <c r="AJ72" s="42"/>
-      <c r="AK72" s="54"/>
+    <row r="72" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A72" s="81"/>
+      <c r="B72"/>
+      <c r="C72" s="39"/>
+      <c r="D72" s="39"/>
+      <c r="H72"/>
+      <c r="I72"/>
+      <c r="J72"/>
+      <c r="K72" s="39"/>
+      <c r="L72" s="39"/>
+      <c r="M72" s="82"/>
+      <c r="N72" s="82"/>
+      <c r="O72" s="81"/>
+      <c r="P72" s="46"/>
+      <c r="Q72" s="46"/>
+      <c r="R72" s="46"/>
+      <c r="S72" s="46"/>
+      <c r="AI72" s="38"/>
+      <c r="AJ72" s="38"/>
+      <c r="AK72" s="50"/>
     </row>
     <row r="73" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A73" s="81"/>
       <c r="B73"/>
       <c r="C73" s="39"/>
       <c r="D73" s="39"/>
-      <c r="H73"/>
+      <c r="H73" s="78"/>
       <c r="I73"/>
       <c r="J73"/>
       <c r="K73" s="39"/>
       <c r="L73" s="39"/>
-      <c r="M73" s="82"/>
-      <c r="N73" s="82"/>
+      <c r="M73" s="81"/>
+      <c r="N73" s="81"/>
       <c r="O73" s="81"/>
       <c r="P73" s="46"/>
       <c r="Q73" s="46"/>
@@ -6464,22 +6489,14 @@
       <c r="AK73" s="50"/>
     </row>
     <row r="74" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A74" s="81"/>
+      <c r="A74"/>
       <c r="B74"/>
       <c r="C74" s="39"/>
       <c r="D74" s="39"/>
-      <c r="H74" s="78"/>
       <c r="I74"/>
       <c r="J74"/>
       <c r="K74" s="39"/>
       <c r="L74" s="39"/>
-      <c r="M74" s="81"/>
-      <c r="N74" s="81"/>
-      <c r="O74" s="81"/>
-      <c r="P74" s="46"/>
-      <c r="Q74" s="46"/>
-      <c r="R74" s="46"/>
-      <c r="S74" s="46"/>
       <c r="AI74" s="38"/>
       <c r="AJ74" s="38"/>
       <c r="AK74" s="50"/>
@@ -6502,10 +6519,12 @@
       <c r="B76"/>
       <c r="C76" s="39"/>
       <c r="D76" s="39"/>
+      <c r="H76" s="46"/>
       <c r="I76"/>
       <c r="J76"/>
       <c r="K76" s="39"/>
       <c r="L76" s="39"/>
+      <c r="O76" s="46"/>
       <c r="AI76" s="38"/>
       <c r="AJ76" s="38"/>
       <c r="AK76" s="50"/>
@@ -6725,12 +6744,10 @@
       <c r="B91"/>
       <c r="C91" s="39"/>
       <c r="D91" s="39"/>
-      <c r="H91" s="46"/>
       <c r="I91"/>
       <c r="J91"/>
       <c r="K91" s="39"/>
       <c r="L91" s="39"/>
-      <c r="O91" s="46"/>
       <c r="AI91" s="38"/>
       <c r="AJ91" s="38"/>
       <c r="AK91" s="50"/>
@@ -7101,13 +7118,6 @@
     </row>
     <row r="120" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A120"/>
-      <c r="B120"/>
-      <c r="C120" s="39"/>
-      <c r="D120" s="39"/>
-      <c r="I120"/>
-      <c r="J120"/>
-      <c r="K120" s="39"/>
-      <c r="L120" s="39"/>
       <c r="AI120" s="38"/>
       <c r="AJ120" s="38"/>
       <c r="AK120" s="50"/>
@@ -7119,7 +7129,6 @@
       <c r="AK121" s="50"/>
     </row>
     <row r="122" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A122"/>
       <c r="AI122" s="38"/>
       <c r="AJ122" s="38"/>
       <c r="AK122" s="50"/>
@@ -7238,11 +7247,6 @@
       <c r="AI145" s="38"/>
       <c r="AJ145" s="38"/>
       <c r="AK145" s="50"/>
-    </row>
-    <row r="146" spans="35:37" x14ac:dyDescent="0.25">
-      <c r="AI146" s="38"/>
-      <c r="AJ146" s="38"/>
-      <c r="AK146" s="50"/>
     </row>
   </sheetData>
   <phoneticPr fontId="24" type="noConversion"/>

--- a/SubRES_TMPL/SubRES_NewTechs.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF20CE3F-891C-406E-8ED6-5D189703483D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{045C2DFB-485C-4B60-AC23-372C24FA9D95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PRI_Sector_Fuels" sheetId="6" r:id="rId1"/>
@@ -1554,7 +1554,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="160">
   <si>
     <t>~FI_T</t>
   </si>
@@ -2022,6 +2022,18 @@
   </si>
   <si>
     <t>RENTHT</t>
+  </si>
+  <si>
+    <t>RENELC</t>
+  </si>
+  <si>
+    <t>Decentralized Electricity form Solar, Wind and Bio</t>
+  </si>
+  <si>
+    <t>MANELC_TECH</t>
+  </si>
+  <si>
+    <t>MANELC</t>
   </si>
 </sst>
 </file>
@@ -3964,7 +3976,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3360854E-4C4D-467D-BD8A-32231E61C6CE}">
-  <dimension ref="A1:AY145"/>
+  <dimension ref="A1:AY144"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" style="45" customWidth="1"/>
@@ -4227,13 +4239,23 @@
       <c r="AD9" s="50"/>
     </row>
     <row r="10" spans="2:51" x14ac:dyDescent="0.25">
-      <c r="V10" s="50"/>
+      <c r="V10" s="50" t="s">
+        <v>69</v>
+      </c>
       <c r="W10" s="50"/>
-      <c r="X10" s="50"/>
-      <c r="Y10" s="50"/>
-      <c r="Z10" s="50"/>
+      <c r="X10" s="50" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y10" s="50" t="s">
+        <v>157</v>
+      </c>
+      <c r="Z10" s="77" t="s">
+        <v>58</v>
+      </c>
       <c r="AA10" s="50"/>
-      <c r="AB10" s="50"/>
+      <c r="AB10" s="77" t="s">
+        <v>88</v>
+      </c>
       <c r="AC10" s="50"/>
       <c r="AD10" s="50"/>
     </row>
@@ -5224,8 +5246,9 @@
       <c r="C26" s="50" t="s">
         <v>130</v>
       </c>
-      <c r="D26" s="50" t="s">
-        <v>69</v>
+      <c r="D26" s="50" t="str">
+        <f>X10</f>
+        <v>RENELC</v>
       </c>
       <c r="E26" s="43">
         <v>2030</v>
@@ -5301,8 +5324,9 @@
       <c r="C27" s="50" t="s">
         <v>131</v>
       </c>
-      <c r="D27" s="50" t="s">
-        <v>69</v>
+      <c r="D27" s="50" t="str">
+        <f>X10</f>
+        <v>RENELC</v>
       </c>
       <c r="E27" s="43">
         <v>2030</v>
@@ -5435,8 +5459,9 @@
       <c r="C29" s="45" t="s">
         <v>135</v>
       </c>
-      <c r="D29" s="50" t="s">
-        <v>69</v>
+      <c r="D29" s="50" t="str">
+        <f>X10</f>
+        <v>RENELC</v>
       </c>
       <c r="E29" s="43">
         <v>2030</v>
@@ -5563,17 +5588,41 @@
       <c r="AW30" s="77"/>
     </row>
     <row r="31" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="45"/>
-      <c r="C31" s="50"/>
-      <c r="D31" s="84"/>
-      <c r="E31" s="43"/>
-      <c r="F31" s="64"/>
-      <c r="G31" s="64"/>
-      <c r="H31" s="43"/>
-      <c r="I31" s="64"/>
-      <c r="J31" s="64"/>
-      <c r="K31" s="64"/>
-      <c r="L31" s="64"/>
+      <c r="B31" s="50" t="str">
+        <f>X17</f>
+        <v>Furnace</v>
+      </c>
+      <c r="C31" s="50" t="str">
+        <f>X10</f>
+        <v>RENELC</v>
+      </c>
+      <c r="D31" s="84" t="s">
+        <v>107</v>
+      </c>
+      <c r="E31" s="43">
+        <v>2030</v>
+      </c>
+      <c r="F31" s="83">
+        <v>1</v>
+      </c>
+      <c r="G31" s="64">
+        <v>1</v>
+      </c>
+      <c r="H31" s="46">
+        <v>100</v>
+      </c>
+      <c r="I31" s="46">
+        <v>0</v>
+      </c>
+      <c r="J31" s="46">
+        <v>0</v>
+      </c>
+      <c r="K31" s="46">
+        <v>0</v>
+      </c>
+      <c r="L31" s="46">
+        <v>0</v>
+      </c>
       <c r="M31" s="68"/>
       <c r="N31" s="68"/>
       <c r="O31" s="64"/>
@@ -5607,17 +5656,41 @@
       <c r="AW31" s="45"/>
     </row>
     <row r="32" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="50"/>
-      <c r="C32" s="50"/>
-      <c r="D32" s="50"/>
-      <c r="E32" s="43"/>
-      <c r="F32" s="64"/>
-      <c r="G32" s="64"/>
-      <c r="H32" s="43"/>
-      <c r="I32" s="64"/>
-      <c r="J32" s="64"/>
-      <c r="K32" s="64"/>
-      <c r="L32" s="64"/>
+      <c r="B32" s="50" t="str">
+        <f>X21</f>
+        <v>ELCBoiler</v>
+      </c>
+      <c r="C32" s="50" t="str">
+        <f>X10</f>
+        <v>RENELC</v>
+      </c>
+      <c r="D32" s="50" t="s">
+        <v>107</v>
+      </c>
+      <c r="E32" s="43">
+        <v>2030</v>
+      </c>
+      <c r="F32" s="64">
+        <v>1</v>
+      </c>
+      <c r="G32" s="64">
+        <v>1</v>
+      </c>
+      <c r="H32" s="43">
+        <v>100</v>
+      </c>
+      <c r="I32" s="64">
+        <v>0</v>
+      </c>
+      <c r="J32" s="64">
+        <v>0</v>
+      </c>
+      <c r="K32" s="64">
+        <v>0</v>
+      </c>
+      <c r="L32" s="64">
+        <v>0</v>
+      </c>
       <c r="M32" s="68"/>
       <c r="N32" s="68"/>
       <c r="O32" s="64"/>
@@ -5625,13 +5698,13 @@
       <c r="Q32" s="64"/>
       <c r="R32" s="68"/>
       <c r="S32" s="43"/>
-      <c r="V32" s="45"/>
-      <c r="W32" s="45"/>
-      <c r="X32" s="45"/>
-      <c r="Y32" s="45"/>
-      <c r="Z32" s="45"/>
-      <c r="AA32" s="45"/>
-      <c r="AB32" s="45"/>
+      <c r="V32" s="38"/>
+      <c r="W32" s="38"/>
+      <c r="X32" s="39"/>
+      <c r="Y32" s="40"/>
+      <c r="Z32" s="38"/>
+      <c r="AA32" s="38"/>
+      <c r="AB32" s="38"/>
       <c r="AC32" s="45"/>
       <c r="AD32" s="45"/>
       <c r="AI32"/>
@@ -5649,20 +5722,45 @@
       <c r="AV32" s="45"/>
     </row>
     <row r="33" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="50"/>
-      <c r="C33" s="50"/>
-      <c r="D33" s="50"/>
-      <c r="E33" s="43"/>
-      <c r="H33" s="43"/>
-      <c r="I33" s="64"/>
-      <c r="J33" s="45"/>
-      <c r="L33" s="64"/>
-      <c r="M33" s="68"/>
+      <c r="B33" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="C33" s="50" t="s">
+        <v>156</v>
+      </c>
+      <c r="D33" s="50" t="s">
+        <v>159</v>
+      </c>
+      <c r="E33" s="43">
+        <v>2030</v>
+      </c>
+      <c r="F33" s="83">
+        <v>1</v>
+      </c>
+      <c r="G33" s="64">
+        <v>1</v>
+      </c>
+      <c r="H33" s="46">
+        <v>100</v>
+      </c>
+      <c r="I33" s="46">
+        <v>0</v>
+      </c>
+      <c r="J33" s="46">
+        <v>0</v>
+      </c>
+      <c r="K33" s="46">
+        <v>0</v>
+      </c>
+      <c r="L33" s="46">
+        <v>0</v>
+      </c>
+      <c r="M33" s="43"/>
       <c r="N33" s="68"/>
-      <c r="O33" s="64"/>
-      <c r="P33" s="64"/>
-      <c r="Q33" s="64"/>
-      <c r="R33" s="68"/>
+      <c r="O33" s="43"/>
+      <c r="P33" s="43"/>
+      <c r="Q33" s="43"/>
+      <c r="R33" s="43"/>
       <c r="S33" s="43"/>
       <c r="V33" s="38"/>
       <c r="W33" s="38"/>
@@ -5688,28 +5786,20 @@
       <c r="AV33" s="45"/>
     </row>
     <row r="34" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="50"/>
+      <c r="B34" s="45"/>
       <c r="C34" s="50"/>
       <c r="D34" s="50"/>
-      <c r="E34" s="43"/>
-      <c r="H34" s="43"/>
-      <c r="I34" s="64"/>
-      <c r="J34" s="45"/>
-      <c r="L34" s="64"/>
-      <c r="M34" s="43"/>
-      <c r="N34" s="68"/>
-      <c r="O34" s="43"/>
-      <c r="P34" s="43"/>
-      <c r="Q34" s="43"/>
-      <c r="R34" s="43"/>
-      <c r="S34" s="43"/>
-      <c r="V34" s="38"/>
-      <c r="W34" s="38"/>
-      <c r="X34" s="39"/>
-      <c r="Y34" s="40"/>
-      <c r="Z34" s="38"/>
-      <c r="AA34" s="38"/>
-      <c r="AB34" s="38"/>
+      <c r="E34" s="64"/>
+      <c r="F34" s="65"/>
+      <c r="K34" s="45"/>
+      <c r="N34" s="65"/>
+      <c r="V34" s="45"/>
+      <c r="W34" s="45"/>
+      <c r="X34" s="45"/>
+      <c r="Y34" s="45"/>
+      <c r="Z34" s="50"/>
+      <c r="AA34" s="50"/>
+      <c r="AB34" s="63"/>
       <c r="AC34" s="45"/>
       <c r="AD34" s="45"/>
       <c r="AI34"/>
@@ -5727,20 +5817,19 @@
       <c r="AV34" s="45"/>
     </row>
     <row r="35" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="45"/>
+      <c r="B35" s="50"/>
       <c r="C35" s="50"/>
       <c r="D35" s="50"/>
       <c r="E35" s="64"/>
       <c r="F35" s="65"/>
+      <c r="J35" s="66"/>
       <c r="K35" s="45"/>
       <c r="N35" s="65"/>
       <c r="V35" s="45"/>
-      <c r="W35" s="45"/>
       <c r="X35" s="45"/>
-      <c r="Y35" s="45"/>
-      <c r="Z35" s="50"/>
-      <c r="AA35" s="50"/>
-      <c r="AB35" s="63"/>
+      <c r="Z35" s="54"/>
+      <c r="AA35" s="54"/>
+      <c r="AB35" s="45"/>
       <c r="AC35" s="45"/>
       <c r="AD35" s="45"/>
       <c r="AI35"/>
@@ -5759,20 +5848,25 @@
     </row>
     <row r="36" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B36" s="50"/>
-      <c r="C36" s="50"/>
+      <c r="C36" s="45"/>
       <c r="D36" s="50"/>
       <c r="E36" s="64"/>
-      <c r="F36" s="65"/>
-      <c r="J36" s="66"/>
+      <c r="F36" s="67"/>
+      <c r="G36" s="45"/>
+      <c r="H36" s="45"/>
+      <c r="I36" s="45"/>
+      <c r="J36" s="68"/>
       <c r="K36" s="45"/>
-      <c r="N36" s="65"/>
       <c r="V36" s="45"/>
+      <c r="W36" s="45"/>
       <c r="X36" s="45"/>
-      <c r="Z36" s="54"/>
-      <c r="AA36" s="54"/>
+      <c r="Y36" s="45"/>
+      <c r="Z36" s="45"/>
+      <c r="AA36" s="45"/>
       <c r="AB36" s="45"/>
       <c r="AC36" s="45"/>
       <c r="AD36" s="45"/>
+      <c r="AE36" s="45"/>
       <c r="AI36"/>
       <c r="AJ36"/>
       <c r="AK36" s="39"/>
@@ -5788,9 +5882,9 @@
       <c r="AV36" s="45"/>
     </row>
     <row r="37" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="50"/>
+      <c r="B37" s="45"/>
       <c r="C37" s="45"/>
-      <c r="D37" s="50"/>
+      <c r="D37" s="45"/>
       <c r="E37" s="64"/>
       <c r="F37" s="67"/>
       <c r="G37" s="45"/>
@@ -5822,45 +5916,30 @@
       <c r="AU37" s="45"/>
       <c r="AV37" s="45"/>
     </row>
-    <row r="38" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="45"/>
-      <c r="C38" s="45"/>
-      <c r="D38" s="45"/>
-      <c r="E38" s="64"/>
+    <row r="38" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A38" s="46"/>
       <c r="F38" s="67"/>
-      <c r="G38" s="45"/>
-      <c r="H38" s="45"/>
-      <c r="I38" s="45"/>
-      <c r="J38" s="68"/>
-      <c r="K38" s="45"/>
-      <c r="V38" s="45"/>
-      <c r="W38" s="45"/>
-      <c r="X38" s="45"/>
-      <c r="Y38" s="45"/>
-      <c r="Z38" s="45"/>
-      <c r="AA38" s="45"/>
-      <c r="AB38" s="45"/>
-      <c r="AC38" s="45"/>
-      <c r="AD38" s="45"/>
-      <c r="AE38" s="45"/>
+      <c r="G38" s="43"/>
+      <c r="H38" s="69"/>
+      <c r="M38" s="46"/>
+      <c r="N38" s="46"/>
+      <c r="O38" s="46"/>
+      <c r="P38" s="46"/>
+      <c r="Q38" s="46"/>
+      <c r="R38" s="46"/>
+      <c r="S38" s="46"/>
       <c r="AI38"/>
       <c r="AJ38"/>
       <c r="AK38" s="39"/>
       <c r="AL38" s="39"/>
-      <c r="AM38" s="45"/>
-      <c r="AN38" s="45"/>
-      <c r="AO38" s="45"/>
+      <c r="AP38" s="46"/>
       <c r="AQ38"/>
       <c r="AR38"/>
       <c r="AS38" s="39"/>
       <c r="AT38" s="39"/>
-      <c r="AU38" s="45"/>
-      <c r="AV38" s="45"/>
     </row>
     <row r="39" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A39" s="46"/>
-      <c r="F39" s="67"/>
-      <c r="G39" s="43"/>
       <c r="H39" s="69"/>
       <c r="M39" s="46"/>
       <c r="N39" s="46"/>
@@ -5880,29 +5959,24 @@
       <c r="AT39" s="39"/>
     </row>
     <row r="40" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A40" s="46"/>
+      <c r="B40" s="70"/>
+      <c r="C40" s="45" t="s">
+        <v>82</v>
+      </c>
       <c r="H40" s="69"/>
-      <c r="M40" s="46"/>
-      <c r="N40" s="46"/>
-      <c r="O40" s="46"/>
-      <c r="P40" s="46"/>
-      <c r="Q40" s="46"/>
-      <c r="R40" s="46"/>
-      <c r="S40" s="46"/>
       <c r="AI40"/>
       <c r="AJ40"/>
       <c r="AK40" s="39"/>
       <c r="AL40" s="39"/>
-      <c r="AP40" s="46"/>
       <c r="AQ40"/>
       <c r="AR40"/>
       <c r="AS40" s="39"/>
       <c r="AT40" s="39"/>
     </row>
     <row r="41" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="B41" s="70"/>
+      <c r="B41" s="71"/>
       <c r="C41" s="45" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H41" s="69"/>
       <c r="AI41"/>
@@ -5915,10 +5989,6 @@
       <c r="AT41" s="39"/>
     </row>
     <row r="42" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="B42" s="71"/>
-      <c r="C42" s="45" t="s">
-        <v>83</v>
-      </c>
       <c r="H42" s="69"/>
       <c r="AI42"/>
       <c r="AJ42"/>
@@ -5930,7 +6000,6 @@
       <c r="AT42" s="39"/>
     </row>
     <row r="43" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="H43" s="69"/>
       <c r="AI43"/>
       <c r="AJ43"/>
       <c r="AK43" s="39"/>
@@ -5951,6 +6020,7 @@
       <c r="AT44" s="39"/>
     </row>
     <row r="45" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="E45" s="43"/>
       <c r="AI45"/>
       <c r="AJ45"/>
       <c r="AK45" s="39"/>
@@ -5961,7 +6031,6 @@
       <c r="AT45" s="39"/>
     </row>
     <row r="46" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="E46" s="43"/>
       <c r="AI46"/>
       <c r="AJ46"/>
       <c r="AK46" s="39"/>
@@ -6022,6 +6091,17 @@
       <c r="AT51" s="39"/>
     </row>
     <row r="52" spans="2:46" x14ac:dyDescent="0.25">
+      <c r="B52" s="73"/>
+      <c r="C52" s="73"/>
+      <c r="D52"/>
+      <c r="E52"/>
+      <c r="F52"/>
+      <c r="G52"/>
+      <c r="H52"/>
+      <c r="I52"/>
+      <c r="J52"/>
+      <c r="K52"/>
+      <c r="L52"/>
       <c r="AI52"/>
       <c r="AJ52"/>
       <c r="AK52" s="39"/>
@@ -6031,18 +6111,18 @@
       <c r="AS52" s="39"/>
       <c r="AT52" s="39"/>
     </row>
-    <row r="53" spans="2:46" x14ac:dyDescent="0.25">
-      <c r="B53" s="73"/>
-      <c r="C53" s="73"/>
-      <c r="D53"/>
-      <c r="E53"/>
-      <c r="F53"/>
-      <c r="G53"/>
-      <c r="H53"/>
-      <c r="I53"/>
-      <c r="J53"/>
-      <c r="K53"/>
-      <c r="L53"/>
+    <row r="53" spans="2:46" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B53" s="74"/>
+      <c r="C53" s="74"/>
+      <c r="D53" s="74"/>
+      <c r="E53" s="74"/>
+      <c r="F53" s="74"/>
+      <c r="G53" s="74"/>
+      <c r="H53" s="74"/>
+      <c r="I53" s="74"/>
+      <c r="J53" s="74"/>
+      <c r="K53" s="74"/>
+      <c r="L53" s="74"/>
       <c r="AI53"/>
       <c r="AJ53"/>
       <c r="AK53" s="39"/>
@@ -6052,18 +6132,18 @@
       <c r="AS53" s="39"/>
       <c r="AT53" s="39"/>
     </row>
-    <row r="54" spans="2:46" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="74"/>
-      <c r="C54" s="74"/>
-      <c r="D54" s="74"/>
-      <c r="E54" s="74"/>
-      <c r="F54" s="74"/>
-      <c r="G54" s="74"/>
-      <c r="H54" s="74"/>
-      <c r="I54" s="74"/>
-      <c r="J54" s="74"/>
-      <c r="K54" s="74"/>
-      <c r="L54" s="74"/>
+    <row r="54" spans="2:46" x14ac:dyDescent="0.25">
+      <c r="B54"/>
+      <c r="C54"/>
+      <c r="D54"/>
+      <c r="E54" s="1"/>
+      <c r="F54"/>
+      <c r="G54"/>
+      <c r="H54"/>
+      <c r="I54"/>
+      <c r="J54"/>
+      <c r="K54"/>
+      <c r="L54"/>
       <c r="AI54"/>
       <c r="AJ54"/>
       <c r="AK54" s="39"/>
@@ -6221,17 +6301,6 @@
       <c r="AT61" s="39"/>
     </row>
     <row r="62" spans="2:46" x14ac:dyDescent="0.25">
-      <c r="B62"/>
-      <c r="C62"/>
-      <c r="D62"/>
-      <c r="E62" s="1"/>
-      <c r="F62"/>
-      <c r="G62"/>
-      <c r="H62"/>
-      <c r="I62"/>
-      <c r="J62"/>
-      <c r="K62"/>
-      <c r="L62"/>
       <c r="AI62"/>
       <c r="AJ62"/>
       <c r="AK62" s="39"/>
@@ -6262,6 +6331,15 @@
       <c r="AT64" s="39"/>
     </row>
     <row r="65" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="V65" s="46"/>
+      <c r="W65" s="46"/>
+      <c r="X65" s="46"/>
+      <c r="Y65" s="46"/>
+      <c r="Z65" s="46"/>
+      <c r="AA65" s="46"/>
+      <c r="AB65" s="46"/>
+      <c r="AC65" s="46"/>
+      <c r="AD65" s="46"/>
       <c r="AI65"/>
       <c r="AJ65"/>
       <c r="AK65" s="39"/>
@@ -6281,6 +6359,7 @@
       <c r="AB66" s="46"/>
       <c r="AC66" s="46"/>
       <c r="AD66" s="46"/>
+      <c r="AE66" s="46"/>
       <c r="AI66"/>
       <c r="AJ66"/>
       <c r="AK66" s="39"/>
@@ -6291,6 +6370,16 @@
       <c r="AT66" s="39"/>
     </row>
     <row r="67" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="B67"/>
+      <c r="C67"/>
+      <c r="E67" s="73"/>
+      <c r="F67" s="73"/>
+      <c r="G67" s="1"/>
+      <c r="H67"/>
+      <c r="I67" s="73"/>
+      <c r="J67"/>
+      <c r="K67"/>
+      <c r="L67" s="73"/>
       <c r="V67" s="46"/>
       <c r="W67" s="46"/>
       <c r="X67" s="46"/>
@@ -6310,52 +6399,64 @@
       <c r="AS67" s="39"/>
       <c r="AT67" s="39"/>
     </row>
-    <row r="68" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="B68"/>
-      <c r="C68"/>
-      <c r="E68" s="73"/>
-      <c r="F68" s="73"/>
-      <c r="G68" s="1"/>
-      <c r="H68"/>
-      <c r="I68" s="73"/>
-      <c r="J68"/>
-      <c r="K68"/>
-      <c r="L68" s="73"/>
-      <c r="V68" s="46"/>
-      <c r="W68" s="46"/>
-      <c r="X68" s="46"/>
-      <c r="Y68" s="46"/>
-      <c r="Z68" s="46"/>
-      <c r="AA68" s="46"/>
-      <c r="AB68" s="46"/>
-      <c r="AC68" s="46"/>
-      <c r="AD68" s="46"/>
-      <c r="AE68" s="46"/>
+    <row r="68" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="45"/>
+      <c r="B68" s="79"/>
+      <c r="C68" s="79"/>
+      <c r="D68" s="79"/>
+      <c r="E68" s="79"/>
+      <c r="F68" s="79"/>
+      <c r="G68" s="79"/>
+      <c r="H68" s="80"/>
+      <c r="I68" s="79"/>
+      <c r="J68" s="79"/>
+      <c r="K68" s="79"/>
+      <c r="L68" s="79"/>
+      <c r="M68" s="45"/>
+      <c r="N68" s="45"/>
+      <c r="O68" s="45"/>
+      <c r="P68" s="45"/>
+      <c r="Q68" s="45"/>
+      <c r="R68" s="45"/>
+      <c r="S68" s="45"/>
+      <c r="V68" s="45"/>
+      <c r="W68" s="45"/>
+      <c r="X68" s="45"/>
+      <c r="Y68" s="45"/>
+      <c r="Z68" s="45"/>
+      <c r="AA68" s="45"/>
+      <c r="AB68" s="45"/>
+      <c r="AC68" s="45"/>
+      <c r="AD68" s="45"/>
       <c r="AI68"/>
-      <c r="AJ68"/>
+      <c r="AJ68" s="80"/>
       <c r="AK68" s="39"/>
-      <c r="AL68" s="39"/>
+      <c r="AL68" s="41"/>
+      <c r="AM68" s="45"/>
+      <c r="AN68" s="45"/>
       <c r="AQ68"/>
-      <c r="AR68"/>
+      <c r="AR68" s="80"/>
       <c r="AS68" s="39"/>
-      <c r="AT68" s="39"/>
+      <c r="AT68" s="41"/>
+      <c r="AU68" s="45"/>
+      <c r="AV68" s="45"/>
     </row>
     <row r="69" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="45"/>
-      <c r="B69" s="79"/>
-      <c r="C69" s="79"/>
-      <c r="D69" s="79"/>
-      <c r="E69" s="79"/>
-      <c r="F69" s="79"/>
-      <c r="G69" s="79"/>
+      <c r="A69" s="73"/>
+      <c r="B69" s="81"/>
+      <c r="C69" s="82"/>
+      <c r="D69" s="81"/>
+      <c r="E69" s="81"/>
+      <c r="F69" s="81"/>
+      <c r="G69" s="81"/>
       <c r="H69" s="80"/>
-      <c r="I69" s="79"/>
-      <c r="J69" s="79"/>
-      <c r="K69" s="79"/>
-      <c r="L69" s="79"/>
-      <c r="M69" s="45"/>
-      <c r="N69" s="45"/>
-      <c r="O69" s="45"/>
+      <c r="I69" s="81"/>
+      <c r="J69" s="81"/>
+      <c r="K69" s="82"/>
+      <c r="L69" s="82"/>
+      <c r="M69" s="73"/>
+      <c r="N69" s="73"/>
+      <c r="O69" s="1"/>
       <c r="P69" s="45"/>
       <c r="Q69" s="45"/>
       <c r="R69" s="45"/>
@@ -6369,23 +6470,15 @@
       <c r="AB69" s="45"/>
       <c r="AC69" s="45"/>
       <c r="AD69" s="45"/>
-      <c r="AI69"/>
-      <c r="AJ69" s="80"/>
-      <c r="AK69" s="39"/>
-      <c r="AL69" s="41"/>
-      <c r="AM69" s="45"/>
-      <c r="AN69" s="45"/>
-      <c r="AQ69"/>
-      <c r="AR69" s="80"/>
-      <c r="AS69" s="39"/>
-      <c r="AT69" s="41"/>
-      <c r="AU69" s="45"/>
-      <c r="AV69" s="45"/>
+      <c r="AE69" s="45"/>
+      <c r="AI69" s="42"/>
+      <c r="AJ69" s="42"/>
+      <c r="AK69" s="54"/>
     </row>
     <row r="70" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="73"/>
+      <c r="A70" s="79"/>
       <c r="B70" s="81"/>
-      <c r="C70" s="82"/>
+      <c r="C70" s="81"/>
       <c r="D70" s="81"/>
       <c r="E70" s="81"/>
       <c r="F70" s="81"/>
@@ -6393,15 +6486,11 @@
       <c r="H70" s="80"/>
       <c r="I70" s="81"/>
       <c r="J70" s="81"/>
-      <c r="K70" s="82"/>
-      <c r="L70" s="82"/>
-      <c r="M70" s="73"/>
-      <c r="N70" s="73"/>
-      <c r="O70" s="1"/>
-      <c r="P70" s="45"/>
-      <c r="Q70" s="45"/>
-      <c r="R70" s="45"/>
-      <c r="S70" s="45"/>
+      <c r="K70" s="81"/>
+      <c r="L70" s="81"/>
+      <c r="M70" s="79"/>
+      <c r="N70" s="79"/>
+      <c r="O70" s="79"/>
       <c r="V70" s="45"/>
       <c r="W70" s="45"/>
       <c r="X70" s="45"/>
@@ -6416,48 +6505,39 @@
       <c r="AJ70" s="42"/>
       <c r="AK70" s="54"/>
     </row>
-    <row r="71" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="79"/>
-      <c r="B71" s="81"/>
-      <c r="C71" s="81"/>
-      <c r="D71" s="81"/>
-      <c r="E71" s="81"/>
-      <c r="F71" s="81"/>
-      <c r="G71" s="81"/>
-      <c r="H71" s="80"/>
-      <c r="I71" s="81"/>
-      <c r="J71" s="81"/>
-      <c r="K71" s="81"/>
-      <c r="L71" s="81"/>
-      <c r="M71" s="79"/>
-      <c r="N71" s="79"/>
-      <c r="O71" s="79"/>
-      <c r="V71" s="45"/>
-      <c r="W71" s="45"/>
-      <c r="X71" s="45"/>
-      <c r="Y71" s="45"/>
-      <c r="Z71" s="45"/>
-      <c r="AA71" s="45"/>
-      <c r="AB71" s="45"/>
-      <c r="AC71" s="45"/>
-      <c r="AD71" s="45"/>
-      <c r="AE71" s="45"/>
-      <c r="AI71" s="42"/>
-      <c r="AJ71" s="42"/>
-      <c r="AK71" s="54"/>
+    <row r="71" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A71" s="81"/>
+      <c r="B71"/>
+      <c r="C71" s="39"/>
+      <c r="D71" s="39"/>
+      <c r="H71"/>
+      <c r="I71"/>
+      <c r="J71"/>
+      <c r="K71" s="39"/>
+      <c r="L71" s="39"/>
+      <c r="M71" s="82"/>
+      <c r="N71" s="82"/>
+      <c r="O71" s="81"/>
+      <c r="P71" s="46"/>
+      <c r="Q71" s="46"/>
+      <c r="R71" s="46"/>
+      <c r="S71" s="46"/>
+      <c r="AI71" s="38"/>
+      <c r="AJ71" s="38"/>
+      <c r="AK71" s="50"/>
     </row>
     <row r="72" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A72" s="81"/>
       <c r="B72"/>
       <c r="C72" s="39"/>
       <c r="D72" s="39"/>
-      <c r="H72"/>
+      <c r="H72" s="78"/>
       <c r="I72"/>
       <c r="J72"/>
       <c r="K72" s="39"/>
       <c r="L72" s="39"/>
-      <c r="M72" s="82"/>
-      <c r="N72" s="82"/>
+      <c r="M72" s="81"/>
+      <c r="N72" s="81"/>
       <c r="O72" s="81"/>
       <c r="P72" s="46"/>
       <c r="Q72" s="46"/>
@@ -6468,22 +6548,14 @@
       <c r="AK72" s="50"/>
     </row>
     <row r="73" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A73" s="81"/>
+      <c r="A73"/>
       <c r="B73"/>
       <c r="C73" s="39"/>
       <c r="D73" s="39"/>
-      <c r="H73" s="78"/>
       <c r="I73"/>
       <c r="J73"/>
       <c r="K73" s="39"/>
       <c r="L73" s="39"/>
-      <c r="M73" s="81"/>
-      <c r="N73" s="81"/>
-      <c r="O73" s="81"/>
-      <c r="P73" s="46"/>
-      <c r="Q73" s="46"/>
-      <c r="R73" s="46"/>
-      <c r="S73" s="46"/>
       <c r="AI73" s="38"/>
       <c r="AJ73" s="38"/>
       <c r="AK73" s="50"/>
@@ -6506,10 +6578,12 @@
       <c r="B75"/>
       <c r="C75" s="39"/>
       <c r="D75" s="39"/>
+      <c r="H75" s="46"/>
       <c r="I75"/>
       <c r="J75"/>
       <c r="K75" s="39"/>
       <c r="L75" s="39"/>
+      <c r="O75" s="46"/>
       <c r="AI75" s="38"/>
       <c r="AJ75" s="38"/>
       <c r="AK75" s="50"/>
@@ -6729,12 +6803,10 @@
       <c r="B90"/>
       <c r="C90" s="39"/>
       <c r="D90" s="39"/>
-      <c r="H90" s="46"/>
       <c r="I90"/>
       <c r="J90"/>
       <c r="K90" s="39"/>
       <c r="L90" s="39"/>
-      <c r="O90" s="46"/>
       <c r="AI90" s="38"/>
       <c r="AJ90" s="38"/>
       <c r="AK90" s="50"/>
@@ -7105,13 +7177,6 @@
     </row>
     <row r="119" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A119"/>
-      <c r="B119"/>
-      <c r="C119" s="39"/>
-      <c r="D119" s="39"/>
-      <c r="I119"/>
-      <c r="J119"/>
-      <c r="K119" s="39"/>
-      <c r="L119" s="39"/>
       <c r="AI119" s="38"/>
       <c r="AJ119" s="38"/>
       <c r="AK119" s="50"/>
@@ -7123,7 +7188,6 @@
       <c r="AK120" s="50"/>
     </row>
     <row r="121" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A121"/>
       <c r="AI121" s="38"/>
       <c r="AJ121" s="38"/>
       <c r="AK121" s="50"/>
@@ -7242,11 +7306,6 @@
       <c r="AI144" s="38"/>
       <c r="AJ144" s="38"/>
       <c r="AK144" s="50"/>
-    </row>
-    <row r="145" spans="35:37" x14ac:dyDescent="0.25">
-      <c r="AI145" s="38"/>
-      <c r="AJ145" s="38"/>
-      <c r="AK145" s="50"/>
     </row>
   </sheetData>
   <phoneticPr fontId="24" type="noConversion"/>

--- a/SubRES_TMPL/SubRES_NewTechs.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{045C2DFB-485C-4B60-AC23-372C24FA9D95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A55822D4-D0EC-4C0C-8FEB-8C359C53E3FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1125,7 +1125,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB14" authorId="2" shapeId="0" xr:uid="{5EE58488-723F-4683-9026-2F0EE70F8071}">
+    <comment ref="AB16" authorId="2" shapeId="0" xr:uid="{5EE58488-723F-4683-9026-2F0EE70F8071}">
       <text>
         <r>
           <rPr>
@@ -1218,7 +1218,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC14" authorId="1" shapeId="0" xr:uid="{308E9284-8F99-498B-A3DD-262799AF67EB}">
+    <comment ref="AC16" authorId="1" shapeId="0" xr:uid="{308E9284-8F99-498B-A3DD-262799AF67EB}">
       <text>
         <r>
           <rPr>
@@ -1243,7 +1243,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AD14" authorId="2" shapeId="0" xr:uid="{FD29F772-15B8-47C4-8D7A-88CCF8F71647}">
+    <comment ref="AD16" authorId="2" shapeId="0" xr:uid="{FD29F772-15B8-47C4-8D7A-88CCF8F71647}">
       <text>
         <r>
           <rPr>
@@ -1306,7 +1306,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V15" authorId="2" shapeId="0" xr:uid="{BAA0F8AB-741B-4302-9E54-000CB5DC4ACF}">
+    <comment ref="V17" authorId="2" shapeId="0" xr:uid="{BAA0F8AB-741B-4302-9E54-000CB5DC4ACF}">
       <text>
         <r>
           <rPr>
@@ -1554,7 +1554,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="166">
   <si>
     <t>~FI_T</t>
   </si>
@@ -2015,18 +2015,9 @@
     <t>Renewable Manufacturing Process Heat Aggregator</t>
   </si>
   <si>
-    <t>RENHEAT</t>
-  </si>
-  <si>
     <t>Process heat from all renewables</t>
   </si>
   <si>
-    <t>RENTHT</t>
-  </si>
-  <si>
-    <t>RENELC</t>
-  </si>
-  <si>
     <t>Decentralized Electricity form Solar, Wind and Bio</t>
   </si>
   <si>
@@ -2034,6 +2025,33 @@
   </si>
   <si>
     <t>MANELC</t>
+  </si>
+  <si>
+    <t>DECHEAT</t>
+  </si>
+  <si>
+    <t>DECPOWER</t>
+  </si>
+  <si>
+    <t>RNWHEAT</t>
+  </si>
+  <si>
+    <t>Renewable Heat Aggrigator</t>
+  </si>
+  <si>
+    <t>RNWTHT</t>
+  </si>
+  <si>
+    <t>GHEAT</t>
+  </si>
+  <si>
+    <t>Grid electricity-based heat</t>
+  </si>
+  <si>
+    <t>GTHT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grid Electricity Based Heat Aggregator </t>
   </si>
 </sst>
 </file>
@@ -2045,7 +2063,7 @@
     <numFmt numFmtId="165" formatCode="\Te\x\t"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="30" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -2202,7 +2220,33 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF000000"/>
+      <color rgb="FF00B0F0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF00B0F0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="7"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -2345,7 +2389,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
@@ -2474,7 +2518,6 @@
     <xf numFmtId="0" fontId="23" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="21" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="21" fillId="8" borderId="0" xfId="21" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="21" fillId="8" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="21" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="21" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="21" fillId="0" borderId="0" xfId="21" applyFont="1"/>
@@ -2503,9 +2546,41 @@
     </xf>
     <xf numFmtId="2" fontId="16" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="4" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="4" applyFont="1"/>
+    <xf numFmtId="165" fontId="25" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="25" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="25" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" xfId="4" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="25" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="25" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="16" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" xfId="4" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="16" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="16" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="28" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="28" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="0" xfId="4" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="28" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="4" applyFont="1"/>
+    <xf numFmtId="166" fontId="28" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="28" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="28" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="22">
     <cellStyle name="20% - Accent5 2" xfId="18" xr:uid="{4C3A48E2-3C46-4D12-9A64-54698D8BF8EE}"/>
@@ -2995,10 +3070,10 @@
       <c r="D2" s="38" t="s">
         <v>73</v>
       </c>
-      <c r="E2" s="72" t="s">
+      <c r="E2" s="71" t="s">
         <v>58</v>
       </c>
-      <c r="F2" s="72" t="s">
+      <c r="F2" s="71" t="s">
         <v>109</v>
       </c>
       <c r="G2" s="14"/>
@@ -3021,10 +3096,10 @@
       <c r="D3" s="38" t="s">
         <v>74</v>
       </c>
-      <c r="E3" s="72" t="s">
+      <c r="E3" s="71" t="s">
         <v>58</v>
       </c>
-      <c r="F3" s="72" t="s">
+      <c r="F3" s="71" t="s">
         <v>109</v>
       </c>
       <c r="G3" s="14"/>
@@ -3063,10 +3138,10 @@
       <c r="D4" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="E4" s="72" t="s">
+      <c r="E4" s="71" t="s">
         <v>58</v>
       </c>
-      <c r="F4" s="72" t="s">
+      <c r="F4" s="71" t="s">
         <v>109</v>
       </c>
       <c r="G4" s="14"/>
@@ -3105,10 +3180,10 @@
       <c r="D5" s="38" t="s">
         <v>75</v>
       </c>
-      <c r="E5" s="72" t="s">
+      <c r="E5" s="71" t="s">
         <v>58</v>
       </c>
-      <c r="F5" s="72" t="s">
+      <c r="F5" s="71" t="s">
         <v>109</v>
       </c>
       <c r="G5" s="14"/>
@@ -3976,7 +4051,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3360854E-4C4D-467D-BD8A-32231E61C6CE}">
-  <dimension ref="A1:AY144"/>
+  <dimension ref="A1:AY145"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" style="45" customWidth="1"/>
@@ -4137,19 +4212,19 @@
       <c r="E5" s="53"/>
       <c r="F5" s="53"/>
       <c r="G5" s="53"/>
-      <c r="V5" s="77" t="s">
+      <c r="V5" s="76" t="s">
         <v>69</v>
       </c>
       <c r="X5" s="45" t="s">
         <v>131</v>
       </c>
-      <c r="Y5" s="77" t="s">
+      <c r="Y5" s="76" t="s">
         <v>132</v>
       </c>
-      <c r="Z5" s="77" t="s">
+      <c r="Z5" s="76" t="s">
         <v>58</v>
       </c>
-      <c r="AB5" s="77" t="s">
+      <c r="AB5" s="76" t="s">
         <v>88</v>
       </c>
     </row>
@@ -4160,19 +4235,19 @@
       <c r="E6" s="53"/>
       <c r="F6" s="53"/>
       <c r="G6" s="53"/>
-      <c r="V6" s="77" t="s">
+      <c r="V6" s="76" t="s">
         <v>69</v>
       </c>
       <c r="X6" s="45" t="s">
         <v>130</v>
       </c>
-      <c r="Y6" s="77" t="s">
+      <c r="Y6" s="76" t="s">
         <v>133</v>
       </c>
-      <c r="Z6" s="77" t="s">
+      <c r="Z6" s="76" t="s">
         <v>58</v>
       </c>
-      <c r="AB6" s="77" t="s">
+      <c r="AB6" s="76" t="s">
         <v>88</v>
       </c>
     </row>
@@ -4192,10 +4267,10 @@
       <c r="Y7" s="45" t="s">
         <v>136</v>
       </c>
-      <c r="Z7" s="77" t="s">
+      <c r="Z7" s="76" t="s">
         <v>58</v>
       </c>
-      <c r="AB7" s="77" t="s">
+      <c r="AB7" s="76" t="s">
         <v>88</v>
       </c>
     </row>
@@ -4209,10 +4284,10 @@
       <c r="Y8" s="45" t="s">
         <v>141</v>
       </c>
-      <c r="Z8" s="77" t="s">
+      <c r="Z8" s="76" t="s">
         <v>58</v>
       </c>
-      <c r="AB8" s="77" t="s">
+      <c r="AB8" s="76" t="s">
         <v>88</v>
       </c>
       <c r="AE8" s="46"/>
@@ -4223,16 +4298,16 @@
       </c>
       <c r="W9" s="50"/>
       <c r="X9" s="50" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y9" s="50" t="s">
         <v>153</v>
       </c>
-      <c r="Y9" s="50" t="s">
-        <v>154</v>
-      </c>
-      <c r="Z9" s="77" t="s">
+      <c r="Z9" s="76" t="s">
         <v>58</v>
       </c>
       <c r="AA9" s="50"/>
-      <c r="AB9" s="77" t="s">
+      <c r="AB9" s="76" t="s">
         <v>88</v>
       </c>
       <c r="AC9" s="50"/>
@@ -4244,899 +4319,760 @@
       </c>
       <c r="W10" s="50"/>
       <c r="X10" s="50" t="s">
-        <v>156</v>
+        <v>129</v>
       </c>
       <c r="Y10" s="50" t="s">
-        <v>157</v>
-      </c>
-      <c r="Z10" s="77" t="s">
+        <v>154</v>
+      </c>
+      <c r="Z10" s="76" t="s">
         <v>58</v>
       </c>
       <c r="AA10" s="50"/>
-      <c r="AB10" s="77" t="s">
+      <c r="AB10" s="76" t="s">
         <v>88</v>
       </c>
       <c r="AC10" s="50"/>
       <c r="AD10" s="50"/>
     </row>
+    <row r="11" spans="2:51" x14ac:dyDescent="0.25">
+      <c r="V11" s="45" t="s">
+        <v>139</v>
+      </c>
+      <c r="X11" s="45" t="s">
+        <v>159</v>
+      </c>
+      <c r="Y11" s="45" t="s">
+        <v>160</v>
+      </c>
+      <c r="Z11" s="76" t="s">
+        <v>58</v>
+      </c>
+      <c r="AB11" s="76" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12" spans="2:51" x14ac:dyDescent="0.25">
+      <c r="V12" s="45" t="s">
+        <v>139</v>
+      </c>
+      <c r="X12" s="45" t="s">
+        <v>162</v>
+      </c>
+      <c r="Y12" s="45" t="s">
+        <v>163</v>
+      </c>
+      <c r="Z12" s="76" t="s">
+        <v>58</v>
+      </c>
+      <c r="AB12" s="76" t="s">
+        <v>88</v>
+      </c>
+    </row>
     <row r="13" spans="2:51" x14ac:dyDescent="0.25">
-      <c r="D13" s="55" t="s">
+      <c r="Z13" s="76"/>
+      <c r="AB13" s="76"/>
+    </row>
+    <row r="15" spans="2:51" x14ac:dyDescent="0.25">
+      <c r="D15" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="E13" s="55"/>
-      <c r="F13" s="55"/>
-      <c r="H13" s="55"/>
-      <c r="V13" s="49" t="s">
+      <c r="E15" s="55"/>
+      <c r="F15" s="55"/>
+      <c r="H15" s="55"/>
+      <c r="V15" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="W13" s="49"/>
-      <c r="X13" s="50"/>
-      <c r="Y13" s="50"/>
-      <c r="Z13" s="50"/>
-      <c r="AA13" s="50"/>
-      <c r="AB13" s="50"/>
-      <c r="AC13" s="50"/>
-      <c r="AD13" s="50"/>
-      <c r="AI13"/>
-      <c r="AJ13" s="39"/>
-      <c r="AK13" s="77"/>
-      <c r="AL13" s="77"/>
-      <c r="AM13" s="77"/>
-      <c r="AN13" s="77"/>
-      <c r="AO13" s="77"/>
-      <c r="AP13" s="77"/>
-      <c r="AQ13" s="77"/>
-      <c r="AR13" s="77"/>
-      <c r="AS13" s="77"/>
-      <c r="AT13" s="77"/>
-      <c r="AU13" s="77"/>
-      <c r="AV13" s="77"/>
-      <c r="AW13" s="77"/>
-    </row>
-    <row r="14" spans="2:51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="C14" s="56" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="56" t="s">
-        <v>4</v>
-      </c>
-      <c r="E14" s="57" t="s">
-        <v>113</v>
-      </c>
-      <c r="F14" s="57" t="s">
-        <v>16</v>
-      </c>
-      <c r="G14" s="57" t="s">
-        <v>34</v>
-      </c>
-      <c r="H14" s="57" t="s">
-        <v>47</v>
-      </c>
-      <c r="I14" s="57" t="s">
-        <v>36</v>
-      </c>
-      <c r="J14" s="59" t="s">
-        <v>5</v>
-      </c>
-      <c r="K14" s="59" t="s">
-        <v>98</v>
-      </c>
-      <c r="L14" s="57" t="s">
-        <v>56</v>
-      </c>
-      <c r="M14" s="59" t="s">
-        <v>103</v>
-      </c>
-      <c r="N14" s="58" t="s">
-        <v>112</v>
-      </c>
-      <c r="O14" s="59" t="s">
-        <v>115</v>
-      </c>
-      <c r="P14" s="59" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q14" s="59" t="s">
-        <v>117</v>
-      </c>
-      <c r="R14" s="59" t="s">
-        <v>118</v>
-      </c>
-      <c r="S14" s="59" t="s">
-        <v>126</v>
-      </c>
-      <c r="V14" s="51" t="s">
-        <v>15</v>
-      </c>
-      <c r="W14" s="52" t="s">
-        <v>42</v>
-      </c>
-      <c r="X14" s="51" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y14" s="51" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z14" s="51" t="s">
-        <v>18</v>
-      </c>
-      <c r="AA14" s="51" t="s">
-        <v>19</v>
-      </c>
-      <c r="AB14" s="51" t="s">
-        <v>20</v>
-      </c>
-      <c r="AC14" s="51" t="s">
-        <v>21</v>
-      </c>
-      <c r="AD14" s="51" t="s">
-        <v>22</v>
-      </c>
-      <c r="AI14"/>
-      <c r="AJ14" s="39"/>
-      <c r="AK14" s="77"/>
-      <c r="AL14" s="77"/>
-      <c r="AM14" s="77"/>
-      <c r="AN14" s="77"/>
-      <c r="AO14" s="77"/>
-      <c r="AP14" s="77"/>
-      <c r="AQ14" s="77"/>
-      <c r="AR14" s="77"/>
-      <c r="AS14" s="77"/>
-      <c r="AT14" s="77"/>
-      <c r="AU14" s="77"/>
-      <c r="AV14" s="77"/>
-      <c r="AW14" s="77"/>
-      <c r="AY14" s="46"/>
-    </row>
-    <row r="15" spans="2:51" ht="31.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="32" t="s">
-        <v>48</v>
-      </c>
-      <c r="C15" s="32" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" s="32" t="s">
-        <v>33</v>
-      </c>
-      <c r="E15" s="32" t="s">
-        <v>54</v>
-      </c>
-      <c r="F15" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="G15" s="33" t="s">
-        <v>49</v>
-      </c>
-      <c r="H15" s="32" t="s">
-        <v>57</v>
-      </c>
-      <c r="I15" s="32" t="s">
-        <v>86</v>
-      </c>
-      <c r="J15" s="33" t="s">
-        <v>37</v>
-      </c>
-      <c r="K15" s="33" t="s">
-        <v>99</v>
-      </c>
-      <c r="L15" s="33" t="s">
-        <v>80</v>
-      </c>
-      <c r="M15" s="33" t="s">
-        <v>104</v>
-      </c>
-      <c r="N15" s="32" t="s">
-        <v>85</v>
-      </c>
-      <c r="O15" s="33" t="s">
-        <v>114</v>
-      </c>
-      <c r="P15" s="33" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q15" s="33" t="s">
-        <v>114</v>
-      </c>
-      <c r="R15" s="75" t="s">
-        <v>114</v>
-      </c>
-      <c r="S15" s="75" t="s">
-        <v>127</v>
-      </c>
-      <c r="V15" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="W15" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="X15" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y15" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z15" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="AA15" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB15" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="AC15" s="31" t="s">
-        <v>52</v>
-      </c>
-      <c r="AD15" s="31" t="s">
-        <v>31</v>
-      </c>
+      <c r="W15" s="49"/>
+      <c r="X15" s="50"/>
+      <c r="Y15" s="50"/>
+      <c r="Z15" s="50"/>
+      <c r="AA15" s="50"/>
+      <c r="AB15" s="50"/>
+      <c r="AC15" s="50"/>
+      <c r="AD15" s="50"/>
       <c r="AI15"/>
       <c r="AJ15" s="39"/>
-      <c r="AY15" s="46"/>
-    </row>
-    <row r="16" spans="2:51" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="C16" s="34"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="35"/>
-      <c r="F16" s="35"/>
-      <c r="G16" s="36"/>
-      <c r="H16" s="35" t="s">
-        <v>54</v>
-      </c>
-      <c r="I16" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="J16" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="K16" s="35" t="s">
-        <v>134</v>
-      </c>
-      <c r="L16" s="36"/>
-      <c r="M16" s="36" t="s">
-        <v>105</v>
-      </c>
-      <c r="N16" s="35"/>
-      <c r="O16" s="36"/>
-      <c r="P16" s="36"/>
-      <c r="Q16" s="36"/>
-      <c r="R16" s="35"/>
-      <c r="S16" s="76"/>
-      <c r="V16" s="31" t="s">
-        <v>81</v>
-      </c>
-      <c r="W16" s="31"/>
-      <c r="X16" s="31"/>
-      <c r="Y16" s="31"/>
-      <c r="Z16" s="31"/>
-      <c r="AA16" s="31"/>
-      <c r="AB16" s="31"/>
-      <c r="AC16" s="31"/>
-      <c r="AD16" s="31"/>
+      <c r="AK15" s="76"/>
+      <c r="AL15" s="76"/>
+      <c r="AM15" s="76"/>
+      <c r="AN15" s="76"/>
+      <c r="AO15" s="76"/>
+      <c r="AP15" s="76"/>
+      <c r="AQ15" s="76"/>
+      <c r="AR15" s="76"/>
+      <c r="AS15" s="76"/>
+      <c r="AT15" s="76"/>
+      <c r="AU15" s="76"/>
+      <c r="AV15" s="76"/>
+      <c r="AW15" s="76"/>
+    </row>
+    <row r="16" spans="2:51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="56" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="E16" s="57" t="s">
+        <v>113</v>
+      </c>
+      <c r="F16" s="57" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" s="57" t="s">
+        <v>34</v>
+      </c>
+      <c r="H16" s="57" t="s">
+        <v>47</v>
+      </c>
+      <c r="I16" s="57" t="s">
+        <v>36</v>
+      </c>
+      <c r="J16" s="59" t="s">
+        <v>5</v>
+      </c>
+      <c r="K16" s="59" t="s">
+        <v>98</v>
+      </c>
+      <c r="L16" s="57" t="s">
+        <v>56</v>
+      </c>
+      <c r="M16" s="59" t="s">
+        <v>103</v>
+      </c>
+      <c r="N16" s="58" t="s">
+        <v>112</v>
+      </c>
+      <c r="O16" s="59" t="s">
+        <v>115</v>
+      </c>
+      <c r="P16" s="59" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q16" s="59" t="s">
+        <v>117</v>
+      </c>
+      <c r="R16" s="59" t="s">
+        <v>118</v>
+      </c>
+      <c r="S16" s="59" t="s">
+        <v>126</v>
+      </c>
+      <c r="V16" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="W16" s="52" t="s">
+        <v>42</v>
+      </c>
+      <c r="X16" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y16" s="51" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z16" s="51" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA16" s="51" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB16" s="51" t="s">
+        <v>20</v>
+      </c>
+      <c r="AC16" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="AD16" s="51" t="s">
+        <v>22</v>
+      </c>
       <c r="AI16"/>
       <c r="AJ16" s="39"/>
+      <c r="AK16" s="76"/>
+      <c r="AL16" s="76"/>
+      <c r="AM16" s="76"/>
+      <c r="AN16" s="76"/>
+      <c r="AO16" s="76"/>
+      <c r="AP16" s="76"/>
+      <c r="AQ16" s="76"/>
+      <c r="AR16" s="76"/>
+      <c r="AS16" s="76"/>
+      <c r="AT16" s="76"/>
+      <c r="AU16" s="76"/>
+      <c r="AV16" s="76"/>
+      <c r="AW16" s="76"/>
       <c r="AY16" s="46"/>
     </row>
-    <row r="17" spans="2:51" x14ac:dyDescent="0.25">
-      <c r="B17" s="45" t="str">
-        <f>X17</f>
-        <v>Furnace</v>
-      </c>
-      <c r="C17" s="45" t="s">
-        <v>69</v>
-      </c>
-      <c r="D17" s="50" t="s">
-        <v>107</v>
-      </c>
-      <c r="E17" s="43">
-        <v>2030</v>
-      </c>
-      <c r="F17" s="64">
-        <v>1</v>
-      </c>
-      <c r="G17" s="64">
-        <v>1</v>
-      </c>
-      <c r="H17" s="43">
-        <v>25</v>
-      </c>
-      <c r="I17" s="64">
-        <v>81</v>
-      </c>
-      <c r="J17" s="64">
-        <v>0</v>
-      </c>
-      <c r="K17" s="64">
-        <v>0.24</v>
-      </c>
-      <c r="L17" s="64">
-        <v>8.76</v>
-      </c>
-      <c r="M17" s="43"/>
-      <c r="N17" s="64">
-        <v>0.1</v>
-      </c>
-      <c r="O17" s="64">
-        <v>0.15</v>
-      </c>
-      <c r="P17" s="64">
-        <v>0.2</v>
-      </c>
-      <c r="Q17" s="64">
-        <v>0.25</v>
-      </c>
-      <c r="R17" s="64">
-        <v>0.35</v>
-      </c>
-      <c r="S17" s="43"/>
-      <c r="V17" s="60" t="s">
-        <v>128</v>
-      </c>
-      <c r="W17" s="60"/>
-      <c r="X17" s="61" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y17" s="62" t="s">
-        <v>142</v>
-      </c>
-      <c r="Z17" s="45" t="s">
-        <v>58</v>
-      </c>
-      <c r="AA17" s="45" t="s">
-        <v>87</v>
-      </c>
-      <c r="AB17" s="63" t="s">
-        <v>88</v>
-      </c>
-      <c r="AC17" s="46"/>
-      <c r="AD17" s="46"/>
+    <row r="17" spans="2:51" ht="31.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="E17" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="F17" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="G17" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="H17" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="I17" s="32" t="s">
+        <v>86</v>
+      </c>
+      <c r="J17" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="K17" s="33" t="s">
+        <v>99</v>
+      </c>
+      <c r="L17" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="M17" s="33" t="s">
+        <v>104</v>
+      </c>
+      <c r="N17" s="32" t="s">
+        <v>85</v>
+      </c>
+      <c r="O17" s="33" t="s">
+        <v>114</v>
+      </c>
+      <c r="P17" s="33" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q17" s="33" t="s">
+        <v>114</v>
+      </c>
+      <c r="R17" s="74" t="s">
+        <v>114</v>
+      </c>
+      <c r="S17" s="74" t="s">
+        <v>127</v>
+      </c>
+      <c r="V17" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="W17" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="X17" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y17" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z17" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA17" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB17" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="AC17" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD17" s="31" t="s">
+        <v>31</v>
+      </c>
       <c r="AI17"/>
       <c r="AJ17" s="39"/>
-      <c r="AK17" s="77"/>
-      <c r="AL17" s="77"/>
-      <c r="AM17" s="77"/>
-      <c r="AN17" s="77"/>
-      <c r="AO17" s="77"/>
-      <c r="AP17" s="77"/>
-      <c r="AQ17" s="77"/>
-      <c r="AR17" s="77"/>
-      <c r="AS17" s="77"/>
-      <c r="AT17" s="77"/>
-      <c r="AU17" s="77"/>
-      <c r="AV17" s="77"/>
-      <c r="AW17" s="77"/>
       <c r="AY17" s="46"/>
     </row>
-    <row r="18" spans="2:51" x14ac:dyDescent="0.25">
-      <c r="B18" s="45" t="str">
-        <f>X$18</f>
+    <row r="18" spans="2:51" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" s="34"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="35"/>
+      <c r="G18" s="36"/>
+      <c r="H18" s="35" t="s">
+        <v>54</v>
+      </c>
+      <c r="I18" s="35" t="s">
+        <v>111</v>
+      </c>
+      <c r="J18" s="35" t="s">
+        <v>111</v>
+      </c>
+      <c r="K18" s="35" t="s">
+        <v>134</v>
+      </c>
+      <c r="L18" s="36"/>
+      <c r="M18" s="36" t="s">
+        <v>105</v>
+      </c>
+      <c r="N18" s="35"/>
+      <c r="O18" s="36"/>
+      <c r="P18" s="36"/>
+      <c r="Q18" s="36"/>
+      <c r="R18" s="35"/>
+      <c r="S18" s="75"/>
+      <c r="V18" s="31" t="s">
+        <v>81</v>
+      </c>
+      <c r="W18" s="31"/>
+      <c r="X18" s="31"/>
+      <c r="Y18" s="31"/>
+      <c r="Z18" s="31"/>
+      <c r="AA18" s="31"/>
+      <c r="AB18" s="31"/>
+      <c r="AC18" s="31"/>
+      <c r="AD18" s="31"/>
+      <c r="AI18"/>
+      <c r="AJ18" s="39"/>
+      <c r="AY18" s="46"/>
+    </row>
+    <row r="19" spans="2:51" s="85" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="85" t="str">
+        <f>X19</f>
+        <v>Furnace</v>
+      </c>
+      <c r="C19" s="85" t="s">
+        <v>69</v>
+      </c>
+      <c r="D19" s="86" t="str">
+        <f>X12</f>
+        <v>GHEAT</v>
+      </c>
+      <c r="E19" s="87">
+        <v>2030</v>
+      </c>
+      <c r="F19" s="88">
+        <v>1</v>
+      </c>
+      <c r="G19" s="88">
+        <v>1</v>
+      </c>
+      <c r="H19" s="87">
+        <v>25</v>
+      </c>
+      <c r="I19" s="88">
+        <v>81</v>
+      </c>
+      <c r="J19" s="88">
+        <v>0</v>
+      </c>
+      <c r="K19" s="88">
+        <v>0.24</v>
+      </c>
+      <c r="L19" s="88">
+        <v>8.76</v>
+      </c>
+      <c r="M19" s="87"/>
+      <c r="N19" s="88">
+        <v>0.1</v>
+      </c>
+      <c r="O19" s="88">
+        <v>0.15</v>
+      </c>
+      <c r="P19" s="88">
+        <v>0.2</v>
+      </c>
+      <c r="Q19" s="88">
+        <v>0.25</v>
+      </c>
+      <c r="R19" s="88">
+        <v>0.35</v>
+      </c>
+      <c r="S19" s="87"/>
+      <c r="T19" s="89"/>
+      <c r="U19" s="89"/>
+      <c r="V19" s="90" t="s">
+        <v>139</v>
+      </c>
+      <c r="W19" s="90"/>
+      <c r="X19" s="91" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y19" s="92" t="s">
+        <v>142</v>
+      </c>
+      <c r="Z19" s="85" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA19" s="85" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB19" s="93" t="s">
+        <v>88</v>
+      </c>
+      <c r="AC19" s="89"/>
+      <c r="AD19" s="89"/>
+      <c r="AI19" s="94"/>
+      <c r="AJ19" s="95"/>
+      <c r="AY19" s="89"/>
+    </row>
+    <row r="20" spans="2:51" s="76" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="76" t="str">
+        <f>X$20</f>
         <v>BIOBoiler</v>
       </c>
-      <c r="C18" s="45" t="str">
+      <c r="C20" s="76" t="str">
         <f>PRI_Sector_Fuels!P5</f>
         <v>MANBIOMIN</v>
       </c>
-      <c r="D18" s="50" t="str">
+      <c r="D20" s="83" t="str">
         <f>X9</f>
-        <v>RENHEAT</v>
-      </c>
-      <c r="E18" s="43">
+        <v>DECHEAT</v>
+      </c>
+      <c r="E20" s="96">
         <v>2030</v>
       </c>
-      <c r="F18" s="64">
+      <c r="F20" s="82">
         <v>0.7</v>
       </c>
-      <c r="G18" s="64">
+      <c r="G20" s="82">
         <v>0.98</v>
       </c>
-      <c r="H18" s="43">
+      <c r="H20" s="96">
         <v>25</v>
       </c>
-      <c r="I18" s="64">
+      <c r="I20" s="82">
         <v>797.9</v>
       </c>
-      <c r="J18" s="64">
+      <c r="J20" s="82">
         <v>48.48</v>
       </c>
-      <c r="K18" s="64">
+      <c r="K20" s="82">
         <v>3.75</v>
       </c>
-      <c r="L18" s="64">
+      <c r="L20" s="82">
         <v>8.76</v>
       </c>
-      <c r="M18" s="43"/>
-      <c r="N18" s="68"/>
-      <c r="O18" s="43"/>
-      <c r="P18" s="43"/>
-      <c r="Q18" s="43"/>
-      <c r="R18" s="43"/>
-      <c r="S18" s="43"/>
-      <c r="V18" s="87" t="s">
+      <c r="M20" s="96"/>
+      <c r="N20" s="97"/>
+      <c r="O20" s="96"/>
+      <c r="P20" s="96"/>
+      <c r="Q20" s="96"/>
+      <c r="R20" s="96"/>
+      <c r="S20" s="96"/>
+      <c r="T20" s="98"/>
+      <c r="U20" s="98"/>
+      <c r="V20" s="84" t="s">
         <v>139</v>
       </c>
-      <c r="W18" s="60"/>
-      <c r="X18" s="61" t="s">
+      <c r="W20" s="84"/>
+      <c r="X20" s="99" t="s">
         <v>94</v>
       </c>
-      <c r="Y18" s="62" t="s">
+      <c r="Y20" s="100" t="s">
         <v>143</v>
       </c>
-      <c r="Z18" s="45" t="s">
+      <c r="Z20" s="76" t="s">
         <v>58</v>
       </c>
-      <c r="AA18" s="45" t="s">
+      <c r="AA20" s="76" t="s">
         <v>87</v>
       </c>
-      <c r="AB18" s="63" t="s">
+      <c r="AB20" s="101" t="s">
         <v>88</v>
       </c>
-      <c r="AC18" s="46"/>
-      <c r="AD18" s="46"/>
-      <c r="AI18"/>
-      <c r="AJ18" s="39"/>
-      <c r="AK18" s="77"/>
-      <c r="AL18" s="77"/>
-      <c r="AM18" s="77"/>
-      <c r="AN18" s="77"/>
-      <c r="AO18" s="77"/>
-      <c r="AP18" s="77"/>
-      <c r="AQ18" s="77"/>
-      <c r="AR18" s="77"/>
-      <c r="AS18" s="77"/>
-      <c r="AT18" s="77"/>
-      <c r="AU18" s="77"/>
-      <c r="AV18" s="77"/>
-      <c r="AW18" s="77"/>
-      <c r="AY18" s="46"/>
-    </row>
-    <row r="19" spans="2:51" x14ac:dyDescent="0.25">
-      <c r="B19" s="45" t="str">
+      <c r="AC20" s="98"/>
+      <c r="AD20" s="98"/>
+      <c r="AI20" s="14"/>
+      <c r="AJ20" s="12"/>
+      <c r="AY20" s="98"/>
+    </row>
+    <row r="21" spans="2:51" s="85" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="85" t="str">
+        <f>X23</f>
+        <v>ELCBoiler</v>
+      </c>
+      <c r="C21" s="85" t="s">
+        <v>69</v>
+      </c>
+      <c r="D21" s="86" t="str">
+        <f>X12</f>
+        <v>GHEAT</v>
+      </c>
+      <c r="E21" s="87">
+        <v>2030</v>
+      </c>
+      <c r="F21" s="88">
+        <v>0.99</v>
+      </c>
+      <c r="G21" s="88">
+        <v>1</v>
+      </c>
+      <c r="H21" s="87">
+        <v>25</v>
+      </c>
+      <c r="I21" s="88">
+        <v>112.9</v>
+      </c>
+      <c r="J21" s="88">
+        <v>14.26</v>
+      </c>
+      <c r="K21" s="88">
+        <v>1.22</v>
+      </c>
+      <c r="L21" s="88">
+        <v>8.76</v>
+      </c>
+      <c r="M21" s="87"/>
+      <c r="S21" s="87"/>
+      <c r="T21" s="89"/>
+      <c r="U21" s="89"/>
+      <c r="V21" s="90" t="s">
+        <v>128</v>
+      </c>
+      <c r="W21" s="90"/>
+      <c r="X21" s="91" t="s">
+        <v>95</v>
+      </c>
+      <c r="Y21" s="92" t="s">
+        <v>144</v>
+      </c>
+      <c r="Z21" s="85" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA21" s="85" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB21" s="93" t="s">
+        <v>88</v>
+      </c>
+      <c r="AC21" s="89"/>
+      <c r="AD21" s="89"/>
+      <c r="AI21" s="94"/>
+      <c r="AJ21" s="95"/>
+      <c r="AY21" s="89"/>
+    </row>
+    <row r="22" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="45" t="str">
         <f>X21</f>
-        <v>ELCBoiler</v>
-      </c>
-      <c r="C19" s="45" t="s">
-        <v>69</v>
-      </c>
-      <c r="D19" s="50" t="s">
-        <v>107</v>
-      </c>
-      <c r="E19" s="43">
-        <v>2030</v>
-      </c>
-      <c r="F19" s="64">
-        <v>0.99</v>
-      </c>
-      <c r="G19" s="64">
-        <v>1</v>
-      </c>
-      <c r="H19" s="43">
-        <v>25</v>
-      </c>
-      <c r="I19" s="64">
-        <v>112.9</v>
-      </c>
-      <c r="J19" s="64">
-        <v>14.26</v>
-      </c>
-      <c r="K19" s="64">
-        <v>1.22</v>
-      </c>
-      <c r="L19" s="64">
-        <v>8.76</v>
-      </c>
-      <c r="M19" s="43"/>
-      <c r="S19" s="43"/>
-      <c r="V19" s="60" t="s">
-        <v>128</v>
-      </c>
-      <c r="W19" s="60"/>
-      <c r="X19" s="61" t="s">
-        <v>95</v>
-      </c>
-      <c r="Y19" s="62" t="s">
-        <v>144</v>
-      </c>
-      <c r="Z19" s="45" t="s">
-        <v>58</v>
-      </c>
-      <c r="AA19" s="45" t="s">
-        <v>87</v>
-      </c>
-      <c r="AB19" s="63" t="s">
-        <v>88</v>
-      </c>
-      <c r="AC19" s="46"/>
-      <c r="AD19" s="46"/>
-      <c r="AI19"/>
-      <c r="AJ19" s="39"/>
-      <c r="AY19" s="46"/>
-    </row>
-    <row r="20" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="45" t="str">
-        <f>X19</f>
         <v>BIOKiln</v>
       </c>
-      <c r="C20" s="45" t="str">
+      <c r="C22" s="45" t="str">
         <f>PRI_Sector_Fuels!P5</f>
         <v>MANBIOMIN</v>
       </c>
-      <c r="D20" s="50" t="s">
+      <c r="D22" s="50" t="s">
         <v>108</v>
       </c>
-      <c r="E20" s="43">
+      <c r="E22" s="43">
         <v>2030</v>
       </c>
-      <c r="F20" s="64">
+      <c r="F22" s="64">
         <v>0.55600000000000005</v>
       </c>
-      <c r="G20" s="64">
+      <c r="G22" s="64">
         <v>0.98</v>
       </c>
-      <c r="H20" s="43">
+      <c r="H22" s="43">
         <v>25</v>
       </c>
-      <c r="I20" s="64">
+      <c r="I22" s="64">
         <v>297.10000000000002</v>
       </c>
-      <c r="J20" s="64">
+      <c r="J22" s="64">
         <v>4.46</v>
       </c>
-      <c r="K20" s="64">
+      <c r="K22" s="64">
         <v>0.45</v>
       </c>
-      <c r="L20" s="64">
+      <c r="L22" s="64">
         <v>8.76</v>
       </c>
-      <c r="M20" s="43"/>
-      <c r="N20" s="64">
+      <c r="M22" s="43"/>
+      <c r="N22" s="64">
         <v>0.1</v>
       </c>
-      <c r="O20" s="64">
+      <c r="O22" s="64">
         <v>0.15</v>
       </c>
-      <c r="P20" s="64">
+      <c r="P22" s="64">
         <v>0.2</v>
       </c>
-      <c r="Q20" s="64">
+      <c r="Q22" s="64">
         <v>0.25</v>
       </c>
-      <c r="R20" s="64">
+      <c r="R22" s="64">
         <v>0.35</v>
       </c>
-      <c r="S20" s="43"/>
-      <c r="V20" s="60" t="s">
+      <c r="S22" s="43"/>
+      <c r="V22" s="60" t="s">
         <v>128</v>
       </c>
-      <c r="W20" s="60"/>
-      <c r="X20" s="61" t="s">
+      <c r="W22" s="60"/>
+      <c r="X22" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="Y20" s="62" t="s">
+      <c r="Y22" s="62" t="s">
         <v>145</v>
       </c>
-      <c r="Z20" s="45" t="s">
+      <c r="Z22" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="AA20" s="45" t="s">
+      <c r="AA22" s="45" t="s">
         <v>87</v>
       </c>
-      <c r="AB20" s="63" t="s">
+      <c r="AB22" s="63" t="s">
         <v>88</v>
       </c>
-      <c r="AI20"/>
-      <c r="AJ20"/>
-      <c r="AK20" s="45"/>
-      <c r="AL20" s="45"/>
-      <c r="AM20" s="45"/>
-      <c r="AN20" s="45"/>
-      <c r="AO20" s="45"/>
-      <c r="AP20" s="45"/>
-      <c r="AQ20" s="45"/>
-      <c r="AR20" s="45"/>
-      <c r="AS20" s="45"/>
-      <c r="AT20" s="45"/>
-      <c r="AU20" s="45"/>
-      <c r="AV20" s="45"/>
-      <c r="AW20" s="45"/>
-    </row>
-    <row r="21" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="50" t="str">
-        <f>X20</f>
+      <c r="AI22"/>
+      <c r="AJ22"/>
+      <c r="AK22" s="45"/>
+      <c r="AL22" s="45"/>
+      <c r="AM22" s="45"/>
+      <c r="AN22" s="45"/>
+      <c r="AO22" s="45"/>
+      <c r="AP22" s="45"/>
+      <c r="AQ22" s="45"/>
+      <c r="AR22" s="45"/>
+      <c r="AS22" s="45"/>
+      <c r="AT22" s="45"/>
+      <c r="AU22" s="45"/>
+      <c r="AV22" s="45"/>
+      <c r="AW22" s="45"/>
+    </row>
+    <row r="23" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="50" t="str">
+        <f>X22</f>
         <v>GASBoiler</v>
       </c>
-      <c r="C21" s="45" t="str">
+      <c r="C23" s="45" t="str">
         <f>PRI_Sector_Fuels!P6</f>
         <v>MANGASMIN</v>
       </c>
-      <c r="D21" s="50" t="s">
+      <c r="D23" s="50" t="s">
         <v>107</v>
       </c>
-      <c r="E21" s="43">
+      <c r="E23" s="43">
         <v>2030</v>
       </c>
-      <c r="F21" s="64">
+      <c r="F23" s="64">
         <v>0.75</v>
       </c>
-      <c r="G21" s="64">
+      <c r="G23" s="64">
         <v>0.99</v>
       </c>
-      <c r="H21" s="43">
+      <c r="H23" s="43">
         <v>25</v>
       </c>
-      <c r="I21" s="64">
+      <c r="I23" s="64">
         <v>61.4</v>
       </c>
-      <c r="J21" s="64">
+      <c r="J23" s="64">
         <v>2.57</v>
       </c>
-      <c r="K21" s="64">
+      <c r="K23" s="64">
         <v>1.35</v>
       </c>
-      <c r="L21" s="64">
+      <c r="L23" s="64">
         <v>8.76</v>
       </c>
-      <c r="M21" s="43"/>
-      <c r="N21" s="68"/>
-      <c r="O21" s="43"/>
-      <c r="P21" s="43"/>
-      <c r="Q21" s="43"/>
-      <c r="R21" s="43"/>
-      <c r="S21" s="43"/>
-      <c r="V21" s="60" t="s">
-        <v>128</v>
-      </c>
-      <c r="W21" s="60"/>
-      <c r="X21" s="61" t="s">
+      <c r="M23" s="43"/>
+      <c r="N23" s="67"/>
+      <c r="O23" s="43"/>
+      <c r="P23" s="43"/>
+      <c r="Q23" s="43"/>
+      <c r="R23" s="43"/>
+      <c r="S23" s="43"/>
+      <c r="V23" s="60" t="s">
+        <v>139</v>
+      </c>
+      <c r="W23" s="60"/>
+      <c r="X23" s="61" t="s">
         <v>97</v>
       </c>
-      <c r="Y21" s="62" t="s">
+      <c r="Y23" s="62" t="s">
         <v>146</v>
       </c>
-      <c r="Z21" s="45" t="s">
+      <c r="Z23" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="AA21" s="45" t="s">
+      <c r="AA23" s="45" t="s">
         <v>87</v>
       </c>
-      <c r="AB21" s="63" t="s">
+      <c r="AB23" s="63" t="s">
         <v>88</v>
       </c>
-      <c r="AI21"/>
-      <c r="AJ21"/>
-      <c r="AK21" s="77"/>
-      <c r="AL21" s="77"/>
-      <c r="AM21" s="77"/>
-      <c r="AN21" s="77"/>
-      <c r="AO21" s="77"/>
-      <c r="AP21" s="77"/>
-      <c r="AQ21" s="77"/>
-      <c r="AR21" s="77"/>
-      <c r="AS21" s="77"/>
-      <c r="AT21" s="77"/>
-      <c r="AU21" s="77"/>
-      <c r="AV21" s="77"/>
-      <c r="AW21" s="77"/>
-    </row>
-    <row r="22" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="50" t="str">
-        <f>X23</f>
+      <c r="AI23"/>
+      <c r="AJ23"/>
+      <c r="AK23" s="76"/>
+      <c r="AL23" s="76"/>
+      <c r="AM23" s="76"/>
+      <c r="AN23" s="76"/>
+      <c r="AO23" s="76"/>
+      <c r="AP23" s="76"/>
+      <c r="AQ23" s="76"/>
+      <c r="AR23" s="76"/>
+      <c r="AS23" s="76"/>
+      <c r="AT23" s="76"/>
+      <c r="AU23" s="76"/>
+      <c r="AV23" s="76"/>
+      <c r="AW23" s="76"/>
+    </row>
+    <row r="24" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="50" t="str">
+        <f>X25</f>
         <v>WNDTRBN</v>
       </c>
-      <c r="C22" s="45" t="str">
+      <c r="C24" s="45" t="str">
         <f>PRI_Sector_Fuels!D19</f>
         <v>WIND</v>
       </c>
-      <c r="D22" s="50" t="s">
+      <c r="D24" s="50" t="s">
         <v>130</v>
-      </c>
-      <c r="E22" s="43">
-        <v>2030</v>
-      </c>
-      <c r="F22" s="83">
-        <v>1</v>
-      </c>
-      <c r="G22" s="64">
-        <v>0.97</v>
-      </c>
-      <c r="H22" s="43">
-        <v>25</v>
-      </c>
-      <c r="I22" s="64">
-        <v>1041</v>
-      </c>
-      <c r="J22" s="64">
-        <v>38</v>
-      </c>
-      <c r="K22" s="64">
-        <v>0</v>
-      </c>
-      <c r="L22" s="64">
-        <v>8.76</v>
-      </c>
-      <c r="M22" s="68"/>
-      <c r="N22" s="68"/>
-      <c r="O22" s="64"/>
-      <c r="P22" s="64"/>
-      <c r="Q22" s="64"/>
-      <c r="R22" s="68"/>
-      <c r="S22" s="43">
-        <v>0.2</v>
-      </c>
-      <c r="V22" s="60" t="s">
-        <v>139</v>
-      </c>
-      <c r="W22" s="60"/>
-      <c r="X22" s="61" t="s">
-        <v>65</v>
-      </c>
-      <c r="Y22" s="62" t="s">
-        <v>147</v>
-      </c>
-      <c r="Z22" s="45" t="s">
-        <v>58</v>
-      </c>
-      <c r="AA22" s="45" t="s">
-        <v>87</v>
-      </c>
-      <c r="AB22" s="46" t="s">
-        <v>88</v>
-      </c>
-      <c r="AI22"/>
-      <c r="AJ22"/>
-      <c r="AK22" s="77"/>
-      <c r="AL22" s="77"/>
-      <c r="AM22" s="77"/>
-      <c r="AN22" s="77"/>
-      <c r="AO22" s="77"/>
-      <c r="AP22" s="77"/>
-      <c r="AQ22" s="77"/>
-      <c r="AR22" s="77"/>
-      <c r="AS22" s="77"/>
-      <c r="AT22" s="77"/>
-      <c r="AU22" s="77"/>
-      <c r="AV22" s="77"/>
-      <c r="AW22" s="77"/>
-    </row>
-    <row r="23" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="50" t="str">
-        <f>X24</f>
-        <v>SOLPV</v>
-      </c>
-      <c r="C23" s="45" t="str">
-        <f>PRI_Sector_Fuels!D20</f>
-        <v>SOLAR</v>
-      </c>
-      <c r="D23" s="50" t="s">
-        <v>131</v>
-      </c>
-      <c r="E23" s="43">
-        <v>2030</v>
-      </c>
-      <c r="F23" s="83">
-        <v>0.20499999999999999</v>
-      </c>
-      <c r="G23" s="64">
-        <v>0.99</v>
-      </c>
-      <c r="H23" s="43">
-        <v>25</v>
-      </c>
-      <c r="I23" s="64">
-        <v>691</v>
-      </c>
-      <c r="J23" s="64">
-        <v>6.99</v>
-      </c>
-      <c r="K23" s="64">
-        <v>0</v>
-      </c>
-      <c r="L23" s="64">
-        <v>8.76</v>
-      </c>
-      <c r="M23" s="68"/>
-      <c r="N23" s="68"/>
-      <c r="O23" s="64"/>
-      <c r="P23" s="64"/>
-      <c r="Q23" s="64"/>
-      <c r="R23" s="68"/>
-      <c r="S23" s="43">
-        <v>0.3</v>
-      </c>
-      <c r="V23" s="60" t="s">
-        <v>69</v>
-      </c>
-      <c r="W23" s="60"/>
-      <c r="X23" s="61" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y23" s="62" t="s">
-        <v>148</v>
-      </c>
-      <c r="Z23" s="45" t="s">
-        <v>58</v>
-      </c>
-      <c r="AA23" s="45" t="s">
-        <v>87</v>
-      </c>
-      <c r="AB23" s="46" t="s">
-        <v>88</v>
-      </c>
-      <c r="AI23"/>
-      <c r="AJ23"/>
-      <c r="AK23" s="45"/>
-      <c r="AL23" s="45"/>
-      <c r="AM23" s="45"/>
-      <c r="AN23" s="45"/>
-      <c r="AO23" s="45"/>
-      <c r="AP23" s="45"/>
-      <c r="AQ23" s="45"/>
-      <c r="AR23" s="45"/>
-      <c r="AS23" s="45"/>
-      <c r="AT23" s="45"/>
-      <c r="AU23" s="45"/>
-      <c r="AV23" s="45"/>
-      <c r="AW23" s="45"/>
-    </row>
-    <row r="24" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="50" t="str">
-        <f>X22</f>
-        <v>CSP</v>
-      </c>
-      <c r="C24" s="45" t="str">
-        <f>PRI_Sector_Fuels!D20</f>
-        <v>SOLAR</v>
-      </c>
-      <c r="D24" s="50" t="str">
-        <f>X9</f>
-        <v>RENHEAT</v>
       </c>
       <c r="E24" s="43">
         <v>2030</v>
       </c>
-      <c r="F24" s="83">
-        <v>0.4</v>
+      <c r="F24" s="82">
+        <v>1</v>
       </c>
       <c r="G24" s="64">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H24" s="43">
         <v>25</v>
       </c>
       <c r="I24" s="64">
-        <v>3677</v>
+        <v>1041</v>
       </c>
       <c r="J24" s="64">
+        <v>38</v>
+      </c>
+      <c r="K24" s="64">
         <v>0</v>
-      </c>
-      <c r="K24" s="64">
-        <v>14</v>
       </c>
       <c r="L24" s="64">
         <v>8.76</v>
       </c>
-      <c r="M24" s="68"/>
-      <c r="N24" s="68"/>
+      <c r="M24" s="67"/>
+      <c r="N24" s="67"/>
       <c r="O24" s="64"/>
       <c r="P24" s="64"/>
       <c r="Q24" s="64"/>
-      <c r="R24" s="68"/>
-      <c r="S24" s="43"/>
+      <c r="R24" s="67"/>
+      <c r="S24" s="43">
+        <v>0.2</v>
+      </c>
       <c r="V24" s="60" t="s">
-        <v>69</v>
+        <v>139</v>
       </c>
       <c r="W24" s="60"/>
       <c r="X24" s="61" t="s">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="Y24" s="62" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="Z24" s="45" t="s">
         <v>58</v>
@@ -5149,46 +5085,49 @@
       </c>
       <c r="AI24"/>
       <c r="AJ24"/>
-      <c r="AK24" s="45"/>
-      <c r="AL24" s="45"/>
-      <c r="AM24" s="45"/>
-      <c r="AN24" s="45"/>
-      <c r="AO24" s="45"/>
-      <c r="AP24" s="45"/>
-      <c r="AQ24" s="45"/>
-      <c r="AR24" s="45"/>
-      <c r="AS24" s="45"/>
-      <c r="AT24" s="45"/>
-      <c r="AU24" s="45"/>
-      <c r="AV24" s="45"/>
-      <c r="AW24" s="45"/>
+      <c r="AK24" s="76"/>
+      <c r="AL24" s="76"/>
+      <c r="AM24" s="76"/>
+      <c r="AN24" s="76"/>
+      <c r="AO24" s="76"/>
+      <c r="AP24" s="76"/>
+      <c r="AQ24" s="76"/>
+      <c r="AR24" s="76"/>
+      <c r="AS24" s="76"/>
+      <c r="AT24" s="76"/>
+      <c r="AU24" s="76"/>
+      <c r="AV24" s="76"/>
+      <c r="AW24" s="76"/>
     </row>
     <row r="25" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B25" s="50" t="str">
-        <f>X20</f>
-        <v>GASBoiler</v>
-      </c>
-      <c r="C25" s="45"/>
+        <f>X26</f>
+        <v>SOLPV</v>
+      </c>
+      <c r="C25" s="45" t="str">
+        <f>PRI_Sector_Fuels!D20</f>
+        <v>SOLAR</v>
+      </c>
       <c r="D25" s="50" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="E25" s="43">
         <v>2030</v>
       </c>
-      <c r="F25" s="83">
-        <v>0.3</v>
+      <c r="F25" s="82">
+        <v>0.20499999999999999</v>
       </c>
       <c r="G25" s="64">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="H25" s="43">
         <v>25</v>
       </c>
       <c r="I25" s="64">
-        <v>0</v>
+        <v>691</v>
       </c>
       <c r="J25" s="64">
-        <v>0</v>
+        <v>6.99</v>
       </c>
       <c r="K25" s="64">
         <v>0</v>
@@ -5196,22 +5135,24 @@
       <c r="L25" s="64">
         <v>8.76</v>
       </c>
-      <c r="M25" s="68"/>
-      <c r="N25" s="68"/>
+      <c r="M25" s="67"/>
+      <c r="N25" s="67"/>
       <c r="O25" s="64"/>
       <c r="P25" s="64"/>
       <c r="Q25" s="64"/>
-      <c r="R25" s="68"/>
-      <c r="S25" s="43"/>
+      <c r="R25" s="67"/>
+      <c r="S25" s="43">
+        <v>0.3</v>
+      </c>
       <c r="V25" s="60" t="s">
         <v>69</v>
       </c>
       <c r="W25" s="60"/>
       <c r="X25" s="61" t="s">
-        <v>129</v>
+        <v>89</v>
       </c>
       <c r="Y25" s="62" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="Z25" s="45" t="s">
         <v>58</v>
@@ -5238,136 +5179,134 @@
       <c r="AV25" s="45"/>
       <c r="AW25" s="45"/>
     </row>
-    <row r="26" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="85" t="str">
-        <f>X25</f>
-        <v>DECELC</v>
-      </c>
-      <c r="C26" s="50" t="s">
-        <v>130</v>
-      </c>
-      <c r="D26" s="50" t="str">
-        <f>X10</f>
-        <v>RENELC</v>
-      </c>
-      <c r="E26" s="43">
+    <row r="26" spans="2:51" s="98" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="83" t="str">
+        <f>X24</f>
+        <v>CSP</v>
+      </c>
+      <c r="C26" s="76" t="str">
+        <f>PRI_Sector_Fuels!D20</f>
+        <v>SOLAR</v>
+      </c>
+      <c r="D26" s="83" t="str">
+        <f>X9</f>
+        <v>DECHEAT</v>
+      </c>
+      <c r="E26" s="96">
         <v>2030</v>
       </c>
-      <c r="F26" s="46">
+      <c r="F26" s="82">
+        <v>0.4</v>
+      </c>
+      <c r="G26" s="82">
         <v>1</v>
       </c>
-      <c r="G26" s="46">
-        <v>1</v>
-      </c>
-      <c r="H26" s="43">
-        <v>100</v>
-      </c>
-      <c r="I26" s="64">
+      <c r="H26" s="96">
+        <v>25</v>
+      </c>
+      <c r="I26" s="82">
+        <v>3677</v>
+      </c>
+      <c r="J26" s="82">
         <v>0</v>
       </c>
-      <c r="J26" s="45">
-        <v>0</v>
-      </c>
-      <c r="K26" s="46">
-        <v>0</v>
-      </c>
-      <c r="L26" s="64">
+      <c r="K26" s="82">
+        <v>14</v>
+      </c>
+      <c r="L26" s="82">
         <v>8.76</v>
       </c>
-      <c r="M26" s="68"/>
-      <c r="N26" s="68"/>
-      <c r="O26" s="64"/>
-      <c r="P26" s="64"/>
-      <c r="Q26" s="64"/>
-      <c r="R26" s="68"/>
-      <c r="S26" s="43"/>
-      <c r="V26" s="60" t="s">
+      <c r="M26" s="97"/>
+      <c r="N26" s="97"/>
+      <c r="O26" s="82"/>
+      <c r="P26" s="82"/>
+      <c r="Q26" s="82"/>
+      <c r="R26" s="97"/>
+      <c r="S26" s="96"/>
+      <c r="V26" s="84" t="s">
         <v>69</v>
       </c>
-      <c r="W26" s="60"/>
-      <c r="X26" s="61" t="s">
-        <v>137</v>
-      </c>
-      <c r="Y26" s="62" t="s">
-        <v>151</v>
-      </c>
-      <c r="Z26" s="45" t="s">
+      <c r="W26" s="84"/>
+      <c r="X26" s="99" t="s">
+        <v>90</v>
+      </c>
+      <c r="Y26" s="100" t="s">
+        <v>149</v>
+      </c>
+      <c r="Z26" s="76" t="s">
         <v>58</v>
       </c>
-      <c r="AA26" s="45" t="s">
+      <c r="AA26" s="76" t="s">
         <v>87</v>
       </c>
-      <c r="AB26" s="46" t="s">
+      <c r="AB26" s="98" t="s">
         <v>88</v>
       </c>
-      <c r="AI26"/>
-      <c r="AJ26"/>
-      <c r="AK26" s="45"/>
-      <c r="AL26" s="45"/>
-      <c r="AM26" s="45"/>
-      <c r="AN26" s="45"/>
-      <c r="AO26" s="45"/>
-      <c r="AP26" s="45"/>
-      <c r="AQ26" s="45"/>
-      <c r="AR26" s="45"/>
-      <c r="AS26" s="45"/>
-      <c r="AT26" s="45"/>
-      <c r="AU26" s="45"/>
-      <c r="AV26" s="45"/>
-      <c r="AW26" s="45"/>
+      <c r="AI26" s="14"/>
+      <c r="AJ26" s="14"/>
+      <c r="AK26" s="76"/>
+      <c r="AL26" s="76"/>
+      <c r="AM26" s="76"/>
+      <c r="AN26" s="76"/>
+      <c r="AO26" s="76"/>
+      <c r="AP26" s="76"/>
+      <c r="AQ26" s="76"/>
+      <c r="AR26" s="76"/>
+      <c r="AS26" s="76"/>
+      <c r="AT26" s="76"/>
+      <c r="AU26" s="76"/>
+      <c r="AV26" s="76"/>
+      <c r="AW26" s="76"/>
     </row>
     <row r="27" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="85" t="str">
-        <f>X25</f>
-        <v>DECELC</v>
-      </c>
-      <c r="C27" s="50" t="s">
-        <v>131</v>
-      </c>
-      <c r="D27" s="50" t="str">
-        <f>X10</f>
-        <v>RENELC</v>
+      <c r="B27" s="50" t="str">
+        <f>X22</f>
+        <v>GASBoiler</v>
+      </c>
+      <c r="C27" s="45"/>
+      <c r="D27" s="50" t="s">
+        <v>106</v>
       </c>
       <c r="E27" s="43">
         <v>2030</v>
       </c>
-      <c r="F27" s="46">
+      <c r="F27" s="82">
+        <v>0.3</v>
+      </c>
+      <c r="G27" s="64">
         <v>1</v>
       </c>
-      <c r="G27" s="46">
-        <v>1</v>
-      </c>
       <c r="H27" s="43">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="I27" s="64">
         <v>0</v>
       </c>
-      <c r="J27" s="45">
+      <c r="J27" s="64">
         <v>0</v>
       </c>
-      <c r="K27" s="46">
+      <c r="K27" s="64">
         <v>0</v>
       </c>
       <c r="L27" s="64">
         <v>8.76</v>
       </c>
-      <c r="M27" s="68"/>
-      <c r="N27" s="68"/>
+      <c r="M27" s="67"/>
+      <c r="N27" s="67"/>
       <c r="O27" s="64"/>
       <c r="P27" s="64"/>
       <c r="Q27" s="64"/>
-      <c r="R27" s="68"/>
+      <c r="R27" s="67"/>
       <c r="S27" s="43"/>
-      <c r="V27" s="45" t="s">
-        <v>139</v>
-      </c>
-      <c r="W27" s="45"/>
-      <c r="X27" s="45" t="s">
-        <v>155</v>
-      </c>
-      <c r="Y27" s="45" t="s">
-        <v>152</v>
+      <c r="V27" s="60" t="s">
+        <v>69</v>
+      </c>
+      <c r="W27" s="60"/>
+      <c r="X27" s="61" t="s">
+        <v>158</v>
+      </c>
+      <c r="Y27" s="62" t="s">
+        <v>150</v>
       </c>
       <c r="Z27" s="45" t="s">
         <v>58</v>
@@ -5394,242 +5333,284 @@
       <c r="AV27" s="45"/>
       <c r="AW27" s="45"/>
     </row>
-    <row r="28" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="50" t="str">
-        <f>X26</f>
+    <row r="28" spans="2:51" s="104" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="102" t="str">
+        <f>X27</f>
+        <v>DECPOWER</v>
+      </c>
+      <c r="C28" s="102" t="s">
+        <v>130</v>
+      </c>
+      <c r="D28" s="102" t="str">
+        <f>X10</f>
+        <v>DECELC</v>
+      </c>
+      <c r="E28" s="103">
+        <v>2030</v>
+      </c>
+      <c r="F28" s="104">
+        <v>1</v>
+      </c>
+      <c r="G28" s="104">
+        <v>1</v>
+      </c>
+      <c r="H28" s="103">
+        <v>100</v>
+      </c>
+      <c r="I28" s="105">
+        <v>0</v>
+      </c>
+      <c r="J28" s="106">
+        <v>0</v>
+      </c>
+      <c r="K28" s="104">
+        <v>0</v>
+      </c>
+      <c r="L28" s="105">
+        <v>8.76</v>
+      </c>
+      <c r="M28" s="107"/>
+      <c r="N28" s="107"/>
+      <c r="O28" s="105"/>
+      <c r="P28" s="105"/>
+      <c r="Q28" s="105"/>
+      <c r="R28" s="107"/>
+      <c r="S28" s="103"/>
+      <c r="V28" s="108" t="s">
+        <v>69</v>
+      </c>
+      <c r="W28" s="108"/>
+      <c r="X28" s="109" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y28" s="110" t="s">
+        <v>151</v>
+      </c>
+      <c r="Z28" s="106" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA28" s="106" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB28" s="104" t="s">
+        <v>88</v>
+      </c>
+      <c r="AI28" s="111"/>
+      <c r="AJ28" s="111"/>
+      <c r="AK28" s="106"/>
+      <c r="AL28" s="106"/>
+      <c r="AM28" s="106"/>
+      <c r="AN28" s="106"/>
+      <c r="AO28" s="106"/>
+      <c r="AP28" s="106"/>
+      <c r="AQ28" s="106"/>
+      <c r="AR28" s="106"/>
+      <c r="AS28" s="106"/>
+      <c r="AT28" s="106"/>
+      <c r="AU28" s="106"/>
+      <c r="AV28" s="106"/>
+      <c r="AW28" s="106"/>
+    </row>
+    <row r="29" spans="2:51" s="104" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="102" t="str">
+        <f>X27</f>
+        <v>DECPOWER</v>
+      </c>
+      <c r="C29" s="102" t="s">
+        <v>131</v>
+      </c>
+      <c r="D29" s="102" t="str">
+        <f>X10</f>
+        <v>DECELC</v>
+      </c>
+      <c r="E29" s="103">
+        <v>2030</v>
+      </c>
+      <c r="F29" s="104">
+        <v>1</v>
+      </c>
+      <c r="G29" s="104">
+        <v>1</v>
+      </c>
+      <c r="H29" s="103">
+        <v>100</v>
+      </c>
+      <c r="I29" s="105">
+        <v>0</v>
+      </c>
+      <c r="J29" s="106">
+        <v>0</v>
+      </c>
+      <c r="K29" s="104">
+        <v>0</v>
+      </c>
+      <c r="L29" s="105">
+        <v>8.76</v>
+      </c>
+      <c r="M29" s="107"/>
+      <c r="N29" s="107"/>
+      <c r="O29" s="105"/>
+      <c r="P29" s="105"/>
+      <c r="Q29" s="105"/>
+      <c r="R29" s="107"/>
+      <c r="S29" s="103"/>
+      <c r="V29" s="46" t="s">
+        <v>128</v>
+      </c>
+      <c r="W29" s="46"/>
+      <c r="X29" s="46" t="s">
+        <v>161</v>
+      </c>
+      <c r="Y29" s="46" t="s">
+        <v>152</v>
+      </c>
+      <c r="Z29" s="106" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA29" s="106" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB29" s="104" t="s">
+        <v>88</v>
+      </c>
+      <c r="AC29" s="46"/>
+      <c r="AI29" s="111"/>
+      <c r="AJ29" s="111"/>
+      <c r="AK29" s="106"/>
+      <c r="AL29" s="106"/>
+      <c r="AM29" s="106"/>
+      <c r="AN29" s="106"/>
+      <c r="AO29" s="106"/>
+      <c r="AP29" s="106"/>
+      <c r="AQ29" s="106"/>
+      <c r="AR29" s="106"/>
+      <c r="AS29" s="106"/>
+      <c r="AT29" s="106"/>
+      <c r="AU29" s="106"/>
+      <c r="AV29" s="106"/>
+      <c r="AW29" s="106"/>
+    </row>
+    <row r="30" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="50" t="str">
+        <f>X28</f>
         <v>BIOPOWER</v>
       </c>
-      <c r="C28" s="50" t="s">
+      <c r="C30" s="50" t="s">
         <v>68</v>
       </c>
-      <c r="D28" s="50" t="s">
+      <c r="D30" s="50" t="s">
         <v>135</v>
-      </c>
-      <c r="E28" s="43">
-        <v>2030</v>
-      </c>
-      <c r="F28" s="46">
-        <v>0.35</v>
-      </c>
-      <c r="G28" s="46">
-        <v>0.98</v>
-      </c>
-      <c r="H28" s="43">
-        <v>20</v>
-      </c>
-      <c r="I28" s="86">
-        <v>3242</v>
-      </c>
-      <c r="J28" s="64">
-        <v>129.68</v>
-      </c>
-      <c r="K28" s="64">
-        <v>0</v>
-      </c>
-      <c r="L28" s="64">
-        <v>8.76</v>
-      </c>
-      <c r="M28" s="68"/>
-      <c r="N28" s="68"/>
-      <c r="O28" s="64"/>
-      <c r="P28" s="64"/>
-      <c r="Q28" s="64"/>
-      <c r="R28" s="68"/>
-      <c r="S28" s="43"/>
-      <c r="AI28"/>
-      <c r="AJ28"/>
-      <c r="AK28" s="45"/>
-      <c r="AL28" s="45"/>
-      <c r="AM28" s="45"/>
-      <c r="AN28" s="45"/>
-      <c r="AO28" s="45"/>
-      <c r="AP28" s="45"/>
-      <c r="AQ28" s="45"/>
-      <c r="AR28" s="45"/>
-      <c r="AS28" s="45"/>
-      <c r="AT28" s="45"/>
-      <c r="AU28" s="45"/>
-      <c r="AV28" s="45"/>
-      <c r="AW28" s="45"/>
-    </row>
-    <row r="29" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="50" t="s">
-        <v>129</v>
-      </c>
-      <c r="C29" s="45" t="s">
-        <v>135</v>
-      </c>
-      <c r="D29" s="50" t="str">
-        <f>X10</f>
-        <v>RENELC</v>
-      </c>
-      <c r="E29" s="43">
-        <v>2030</v>
-      </c>
-      <c r="F29" s="83">
-        <v>1</v>
-      </c>
-      <c r="G29" s="64">
-        <v>1</v>
-      </c>
-      <c r="H29" s="46">
-        <v>100</v>
-      </c>
-      <c r="I29" s="46">
-        <v>0</v>
-      </c>
-      <c r="J29" s="46">
-        <v>0</v>
-      </c>
-      <c r="K29" s="46">
-        <v>0</v>
-      </c>
-      <c r="L29" s="46">
-        <v>0</v>
-      </c>
-      <c r="M29" s="68"/>
-      <c r="N29" s="68"/>
-      <c r="O29" s="64"/>
-      <c r="P29" s="64"/>
-      <c r="Q29" s="64"/>
-      <c r="R29" s="68"/>
-      <c r="S29" s="43"/>
-      <c r="V29" s="45"/>
-      <c r="W29" s="45"/>
-      <c r="X29" s="45"/>
-      <c r="Y29" s="45"/>
-      <c r="Z29" s="45"/>
-      <c r="AA29" s="45"/>
-      <c r="AB29" s="45"/>
-      <c r="AC29" s="45"/>
-      <c r="AD29" s="45"/>
-      <c r="AI29"/>
-      <c r="AJ29"/>
-      <c r="AK29" s="45"/>
-      <c r="AL29" s="45"/>
-      <c r="AM29" s="45"/>
-      <c r="AN29" s="45"/>
-      <c r="AO29" s="45"/>
-      <c r="AP29" s="45"/>
-      <c r="AQ29" s="45"/>
-      <c r="AR29" s="45"/>
-      <c r="AS29" s="45"/>
-      <c r="AT29" s="45"/>
-      <c r="AU29" s="45"/>
-      <c r="AV29" s="45"/>
-      <c r="AW29" s="45"/>
-    </row>
-    <row r="30" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="45" t="str">
-        <f>X27</f>
-        <v>RENTHT</v>
-      </c>
-      <c r="C30" s="50" t="str">
-        <f>X9</f>
-        <v>RENHEAT</v>
-      </c>
-      <c r="D30" s="84" t="s">
-        <v>107</v>
       </c>
       <c r="E30" s="43">
         <v>2030</v>
       </c>
-      <c r="F30" s="64">
-        <v>1</v>
-      </c>
-      <c r="G30" s="64">
-        <v>1</v>
+      <c r="F30" s="46">
+        <v>0.35</v>
+      </c>
+      <c r="G30" s="46">
+        <v>0.98</v>
       </c>
       <c r="H30" s="43">
-        <v>100</v>
-      </c>
-      <c r="I30" s="64">
-        <v>0</v>
+        <v>20</v>
+      </c>
+      <c r="I30" s="112">
+        <v>3242</v>
       </c>
       <c r="J30" s="64">
-        <v>0</v>
+        <v>129.68</v>
       </c>
       <c r="K30" s="64">
         <v>0</v>
       </c>
       <c r="L30" s="64">
-        <v>0</v>
-      </c>
-      <c r="M30" s="68"/>
-      <c r="N30" s="68"/>
+        <v>8.76</v>
+      </c>
+      <c r="M30" s="67"/>
+      <c r="N30" s="67"/>
       <c r="O30" s="64"/>
       <c r="P30" s="64"/>
       <c r="Q30" s="64"/>
-      <c r="R30" s="68"/>
+      <c r="R30" s="67"/>
       <c r="S30" s="43"/>
-      <c r="V30" s="45"/>
-      <c r="W30" s="45"/>
-      <c r="X30" s="45"/>
-      <c r="Y30" s="45"/>
-      <c r="Z30" s="45"/>
-      <c r="AA30" s="45"/>
-      <c r="AB30" s="45"/>
-      <c r="AC30" s="45"/>
-      <c r="AD30" s="45"/>
-      <c r="AI30"/>
-      <c r="AJ30"/>
-      <c r="AK30" s="77"/>
-      <c r="AL30" s="77"/>
-      <c r="AM30" s="77"/>
-      <c r="AN30" s="77"/>
-      <c r="AO30" s="77"/>
-      <c r="AP30" s="77"/>
-      <c r="AQ30" s="77"/>
-      <c r="AR30" s="77"/>
-      <c r="AS30" s="77"/>
-      <c r="AT30" s="77"/>
-      <c r="AU30" s="77"/>
-      <c r="AV30" s="77"/>
-      <c r="AW30" s="77"/>
-    </row>
-    <row r="31" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="50" t="str">
-        <f>X17</f>
-        <v>Furnace</v>
-      </c>
-      <c r="C31" s="50" t="str">
+      <c r="V30" s="106" t="s">
+        <v>139</v>
+      </c>
+      <c r="W30" s="106"/>
+      <c r="X30" s="106" t="s">
+        <v>164</v>
+      </c>
+      <c r="Y30" s="106" t="s">
+        <v>165</v>
+      </c>
+      <c r="Z30" s="106" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA30" s="106" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB30" s="104" t="s">
+        <v>88</v>
+      </c>
+      <c r="AC30" s="106"/>
+      <c r="AI30" s="38"/>
+      <c r="AJ30" s="38"/>
+      <c r="AK30" s="45"/>
+      <c r="AL30" s="45"/>
+      <c r="AM30" s="45"/>
+      <c r="AN30" s="45"/>
+      <c r="AO30" s="45"/>
+      <c r="AP30" s="45"/>
+      <c r="AQ30" s="45"/>
+      <c r="AR30" s="45"/>
+      <c r="AS30" s="45"/>
+      <c r="AT30" s="45"/>
+      <c r="AU30" s="45"/>
+      <c r="AV30" s="45"/>
+      <c r="AW30" s="45"/>
+    </row>
+    <row r="31" spans="2:51" s="104" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="102" t="str">
+        <f>X27</f>
+        <v>DECPOWER</v>
+      </c>
+      <c r="C31" s="106" t="s">
+        <v>135</v>
+      </c>
+      <c r="D31" s="102" t="str">
         <f>X10</f>
-        <v>RENELC</v>
-      </c>
-      <c r="D31" s="84" t="s">
-        <v>107</v>
-      </c>
-      <c r="E31" s="43">
+        <v>DECELC</v>
+      </c>
+      <c r="E31" s="103">
         <v>2030</v>
       </c>
-      <c r="F31" s="83">
+      <c r="F31" s="105">
         <v>1</v>
       </c>
-      <c r="G31" s="64">
+      <c r="G31" s="105">
         <v>1</v>
       </c>
-      <c r="H31" s="46">
+      <c r="H31" s="104">
         <v>100</v>
       </c>
-      <c r="I31" s="46">
+      <c r="I31" s="104">
         <v>0</v>
       </c>
-      <c r="J31" s="46">
+      <c r="J31" s="104">
         <v>0</v>
       </c>
-      <c r="K31" s="46">
+      <c r="K31" s="104">
         <v>0</v>
       </c>
-      <c r="L31" s="46">
+      <c r="L31" s="104">
         <v>0</v>
       </c>
-      <c r="M31" s="68"/>
-      <c r="N31" s="68"/>
-      <c r="O31" s="64"/>
-      <c r="P31" s="64"/>
-      <c r="Q31" s="64"/>
-      <c r="R31" s="68"/>
-      <c r="S31" s="43"/>
+      <c r="M31" s="107"/>
+      <c r="N31" s="107"/>
+      <c r="O31" s="105"/>
+      <c r="P31" s="105"/>
+      <c r="Q31" s="105"/>
+      <c r="R31" s="107"/>
+      <c r="S31" s="103"/>
       <c r="V31" s="45"/>
       <c r="W31" s="45"/>
       <c r="X31" s="45"/>
@@ -5638,65 +5619,66 @@
       <c r="AA31" s="45"/>
       <c r="AB31" s="45"/>
       <c r="AC31" s="45"/>
-      <c r="AD31" s="45"/>
-      <c r="AI31"/>
-      <c r="AJ31"/>
-      <c r="AK31" s="45"/>
-      <c r="AL31" s="45"/>
-      <c r="AM31" s="45"/>
-      <c r="AN31" s="45"/>
-      <c r="AO31" s="45"/>
-      <c r="AP31" s="45"/>
-      <c r="AQ31" s="45"/>
-      <c r="AR31" s="45"/>
-      <c r="AS31" s="45"/>
-      <c r="AT31" s="45"/>
-      <c r="AU31" s="45"/>
-      <c r="AV31" s="45"/>
-      <c r="AW31" s="45"/>
+      <c r="AD31" s="106"/>
+      <c r="AI31" s="111"/>
+      <c r="AJ31" s="111"/>
+      <c r="AK31" s="106"/>
+      <c r="AL31" s="106"/>
+      <c r="AM31" s="106"/>
+      <c r="AN31" s="106"/>
+      <c r="AO31" s="106"/>
+      <c r="AP31" s="106"/>
+      <c r="AQ31" s="106"/>
+      <c r="AR31" s="106"/>
+      <c r="AS31" s="106"/>
+      <c r="AT31" s="106"/>
+      <c r="AU31" s="106"/>
+      <c r="AV31" s="106"/>
+      <c r="AW31" s="106"/>
     </row>
     <row r="32" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B32" s="50" t="str">
-        <f>X21</f>
-        <v>ELCBoiler</v>
+        <f>X19</f>
+        <v>Furnace</v>
       </c>
       <c r="C32" s="50" t="str">
         <f>X10</f>
-        <v>RENELC</v>
-      </c>
-      <c r="D32" s="50" t="s">
-        <v>107</v>
+        <v>DECELC</v>
+      </c>
+      <c r="D32" s="83" t="str">
+        <f>X9</f>
+        <v>DECHEAT</v>
       </c>
       <c r="E32" s="43">
         <v>2030</v>
       </c>
-      <c r="F32" s="64">
+      <c r="F32" s="82">
         <v>1</v>
       </c>
       <c r="G32" s="64">
         <v>1</v>
       </c>
-      <c r="H32" s="43">
+      <c r="H32" s="46">
         <v>100</v>
       </c>
-      <c r="I32" s="64">
+      <c r="I32" s="46">
         <v>0</v>
       </c>
-      <c r="J32" s="64">
+      <c r="J32" s="46">
         <v>0</v>
       </c>
-      <c r="K32" s="64">
+      <c r="K32" s="46">
         <v>0</v>
       </c>
-      <c r="L32" s="64">
+      <c r="L32" s="46">
         <v>0</v>
       </c>
-      <c r="M32" s="68"/>
-      <c r="N32" s="68"/>
+      <c r="M32" s="67"/>
+      <c r="N32" s="67"/>
       <c r="O32" s="64"/>
       <c r="P32" s="64"/>
       <c r="Q32" s="64"/>
-      <c r="R32" s="68"/>
+      <c r="R32" s="67"/>
       <c r="S32" s="43"/>
       <c r="V32" s="38"/>
       <c r="W32" s="38"/>
@@ -5709,58 +5691,63 @@
       <c r="AD32" s="45"/>
       <c r="AI32"/>
       <c r="AJ32"/>
-      <c r="AK32" s="39"/>
-      <c r="AL32" s="39"/>
+      <c r="AK32" s="45"/>
+      <c r="AL32" s="45"/>
       <c r="AM32" s="45"/>
       <c r="AN32" s="45"/>
       <c r="AO32" s="45"/>
-      <c r="AQ32"/>
-      <c r="AR32"/>
-      <c r="AS32" s="39"/>
-      <c r="AT32" s="39"/>
+      <c r="AP32" s="45"/>
+      <c r="AQ32" s="45"/>
+      <c r="AR32" s="45"/>
+      <c r="AS32" s="45"/>
+      <c r="AT32" s="45"/>
       <c r="AU32" s="45"/>
       <c r="AV32" s="45"/>
+      <c r="AW32" s="45"/>
     </row>
     <row r="33" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="C33" s="50" t="s">
-        <v>156</v>
-      </c>
-      <c r="D33" s="50" t="s">
-        <v>159</v>
+      <c r="B33" s="50" t="str">
+        <f>X23</f>
+        <v>ELCBoiler</v>
+      </c>
+      <c r="C33" s="50" t="str">
+        <f>X10</f>
+        <v>DECELC</v>
+      </c>
+      <c r="D33" s="83" t="str">
+        <f>X9</f>
+        <v>DECHEAT</v>
       </c>
       <c r="E33" s="43">
         <v>2030</v>
       </c>
-      <c r="F33" s="83">
+      <c r="F33" s="64">
         <v>1</v>
       </c>
       <c r="G33" s="64">
         <v>1</v>
       </c>
-      <c r="H33" s="46">
+      <c r="H33" s="43">
         <v>100</v>
       </c>
-      <c r="I33" s="46">
+      <c r="I33" s="64">
         <v>0</v>
       </c>
-      <c r="J33" s="46">
+      <c r="J33" s="64">
         <v>0</v>
       </c>
-      <c r="K33" s="46">
+      <c r="K33" s="64">
         <v>0</v>
       </c>
-      <c r="L33" s="46">
+      <c r="L33" s="64">
         <v>0</v>
       </c>
-      <c r="M33" s="43"/>
-      <c r="N33" s="68"/>
-      <c r="O33" s="43"/>
-      <c r="P33" s="43"/>
-      <c r="Q33" s="43"/>
-      <c r="R33" s="43"/>
+      <c r="M33" s="67"/>
+      <c r="N33" s="67"/>
+      <c r="O33" s="64"/>
+      <c r="P33" s="64"/>
+      <c r="Q33" s="64"/>
+      <c r="R33" s="67"/>
       <c r="S33" s="43"/>
       <c r="V33" s="38"/>
       <c r="W33" s="38"/>
@@ -5786,13 +5773,47 @@
       <c r="AV33" s="45"/>
     </row>
     <row r="34" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="45"/>
-      <c r="C34" s="50"/>
-      <c r="D34" s="50"/>
-      <c r="E34" s="64"/>
-      <c r="F34" s="65"/>
-      <c r="K34" s="45"/>
-      <c r="N34" s="65"/>
+      <c r="B34" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="C34" s="50" t="str">
+        <f>X10</f>
+        <v>DECELC</v>
+      </c>
+      <c r="D34" s="50" t="s">
+        <v>156</v>
+      </c>
+      <c r="E34" s="43">
+        <v>2030</v>
+      </c>
+      <c r="F34" s="82">
+        <v>1</v>
+      </c>
+      <c r="G34" s="64">
+        <v>1</v>
+      </c>
+      <c r="H34" s="46">
+        <v>100</v>
+      </c>
+      <c r="I34" s="46">
+        <v>0</v>
+      </c>
+      <c r="J34" s="46">
+        <v>0</v>
+      </c>
+      <c r="K34" s="46">
+        <v>0</v>
+      </c>
+      <c r="L34" s="46">
+        <v>0</v>
+      </c>
+      <c r="M34" s="43"/>
+      <c r="N34" s="67"/>
+      <c r="O34" s="43"/>
+      <c r="P34" s="43"/>
+      <c r="Q34" s="43"/>
+      <c r="R34" s="43"/>
+      <c r="S34" s="43"/>
       <c r="V34" s="45"/>
       <c r="W34" s="45"/>
       <c r="X34" s="45"/>
@@ -5817,13 +5838,41 @@
       <c r="AV34" s="45"/>
     </row>
     <row r="35" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="50"/>
-      <c r="C35" s="50"/>
-      <c r="D35" s="50"/>
-      <c r="E35" s="64"/>
-      <c r="F35" s="65"/>
-      <c r="J35" s="66"/>
-      <c r="K35" s="45"/>
+      <c r="B35" s="45" t="str">
+        <f>X30</f>
+        <v>GTHT</v>
+      </c>
+      <c r="C35" s="50" t="str">
+        <f>X12</f>
+        <v>GHEAT</v>
+      </c>
+      <c r="D35" s="50" t="s">
+        <v>107</v>
+      </c>
+      <c r="E35" s="43">
+        <v>2030</v>
+      </c>
+      <c r="F35" s="64">
+        <v>1</v>
+      </c>
+      <c r="G35" s="64">
+        <v>1</v>
+      </c>
+      <c r="H35" s="43">
+        <v>100</v>
+      </c>
+      <c r="I35" s="64">
+        <v>0</v>
+      </c>
+      <c r="J35" s="64">
+        <v>0</v>
+      </c>
+      <c r="K35" s="64">
+        <v>0</v>
+      </c>
+      <c r="L35" s="64">
+        <v>0</v>
+      </c>
       <c r="N35" s="65"/>
       <c r="V35" s="45"/>
       <c r="X35" s="45"/>
@@ -5847,16 +5896,42 @@
       <c r="AV35" s="45"/>
     </row>
     <row r="36" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="50"/>
-      <c r="C36" s="45"/>
-      <c r="D36" s="50"/>
-      <c r="E36" s="64"/>
-      <c r="F36" s="67"/>
-      <c r="G36" s="45"/>
-      <c r="H36" s="45"/>
-      <c r="I36" s="45"/>
-      <c r="J36" s="68"/>
-      <c r="K36" s="45"/>
+      <c r="B36" s="45" t="str">
+        <f>X29</f>
+        <v>RNWTHT</v>
+      </c>
+      <c r="C36" s="50" t="str">
+        <f>X12</f>
+        <v>GHEAT</v>
+      </c>
+      <c r="D36" s="50" t="s">
+        <v>107</v>
+      </c>
+      <c r="E36" s="43">
+        <v>2030</v>
+      </c>
+      <c r="F36" s="64">
+        <v>1</v>
+      </c>
+      <c r="G36" s="64">
+        <v>1</v>
+      </c>
+      <c r="H36" s="43">
+        <v>100</v>
+      </c>
+      <c r="I36" s="64">
+        <v>0</v>
+      </c>
+      <c r="J36" s="64">
+        <v>0</v>
+      </c>
+      <c r="K36" s="64">
+        <v>0</v>
+      </c>
+      <c r="L36" s="64">
+        <v>0</v>
+      </c>
+      <c r="N36" s="65"/>
       <c r="V36" s="45"/>
       <c r="W36" s="45"/>
       <c r="X36" s="45"/>
@@ -5866,7 +5941,6 @@
       <c r="AB36" s="45"/>
       <c r="AC36" s="45"/>
       <c r="AD36" s="45"/>
-      <c r="AE36" s="45"/>
       <c r="AI36"/>
       <c r="AJ36"/>
       <c r="AK36" s="39"/>
@@ -5882,15 +5956,24 @@
       <c r="AV36" s="45"/>
     </row>
     <row r="37" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="45"/>
-      <c r="C37" s="45"/>
-      <c r="D37" s="45"/>
+      <c r="B37" s="50" t="str">
+        <f>X29</f>
+        <v>RNWTHT</v>
+      </c>
+      <c r="C37" s="50" t="str">
+        <f>X9</f>
+        <v>DECHEAT</v>
+      </c>
+      <c r="D37" s="50" t="str">
+        <f>X11</f>
+        <v>RNWHEAT</v>
+      </c>
       <c r="E37" s="64"/>
-      <c r="F37" s="67"/>
+      <c r="F37" s="66"/>
       <c r="G37" s="45"/>
       <c r="H37" s="45"/>
       <c r="I37" s="45"/>
-      <c r="J37" s="68"/>
+      <c r="J37" s="67"/>
       <c r="K37" s="45"/>
       <c r="V37" s="45"/>
       <c r="W37" s="45"/>
@@ -5916,31 +5999,46 @@
       <c r="AU37" s="45"/>
       <c r="AV37" s="45"/>
     </row>
-    <row r="38" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A38" s="46"/>
-      <c r="F38" s="67"/>
-      <c r="G38" s="43"/>
-      <c r="H38" s="69"/>
-      <c r="M38" s="46"/>
-      <c r="N38" s="46"/>
-      <c r="O38" s="46"/>
-      <c r="P38" s="46"/>
-      <c r="Q38" s="46"/>
-      <c r="R38" s="46"/>
-      <c r="S38" s="46"/>
+    <row r="38" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="45"/>
+      <c r="C38" s="45"/>
+      <c r="D38" s="45"/>
+      <c r="E38" s="64"/>
+      <c r="F38" s="66"/>
+      <c r="G38" s="45"/>
+      <c r="H38" s="45"/>
+      <c r="I38" s="45"/>
+      <c r="J38" s="67"/>
+      <c r="K38" s="45"/>
+      <c r="V38" s="45"/>
+      <c r="W38" s="45"/>
+      <c r="X38" s="45"/>
+      <c r="Y38" s="45"/>
+      <c r="Z38" s="45"/>
+      <c r="AA38" s="45"/>
+      <c r="AB38" s="45"/>
+      <c r="AC38" s="45"/>
+      <c r="AD38" s="45"/>
+      <c r="AE38" s="45"/>
       <c r="AI38"/>
       <c r="AJ38"/>
       <c r="AK38" s="39"/>
       <c r="AL38" s="39"/>
-      <c r="AP38" s="46"/>
+      <c r="AM38" s="45"/>
+      <c r="AN38" s="45"/>
+      <c r="AO38" s="45"/>
       <c r="AQ38"/>
       <c r="AR38"/>
       <c r="AS38" s="39"/>
       <c r="AT38" s="39"/>
+      <c r="AU38" s="45"/>
+      <c r="AV38" s="45"/>
     </row>
     <row r="39" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A39" s="46"/>
-      <c r="H39" s="69"/>
+      <c r="F39" s="66"/>
+      <c r="G39" s="43"/>
+      <c r="H39" s="68"/>
       <c r="M39" s="46"/>
       <c r="N39" s="46"/>
       <c r="O39" s="46"/>
@@ -5959,26 +6057,31 @@
       <c r="AT39" s="39"/>
     </row>
     <row r="40" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="B40" s="70"/>
-      <c r="C40" s="45" t="s">
-        <v>82</v>
-      </c>
-      <c r="H40" s="69"/>
+      <c r="A40" s="46"/>
+      <c r="H40" s="68"/>
+      <c r="M40" s="46"/>
+      <c r="N40" s="46"/>
+      <c r="O40" s="46"/>
+      <c r="P40" s="46"/>
+      <c r="Q40" s="46"/>
+      <c r="R40" s="46"/>
+      <c r="S40" s="46"/>
       <c r="AI40"/>
       <c r="AJ40"/>
       <c r="AK40" s="39"/>
       <c r="AL40" s="39"/>
+      <c r="AP40" s="46"/>
       <c r="AQ40"/>
       <c r="AR40"/>
       <c r="AS40" s="39"/>
       <c r="AT40" s="39"/>
     </row>
     <row r="41" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="B41" s="71"/>
+      <c r="B41" s="69"/>
       <c r="C41" s="45" t="s">
-        <v>83</v>
-      </c>
-      <c r="H41" s="69"/>
+        <v>82</v>
+      </c>
+      <c r="H41" s="68"/>
       <c r="AI41"/>
       <c r="AJ41"/>
       <c r="AK41" s="39"/>
@@ -5989,7 +6092,11 @@
       <c r="AT41" s="39"/>
     </row>
     <row r="42" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="H42" s="69"/>
+      <c r="B42" s="70"/>
+      <c r="C42" s="45" t="s">
+        <v>83</v>
+      </c>
+      <c r="H42" s="68"/>
       <c r="AI42"/>
       <c r="AJ42"/>
       <c r="AK42" s="39"/>
@@ -6000,6 +6107,7 @@
       <c r="AT42" s="39"/>
     </row>
     <row r="43" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="H43" s="68"/>
       <c r="AI43"/>
       <c r="AJ43"/>
       <c r="AK43" s="39"/>
@@ -6020,7 +6128,6 @@
       <c r="AT44" s="39"/>
     </row>
     <row r="45" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="E45" s="43"/>
       <c r="AI45"/>
       <c r="AJ45"/>
       <c r="AK45" s="39"/>
@@ -6031,6 +6138,7 @@
       <c r="AT45" s="39"/>
     </row>
     <row r="46" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="E46" s="43"/>
       <c r="AI46"/>
       <c r="AJ46"/>
       <c r="AK46" s="39"/>
@@ -6091,17 +6199,6 @@
       <c r="AT51" s="39"/>
     </row>
     <row r="52" spans="2:46" x14ac:dyDescent="0.25">
-      <c r="B52" s="73"/>
-      <c r="C52" s="73"/>
-      <c r="D52"/>
-      <c r="E52"/>
-      <c r="F52"/>
-      <c r="G52"/>
-      <c r="H52"/>
-      <c r="I52"/>
-      <c r="J52"/>
-      <c r="K52"/>
-      <c r="L52"/>
       <c r="AI52"/>
       <c r="AJ52"/>
       <c r="AK52" s="39"/>
@@ -6111,18 +6208,18 @@
       <c r="AS52" s="39"/>
       <c r="AT52" s="39"/>
     </row>
-    <row r="53" spans="2:46" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B53" s="74"/>
-      <c r="C53" s="74"/>
-      <c r="D53" s="74"/>
-      <c r="E53" s="74"/>
-      <c r="F53" s="74"/>
-      <c r="G53" s="74"/>
-      <c r="H53" s="74"/>
-      <c r="I53" s="74"/>
-      <c r="J53" s="74"/>
-      <c r="K53" s="74"/>
-      <c r="L53" s="74"/>
+    <row r="53" spans="2:46" x14ac:dyDescent="0.25">
+      <c r="B53" s="72"/>
+      <c r="C53" s="72"/>
+      <c r="D53"/>
+      <c r="E53"/>
+      <c r="F53"/>
+      <c r="G53"/>
+      <c r="H53"/>
+      <c r="I53"/>
+      <c r="J53"/>
+      <c r="K53"/>
+      <c r="L53"/>
       <c r="AI53"/>
       <c r="AJ53"/>
       <c r="AK53" s="39"/>
@@ -6132,18 +6229,18 @@
       <c r="AS53" s="39"/>
       <c r="AT53" s="39"/>
     </row>
-    <row r="54" spans="2:46" x14ac:dyDescent="0.25">
-      <c r="B54"/>
-      <c r="C54"/>
-      <c r="D54"/>
-      <c r="E54" s="1"/>
-      <c r="F54"/>
-      <c r="G54"/>
-      <c r="H54"/>
-      <c r="I54"/>
-      <c r="J54"/>
-      <c r="K54"/>
-      <c r="L54"/>
+    <row r="54" spans="2:46" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B54" s="73"/>
+      <c r="C54" s="73"/>
+      <c r="D54" s="73"/>
+      <c r="E54" s="73"/>
+      <c r="F54" s="73"/>
+      <c r="G54" s="73"/>
+      <c r="H54" s="73"/>
+      <c r="I54" s="73"/>
+      <c r="J54" s="73"/>
+      <c r="K54" s="73"/>
+      <c r="L54" s="73"/>
       <c r="AI54"/>
       <c r="AJ54"/>
       <c r="AK54" s="39"/>
@@ -6301,6 +6398,17 @@
       <c r="AT61" s="39"/>
     </row>
     <row r="62" spans="2:46" x14ac:dyDescent="0.25">
+      <c r="B62"/>
+      <c r="C62"/>
+      <c r="D62"/>
+      <c r="E62" s="1"/>
+      <c r="F62"/>
+      <c r="G62"/>
+      <c r="H62"/>
+      <c r="I62"/>
+      <c r="J62"/>
+      <c r="K62"/>
+      <c r="L62"/>
       <c r="AI62"/>
       <c r="AJ62"/>
       <c r="AK62" s="39"/>
@@ -6339,7 +6447,6 @@
       <c r="AA65" s="46"/>
       <c r="AB65" s="46"/>
       <c r="AC65" s="46"/>
-      <c r="AD65" s="46"/>
       <c r="AI65"/>
       <c r="AJ65"/>
       <c r="AK65" s="39"/>
@@ -6359,7 +6466,6 @@
       <c r="AB66" s="46"/>
       <c r="AC66" s="46"/>
       <c r="AD66" s="46"/>
-      <c r="AE66" s="46"/>
       <c r="AI66"/>
       <c r="AJ66"/>
       <c r="AK66" s="39"/>
@@ -6370,16 +6476,6 @@
       <c r="AT66" s="39"/>
     </row>
     <row r="67" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="B67"/>
-      <c r="C67"/>
-      <c r="E67" s="73"/>
-      <c r="F67" s="73"/>
-      <c r="G67" s="1"/>
-      <c r="H67"/>
-      <c r="I67" s="73"/>
-      <c r="J67"/>
-      <c r="K67"/>
-      <c r="L67" s="73"/>
       <c r="V67" s="46"/>
       <c r="W67" s="46"/>
       <c r="X67" s="46"/>
@@ -6399,64 +6495,44 @@
       <c r="AS67" s="39"/>
       <c r="AT67" s="39"/>
     </row>
-    <row r="68" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="45"/>
-      <c r="B68" s="79"/>
-      <c r="C68" s="79"/>
-      <c r="D68" s="79"/>
-      <c r="E68" s="79"/>
-      <c r="F68" s="79"/>
-      <c r="G68" s="79"/>
-      <c r="H68" s="80"/>
-      <c r="I68" s="79"/>
-      <c r="J68" s="79"/>
-      <c r="K68" s="79"/>
-      <c r="L68" s="79"/>
-      <c r="M68" s="45"/>
-      <c r="N68" s="45"/>
-      <c r="O68" s="45"/>
-      <c r="P68" s="45"/>
-      <c r="Q68" s="45"/>
-      <c r="R68" s="45"/>
-      <c r="S68" s="45"/>
-      <c r="V68" s="45"/>
-      <c r="W68" s="45"/>
-      <c r="X68" s="45"/>
-      <c r="Y68" s="45"/>
-      <c r="Z68" s="45"/>
-      <c r="AA68" s="45"/>
-      <c r="AB68" s="45"/>
-      <c r="AC68" s="45"/>
-      <c r="AD68" s="45"/>
+    <row r="68" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="B68"/>
+      <c r="C68"/>
+      <c r="E68" s="72"/>
+      <c r="F68" s="72"/>
+      <c r="G68" s="1"/>
+      <c r="H68"/>
+      <c r="I68" s="72"/>
+      <c r="J68"/>
+      <c r="K68"/>
+      <c r="L68" s="72"/>
+      <c r="AD68" s="46"/>
+      <c r="AE68" s="46"/>
       <c r="AI68"/>
-      <c r="AJ68" s="80"/>
+      <c r="AJ68"/>
       <c r="AK68" s="39"/>
-      <c r="AL68" s="41"/>
-      <c r="AM68" s="45"/>
-      <c r="AN68" s="45"/>
+      <c r="AL68" s="39"/>
       <c r="AQ68"/>
-      <c r="AR68" s="80"/>
+      <c r="AR68"/>
       <c r="AS68" s="39"/>
-      <c r="AT68" s="41"/>
-      <c r="AU68" s="45"/>
-      <c r="AV68" s="45"/>
+      <c r="AT68" s="39"/>
     </row>
     <row r="69" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="73"/>
-      <c r="B69" s="81"/>
-      <c r="C69" s="82"/>
-      <c r="D69" s="81"/>
-      <c r="E69" s="81"/>
-      <c r="F69" s="81"/>
-      <c r="G69" s="81"/>
-      <c r="H69" s="80"/>
-      <c r="I69" s="81"/>
-      <c r="J69" s="81"/>
-      <c r="K69" s="82"/>
-      <c r="L69" s="82"/>
-      <c r="M69" s="73"/>
-      <c r="N69" s="73"/>
-      <c r="O69" s="1"/>
+      <c r="A69" s="45"/>
+      <c r="B69" s="78"/>
+      <c r="C69" s="78"/>
+      <c r="D69" s="78"/>
+      <c r="E69" s="78"/>
+      <c r="F69" s="78"/>
+      <c r="G69" s="78"/>
+      <c r="H69" s="79"/>
+      <c r="I69" s="78"/>
+      <c r="J69" s="78"/>
+      <c r="K69" s="78"/>
+      <c r="L69" s="78"/>
+      <c r="M69" s="45"/>
+      <c r="N69" s="45"/>
+      <c r="O69" s="45"/>
       <c r="P69" s="45"/>
       <c r="Q69" s="45"/>
       <c r="R69" s="45"/>
@@ -6470,27 +6546,39 @@
       <c r="AB69" s="45"/>
       <c r="AC69" s="45"/>
       <c r="AD69" s="45"/>
-      <c r="AE69" s="45"/>
-      <c r="AI69" s="42"/>
-      <c r="AJ69" s="42"/>
-      <c r="AK69" s="54"/>
+      <c r="AI69"/>
+      <c r="AJ69" s="79"/>
+      <c r="AK69" s="39"/>
+      <c r="AL69" s="41"/>
+      <c r="AM69" s="45"/>
+      <c r="AN69" s="45"/>
+      <c r="AQ69"/>
+      <c r="AR69" s="79"/>
+      <c r="AS69" s="39"/>
+      <c r="AT69" s="41"/>
+      <c r="AU69" s="45"/>
+      <c r="AV69" s="45"/>
     </row>
     <row r="70" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="79"/>
-      <c r="B70" s="81"/>
+      <c r="A70" s="72"/>
+      <c r="B70" s="80"/>
       <c r="C70" s="81"/>
-      <c r="D70" s="81"/>
-      <c r="E70" s="81"/>
-      <c r="F70" s="81"/>
-      <c r="G70" s="81"/>
-      <c r="H70" s="80"/>
-      <c r="I70" s="81"/>
-      <c r="J70" s="81"/>
+      <c r="D70" s="80"/>
+      <c r="E70" s="80"/>
+      <c r="F70" s="80"/>
+      <c r="G70" s="80"/>
+      <c r="H70" s="79"/>
+      <c r="I70" s="80"/>
+      <c r="J70" s="80"/>
       <c r="K70" s="81"/>
       <c r="L70" s="81"/>
-      <c r="M70" s="79"/>
-      <c r="N70" s="79"/>
-      <c r="O70" s="79"/>
+      <c r="M70" s="72"/>
+      <c r="N70" s="72"/>
+      <c r="O70" s="1"/>
+      <c r="P70" s="45"/>
+      <c r="Q70" s="45"/>
+      <c r="R70" s="45"/>
+      <c r="S70" s="45"/>
       <c r="V70" s="45"/>
       <c r="W70" s="45"/>
       <c r="X70" s="45"/>
@@ -6505,40 +6593,49 @@
       <c r="AJ70" s="42"/>
       <c r="AK70" s="54"/>
     </row>
-    <row r="71" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A71" s="81"/>
-      <c r="B71"/>
-      <c r="C71" s="39"/>
-      <c r="D71" s="39"/>
-      <c r="H71"/>
-      <c r="I71"/>
-      <c r="J71"/>
-      <c r="K71" s="39"/>
-      <c r="L71" s="39"/>
-      <c r="M71" s="82"/>
-      <c r="N71" s="82"/>
-      <c r="O71" s="81"/>
-      <c r="P71" s="46"/>
-      <c r="Q71" s="46"/>
-      <c r="R71" s="46"/>
-      <c r="S71" s="46"/>
-      <c r="AI71" s="38"/>
-      <c r="AJ71" s="38"/>
-      <c r="AK71" s="50"/>
+    <row r="71" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="78"/>
+      <c r="B71" s="80"/>
+      <c r="C71" s="80"/>
+      <c r="D71" s="80"/>
+      <c r="E71" s="80"/>
+      <c r="F71" s="80"/>
+      <c r="G71" s="80"/>
+      <c r="H71" s="79"/>
+      <c r="I71" s="80"/>
+      <c r="J71" s="80"/>
+      <c r="K71" s="80"/>
+      <c r="L71" s="80"/>
+      <c r="M71" s="78"/>
+      <c r="N71" s="78"/>
+      <c r="O71" s="78"/>
+      <c r="V71" s="45"/>
+      <c r="W71" s="45"/>
+      <c r="X71" s="45"/>
+      <c r="Y71" s="45"/>
+      <c r="Z71" s="45"/>
+      <c r="AA71" s="45"/>
+      <c r="AB71" s="45"/>
+      <c r="AC71" s="45"/>
+      <c r="AD71" s="45"/>
+      <c r="AE71" s="45"/>
+      <c r="AI71" s="42"/>
+      <c r="AJ71" s="42"/>
+      <c r="AK71" s="54"/>
     </row>
     <row r="72" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A72" s="81"/>
+      <c r="A72" s="80"/>
       <c r="B72"/>
       <c r="C72" s="39"/>
       <c r="D72" s="39"/>
-      <c r="H72" s="78"/>
+      <c r="H72"/>
       <c r="I72"/>
       <c r="J72"/>
       <c r="K72" s="39"/>
       <c r="L72" s="39"/>
       <c r="M72" s="81"/>
       <c r="N72" s="81"/>
-      <c r="O72" s="81"/>
+      <c r="O72" s="80"/>
       <c r="P72" s="46"/>
       <c r="Q72" s="46"/>
       <c r="R72" s="46"/>
@@ -6548,14 +6645,22 @@
       <c r="AK72" s="50"/>
     </row>
     <row r="73" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A73"/>
+      <c r="A73" s="80"/>
       <c r="B73"/>
       <c r="C73" s="39"/>
       <c r="D73" s="39"/>
+      <c r="H73" s="77"/>
       <c r="I73"/>
       <c r="J73"/>
       <c r="K73" s="39"/>
       <c r="L73" s="39"/>
+      <c r="M73" s="80"/>
+      <c r="N73" s="80"/>
+      <c r="O73" s="80"/>
+      <c r="P73" s="46"/>
+      <c r="Q73" s="46"/>
+      <c r="R73" s="46"/>
+      <c r="S73" s="46"/>
       <c r="AI73" s="38"/>
       <c r="AJ73" s="38"/>
       <c r="AK73" s="50"/>
@@ -6578,12 +6683,10 @@
       <c r="B75"/>
       <c r="C75" s="39"/>
       <c r="D75" s="39"/>
-      <c r="H75" s="46"/>
       <c r="I75"/>
       <c r="J75"/>
       <c r="K75" s="39"/>
       <c r="L75" s="39"/>
-      <c r="O75" s="46"/>
       <c r="AI75" s="38"/>
       <c r="AJ75" s="38"/>
       <c r="AK75" s="50"/>
@@ -6803,10 +6906,12 @@
       <c r="B90"/>
       <c r="C90" s="39"/>
       <c r="D90" s="39"/>
+      <c r="H90" s="46"/>
       <c r="I90"/>
       <c r="J90"/>
       <c r="K90" s="39"/>
       <c r="L90" s="39"/>
+      <c r="O90" s="46"/>
       <c r="AI90" s="38"/>
       <c r="AJ90" s="38"/>
       <c r="AK90" s="50"/>
@@ -7177,6 +7282,13 @@
     </row>
     <row r="119" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A119"/>
+      <c r="B119"/>
+      <c r="C119" s="39"/>
+      <c r="D119" s="39"/>
+      <c r="I119"/>
+      <c r="J119"/>
+      <c r="K119" s="39"/>
+      <c r="L119" s="39"/>
       <c r="AI119" s="38"/>
       <c r="AJ119" s="38"/>
       <c r="AK119" s="50"/>
@@ -7188,6 +7300,7 @@
       <c r="AK120" s="50"/>
     </row>
     <row r="121" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A121"/>
       <c r="AI121" s="38"/>
       <c r="AJ121" s="38"/>
       <c r="AK121" s="50"/>
@@ -7306,6 +7419,11 @@
       <c r="AI144" s="38"/>
       <c r="AJ144" s="38"/>
       <c r="AK144" s="50"/>
+    </row>
+    <row r="145" spans="35:37" x14ac:dyDescent="0.25">
+      <c r="AI145" s="38"/>
+      <c r="AJ145" s="38"/>
+      <c r="AK145" s="50"/>
     </row>
   </sheetData>
   <phoneticPr fontId="24" type="noConversion"/>

--- a/SubRES_TMPL/SubRES_NewTechs.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A55822D4-D0EC-4C0C-8FEB-8C359C53E3FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EB48BC1-051A-48F1-A643-268D386270B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1125,7 +1125,250 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB16" authorId="2" shapeId="0" xr:uid="{5EE58488-723F-4683-9026-2F0EE70F8071}">
+    <comment ref="V18" authorId="2" shapeId="0" xr:uid="{BAA0F8AB-741B-4302-9E54-000CB5DC4ACF}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Sets declarations are </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>inherited. 
+Allowed Process Sets</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+ELE </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>(Thermal Electric Power Plant)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+CHP </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>(Combined Heat and Power)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+STGTSS </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>(Pump Storage)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+STGIPS</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (Pump Storage IP)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+PRE </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>(Genric Process/Technology)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+DMD</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (Demand Device)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+IMP </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">(Import)
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>EXP</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (Export)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+MIN </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>(Mining Process)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+RNW </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>(Renewable Technology)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+HPL</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (Heating Plant)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AB18" authorId="2" shapeId="0" xr:uid="{5EE58488-723F-4683-9026-2F0EE70F8071}">
       <text>
         <r>
           <rPr>
@@ -1218,7 +1461,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC16" authorId="1" shapeId="0" xr:uid="{308E9284-8F99-498B-A3DD-262799AF67EB}">
+    <comment ref="AC18" authorId="1" shapeId="0" xr:uid="{308E9284-8F99-498B-A3DD-262799AF67EB}">
       <text>
         <r>
           <rPr>
@@ -1243,7 +1486,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AD16" authorId="2" shapeId="0" xr:uid="{FD29F772-15B8-47C4-8D7A-88CCF8F71647}">
+    <comment ref="AD18" authorId="2" shapeId="0" xr:uid="{FD29F772-15B8-47C4-8D7A-88CCF8F71647}">
       <text>
         <r>
           <rPr>
@@ -1303,249 +1546,6 @@
           </rPr>
           <t xml:space="preserve">
 YES</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="V17" authorId="2" shapeId="0" xr:uid="{BAA0F8AB-741B-4302-9E54-000CB5DC4ACF}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Sets declarations are </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>inherited. 
-Allowed Process Sets</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-ELE </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>(Thermal Electric Power Plant)</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-CHP </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>(Combined Heat and Power)</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-STGTSS </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>(Pump Storage)</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-STGIPS</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (Pump Storage IP)</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-PRE </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>(Genric Process/Technology)</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-DMD</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (Demand Device)</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-IMP </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">(Import)
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>EXP</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (Export)</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-MIN </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>(Mining Process)</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-RNW </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>(Renewable Technology)</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-HPL</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (Heating Plant)</t>
         </r>
       </text>
     </comment>
@@ -1554,7 +1554,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="170">
   <si>
     <t>~FI_T</t>
   </si>
@@ -1976,12 +1976,6 @@
     <t>HEAT</t>
   </si>
   <si>
-    <t>SOLTHERMAL</t>
-  </si>
-  <si>
-    <t>Process heat from Solar</t>
-  </si>
-  <si>
     <t>Electricity to Manufacturing Process Heat Conversion Technology</t>
   </si>
   <si>
@@ -2015,9 +2009,6 @@
     <t>Renewable Manufacturing Process Heat Aggregator</t>
   </si>
   <si>
-    <t>Process heat from all renewables</t>
-  </si>
-  <si>
     <t>Decentralized Electricity form Solar, Wind and Bio</t>
   </si>
   <si>
@@ -2042,9 +2033,6 @@
     <t>RNWTHT</t>
   </si>
   <si>
-    <t>GHEAT</t>
-  </si>
-  <si>
     <t>Grid electricity-based heat</t>
   </si>
   <si>
@@ -2052,6 +2040,30 @@
   </si>
   <si>
     <t xml:space="preserve">Grid Electricity Based Heat Aggregator </t>
+  </si>
+  <si>
+    <t>GEHEAT</t>
+  </si>
+  <si>
+    <t>DECEHEAT</t>
+  </si>
+  <si>
+    <t>Decentralized Electricity fbased heat</t>
+  </si>
+  <si>
+    <t>Process heat from  renewables-CSP and BIO</t>
+  </si>
+  <si>
+    <t>ELCHEAT</t>
+  </si>
+  <si>
+    <t>Electricity-based process heat</t>
+  </si>
+  <si>
+    <t>ETHT</t>
+  </si>
+  <si>
+    <t>Electricity-based process heat-aggrigator</t>
   </si>
 </sst>
 </file>
@@ -4051,7 +4063,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3360854E-4C4D-467D-BD8A-32231E61C6CE}">
-  <dimension ref="A1:AY145"/>
+  <dimension ref="A1:AY147"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" style="45" customWidth="1"/>
@@ -4070,7 +4082,7 @@
     <col min="20" max="21" width="8.21875" style="46" customWidth="1"/>
     <col min="22" max="22" width="12.77734375" style="45" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="7.21875" style="45" customWidth="1"/>
-    <col min="24" max="24" width="11.44140625" style="45" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.44140625" style="45" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="63.77734375" style="45" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="8.21875" style="45" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="11.77734375" style="45" customWidth="1"/>
@@ -4087,7 +4099,7 @@
     <col min="45" max="16384" width="8.77734375" style="45"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:51" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:49" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B1" s="44" t="s">
         <v>38</v>
       </c>
@@ -4108,7 +4120,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="2:51" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:49" ht="31.2" x14ac:dyDescent="0.3">
       <c r="B2" s="47" t="s">
         <v>92</v>
       </c>
@@ -4141,7 +4153,7 @@
       <c r="AC2" s="50"/>
       <c r="AD2" s="50"/>
     </row>
-    <row r="3" spans="2:51" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:49" x14ac:dyDescent="0.25">
       <c r="V3" s="51" t="s">
         <v>8</v>
       </c>
@@ -4170,7 +4182,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="2:51" ht="22.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:49" ht="22.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="53"/>
       <c r="C4" s="53"/>
       <c r="D4" s="53"/>
@@ -4205,7 +4217,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="2:51" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:49" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B5" s="53"/>
       <c r="C5" s="53"/>
       <c r="D5" s="53"/>
@@ -4228,7 +4240,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="6" spans="2:51" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:49" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B6" s="53"/>
       <c r="C6" s="53"/>
       <c r="D6" s="53"/>
@@ -4251,7 +4263,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="2:51" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:49" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B7" s="53"/>
       <c r="C7" s="53"/>
       <c r="D7" s="53"/>
@@ -4274,15 +4286,16 @@
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="2:51" x14ac:dyDescent="0.25">
-      <c r="V8" s="45" t="s">
+    <row r="8" spans="2:49" x14ac:dyDescent="0.25">
+      <c r="V8" s="50" t="s">
         <v>139</v>
       </c>
-      <c r="X8" s="45" t="s">
-        <v>140</v>
-      </c>
-      <c r="Y8" s="45" t="s">
-        <v>141</v>
+      <c r="W8" s="50"/>
+      <c r="X8" s="50" t="s">
+        <v>154</v>
+      </c>
+      <c r="Y8" s="50" t="s">
+        <v>165</v>
       </c>
       <c r="Z8" s="76" t="s">
         <v>58</v>
@@ -4292,16 +4305,16 @@
       </c>
       <c r="AE8" s="46"/>
     </row>
-    <row r="9" spans="2:51" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:49" x14ac:dyDescent="0.25">
       <c r="V9" s="50" t="s">
-        <v>139</v>
+        <v>69</v>
       </c>
       <c r="W9" s="50"/>
       <c r="X9" s="50" t="s">
-        <v>157</v>
+        <v>129</v>
       </c>
       <c r="Y9" s="50" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="Z9" s="76" t="s">
         <v>58</v>
@@ -4313,16 +4326,15 @@
       <c r="AC9" s="50"/>
       <c r="AD9" s="50"/>
     </row>
-    <row r="10" spans="2:51" x14ac:dyDescent="0.25">
-      <c r="V10" s="50" t="s">
-        <v>69</v>
-      </c>
-      <c r="W10" s="50"/>
-      <c r="X10" s="50" t="s">
-        <v>129</v>
-      </c>
-      <c r="Y10" s="50" t="s">
-        <v>154</v>
+    <row r="10" spans="2:49" x14ac:dyDescent="0.25">
+      <c r="V10" s="45" t="s">
+        <v>139</v>
+      </c>
+      <c r="X10" s="45" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y10" s="45" t="s">
+        <v>157</v>
       </c>
       <c r="Z10" s="76" t="s">
         <v>58</v>
@@ -4334,15 +4346,15 @@
       <c r="AC10" s="50"/>
       <c r="AD10" s="50"/>
     </row>
-    <row r="11" spans="2:51" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:49" x14ac:dyDescent="0.25">
       <c r="V11" s="45" t="s">
         <v>139</v>
       </c>
       <c r="X11" s="45" t="s">
+        <v>162</v>
+      </c>
+      <c r="Y11" s="45" t="s">
         <v>159</v>
-      </c>
-      <c r="Y11" s="45" t="s">
-        <v>160</v>
       </c>
       <c r="Z11" s="76" t="s">
         <v>58</v>
@@ -4351,15 +4363,15 @@
         <v>88</v>
       </c>
     </row>
-    <row r="12" spans="2:51" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:49" x14ac:dyDescent="0.25">
       <c r="V12" s="45" t="s">
         <v>139</v>
       </c>
       <c r="X12" s="45" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Y12" s="45" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Z12" s="76" t="s">
         <v>58</v>
@@ -4368,126 +4380,44 @@
         <v>88</v>
       </c>
     </row>
-    <row r="13" spans="2:51" x14ac:dyDescent="0.25">
-      <c r="Z13" s="76"/>
-      <c r="AB13" s="76"/>
-    </row>
-    <row r="15" spans="2:51" x14ac:dyDescent="0.25">
-      <c r="D15" s="55" t="s">
+    <row r="13" spans="2:49" x14ac:dyDescent="0.25">
+      <c r="V13" s="45" t="s">
+        <v>139</v>
+      </c>
+      <c r="X13" s="45" t="s">
+        <v>166</v>
+      </c>
+      <c r="Y13" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="Z13" s="76" t="s">
+        <v>58</v>
+      </c>
+      <c r="AB13" s="76" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="14" spans="2:49" x14ac:dyDescent="0.25">
+      <c r="Z14" s="76"/>
+      <c r="AB14" s="76"/>
+    </row>
+    <row r="15" spans="2:49" x14ac:dyDescent="0.25">
+      <c r="AB15" s="76"/>
+    </row>
+    <row r="16" spans="2:49" x14ac:dyDescent="0.25">
+      <c r="D16" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="E15" s="55"/>
-      <c r="F15" s="55"/>
-      <c r="H15" s="55"/>
-      <c r="V15" s="49" t="s">
+      <c r="E16" s="55"/>
+      <c r="F16" s="55"/>
+      <c r="H16" s="55"/>
+      <c r="V16" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="W15" s="49"/>
-      <c r="X15" s="50"/>
-      <c r="Y15" s="50"/>
-      <c r="Z15" s="50"/>
-      <c r="AA15" s="50"/>
-      <c r="AB15" s="50"/>
-      <c r="AC15" s="50"/>
-      <c r="AD15" s="50"/>
-      <c r="AI15"/>
-      <c r="AJ15" s="39"/>
-      <c r="AK15" s="76"/>
-      <c r="AL15" s="76"/>
-      <c r="AM15" s="76"/>
-      <c r="AN15" s="76"/>
-      <c r="AO15" s="76"/>
-      <c r="AP15" s="76"/>
-      <c r="AQ15" s="76"/>
-      <c r="AR15" s="76"/>
-      <c r="AS15" s="76"/>
-      <c r="AT15" s="76"/>
-      <c r="AU15" s="76"/>
-      <c r="AV15" s="76"/>
-      <c r="AW15" s="76"/>
-    </row>
-    <row r="16" spans="2:51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="56" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="56" t="s">
-        <v>4</v>
-      </c>
-      <c r="E16" s="57" t="s">
-        <v>113</v>
-      </c>
-      <c r="F16" s="57" t="s">
-        <v>16</v>
-      </c>
-      <c r="G16" s="57" t="s">
-        <v>34</v>
-      </c>
-      <c r="H16" s="57" t="s">
-        <v>47</v>
-      </c>
-      <c r="I16" s="57" t="s">
-        <v>36</v>
-      </c>
-      <c r="J16" s="59" t="s">
-        <v>5</v>
-      </c>
-      <c r="K16" s="59" t="s">
-        <v>98</v>
-      </c>
-      <c r="L16" s="57" t="s">
-        <v>56</v>
-      </c>
-      <c r="M16" s="59" t="s">
-        <v>103</v>
-      </c>
-      <c r="N16" s="58" t="s">
-        <v>112</v>
-      </c>
-      <c r="O16" s="59" t="s">
-        <v>115</v>
-      </c>
-      <c r="P16" s="59" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q16" s="59" t="s">
-        <v>117</v>
-      </c>
-      <c r="R16" s="59" t="s">
-        <v>118</v>
-      </c>
-      <c r="S16" s="59" t="s">
-        <v>126</v>
-      </c>
-      <c r="V16" s="51" t="s">
-        <v>15</v>
-      </c>
-      <c r="W16" s="52" t="s">
-        <v>42</v>
-      </c>
-      <c r="X16" s="51" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y16" s="51" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z16" s="51" t="s">
-        <v>18</v>
-      </c>
-      <c r="AA16" s="51" t="s">
-        <v>19</v>
-      </c>
-      <c r="AB16" s="51" t="s">
-        <v>20</v>
-      </c>
-      <c r="AC16" s="51" t="s">
-        <v>21</v>
-      </c>
-      <c r="AD16" s="51" t="s">
-        <v>22</v>
-      </c>
+      <c r="W16" s="49"/>
+      <c r="X16" s="50"/>
+      <c r="Y16" s="50"/>
+      <c r="Z16" s="50"/>
       <c r="AI16"/>
       <c r="AJ16" s="39"/>
       <c r="AK16" s="76"/>
@@ -4503,342 +4433,375 @@
       <c r="AU16" s="76"/>
       <c r="AV16" s="76"/>
       <c r="AW16" s="76"/>
-      <c r="AY16" s="46"/>
-    </row>
-    <row r="17" spans="2:51" ht="31.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="32" t="s">
-        <v>48</v>
-      </c>
-      <c r="C17" s="32" t="s">
-        <v>32</v>
-      </c>
-      <c r="D17" s="32" t="s">
-        <v>33</v>
-      </c>
-      <c r="E17" s="32" t="s">
-        <v>54</v>
-      </c>
-      <c r="F17" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="G17" s="33" t="s">
-        <v>49</v>
-      </c>
-      <c r="H17" s="32" t="s">
-        <v>57</v>
-      </c>
-      <c r="I17" s="32" t="s">
-        <v>86</v>
-      </c>
-      <c r="J17" s="33" t="s">
-        <v>37</v>
-      </c>
-      <c r="K17" s="33" t="s">
-        <v>99</v>
-      </c>
-      <c r="L17" s="33" t="s">
-        <v>80</v>
-      </c>
-      <c r="M17" s="33" t="s">
-        <v>104</v>
-      </c>
-      <c r="N17" s="32" t="s">
-        <v>85</v>
-      </c>
-      <c r="O17" s="33" t="s">
-        <v>114</v>
-      </c>
-      <c r="P17" s="33" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q17" s="33" t="s">
-        <v>114</v>
-      </c>
-      <c r="R17" s="74" t="s">
-        <v>114</v>
-      </c>
-      <c r="S17" s="74" t="s">
-        <v>127</v>
-      </c>
-      <c r="V17" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="W17" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="X17" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y17" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z17" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="AA17" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB17" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="AC17" s="31" t="s">
-        <v>52</v>
-      </c>
-      <c r="AD17" s="31" t="s">
-        <v>31</v>
-      </c>
+    </row>
+    <row r="17" spans="2:51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="56" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="E17" s="57" t="s">
+        <v>113</v>
+      </c>
+      <c r="F17" s="57" t="s">
+        <v>16</v>
+      </c>
+      <c r="G17" s="57" t="s">
+        <v>34</v>
+      </c>
+      <c r="H17" s="57" t="s">
+        <v>47</v>
+      </c>
+      <c r="I17" s="57" t="s">
+        <v>36</v>
+      </c>
+      <c r="J17" s="59" t="s">
+        <v>5</v>
+      </c>
+      <c r="K17" s="59" t="s">
+        <v>98</v>
+      </c>
+      <c r="L17" s="57" t="s">
+        <v>56</v>
+      </c>
+      <c r="M17" s="59" t="s">
+        <v>103</v>
+      </c>
+      <c r="N17" s="58" t="s">
+        <v>112</v>
+      </c>
+      <c r="O17" s="59" t="s">
+        <v>115</v>
+      </c>
+      <c r="P17" s="59" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q17" s="59" t="s">
+        <v>117</v>
+      </c>
+      <c r="R17" s="59" t="s">
+        <v>118</v>
+      </c>
+      <c r="S17" s="59" t="s">
+        <v>126</v>
+      </c>
+      <c r="V17" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="W17" s="52" t="s">
+        <v>42</v>
+      </c>
+      <c r="X17" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y17" s="51" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z17" s="51" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA17" s="50"/>
+      <c r="AB17" s="50"/>
+      <c r="AC17" s="50"/>
+      <c r="AD17" s="50"/>
       <c r="AI17"/>
       <c r="AJ17" s="39"/>
+      <c r="AK17" s="76"/>
+      <c r="AL17" s="76"/>
+      <c r="AM17" s="76"/>
+      <c r="AN17" s="76"/>
+      <c r="AO17" s="76"/>
+      <c r="AP17" s="76"/>
+      <c r="AQ17" s="76"/>
+      <c r="AR17" s="76"/>
+      <c r="AS17" s="76"/>
+      <c r="AT17" s="76"/>
+      <c r="AU17" s="76"/>
+      <c r="AV17" s="76"/>
+      <c r="AW17" s="76"/>
       <c r="AY17" s="46"/>
     </row>
-    <row r="18" spans="2:51" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="C18" s="34"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="36"/>
-      <c r="H18" s="35" t="s">
+    <row r="18" spans="2:51" ht="31.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="E18" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="I18" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="J18" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="K18" s="35" t="s">
-        <v>134</v>
-      </c>
-      <c r="L18" s="36"/>
-      <c r="M18" s="36" t="s">
-        <v>105</v>
-      </c>
-      <c r="N18" s="35"/>
-      <c r="O18" s="36"/>
-      <c r="P18" s="36"/>
-      <c r="Q18" s="36"/>
-      <c r="R18" s="35"/>
-      <c r="S18" s="75"/>
+      <c r="F18" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="G18" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="H18" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="I18" s="32" t="s">
+        <v>86</v>
+      </c>
+      <c r="J18" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="K18" s="33" t="s">
+        <v>99</v>
+      </c>
+      <c r="L18" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="M18" s="33" t="s">
+        <v>104</v>
+      </c>
+      <c r="N18" s="32" t="s">
+        <v>85</v>
+      </c>
+      <c r="O18" s="33" t="s">
+        <v>114</v>
+      </c>
+      <c r="P18" s="33" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q18" s="33" t="s">
+        <v>114</v>
+      </c>
+      <c r="R18" s="74" t="s">
+        <v>114</v>
+      </c>
+      <c r="S18" s="74" t="s">
+        <v>127</v>
+      </c>
       <c r="V18" s="31" t="s">
-        <v>81</v>
-      </c>
-      <c r="W18" s="31"/>
-      <c r="X18" s="31"/>
-      <c r="Y18" s="31"/>
-      <c r="Z18" s="31"/>
-      <c r="AA18" s="31"/>
-      <c r="AB18" s="31"/>
-      <c r="AC18" s="31"/>
-      <c r="AD18" s="31"/>
+        <v>50</v>
+      </c>
+      <c r="W18" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="X18" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y18" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z18" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA18" s="51" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB18" s="51" t="s">
+        <v>20</v>
+      </c>
+      <c r="AC18" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="AD18" s="51" t="s">
+        <v>22</v>
+      </c>
       <c r="AI18"/>
       <c r="AJ18" s="39"/>
       <c r="AY18" s="46"/>
     </row>
-    <row r="19" spans="2:51" s="85" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="85" t="str">
-        <f>X19</f>
+    <row r="19" spans="2:51" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="34"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="35"/>
+      <c r="G19" s="36"/>
+      <c r="H19" s="35" t="s">
+        <v>54</v>
+      </c>
+      <c r="I19" s="35" t="s">
+        <v>111</v>
+      </c>
+      <c r="J19" s="35" t="s">
+        <v>111</v>
+      </c>
+      <c r="K19" s="35" t="s">
+        <v>134</v>
+      </c>
+      <c r="L19" s="36"/>
+      <c r="M19" s="36" t="s">
+        <v>105</v>
+      </c>
+      <c r="N19" s="35"/>
+      <c r="O19" s="36"/>
+      <c r="P19" s="36"/>
+      <c r="Q19" s="36"/>
+      <c r="R19" s="35"/>
+      <c r="S19" s="75"/>
+      <c r="V19" s="31" t="s">
+        <v>81</v>
+      </c>
+      <c r="W19" s="31"/>
+      <c r="X19" s="31"/>
+      <c r="Y19" s="31"/>
+      <c r="Z19" s="31"/>
+      <c r="AA19" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB19" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="AC19" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD19" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI19"/>
+      <c r="AJ19" s="39"/>
+      <c r="AY19" s="46"/>
+    </row>
+    <row r="20" spans="2:51" s="85" customFormat="1" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="85" t="str">
+        <f>X20</f>
         <v>Furnace</v>
       </c>
-      <c r="C19" s="85" t="s">
+      <c r="C20" s="85" t="s">
         <v>69</v>
       </c>
-      <c r="D19" s="86" t="str">
-        <f>X12</f>
-        <v>GHEAT</v>
-      </c>
-      <c r="E19" s="87">
+      <c r="D20" s="86" t="str">
+        <f>X11</f>
+        <v>GEHEAT</v>
+      </c>
+      <c r="E20" s="87">
         <v>2030</v>
       </c>
-      <c r="F19" s="88">
+      <c r="F20" s="88">
         <v>1</v>
       </c>
-      <c r="G19" s="88">
+      <c r="G20" s="88">
         <v>1</v>
       </c>
-      <c r="H19" s="87">
+      <c r="H20" s="87">
         <v>25</v>
       </c>
-      <c r="I19" s="88">
+      <c r="I20" s="88">
         <v>81</v>
       </c>
-      <c r="J19" s="88">
+      <c r="J20" s="88">
         <v>0</v>
       </c>
-      <c r="K19" s="88">
+      <c r="K20" s="88">
         <v>0.24</v>
       </c>
-      <c r="L19" s="88">
+      <c r="L20" s="88">
         <v>8.76</v>
       </c>
-      <c r="M19" s="87"/>
-      <c r="N19" s="88">
+      <c r="M20" s="87"/>
+      <c r="N20" s="88">
         <v>0.1</v>
       </c>
-      <c r="O19" s="88">
+      <c r="O20" s="88">
         <v>0.15</v>
       </c>
-      <c r="P19" s="88">
+      <c r="P20" s="88">
         <v>0.2</v>
       </c>
-      <c r="Q19" s="88">
+      <c r="Q20" s="88">
         <v>0.25</v>
       </c>
-      <c r="R19" s="88">
+      <c r="R20" s="88">
         <v>0.35</v>
       </c>
-      <c r="S19" s="87"/>
-      <c r="T19" s="89"/>
-      <c r="U19" s="89"/>
-      <c r="V19" s="90" t="s">
+      <c r="S20" s="87"/>
+      <c r="T20" s="89"/>
+      <c r="U20" s="89"/>
+      <c r="V20" s="90" t="s">
         <v>139</v>
       </c>
-      <c r="W19" s="90"/>
-      <c r="X19" s="91" t="s">
+      <c r="W20" s="90"/>
+      <c r="X20" s="91" t="s">
         <v>66</v>
       </c>
-      <c r="Y19" s="92" t="s">
-        <v>142</v>
-      </c>
-      <c r="Z19" s="85" t="s">
+      <c r="Y20" s="92" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z20" s="85" t="s">
         <v>58</v>
       </c>
-      <c r="AA19" s="85" t="s">
+      <c r="AA20" s="31" t="s">
         <v>87</v>
       </c>
-      <c r="AB19" s="93" t="s">
+      <c r="AB20" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="AC19" s="89"/>
-      <c r="AD19" s="89"/>
-      <c r="AI19" s="94"/>
-      <c r="AJ19" s="95"/>
-      <c r="AY19" s="89"/>
-    </row>
-    <row r="20" spans="2:51" s="76" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="76" t="str">
-        <f>X$20</f>
+      <c r="AC20" s="31"/>
+      <c r="AD20" s="31"/>
+      <c r="AI20" s="94"/>
+      <c r="AJ20" s="95"/>
+      <c r="AY20" s="89"/>
+    </row>
+    <row r="21" spans="2:51" s="76" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="76" t="str">
+        <f>X$21</f>
         <v>BIOBoiler</v>
       </c>
-      <c r="C20" s="76" t="str">
+      <c r="C21" s="76" t="str">
         <f>PRI_Sector_Fuels!P5</f>
         <v>MANBIOMIN</v>
       </c>
-      <c r="D20" s="83" t="str">
-        <f>X9</f>
+      <c r="D21" s="83" t="str">
+        <f>X8</f>
         <v>DECHEAT</v>
       </c>
-      <c r="E20" s="96">
+      <c r="E21" s="96">
         <v>2030</v>
       </c>
-      <c r="F20" s="82">
+      <c r="F21" s="82">
         <v>0.7</v>
       </c>
-      <c r="G20" s="82">
+      <c r="G21" s="82">
         <v>0.98</v>
       </c>
-      <c r="H20" s="96">
+      <c r="H21" s="96">
         <v>25</v>
       </c>
-      <c r="I20" s="82">
+      <c r="I21" s="82">
         <v>797.9</v>
       </c>
-      <c r="J20" s="82">
+      <c r="J21" s="82">
         <v>48.48</v>
       </c>
-      <c r="K20" s="82">
+      <c r="K21" s="82">
         <v>3.75</v>
       </c>
-      <c r="L20" s="82">
+      <c r="L21" s="82">
         <v>8.76</v>
       </c>
-      <c r="M20" s="96"/>
-      <c r="N20" s="97"/>
-      <c r="O20" s="96"/>
-      <c r="P20" s="96"/>
-      <c r="Q20" s="96"/>
-      <c r="R20" s="96"/>
-      <c r="S20" s="96"/>
-      <c r="T20" s="98"/>
-      <c r="U20" s="98"/>
-      <c r="V20" s="84" t="s">
+      <c r="M21" s="96"/>
+      <c r="N21" s="97"/>
+      <c r="O21" s="96"/>
+      <c r="P21" s="96"/>
+      <c r="Q21" s="96"/>
+      <c r="R21" s="96"/>
+      <c r="S21" s="96"/>
+      <c r="T21" s="98"/>
+      <c r="U21" s="98"/>
+      <c r="V21" s="84" t="s">
         <v>139</v>
       </c>
-      <c r="W20" s="84"/>
-      <c r="X20" s="99" t="s">
+      <c r="W21" s="84"/>
+      <c r="X21" s="99" t="s">
         <v>94</v>
       </c>
-      <c r="Y20" s="100" t="s">
-        <v>143</v>
-      </c>
-      <c r="Z20" s="76" t="s">
-        <v>58</v>
-      </c>
-      <c r="AA20" s="76" t="s">
-        <v>87</v>
-      </c>
-      <c r="AB20" s="101" t="s">
-        <v>88</v>
-      </c>
-      <c r="AC20" s="98"/>
-      <c r="AD20" s="98"/>
-      <c r="AI20" s="14"/>
-      <c r="AJ20" s="12"/>
-      <c r="AY20" s="98"/>
-    </row>
-    <row r="21" spans="2:51" s="85" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="85" t="str">
-        <f>X23</f>
-        <v>ELCBoiler</v>
-      </c>
-      <c r="C21" s="85" t="s">
-        <v>69</v>
-      </c>
-      <c r="D21" s="86" t="str">
-        <f>X12</f>
-        <v>GHEAT</v>
-      </c>
-      <c r="E21" s="87">
-        <v>2030</v>
-      </c>
-      <c r="F21" s="88">
-        <v>0.99</v>
-      </c>
-      <c r="G21" s="88">
-        <v>1</v>
-      </c>
-      <c r="H21" s="87">
-        <v>25</v>
-      </c>
-      <c r="I21" s="88">
-        <v>112.9</v>
-      </c>
-      <c r="J21" s="88">
-        <v>14.26</v>
-      </c>
-      <c r="K21" s="88">
-        <v>1.22</v>
-      </c>
-      <c r="L21" s="88">
-        <v>8.76</v>
-      </c>
-      <c r="M21" s="87"/>
-      <c r="S21" s="87"/>
-      <c r="T21" s="89"/>
-      <c r="U21" s="89"/>
-      <c r="V21" s="90" t="s">
-        <v>128</v>
-      </c>
-      <c r="W21" s="90"/>
-      <c r="X21" s="91" t="s">
-        <v>95</v>
-      </c>
-      <c r="Y21" s="92" t="s">
-        <v>144</v>
-      </c>
-      <c r="Z21" s="85" t="s">
+      <c r="Y21" s="100" t="s">
+        <v>141</v>
+      </c>
+      <c r="Z21" s="76" t="s">
         <v>58</v>
       </c>
       <c r="AA21" s="85" t="s">
@@ -4849,230 +4812,217 @@
       </c>
       <c r="AC21" s="89"/>
       <c r="AD21" s="89"/>
-      <c r="AI21" s="94"/>
-      <c r="AJ21" s="95"/>
-      <c r="AY21" s="89"/>
-    </row>
-    <row r="22" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="45" t="str">
-        <f>X21</f>
+      <c r="AI21" s="14"/>
+      <c r="AJ21" s="12"/>
+      <c r="AY21" s="98"/>
+    </row>
+    <row r="22" spans="2:51" s="85" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="85" t="str">
+        <f>X24</f>
+        <v>ELCBoiler</v>
+      </c>
+      <c r="C22" s="85" t="s">
+        <v>69</v>
+      </c>
+      <c r="D22" s="86" t="str">
+        <f>X11</f>
+        <v>GEHEAT</v>
+      </c>
+      <c r="E22" s="87">
+        <v>2030</v>
+      </c>
+      <c r="F22" s="88">
+        <v>0.99</v>
+      </c>
+      <c r="G22" s="88">
+        <v>1</v>
+      </c>
+      <c r="H22" s="87">
+        <v>25</v>
+      </c>
+      <c r="I22" s="88">
+        <v>112.9</v>
+      </c>
+      <c r="J22" s="88">
+        <v>14.26</v>
+      </c>
+      <c r="K22" s="88">
+        <v>1.22</v>
+      </c>
+      <c r="L22" s="88">
+        <v>8.76</v>
+      </c>
+      <c r="M22" s="87"/>
+      <c r="S22" s="87"/>
+      <c r="T22" s="89"/>
+      <c r="U22" s="89"/>
+      <c r="V22" s="90" t="s">
+        <v>128</v>
+      </c>
+      <c r="W22" s="90"/>
+      <c r="X22" s="91" t="s">
+        <v>95</v>
+      </c>
+      <c r="Y22" s="92" t="s">
+        <v>142</v>
+      </c>
+      <c r="Z22" s="85" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA22" s="76" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB22" s="101" t="s">
+        <v>88</v>
+      </c>
+      <c r="AC22" s="98"/>
+      <c r="AD22" s="98"/>
+      <c r="AI22" s="94"/>
+      <c r="AJ22" s="95"/>
+      <c r="AY22" s="89"/>
+    </row>
+    <row r="23" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="45" t="str">
+        <f>X22</f>
         <v>BIOKiln</v>
       </c>
-      <c r="C22" s="45" t="str">
+      <c r="C23" s="45" t="str">
         <f>PRI_Sector_Fuels!P5</f>
         <v>MANBIOMIN</v>
       </c>
-      <c r="D22" s="50" t="s">
+      <c r="D23" s="50" t="s">
         <v>108</v>
       </c>
-      <c r="E22" s="43">
+      <c r="E23" s="43">
         <v>2030</v>
       </c>
-      <c r="F22" s="64">
+      <c r="F23" s="64">
         <v>0.55600000000000005</v>
       </c>
-      <c r="G22" s="64">
+      <c r="G23" s="64">
         <v>0.98</v>
       </c>
-      <c r="H22" s="43">
+      <c r="H23" s="43">
         <v>25</v>
       </c>
-      <c r="I22" s="64">
+      <c r="I23" s="64">
         <v>297.10000000000002</v>
       </c>
-      <c r="J22" s="64">
+      <c r="J23" s="64">
         <v>4.46</v>
       </c>
-      <c r="K22" s="64">
+      <c r="K23" s="64">
         <v>0.45</v>
       </c>
-      <c r="L22" s="64">
+      <c r="L23" s="64">
         <v>8.76</v>
       </c>
-      <c r="M22" s="43"/>
-      <c r="N22" s="64">
+      <c r="M23" s="43"/>
+      <c r="N23" s="64">
         <v>0.1</v>
       </c>
-      <c r="O22" s="64">
+      <c r="O23" s="64">
         <v>0.15</v>
       </c>
-      <c r="P22" s="64">
+      <c r="P23" s="64">
         <v>0.2</v>
       </c>
-      <c r="Q22" s="64">
+      <c r="Q23" s="64">
         <v>0.25</v>
       </c>
-      <c r="R22" s="64">
+      <c r="R23" s="64">
         <v>0.35</v>
       </c>
-      <c r="S22" s="43"/>
-      <c r="V22" s="60" t="s">
+      <c r="S23" s="43"/>
+      <c r="V23" s="60" t="s">
         <v>128</v>
       </c>
-      <c r="W22" s="60"/>
-      <c r="X22" s="61" t="s">
+      <c r="W23" s="60"/>
+      <c r="X23" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="Y22" s="62" t="s">
-        <v>145</v>
-      </c>
-      <c r="Z22" s="45" t="s">
+      <c r="Y23" s="62" t="s">
+        <v>143</v>
+      </c>
+      <c r="Z23" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="AA22" s="45" t="s">
+      <c r="AA23" s="85" t="s">
         <v>87</v>
       </c>
-      <c r="AB22" s="63" t="s">
+      <c r="AB23" s="93" t="s">
         <v>88</v>
       </c>
-      <c r="AI22"/>
-      <c r="AJ22"/>
-      <c r="AK22" s="45"/>
-      <c r="AL22" s="45"/>
-      <c r="AM22" s="45"/>
-      <c r="AN22" s="45"/>
-      <c r="AO22" s="45"/>
-      <c r="AP22" s="45"/>
-      <c r="AQ22" s="45"/>
-      <c r="AR22" s="45"/>
-      <c r="AS22" s="45"/>
-      <c r="AT22" s="45"/>
-      <c r="AU22" s="45"/>
-      <c r="AV22" s="45"/>
-      <c r="AW22" s="45"/>
-    </row>
-    <row r="23" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="50" t="str">
-        <f>X22</f>
+      <c r="AC23" s="89"/>
+      <c r="AD23" s="89"/>
+      <c r="AI23"/>
+      <c r="AJ23"/>
+      <c r="AK23" s="45"/>
+      <c r="AL23" s="45"/>
+      <c r="AM23" s="45"/>
+      <c r="AN23" s="45"/>
+      <c r="AO23" s="45"/>
+      <c r="AP23" s="45"/>
+      <c r="AQ23" s="45"/>
+      <c r="AR23" s="45"/>
+      <c r="AS23" s="45"/>
+      <c r="AT23" s="45"/>
+      <c r="AU23" s="45"/>
+      <c r="AV23" s="45"/>
+      <c r="AW23" s="45"/>
+    </row>
+    <row r="24" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="50" t="str">
+        <f>X23</f>
         <v>GASBoiler</v>
       </c>
-      <c r="C23" s="45" t="str">
+      <c r="C24" s="45" t="str">
         <f>PRI_Sector_Fuels!P6</f>
         <v>MANGASMIN</v>
       </c>
-      <c r="D23" s="50" t="s">
+      <c r="D24" s="50" t="s">
         <v>107</v>
-      </c>
-      <c r="E23" s="43">
-        <v>2030</v>
-      </c>
-      <c r="F23" s="64">
-        <v>0.75</v>
-      </c>
-      <c r="G23" s="64">
-        <v>0.99</v>
-      </c>
-      <c r="H23" s="43">
-        <v>25</v>
-      </c>
-      <c r="I23" s="64">
-        <v>61.4</v>
-      </c>
-      <c r="J23" s="64">
-        <v>2.57</v>
-      </c>
-      <c r="K23" s="64">
-        <v>1.35</v>
-      </c>
-      <c r="L23" s="64">
-        <v>8.76</v>
-      </c>
-      <c r="M23" s="43"/>
-      <c r="N23" s="67"/>
-      <c r="O23" s="43"/>
-      <c r="P23" s="43"/>
-      <c r="Q23" s="43"/>
-      <c r="R23" s="43"/>
-      <c r="S23" s="43"/>
-      <c r="V23" s="60" t="s">
-        <v>139</v>
-      </c>
-      <c r="W23" s="60"/>
-      <c r="X23" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="Y23" s="62" t="s">
-        <v>146</v>
-      </c>
-      <c r="Z23" s="45" t="s">
-        <v>58</v>
-      </c>
-      <c r="AA23" s="45" t="s">
-        <v>87</v>
-      </c>
-      <c r="AB23" s="63" t="s">
-        <v>88</v>
-      </c>
-      <c r="AI23"/>
-      <c r="AJ23"/>
-      <c r="AK23" s="76"/>
-      <c r="AL23" s="76"/>
-      <c r="AM23" s="76"/>
-      <c r="AN23" s="76"/>
-      <c r="AO23" s="76"/>
-      <c r="AP23" s="76"/>
-      <c r="AQ23" s="76"/>
-      <c r="AR23" s="76"/>
-      <c r="AS23" s="76"/>
-      <c r="AT23" s="76"/>
-      <c r="AU23" s="76"/>
-      <c r="AV23" s="76"/>
-      <c r="AW23" s="76"/>
-    </row>
-    <row r="24" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="50" t="str">
-        <f>X25</f>
-        <v>WNDTRBN</v>
-      </c>
-      <c r="C24" s="45" t="str">
-        <f>PRI_Sector_Fuels!D19</f>
-        <v>WIND</v>
-      </c>
-      <c r="D24" s="50" t="s">
-        <v>130</v>
       </c>
       <c r="E24" s="43">
         <v>2030</v>
       </c>
-      <c r="F24" s="82">
-        <v>1</v>
+      <c r="F24" s="64">
+        <v>0.75</v>
       </c>
       <c r="G24" s="64">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="H24" s="43">
         <v>25</v>
       </c>
       <c r="I24" s="64">
-        <v>1041</v>
+        <v>61.4</v>
       </c>
       <c r="J24" s="64">
-        <v>38</v>
+        <v>2.57</v>
       </c>
       <c r="K24" s="64">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="L24" s="64">
         <v>8.76</v>
       </c>
-      <c r="M24" s="67"/>
+      <c r="M24" s="43"/>
       <c r="N24" s="67"/>
-      <c r="O24" s="64"/>
-      <c r="P24" s="64"/>
-      <c r="Q24" s="64"/>
-      <c r="R24" s="67"/>
-      <c r="S24" s="43">
-        <v>0.2</v>
-      </c>
+      <c r="O24" s="43"/>
+      <c r="P24" s="43"/>
+      <c r="Q24" s="43"/>
+      <c r="R24" s="43"/>
+      <c r="S24" s="43"/>
       <c r="V24" s="60" t="s">
         <v>139</v>
       </c>
       <c r="W24" s="60"/>
       <c r="X24" s="61" t="s">
-        <v>65</v>
+        <v>97</v>
       </c>
       <c r="Y24" s="62" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="Z24" s="45" t="s">
         <v>58</v>
@@ -5080,7 +5030,7 @@
       <c r="AA24" s="45" t="s">
         <v>87</v>
       </c>
-      <c r="AB24" s="46" t="s">
+      <c r="AB24" s="63" t="s">
         <v>88</v>
       </c>
       <c r="AI24"/>
@@ -5102,32 +5052,32 @@
     <row r="25" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B25" s="50" t="str">
         <f>X26</f>
-        <v>SOLPV</v>
+        <v>WNDTRBN</v>
       </c>
       <c r="C25" s="45" t="str">
-        <f>PRI_Sector_Fuels!D20</f>
-        <v>SOLAR</v>
+        <f>PRI_Sector_Fuels!D19</f>
+        <v>WIND</v>
       </c>
       <c r="D25" s="50" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E25" s="43">
         <v>2030</v>
       </c>
       <c r="F25" s="82">
-        <v>0.20499999999999999</v>
+        <v>1</v>
       </c>
       <c r="G25" s="64">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="H25" s="43">
         <v>25</v>
       </c>
       <c r="I25" s="64">
-        <v>691</v>
+        <v>1041</v>
       </c>
       <c r="J25" s="64">
-        <v>6.99</v>
+        <v>38</v>
       </c>
       <c r="K25" s="64">
         <v>0</v>
@@ -5142,17 +5092,17 @@
       <c r="Q25" s="64"/>
       <c r="R25" s="67"/>
       <c r="S25" s="43">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="V25" s="60" t="s">
-        <v>69</v>
+        <v>139</v>
       </c>
       <c r="W25" s="60"/>
       <c r="X25" s="61" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="Y25" s="62" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="Z25" s="45" t="s">
         <v>58</v>
@@ -5160,155 +5110,160 @@
       <c r="AA25" s="45" t="s">
         <v>87</v>
       </c>
-      <c r="AB25" s="46" t="s">
+      <c r="AB25" s="63" t="s">
         <v>88</v>
       </c>
       <c r="AI25"/>
       <c r="AJ25"/>
-      <c r="AK25" s="45"/>
-      <c r="AL25" s="45"/>
-      <c r="AM25" s="45"/>
-      <c r="AN25" s="45"/>
-      <c r="AO25" s="45"/>
-      <c r="AP25" s="45"/>
-      <c r="AQ25" s="45"/>
-      <c r="AR25" s="45"/>
-      <c r="AS25" s="45"/>
-      <c r="AT25" s="45"/>
-      <c r="AU25" s="45"/>
-      <c r="AV25" s="45"/>
-      <c r="AW25" s="45"/>
-    </row>
-    <row r="26" spans="2:51" s="98" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="83" t="str">
-        <f>X24</f>
-        <v>CSP</v>
-      </c>
-      <c r="C26" s="76" t="str">
+      <c r="AK25" s="76"/>
+      <c r="AL25" s="76"/>
+      <c r="AM25" s="76"/>
+      <c r="AN25" s="76"/>
+      <c r="AO25" s="76"/>
+      <c r="AP25" s="76"/>
+      <c r="AQ25" s="76"/>
+      <c r="AR25" s="76"/>
+      <c r="AS25" s="76"/>
+      <c r="AT25" s="76"/>
+      <c r="AU25" s="76"/>
+      <c r="AV25" s="76"/>
+      <c r="AW25" s="76"/>
+    </row>
+    <row r="26" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="50" t="str">
+        <f>X27</f>
+        <v>SOLPV</v>
+      </c>
+      <c r="C26" s="45" t="str">
         <f>PRI_Sector_Fuels!D20</f>
         <v>SOLAR</v>
       </c>
-      <c r="D26" s="83" t="str">
-        <f>X9</f>
+      <c r="D26" s="50" t="s">
+        <v>131</v>
+      </c>
+      <c r="E26" s="43">
+        <v>2030</v>
+      </c>
+      <c r="F26" s="82">
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="G26" s="64">
+        <v>0.99</v>
+      </c>
+      <c r="H26" s="43">
+        <v>25</v>
+      </c>
+      <c r="I26" s="64">
+        <v>691</v>
+      </c>
+      <c r="J26" s="64">
+        <v>6.99</v>
+      </c>
+      <c r="K26" s="64">
+        <v>0</v>
+      </c>
+      <c r="L26" s="64">
+        <v>8.76</v>
+      </c>
+      <c r="M26" s="67"/>
+      <c r="N26" s="67"/>
+      <c r="O26" s="64"/>
+      <c r="P26" s="64"/>
+      <c r="Q26" s="64"/>
+      <c r="R26" s="67"/>
+      <c r="S26" s="43">
+        <v>0.3</v>
+      </c>
+      <c r="V26" s="60" t="s">
+        <v>69</v>
+      </c>
+      <c r="W26" s="60"/>
+      <c r="X26" s="61" t="s">
+        <v>89</v>
+      </c>
+      <c r="Y26" s="62" t="s">
+        <v>146</v>
+      </c>
+      <c r="Z26" s="45" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA26" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB26" s="46" t="s">
+        <v>88</v>
+      </c>
+      <c r="AI26"/>
+      <c r="AJ26"/>
+      <c r="AK26" s="45"/>
+      <c r="AL26" s="45"/>
+      <c r="AM26" s="45"/>
+      <c r="AN26" s="45"/>
+      <c r="AO26" s="45"/>
+      <c r="AP26" s="45"/>
+      <c r="AQ26" s="45"/>
+      <c r="AR26" s="45"/>
+      <c r="AS26" s="45"/>
+      <c r="AT26" s="45"/>
+      <c r="AU26" s="45"/>
+      <c r="AV26" s="45"/>
+      <c r="AW26" s="45"/>
+    </row>
+    <row r="27" spans="2:51" s="98" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="83" t="str">
+        <f>X25</f>
+        <v>CSP</v>
+      </c>
+      <c r="C27" s="76" t="str">
+        <f>PRI_Sector_Fuels!D20</f>
+        <v>SOLAR</v>
+      </c>
+      <c r="D27" s="83" t="str">
+        <f>X8</f>
         <v>DECHEAT</v>
       </c>
-      <c r="E26" s="96">
+      <c r="E27" s="96">
         <v>2030</v>
       </c>
-      <c r="F26" s="82">
+      <c r="F27" s="82">
         <v>0.4</v>
       </c>
-      <c r="G26" s="82">
+      <c r="G27" s="82">
         <v>1</v>
       </c>
-      <c r="H26" s="96">
+      <c r="H27" s="96">
         <v>25</v>
       </c>
-      <c r="I26" s="82">
+      <c r="I27" s="82">
         <v>3677</v>
       </c>
-      <c r="J26" s="82">
+      <c r="J27" s="82">
         <v>0</v>
       </c>
-      <c r="K26" s="82">
+      <c r="K27" s="82">
         <v>14</v>
       </c>
-      <c r="L26" s="82">
+      <c r="L27" s="82">
         <v>8.76</v>
       </c>
-      <c r="M26" s="97"/>
-      <c r="N26" s="97"/>
-      <c r="O26" s="82"/>
-      <c r="P26" s="82"/>
-      <c r="Q26" s="82"/>
-      <c r="R26" s="97"/>
-      <c r="S26" s="96"/>
-      <c r="V26" s="84" t="s">
+      <c r="M27" s="97"/>
+      <c r="N27" s="97"/>
+      <c r="O27" s="82"/>
+      <c r="P27" s="82"/>
+      <c r="Q27" s="82"/>
+      <c r="R27" s="97"/>
+      <c r="S27" s="96"/>
+      <c r="V27" s="84" t="s">
         <v>69</v>
       </c>
-      <c r="W26" s="84"/>
-      <c r="X26" s="99" t="s">
+      <c r="W27" s="84"/>
+      <c r="X27" s="99" t="s">
         <v>90</v>
       </c>
-      <c r="Y26" s="100" t="s">
-        <v>149</v>
-      </c>
-      <c r="Z26" s="76" t="s">
-        <v>58</v>
-      </c>
-      <c r="AA26" s="76" t="s">
-        <v>87</v>
-      </c>
-      <c r="AB26" s="98" t="s">
-        <v>88</v>
-      </c>
-      <c r="AI26" s="14"/>
-      <c r="AJ26" s="14"/>
-      <c r="AK26" s="76"/>
-      <c r="AL26" s="76"/>
-      <c r="AM26" s="76"/>
-      <c r="AN26" s="76"/>
-      <c r="AO26" s="76"/>
-      <c r="AP26" s="76"/>
-      <c r="AQ26" s="76"/>
-      <c r="AR26" s="76"/>
-      <c r="AS26" s="76"/>
-      <c r="AT26" s="76"/>
-      <c r="AU26" s="76"/>
-      <c r="AV26" s="76"/>
-      <c r="AW26" s="76"/>
-    </row>
-    <row r="27" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="50" t="str">
-        <f>X22</f>
-        <v>GASBoiler</v>
-      </c>
-      <c r="C27" s="45"/>
-      <c r="D27" s="50" t="s">
-        <v>106</v>
-      </c>
-      <c r="E27" s="43">
-        <v>2030</v>
-      </c>
-      <c r="F27" s="82">
-        <v>0.3</v>
-      </c>
-      <c r="G27" s="64">
-        <v>1</v>
-      </c>
-      <c r="H27" s="43">
-        <v>25</v>
-      </c>
-      <c r="I27" s="64">
-        <v>0</v>
-      </c>
-      <c r="J27" s="64">
-        <v>0</v>
-      </c>
-      <c r="K27" s="64">
-        <v>0</v>
-      </c>
-      <c r="L27" s="64">
-        <v>8.76</v>
-      </c>
-      <c r="M27" s="67"/>
-      <c r="N27" s="67"/>
-      <c r="O27" s="64"/>
-      <c r="P27" s="64"/>
-      <c r="Q27" s="64"/>
-      <c r="R27" s="67"/>
-      <c r="S27" s="43"/>
-      <c r="V27" s="60" t="s">
-        <v>69</v>
-      </c>
-      <c r="W27" s="60"/>
-      <c r="X27" s="61" t="s">
-        <v>158</v>
-      </c>
-      <c r="Y27" s="62" t="s">
-        <v>150</v>
-      </c>
-      <c r="Z27" s="45" t="s">
+      <c r="Y27" s="100" t="s">
+        <v>147</v>
+      </c>
+      <c r="Z27" s="76" t="s">
         <v>58</v>
       </c>
       <c r="AA27" s="45" t="s">
@@ -5317,110 +5272,111 @@
       <c r="AB27" s="46" t="s">
         <v>88</v>
       </c>
-      <c r="AI27"/>
-      <c r="AJ27"/>
-      <c r="AK27" s="45"/>
-      <c r="AL27" s="45"/>
-      <c r="AM27" s="45"/>
-      <c r="AN27" s="45"/>
-      <c r="AO27" s="45"/>
-      <c r="AP27" s="45"/>
-      <c r="AQ27" s="45"/>
-      <c r="AR27" s="45"/>
-      <c r="AS27" s="45"/>
-      <c r="AT27" s="45"/>
-      <c r="AU27" s="45"/>
-      <c r="AV27" s="45"/>
-      <c r="AW27" s="45"/>
-    </row>
-    <row r="28" spans="2:51" s="104" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="102" t="str">
-        <f>X27</f>
-        <v>DECPOWER</v>
-      </c>
-      <c r="C28" s="102" t="s">
-        <v>130</v>
-      </c>
-      <c r="D28" s="102" t="str">
-        <f>X10</f>
-        <v>DECELC</v>
-      </c>
-      <c r="E28" s="103">
+      <c r="AC27" s="46"/>
+      <c r="AD27" s="46"/>
+      <c r="AI27" s="14"/>
+      <c r="AJ27" s="14"/>
+      <c r="AK27" s="76"/>
+      <c r="AL27" s="76"/>
+      <c r="AM27" s="76"/>
+      <c r="AN27" s="76"/>
+      <c r="AO27" s="76"/>
+      <c r="AP27" s="76"/>
+      <c r="AQ27" s="76"/>
+      <c r="AR27" s="76"/>
+      <c r="AS27" s="76"/>
+      <c r="AT27" s="76"/>
+      <c r="AU27" s="76"/>
+      <c r="AV27" s="76"/>
+      <c r="AW27" s="76"/>
+    </row>
+    <row r="28" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="50" t="str">
+        <f>X23</f>
+        <v>GASBoiler</v>
+      </c>
+      <c r="C28" s="45"/>
+      <c r="D28" s="50" t="s">
+        <v>106</v>
+      </c>
+      <c r="E28" s="43">
         <v>2030</v>
       </c>
-      <c r="F28" s="104">
+      <c r="F28" s="82">
+        <v>0.3</v>
+      </c>
+      <c r="G28" s="64">
         <v>1</v>
       </c>
-      <c r="G28" s="104">
-        <v>1</v>
-      </c>
-      <c r="H28" s="103">
-        <v>100</v>
-      </c>
-      <c r="I28" s="105">
+      <c r="H28" s="43">
+        <v>25</v>
+      </c>
+      <c r="I28" s="64">
         <v>0</v>
       </c>
-      <c r="J28" s="106">
+      <c r="J28" s="64">
         <v>0</v>
       </c>
-      <c r="K28" s="104">
+      <c r="K28" s="64">
         <v>0</v>
       </c>
-      <c r="L28" s="105">
+      <c r="L28" s="64">
         <v>8.76</v>
       </c>
-      <c r="M28" s="107"/>
-      <c r="N28" s="107"/>
-      <c r="O28" s="105"/>
-      <c r="P28" s="105"/>
-      <c r="Q28" s="105"/>
-      <c r="R28" s="107"/>
-      <c r="S28" s="103"/>
-      <c r="V28" s="108" t="s">
+      <c r="M28" s="67"/>
+      <c r="N28" s="67"/>
+      <c r="O28" s="64"/>
+      <c r="P28" s="64"/>
+      <c r="Q28" s="64"/>
+      <c r="R28" s="67"/>
+      <c r="S28" s="43"/>
+      <c r="V28" s="60" t="s">
         <v>69</v>
       </c>
-      <c r="W28" s="108"/>
-      <c r="X28" s="109" t="s">
-        <v>137</v>
-      </c>
-      <c r="Y28" s="110" t="s">
-        <v>151</v>
-      </c>
-      <c r="Z28" s="106" t="s">
+      <c r="W28" s="60"/>
+      <c r="X28" s="61" t="s">
+        <v>155</v>
+      </c>
+      <c r="Y28" s="62" t="s">
+        <v>148</v>
+      </c>
+      <c r="Z28" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="AA28" s="106" t="s">
+      <c r="AA28" s="76" t="s">
         <v>87</v>
       </c>
-      <c r="AB28" s="104" t="s">
+      <c r="AB28" s="98" t="s">
         <v>88</v>
       </c>
-      <c r="AI28" s="111"/>
-      <c r="AJ28" s="111"/>
-      <c r="AK28" s="106"/>
-      <c r="AL28" s="106"/>
-      <c r="AM28" s="106"/>
-      <c r="AN28" s="106"/>
-      <c r="AO28" s="106"/>
-      <c r="AP28" s="106"/>
-      <c r="AQ28" s="106"/>
-      <c r="AR28" s="106"/>
-      <c r="AS28" s="106"/>
-      <c r="AT28" s="106"/>
-      <c r="AU28" s="106"/>
-      <c r="AV28" s="106"/>
-      <c r="AW28" s="106"/>
+      <c r="AC28" s="98"/>
+      <c r="AD28" s="98"/>
+      <c r="AI28"/>
+      <c r="AJ28"/>
+      <c r="AK28" s="45"/>
+      <c r="AL28" s="45"/>
+      <c r="AM28" s="45"/>
+      <c r="AN28" s="45"/>
+      <c r="AO28" s="45"/>
+      <c r="AP28" s="45"/>
+      <c r="AQ28" s="45"/>
+      <c r="AR28" s="45"/>
+      <c r="AS28" s="45"/>
+      <c r="AT28" s="45"/>
+      <c r="AU28" s="45"/>
+      <c r="AV28" s="45"/>
+      <c r="AW28" s="45"/>
     </row>
     <row r="29" spans="2:51" s="104" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B29" s="102" t="str">
-        <f>X27</f>
+        <f>X28</f>
         <v>DECPOWER</v>
       </c>
       <c r="C29" s="102" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D29" s="102" t="str">
-        <f>X10</f>
+        <f>X9</f>
         <v>DECELC</v>
       </c>
       <c r="E29" s="103">
@@ -5454,26 +5410,27 @@
       <c r="Q29" s="105"/>
       <c r="R29" s="107"/>
       <c r="S29" s="103"/>
-      <c r="V29" s="46" t="s">
-        <v>128</v>
-      </c>
-      <c r="W29" s="46"/>
-      <c r="X29" s="46" t="s">
-        <v>161</v>
-      </c>
-      <c r="Y29" s="46" t="s">
-        <v>152</v>
+      <c r="V29" s="108" t="s">
+        <v>69</v>
+      </c>
+      <c r="W29" s="108"/>
+      <c r="X29" s="109" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y29" s="110" t="s">
+        <v>149</v>
       </c>
       <c r="Z29" s="106" t="s">
         <v>58</v>
       </c>
-      <c r="AA29" s="106" t="s">
+      <c r="AA29" s="45" t="s">
         <v>87</v>
       </c>
-      <c r="AB29" s="104" t="s">
+      <c r="AB29" s="46" t="s">
         <v>88</v>
       </c>
       <c r="AC29" s="46"/>
+      <c r="AD29" s="46"/>
       <c r="AI29" s="111"/>
       <c r="AJ29" s="111"/>
       <c r="AK29" s="106"/>
@@ -5490,57 +5447,58 @@
       <c r="AV29" s="106"/>
       <c r="AW29" s="106"/>
     </row>
-    <row r="30" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="50" t="str">
+    <row r="30" spans="2:51" s="104" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="102" t="str">
         <f>X28</f>
-        <v>BIOPOWER</v>
-      </c>
-      <c r="C30" s="50" t="s">
-        <v>68</v>
-      </c>
-      <c r="D30" s="50" t="s">
-        <v>135</v>
-      </c>
-      <c r="E30" s="43">
+        <v>DECPOWER</v>
+      </c>
+      <c r="C30" s="102" t="s">
+        <v>131</v>
+      </c>
+      <c r="D30" s="102" t="str">
+        <f>X9</f>
+        <v>DECELC</v>
+      </c>
+      <c r="E30" s="103">
         <v>2030</v>
       </c>
-      <c r="F30" s="46">
-        <v>0.35</v>
-      </c>
-      <c r="G30" s="46">
-        <v>0.98</v>
-      </c>
-      <c r="H30" s="43">
-        <v>20</v>
-      </c>
-      <c r="I30" s="112">
-        <v>3242</v>
-      </c>
-      <c r="J30" s="64">
-        <v>129.68</v>
-      </c>
-      <c r="K30" s="64">
+      <c r="F30" s="104">
+        <v>1</v>
+      </c>
+      <c r="G30" s="104">
+        <v>1</v>
+      </c>
+      <c r="H30" s="103">
+        <v>100</v>
+      </c>
+      <c r="I30" s="105">
         <v>0</v>
       </c>
-      <c r="L30" s="64">
+      <c r="J30" s="106">
+        <v>0</v>
+      </c>
+      <c r="K30" s="104">
+        <v>0</v>
+      </c>
+      <c r="L30" s="105">
         <v>8.76</v>
       </c>
-      <c r="M30" s="67"/>
-      <c r="N30" s="67"/>
-      <c r="O30" s="64"/>
-      <c r="P30" s="64"/>
-      <c r="Q30" s="64"/>
-      <c r="R30" s="67"/>
-      <c r="S30" s="43"/>
-      <c r="V30" s="106" t="s">
-        <v>139</v>
-      </c>
-      <c r="W30" s="106"/>
-      <c r="X30" s="106" t="s">
-        <v>164</v>
-      </c>
-      <c r="Y30" s="106" t="s">
-        <v>165</v>
+      <c r="M30" s="107"/>
+      <c r="N30" s="107"/>
+      <c r="O30" s="105"/>
+      <c r="P30" s="105"/>
+      <c r="Q30" s="105"/>
+      <c r="R30" s="107"/>
+      <c r="S30" s="103"/>
+      <c r="V30" s="46" t="s">
+        <v>128</v>
+      </c>
+      <c r="W30" s="46"/>
+      <c r="X30" s="46" t="s">
+        <v>158</v>
+      </c>
+      <c r="Y30" s="46" t="s">
+        <v>150</v>
       </c>
       <c r="Z30" s="106" t="s">
         <v>58</v>
@@ -5551,195 +5509,215 @@
       <c r="AB30" s="104" t="s">
         <v>88</v>
       </c>
-      <c r="AC30" s="106"/>
-      <c r="AI30" s="38"/>
-      <c r="AJ30" s="38"/>
-      <c r="AK30" s="45"/>
-      <c r="AL30" s="45"/>
-      <c r="AM30" s="45"/>
-      <c r="AN30" s="45"/>
-      <c r="AO30" s="45"/>
-      <c r="AP30" s="45"/>
-      <c r="AQ30" s="45"/>
-      <c r="AR30" s="45"/>
-      <c r="AS30" s="45"/>
-      <c r="AT30" s="45"/>
-      <c r="AU30" s="45"/>
-      <c r="AV30" s="45"/>
-      <c r="AW30" s="45"/>
-    </row>
-    <row r="31" spans="2:51" s="104" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="102" t="str">
-        <f>X27</f>
+      <c r="AI30" s="111"/>
+      <c r="AJ30" s="111"/>
+      <c r="AK30" s="106"/>
+      <c r="AL30" s="106"/>
+      <c r="AM30" s="106"/>
+      <c r="AN30" s="106"/>
+      <c r="AO30" s="106"/>
+      <c r="AP30" s="106"/>
+      <c r="AQ30" s="106"/>
+      <c r="AR30" s="106"/>
+      <c r="AS30" s="106"/>
+      <c r="AT30" s="106"/>
+      <c r="AU30" s="106"/>
+      <c r="AV30" s="106"/>
+      <c r="AW30" s="106"/>
+    </row>
+    <row r="31" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="50" t="str">
+        <f>X29</f>
+        <v>BIOPOWER</v>
+      </c>
+      <c r="C31" s="50" t="s">
+        <v>68</v>
+      </c>
+      <c r="D31" s="50" t="s">
+        <v>135</v>
+      </c>
+      <c r="E31" s="43">
+        <v>2030</v>
+      </c>
+      <c r="F31" s="46">
+        <v>0.35</v>
+      </c>
+      <c r="G31" s="46">
+        <v>0.98</v>
+      </c>
+      <c r="H31" s="43">
+        <v>20</v>
+      </c>
+      <c r="I31" s="112">
+        <v>3242</v>
+      </c>
+      <c r="J31" s="64">
+        <v>129.68</v>
+      </c>
+      <c r="K31" s="64">
+        <v>0</v>
+      </c>
+      <c r="L31" s="64">
+        <v>8.76</v>
+      </c>
+      <c r="M31" s="67"/>
+      <c r="N31" s="67"/>
+      <c r="O31" s="64"/>
+      <c r="P31" s="64"/>
+      <c r="Q31" s="64"/>
+      <c r="R31" s="67"/>
+      <c r="S31" s="43"/>
+      <c r="V31" s="106" t="s">
+        <v>139</v>
+      </c>
+      <c r="W31" s="106"/>
+      <c r="X31" s="106" t="s">
+        <v>160</v>
+      </c>
+      <c r="Y31" s="106" t="s">
+        <v>161</v>
+      </c>
+      <c r="Z31" s="106" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA31" s="106" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB31" s="104" t="s">
+        <v>88</v>
+      </c>
+      <c r="AD31" s="104"/>
+      <c r="AI31" s="38"/>
+      <c r="AJ31" s="38"/>
+      <c r="AK31" s="45"/>
+      <c r="AL31" s="45"/>
+      <c r="AM31" s="45"/>
+      <c r="AN31" s="45"/>
+      <c r="AO31" s="45"/>
+      <c r="AP31" s="45"/>
+      <c r="AQ31" s="45"/>
+      <c r="AR31" s="45"/>
+      <c r="AS31" s="45"/>
+      <c r="AT31" s="45"/>
+      <c r="AU31" s="45"/>
+      <c r="AV31" s="45"/>
+      <c r="AW31" s="45"/>
+    </row>
+    <row r="32" spans="2:51" s="104" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="102" t="str">
+        <f>X28</f>
         <v>DECPOWER</v>
       </c>
-      <c r="C31" s="106" t="s">
+      <c r="C32" s="106" t="s">
         <v>135</v>
       </c>
-      <c r="D31" s="102" t="str">
-        <f>X10</f>
+      <c r="D32" s="102" t="str">
+        <f>X9</f>
         <v>DECELC</v>
       </c>
-      <c r="E31" s="103">
+      <c r="E32" s="103">
         <v>2030</v>
       </c>
-      <c r="F31" s="105">
+      <c r="F32" s="105">
         <v>1</v>
       </c>
-      <c r="G31" s="105">
+      <c r="G32" s="105">
         <v>1</v>
       </c>
-      <c r="H31" s="104">
+      <c r="H32" s="104">
         <v>100</v>
       </c>
-      <c r="I31" s="104">
+      <c r="I32" s="104">
         <v>0</v>
       </c>
-      <c r="J31" s="104">
+      <c r="J32" s="104">
         <v>0</v>
       </c>
-      <c r="K31" s="104">
+      <c r="K32" s="104">
         <v>0</v>
       </c>
-      <c r="L31" s="104">
+      <c r="L32" s="104">
         <v>0</v>
       </c>
-      <c r="M31" s="107"/>
-      <c r="N31" s="107"/>
-      <c r="O31" s="105"/>
-      <c r="P31" s="105"/>
-      <c r="Q31" s="105"/>
-      <c r="R31" s="107"/>
-      <c r="S31" s="103"/>
-      <c r="V31" s="45"/>
-      <c r="W31" s="45"/>
-      <c r="X31" s="45"/>
-      <c r="Y31" s="45"/>
-      <c r="Z31" s="45"/>
-      <c r="AA31" s="45"/>
-      <c r="AB31" s="45"/>
-      <c r="AC31" s="45"/>
-      <c r="AD31" s="106"/>
-      <c r="AI31" s="111"/>
-      <c r="AJ31" s="111"/>
-      <c r="AK31" s="106"/>
-      <c r="AL31" s="106"/>
-      <c r="AM31" s="106"/>
-      <c r="AN31" s="106"/>
-      <c r="AO31" s="106"/>
-      <c r="AP31" s="106"/>
-      <c r="AQ31" s="106"/>
-      <c r="AR31" s="106"/>
-      <c r="AS31" s="106"/>
-      <c r="AT31" s="106"/>
-      <c r="AU31" s="106"/>
-      <c r="AV31" s="106"/>
-      <c r="AW31" s="106"/>
-    </row>
-    <row r="32" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="50" t="str">
-        <f>X19</f>
+      <c r="M32" s="107"/>
+      <c r="N32" s="107"/>
+      <c r="O32" s="105"/>
+      <c r="P32" s="105"/>
+      <c r="Q32" s="105"/>
+      <c r="R32" s="107"/>
+      <c r="S32" s="103"/>
+      <c r="V32" s="45" t="s">
+        <v>139</v>
+      </c>
+      <c r="W32" s="45"/>
+      <c r="X32" s="45" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y32" s="45" t="s">
+        <v>169</v>
+      </c>
+      <c r="Z32" s="106" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA32" s="106" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB32" s="104" t="s">
+        <v>88</v>
+      </c>
+      <c r="AC32" s="106"/>
+      <c r="AD32" s="46"/>
+      <c r="AI32" s="111"/>
+      <c r="AJ32" s="111"/>
+      <c r="AK32" s="106"/>
+      <c r="AL32" s="106"/>
+      <c r="AM32" s="106"/>
+      <c r="AN32" s="106"/>
+      <c r="AO32" s="106"/>
+      <c r="AP32" s="106"/>
+      <c r="AQ32" s="106"/>
+      <c r="AR32" s="106"/>
+      <c r="AS32" s="106"/>
+      <c r="AT32" s="106"/>
+      <c r="AU32" s="106"/>
+      <c r="AV32" s="106"/>
+      <c r="AW32" s="106"/>
+    </row>
+    <row r="33" spans="1:49" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="50" t="str">
+        <f>X20</f>
         <v>Furnace</v>
       </c>
-      <c r="C32" s="50" t="str">
-        <f>X10</f>
+      <c r="C33" s="50" t="str">
+        <f>X9</f>
         <v>DECELC</v>
       </c>
-      <c r="D32" s="83" t="str">
-        <f>X9</f>
-        <v>DECHEAT</v>
-      </c>
-      <c r="E32" s="43">
-        <v>2030</v>
-      </c>
-      <c r="F32" s="82">
-        <v>1</v>
-      </c>
-      <c r="G32" s="64">
-        <v>1</v>
-      </c>
-      <c r="H32" s="46">
-        <v>100</v>
-      </c>
-      <c r="I32" s="46">
-        <v>0</v>
-      </c>
-      <c r="J32" s="46">
-        <v>0</v>
-      </c>
-      <c r="K32" s="46">
-        <v>0</v>
-      </c>
-      <c r="L32" s="46">
-        <v>0</v>
-      </c>
-      <c r="M32" s="67"/>
-      <c r="N32" s="67"/>
-      <c r="O32" s="64"/>
-      <c r="P32" s="64"/>
-      <c r="Q32" s="64"/>
-      <c r="R32" s="67"/>
-      <c r="S32" s="43"/>
-      <c r="V32" s="38"/>
-      <c r="W32" s="38"/>
-      <c r="X32" s="39"/>
-      <c r="Y32" s="40"/>
-      <c r="Z32" s="38"/>
-      <c r="AA32" s="38"/>
-      <c r="AB32" s="38"/>
-      <c r="AC32" s="45"/>
-      <c r="AD32" s="45"/>
-      <c r="AI32"/>
-      <c r="AJ32"/>
-      <c r="AK32" s="45"/>
-      <c r="AL32" s="45"/>
-      <c r="AM32" s="45"/>
-      <c r="AN32" s="45"/>
-      <c r="AO32" s="45"/>
-      <c r="AP32" s="45"/>
-      <c r="AQ32" s="45"/>
-      <c r="AR32" s="45"/>
-      <c r="AS32" s="45"/>
-      <c r="AT32" s="45"/>
-      <c r="AU32" s="45"/>
-      <c r="AV32" s="45"/>
-      <c r="AW32" s="45"/>
-    </row>
-    <row r="33" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="50" t="str">
-        <f>X23</f>
-        <v>ELCBoiler</v>
-      </c>
-      <c r="C33" s="50" t="str">
-        <f>X10</f>
-        <v>DECELC</v>
-      </c>
       <c r="D33" s="83" t="str">
-        <f>X9</f>
-        <v>DECHEAT</v>
+        <f>X12</f>
+        <v>DECEHEAT</v>
       </c>
       <c r="E33" s="43">
         <v>2030</v>
       </c>
-      <c r="F33" s="64">
+      <c r="F33" s="82">
         <v>1</v>
       </c>
       <c r="G33" s="64">
         <v>1</v>
       </c>
-      <c r="H33" s="43">
+      <c r="H33" s="46">
         <v>100</v>
       </c>
-      <c r="I33" s="64">
+      <c r="I33" s="46">
         <v>0</v>
       </c>
-      <c r="J33" s="64">
+      <c r="J33" s="46">
         <v>0</v>
       </c>
-      <c r="K33" s="64">
+      <c r="K33" s="46">
         <v>0</v>
       </c>
-      <c r="L33" s="64">
+      <c r="L33" s="46">
         <v>0</v>
       </c>
       <c r="M33" s="67"/>
@@ -5754,73 +5732,77 @@
       <c r="X33" s="39"/>
       <c r="Y33" s="40"/>
       <c r="Z33" s="38"/>
-      <c r="AA33" s="38"/>
-      <c r="AB33" s="38"/>
+      <c r="AA33" s="45"/>
+      <c r="AB33" s="45"/>
       <c r="AC33" s="45"/>
-      <c r="AD33" s="45"/>
+      <c r="AD33" s="106"/>
       <c r="AI33"/>
       <c r="AJ33"/>
-      <c r="AK33" s="39"/>
-      <c r="AL33" s="39"/>
+      <c r="AK33" s="45"/>
+      <c r="AL33" s="45"/>
       <c r="AM33" s="45"/>
       <c r="AN33" s="45"/>
       <c r="AO33" s="45"/>
-      <c r="AQ33"/>
-      <c r="AR33"/>
-      <c r="AS33" s="39"/>
-      <c r="AT33" s="39"/>
+      <c r="AP33" s="45"/>
+      <c r="AQ33" s="45"/>
+      <c r="AR33" s="45"/>
+      <c r="AS33" s="45"/>
+      <c r="AT33" s="45"/>
       <c r="AU33" s="45"/>
       <c r="AV33" s="45"/>
-    </row>
-    <row r="34" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="5" t="s">
-        <v>155</v>
+      <c r="AW33" s="45"/>
+    </row>
+    <row r="34" spans="1:49" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="50" t="str">
+        <f>X24</f>
+        <v>ELCBoiler</v>
       </c>
       <c r="C34" s="50" t="str">
-        <f>X10</f>
+        <f>X9</f>
         <v>DECELC</v>
       </c>
-      <c r="D34" s="50" t="s">
-        <v>156</v>
+      <c r="D34" s="83" t="str">
+        <f>X12</f>
+        <v>DECEHEAT</v>
       </c>
       <c r="E34" s="43">
         <v>2030</v>
       </c>
-      <c r="F34" s="82">
+      <c r="F34" s="64">
         <v>1</v>
       </c>
       <c r="G34" s="64">
         <v>1</v>
       </c>
-      <c r="H34" s="46">
+      <c r="H34" s="43">
         <v>100</v>
       </c>
-      <c r="I34" s="46">
+      <c r="I34" s="64">
         <v>0</v>
       </c>
-      <c r="J34" s="46">
+      <c r="J34" s="64">
         <v>0</v>
       </c>
-      <c r="K34" s="46">
+      <c r="K34" s="64">
         <v>0</v>
       </c>
-      <c r="L34" s="46">
+      <c r="L34" s="64">
         <v>0</v>
       </c>
-      <c r="M34" s="43"/>
+      <c r="M34" s="67"/>
       <c r="N34" s="67"/>
-      <c r="O34" s="43"/>
-      <c r="P34" s="43"/>
-      <c r="Q34" s="43"/>
-      <c r="R34" s="43"/>
+      <c r="O34" s="64"/>
+      <c r="P34" s="64"/>
+      <c r="Q34" s="64"/>
+      <c r="R34" s="67"/>
       <c r="S34" s="43"/>
-      <c r="V34" s="45"/>
-      <c r="W34" s="45"/>
-      <c r="X34" s="45"/>
-      <c r="Y34" s="45"/>
-      <c r="Z34" s="50"/>
-      <c r="AA34" s="50"/>
-      <c r="AB34" s="63"/>
+      <c r="V34" s="38"/>
+      <c r="W34" s="38"/>
+      <c r="X34" s="39"/>
+      <c r="Y34" s="40"/>
+      <c r="Z34" s="38"/>
+      <c r="AA34" s="38"/>
+      <c r="AB34" s="38"/>
       <c r="AC34" s="45"/>
       <c r="AD34" s="45"/>
       <c r="AI34"/>
@@ -5837,48 +5819,55 @@
       <c r="AU34" s="45"/>
       <c r="AV34" s="45"/>
     </row>
-    <row r="35" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="45" t="str">
-        <f>X30</f>
-        <v>GTHT</v>
+    <row r="35" spans="1:49" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="5" t="s">
+        <v>152</v>
       </c>
       <c r="C35" s="50" t="str">
-        <f>X12</f>
-        <v>GHEAT</v>
+        <f>X9</f>
+        <v>DECELC</v>
       </c>
       <c r="D35" s="50" t="s">
-        <v>107</v>
+        <v>153</v>
       </c>
       <c r="E35" s="43">
         <v>2030</v>
       </c>
-      <c r="F35" s="64">
+      <c r="F35" s="82">
         <v>1</v>
       </c>
       <c r="G35" s="64">
         <v>1</v>
       </c>
-      <c r="H35" s="43">
+      <c r="H35" s="46">
         <v>100</v>
       </c>
-      <c r="I35" s="64">
+      <c r="I35" s="46">
         <v>0</v>
       </c>
-      <c r="J35" s="64">
+      <c r="J35" s="46">
         <v>0</v>
       </c>
-      <c r="K35" s="64">
+      <c r="K35" s="46">
         <v>0</v>
       </c>
-      <c r="L35" s="64">
+      <c r="L35" s="46">
         <v>0</v>
       </c>
-      <c r="N35" s="65"/>
+      <c r="M35" s="43"/>
+      <c r="N35" s="67"/>
+      <c r="O35" s="43"/>
+      <c r="P35" s="43"/>
+      <c r="Q35" s="43"/>
+      <c r="R35" s="43"/>
+      <c r="S35" s="43"/>
       <c r="V35" s="45"/>
+      <c r="W35" s="45"/>
       <c r="X35" s="45"/>
-      <c r="Z35" s="54"/>
-      <c r="AA35" s="54"/>
-      <c r="AB35" s="45"/>
+      <c r="Y35" s="45"/>
+      <c r="Z35" s="50"/>
+      <c r="AA35" s="38"/>
+      <c r="AB35" s="38"/>
       <c r="AC35" s="45"/>
       <c r="AD35" s="45"/>
       <c r="AI35"/>
@@ -5895,17 +5884,17 @@
       <c r="AU35" s="45"/>
       <c r="AV35" s="45"/>
     </row>
-    <row r="36" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:49" s="46" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B36" s="45" t="str">
-        <f>X29</f>
-        <v>RNWTHT</v>
+        <f>X31</f>
+        <v>GTHT</v>
       </c>
       <c r="C36" s="50" t="str">
-        <f>X12</f>
-        <v>GHEAT</v>
+        <f>X11</f>
+        <v>GEHEAT</v>
       </c>
       <c r="D36" s="50" t="s">
-        <v>107</v>
+        <v>156</v>
       </c>
       <c r="E36" s="43">
         <v>2030</v>
@@ -5933,12 +5922,10 @@
       </c>
       <c r="N36" s="65"/>
       <c r="V36" s="45"/>
-      <c r="W36" s="45"/>
       <c r="X36" s="45"/>
-      <c r="Y36" s="45"/>
-      <c r="Z36" s="45"/>
-      <c r="AA36" s="45"/>
-      <c r="AB36" s="45"/>
+      <c r="Z36" s="54"/>
+      <c r="AA36" s="50"/>
+      <c r="AB36" s="63"/>
       <c r="AC36" s="45"/>
       <c r="AD36" s="45"/>
       <c r="AI36"/>
@@ -5955,36 +5942,53 @@
       <c r="AU36" s="45"/>
       <c r="AV36" s="45"/>
     </row>
-    <row r="37" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="50" t="str">
-        <f>X29</f>
-        <v>RNWTHT</v>
+    <row r="37" spans="1:49" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="45" t="str">
+        <f>X32</f>
+        <v>ETHT</v>
       </c>
       <c r="C37" s="50" t="str">
-        <f>X9</f>
-        <v>DECHEAT</v>
+        <f>X11</f>
+        <v>GEHEAT</v>
       </c>
       <c r="D37" s="50" t="str">
-        <f>X11</f>
-        <v>RNWHEAT</v>
-      </c>
-      <c r="E37" s="64"/>
-      <c r="F37" s="66"/>
-      <c r="G37" s="45"/>
-      <c r="H37" s="45"/>
-      <c r="I37" s="45"/>
-      <c r="J37" s="67"/>
-      <c r="K37" s="45"/>
+        <f>X13</f>
+        <v>ELCHEAT</v>
+      </c>
+      <c r="E37" s="43">
+        <v>2030</v>
+      </c>
+      <c r="F37" s="82">
+        <v>1</v>
+      </c>
+      <c r="G37" s="64">
+        <v>1</v>
+      </c>
+      <c r="H37" s="46">
+        <v>100</v>
+      </c>
+      <c r="I37" s="46">
+        <v>0</v>
+      </c>
+      <c r="J37" s="46">
+        <v>0</v>
+      </c>
+      <c r="K37" s="46">
+        <v>0</v>
+      </c>
+      <c r="L37" s="46">
+        <v>0</v>
+      </c>
+      <c r="N37" s="65"/>
       <c r="V37" s="45"/>
       <c r="W37" s="45"/>
       <c r="X37" s="45"/>
       <c r="Y37" s="45"/>
       <c r="Z37" s="45"/>
-      <c r="AA37" s="45"/>
+      <c r="AA37" s="54"/>
       <c r="AB37" s="45"/>
       <c r="AC37" s="45"/>
       <c r="AD37" s="45"/>
-      <c r="AE37" s="45"/>
       <c r="AI37"/>
       <c r="AJ37"/>
       <c r="AK37" s="39"/>
@@ -5999,27 +6003,53 @@
       <c r="AU37" s="45"/>
       <c r="AV37" s="45"/>
     </row>
-    <row r="38" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="45"/>
-      <c r="C38" s="45"/>
-      <c r="D38" s="45"/>
-      <c r="E38" s="64"/>
-      <c r="F38" s="66"/>
-      <c r="G38" s="45"/>
-      <c r="H38" s="45"/>
-      <c r="I38" s="45"/>
-      <c r="J38" s="67"/>
-      <c r="K38" s="45"/>
+    <row r="38" spans="1:49" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="45" t="str">
+        <f>X32</f>
+        <v>ETHT</v>
+      </c>
+      <c r="C38" s="50" t="str">
+        <f>X12</f>
+        <v>DECEHEAT</v>
+      </c>
+      <c r="D38" s="50" t="str">
+        <f>X13</f>
+        <v>ELCHEAT</v>
+      </c>
+      <c r="E38" s="43">
+        <v>2030</v>
+      </c>
+      <c r="F38" s="64">
+        <v>1</v>
+      </c>
+      <c r="G38" s="64">
+        <v>1</v>
+      </c>
+      <c r="H38" s="43">
+        <v>100</v>
+      </c>
+      <c r="I38" s="64">
+        <v>0</v>
+      </c>
+      <c r="J38" s="64">
+        <v>0</v>
+      </c>
+      <c r="K38" s="64">
+        <v>0</v>
+      </c>
+      <c r="L38" s="64">
+        <v>0</v>
+      </c>
+      <c r="N38" s="65"/>
       <c r="V38" s="45"/>
       <c r="W38" s="45"/>
       <c r="X38" s="45"/>
       <c r="Y38" s="45"/>
       <c r="Z38" s="45"/>
-      <c r="AA38" s="45"/>
+      <c r="AA38" s="54"/>
       <c r="AB38" s="45"/>
       <c r="AC38" s="45"/>
       <c r="AD38" s="45"/>
-      <c r="AE38" s="45"/>
       <c r="AI38"/>
       <c r="AJ38"/>
       <c r="AK38" s="39"/>
@@ -6034,79 +6064,173 @@
       <c r="AU38" s="45"/>
       <c r="AV38" s="45"/>
     </row>
-    <row r="39" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A39" s="46"/>
-      <c r="F39" s="66"/>
-      <c r="G39" s="43"/>
-      <c r="H39" s="68"/>
-      <c r="M39" s="46"/>
-      <c r="N39" s="46"/>
-      <c r="O39" s="46"/>
-      <c r="P39" s="46"/>
-      <c r="Q39" s="46"/>
-      <c r="R39" s="46"/>
-      <c r="S39" s="46"/>
+    <row r="39" spans="1:49" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="45" t="str">
+        <f>X30</f>
+        <v>RNWTHT</v>
+      </c>
+      <c r="C39" s="50" t="str">
+        <f>X13</f>
+        <v>ELCHEAT</v>
+      </c>
+      <c r="D39" s="50" t="s">
+        <v>107</v>
+      </c>
+      <c r="E39" s="43">
+        <v>2030</v>
+      </c>
+      <c r="F39" s="82">
+        <v>1</v>
+      </c>
+      <c r="G39" s="64">
+        <v>1</v>
+      </c>
+      <c r="H39" s="46">
+        <v>100</v>
+      </c>
+      <c r="I39" s="46">
+        <v>0</v>
+      </c>
+      <c r="J39" s="46">
+        <v>0</v>
+      </c>
+      <c r="K39" s="46">
+        <v>0</v>
+      </c>
+      <c r="L39" s="46">
+        <v>0</v>
+      </c>
+      <c r="N39" s="65"/>
+      <c r="V39" s="45"/>
+      <c r="W39" s="45"/>
+      <c r="X39" s="45"/>
+      <c r="Y39" s="45"/>
+      <c r="Z39" s="45"/>
+      <c r="AA39" s="54"/>
+      <c r="AB39" s="45"/>
+      <c r="AC39" s="45"/>
+      <c r="AD39" s="45"/>
       <c r="AI39"/>
       <c r="AJ39"/>
       <c r="AK39" s="39"/>
       <c r="AL39" s="39"/>
-      <c r="AP39" s="46"/>
+      <c r="AM39" s="45"/>
+      <c r="AN39" s="45"/>
+      <c r="AO39" s="45"/>
       <c r="AQ39"/>
       <c r="AR39"/>
       <c r="AS39" s="39"/>
       <c r="AT39" s="39"/>
-    </row>
-    <row r="40" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A40" s="46"/>
-      <c r="H40" s="68"/>
-      <c r="M40" s="46"/>
-      <c r="N40" s="46"/>
-      <c r="O40" s="46"/>
-      <c r="P40" s="46"/>
-      <c r="Q40" s="46"/>
-      <c r="R40" s="46"/>
-      <c r="S40" s="46"/>
+      <c r="AU39" s="45"/>
+      <c r="AV39" s="45"/>
+    </row>
+    <row r="40" spans="1:49" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="50" t="str">
+        <f>X30</f>
+        <v>RNWTHT</v>
+      </c>
+      <c r="C40" s="50" t="str">
+        <f>X8</f>
+        <v>DECHEAT</v>
+      </c>
+      <c r="D40" s="50" t="s">
+        <v>107</v>
+      </c>
+      <c r="E40" s="43">
+        <v>2030</v>
+      </c>
+      <c r="F40" s="82">
+        <v>1</v>
+      </c>
+      <c r="G40" s="64">
+        <v>1</v>
+      </c>
+      <c r="H40" s="46">
+        <v>100</v>
+      </c>
+      <c r="I40" s="46">
+        <v>0</v>
+      </c>
+      <c r="J40" s="46">
+        <v>0</v>
+      </c>
+      <c r="K40" s="46">
+        <v>0</v>
+      </c>
+      <c r="L40" s="46">
+        <v>0</v>
+      </c>
+      <c r="V40" s="45"/>
+      <c r="W40" s="45"/>
+      <c r="X40" s="45"/>
+      <c r="Y40" s="45"/>
+      <c r="Z40" s="45"/>
+      <c r="AA40" s="45"/>
+      <c r="AB40" s="45"/>
+      <c r="AC40" s="45"/>
+      <c r="AD40" s="45"/>
+      <c r="AE40" s="45"/>
       <c r="AI40"/>
       <c r="AJ40"/>
       <c r="AK40" s="39"/>
       <c r="AL40" s="39"/>
-      <c r="AP40" s="46"/>
+      <c r="AM40" s="45"/>
+      <c r="AN40" s="45"/>
+      <c r="AO40" s="45"/>
       <c r="AQ40"/>
       <c r="AR40"/>
       <c r="AS40" s="39"/>
       <c r="AT40" s="39"/>
-    </row>
-    <row r="41" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="B41" s="69"/>
-      <c r="C41" s="45" t="s">
-        <v>82</v>
-      </c>
+      <c r="AU40" s="45"/>
+      <c r="AV40" s="45"/>
+    </row>
+    <row r="41" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="A41" s="46"/>
+      <c r="F41" s="66"/>
+      <c r="G41" s="43"/>
       <c r="H41" s="68"/>
+      <c r="M41" s="46"/>
+      <c r="N41" s="46"/>
+      <c r="O41" s="46"/>
+      <c r="P41" s="46"/>
+      <c r="Q41" s="46"/>
+      <c r="R41" s="46"/>
+      <c r="S41" s="46"/>
       <c r="AI41"/>
       <c r="AJ41"/>
       <c r="AK41" s="39"/>
       <c r="AL41" s="39"/>
+      <c r="AP41" s="46"/>
       <c r="AQ41"/>
       <c r="AR41"/>
       <c r="AS41" s="39"/>
       <c r="AT41" s="39"/>
     </row>
-    <row r="42" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="B42" s="70"/>
-      <c r="C42" s="45" t="s">
-        <v>83</v>
-      </c>
+    <row r="42" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="A42" s="46"/>
       <c r="H42" s="68"/>
+      <c r="M42" s="46"/>
+      <c r="N42" s="46"/>
+      <c r="O42" s="46"/>
+      <c r="P42" s="46"/>
+      <c r="Q42" s="46"/>
+      <c r="R42" s="46"/>
+      <c r="S42" s="46"/>
       <c r="AI42"/>
       <c r="AJ42"/>
       <c r="AK42" s="39"/>
       <c r="AL42" s="39"/>
+      <c r="AP42" s="46"/>
       <c r="AQ42"/>
       <c r="AR42"/>
       <c r="AS42" s="39"/>
       <c r="AT42" s="39"/>
     </row>
-    <row r="43" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="B43" s="69"/>
+      <c r="C43" s="45" t="s">
+        <v>82</v>
+      </c>
       <c r="H43" s="68"/>
       <c r="AI43"/>
       <c r="AJ43"/>
@@ -6117,7 +6241,12 @@
       <c r="AS43" s="39"/>
       <c r="AT43" s="39"/>
     </row>
-    <row r="44" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="B44" s="70"/>
+      <c r="C44" s="45" t="s">
+        <v>83</v>
+      </c>
+      <c r="H44" s="68"/>
       <c r="AI44"/>
       <c r="AJ44"/>
       <c r="AK44" s="39"/>
@@ -6127,7 +6256,8 @@
       <c r="AS44" s="39"/>
       <c r="AT44" s="39"/>
     </row>
-    <row r="45" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="H45" s="68"/>
       <c r="AI45"/>
       <c r="AJ45"/>
       <c r="AK45" s="39"/>
@@ -6137,8 +6267,7 @@
       <c r="AS45" s="39"/>
       <c r="AT45" s="39"/>
     </row>
-    <row r="46" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="E46" s="43"/>
+    <row r="46" spans="1:49" x14ac:dyDescent="0.25">
       <c r="AI46"/>
       <c r="AJ46"/>
       <c r="AK46" s="39"/>
@@ -6148,7 +6277,7 @@
       <c r="AS46" s="39"/>
       <c r="AT46" s="39"/>
     </row>
-    <row r="47" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:49" x14ac:dyDescent="0.25">
       <c r="AI47"/>
       <c r="AJ47"/>
       <c r="AK47" s="39"/>
@@ -6158,7 +6287,8 @@
       <c r="AS47" s="39"/>
       <c r="AT47" s="39"/>
     </row>
-    <row r="48" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="E48" s="43"/>
       <c r="AI48"/>
       <c r="AJ48"/>
       <c r="AK48" s="39"/>
@@ -6209,17 +6339,6 @@
       <c r="AT52" s="39"/>
     </row>
     <row r="53" spans="2:46" x14ac:dyDescent="0.25">
-      <c r="B53" s="72"/>
-      <c r="C53" s="72"/>
-      <c r="D53"/>
-      <c r="E53"/>
-      <c r="F53"/>
-      <c r="G53"/>
-      <c r="H53"/>
-      <c r="I53"/>
-      <c r="J53"/>
-      <c r="K53"/>
-      <c r="L53"/>
       <c r="AI53"/>
       <c r="AJ53"/>
       <c r="AK53" s="39"/>
@@ -6229,18 +6348,7 @@
       <c r="AS53" s="39"/>
       <c r="AT53" s="39"/>
     </row>
-    <row r="54" spans="2:46" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="73"/>
-      <c r="C54" s="73"/>
-      <c r="D54" s="73"/>
-      <c r="E54" s="73"/>
-      <c r="F54" s="73"/>
-      <c r="G54" s="73"/>
-      <c r="H54" s="73"/>
-      <c r="I54" s="73"/>
-      <c r="J54" s="73"/>
-      <c r="K54" s="73"/>
-      <c r="L54" s="73"/>
+    <row r="54" spans="2:46" x14ac:dyDescent="0.25">
       <c r="AI54"/>
       <c r="AJ54"/>
       <c r="AK54" s="39"/>
@@ -6251,10 +6359,10 @@
       <c r="AT54" s="39"/>
     </row>
     <row r="55" spans="2:46" x14ac:dyDescent="0.25">
-      <c r="B55"/>
-      <c r="C55"/>
+      <c r="B55" s="72"/>
+      <c r="C55" s="72"/>
       <c r="D55"/>
-      <c r="E55" s="1"/>
+      <c r="E55"/>
       <c r="F55"/>
       <c r="G55"/>
       <c r="H55"/>
@@ -6271,18 +6379,18 @@
       <c r="AS55" s="39"/>
       <c r="AT55" s="39"/>
     </row>
-    <row r="56" spans="2:46" x14ac:dyDescent="0.25">
-      <c r="B56"/>
-      <c r="C56"/>
-      <c r="D56"/>
-      <c r="E56" s="1"/>
-      <c r="F56"/>
-      <c r="G56"/>
-      <c r="H56"/>
-      <c r="I56"/>
-      <c r="J56"/>
-      <c r="K56"/>
-      <c r="L56"/>
+    <row r="56" spans="2:46" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B56" s="73"/>
+      <c r="C56" s="73"/>
+      <c r="D56" s="73"/>
+      <c r="E56" s="73"/>
+      <c r="F56" s="73"/>
+      <c r="G56" s="73"/>
+      <c r="H56" s="73"/>
+      <c r="I56" s="73"/>
+      <c r="J56" s="73"/>
+      <c r="K56" s="73"/>
+      <c r="L56" s="73"/>
       <c r="AI56"/>
       <c r="AJ56"/>
       <c r="AK56" s="39"/>
@@ -6419,6 +6527,17 @@
       <c r="AT62" s="39"/>
     </row>
     <row r="63" spans="2:46" x14ac:dyDescent="0.25">
+      <c r="B63"/>
+      <c r="C63"/>
+      <c r="D63"/>
+      <c r="E63" s="1"/>
+      <c r="F63"/>
+      <c r="G63"/>
+      <c r="H63"/>
+      <c r="I63"/>
+      <c r="J63"/>
+      <c r="K63"/>
+      <c r="L63"/>
       <c r="AI63"/>
       <c r="AJ63"/>
       <c r="AK63" s="39"/>
@@ -6429,6 +6548,17 @@
       <c r="AT63" s="39"/>
     </row>
     <row r="64" spans="2:46" x14ac:dyDescent="0.25">
+      <c r="B64"/>
+      <c r="C64"/>
+      <c r="D64"/>
+      <c r="E64" s="1"/>
+      <c r="F64"/>
+      <c r="G64"/>
+      <c r="H64"/>
+      <c r="I64"/>
+      <c r="J64"/>
+      <c r="K64"/>
+      <c r="L64"/>
       <c r="AI64"/>
       <c r="AJ64"/>
       <c r="AK64" s="39"/>
@@ -6439,14 +6569,6 @@
       <c r="AT64" s="39"/>
     </row>
     <row r="65" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="V65" s="46"/>
-      <c r="W65" s="46"/>
-      <c r="X65" s="46"/>
-      <c r="Y65" s="46"/>
-      <c r="Z65" s="46"/>
-      <c r="AA65" s="46"/>
-      <c r="AB65" s="46"/>
-      <c r="AC65" s="46"/>
       <c r="AI65"/>
       <c r="AJ65"/>
       <c r="AK65" s="39"/>
@@ -6457,15 +6579,6 @@
       <c r="AT65" s="39"/>
     </row>
     <row r="66" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="V66" s="46"/>
-      <c r="W66" s="46"/>
-      <c r="X66" s="46"/>
-      <c r="Y66" s="46"/>
-      <c r="Z66" s="46"/>
-      <c r="AA66" s="46"/>
-      <c r="AB66" s="46"/>
-      <c r="AC66" s="46"/>
-      <c r="AD66" s="46"/>
       <c r="AI66"/>
       <c r="AJ66"/>
       <c r="AK66" s="39"/>
@@ -6481,11 +6594,6 @@
       <c r="X67" s="46"/>
       <c r="Y67" s="46"/>
       <c r="Z67" s="46"/>
-      <c r="AA67" s="46"/>
-      <c r="AB67" s="46"/>
-      <c r="AC67" s="46"/>
-      <c r="AD67" s="46"/>
-      <c r="AE67" s="46"/>
       <c r="AI67"/>
       <c r="AJ67"/>
       <c r="AK67" s="39"/>
@@ -6496,18 +6604,14 @@
       <c r="AT67" s="39"/>
     </row>
     <row r="68" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="B68"/>
-      <c r="C68"/>
-      <c r="E68" s="72"/>
-      <c r="F68" s="72"/>
-      <c r="G68" s="1"/>
-      <c r="H68"/>
-      <c r="I68" s="72"/>
-      <c r="J68"/>
-      <c r="K68"/>
-      <c r="L68" s="72"/>
-      <c r="AD68" s="46"/>
-      <c r="AE68" s="46"/>
+      <c r="V68" s="46"/>
+      <c r="W68" s="46"/>
+      <c r="X68" s="46"/>
+      <c r="Y68" s="46"/>
+      <c r="Z68" s="46"/>
+      <c r="AA68" s="46"/>
+      <c r="AB68" s="46"/>
+      <c r="AC68" s="46"/>
       <c r="AI68"/>
       <c r="AJ68"/>
       <c r="AK68" s="39"/>
@@ -6517,98 +6621,71 @@
       <c r="AS68" s="39"/>
       <c r="AT68" s="39"/>
     </row>
-    <row r="69" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="45"/>
-      <c r="B69" s="78"/>
-      <c r="C69" s="78"/>
-      <c r="D69" s="78"/>
-      <c r="E69" s="78"/>
-      <c r="F69" s="78"/>
-      <c r="G69" s="78"/>
-      <c r="H69" s="79"/>
-      <c r="I69" s="78"/>
-      <c r="J69" s="78"/>
-      <c r="K69" s="78"/>
-      <c r="L69" s="78"/>
-      <c r="M69" s="45"/>
-      <c r="N69" s="45"/>
-      <c r="O69" s="45"/>
-      <c r="P69" s="45"/>
-      <c r="Q69" s="45"/>
-      <c r="R69" s="45"/>
-      <c r="S69" s="45"/>
-      <c r="V69" s="45"/>
-      <c r="W69" s="45"/>
-      <c r="X69" s="45"/>
-      <c r="Y69" s="45"/>
-      <c r="Z69" s="45"/>
-      <c r="AA69" s="45"/>
-      <c r="AB69" s="45"/>
-      <c r="AC69" s="45"/>
-      <c r="AD69" s="45"/>
+    <row r="69" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="V69" s="46"/>
+      <c r="W69" s="46"/>
+      <c r="X69" s="46"/>
+      <c r="Y69" s="46"/>
+      <c r="Z69" s="46"/>
+      <c r="AA69" s="46"/>
+      <c r="AB69" s="46"/>
+      <c r="AC69" s="46"/>
+      <c r="AD69" s="46"/>
+      <c r="AE69" s="46"/>
       <c r="AI69"/>
-      <c r="AJ69" s="79"/>
+      <c r="AJ69"/>
       <c r="AK69" s="39"/>
-      <c r="AL69" s="41"/>
-      <c r="AM69" s="45"/>
-      <c r="AN69" s="45"/>
+      <c r="AL69" s="39"/>
       <c r="AQ69"/>
-      <c r="AR69" s="79"/>
+      <c r="AR69"/>
       <c r="AS69" s="39"/>
-      <c r="AT69" s="41"/>
-      <c r="AU69" s="45"/>
-      <c r="AV69" s="45"/>
-    </row>
-    <row r="70" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="72"/>
-      <c r="B70" s="80"/>
-      <c r="C70" s="81"/>
-      <c r="D70" s="80"/>
-      <c r="E70" s="80"/>
-      <c r="F70" s="80"/>
-      <c r="G70" s="80"/>
-      <c r="H70" s="79"/>
-      <c r="I70" s="80"/>
-      <c r="J70" s="80"/>
-      <c r="K70" s="81"/>
-      <c r="L70" s="81"/>
-      <c r="M70" s="72"/>
-      <c r="N70" s="72"/>
-      <c r="O70" s="1"/>
-      <c r="P70" s="45"/>
-      <c r="Q70" s="45"/>
-      <c r="R70" s="45"/>
-      <c r="S70" s="45"/>
-      <c r="V70" s="45"/>
-      <c r="W70" s="45"/>
-      <c r="X70" s="45"/>
-      <c r="Y70" s="45"/>
-      <c r="Z70" s="45"/>
-      <c r="AA70" s="45"/>
-      <c r="AB70" s="45"/>
-      <c r="AC70" s="45"/>
-      <c r="AD70" s="45"/>
-      <c r="AE70" s="45"/>
-      <c r="AI70" s="42"/>
-      <c r="AJ70" s="42"/>
-      <c r="AK70" s="54"/>
+      <c r="AT69" s="39"/>
+    </row>
+    <row r="70" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="B70"/>
+      <c r="C70"/>
+      <c r="E70" s="72"/>
+      <c r="F70" s="72"/>
+      <c r="G70" s="1"/>
+      <c r="H70"/>
+      <c r="I70" s="72"/>
+      <c r="J70"/>
+      <c r="K70"/>
+      <c r="L70" s="72"/>
+      <c r="AA70" s="46"/>
+      <c r="AB70" s="46"/>
+      <c r="AC70" s="46"/>
+      <c r="AD70" s="46"/>
+      <c r="AE70" s="46"/>
+      <c r="AI70"/>
+      <c r="AJ70"/>
+      <c r="AK70" s="39"/>
+      <c r="AL70" s="39"/>
+      <c r="AQ70"/>
+      <c r="AR70"/>
+      <c r="AS70" s="39"/>
+      <c r="AT70" s="39"/>
     </row>
     <row r="71" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="78"/>
-      <c r="B71" s="80"/>
-      <c r="C71" s="80"/>
-      <c r="D71" s="80"/>
-      <c r="E71" s="80"/>
-      <c r="F71" s="80"/>
-      <c r="G71" s="80"/>
+      <c r="A71" s="45"/>
+      <c r="B71" s="78"/>
+      <c r="C71" s="78"/>
+      <c r="D71" s="78"/>
+      <c r="E71" s="78"/>
+      <c r="F71" s="78"/>
+      <c r="G71" s="78"/>
       <c r="H71" s="79"/>
-      <c r="I71" s="80"/>
-      <c r="J71" s="80"/>
-      <c r="K71" s="80"/>
-      <c r="L71" s="80"/>
-      <c r="M71" s="78"/>
-      <c r="N71" s="78"/>
-      <c r="O71" s="78"/>
+      <c r="I71" s="78"/>
+      <c r="J71" s="78"/>
+      <c r="K71" s="78"/>
+      <c r="L71" s="78"/>
+      <c r="M71" s="45"/>
+      <c r="N71" s="45"/>
+      <c r="O71" s="45"/>
+      <c r="P71" s="45"/>
+      <c r="Q71" s="45"/>
+      <c r="R71" s="45"/>
+      <c r="S71" s="45"/>
       <c r="V71" s="45"/>
       <c r="W71" s="45"/>
       <c r="X71" s="45"/>
@@ -6617,76 +6694,121 @@
       <c r="AA71" s="45"/>
       <c r="AB71" s="45"/>
       <c r="AC71" s="45"/>
-      <c r="AD71" s="45"/>
-      <c r="AE71" s="45"/>
-      <c r="AI71" s="42"/>
-      <c r="AJ71" s="42"/>
-      <c r="AK71" s="54"/>
-    </row>
-    <row r="72" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A72" s="80"/>
-      <c r="B72"/>
-      <c r="C72" s="39"/>
-      <c r="D72" s="39"/>
-      <c r="H72"/>
-      <c r="I72"/>
-      <c r="J72"/>
-      <c r="K72" s="39"/>
-      <c r="L72" s="39"/>
-      <c r="M72" s="81"/>
-      <c r="N72" s="81"/>
-      <c r="O72" s="80"/>
-      <c r="P72" s="46"/>
-      <c r="Q72" s="46"/>
-      <c r="R72" s="46"/>
-      <c r="S72" s="46"/>
-      <c r="AI72" s="38"/>
-      <c r="AJ72" s="38"/>
-      <c r="AK72" s="50"/>
-    </row>
-    <row r="73" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A73" s="80"/>
-      <c r="B73"/>
-      <c r="C73" s="39"/>
-      <c r="D73" s="39"/>
-      <c r="H73" s="77"/>
-      <c r="I73"/>
-      <c r="J73"/>
-      <c r="K73" s="39"/>
-      <c r="L73" s="39"/>
-      <c r="M73" s="80"/>
-      <c r="N73" s="80"/>
-      <c r="O73" s="80"/>
-      <c r="P73" s="46"/>
-      <c r="Q73" s="46"/>
-      <c r="R73" s="46"/>
-      <c r="S73" s="46"/>
-      <c r="AI73" s="38"/>
-      <c r="AJ73" s="38"/>
-      <c r="AK73" s="50"/>
+      <c r="AI71"/>
+      <c r="AJ71" s="79"/>
+      <c r="AK71" s="39"/>
+      <c r="AL71" s="41"/>
+      <c r="AM71" s="45"/>
+      <c r="AN71" s="45"/>
+      <c r="AQ71"/>
+      <c r="AR71" s="79"/>
+      <c r="AS71" s="39"/>
+      <c r="AT71" s="41"/>
+      <c r="AU71" s="45"/>
+      <c r="AV71" s="45"/>
+    </row>
+    <row r="72" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="72"/>
+      <c r="B72" s="80"/>
+      <c r="C72" s="81"/>
+      <c r="D72" s="80"/>
+      <c r="E72" s="80"/>
+      <c r="F72" s="80"/>
+      <c r="G72" s="80"/>
+      <c r="H72" s="79"/>
+      <c r="I72" s="80"/>
+      <c r="J72" s="80"/>
+      <c r="K72" s="81"/>
+      <c r="L72" s="81"/>
+      <c r="M72" s="72"/>
+      <c r="N72" s="72"/>
+      <c r="O72" s="1"/>
+      <c r="P72" s="45"/>
+      <c r="Q72" s="45"/>
+      <c r="R72" s="45"/>
+      <c r="S72" s="45"/>
+      <c r="V72" s="45"/>
+      <c r="W72" s="45"/>
+      <c r="X72" s="45"/>
+      <c r="Y72" s="45"/>
+      <c r="Z72" s="45"/>
+      <c r="AA72" s="45"/>
+      <c r="AB72" s="45"/>
+      <c r="AC72" s="45"/>
+      <c r="AD72" s="45"/>
+      <c r="AE72" s="45"/>
+      <c r="AI72" s="42"/>
+      <c r="AJ72" s="42"/>
+      <c r="AK72" s="54"/>
+    </row>
+    <row r="73" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="78"/>
+      <c r="B73" s="80"/>
+      <c r="C73" s="80"/>
+      <c r="D73" s="80"/>
+      <c r="E73" s="80"/>
+      <c r="F73" s="80"/>
+      <c r="G73" s="80"/>
+      <c r="H73" s="79"/>
+      <c r="I73" s="80"/>
+      <c r="J73" s="80"/>
+      <c r="K73" s="80"/>
+      <c r="L73" s="80"/>
+      <c r="M73" s="78"/>
+      <c r="N73" s="78"/>
+      <c r="O73" s="78"/>
+      <c r="V73" s="45"/>
+      <c r="W73" s="45"/>
+      <c r="X73" s="45"/>
+      <c r="Y73" s="45"/>
+      <c r="Z73" s="45"/>
+      <c r="AA73" s="45"/>
+      <c r="AB73" s="45"/>
+      <c r="AC73" s="45"/>
+      <c r="AD73" s="45"/>
+      <c r="AE73" s="45"/>
+      <c r="AI73" s="42"/>
+      <c r="AJ73" s="42"/>
+      <c r="AK73" s="54"/>
     </row>
     <row r="74" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A74"/>
+      <c r="A74" s="80"/>
       <c r="B74"/>
       <c r="C74" s="39"/>
       <c r="D74" s="39"/>
+      <c r="H74"/>
       <c r="I74"/>
       <c r="J74"/>
       <c r="K74" s="39"/>
       <c r="L74" s="39"/>
+      <c r="M74" s="81"/>
+      <c r="N74" s="81"/>
+      <c r="O74" s="80"/>
+      <c r="P74" s="46"/>
+      <c r="Q74" s="46"/>
+      <c r="R74" s="46"/>
+      <c r="S74" s="46"/>
       <c r="AI74" s="38"/>
       <c r="AJ74" s="38"/>
       <c r="AK74" s="50"/>
     </row>
     <row r="75" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A75"/>
+      <c r="A75" s="80"/>
       <c r="B75"/>
       <c r="C75" s="39"/>
       <c r="D75" s="39"/>
+      <c r="H75" s="77"/>
       <c r="I75"/>
       <c r="J75"/>
       <c r="K75" s="39"/>
       <c r="L75" s="39"/>
+      <c r="M75" s="80"/>
+      <c r="N75" s="80"/>
+      <c r="O75" s="80"/>
+      <c r="P75" s="46"/>
+      <c r="Q75" s="46"/>
+      <c r="R75" s="46"/>
+      <c r="S75" s="46"/>
       <c r="AI75" s="38"/>
       <c r="AJ75" s="38"/>
       <c r="AK75" s="50"/>
@@ -6696,12 +6818,10 @@
       <c r="B76"/>
       <c r="C76" s="39"/>
       <c r="D76" s="39"/>
-      <c r="H76" s="46"/>
       <c r="I76"/>
       <c r="J76"/>
       <c r="K76" s="39"/>
       <c r="L76" s="39"/>
-      <c r="O76" s="46"/>
       <c r="AI76" s="38"/>
       <c r="AJ76" s="38"/>
       <c r="AK76" s="50"/>
@@ -6711,12 +6831,10 @@
       <c r="B77"/>
       <c r="C77" s="39"/>
       <c r="D77" s="39"/>
-      <c r="H77" s="46"/>
       <c r="I77"/>
       <c r="J77"/>
       <c r="K77" s="39"/>
       <c r="L77" s="39"/>
-      <c r="O77" s="46"/>
       <c r="AI77" s="38"/>
       <c r="AJ77" s="38"/>
       <c r="AK77" s="50"/>
@@ -6921,10 +7039,12 @@
       <c r="B91"/>
       <c r="C91" s="39"/>
       <c r="D91" s="39"/>
+      <c r="H91" s="46"/>
       <c r="I91"/>
       <c r="J91"/>
       <c r="K91" s="39"/>
       <c r="L91" s="39"/>
+      <c r="O91" s="46"/>
       <c r="AI91" s="38"/>
       <c r="AJ91" s="38"/>
       <c r="AK91" s="50"/>
@@ -6934,10 +7054,12 @@
       <c r="B92"/>
       <c r="C92" s="39"/>
       <c r="D92" s="39"/>
+      <c r="H92" s="46"/>
       <c r="I92"/>
       <c r="J92"/>
       <c r="K92" s="39"/>
       <c r="L92" s="39"/>
+      <c r="O92" s="46"/>
       <c r="AI92" s="38"/>
       <c r="AJ92" s="38"/>
       <c r="AK92" s="50"/>
@@ -7295,22 +7417,38 @@
     </row>
     <row r="120" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A120"/>
+      <c r="B120"/>
+      <c r="C120" s="39"/>
+      <c r="D120" s="39"/>
+      <c r="I120"/>
+      <c r="J120"/>
+      <c r="K120" s="39"/>
+      <c r="L120" s="39"/>
       <c r="AI120" s="38"/>
       <c r="AJ120" s="38"/>
       <c r="AK120" s="50"/>
     </row>
     <row r="121" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A121"/>
+      <c r="B121"/>
+      <c r="C121" s="39"/>
+      <c r="D121" s="39"/>
+      <c r="I121"/>
+      <c r="J121"/>
+      <c r="K121" s="39"/>
+      <c r="L121" s="39"/>
       <c r="AI121" s="38"/>
       <c r="AJ121" s="38"/>
       <c r="AK121" s="50"/>
     </row>
     <row r="122" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A122"/>
       <c r="AI122" s="38"/>
       <c r="AJ122" s="38"/>
       <c r="AK122" s="50"/>
     </row>
     <row r="123" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A123"/>
       <c r="AI123" s="38"/>
       <c r="AJ123" s="38"/>
       <c r="AK123" s="50"/>
@@ -7424,6 +7562,16 @@
       <c r="AI145" s="38"/>
       <c r="AJ145" s="38"/>
       <c r="AK145" s="50"/>
+    </row>
+    <row r="146" spans="35:37" x14ac:dyDescent="0.25">
+      <c r="AI146" s="38"/>
+      <c r="AJ146" s="38"/>
+      <c r="AK146" s="50"/>
+    </row>
+    <row r="147" spans="35:37" x14ac:dyDescent="0.25">
+      <c r="AI147" s="38"/>
+      <c r="AJ147" s="38"/>
+      <c r="AK147" s="50"/>
     </row>
   </sheetData>
   <phoneticPr fontId="24" type="noConversion"/>

--- a/SubRES_TMPL/SubRES_NewTechs.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EB48BC1-051A-48F1-A643-268D386270B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20DAA749-402A-4046-9B6A-05C1A2029F7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1554,7 +1554,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="171">
   <si>
     <t>~FI_T</t>
   </si>
@@ -2064,6 +2064,9 @@
   </si>
   <si>
     <t>Electricity-based process heat-aggrigator</t>
+  </si>
+  <si>
+    <t>ELC to MANELC transformation</t>
   </si>
 </sst>
 </file>
@@ -5727,13 +5730,25 @@
       <c r="Q33" s="64"/>
       <c r="R33" s="67"/>
       <c r="S33" s="43"/>
-      <c r="V33" s="38"/>
+      <c r="V33" s="38" t="s">
+        <v>69</v>
+      </c>
       <c r="W33" s="38"/>
-      <c r="X33" s="39"/>
-      <c r="Y33" s="40"/>
-      <c r="Z33" s="38"/>
-      <c r="AA33" s="45"/>
-      <c r="AB33" s="45"/>
+      <c r="X33" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="Y33" s="40" t="s">
+        <v>170</v>
+      </c>
+      <c r="Z33" s="106" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA33" s="106" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB33" s="104" t="s">
+        <v>88</v>
+      </c>
       <c r="AC33" s="45"/>
       <c r="AD33" s="106"/>
       <c r="AI33"/>
@@ -5820,8 +5835,9 @@
       <c r="AV34" s="45"/>
     </row>
     <row r="35" spans="1:49" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="5" t="s">
-        <v>152</v>
+      <c r="B35" s="5" t="str">
+        <f>X33</f>
+        <v>MANELC_TECH</v>
       </c>
       <c r="C35" s="50" t="str">
         <f>X9</f>
@@ -7577,6 +7593,9 @@
   <phoneticPr fontId="24" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="C35" formula="1"/>
+  </ignoredErrors>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/SubRES_TMPL/SubRES_NewTechs.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20DAA749-402A-4046-9B6A-05C1A2029F7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A15B212-36D6-4A0C-B8EE-086BF3658306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PRI_Sector_Fuels" sheetId="6" r:id="rId1"/>
@@ -1125,7 +1125,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V18" authorId="2" shapeId="0" xr:uid="{BAA0F8AB-741B-4302-9E54-000CB5DC4ACF}">
+    <comment ref="V19" authorId="2" shapeId="0" xr:uid="{BAA0F8AB-741B-4302-9E54-000CB5DC4ACF}">
       <text>
         <r>
           <rPr>
@@ -1368,7 +1368,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB18" authorId="2" shapeId="0" xr:uid="{5EE58488-723F-4683-9026-2F0EE70F8071}">
+    <comment ref="AB19" authorId="2" shapeId="0" xr:uid="{5EE58488-723F-4683-9026-2F0EE70F8071}">
       <text>
         <r>
           <rPr>
@@ -1461,7 +1461,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC18" authorId="1" shapeId="0" xr:uid="{308E9284-8F99-498B-A3DD-262799AF67EB}">
+    <comment ref="AC19" authorId="1" shapeId="0" xr:uid="{308E9284-8F99-498B-A3DD-262799AF67EB}">
       <text>
         <r>
           <rPr>
@@ -1486,7 +1486,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AD18" authorId="2" shapeId="0" xr:uid="{FD29F772-15B8-47C4-8D7A-88CCF8F71647}">
+    <comment ref="AD19" authorId="2" shapeId="0" xr:uid="{FD29F772-15B8-47C4-8D7A-88CCF8F71647}">
       <text>
         <r>
           <rPr>
@@ -1554,7 +1554,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="172">
   <si>
     <t>~FI_T</t>
   </si>
@@ -2018,30 +2018,18 @@
     <t>MANELC</t>
   </si>
   <si>
-    <t>DECHEAT</t>
-  </si>
-  <si>
     <t>DECPOWER</t>
   </si>
   <si>
     <t>RNWHEAT</t>
   </si>
   <si>
-    <t>Renewable Heat Aggrigator</t>
-  </si>
-  <si>
     <t>RNWTHT</t>
   </si>
   <si>
     <t>Grid electricity-based heat</t>
   </si>
   <si>
-    <t>GTHT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grid Electricity Based Heat Aggregator </t>
-  </si>
-  <si>
     <t>GEHEAT</t>
   </si>
   <si>
@@ -2067,6 +2055,21 @@
   </si>
   <si>
     <t>ELC to MANELC transformation</t>
+  </si>
+  <si>
+    <t>DECRHEAT</t>
+  </si>
+  <si>
+    <t>Renewable Heat Aggrigator from all renewables including elc</t>
+  </si>
+  <si>
+    <t>HEAt</t>
+  </si>
+  <si>
+    <t>PTHT</t>
+  </si>
+  <si>
+    <t>Manufacturing process heat aggrigator</t>
   </si>
 </sst>
 </file>
@@ -2078,7 +2081,7 @@
     <numFmt numFmtId="165" formatCode="\Te\x\t"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="30" x14ac:knownFonts="1">
+  <fonts count="32" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -2265,6 +2268,19 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="12">
     <fill>
@@ -2404,7 +2420,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="113">
+  <cellXfs count="127">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
@@ -2596,6 +2612,22 @@
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="0" xfId="4" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="4" applyFont="1"/>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="30" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="30" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="30" fillId="8" borderId="0" xfId="21" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="30" fillId="8" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="31" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="28" fillId="8" borderId="0" xfId="21" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="28" fillId="8" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="22">
     <cellStyle name="20% - Accent5 2" xfId="18" xr:uid="{4C3A48E2-3C46-4D12-9A64-54698D8BF8EE}"/>
@@ -4066,7 +4098,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3360854E-4C4D-467D-BD8A-32231E61C6CE}">
-  <dimension ref="A1:AY147"/>
+  <dimension ref="A1:AY148"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" style="45" customWidth="1"/>
@@ -4085,7 +4117,7 @@
     <col min="20" max="21" width="8.21875" style="46" customWidth="1"/>
     <col min="22" max="22" width="12.77734375" style="45" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="7.21875" style="45" customWidth="1"/>
-    <col min="24" max="24" width="13.44140625" style="45" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5546875" style="45" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="63.77734375" style="45" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="8.21875" style="45" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="11.77734375" style="45" customWidth="1"/>
@@ -4102,7 +4134,7 @@
     <col min="45" max="16384" width="8.77734375" style="45"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:49" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:31" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B1" s="44" t="s">
         <v>38</v>
       </c>
@@ -4123,7 +4155,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="2:49" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:31" ht="31.2" x14ac:dyDescent="0.3">
       <c r="B2" s="47" t="s">
         <v>92</v>
       </c>
@@ -4156,7 +4188,7 @@
       <c r="AC2" s="50"/>
       <c r="AD2" s="50"/>
     </row>
-    <row r="3" spans="2:49" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:31" x14ac:dyDescent="0.25">
       <c r="V3" s="51" t="s">
         <v>8</v>
       </c>
@@ -4185,7 +4217,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="2:49" ht="22.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:31" ht="22.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="53"/>
       <c r="C4" s="53"/>
       <c r="D4" s="53"/>
@@ -4220,7 +4252,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="2:49" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:31" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B5" s="53"/>
       <c r="C5" s="53"/>
       <c r="D5" s="53"/>
@@ -4243,7 +4275,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="6" spans="2:49" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:31" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B6" s="53"/>
       <c r="C6" s="53"/>
       <c r="D6" s="53"/>
@@ -4266,7 +4298,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="2:49" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:31" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B7" s="53"/>
       <c r="C7" s="53"/>
       <c r="D7" s="53"/>
@@ -4289,16 +4321,16 @@
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="2:49" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:31" x14ac:dyDescent="0.25">
       <c r="V8" s="50" t="s">
         <v>139</v>
       </c>
       <c r="W8" s="50"/>
       <c r="X8" s="50" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="Y8" s="50" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="Z8" s="76" t="s">
         <v>58</v>
@@ -4308,7 +4340,7 @@
       </c>
       <c r="AE8" s="46"/>
     </row>
-    <row r="9" spans="2:49" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:31" x14ac:dyDescent="0.25">
       <c r="V9" s="50" t="s">
         <v>69</v>
       </c>
@@ -4329,15 +4361,15 @@
       <c r="AC9" s="50"/>
       <c r="AD9" s="50"/>
     </row>
-    <row r="10" spans="2:49" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:31" x14ac:dyDescent="0.25">
       <c r="V10" s="45" t="s">
         <v>139</v>
       </c>
       <c r="X10" s="45" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="Y10" s="45" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="Z10" s="76" t="s">
         <v>58</v>
@@ -4349,15 +4381,15 @@
       <c r="AC10" s="50"/>
       <c r="AD10" s="50"/>
     </row>
-    <row r="11" spans="2:49" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:31" x14ac:dyDescent="0.25">
       <c r="V11" s="45" t="s">
         <v>139</v>
       </c>
       <c r="X11" s="45" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="Y11" s="45" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="Z11" s="76" t="s">
         <v>58</v>
@@ -4366,15 +4398,15 @@
         <v>88</v>
       </c>
     </row>
-    <row r="12" spans="2:49" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:31" x14ac:dyDescent="0.25">
       <c r="V12" s="45" t="s">
         <v>139</v>
       </c>
       <c r="X12" s="45" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="Y12" s="45" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="Z12" s="76" t="s">
         <v>58</v>
@@ -4383,15 +4415,15 @@
         <v>88</v>
       </c>
     </row>
-    <row r="13" spans="2:49" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:31" x14ac:dyDescent="0.25">
       <c r="V13" s="45" t="s">
         <v>139</v>
       </c>
       <c r="X13" s="45" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="Y13" s="45" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="Z13" s="76" t="s">
         <v>58</v>
@@ -4400,117 +4432,31 @@
         <v>88</v>
       </c>
     </row>
-    <row r="14" spans="2:49" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:31" x14ac:dyDescent="0.25">
       <c r="Z14" s="76"/>
       <c r="AB14" s="76"/>
     </row>
-    <row r="15" spans="2:49" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:31" x14ac:dyDescent="0.25">
+      <c r="Z15" s="76"/>
       <c r="AB15" s="76"/>
     </row>
-    <row r="16" spans="2:49" x14ac:dyDescent="0.25">
-      <c r="D16" s="55" t="s">
+    <row r="16" spans="2:31" x14ac:dyDescent="0.25">
+      <c r="AB16" s="76"/>
+    </row>
+    <row r="17" spans="2:51" x14ac:dyDescent="0.25">
+      <c r="D17" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="E16" s="55"/>
-      <c r="F16" s="55"/>
-      <c r="H16" s="55"/>
-      <c r="V16" s="49" t="s">
+      <c r="E17" s="55"/>
+      <c r="F17" s="55"/>
+      <c r="H17" s="55"/>
+      <c r="V17" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="W16" s="49"/>
-      <c r="X16" s="50"/>
-      <c r="Y16" s="50"/>
-      <c r="Z16" s="50"/>
-      <c r="AI16"/>
-      <c r="AJ16" s="39"/>
-      <c r="AK16" s="76"/>
-      <c r="AL16" s="76"/>
-      <c r="AM16" s="76"/>
-      <c r="AN16" s="76"/>
-      <c r="AO16" s="76"/>
-      <c r="AP16" s="76"/>
-      <c r="AQ16" s="76"/>
-      <c r="AR16" s="76"/>
-      <c r="AS16" s="76"/>
-      <c r="AT16" s="76"/>
-      <c r="AU16" s="76"/>
-      <c r="AV16" s="76"/>
-      <c r="AW16" s="76"/>
-    </row>
-    <row r="17" spans="2:51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="C17" s="56" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="56" t="s">
-        <v>4</v>
-      </c>
-      <c r="E17" s="57" t="s">
-        <v>113</v>
-      </c>
-      <c r="F17" s="57" t="s">
-        <v>16</v>
-      </c>
-      <c r="G17" s="57" t="s">
-        <v>34</v>
-      </c>
-      <c r="H17" s="57" t="s">
-        <v>47</v>
-      </c>
-      <c r="I17" s="57" t="s">
-        <v>36</v>
-      </c>
-      <c r="J17" s="59" t="s">
-        <v>5</v>
-      </c>
-      <c r="K17" s="59" t="s">
-        <v>98</v>
-      </c>
-      <c r="L17" s="57" t="s">
-        <v>56</v>
-      </c>
-      <c r="M17" s="59" t="s">
-        <v>103</v>
-      </c>
-      <c r="N17" s="58" t="s">
-        <v>112</v>
-      </c>
-      <c r="O17" s="59" t="s">
-        <v>115</v>
-      </c>
-      <c r="P17" s="59" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q17" s="59" t="s">
-        <v>117</v>
-      </c>
-      <c r="R17" s="59" t="s">
-        <v>118</v>
-      </c>
-      <c r="S17" s="59" t="s">
-        <v>126</v>
-      </c>
-      <c r="V17" s="51" t="s">
-        <v>15</v>
-      </c>
-      <c r="W17" s="52" t="s">
-        <v>42</v>
-      </c>
-      <c r="X17" s="51" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y17" s="51" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z17" s="51" t="s">
-        <v>18</v>
-      </c>
-      <c r="AA17" s="50"/>
-      <c r="AB17" s="50"/>
-      <c r="AC17" s="50"/>
-      <c r="AD17" s="50"/>
+      <c r="W17" s="49"/>
+      <c r="X17" s="50"/>
+      <c r="Y17" s="50"/>
+      <c r="Z17" s="50"/>
       <c r="AI17"/>
       <c r="AJ17" s="39"/>
       <c r="AK17" s="76"/>
@@ -4526,586 +4472,596 @@
       <c r="AU17" s="76"/>
       <c r="AV17" s="76"/>
       <c r="AW17" s="76"/>
-      <c r="AY17" s="46"/>
-    </row>
-    <row r="18" spans="2:51" ht="31.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="32" t="s">
-        <v>48</v>
-      </c>
-      <c r="C18" s="32" t="s">
-        <v>32</v>
-      </c>
-      <c r="D18" s="32" t="s">
-        <v>33</v>
-      </c>
-      <c r="E18" s="32" t="s">
-        <v>54</v>
-      </c>
-      <c r="F18" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="G18" s="33" t="s">
-        <v>49</v>
-      </c>
-      <c r="H18" s="32" t="s">
-        <v>57</v>
-      </c>
-      <c r="I18" s="32" t="s">
-        <v>86</v>
-      </c>
-      <c r="J18" s="33" t="s">
-        <v>37</v>
-      </c>
-      <c r="K18" s="33" t="s">
-        <v>99</v>
-      </c>
-      <c r="L18" s="33" t="s">
-        <v>80</v>
-      </c>
-      <c r="M18" s="33" t="s">
-        <v>104</v>
-      </c>
-      <c r="N18" s="32" t="s">
-        <v>85</v>
-      </c>
-      <c r="O18" s="33" t="s">
-        <v>114</v>
-      </c>
-      <c r="P18" s="33" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q18" s="33" t="s">
-        <v>114</v>
-      </c>
-      <c r="R18" s="74" t="s">
-        <v>114</v>
-      </c>
-      <c r="S18" s="74" t="s">
-        <v>127</v>
-      </c>
-      <c r="V18" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="W18" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="X18" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y18" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z18" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="AA18" s="51" t="s">
-        <v>19</v>
-      </c>
-      <c r="AB18" s="51" t="s">
-        <v>20</v>
-      </c>
-      <c r="AC18" s="51" t="s">
-        <v>21</v>
-      </c>
-      <c r="AD18" s="51" t="s">
-        <v>22</v>
-      </c>
+    </row>
+    <row r="18" spans="2:51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="56" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="E18" s="57" t="s">
+        <v>113</v>
+      </c>
+      <c r="F18" s="57" t="s">
+        <v>16</v>
+      </c>
+      <c r="G18" s="57" t="s">
+        <v>34</v>
+      </c>
+      <c r="H18" s="57" t="s">
+        <v>47</v>
+      </c>
+      <c r="I18" s="57" t="s">
+        <v>36</v>
+      </c>
+      <c r="J18" s="59" t="s">
+        <v>5</v>
+      </c>
+      <c r="K18" s="59" t="s">
+        <v>98</v>
+      </c>
+      <c r="L18" s="57" t="s">
+        <v>56</v>
+      </c>
+      <c r="M18" s="59" t="s">
+        <v>103</v>
+      </c>
+      <c r="N18" s="58" t="s">
+        <v>112</v>
+      </c>
+      <c r="O18" s="59" t="s">
+        <v>115</v>
+      </c>
+      <c r="P18" s="59" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q18" s="59" t="s">
+        <v>117</v>
+      </c>
+      <c r="R18" s="59" t="s">
+        <v>118</v>
+      </c>
+      <c r="S18" s="59" t="s">
+        <v>126</v>
+      </c>
+      <c r="V18" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="W18" s="52" t="s">
+        <v>42</v>
+      </c>
+      <c r="X18" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y18" s="51" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z18" s="51" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA18" s="50"/>
+      <c r="AB18" s="50"/>
+      <c r="AC18" s="50"/>
+      <c r="AD18" s="50"/>
       <c r="AI18"/>
       <c r="AJ18" s="39"/>
+      <c r="AK18" s="76"/>
+      <c r="AL18" s="76"/>
+      <c r="AM18" s="76"/>
+      <c r="AN18" s="76"/>
+      <c r="AO18" s="76"/>
+      <c r="AP18" s="76"/>
+      <c r="AQ18" s="76"/>
+      <c r="AR18" s="76"/>
+      <c r="AS18" s="76"/>
+      <c r="AT18" s="76"/>
+      <c r="AU18" s="76"/>
+      <c r="AV18" s="76"/>
+      <c r="AW18" s="76"/>
       <c r="AY18" s="46"/>
     </row>
-    <row r="19" spans="2:51" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="C19" s="34"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="36"/>
-      <c r="H19" s="35" t="s">
+    <row r="19" spans="2:51" ht="31.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="E19" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="I19" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="J19" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="K19" s="35" t="s">
-        <v>134</v>
-      </c>
-      <c r="L19" s="36"/>
-      <c r="M19" s="36" t="s">
-        <v>105</v>
-      </c>
-      <c r="N19" s="35"/>
-      <c r="O19" s="36"/>
-      <c r="P19" s="36"/>
-      <c r="Q19" s="36"/>
-      <c r="R19" s="35"/>
-      <c r="S19" s="75"/>
+      <c r="F19" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="G19" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="H19" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="I19" s="32" t="s">
+        <v>86</v>
+      </c>
+      <c r="J19" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="K19" s="33" t="s">
+        <v>99</v>
+      </c>
+      <c r="L19" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="M19" s="33" t="s">
+        <v>104</v>
+      </c>
+      <c r="N19" s="32" t="s">
+        <v>85</v>
+      </c>
+      <c r="O19" s="33" t="s">
+        <v>114</v>
+      </c>
+      <c r="P19" s="33" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q19" s="33" t="s">
+        <v>114</v>
+      </c>
+      <c r="R19" s="74" t="s">
+        <v>114</v>
+      </c>
+      <c r="S19" s="74" t="s">
+        <v>127</v>
+      </c>
       <c r="V19" s="31" t="s">
-        <v>81</v>
-      </c>
-      <c r="W19" s="31"/>
-      <c r="X19" s="31"/>
-      <c r="Y19" s="31"/>
-      <c r="Z19" s="31"/>
-      <c r="AA19" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB19" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="AC19" s="31" t="s">
-        <v>52</v>
-      </c>
-      <c r="AD19" s="31" t="s">
-        <v>31</v>
+        <v>50</v>
+      </c>
+      <c r="W19" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="X19" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y19" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z19" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA19" s="51" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB19" s="51" t="s">
+        <v>20</v>
+      </c>
+      <c r="AC19" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="AD19" s="51" t="s">
+        <v>22</v>
       </c>
       <c r="AI19"/>
       <c r="AJ19" s="39"/>
       <c r="AY19" s="46"/>
     </row>
-    <row r="20" spans="2:51" s="85" customFormat="1" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="85" t="str">
-        <f>X20</f>
+    <row r="20" spans="2:51" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" s="34"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="35"/>
+      <c r="G20" s="36"/>
+      <c r="H20" s="35" t="s">
+        <v>54</v>
+      </c>
+      <c r="I20" s="35" t="s">
+        <v>111</v>
+      </c>
+      <c r="J20" s="35" t="s">
+        <v>111</v>
+      </c>
+      <c r="K20" s="35" t="s">
+        <v>134</v>
+      </c>
+      <c r="L20" s="36"/>
+      <c r="M20" s="36" t="s">
+        <v>105</v>
+      </c>
+      <c r="N20" s="35"/>
+      <c r="O20" s="36"/>
+      <c r="P20" s="36"/>
+      <c r="Q20" s="36"/>
+      <c r="R20" s="35"/>
+      <c r="S20" s="75"/>
+      <c r="V20" s="31" t="s">
+        <v>81</v>
+      </c>
+      <c r="W20" s="31"/>
+      <c r="X20" s="31"/>
+      <c r="Y20" s="31"/>
+      <c r="Z20" s="31"/>
+      <c r="AA20" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB20" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="AC20" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD20" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI20"/>
+      <c r="AJ20" s="39"/>
+      <c r="AY20" s="46"/>
+    </row>
+    <row r="21" spans="2:51" s="85" customFormat="1" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="85" t="str">
+        <f>X21</f>
         <v>Furnace</v>
       </c>
-      <c r="C20" s="85" t="s">
+      <c r="C21" s="85" t="s">
         <v>69</v>
       </c>
-      <c r="D20" s="86" t="str">
+      <c r="D21" s="86" t="str">
         <f>X11</f>
         <v>GEHEAT</v>
       </c>
-      <c r="E20" s="87">
+      <c r="E21" s="87">
         <v>2030</v>
       </c>
-      <c r="F20" s="88">
+      <c r="F21" s="88">
         <v>1</v>
       </c>
-      <c r="G20" s="88">
+      <c r="G21" s="88">
         <v>1</v>
       </c>
-      <c r="H20" s="87">
+      <c r="H21" s="87">
         <v>25</v>
       </c>
-      <c r="I20" s="88">
+      <c r="I21" s="88">
         <v>81</v>
       </c>
-      <c r="J20" s="88">
+      <c r="J21" s="88">
         <v>0</v>
       </c>
-      <c r="K20" s="88">
+      <c r="K21" s="88">
         <v>0.24</v>
       </c>
-      <c r="L20" s="88">
+      <c r="L21" s="88">
         <v>8.76</v>
       </c>
-      <c r="M20" s="87"/>
-      <c r="N20" s="88">
+      <c r="M21" s="87"/>
+      <c r="N21" s="88">
         <v>0.1</v>
       </c>
-      <c r="O20" s="88">
+      <c r="O21" s="88">
         <v>0.15</v>
       </c>
-      <c r="P20" s="88">
+      <c r="P21" s="88">
         <v>0.2</v>
       </c>
-      <c r="Q20" s="88">
+      <c r="Q21" s="88">
         <v>0.25</v>
       </c>
-      <c r="R20" s="88">
+      <c r="R21" s="88">
         <v>0.35</v>
       </c>
-      <c r="S20" s="87"/>
-      <c r="T20" s="89"/>
-      <c r="U20" s="89"/>
-      <c r="V20" s="90" t="s">
+      <c r="S21" s="87"/>
+      <c r="T21" s="89"/>
+      <c r="U21" s="89"/>
+      <c r="V21" s="90" t="s">
         <v>139</v>
       </c>
-      <c r="W20" s="90"/>
-      <c r="X20" s="91" t="s">
+      <c r="W21" s="90"/>
+      <c r="X21" s="91" t="s">
         <v>66</v>
       </c>
-      <c r="Y20" s="92" t="s">
+      <c r="Y21" s="92" t="s">
         <v>140</v>
       </c>
-      <c r="Z20" s="85" t="s">
+      <c r="Z21" s="85" t="s">
         <v>58</v>
       </c>
-      <c r="AA20" s="31" t="s">
+      <c r="AA21" s="31" t="s">
         <v>87</v>
       </c>
-      <c r="AB20" s="31" t="s">
+      <c r="AB21" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="AC20" s="31"/>
-      <c r="AD20" s="31"/>
-      <c r="AI20" s="94"/>
-      <c r="AJ20" s="95"/>
-      <c r="AY20" s="89"/>
-    </row>
-    <row r="21" spans="2:51" s="76" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="76" t="str">
-        <f>X$21</f>
+      <c r="AC21" s="31"/>
+      <c r="AD21" s="31"/>
+      <c r="AI21" s="94"/>
+      <c r="AJ21" s="95"/>
+      <c r="AY21" s="89"/>
+    </row>
+    <row r="22" spans="2:51" s="76" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="76" t="str">
+        <f>X$22</f>
         <v>BIOBoiler</v>
       </c>
-      <c r="C21" s="76" t="str">
+      <c r="C22" s="76" t="str">
         <f>PRI_Sector_Fuels!P5</f>
         <v>MANBIOMIN</v>
       </c>
-      <c r="D21" s="83" t="str">
+      <c r="D22" s="83" t="str">
         <f>X8</f>
-        <v>DECHEAT</v>
-      </c>
-      <c r="E21" s="96">
+        <v>DECRHEAT</v>
+      </c>
+      <c r="E22" s="96">
         <v>2030</v>
       </c>
-      <c r="F21" s="82">
+      <c r="F22" s="82">
         <v>0.7</v>
       </c>
-      <c r="G21" s="82">
+      <c r="G22" s="82">
         <v>0.98</v>
       </c>
-      <c r="H21" s="96">
+      <c r="H22" s="96">
         <v>25</v>
       </c>
-      <c r="I21" s="82">
+      <c r="I22" s="82">
         <v>797.9</v>
       </c>
-      <c r="J21" s="82">
+      <c r="J22" s="82">
         <v>48.48</v>
       </c>
-      <c r="K21" s="82">
+      <c r="K22" s="82">
         <v>3.75</v>
       </c>
-      <c r="L21" s="82">
+      <c r="L22" s="82">
         <v>8.76</v>
       </c>
-      <c r="M21" s="96"/>
-      <c r="N21" s="97"/>
-      <c r="O21" s="96"/>
-      <c r="P21" s="96"/>
-      <c r="Q21" s="96"/>
-      <c r="R21" s="96"/>
-      <c r="S21" s="96"/>
-      <c r="T21" s="98"/>
-      <c r="U21" s="98"/>
-      <c r="V21" s="84" t="s">
+      <c r="M22" s="96"/>
+      <c r="N22" s="97"/>
+      <c r="O22" s="96"/>
+      <c r="P22" s="96"/>
+      <c r="Q22" s="96"/>
+      <c r="R22" s="96"/>
+      <c r="S22" s="96"/>
+      <c r="T22" s="98"/>
+      <c r="U22" s="98"/>
+      <c r="V22" s="84" t="s">
         <v>139</v>
       </c>
-      <c r="W21" s="84"/>
-      <c r="X21" s="99" t="s">
+      <c r="W22" s="84"/>
+      <c r="X22" s="99" t="s">
         <v>94</v>
       </c>
-      <c r="Y21" s="100" t="s">
+      <c r="Y22" s="100" t="s">
         <v>141</v>
       </c>
-      <c r="Z21" s="76" t="s">
+      <c r="Z22" s="76" t="s">
         <v>58</v>
       </c>
-      <c r="AA21" s="85" t="s">
+      <c r="AA22" s="85" t="s">
         <v>87</v>
       </c>
-      <c r="AB21" s="93" t="s">
+      <c r="AB22" s="93" t="s">
         <v>88</v>
       </c>
-      <c r="AC21" s="89"/>
-      <c r="AD21" s="89"/>
-      <c r="AI21" s="14"/>
-      <c r="AJ21" s="12"/>
-      <c r="AY21" s="98"/>
-    </row>
-    <row r="22" spans="2:51" s="85" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="85" t="str">
-        <f>X24</f>
+      <c r="AC22" s="89"/>
+      <c r="AD22" s="89"/>
+      <c r="AI22" s="14"/>
+      <c r="AJ22" s="12"/>
+      <c r="AY22" s="98"/>
+    </row>
+    <row r="23" spans="2:51" s="85" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="85" t="str">
+        <f>X25</f>
         <v>ELCBoiler</v>
       </c>
-      <c r="C22" s="85" t="s">
+      <c r="C23" s="85" t="s">
         <v>69</v>
       </c>
-      <c r="D22" s="86" t="str">
+      <c r="D23" s="86" t="str">
         <f>X11</f>
         <v>GEHEAT</v>
       </c>
-      <c r="E22" s="87">
+      <c r="E23" s="87">
         <v>2030</v>
       </c>
-      <c r="F22" s="88">
+      <c r="F23" s="88">
         <v>0.99</v>
       </c>
-      <c r="G22" s="88">
+      <c r="G23" s="88">
         <v>1</v>
       </c>
-      <c r="H22" s="87">
+      <c r="H23" s="87">
         <v>25</v>
       </c>
-      <c r="I22" s="88">
+      <c r="I23" s="88">
         <v>112.9</v>
       </c>
-      <c r="J22" s="88">
+      <c r="J23" s="88">
         <v>14.26</v>
       </c>
-      <c r="K22" s="88">
+      <c r="K23" s="88">
         <v>1.22</v>
       </c>
-      <c r="L22" s="88">
+      <c r="L23" s="88">
         <v>8.76</v>
       </c>
-      <c r="M22" s="87"/>
-      <c r="S22" s="87"/>
-      <c r="T22" s="89"/>
-      <c r="U22" s="89"/>
-      <c r="V22" s="90" t="s">
+      <c r="M23" s="87"/>
+      <c r="S23" s="87"/>
+      <c r="T23" s="89"/>
+      <c r="U23" s="89"/>
+      <c r="V23" s="90" t="s">
         <v>128</v>
       </c>
-      <c r="W22" s="90"/>
-      <c r="X22" s="91" t="s">
+      <c r="W23" s="90"/>
+      <c r="X23" s="91" t="s">
         <v>95</v>
       </c>
-      <c r="Y22" s="92" t="s">
+      <c r="Y23" s="92" t="s">
         <v>142</v>
       </c>
-      <c r="Z22" s="85" t="s">
+      <c r="Z23" s="85" t="s">
         <v>58</v>
       </c>
-      <c r="AA22" s="76" t="s">
+      <c r="AA23" s="76" t="s">
         <v>87</v>
       </c>
-      <c r="AB22" s="101" t="s">
+      <c r="AB23" s="101" t="s">
         <v>88</v>
       </c>
-      <c r="AC22" s="98"/>
-      <c r="AD22" s="98"/>
-      <c r="AI22" s="94"/>
-      <c r="AJ22" s="95"/>
-      <c r="AY22" s="89"/>
-    </row>
-    <row r="23" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="45" t="str">
-        <f>X22</f>
+      <c r="AC23" s="98"/>
+      <c r="AD23" s="98"/>
+      <c r="AI23" s="94"/>
+      <c r="AJ23" s="95"/>
+      <c r="AY23" s="89"/>
+    </row>
+    <row r="24" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="45" t="str">
+        <f>X23</f>
         <v>BIOKiln</v>
       </c>
-      <c r="C23" s="45" t="str">
+      <c r="C24" s="45" t="str">
         <f>PRI_Sector_Fuels!P5</f>
         <v>MANBIOMIN</v>
       </c>
-      <c r="D23" s="50" t="s">
+      <c r="D24" s="50" t="s">
         <v>108</v>
       </c>
-      <c r="E23" s="43">
+      <c r="E24" s="43">
         <v>2030</v>
       </c>
-      <c r="F23" s="64">
+      <c r="F24" s="64">
         <v>0.55600000000000005</v>
       </c>
-      <c r="G23" s="64">
+      <c r="G24" s="64">
         <v>0.98</v>
       </c>
-      <c r="H23" s="43">
+      <c r="H24" s="43">
         <v>25</v>
       </c>
-      <c r="I23" s="64">
+      <c r="I24" s="64">
         <v>297.10000000000002</v>
       </c>
-      <c r="J23" s="64">
+      <c r="J24" s="64">
         <v>4.46</v>
       </c>
-      <c r="K23" s="64">
+      <c r="K24" s="64">
         <v>0.45</v>
       </c>
-      <c r="L23" s="64">
+      <c r="L24" s="64">
         <v>8.76</v>
       </c>
-      <c r="M23" s="43"/>
-      <c r="N23" s="64">
+      <c r="M24" s="43"/>
+      <c r="N24" s="64">
         <v>0.1</v>
       </c>
-      <c r="O23" s="64">
+      <c r="O24" s="64">
         <v>0.15</v>
       </c>
-      <c r="P23" s="64">
+      <c r="P24" s="64">
         <v>0.2</v>
       </c>
-      <c r="Q23" s="64">
+      <c r="Q24" s="64">
         <v>0.25</v>
       </c>
-      <c r="R23" s="64">
+      <c r="R24" s="64">
         <v>0.35</v>
       </c>
-      <c r="S23" s="43"/>
-      <c r="V23" s="60" t="s">
+      <c r="S24" s="43"/>
+      <c r="V24" s="60" t="s">
         <v>128</v>
       </c>
-      <c r="W23" s="60"/>
-      <c r="X23" s="61" t="s">
+      <c r="W24" s="60"/>
+      <c r="X24" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="Y23" s="62" t="s">
+      <c r="Y24" s="62" t="s">
         <v>143</v>
       </c>
-      <c r="Z23" s="45" t="s">
+      <c r="Z24" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="AA23" s="85" t="s">
+      <c r="AA24" s="85" t="s">
         <v>87</v>
       </c>
-      <c r="AB23" s="93" t="s">
+      <c r="AB24" s="93" t="s">
         <v>88</v>
       </c>
-      <c r="AC23" s="89"/>
-      <c r="AD23" s="89"/>
-      <c r="AI23"/>
-      <c r="AJ23"/>
-      <c r="AK23" s="45"/>
-      <c r="AL23" s="45"/>
-      <c r="AM23" s="45"/>
-      <c r="AN23" s="45"/>
-      <c r="AO23" s="45"/>
-      <c r="AP23" s="45"/>
-      <c r="AQ23" s="45"/>
-      <c r="AR23" s="45"/>
-      <c r="AS23" s="45"/>
-      <c r="AT23" s="45"/>
-      <c r="AU23" s="45"/>
-      <c r="AV23" s="45"/>
-      <c r="AW23" s="45"/>
-    </row>
-    <row r="24" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="50" t="str">
-        <f>X23</f>
+      <c r="AC24" s="89"/>
+      <c r="AD24" s="89"/>
+      <c r="AI24"/>
+      <c r="AJ24"/>
+      <c r="AK24" s="45"/>
+      <c r="AL24" s="45"/>
+      <c r="AM24" s="45"/>
+      <c r="AN24" s="45"/>
+      <c r="AO24" s="45"/>
+      <c r="AP24" s="45"/>
+      <c r="AQ24" s="45"/>
+      <c r="AR24" s="45"/>
+      <c r="AS24" s="45"/>
+      <c r="AT24" s="45"/>
+      <c r="AU24" s="45"/>
+      <c r="AV24" s="45"/>
+      <c r="AW24" s="45"/>
+    </row>
+    <row r="25" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="50" t="str">
+        <f>X24</f>
         <v>GASBoiler</v>
       </c>
-      <c r="C24" s="45" t="str">
+      <c r="C25" s="45" t="str">
         <f>PRI_Sector_Fuels!P6</f>
         <v>MANGASMIN</v>
       </c>
-      <c r="D24" s="50" t="s">
+      <c r="D25" s="50" t="s">
         <v>107</v>
-      </c>
-      <c r="E24" s="43">
-        <v>2030</v>
-      </c>
-      <c r="F24" s="64">
-        <v>0.75</v>
-      </c>
-      <c r="G24" s="64">
-        <v>0.99</v>
-      </c>
-      <c r="H24" s="43">
-        <v>25</v>
-      </c>
-      <c r="I24" s="64">
-        <v>61.4</v>
-      </c>
-      <c r="J24" s="64">
-        <v>2.57</v>
-      </c>
-      <c r="K24" s="64">
-        <v>1.35</v>
-      </c>
-      <c r="L24" s="64">
-        <v>8.76</v>
-      </c>
-      <c r="M24" s="43"/>
-      <c r="N24" s="67"/>
-      <c r="O24" s="43"/>
-      <c r="P24" s="43"/>
-      <c r="Q24" s="43"/>
-      <c r="R24" s="43"/>
-      <c r="S24" s="43"/>
-      <c r="V24" s="60" t="s">
-        <v>139</v>
-      </c>
-      <c r="W24" s="60"/>
-      <c r="X24" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="Y24" s="62" t="s">
-        <v>144</v>
-      </c>
-      <c r="Z24" s="45" t="s">
-        <v>58</v>
-      </c>
-      <c r="AA24" s="45" t="s">
-        <v>87</v>
-      </c>
-      <c r="AB24" s="63" t="s">
-        <v>88</v>
-      </c>
-      <c r="AI24"/>
-      <c r="AJ24"/>
-      <c r="AK24" s="76"/>
-      <c r="AL24" s="76"/>
-      <c r="AM24" s="76"/>
-      <c r="AN24" s="76"/>
-      <c r="AO24" s="76"/>
-      <c r="AP24" s="76"/>
-      <c r="AQ24" s="76"/>
-      <c r="AR24" s="76"/>
-      <c r="AS24" s="76"/>
-      <c r="AT24" s="76"/>
-      <c r="AU24" s="76"/>
-      <c r="AV24" s="76"/>
-      <c r="AW24" s="76"/>
-    </row>
-    <row r="25" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="50" t="str">
-        <f>X26</f>
-        <v>WNDTRBN</v>
-      </c>
-      <c r="C25" s="45" t="str">
-        <f>PRI_Sector_Fuels!D19</f>
-        <v>WIND</v>
-      </c>
-      <c r="D25" s="50" t="s">
-        <v>130</v>
       </c>
       <c r="E25" s="43">
         <v>2030</v>
       </c>
-      <c r="F25" s="82">
-        <v>1</v>
+      <c r="F25" s="64">
+        <v>0.75</v>
       </c>
       <c r="G25" s="64">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="H25" s="43">
         <v>25</v>
       </c>
       <c r="I25" s="64">
-        <v>1041</v>
+        <v>61.4</v>
       </c>
       <c r="J25" s="64">
-        <v>38</v>
+        <v>2.57</v>
       </c>
       <c r="K25" s="64">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="L25" s="64">
         <v>8.76</v>
       </c>
-      <c r="M25" s="67"/>
+      <c r="M25" s="43"/>
       <c r="N25" s="67"/>
-      <c r="O25" s="64"/>
-      <c r="P25" s="64"/>
-      <c r="Q25" s="64"/>
-      <c r="R25" s="67"/>
-      <c r="S25" s="43">
-        <v>0.2</v>
-      </c>
+      <c r="O25" s="43"/>
+      <c r="P25" s="43"/>
+      <c r="Q25" s="43"/>
+      <c r="R25" s="43"/>
+      <c r="S25" s="43"/>
       <c r="V25" s="60" t="s">
         <v>139</v>
       </c>
       <c r="W25" s="60"/>
       <c r="X25" s="61" t="s">
-        <v>65</v>
+        <v>97</v>
       </c>
       <c r="Y25" s="62" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Z25" s="45" t="s">
         <v>58</v>
@@ -5135,32 +5091,32 @@
     <row r="26" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B26" s="50" t="str">
         <f>X27</f>
-        <v>SOLPV</v>
+        <v>WNDTRBN</v>
       </c>
       <c r="C26" s="45" t="str">
-        <f>PRI_Sector_Fuels!D20</f>
-        <v>SOLAR</v>
+        <f>PRI_Sector_Fuels!D19</f>
+        <v>WIND</v>
       </c>
       <c r="D26" s="50" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E26" s="43">
         <v>2030</v>
       </c>
       <c r="F26" s="82">
-        <v>0.20499999999999999</v>
+        <v>1</v>
       </c>
       <c r="G26" s="64">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="H26" s="43">
         <v>25</v>
       </c>
       <c r="I26" s="64">
-        <v>691</v>
+        <v>1041</v>
       </c>
       <c r="J26" s="64">
-        <v>6.99</v>
+        <v>38</v>
       </c>
       <c r="K26" s="64">
         <v>0</v>
@@ -5175,17 +5131,17 @@
       <c r="Q26" s="64"/>
       <c r="R26" s="67"/>
       <c r="S26" s="43">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="V26" s="60" t="s">
-        <v>69</v>
+        <v>139</v>
       </c>
       <c r="W26" s="60"/>
       <c r="X26" s="61" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="Y26" s="62" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Z26" s="45" t="s">
         <v>58</v>
@@ -5193,80 +5149,81 @@
       <c r="AA26" s="45" t="s">
         <v>87</v>
       </c>
-      <c r="AB26" s="46" t="s">
+      <c r="AB26" s="63" t="s">
         <v>88</v>
       </c>
       <c r="AI26"/>
       <c r="AJ26"/>
-      <c r="AK26" s="45"/>
-      <c r="AL26" s="45"/>
-      <c r="AM26" s="45"/>
-      <c r="AN26" s="45"/>
-      <c r="AO26" s="45"/>
-      <c r="AP26" s="45"/>
-      <c r="AQ26" s="45"/>
-      <c r="AR26" s="45"/>
-      <c r="AS26" s="45"/>
-      <c r="AT26" s="45"/>
-      <c r="AU26" s="45"/>
-      <c r="AV26" s="45"/>
-      <c r="AW26" s="45"/>
-    </row>
-    <row r="27" spans="2:51" s="98" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="83" t="str">
-        <f>X25</f>
-        <v>CSP</v>
-      </c>
-      <c r="C27" s="76" t="str">
+      <c r="AK26" s="76"/>
+      <c r="AL26" s="76"/>
+      <c r="AM26" s="76"/>
+      <c r="AN26" s="76"/>
+      <c r="AO26" s="76"/>
+      <c r="AP26" s="76"/>
+      <c r="AQ26" s="76"/>
+      <c r="AR26" s="76"/>
+      <c r="AS26" s="76"/>
+      <c r="AT26" s="76"/>
+      <c r="AU26" s="76"/>
+      <c r="AV26" s="76"/>
+      <c r="AW26" s="76"/>
+    </row>
+    <row r="27" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="50" t="str">
+        <f>X28</f>
+        <v>SOLPV</v>
+      </c>
+      <c r="C27" s="45" t="str">
         <f>PRI_Sector_Fuels!D20</f>
         <v>SOLAR</v>
       </c>
-      <c r="D27" s="83" t="str">
-        <f>X8</f>
-        <v>DECHEAT</v>
-      </c>
-      <c r="E27" s="96">
+      <c r="D27" s="50" t="s">
+        <v>131</v>
+      </c>
+      <c r="E27" s="43">
         <v>2030</v>
       </c>
       <c r="F27" s="82">
-        <v>0.4</v>
-      </c>
-      <c r="G27" s="82">
-        <v>1</v>
-      </c>
-      <c r="H27" s="96">
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="G27" s="64">
+        <v>0.99</v>
+      </c>
+      <c r="H27" s="43">
         <v>25</v>
       </c>
-      <c r="I27" s="82">
-        <v>3677</v>
-      </c>
-      <c r="J27" s="82">
+      <c r="I27" s="64">
+        <v>691</v>
+      </c>
+      <c r="J27" s="64">
+        <v>6.99</v>
+      </c>
+      <c r="K27" s="64">
         <v>0</v>
       </c>
-      <c r="K27" s="82">
-        <v>14</v>
-      </c>
-      <c r="L27" s="82">
+      <c r="L27" s="64">
         <v>8.76</v>
       </c>
-      <c r="M27" s="97"/>
-      <c r="N27" s="97"/>
-      <c r="O27" s="82"/>
-      <c r="P27" s="82"/>
-      <c r="Q27" s="82"/>
-      <c r="R27" s="97"/>
-      <c r="S27" s="96"/>
-      <c r="V27" s="84" t="s">
+      <c r="M27" s="67"/>
+      <c r="N27" s="67"/>
+      <c r="O27" s="64"/>
+      <c r="P27" s="64"/>
+      <c r="Q27" s="64"/>
+      <c r="R27" s="67"/>
+      <c r="S27" s="43">
+        <v>0.3</v>
+      </c>
+      <c r="V27" s="60" t="s">
         <v>69</v>
       </c>
-      <c r="W27" s="84"/>
-      <c r="X27" s="99" t="s">
-        <v>90</v>
-      </c>
-      <c r="Y27" s="100" t="s">
-        <v>147</v>
-      </c>
-      <c r="Z27" s="76" t="s">
+      <c r="W27" s="60"/>
+      <c r="X27" s="61" t="s">
+        <v>89</v>
+      </c>
+      <c r="Y27" s="62" t="s">
+        <v>146</v>
+      </c>
+      <c r="Z27" s="45" t="s">
         <v>58</v>
       </c>
       <c r="AA27" s="45" t="s">
@@ -5275,188 +5232,187 @@
       <c r="AB27" s="46" t="s">
         <v>88</v>
       </c>
-      <c r="AC27" s="46"/>
-      <c r="AD27" s="46"/>
-      <c r="AI27" s="14"/>
-      <c r="AJ27" s="14"/>
-      <c r="AK27" s="76"/>
-      <c r="AL27" s="76"/>
-      <c r="AM27" s="76"/>
-      <c r="AN27" s="76"/>
-      <c r="AO27" s="76"/>
-      <c r="AP27" s="76"/>
-      <c r="AQ27" s="76"/>
-      <c r="AR27" s="76"/>
-      <c r="AS27" s="76"/>
-      <c r="AT27" s="76"/>
-      <c r="AU27" s="76"/>
-      <c r="AV27" s="76"/>
-      <c r="AW27" s="76"/>
-    </row>
-    <row r="28" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="50" t="str">
-        <f>X23</f>
+      <c r="AI27"/>
+      <c r="AJ27"/>
+      <c r="AK27" s="45"/>
+      <c r="AL27" s="45"/>
+      <c r="AM27" s="45"/>
+      <c r="AN27" s="45"/>
+      <c r="AO27" s="45"/>
+      <c r="AP27" s="45"/>
+      <c r="AQ27" s="45"/>
+      <c r="AR27" s="45"/>
+      <c r="AS27" s="45"/>
+      <c r="AT27" s="45"/>
+      <c r="AU27" s="45"/>
+      <c r="AV27" s="45"/>
+      <c r="AW27" s="45"/>
+    </row>
+    <row r="28" spans="2:51" s="98" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="83" t="str">
+        <f>X26</f>
+        <v>CSP</v>
+      </c>
+      <c r="C28" s="76" t="str">
+        <f>PRI_Sector_Fuels!D20</f>
+        <v>SOLAR</v>
+      </c>
+      <c r="D28" s="83" t="str">
+        <f>X8</f>
+        <v>DECRHEAT</v>
+      </c>
+      <c r="E28" s="96">
+        <v>2030</v>
+      </c>
+      <c r="F28" s="82">
+        <v>0.4</v>
+      </c>
+      <c r="G28" s="82">
+        <v>1</v>
+      </c>
+      <c r="H28" s="96">
+        <v>25</v>
+      </c>
+      <c r="I28" s="82">
+        <v>3677</v>
+      </c>
+      <c r="J28" s="82">
+        <v>0</v>
+      </c>
+      <c r="K28" s="82">
+        <v>14</v>
+      </c>
+      <c r="L28" s="82">
+        <v>8.76</v>
+      </c>
+      <c r="M28" s="97"/>
+      <c r="N28" s="97"/>
+      <c r="O28" s="82"/>
+      <c r="P28" s="82"/>
+      <c r="Q28" s="82"/>
+      <c r="R28" s="97"/>
+      <c r="S28" s="96"/>
+      <c r="V28" s="84" t="s">
+        <v>69</v>
+      </c>
+      <c r="W28" s="84"/>
+      <c r="X28" s="99" t="s">
+        <v>90</v>
+      </c>
+      <c r="Y28" s="100" t="s">
+        <v>147</v>
+      </c>
+      <c r="Z28" s="76" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA28" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB28" s="46" t="s">
+        <v>88</v>
+      </c>
+      <c r="AC28" s="46"/>
+      <c r="AD28" s="46"/>
+      <c r="AI28" s="14"/>
+      <c r="AJ28" s="14"/>
+      <c r="AK28" s="76"/>
+      <c r="AL28" s="76"/>
+      <c r="AM28" s="76"/>
+      <c r="AN28" s="76"/>
+      <c r="AO28" s="76"/>
+      <c r="AP28" s="76"/>
+      <c r="AQ28" s="76"/>
+      <c r="AR28" s="76"/>
+      <c r="AS28" s="76"/>
+      <c r="AT28" s="76"/>
+      <c r="AU28" s="76"/>
+      <c r="AV28" s="76"/>
+      <c r="AW28" s="76"/>
+    </row>
+    <row r="29" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="50" t="str">
+        <f>X24</f>
         <v>GASBoiler</v>
       </c>
-      <c r="C28" s="45"/>
-      <c r="D28" s="50" t="s">
+      <c r="C29" s="45"/>
+      <c r="D29" s="50" t="s">
         <v>106</v>
       </c>
-      <c r="E28" s="43">
+      <c r="E29" s="43">
         <v>2030</v>
       </c>
-      <c r="F28" s="82">
+      <c r="F29" s="82">
         <v>0.3</v>
       </c>
-      <c r="G28" s="64">
+      <c r="G29" s="64">
         <v>1</v>
       </c>
-      <c r="H28" s="43">
+      <c r="H29" s="43">
         <v>25</v>
       </c>
-      <c r="I28" s="64">
+      <c r="I29" s="64">
         <v>0</v>
       </c>
-      <c r="J28" s="64">
+      <c r="J29" s="64">
         <v>0</v>
       </c>
-      <c r="K28" s="64">
+      <c r="K29" s="64">
         <v>0</v>
       </c>
-      <c r="L28" s="64">
+      <c r="L29" s="64">
         <v>8.76</v>
       </c>
-      <c r="M28" s="67"/>
-      <c r="N28" s="67"/>
-      <c r="O28" s="64"/>
-      <c r="P28" s="64"/>
-      <c r="Q28" s="64"/>
-      <c r="R28" s="67"/>
-      <c r="S28" s="43"/>
-      <c r="V28" s="60" t="s">
+      <c r="M29" s="67"/>
+      <c r="N29" s="67"/>
+      <c r="O29" s="64"/>
+      <c r="P29" s="64"/>
+      <c r="Q29" s="64"/>
+      <c r="R29" s="67"/>
+      <c r="S29" s="43"/>
+      <c r="V29" s="60" t="s">
         <v>69</v>
       </c>
-      <c r="W28" s="60"/>
-      <c r="X28" s="61" t="s">
-        <v>155</v>
-      </c>
-      <c r="Y28" s="62" t="s">
+      <c r="W29" s="60"/>
+      <c r="X29" s="61" t="s">
+        <v>154</v>
+      </c>
+      <c r="Y29" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="Z28" s="45" t="s">
+      <c r="Z29" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="AA28" s="76" t="s">
+      <c r="AA29" s="76" t="s">
         <v>87</v>
       </c>
-      <c r="AB28" s="98" t="s">
+      <c r="AB29" s="98" t="s">
         <v>88</v>
       </c>
-      <c r="AC28" s="98"/>
-      <c r="AD28" s="98"/>
-      <c r="AI28"/>
-      <c r="AJ28"/>
-      <c r="AK28" s="45"/>
-      <c r="AL28" s="45"/>
-      <c r="AM28" s="45"/>
-      <c r="AN28" s="45"/>
-      <c r="AO28" s="45"/>
-      <c r="AP28" s="45"/>
-      <c r="AQ28" s="45"/>
-      <c r="AR28" s="45"/>
-      <c r="AS28" s="45"/>
-      <c r="AT28" s="45"/>
-      <c r="AU28" s="45"/>
-      <c r="AV28" s="45"/>
-      <c r="AW28" s="45"/>
-    </row>
-    <row r="29" spans="2:51" s="104" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="102" t="str">
-        <f>X28</f>
-        <v>DECPOWER</v>
-      </c>
-      <c r="C29" s="102" t="s">
-        <v>130</v>
-      </c>
-      <c r="D29" s="102" t="str">
-        <f>X9</f>
-        <v>DECELC</v>
-      </c>
-      <c r="E29" s="103">
-        <v>2030</v>
-      </c>
-      <c r="F29" s="104">
-        <v>1</v>
-      </c>
-      <c r="G29" s="104">
-        <v>1</v>
-      </c>
-      <c r="H29" s="103">
-        <v>100</v>
-      </c>
-      <c r="I29" s="105">
-        <v>0</v>
-      </c>
-      <c r="J29" s="106">
-        <v>0</v>
-      </c>
-      <c r="K29" s="104">
-        <v>0</v>
-      </c>
-      <c r="L29" s="105">
-        <v>8.76</v>
-      </c>
-      <c r="M29" s="107"/>
-      <c r="N29" s="107"/>
-      <c r="O29" s="105"/>
-      <c r="P29" s="105"/>
-      <c r="Q29" s="105"/>
-      <c r="R29" s="107"/>
-      <c r="S29" s="103"/>
-      <c r="V29" s="108" t="s">
-        <v>69</v>
-      </c>
-      <c r="W29" s="108"/>
-      <c r="X29" s="109" t="s">
-        <v>137</v>
-      </c>
-      <c r="Y29" s="110" t="s">
-        <v>149</v>
-      </c>
-      <c r="Z29" s="106" t="s">
-        <v>58</v>
-      </c>
-      <c r="AA29" s="45" t="s">
-        <v>87</v>
-      </c>
-      <c r="AB29" s="46" t="s">
-        <v>88</v>
-      </c>
-      <c r="AC29" s="46"/>
-      <c r="AD29" s="46"/>
-      <c r="AI29" s="111"/>
-      <c r="AJ29" s="111"/>
-      <c r="AK29" s="106"/>
-      <c r="AL29" s="106"/>
-      <c r="AM29" s="106"/>
-      <c r="AN29" s="106"/>
-      <c r="AO29" s="106"/>
-      <c r="AP29" s="106"/>
-      <c r="AQ29" s="106"/>
-      <c r="AR29" s="106"/>
-      <c r="AS29" s="106"/>
-      <c r="AT29" s="106"/>
-      <c r="AU29" s="106"/>
-      <c r="AV29" s="106"/>
-      <c r="AW29" s="106"/>
+      <c r="AC29" s="98"/>
+      <c r="AD29" s="98"/>
+      <c r="AI29"/>
+      <c r="AJ29"/>
+      <c r="AK29" s="45"/>
+      <c r="AL29" s="45"/>
+      <c r="AM29" s="45"/>
+      <c r="AN29" s="45"/>
+      <c r="AO29" s="45"/>
+      <c r="AP29" s="45"/>
+      <c r="AQ29" s="45"/>
+      <c r="AR29" s="45"/>
+      <c r="AS29" s="45"/>
+      <c r="AT29" s="45"/>
+      <c r="AU29" s="45"/>
+      <c r="AV29" s="45"/>
+      <c r="AW29" s="45"/>
     </row>
     <row r="30" spans="2:51" s="104" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B30" s="102" t="str">
-        <f>X28</f>
+        <f>X29</f>
         <v>DECPOWER</v>
       </c>
       <c r="C30" s="102" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D30" s="102" t="str">
         <f>X9</f>
@@ -5493,25 +5449,27 @@
       <c r="Q30" s="105"/>
       <c r="R30" s="107"/>
       <c r="S30" s="103"/>
-      <c r="V30" s="46" t="s">
-        <v>128</v>
-      </c>
-      <c r="W30" s="46"/>
-      <c r="X30" s="46" t="s">
-        <v>158</v>
-      </c>
-      <c r="Y30" s="46" t="s">
-        <v>150</v>
+      <c r="V30" s="108" t="s">
+        <v>69</v>
+      </c>
+      <c r="W30" s="108"/>
+      <c r="X30" s="109" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y30" s="110" t="s">
+        <v>149</v>
       </c>
       <c r="Z30" s="106" t="s">
         <v>58</v>
       </c>
-      <c r="AA30" s="106" t="s">
+      <c r="AA30" s="45" t="s">
         <v>87</v>
       </c>
-      <c r="AB30" s="104" t="s">
+      <c r="AB30" s="46" t="s">
         <v>88</v>
       </c>
+      <c r="AC30" s="46"/>
+      <c r="AD30" s="46"/>
       <c r="AI30" s="111"/>
       <c r="AJ30" s="111"/>
       <c r="AK30" s="106"/>
@@ -5528,57 +5486,58 @@
       <c r="AV30" s="106"/>
       <c r="AW30" s="106"/>
     </row>
-    <row r="31" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="50" t="str">
+    <row r="31" spans="2:51" s="104" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="102" t="str">
         <f>X29</f>
-        <v>BIOPOWER</v>
-      </c>
-      <c r="C31" s="50" t="s">
-        <v>68</v>
-      </c>
-      <c r="D31" s="50" t="s">
-        <v>135</v>
-      </c>
-      <c r="E31" s="43">
+        <v>DECPOWER</v>
+      </c>
+      <c r="C31" s="102" t="s">
+        <v>131</v>
+      </c>
+      <c r="D31" s="102" t="str">
+        <f>X9</f>
+        <v>DECELC</v>
+      </c>
+      <c r="E31" s="103">
         <v>2030</v>
       </c>
-      <c r="F31" s="46">
-        <v>0.35</v>
-      </c>
-      <c r="G31" s="46">
-        <v>0.98</v>
-      </c>
-      <c r="H31" s="43">
-        <v>20</v>
-      </c>
-      <c r="I31" s="112">
-        <v>3242</v>
-      </c>
-      <c r="J31" s="64">
-        <v>129.68</v>
-      </c>
-      <c r="K31" s="64">
+      <c r="F31" s="104">
+        <v>1</v>
+      </c>
+      <c r="G31" s="104">
+        <v>1</v>
+      </c>
+      <c r="H31" s="103">
+        <v>100</v>
+      </c>
+      <c r="I31" s="105">
         <v>0</v>
       </c>
-      <c r="L31" s="64">
+      <c r="J31" s="106">
+        <v>0</v>
+      </c>
+      <c r="K31" s="104">
+        <v>0</v>
+      </c>
+      <c r="L31" s="105">
         <v>8.76</v>
       </c>
-      <c r="M31" s="67"/>
-      <c r="N31" s="67"/>
-      <c r="O31" s="64"/>
-      <c r="P31" s="64"/>
-      <c r="Q31" s="64"/>
-      <c r="R31" s="67"/>
-      <c r="S31" s="43"/>
-      <c r="V31" s="106" t="s">
-        <v>139</v>
-      </c>
-      <c r="W31" s="106"/>
-      <c r="X31" s="106" t="s">
-        <v>160</v>
-      </c>
-      <c r="Y31" s="106" t="s">
-        <v>161</v>
+      <c r="M31" s="107"/>
+      <c r="N31" s="107"/>
+      <c r="O31" s="105"/>
+      <c r="P31" s="105"/>
+      <c r="Q31" s="105"/>
+      <c r="R31" s="107"/>
+      <c r="S31" s="103"/>
+      <c r="V31" s="46" t="s">
+        <v>169</v>
+      </c>
+      <c r="W31" s="46"/>
+      <c r="X31" s="46" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y31" s="46" t="s">
+        <v>150</v>
       </c>
       <c r="Z31" s="106" t="s">
         <v>58</v>
@@ -5589,294 +5548,305 @@
       <c r="AB31" s="104" t="s">
         <v>88</v>
       </c>
-      <c r="AD31" s="104"/>
-      <c r="AI31" s="38"/>
-      <c r="AJ31" s="38"/>
-      <c r="AK31" s="45"/>
-      <c r="AL31" s="45"/>
-      <c r="AM31" s="45"/>
-      <c r="AN31" s="45"/>
-      <c r="AO31" s="45"/>
-      <c r="AP31" s="45"/>
-      <c r="AQ31" s="45"/>
-      <c r="AR31" s="45"/>
-      <c r="AS31" s="45"/>
-      <c r="AT31" s="45"/>
-      <c r="AU31" s="45"/>
-      <c r="AV31" s="45"/>
-      <c r="AW31" s="45"/>
-    </row>
-    <row r="32" spans="2:51" s="104" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="102" t="str">
-        <f>X28</f>
+      <c r="AI31" s="111"/>
+      <c r="AJ31" s="111"/>
+      <c r="AK31" s="106"/>
+      <c r="AL31" s="106"/>
+      <c r="AM31" s="106"/>
+      <c r="AN31" s="106"/>
+      <c r="AO31" s="106"/>
+      <c r="AP31" s="106"/>
+      <c r="AQ31" s="106"/>
+      <c r="AR31" s="106"/>
+      <c r="AS31" s="106"/>
+      <c r="AT31" s="106"/>
+      <c r="AU31" s="106"/>
+      <c r="AV31" s="106"/>
+      <c r="AW31" s="106"/>
+    </row>
+    <row r="32" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="50" t="str">
+        <f>X30</f>
+        <v>BIOPOWER</v>
+      </c>
+      <c r="C32" s="50" t="s">
+        <v>68</v>
+      </c>
+      <c r="D32" s="50" t="s">
+        <v>135</v>
+      </c>
+      <c r="E32" s="43">
+        <v>2030</v>
+      </c>
+      <c r="F32" s="46">
+        <v>0.35</v>
+      </c>
+      <c r="G32" s="46">
+        <v>0.98</v>
+      </c>
+      <c r="H32" s="43">
+        <v>20</v>
+      </c>
+      <c r="I32" s="112">
+        <v>3242</v>
+      </c>
+      <c r="J32" s="64">
+        <v>129.68</v>
+      </c>
+      <c r="K32" s="64">
+        <v>0</v>
+      </c>
+      <c r="L32" s="64">
+        <v>8.76</v>
+      </c>
+      <c r="M32" s="67"/>
+      <c r="N32" s="67"/>
+      <c r="O32" s="64"/>
+      <c r="P32" s="64"/>
+      <c r="Q32" s="64"/>
+      <c r="R32" s="67"/>
+      <c r="S32" s="43"/>
+      <c r="V32" s="45" t="s">
+        <v>139</v>
+      </c>
+      <c r="W32" s="45"/>
+      <c r="X32" s="45" t="s">
+        <v>164</v>
+      </c>
+      <c r="Y32" s="45" t="s">
+        <v>165</v>
+      </c>
+      <c r="Z32" s="106" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA32" s="106" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB32" s="104" t="s">
+        <v>88</v>
+      </c>
+      <c r="AD32" s="104"/>
+      <c r="AI32" s="38"/>
+      <c r="AJ32" s="38"/>
+      <c r="AK32" s="45"/>
+      <c r="AL32" s="45"/>
+      <c r="AM32" s="45"/>
+      <c r="AN32" s="45"/>
+      <c r="AO32" s="45"/>
+      <c r="AP32" s="45"/>
+      <c r="AQ32" s="45"/>
+      <c r="AR32" s="45"/>
+      <c r="AS32" s="45"/>
+      <c r="AT32" s="45"/>
+      <c r="AU32" s="45"/>
+      <c r="AV32" s="45"/>
+      <c r="AW32" s="45"/>
+    </row>
+    <row r="33" spans="1:49" s="104" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="102" t="str">
+        <f>X29</f>
         <v>DECPOWER</v>
       </c>
-      <c r="C32" s="106" t="s">
+      <c r="C33" s="106" t="s">
         <v>135</v>
       </c>
-      <c r="D32" s="102" t="str">
+      <c r="D33" s="102" t="str">
         <f>X9</f>
         <v>DECELC</v>
       </c>
-      <c r="E32" s="103">
+      <c r="E33" s="103">
         <v>2030</v>
       </c>
-      <c r="F32" s="105">
+      <c r="F33" s="105">
         <v>1</v>
       </c>
-      <c r="G32" s="105">
+      <c r="G33" s="105">
         <v>1</v>
       </c>
-      <c r="H32" s="104">
+      <c r="H33" s="104">
         <v>100</v>
       </c>
-      <c r="I32" s="104">
+      <c r="I33" s="104">
         <v>0</v>
       </c>
-      <c r="J32" s="104">
+      <c r="J33" s="104">
         <v>0</v>
       </c>
-      <c r="K32" s="104">
+      <c r="K33" s="104">
         <v>0</v>
       </c>
-      <c r="L32" s="104">
+      <c r="L33" s="104">
         <v>0</v>
       </c>
-      <c r="M32" s="107"/>
-      <c r="N32" s="107"/>
-      <c r="O32" s="105"/>
-      <c r="P32" s="105"/>
-      <c r="Q32" s="105"/>
-      <c r="R32" s="107"/>
-      <c r="S32" s="103"/>
-      <c r="V32" s="45" t="s">
-        <v>139</v>
-      </c>
-      <c r="W32" s="45"/>
-      <c r="X32" s="45" t="s">
-        <v>168</v>
-      </c>
-      <c r="Y32" s="45" t="s">
-        <v>169</v>
-      </c>
-      <c r="Z32" s="106" t="s">
+      <c r="M33" s="107"/>
+      <c r="N33" s="107"/>
+      <c r="O33" s="105"/>
+      <c r="P33" s="105"/>
+      <c r="Q33" s="105"/>
+      <c r="R33" s="107"/>
+      <c r="S33" s="103"/>
+      <c r="V33" s="111" t="s">
+        <v>128</v>
+      </c>
+      <c r="W33" s="111"/>
+      <c r="X33" s="106" t="s">
+        <v>152</v>
+      </c>
+      <c r="Y33" s="126" t="s">
+        <v>166</v>
+      </c>
+      <c r="Z33" s="106" t="s">
         <v>58</v>
       </c>
-      <c r="AA32" s="106" t="s">
+      <c r="AA33" s="106" t="s">
         <v>87</v>
       </c>
-      <c r="AB32" s="104" t="s">
+      <c r="AB33" s="104" t="s">
         <v>88</v>
       </c>
-      <c r="AC32" s="106"/>
-      <c r="AD32" s="46"/>
-      <c r="AI32" s="111"/>
-      <c r="AJ32" s="111"/>
-      <c r="AK32" s="106"/>
-      <c r="AL32" s="106"/>
-      <c r="AM32" s="106"/>
-      <c r="AN32" s="106"/>
-      <c r="AO32" s="106"/>
-      <c r="AP32" s="106"/>
-      <c r="AQ32" s="106"/>
-      <c r="AR32" s="106"/>
-      <c r="AS32" s="106"/>
-      <c r="AT32" s="106"/>
-      <c r="AU32" s="106"/>
-      <c r="AV32" s="106"/>
-      <c r="AW32" s="106"/>
-    </row>
-    <row r="33" spans="1:49" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="50" t="str">
-        <f>X20</f>
+      <c r="AC33" s="106"/>
+      <c r="AD33" s="46"/>
+      <c r="AI33" s="111"/>
+      <c r="AJ33" s="111"/>
+      <c r="AK33" s="106"/>
+      <c r="AL33" s="106"/>
+      <c r="AM33" s="106"/>
+      <c r="AN33" s="106"/>
+      <c r="AO33" s="106"/>
+      <c r="AP33" s="106"/>
+      <c r="AQ33" s="106"/>
+      <c r="AR33" s="106"/>
+      <c r="AS33" s="106"/>
+      <c r="AT33" s="106"/>
+      <c r="AU33" s="106"/>
+      <c r="AV33" s="106"/>
+      <c r="AW33" s="106"/>
+    </row>
+    <row r="34" spans="1:49" s="104" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="102" t="str">
+        <f>X21</f>
         <v>Furnace</v>
       </c>
-      <c r="C33" s="50" t="str">
+      <c r="C34" s="102" t="str">
         <f>X9</f>
         <v>DECELC</v>
       </c>
-      <c r="D33" s="83" t="str">
+      <c r="D34" s="102" t="str">
         <f>X12</f>
         <v>DECEHEAT</v>
       </c>
-      <c r="E33" s="43">
+      <c r="E34" s="103">
         <v>2030</v>
       </c>
-      <c r="F33" s="82">
+      <c r="F34" s="105">
         <v>1</v>
       </c>
-      <c r="G33" s="64">
+      <c r="G34" s="105">
         <v>1</v>
       </c>
-      <c r="H33" s="46">
+      <c r="H34" s="104">
         <v>100</v>
       </c>
-      <c r="I33" s="46">
+      <c r="I34" s="104">
         <v>0</v>
       </c>
-      <c r="J33" s="46">
+      <c r="J34" s="104">
         <v>0</v>
       </c>
-      <c r="K33" s="46">
+      <c r="K34" s="104">
         <v>0</v>
       </c>
-      <c r="L33" s="46">
+      <c r="L34" s="104">
         <v>0</v>
       </c>
-      <c r="M33" s="67"/>
-      <c r="N33" s="67"/>
-      <c r="O33" s="64"/>
-      <c r="P33" s="64"/>
-      <c r="Q33" s="64"/>
-      <c r="R33" s="67"/>
-      <c r="S33" s="43"/>
-      <c r="V33" s="38" t="s">
-        <v>69</v>
-      </c>
-      <c r="W33" s="38"/>
-      <c r="X33" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="Y33" s="40" t="s">
+      <c r="M34" s="107"/>
+      <c r="N34" s="107"/>
+      <c r="O34" s="105"/>
+      <c r="P34" s="105"/>
+      <c r="Q34" s="105"/>
+      <c r="R34" s="107"/>
+      <c r="S34" s="103"/>
+      <c r="V34" s="111" t="s">
+        <v>128</v>
+      </c>
+      <c r="W34" s="111"/>
+      <c r="X34" s="125" t="s">
         <v>170</v>
       </c>
-      <c r="Z33" s="106" t="s">
+      <c r="Y34" s="126" t="s">
+        <v>171</v>
+      </c>
+      <c r="Z34" s="106" t="s">
         <v>58</v>
       </c>
-      <c r="AA33" s="106" t="s">
+      <c r="AA34" s="106" t="s">
         <v>87</v>
       </c>
-      <c r="AB33" s="104" t="s">
+      <c r="AB34" s="104" t="s">
         <v>88</v>
       </c>
-      <c r="AC33" s="45"/>
-      <c r="AD33" s="106"/>
-      <c r="AI33"/>
-      <c r="AJ33"/>
-      <c r="AK33" s="45"/>
-      <c r="AL33" s="45"/>
-      <c r="AM33" s="45"/>
-      <c r="AN33" s="45"/>
-      <c r="AO33" s="45"/>
-      <c r="AP33" s="45"/>
-      <c r="AQ33" s="45"/>
-      <c r="AR33" s="45"/>
-      <c r="AS33" s="45"/>
-      <c r="AT33" s="45"/>
-      <c r="AU33" s="45"/>
-      <c r="AV33" s="45"/>
-      <c r="AW33" s="45"/>
-    </row>
-    <row r="34" spans="1:49" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="50" t="str">
-        <f>X24</f>
+      <c r="AC34" s="106"/>
+      <c r="AD34" s="106"/>
+      <c r="AI34" s="111"/>
+      <c r="AJ34" s="111"/>
+      <c r="AK34" s="106"/>
+      <c r="AL34" s="106"/>
+      <c r="AM34" s="106"/>
+      <c r="AN34" s="106"/>
+      <c r="AO34" s="106"/>
+      <c r="AP34" s="106"/>
+      <c r="AQ34" s="106"/>
+      <c r="AR34" s="106"/>
+      <c r="AS34" s="106"/>
+      <c r="AT34" s="106"/>
+      <c r="AU34" s="106"/>
+      <c r="AV34" s="106"/>
+      <c r="AW34" s="106"/>
+    </row>
+    <row r="35" spans="1:49" s="104" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="102" t="str">
+        <f>X25</f>
         <v>ELCBoiler</v>
       </c>
-      <c r="C34" s="50" t="str">
+      <c r="C35" s="102" t="str">
         <f>X9</f>
         <v>DECELC</v>
       </c>
-      <c r="D34" s="83" t="str">
+      <c r="D35" s="102" t="str">
         <f>X12</f>
         <v>DECEHEAT</v>
       </c>
-      <c r="E34" s="43">
+      <c r="E35" s="103">
         <v>2030</v>
       </c>
-      <c r="F34" s="64">
+      <c r="F35" s="105">
         <v>1</v>
       </c>
-      <c r="G34" s="64">
+      <c r="G35" s="105">
         <v>1</v>
       </c>
-      <c r="H34" s="43">
+      <c r="H35" s="103">
         <v>100</v>
       </c>
-      <c r="I34" s="64">
+      <c r="I35" s="105">
         <v>0</v>
       </c>
-      <c r="J34" s="64">
+      <c r="J35" s="105">
         <v>0</v>
       </c>
-      <c r="K34" s="64">
+      <c r="K35" s="105">
         <v>0</v>
       </c>
-      <c r="L34" s="64">
+      <c r="L35" s="105">
         <v>0</v>
       </c>
-      <c r="M34" s="67"/>
-      <c r="N34" s="67"/>
-      <c r="O34" s="64"/>
-      <c r="P34" s="64"/>
-      <c r="Q34" s="64"/>
-      <c r="R34" s="67"/>
-      <c r="S34" s="43"/>
-      <c r="V34" s="38"/>
-      <c r="W34" s="38"/>
-      <c r="X34" s="39"/>
-      <c r="Y34" s="40"/>
-      <c r="Z34" s="38"/>
-      <c r="AA34" s="38"/>
-      <c r="AB34" s="38"/>
-      <c r="AC34" s="45"/>
-      <c r="AD34" s="45"/>
-      <c r="AI34"/>
-      <c r="AJ34"/>
-      <c r="AK34" s="39"/>
-      <c r="AL34" s="39"/>
-      <c r="AM34" s="45"/>
-      <c r="AN34" s="45"/>
-      <c r="AO34" s="45"/>
-      <c r="AQ34"/>
-      <c r="AR34"/>
-      <c r="AS34" s="39"/>
-      <c r="AT34" s="39"/>
-      <c r="AU34" s="45"/>
-      <c r="AV34" s="45"/>
-    </row>
-    <row r="35" spans="1:49" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="5" t="str">
-        <f>X33</f>
-        <v>MANELC_TECH</v>
-      </c>
-      <c r="C35" s="50" t="str">
-        <f>X9</f>
-        <v>DECELC</v>
-      </c>
-      <c r="D35" s="50" t="s">
-        <v>153</v>
-      </c>
-      <c r="E35" s="43">
-        <v>2030</v>
-      </c>
-      <c r="F35" s="82">
-        <v>1</v>
-      </c>
-      <c r="G35" s="64">
-        <v>1</v>
-      </c>
-      <c r="H35" s="46">
-        <v>100</v>
-      </c>
-      <c r="I35" s="46">
-        <v>0</v>
-      </c>
-      <c r="J35" s="46">
-        <v>0</v>
-      </c>
-      <c r="K35" s="46">
-        <v>0</v>
-      </c>
-      <c r="L35" s="46">
-        <v>0</v>
-      </c>
-      <c r="M35" s="43"/>
-      <c r="N35" s="67"/>
-      <c r="O35" s="43"/>
-      <c r="P35" s="43"/>
-      <c r="Q35" s="43"/>
-      <c r="R35" s="43"/>
-      <c r="S35" s="43"/>
+      <c r="M35" s="107"/>
+      <c r="N35" s="107"/>
+      <c r="O35" s="105"/>
+      <c r="P35" s="105"/>
+      <c r="Q35" s="105"/>
+      <c r="R35" s="107"/>
+      <c r="S35" s="103"/>
       <c r="V35" s="45"/>
       <c r="W35" s="45"/>
       <c r="X35" s="45"/>
@@ -5884,64 +5854,72 @@
       <c r="Z35" s="50"/>
       <c r="AA35" s="38"/>
       <c r="AB35" s="38"/>
-      <c r="AC35" s="45"/>
-      <c r="AD35" s="45"/>
-      <c r="AI35"/>
-      <c r="AJ35"/>
-      <c r="AK35" s="39"/>
-      <c r="AL35" s="39"/>
-      <c r="AM35" s="45"/>
-      <c r="AN35" s="45"/>
-      <c r="AO35" s="45"/>
-      <c r="AQ35"/>
-      <c r="AR35"/>
-      <c r="AS35" s="39"/>
-      <c r="AT35" s="39"/>
-      <c r="AU35" s="45"/>
-      <c r="AV35" s="45"/>
+      <c r="AC35" s="106"/>
+      <c r="AD35" s="106"/>
+      <c r="AI35" s="111"/>
+      <c r="AJ35" s="111"/>
+      <c r="AK35" s="125"/>
+      <c r="AL35" s="125"/>
+      <c r="AM35" s="106"/>
+      <c r="AN35" s="106"/>
+      <c r="AO35" s="106"/>
+      <c r="AQ35" s="111"/>
+      <c r="AR35" s="111"/>
+      <c r="AS35" s="125"/>
+      <c r="AT35" s="125"/>
+      <c r="AU35" s="106"/>
+      <c r="AV35" s="106"/>
     </row>
     <row r="36" spans="1:49" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="45" t="str">
-        <f>X31</f>
-        <v>GTHT</v>
+      <c r="B36" s="5" t="str">
+        <f>X33</f>
+        <v>MANELC_TECH</v>
       </c>
       <c r="C36" s="50" t="str">
-        <f>X11</f>
-        <v>GEHEAT</v>
+        <f>X9</f>
+        <v>DECELC</v>
       </c>
       <c r="D36" s="50" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E36" s="43">
         <v>2030</v>
       </c>
-      <c r="F36" s="64">
+      <c r="F36" s="82">
         <v>1</v>
       </c>
       <c r="G36" s="64">
         <v>1</v>
       </c>
-      <c r="H36" s="43">
+      <c r="H36" s="46">
         <v>100</v>
       </c>
-      <c r="I36" s="64">
+      <c r="I36" s="46">
         <v>0</v>
       </c>
-      <c r="J36" s="64">
+      <c r="J36" s="46">
         <v>0</v>
       </c>
-      <c r="K36" s="64">
+      <c r="K36" s="46">
         <v>0</v>
       </c>
-      <c r="L36" s="64">
+      <c r="L36" s="46">
         <v>0</v>
       </c>
-      <c r="N36" s="65"/>
-      <c r="V36" s="45"/>
-      <c r="X36" s="45"/>
-      <c r="Z36" s="54"/>
-      <c r="AA36" s="50"/>
-      <c r="AB36" s="63"/>
+      <c r="M36" s="43"/>
+      <c r="N36" s="67"/>
+      <c r="O36" s="43"/>
+      <c r="P36" s="43"/>
+      <c r="Q36" s="43"/>
+      <c r="R36" s="43"/>
+      <c r="S36" s="43"/>
+      <c r="V36" s="114"/>
+      <c r="W36" s="113"/>
+      <c r="X36" s="114"/>
+      <c r="Y36" s="113"/>
+      <c r="Z36" s="119"/>
+      <c r="AA36" s="115"/>
+      <c r="AB36" s="120"/>
       <c r="AC36" s="45"/>
       <c r="AD36" s="45"/>
       <c r="AI36"/>
@@ -5958,105 +5936,105 @@
       <c r="AU36" s="45"/>
       <c r="AV36" s="45"/>
     </row>
-    <row r="37" spans="1:49" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="45" t="str">
+    <row r="37" spans="1:49" s="113" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="114" t="str">
         <f>X32</f>
         <v>ETHT</v>
       </c>
-      <c r="C37" s="50" t="str">
+      <c r="C37" s="115" t="str">
         <f>X11</f>
         <v>GEHEAT</v>
       </c>
-      <c r="D37" s="50" t="str">
+      <c r="D37" s="115" t="str">
         <f>X13</f>
         <v>ELCHEAT</v>
       </c>
-      <c r="E37" s="43">
+      <c r="E37" s="116">
         <v>2030</v>
       </c>
-      <c r="F37" s="82">
+      <c r="F37" s="117">
         <v>1</v>
       </c>
-      <c r="G37" s="64">
+      <c r="G37" s="117">
         <v>1</v>
       </c>
-      <c r="H37" s="46">
+      <c r="H37" s="116">
         <v>100</v>
       </c>
-      <c r="I37" s="46">
+      <c r="I37" s="117">
         <v>0</v>
       </c>
-      <c r="J37" s="46">
+      <c r="J37" s="117">
         <v>0</v>
       </c>
-      <c r="K37" s="46">
+      <c r="K37" s="117">
         <v>0</v>
       </c>
-      <c r="L37" s="46">
+      <c r="L37" s="117">
         <v>0</v>
       </c>
-      <c r="N37" s="65"/>
-      <c r="V37" s="45"/>
-      <c r="W37" s="45"/>
-      <c r="X37" s="45"/>
-      <c r="Y37" s="45"/>
-      <c r="Z37" s="45"/>
-      <c r="AA37" s="54"/>
-      <c r="AB37" s="45"/>
-      <c r="AC37" s="45"/>
-      <c r="AD37" s="45"/>
-      <c r="AI37"/>
-      <c r="AJ37"/>
-      <c r="AK37" s="39"/>
-      <c r="AL37" s="39"/>
-      <c r="AM37" s="45"/>
-      <c r="AN37" s="45"/>
-      <c r="AO37" s="45"/>
-      <c r="AQ37"/>
-      <c r="AR37"/>
-      <c r="AS37" s="39"/>
-      <c r="AT37" s="39"/>
-      <c r="AU37" s="45"/>
-      <c r="AV37" s="45"/>
-    </row>
-    <row r="38" spans="1:49" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="45" t="str">
+      <c r="N37" s="118"/>
+      <c r="V37" s="106"/>
+      <c r="W37" s="106"/>
+      <c r="X37" s="106"/>
+      <c r="Y37" s="106"/>
+      <c r="Z37" s="106"/>
+      <c r="AA37" s="124"/>
+      <c r="AB37" s="106"/>
+      <c r="AC37" s="114"/>
+      <c r="AD37" s="114"/>
+      <c r="AI37" s="121"/>
+      <c r="AJ37" s="121"/>
+      <c r="AK37" s="122"/>
+      <c r="AL37" s="122"/>
+      <c r="AM37" s="114"/>
+      <c r="AN37" s="114"/>
+      <c r="AO37" s="114"/>
+      <c r="AQ37" s="121"/>
+      <c r="AR37" s="121"/>
+      <c r="AS37" s="122"/>
+      <c r="AT37" s="122"/>
+      <c r="AU37" s="114"/>
+      <c r="AV37" s="114"/>
+    </row>
+    <row r="38" spans="1:49" s="104" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="106" t="str">
         <f>X32</f>
         <v>ETHT</v>
       </c>
-      <c r="C38" s="50" t="str">
+      <c r="C38" s="102" t="str">
         <f>X12</f>
         <v>DECEHEAT</v>
       </c>
-      <c r="D38" s="50" t="str">
+      <c r="D38" s="102" t="str">
         <f>X13</f>
         <v>ELCHEAT</v>
       </c>
-      <c r="E38" s="43">
+      <c r="E38" s="103">
         <v>2030</v>
       </c>
-      <c r="F38" s="64">
+      <c r="F38" s="105">
         <v>1</v>
       </c>
-      <c r="G38" s="64">
+      <c r="G38" s="105">
         <v>1</v>
       </c>
-      <c r="H38" s="43">
+      <c r="H38" s="103">
         <v>100</v>
       </c>
-      <c r="I38" s="64">
+      <c r="I38" s="105">
         <v>0</v>
       </c>
-      <c r="J38" s="64">
+      <c r="J38" s="105">
         <v>0</v>
       </c>
-      <c r="K38" s="64">
+      <c r="K38" s="105">
         <v>0</v>
       </c>
-      <c r="L38" s="64">
+      <c r="L38" s="105">
         <v>0</v>
       </c>
-      <c r="N38" s="65"/>
+      <c r="N38" s="123"/>
       <c r="V38" s="45"/>
       <c r="W38" s="45"/>
       <c r="X38" s="45"/>
@@ -6064,33 +6042,34 @@
       <c r="Z38" s="45"/>
       <c r="AA38" s="54"/>
       <c r="AB38" s="45"/>
-      <c r="AC38" s="45"/>
-      <c r="AD38" s="45"/>
-      <c r="AI38"/>
-      <c r="AJ38"/>
-      <c r="AK38" s="39"/>
-      <c r="AL38" s="39"/>
-      <c r="AM38" s="45"/>
-      <c r="AN38" s="45"/>
-      <c r="AO38" s="45"/>
-      <c r="AQ38"/>
-      <c r="AR38"/>
-      <c r="AS38" s="39"/>
-      <c r="AT38" s="39"/>
-      <c r="AU38" s="45"/>
-      <c r="AV38" s="45"/>
+      <c r="AC38" s="106"/>
+      <c r="AD38" s="106"/>
+      <c r="AI38" s="111"/>
+      <c r="AJ38" s="111"/>
+      <c r="AK38" s="125"/>
+      <c r="AL38" s="125"/>
+      <c r="AM38" s="106"/>
+      <c r="AN38" s="106"/>
+      <c r="AO38" s="106"/>
+      <c r="AQ38" s="111"/>
+      <c r="AR38" s="111"/>
+      <c r="AS38" s="125"/>
+      <c r="AT38" s="125"/>
+      <c r="AU38" s="106"/>
+      <c r="AV38" s="106"/>
     </row>
     <row r="39" spans="1:49" s="46" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B39" s="45" t="str">
-        <f>X30</f>
+        <f>X31</f>
         <v>RNWTHT</v>
       </c>
       <c r="C39" s="50" t="str">
         <f>X13</f>
         <v>ELCHEAT</v>
       </c>
-      <c r="D39" s="50" t="s">
-        <v>107</v>
+      <c r="D39" s="50" t="str">
+        <f>X10</f>
+        <v>RNWHEAT</v>
       </c>
       <c r="E39" s="43">
         <v>2030</v>
@@ -6122,7 +6101,7 @@
       <c r="X39" s="45"/>
       <c r="Y39" s="45"/>
       <c r="Z39" s="45"/>
-      <c r="AA39" s="54"/>
+      <c r="AA39" s="45"/>
       <c r="AB39" s="45"/>
       <c r="AC39" s="45"/>
       <c r="AD39" s="45"/>
@@ -6142,15 +6121,16 @@
     </row>
     <row r="40" spans="1:49" s="46" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B40" s="50" t="str">
-        <f>X30</f>
+        <f>X31</f>
         <v>RNWTHT</v>
       </c>
       <c r="C40" s="50" t="str">
         <f>X8</f>
-        <v>DECHEAT</v>
-      </c>
-      <c r="D40" s="50" t="s">
-        <v>107</v>
+        <v>DECRHEAT</v>
+      </c>
+      <c r="D40" s="50" t="str">
+        <f>X10</f>
+        <v>RNWHEAT</v>
       </c>
       <c r="E40" s="43">
         <v>2030</v>
@@ -6200,30 +6180,70 @@
       <c r="AU40" s="45"/>
       <c r="AV40" s="45"/>
     </row>
-    <row r="41" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A41" s="46"/>
-      <c r="F41" s="66"/>
-      <c r="G41" s="43"/>
-      <c r="H41" s="68"/>
-      <c r="M41" s="46"/>
-      <c r="N41" s="46"/>
-      <c r="O41" s="46"/>
-      <c r="P41" s="46"/>
-      <c r="Q41" s="46"/>
-      <c r="R41" s="46"/>
-      <c r="S41" s="46"/>
+    <row r="41" spans="1:49" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="50" t="str">
+        <f>X34</f>
+        <v>PTHT</v>
+      </c>
+      <c r="C41" s="50" t="str">
+        <f>X10</f>
+        <v>RNWHEAT</v>
+      </c>
+      <c r="D41" s="50" t="s">
+        <v>107</v>
+      </c>
+      <c r="E41" s="43">
+        <v>2030</v>
+      </c>
+      <c r="F41" s="82">
+        <v>1</v>
+      </c>
+      <c r="G41" s="64">
+        <v>1</v>
+      </c>
+      <c r="H41" s="46">
+        <v>100</v>
+      </c>
+      <c r="I41" s="46">
+        <v>0</v>
+      </c>
+      <c r="J41" s="46">
+        <v>0</v>
+      </c>
+      <c r="K41" s="46">
+        <v>0</v>
+      </c>
+      <c r="L41" s="46">
+        <v>0</v>
+      </c>
+      <c r="V41" s="45"/>
+      <c r="W41" s="45"/>
+      <c r="X41" s="45"/>
+      <c r="Y41" s="45"/>
+      <c r="Z41" s="45"/>
+      <c r="AA41" s="45"/>
+      <c r="AB41" s="45"/>
+      <c r="AC41" s="45"/>
+      <c r="AD41" s="45"/>
+      <c r="AE41" s="45"/>
       <c r="AI41"/>
       <c r="AJ41"/>
       <c r="AK41" s="39"/>
       <c r="AL41" s="39"/>
-      <c r="AP41" s="46"/>
+      <c r="AM41" s="45"/>
+      <c r="AN41" s="45"/>
+      <c r="AO41" s="45"/>
       <c r="AQ41"/>
       <c r="AR41"/>
       <c r="AS41" s="39"/>
       <c r="AT41" s="39"/>
+      <c r="AU41" s="45"/>
+      <c r="AV41" s="45"/>
     </row>
     <row r="42" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A42" s="46"/>
+      <c r="F42" s="66"/>
+      <c r="G42" s="43"/>
       <c r="H42" s="68"/>
       <c r="M42" s="46"/>
       <c r="N42" s="46"/>
@@ -6243,24 +6263,29 @@
       <c r="AT42" s="39"/>
     </row>
     <row r="43" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="B43" s="69"/>
-      <c r="C43" s="45" t="s">
-        <v>82</v>
-      </c>
+      <c r="A43" s="46"/>
       <c r="H43" s="68"/>
+      <c r="M43" s="46"/>
+      <c r="N43" s="46"/>
+      <c r="O43" s="46"/>
+      <c r="P43" s="46"/>
+      <c r="Q43" s="46"/>
+      <c r="R43" s="46"/>
+      <c r="S43" s="46"/>
       <c r="AI43"/>
       <c r="AJ43"/>
       <c r="AK43" s="39"/>
       <c r="AL43" s="39"/>
+      <c r="AP43" s="46"/>
       <c r="AQ43"/>
       <c r="AR43"/>
       <c r="AS43" s="39"/>
       <c r="AT43" s="39"/>
     </row>
     <row r="44" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="B44" s="70"/>
+      <c r="B44" s="69"/>
       <c r="C44" s="45" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H44" s="68"/>
       <c r="AI44"/>
@@ -6273,6 +6298,10 @@
       <c r="AT44" s="39"/>
     </row>
     <row r="45" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="B45" s="70"/>
+      <c r="C45" s="45" t="s">
+        <v>83</v>
+      </c>
       <c r="H45" s="68"/>
       <c r="AI45"/>
       <c r="AJ45"/>
@@ -6284,6 +6313,7 @@
       <c r="AT45" s="39"/>
     </row>
     <row r="46" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="H46" s="68"/>
       <c r="AI46"/>
       <c r="AJ46"/>
       <c r="AK46" s="39"/>
@@ -6304,7 +6334,6 @@
       <c r="AT47" s="39"/>
     </row>
     <row r="48" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="E48" s="43"/>
       <c r="AI48"/>
       <c r="AJ48"/>
       <c r="AK48" s="39"/>
@@ -6315,6 +6344,7 @@
       <c r="AT48" s="39"/>
     </row>
     <row r="49" spans="2:46" x14ac:dyDescent="0.25">
+      <c r="E49" s="43"/>
       <c r="AI49"/>
       <c r="AJ49"/>
       <c r="AK49" s="39"/>
@@ -6375,17 +6405,6 @@
       <c r="AT54" s="39"/>
     </row>
     <row r="55" spans="2:46" x14ac:dyDescent="0.25">
-      <c r="B55" s="72"/>
-      <c r="C55" s="72"/>
-      <c r="D55"/>
-      <c r="E55"/>
-      <c r="F55"/>
-      <c r="G55"/>
-      <c r="H55"/>
-      <c r="I55"/>
-      <c r="J55"/>
-      <c r="K55"/>
-      <c r="L55"/>
       <c r="AI55"/>
       <c r="AJ55"/>
       <c r="AK55" s="39"/>
@@ -6395,18 +6414,18 @@
       <c r="AS55" s="39"/>
       <c r="AT55" s="39"/>
     </row>
-    <row r="56" spans="2:46" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="73"/>
-      <c r="C56" s="73"/>
-      <c r="D56" s="73"/>
-      <c r="E56" s="73"/>
-      <c r="F56" s="73"/>
-      <c r="G56" s="73"/>
-      <c r="H56" s="73"/>
-      <c r="I56" s="73"/>
-      <c r="J56" s="73"/>
-      <c r="K56" s="73"/>
-      <c r="L56" s="73"/>
+    <row r="56" spans="2:46" x14ac:dyDescent="0.25">
+      <c r="B56" s="72"/>
+      <c r="C56" s="72"/>
+      <c r="D56"/>
+      <c r="E56"/>
+      <c r="F56"/>
+      <c r="G56"/>
+      <c r="H56"/>
+      <c r="I56"/>
+      <c r="J56"/>
+      <c r="K56"/>
+      <c r="L56"/>
       <c r="AI56"/>
       <c r="AJ56"/>
       <c r="AK56" s="39"/>
@@ -6416,18 +6435,18 @@
       <c r="AS56" s="39"/>
       <c r="AT56" s="39"/>
     </row>
-    <row r="57" spans="2:46" x14ac:dyDescent="0.25">
-      <c r="B57"/>
-      <c r="C57"/>
-      <c r="D57"/>
-      <c r="E57" s="1"/>
-      <c r="F57"/>
-      <c r="G57"/>
-      <c r="H57"/>
-      <c r="I57"/>
-      <c r="J57"/>
-      <c r="K57"/>
-      <c r="L57"/>
+    <row r="57" spans="2:46" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B57" s="73"/>
+      <c r="C57" s="73"/>
+      <c r="D57" s="73"/>
+      <c r="E57" s="73"/>
+      <c r="F57" s="73"/>
+      <c r="G57" s="73"/>
+      <c r="H57" s="73"/>
+      <c r="I57" s="73"/>
+      <c r="J57" s="73"/>
+      <c r="K57" s="73"/>
+      <c r="L57" s="73"/>
       <c r="AI57"/>
       <c r="AJ57"/>
       <c r="AK57" s="39"/>
@@ -6585,6 +6604,17 @@
       <c r="AT64" s="39"/>
     </row>
     <row r="65" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="B65"/>
+      <c r="C65"/>
+      <c r="D65"/>
+      <c r="E65" s="1"/>
+      <c r="F65"/>
+      <c r="G65"/>
+      <c r="H65"/>
+      <c r="I65"/>
+      <c r="J65"/>
+      <c r="K65"/>
+      <c r="L65"/>
       <c r="AI65"/>
       <c r="AJ65"/>
       <c r="AK65" s="39"/>
@@ -6627,7 +6657,6 @@
       <c r="Z68" s="46"/>
       <c r="AA68" s="46"/>
       <c r="AB68" s="46"/>
-      <c r="AC68" s="46"/>
       <c r="AI68"/>
       <c r="AJ68"/>
       <c r="AK68" s="39"/>
@@ -6646,8 +6675,6 @@
       <c r="AA69" s="46"/>
       <c r="AB69" s="46"/>
       <c r="AC69" s="46"/>
-      <c r="AD69" s="46"/>
-      <c r="AE69" s="46"/>
       <c r="AI69"/>
       <c r="AJ69"/>
       <c r="AK69" s="39"/>
@@ -6658,16 +6685,6 @@
       <c r="AT69" s="39"/>
     </row>
     <row r="70" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="B70"/>
-      <c r="C70"/>
-      <c r="E70" s="72"/>
-      <c r="F70" s="72"/>
-      <c r="G70" s="1"/>
-      <c r="H70"/>
-      <c r="I70" s="72"/>
-      <c r="J70"/>
-      <c r="K70"/>
-      <c r="L70" s="72"/>
       <c r="AA70" s="46"/>
       <c r="AB70" s="46"/>
       <c r="AC70" s="46"/>
@@ -6682,63 +6699,45 @@
       <c r="AS70" s="39"/>
       <c r="AT70" s="39"/>
     </row>
-    <row r="71" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="45"/>
-      <c r="B71" s="78"/>
-      <c r="C71" s="78"/>
-      <c r="D71" s="78"/>
-      <c r="E71" s="78"/>
-      <c r="F71" s="78"/>
-      <c r="G71" s="78"/>
-      <c r="H71" s="79"/>
-      <c r="I71" s="78"/>
-      <c r="J71" s="78"/>
-      <c r="K71" s="78"/>
-      <c r="L71" s="78"/>
-      <c r="M71" s="45"/>
-      <c r="N71" s="45"/>
-      <c r="O71" s="45"/>
-      <c r="P71" s="45"/>
-      <c r="Q71" s="45"/>
-      <c r="R71" s="45"/>
-      <c r="S71" s="45"/>
-      <c r="V71" s="45"/>
-      <c r="W71" s="45"/>
-      <c r="X71" s="45"/>
-      <c r="Y71" s="45"/>
-      <c r="Z71" s="45"/>
-      <c r="AA71" s="45"/>
-      <c r="AB71" s="45"/>
-      <c r="AC71" s="45"/>
+    <row r="71" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="B71"/>
+      <c r="C71"/>
+      <c r="E71" s="72"/>
+      <c r="F71" s="72"/>
+      <c r="G71" s="1"/>
+      <c r="H71"/>
+      <c r="I71" s="72"/>
+      <c r="J71"/>
+      <c r="K71"/>
+      <c r="L71" s="72"/>
+      <c r="AC71" s="46"/>
+      <c r="AD71" s="46"/>
+      <c r="AE71" s="46"/>
       <c r="AI71"/>
-      <c r="AJ71" s="79"/>
+      <c r="AJ71"/>
       <c r="AK71" s="39"/>
-      <c r="AL71" s="41"/>
-      <c r="AM71" s="45"/>
-      <c r="AN71" s="45"/>
+      <c r="AL71" s="39"/>
       <c r="AQ71"/>
-      <c r="AR71" s="79"/>
+      <c r="AR71"/>
       <c r="AS71" s="39"/>
-      <c r="AT71" s="41"/>
-      <c r="AU71" s="45"/>
-      <c r="AV71" s="45"/>
+      <c r="AT71" s="39"/>
     </row>
     <row r="72" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="72"/>
-      <c r="B72" s="80"/>
-      <c r="C72" s="81"/>
-      <c r="D72" s="80"/>
-      <c r="E72" s="80"/>
-      <c r="F72" s="80"/>
-      <c r="G72" s="80"/>
+      <c r="A72" s="45"/>
+      <c r="B72" s="78"/>
+      <c r="C72" s="78"/>
+      <c r="D72" s="78"/>
+      <c r="E72" s="78"/>
+      <c r="F72" s="78"/>
+      <c r="G72" s="78"/>
       <c r="H72" s="79"/>
-      <c r="I72" s="80"/>
-      <c r="J72" s="80"/>
-      <c r="K72" s="81"/>
-      <c r="L72" s="81"/>
-      <c r="M72" s="72"/>
-      <c r="N72" s="72"/>
-      <c r="O72" s="1"/>
+      <c r="I72" s="78"/>
+      <c r="J72" s="78"/>
+      <c r="K72" s="78"/>
+      <c r="L72" s="78"/>
+      <c r="M72" s="45"/>
+      <c r="N72" s="45"/>
+      <c r="O72" s="45"/>
       <c r="P72" s="45"/>
       <c r="Q72" s="45"/>
       <c r="R72" s="45"/>
@@ -6751,16 +6750,23 @@
       <c r="AA72" s="45"/>
       <c r="AB72" s="45"/>
       <c r="AC72" s="45"/>
-      <c r="AD72" s="45"/>
-      <c r="AE72" s="45"/>
-      <c r="AI72" s="42"/>
-      <c r="AJ72" s="42"/>
-      <c r="AK72" s="54"/>
+      <c r="AI72"/>
+      <c r="AJ72" s="79"/>
+      <c r="AK72" s="39"/>
+      <c r="AL72" s="41"/>
+      <c r="AM72" s="45"/>
+      <c r="AN72" s="45"/>
+      <c r="AQ72"/>
+      <c r="AR72" s="79"/>
+      <c r="AS72" s="39"/>
+      <c r="AT72" s="41"/>
+      <c r="AU72" s="45"/>
+      <c r="AV72" s="45"/>
     </row>
     <row r="73" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="78"/>
+      <c r="A73" s="72"/>
       <c r="B73" s="80"/>
-      <c r="C73" s="80"/>
+      <c r="C73" s="81"/>
       <c r="D73" s="80"/>
       <c r="E73" s="80"/>
       <c r="F73" s="80"/>
@@ -6768,11 +6774,15 @@
       <c r="H73" s="79"/>
       <c r="I73" s="80"/>
       <c r="J73" s="80"/>
-      <c r="K73" s="80"/>
-      <c r="L73" s="80"/>
-      <c r="M73" s="78"/>
-      <c r="N73" s="78"/>
-      <c r="O73" s="78"/>
+      <c r="K73" s="81"/>
+      <c r="L73" s="81"/>
+      <c r="M73" s="72"/>
+      <c r="N73" s="72"/>
+      <c r="O73" s="1"/>
+      <c r="P73" s="45"/>
+      <c r="Q73" s="45"/>
+      <c r="R73" s="45"/>
+      <c r="S73" s="45"/>
       <c r="V73" s="45"/>
       <c r="W73" s="45"/>
       <c r="X73" s="45"/>
@@ -6787,39 +6797,48 @@
       <c r="AJ73" s="42"/>
       <c r="AK73" s="54"/>
     </row>
-    <row r="74" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A74" s="80"/>
-      <c r="B74"/>
-      <c r="C74" s="39"/>
-      <c r="D74" s="39"/>
-      <c r="H74"/>
-      <c r="I74"/>
-      <c r="J74"/>
-      <c r="K74" s="39"/>
-      <c r="L74" s="39"/>
-      <c r="M74" s="81"/>
-      <c r="N74" s="81"/>
-      <c r="O74" s="80"/>
-      <c r="P74" s="46"/>
-      <c r="Q74" s="46"/>
-      <c r="R74" s="46"/>
-      <c r="S74" s="46"/>
-      <c r="AI74" s="38"/>
-      <c r="AJ74" s="38"/>
-      <c r="AK74" s="50"/>
+    <row r="74" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="78"/>
+      <c r="B74" s="80"/>
+      <c r="C74" s="80"/>
+      <c r="D74" s="80"/>
+      <c r="E74" s="80"/>
+      <c r="F74" s="80"/>
+      <c r="G74" s="80"/>
+      <c r="H74" s="79"/>
+      <c r="I74" s="80"/>
+      <c r="J74" s="80"/>
+      <c r="K74" s="80"/>
+      <c r="L74" s="80"/>
+      <c r="M74" s="78"/>
+      <c r="N74" s="78"/>
+      <c r="O74" s="78"/>
+      <c r="V74" s="45"/>
+      <c r="W74" s="45"/>
+      <c r="X74" s="45"/>
+      <c r="Y74" s="45"/>
+      <c r="Z74" s="45"/>
+      <c r="AA74" s="45"/>
+      <c r="AB74" s="45"/>
+      <c r="AC74" s="45"/>
+      <c r="AD74" s="45"/>
+      <c r="AE74" s="45"/>
+      <c r="AI74" s="42"/>
+      <c r="AJ74" s="42"/>
+      <c r="AK74" s="54"/>
     </row>
     <row r="75" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A75" s="80"/>
       <c r="B75"/>
       <c r="C75" s="39"/>
       <c r="D75" s="39"/>
-      <c r="H75" s="77"/>
+      <c r="H75"/>
       <c r="I75"/>
       <c r="J75"/>
       <c r="K75" s="39"/>
       <c r="L75" s="39"/>
-      <c r="M75" s="80"/>
-      <c r="N75" s="80"/>
+      <c r="M75" s="81"/>
+      <c r="N75" s="81"/>
       <c r="O75" s="80"/>
       <c r="P75" s="46"/>
       <c r="Q75" s="46"/>
@@ -6830,14 +6849,22 @@
       <c r="AK75" s="50"/>
     </row>
     <row r="76" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A76"/>
+      <c r="A76" s="80"/>
       <c r="B76"/>
       <c r="C76" s="39"/>
       <c r="D76" s="39"/>
+      <c r="H76" s="77"/>
       <c r="I76"/>
       <c r="J76"/>
       <c r="K76" s="39"/>
       <c r="L76" s="39"/>
+      <c r="M76" s="80"/>
+      <c r="N76" s="80"/>
+      <c r="O76" s="80"/>
+      <c r="P76" s="46"/>
+      <c r="Q76" s="46"/>
+      <c r="R76" s="46"/>
+      <c r="S76" s="46"/>
       <c r="AI76" s="38"/>
       <c r="AJ76" s="38"/>
       <c r="AK76" s="50"/>
@@ -6860,12 +6887,10 @@
       <c r="B78"/>
       <c r="C78" s="39"/>
       <c r="D78" s="39"/>
-      <c r="H78" s="46"/>
       <c r="I78"/>
       <c r="J78"/>
       <c r="K78" s="39"/>
       <c r="L78" s="39"/>
-      <c r="O78" s="46"/>
       <c r="AI78" s="38"/>
       <c r="AJ78" s="38"/>
       <c r="AK78" s="50"/>
@@ -7085,10 +7110,12 @@
       <c r="B93"/>
       <c r="C93" s="39"/>
       <c r="D93" s="39"/>
+      <c r="H93" s="46"/>
       <c r="I93"/>
       <c r="J93"/>
       <c r="K93" s="39"/>
       <c r="L93" s="39"/>
+      <c r="O93" s="46"/>
       <c r="AI93" s="38"/>
       <c r="AJ93" s="38"/>
       <c r="AK93" s="50"/>
@@ -7459,6 +7486,13 @@
     </row>
     <row r="122" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A122"/>
+      <c r="B122"/>
+      <c r="C122" s="39"/>
+      <c r="D122" s="39"/>
+      <c r="I122"/>
+      <c r="J122"/>
+      <c r="K122" s="39"/>
+      <c r="L122" s="39"/>
       <c r="AI122" s="38"/>
       <c r="AJ122" s="38"/>
       <c r="AK122" s="50"/>
@@ -7470,6 +7504,7 @@
       <c r="AK123" s="50"/>
     </row>
     <row r="124" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A124"/>
       <c r="AI124" s="38"/>
       <c r="AJ124" s="38"/>
       <c r="AK124" s="50"/>
@@ -7588,13 +7623,18 @@
       <c r="AI147" s="38"/>
       <c r="AJ147" s="38"/>
       <c r="AK147" s="50"/>
+    </row>
+    <row r="148" spans="35:37" x14ac:dyDescent="0.25">
+      <c r="AI148" s="38"/>
+      <c r="AJ148" s="38"/>
+      <c r="AK148" s="50"/>
     </row>
   </sheetData>
   <phoneticPr fontId="24" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="C35" formula="1"/>
+    <ignoredError sqref="C36" formula="1"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId2"/>
 </worksheet>

--- a/SubRES_TMPL/SubRES_NewTechs.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A15B212-36D6-4A0C-B8EE-086BF3658306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CF0000B-F091-4853-8725-B85E8104F935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PRI_Sector_Fuels" sheetId="6" r:id="rId1"/>
@@ -2282,7 +2282,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2343,6 +2343,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2420,7 +2426,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="127">
+  <cellXfs count="132">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
@@ -2547,10 +2553,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="21" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="21" fillId="8" borderId="0" xfId="21" applyFont="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="21" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="21" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="21" fillId="0" borderId="0" xfId="21" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="7" borderId="0" xfId="4" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="21" fillId="10" borderId="0" xfId="4" applyFont="1" applyFill="1"/>
@@ -2575,13 +2577,10 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="16" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="4" applyFont="1"/>
     <xf numFmtId="165" fontId="25" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="25" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="25" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="25" fillId="8" borderId="0" xfId="4" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="25" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="25" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -2591,8 +2590,6 @@
     <xf numFmtId="0" fontId="26" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="16" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="8" borderId="0" xfId="4" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="16" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="16" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2600,34 +2597,48 @@
     </xf>
     <xf numFmtId="0" fontId="27" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="28" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="28" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="28" fillId="8" borderId="0" xfId="4" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="28" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="4" applyFont="1"/>
-    <xf numFmtId="166" fontId="28" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="28" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="28" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="28" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="30" fillId="8" borderId="0" xfId="4" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="4" applyFont="1"/>
     <xf numFmtId="165" fontId="30" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="30" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="30" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="30" fillId="8" borderId="0" xfId="21" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="30" fillId="8" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="31" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="28" fillId="8" borderId="0" xfId="21" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="28" fillId="8" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="25" fillId="12" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="25" fillId="12" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="16" fillId="12" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="16" fillId="12" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="16" fillId="12" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" xfId="4" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="21" fillId="12" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="21" fillId="12" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="21" fillId="12" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="28" fillId="12" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" xfId="4" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="28" fillId="12" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="28" fillId="12" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" xfId="4" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="29" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="30" fillId="12" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="30" fillId="12" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" xfId="4" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="30" fillId="12" borderId="0" xfId="21" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="28" fillId="12" borderId="0" xfId="21" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="21" fillId="12" borderId="0" xfId="21" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="21" fillId="12" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="22">
     <cellStyle name="20% - Accent5 2" xfId="18" xr:uid="{4C3A48E2-3C46-4D12-9A64-54698D8BF8EE}"/>
@@ -3117,10 +3128,10 @@
       <c r="D2" s="38" t="s">
         <v>73</v>
       </c>
-      <c r="E2" s="71" t="s">
+      <c r="E2" s="67" t="s">
         <v>58</v>
       </c>
-      <c r="F2" s="71" t="s">
+      <c r="F2" s="67" t="s">
         <v>109</v>
       </c>
       <c r="G2" s="14"/>
@@ -3143,10 +3154,10 @@
       <c r="D3" s="38" t="s">
         <v>74</v>
       </c>
-      <c r="E3" s="71" t="s">
+      <c r="E3" s="67" t="s">
         <v>58</v>
       </c>
-      <c r="F3" s="71" t="s">
+      <c r="F3" s="67" t="s">
         <v>109</v>
       </c>
       <c r="G3" s="14"/>
@@ -3185,10 +3196,10 @@
       <c r="D4" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="E4" s="71" t="s">
+      <c r="E4" s="67" t="s">
         <v>58</v>
       </c>
-      <c r="F4" s="71" t="s">
+      <c r="F4" s="67" t="s">
         <v>109</v>
       </c>
       <c r="G4" s="14"/>
@@ -3227,10 +3238,10 @@
       <c r="D5" s="38" t="s">
         <v>75</v>
       </c>
-      <c r="E5" s="71" t="s">
+      <c r="E5" s="67" t="s">
         <v>58</v>
       </c>
-      <c r="F5" s="71" t="s">
+      <c r="F5" s="67" t="s">
         <v>109</v>
       </c>
       <c r="G5" s="14"/>
@@ -4259,19 +4270,19 @@
       <c r="E5" s="53"/>
       <c r="F5" s="53"/>
       <c r="G5" s="53"/>
-      <c r="V5" s="76" t="s">
+      <c r="V5" s="72" t="s">
         <v>69</v>
       </c>
       <c r="X5" s="45" t="s">
         <v>131</v>
       </c>
-      <c r="Y5" s="76" t="s">
+      <c r="Y5" s="72" t="s">
         <v>132</v>
       </c>
-      <c r="Z5" s="76" t="s">
+      <c r="Z5" s="72" t="s">
         <v>58</v>
       </c>
-      <c r="AB5" s="76" t="s">
+      <c r="AB5" s="72" t="s">
         <v>88</v>
       </c>
     </row>
@@ -4282,19 +4293,19 @@
       <c r="E6" s="53"/>
       <c r="F6" s="53"/>
       <c r="G6" s="53"/>
-      <c r="V6" s="76" t="s">
+      <c r="V6" s="72" t="s">
         <v>69</v>
       </c>
       <c r="X6" s="45" t="s">
         <v>130</v>
       </c>
-      <c r="Y6" s="76" t="s">
+      <c r="Y6" s="72" t="s">
         <v>133</v>
       </c>
-      <c r="Z6" s="76" t="s">
+      <c r="Z6" s="72" t="s">
         <v>58</v>
       </c>
-      <c r="AB6" s="76" t="s">
+      <c r="AB6" s="72" t="s">
         <v>88</v>
       </c>
     </row>
@@ -4314,10 +4325,10 @@
       <c r="Y7" s="45" t="s">
         <v>136</v>
       </c>
-      <c r="Z7" s="76" t="s">
+      <c r="Z7" s="72" t="s">
         <v>58</v>
       </c>
-      <c r="AB7" s="76" t="s">
+      <c r="AB7" s="72" t="s">
         <v>88</v>
       </c>
     </row>
@@ -4332,10 +4343,10 @@
       <c r="Y8" s="50" t="s">
         <v>161</v>
       </c>
-      <c r="Z8" s="76" t="s">
+      <c r="Z8" s="72" t="s">
         <v>58</v>
       </c>
-      <c r="AB8" s="76" t="s">
+      <c r="AB8" s="72" t="s">
         <v>88</v>
       </c>
       <c r="AE8" s="46"/>
@@ -4351,11 +4362,11 @@
       <c r="Y9" s="50" t="s">
         <v>151</v>
       </c>
-      <c r="Z9" s="76" t="s">
+      <c r="Z9" s="72" t="s">
         <v>58</v>
       </c>
       <c r="AA9" s="50"/>
-      <c r="AB9" s="76" t="s">
+      <c r="AB9" s="72" t="s">
         <v>88</v>
       </c>
       <c r="AC9" s="50"/>
@@ -4371,11 +4382,11 @@
       <c r="Y10" s="45" t="s">
         <v>168</v>
       </c>
-      <c r="Z10" s="76" t="s">
+      <c r="Z10" s="72" t="s">
         <v>58</v>
       </c>
       <c r="AA10" s="50"/>
-      <c r="AB10" s="76" t="s">
+      <c r="AB10" s="72" t="s">
         <v>88</v>
       </c>
       <c r="AC10" s="50"/>
@@ -4391,10 +4402,10 @@
       <c r="Y11" s="45" t="s">
         <v>157</v>
       </c>
-      <c r="Z11" s="76" t="s">
+      <c r="Z11" s="72" t="s">
         <v>58</v>
       </c>
-      <c r="AB11" s="76" t="s">
+      <c r="AB11" s="72" t="s">
         <v>88</v>
       </c>
     </row>
@@ -4408,10 +4419,10 @@
       <c r="Y12" s="45" t="s">
         <v>160</v>
       </c>
-      <c r="Z12" s="76" t="s">
+      <c r="Z12" s="72" t="s">
         <v>58</v>
       </c>
-      <c r="AB12" s="76" t="s">
+      <c r="AB12" s="72" t="s">
         <v>88</v>
       </c>
     </row>
@@ -4425,23 +4436,23 @@
       <c r="Y13" s="45" t="s">
         <v>163</v>
       </c>
-      <c r="Z13" s="76" t="s">
+      <c r="Z13" s="72" t="s">
         <v>58</v>
       </c>
-      <c r="AB13" s="76" t="s">
+      <c r="AB13" s="72" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="14" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="Z14" s="76"/>
-      <c r="AB14" s="76"/>
+      <c r="Z14" s="72"/>
+      <c r="AB14" s="72"/>
     </row>
     <row r="15" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="Z15" s="76"/>
-      <c r="AB15" s="76"/>
+      <c r="Z15" s="72"/>
+      <c r="AB15" s="72"/>
     </row>
     <row r="16" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="AB16" s="76"/>
+      <c r="AB16" s="72"/>
     </row>
     <row r="17" spans="2:51" x14ac:dyDescent="0.25">
       <c r="D17" s="55" t="s">
@@ -4459,19 +4470,19 @@
       <c r="Z17" s="50"/>
       <c r="AI17"/>
       <c r="AJ17" s="39"/>
-      <c r="AK17" s="76"/>
-      <c r="AL17" s="76"/>
-      <c r="AM17" s="76"/>
-      <c r="AN17" s="76"/>
-      <c r="AO17" s="76"/>
-      <c r="AP17" s="76"/>
-      <c r="AQ17" s="76"/>
-      <c r="AR17" s="76"/>
-      <c r="AS17" s="76"/>
-      <c r="AT17" s="76"/>
-      <c r="AU17" s="76"/>
-      <c r="AV17" s="76"/>
-      <c r="AW17" s="76"/>
+      <c r="AK17" s="72"/>
+      <c r="AL17" s="72"/>
+      <c r="AM17" s="72"/>
+      <c r="AN17" s="72"/>
+      <c r="AO17" s="72"/>
+      <c r="AP17" s="72"/>
+      <c r="AQ17" s="72"/>
+      <c r="AR17" s="72"/>
+      <c r="AS17" s="72"/>
+      <c r="AT17" s="72"/>
+      <c r="AU17" s="72"/>
+      <c r="AV17" s="72"/>
+      <c r="AW17" s="72"/>
     </row>
     <row r="18" spans="2:51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="56" t="s">
@@ -4549,19 +4560,19 @@
       <c r="AD18" s="50"/>
       <c r="AI18"/>
       <c r="AJ18" s="39"/>
-      <c r="AK18" s="76"/>
-      <c r="AL18" s="76"/>
-      <c r="AM18" s="76"/>
-      <c r="AN18" s="76"/>
-      <c r="AO18" s="76"/>
-      <c r="AP18" s="76"/>
-      <c r="AQ18" s="76"/>
-      <c r="AR18" s="76"/>
-      <c r="AS18" s="76"/>
-      <c r="AT18" s="76"/>
-      <c r="AU18" s="76"/>
-      <c r="AV18" s="76"/>
-      <c r="AW18" s="76"/>
+      <c r="AK18" s="72"/>
+      <c r="AL18" s="72"/>
+      <c r="AM18" s="72"/>
+      <c r="AN18" s="72"/>
+      <c r="AO18" s="72"/>
+      <c r="AP18" s="72"/>
+      <c r="AQ18" s="72"/>
+      <c r="AR18" s="72"/>
+      <c r="AS18" s="72"/>
+      <c r="AT18" s="72"/>
+      <c r="AU18" s="72"/>
+      <c r="AV18" s="72"/>
+      <c r="AW18" s="72"/>
       <c r="AY18" s="46"/>
     </row>
     <row r="19" spans="2:51" ht="31.8" thickBot="1" x14ac:dyDescent="0.3">
@@ -4613,10 +4624,10 @@
       <c r="Q19" s="33" t="s">
         <v>114</v>
       </c>
-      <c r="R19" s="74" t="s">
+      <c r="R19" s="70" t="s">
         <v>114</v>
       </c>
-      <c r="S19" s="74" t="s">
+      <c r="S19" s="70" t="s">
         <v>127</v>
       </c>
       <c r="V19" s="31" t="s">
@@ -4680,7 +4691,7 @@
       <c r="P20" s="36"/>
       <c r="Q20" s="36"/>
       <c r="R20" s="35"/>
-      <c r="S20" s="75"/>
+      <c r="S20" s="71"/>
       <c r="V20" s="31" t="s">
         <v>81</v>
       </c>
@@ -4704,72 +4715,72 @@
       <c r="AJ20" s="39"/>
       <c r="AY20" s="46"/>
     </row>
-    <row r="21" spans="2:51" s="85" customFormat="1" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="85" t="str">
+    <row r="21" spans="2:51" s="80" customFormat="1" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="80" t="str">
         <f>X21</f>
         <v>Furnace</v>
       </c>
-      <c r="C21" s="85" t="s">
+      <c r="C21" s="80" t="s">
         <v>69</v>
       </c>
-      <c r="D21" s="86" t="str">
+      <c r="D21" s="81" t="str">
         <f>X11</f>
         <v>GEHEAT</v>
       </c>
-      <c r="E21" s="87">
+      <c r="E21" s="110">
         <v>2030</v>
       </c>
-      <c r="F21" s="88">
+      <c r="F21" s="111">
         <v>1</v>
       </c>
-      <c r="G21" s="88">
+      <c r="G21" s="111">
         <v>1</v>
       </c>
-      <c r="H21" s="87">
+      <c r="H21" s="110">
         <v>25</v>
       </c>
-      <c r="I21" s="88">
+      <c r="I21" s="111">
         <v>81</v>
       </c>
-      <c r="J21" s="88">
+      <c r="J21" s="111">
         <v>0</v>
       </c>
-      <c r="K21" s="88">
+      <c r="K21" s="111">
         <v>0.24</v>
       </c>
-      <c r="L21" s="88">
+      <c r="L21" s="111">
         <v>8.76</v>
       </c>
-      <c r="M21" s="87"/>
-      <c r="N21" s="88">
+      <c r="M21" s="110"/>
+      <c r="N21" s="111">
         <v>0.1</v>
       </c>
-      <c r="O21" s="88">
+      <c r="O21" s="111">
         <v>0.15</v>
       </c>
-      <c r="P21" s="88">
+      <c r="P21" s="111">
         <v>0.2</v>
       </c>
-      <c r="Q21" s="88">
+      <c r="Q21" s="111">
         <v>0.25</v>
       </c>
-      <c r="R21" s="88">
+      <c r="R21" s="111">
         <v>0.35</v>
       </c>
-      <c r="S21" s="87"/>
-      <c r="T21" s="89"/>
-      <c r="U21" s="89"/>
-      <c r="V21" s="90" t="s">
+      <c r="S21" s="110"/>
+      <c r="T21" s="82"/>
+      <c r="U21" s="82"/>
+      <c r="V21" s="83" t="s">
         <v>139</v>
       </c>
-      <c r="W21" s="90"/>
-      <c r="X21" s="91" t="s">
+      <c r="W21" s="83"/>
+      <c r="X21" s="84" t="s">
         <v>66</v>
       </c>
-      <c r="Y21" s="92" t="s">
+      <c r="Y21" s="85" t="s">
         <v>140</v>
       </c>
-      <c r="Z21" s="85" t="s">
+      <c r="Z21" s="80" t="s">
         <v>58</v>
       </c>
       <c r="AA21" s="31" t="s">
@@ -4780,145 +4791,150 @@
       </c>
       <c r="AC21" s="31"/>
       <c r="AD21" s="31"/>
-      <c r="AI21" s="94"/>
-      <c r="AJ21" s="95"/>
-      <c r="AY21" s="89"/>
-    </row>
-    <row r="22" spans="2:51" s="76" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="76" t="str">
+      <c r="AI21" s="87"/>
+      <c r="AJ21" s="88"/>
+      <c r="AY21" s="82"/>
+    </row>
+    <row r="22" spans="2:51" s="72" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="72" t="str">
         <f>X$22</f>
         <v>BIOBoiler</v>
       </c>
-      <c r="C22" s="76" t="str">
+      <c r="C22" s="72" t="str">
         <f>PRI_Sector_Fuels!P5</f>
         <v>MANBIOMIN</v>
       </c>
-      <c r="D22" s="83" t="str">
+      <c r="D22" s="78" t="str">
         <f>X8</f>
         <v>DECRHEAT</v>
       </c>
-      <c r="E22" s="96">
+      <c r="E22" s="112">
         <v>2030</v>
       </c>
-      <c r="F22" s="82">
+      <c r="F22" s="113">
         <v>0.7</v>
       </c>
-      <c r="G22" s="82">
+      <c r="G22" s="113">
         <v>0.98</v>
       </c>
-      <c r="H22" s="96">
+      <c r="H22" s="112">
         <v>25</v>
       </c>
-      <c r="I22" s="82">
+      <c r="I22" s="113">
         <v>797.9</v>
       </c>
-      <c r="J22" s="82">
+      <c r="J22" s="113">
         <v>48.48</v>
       </c>
-      <c r="K22" s="82">
+      <c r="K22" s="113">
         <v>3.75</v>
       </c>
-      <c r="L22" s="82">
+      <c r="L22" s="113">
         <v>8.76</v>
       </c>
-      <c r="M22" s="96"/>
-      <c r="N22" s="97"/>
-      <c r="O22" s="96"/>
-      <c r="P22" s="96"/>
-      <c r="Q22" s="96"/>
-      <c r="R22" s="96"/>
-      <c r="S22" s="96"/>
-      <c r="T22" s="98"/>
-      <c r="U22" s="98"/>
-      <c r="V22" s="84" t="s">
+      <c r="M22" s="112"/>
+      <c r="N22" s="114"/>
+      <c r="O22" s="112"/>
+      <c r="P22" s="112"/>
+      <c r="Q22" s="112"/>
+      <c r="R22" s="112"/>
+      <c r="S22" s="112"/>
+      <c r="T22" s="89"/>
+      <c r="U22" s="89"/>
+      <c r="V22" s="79" t="s">
         <v>139</v>
       </c>
-      <c r="W22" s="84"/>
-      <c r="X22" s="99" t="s">
+      <c r="W22" s="79"/>
+      <c r="X22" s="90" t="s">
         <v>94</v>
       </c>
-      <c r="Y22" s="100" t="s">
+      <c r="Y22" s="91" t="s">
         <v>141</v>
       </c>
-      <c r="Z22" s="76" t="s">
+      <c r="Z22" s="72" t="s">
         <v>58</v>
       </c>
-      <c r="AA22" s="85" t="s">
+      <c r="AA22" s="80" t="s">
         <v>87</v>
       </c>
-      <c r="AB22" s="93" t="s">
+      <c r="AB22" s="86" t="s">
         <v>88</v>
       </c>
-      <c r="AC22" s="89"/>
-      <c r="AD22" s="89"/>
+      <c r="AC22" s="82"/>
+      <c r="AD22" s="82"/>
       <c r="AI22" s="14"/>
       <c r="AJ22" s="12"/>
-      <c r="AY22" s="98"/>
-    </row>
-    <row r="23" spans="2:51" s="85" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="85" t="str">
+      <c r="AY22" s="89"/>
+    </row>
+    <row r="23" spans="2:51" s="80" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="80" t="str">
         <f>X25</f>
         <v>ELCBoiler</v>
       </c>
-      <c r="C23" s="85" t="s">
+      <c r="C23" s="80" t="s">
         <v>69</v>
       </c>
-      <c r="D23" s="86" t="str">
+      <c r="D23" s="81" t="str">
         <f>X11</f>
         <v>GEHEAT</v>
       </c>
-      <c r="E23" s="87">
+      <c r="E23" s="110">
         <v>2030</v>
       </c>
-      <c r="F23" s="88">
+      <c r="F23" s="111">
         <v>0.99</v>
       </c>
-      <c r="G23" s="88">
+      <c r="G23" s="111">
         <v>1</v>
       </c>
-      <c r="H23" s="87">
+      <c r="H23" s="110">
         <v>25</v>
       </c>
-      <c r="I23" s="88">
+      <c r="I23" s="111">
         <v>112.9</v>
       </c>
-      <c r="J23" s="88">
+      <c r="J23" s="111">
         <v>14.26</v>
       </c>
-      <c r="K23" s="88">
+      <c r="K23" s="111">
         <v>1.22</v>
       </c>
-      <c r="L23" s="88">
+      <c r="L23" s="111">
         <v>8.76</v>
       </c>
-      <c r="M23" s="87"/>
-      <c r="S23" s="87"/>
-      <c r="T23" s="89"/>
-      <c r="U23" s="89"/>
-      <c r="V23" s="90" t="s">
+      <c r="M23" s="110"/>
+      <c r="N23" s="115"/>
+      <c r="O23" s="115"/>
+      <c r="P23" s="115"/>
+      <c r="Q23" s="115"/>
+      <c r="R23" s="115"/>
+      <c r="S23" s="110"/>
+      <c r="T23" s="82"/>
+      <c r="U23" s="82"/>
+      <c r="V23" s="83" t="s">
         <v>128</v>
       </c>
-      <c r="W23" s="90"/>
-      <c r="X23" s="91" t="s">
+      <c r="W23" s="83"/>
+      <c r="X23" s="84" t="s">
         <v>95</v>
       </c>
-      <c r="Y23" s="92" t="s">
+      <c r="Y23" s="85" t="s">
         <v>142</v>
       </c>
-      <c r="Z23" s="85" t="s">
+      <c r="Z23" s="80" t="s">
         <v>58</v>
       </c>
-      <c r="AA23" s="76" t="s">
+      <c r="AA23" s="72" t="s">
         <v>87</v>
       </c>
-      <c r="AB23" s="101" t="s">
+      <c r="AB23" s="92" t="s">
         <v>88</v>
       </c>
-      <c r="AC23" s="98"/>
-      <c r="AD23" s="98"/>
-      <c r="AI23" s="94"/>
-      <c r="AJ23" s="95"/>
-      <c r="AY23" s="89"/>
+      <c r="AC23" s="89"/>
+      <c r="AD23" s="89"/>
+      <c r="AI23" s="87"/>
+      <c r="AJ23" s="88"/>
+      <c r="AY23" s="82"/>
     </row>
     <row r="24" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B24" s="45" t="str">
@@ -4932,47 +4948,47 @@
       <c r="D24" s="50" t="s">
         <v>108</v>
       </c>
-      <c r="E24" s="43">
+      <c r="E24" s="116">
         <v>2030</v>
       </c>
-      <c r="F24" s="64">
+      <c r="F24" s="117">
         <v>0.55600000000000005</v>
       </c>
-      <c r="G24" s="64">
+      <c r="G24" s="117">
         <v>0.98</v>
       </c>
-      <c r="H24" s="43">
+      <c r="H24" s="116">
         <v>25</v>
       </c>
-      <c r="I24" s="64">
+      <c r="I24" s="117">
         <v>297.10000000000002</v>
       </c>
-      <c r="J24" s="64">
+      <c r="J24" s="117">
         <v>4.46</v>
       </c>
-      <c r="K24" s="64">
+      <c r="K24" s="117">
         <v>0.45</v>
       </c>
-      <c r="L24" s="64">
+      <c r="L24" s="117">
         <v>8.76</v>
       </c>
-      <c r="M24" s="43"/>
-      <c r="N24" s="64">
+      <c r="M24" s="116"/>
+      <c r="N24" s="117">
         <v>0.1</v>
       </c>
-      <c r="O24" s="64">
+      <c r="O24" s="117">
         <v>0.15</v>
       </c>
-      <c r="P24" s="64">
+      <c r="P24" s="117">
         <v>0.2</v>
       </c>
-      <c r="Q24" s="64">
+      <c r="Q24" s="117">
         <v>0.25</v>
       </c>
-      <c r="R24" s="64">
+      <c r="R24" s="117">
         <v>0.35</v>
       </c>
-      <c r="S24" s="43"/>
+      <c r="S24" s="116"/>
       <c r="V24" s="60" t="s">
         <v>128</v>
       </c>
@@ -4986,14 +5002,14 @@
       <c r="Z24" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="AA24" s="85" t="s">
+      <c r="AA24" s="80" t="s">
         <v>87</v>
       </c>
-      <c r="AB24" s="93" t="s">
+      <c r="AB24" s="86" t="s">
         <v>88</v>
       </c>
-      <c r="AC24" s="89"/>
-      <c r="AD24" s="89"/>
+      <c r="AC24" s="82"/>
+      <c r="AD24" s="82"/>
       <c r="AI24"/>
       <c r="AJ24"/>
       <c r="AK24" s="45"/>
@@ -5022,37 +5038,37 @@
       <c r="D25" s="50" t="s">
         <v>107</v>
       </c>
-      <c r="E25" s="43">
+      <c r="E25" s="116">
         <v>2030</v>
       </c>
-      <c r="F25" s="64">
+      <c r="F25" s="117">
         <v>0.75</v>
       </c>
-      <c r="G25" s="64">
+      <c r="G25" s="117">
         <v>0.99</v>
       </c>
-      <c r="H25" s="43">
+      <c r="H25" s="116">
         <v>25</v>
       </c>
-      <c r="I25" s="64">
+      <c r="I25" s="117">
         <v>61.4</v>
       </c>
-      <c r="J25" s="64">
+      <c r="J25" s="117">
         <v>2.57</v>
       </c>
-      <c r="K25" s="64">
+      <c r="K25" s="117">
         <v>1.35</v>
       </c>
-      <c r="L25" s="64">
+      <c r="L25" s="117">
         <v>8.76</v>
       </c>
-      <c r="M25" s="43"/>
-      <c r="N25" s="67"/>
-      <c r="O25" s="43"/>
-      <c r="P25" s="43"/>
-      <c r="Q25" s="43"/>
-      <c r="R25" s="43"/>
-      <c r="S25" s="43"/>
+      <c r="M25" s="116"/>
+      <c r="N25" s="118"/>
+      <c r="O25" s="116"/>
+      <c r="P25" s="116"/>
+      <c r="Q25" s="116"/>
+      <c r="R25" s="116"/>
+      <c r="S25" s="116"/>
       <c r="V25" s="60" t="s">
         <v>139</v>
       </c>
@@ -5074,19 +5090,19 @@
       </c>
       <c r="AI25"/>
       <c r="AJ25"/>
-      <c r="AK25" s="76"/>
-      <c r="AL25" s="76"/>
-      <c r="AM25" s="76"/>
-      <c r="AN25" s="76"/>
-      <c r="AO25" s="76"/>
-      <c r="AP25" s="76"/>
-      <c r="AQ25" s="76"/>
-      <c r="AR25" s="76"/>
-      <c r="AS25" s="76"/>
-      <c r="AT25" s="76"/>
-      <c r="AU25" s="76"/>
-      <c r="AV25" s="76"/>
-      <c r="AW25" s="76"/>
+      <c r="AK25" s="72"/>
+      <c r="AL25" s="72"/>
+      <c r="AM25" s="72"/>
+      <c r="AN25" s="72"/>
+      <c r="AO25" s="72"/>
+      <c r="AP25" s="72"/>
+      <c r="AQ25" s="72"/>
+      <c r="AR25" s="72"/>
+      <c r="AS25" s="72"/>
+      <c r="AT25" s="72"/>
+      <c r="AU25" s="72"/>
+      <c r="AV25" s="72"/>
+      <c r="AW25" s="72"/>
     </row>
     <row r="26" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B26" s="50" t="str">
@@ -5100,37 +5116,37 @@
       <c r="D26" s="50" t="s">
         <v>130</v>
       </c>
-      <c r="E26" s="43">
+      <c r="E26" s="116">
         <v>2030</v>
       </c>
-      <c r="F26" s="82">
+      <c r="F26" s="113">
         <v>1</v>
       </c>
-      <c r="G26" s="64">
+      <c r="G26" s="117">
         <v>0.97</v>
       </c>
-      <c r="H26" s="43">
+      <c r="H26" s="116">
         <v>25</v>
       </c>
-      <c r="I26" s="64">
+      <c r="I26" s="117">
         <v>1041</v>
       </c>
-      <c r="J26" s="64">
+      <c r="J26" s="117">
         <v>38</v>
       </c>
-      <c r="K26" s="64">
+      <c r="K26" s="117">
         <v>0</v>
       </c>
-      <c r="L26" s="64">
+      <c r="L26" s="117">
         <v>8.76</v>
       </c>
-      <c r="M26" s="67"/>
-      <c r="N26" s="67"/>
-      <c r="O26" s="64"/>
-      <c r="P26" s="64"/>
-      <c r="Q26" s="64"/>
-      <c r="R26" s="67"/>
-      <c r="S26" s="43">
+      <c r="M26" s="118"/>
+      <c r="N26" s="118"/>
+      <c r="O26" s="117"/>
+      <c r="P26" s="117"/>
+      <c r="Q26" s="117"/>
+      <c r="R26" s="118"/>
+      <c r="S26" s="116">
         <v>0.2</v>
       </c>
       <c r="V26" s="60" t="s">
@@ -5154,19 +5170,19 @@
       </c>
       <c r="AI26"/>
       <c r="AJ26"/>
-      <c r="AK26" s="76"/>
-      <c r="AL26" s="76"/>
-      <c r="AM26" s="76"/>
-      <c r="AN26" s="76"/>
-      <c r="AO26" s="76"/>
-      <c r="AP26" s="76"/>
-      <c r="AQ26" s="76"/>
-      <c r="AR26" s="76"/>
-      <c r="AS26" s="76"/>
-      <c r="AT26" s="76"/>
-      <c r="AU26" s="76"/>
-      <c r="AV26" s="76"/>
-      <c r="AW26" s="76"/>
+      <c r="AK26" s="72"/>
+      <c r="AL26" s="72"/>
+      <c r="AM26" s="72"/>
+      <c r="AN26" s="72"/>
+      <c r="AO26" s="72"/>
+      <c r="AP26" s="72"/>
+      <c r="AQ26" s="72"/>
+      <c r="AR26" s="72"/>
+      <c r="AS26" s="72"/>
+      <c r="AT26" s="72"/>
+      <c r="AU26" s="72"/>
+      <c r="AV26" s="72"/>
+      <c r="AW26" s="72"/>
     </row>
     <row r="27" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B27" s="50" t="str">
@@ -5180,37 +5196,37 @@
       <c r="D27" s="50" t="s">
         <v>131</v>
       </c>
-      <c r="E27" s="43">
+      <c r="E27" s="116">
         <v>2030</v>
       </c>
-      <c r="F27" s="82">
+      <c r="F27" s="113">
         <v>0.20499999999999999</v>
       </c>
-      <c r="G27" s="64">
+      <c r="G27" s="117">
         <v>0.99</v>
       </c>
-      <c r="H27" s="43">
+      <c r="H27" s="116">
         <v>25</v>
       </c>
-      <c r="I27" s="64">
+      <c r="I27" s="117">
         <v>691</v>
       </c>
-      <c r="J27" s="64">
+      <c r="J27" s="117">
         <v>6.99</v>
       </c>
-      <c r="K27" s="64">
+      <c r="K27" s="117">
         <v>0</v>
       </c>
-      <c r="L27" s="64">
+      <c r="L27" s="117">
         <v>8.76</v>
       </c>
-      <c r="M27" s="67"/>
-      <c r="N27" s="67"/>
-      <c r="O27" s="64"/>
-      <c r="P27" s="64"/>
-      <c r="Q27" s="64"/>
-      <c r="R27" s="67"/>
-      <c r="S27" s="43">
+      <c r="M27" s="118"/>
+      <c r="N27" s="118"/>
+      <c r="O27" s="117"/>
+      <c r="P27" s="117"/>
+      <c r="Q27" s="117"/>
+      <c r="R27" s="118"/>
+      <c r="S27" s="116">
         <v>0.3</v>
       </c>
       <c r="V27" s="60" t="s">
@@ -5248,61 +5264,61 @@
       <c r="AV27" s="45"/>
       <c r="AW27" s="45"/>
     </row>
-    <row r="28" spans="2:51" s="98" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="83" t="str">
+    <row r="28" spans="2:51" s="89" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="78" t="str">
         <f>X26</f>
         <v>CSP</v>
       </c>
-      <c r="C28" s="76" t="str">
+      <c r="C28" s="72" t="str">
         <f>PRI_Sector_Fuels!D20</f>
         <v>SOLAR</v>
       </c>
-      <c r="D28" s="83" t="str">
+      <c r="D28" s="78" t="str">
         <f>X8</f>
         <v>DECRHEAT</v>
       </c>
-      <c r="E28" s="96">
+      <c r="E28" s="112">
         <v>2030</v>
       </c>
-      <c r="F28" s="82">
+      <c r="F28" s="113">
         <v>0.4</v>
       </c>
-      <c r="G28" s="82">
+      <c r="G28" s="113">
         <v>1</v>
       </c>
-      <c r="H28" s="96">
+      <c r="H28" s="112">
         <v>25</v>
       </c>
-      <c r="I28" s="82">
+      <c r="I28" s="113">
         <v>3677</v>
       </c>
-      <c r="J28" s="82">
+      <c r="J28" s="113">
         <v>0</v>
       </c>
-      <c r="K28" s="82">
+      <c r="K28" s="113">
         <v>14</v>
       </c>
-      <c r="L28" s="82">
+      <c r="L28" s="113">
         <v>8.76</v>
       </c>
-      <c r="M28" s="97"/>
-      <c r="N28" s="97"/>
-      <c r="O28" s="82"/>
-      <c r="P28" s="82"/>
-      <c r="Q28" s="82"/>
-      <c r="R28" s="97"/>
-      <c r="S28" s="96"/>
-      <c r="V28" s="84" t="s">
+      <c r="M28" s="114"/>
+      <c r="N28" s="114"/>
+      <c r="O28" s="113"/>
+      <c r="P28" s="113"/>
+      <c r="Q28" s="113"/>
+      <c r="R28" s="114"/>
+      <c r="S28" s="112"/>
+      <c r="V28" s="79" t="s">
         <v>69</v>
       </c>
-      <c r="W28" s="84"/>
-      <c r="X28" s="99" t="s">
+      <c r="W28" s="79"/>
+      <c r="X28" s="90" t="s">
         <v>90</v>
       </c>
-      <c r="Y28" s="100" t="s">
+      <c r="Y28" s="91" t="s">
         <v>147</v>
       </c>
-      <c r="Z28" s="76" t="s">
+      <c r="Z28" s="72" t="s">
         <v>58</v>
       </c>
       <c r="AA28" s="45" t="s">
@@ -5315,19 +5331,19 @@
       <c r="AD28" s="46"/>
       <c r="AI28" s="14"/>
       <c r="AJ28" s="14"/>
-      <c r="AK28" s="76"/>
-      <c r="AL28" s="76"/>
-      <c r="AM28" s="76"/>
-      <c r="AN28" s="76"/>
-      <c r="AO28" s="76"/>
-      <c r="AP28" s="76"/>
-      <c r="AQ28" s="76"/>
-      <c r="AR28" s="76"/>
-      <c r="AS28" s="76"/>
-      <c r="AT28" s="76"/>
-      <c r="AU28" s="76"/>
-      <c r="AV28" s="76"/>
-      <c r="AW28" s="76"/>
+      <c r="AK28" s="72"/>
+      <c r="AL28" s="72"/>
+      <c r="AM28" s="72"/>
+      <c r="AN28" s="72"/>
+      <c r="AO28" s="72"/>
+      <c r="AP28" s="72"/>
+      <c r="AQ28" s="72"/>
+      <c r="AR28" s="72"/>
+      <c r="AS28" s="72"/>
+      <c r="AT28" s="72"/>
+      <c r="AU28" s="72"/>
+      <c r="AV28" s="72"/>
+      <c r="AW28" s="72"/>
     </row>
     <row r="29" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B29" s="50" t="str">
@@ -5338,37 +5354,37 @@
       <c r="D29" s="50" t="s">
         <v>106</v>
       </c>
-      <c r="E29" s="43">
+      <c r="E29" s="116">
         <v>2030</v>
       </c>
-      <c r="F29" s="82">
+      <c r="F29" s="113">
         <v>0.3</v>
       </c>
-      <c r="G29" s="64">
+      <c r="G29" s="117">
         <v>1</v>
       </c>
-      <c r="H29" s="43">
+      <c r="H29" s="116">
         <v>25</v>
       </c>
-      <c r="I29" s="64">
+      <c r="I29" s="117">
         <v>0</v>
       </c>
-      <c r="J29" s="64">
+      <c r="J29" s="117">
         <v>0</v>
       </c>
-      <c r="K29" s="64">
+      <c r="K29" s="117">
         <v>0</v>
       </c>
-      <c r="L29" s="64">
+      <c r="L29" s="117">
         <v>8.76</v>
       </c>
-      <c r="M29" s="67"/>
-      <c r="N29" s="67"/>
-      <c r="O29" s="64"/>
-      <c r="P29" s="64"/>
-      <c r="Q29" s="64"/>
-      <c r="R29" s="67"/>
-      <c r="S29" s="43"/>
+      <c r="M29" s="118"/>
+      <c r="N29" s="118"/>
+      <c r="O29" s="117"/>
+      <c r="P29" s="117"/>
+      <c r="Q29" s="117"/>
+      <c r="R29" s="118"/>
+      <c r="S29" s="116"/>
       <c r="V29" s="60" t="s">
         <v>69</v>
       </c>
@@ -5382,14 +5398,14 @@
       <c r="Z29" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="AA29" s="76" t="s">
+      <c r="AA29" s="72" t="s">
         <v>87</v>
       </c>
-      <c r="AB29" s="98" t="s">
+      <c r="AB29" s="89" t="s">
         <v>88</v>
       </c>
-      <c r="AC29" s="98"/>
-      <c r="AD29" s="98"/>
+      <c r="AC29" s="89"/>
+      <c r="AD29" s="89"/>
       <c r="AI29"/>
       <c r="AJ29"/>
       <c r="AK29" s="45"/>
@@ -5406,60 +5422,60 @@
       <c r="AV29" s="45"/>
       <c r="AW29" s="45"/>
     </row>
-    <row r="30" spans="2:51" s="104" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="102" t="str">
+    <row r="30" spans="2:51" s="94" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="93" t="str">
         <f>X29</f>
         <v>DECPOWER</v>
       </c>
-      <c r="C30" s="102" t="s">
+      <c r="C30" s="93" t="s">
         <v>130</v>
       </c>
-      <c r="D30" s="102" t="str">
+      <c r="D30" s="93" t="str">
         <f>X9</f>
         <v>DECELC</v>
       </c>
-      <c r="E30" s="103">
+      <c r="E30" s="119">
         <v>2030</v>
       </c>
-      <c r="F30" s="104">
+      <c r="F30" s="120">
         <v>1</v>
       </c>
-      <c r="G30" s="104">
+      <c r="G30" s="120">
         <v>1</v>
       </c>
-      <c r="H30" s="103">
+      <c r="H30" s="119">
         <v>100</v>
       </c>
-      <c r="I30" s="105">
+      <c r="I30" s="121">
         <v>0</v>
       </c>
-      <c r="J30" s="106">
+      <c r="J30" s="120">
         <v>0</v>
       </c>
-      <c r="K30" s="104">
+      <c r="K30" s="120">
         <v>0</v>
       </c>
-      <c r="L30" s="105">
+      <c r="L30" s="121">
         <v>8.76</v>
       </c>
-      <c r="M30" s="107"/>
-      <c r="N30" s="107"/>
-      <c r="O30" s="105"/>
-      <c r="P30" s="105"/>
-      <c r="Q30" s="105"/>
-      <c r="R30" s="107"/>
-      <c r="S30" s="103"/>
-      <c r="V30" s="108" t="s">
+      <c r="M30" s="122"/>
+      <c r="N30" s="122"/>
+      <c r="O30" s="121"/>
+      <c r="P30" s="121"/>
+      <c r="Q30" s="121"/>
+      <c r="R30" s="122"/>
+      <c r="S30" s="119"/>
+      <c r="V30" s="96" t="s">
         <v>69</v>
       </c>
-      <c r="W30" s="108"/>
-      <c r="X30" s="109" t="s">
+      <c r="W30" s="96"/>
+      <c r="X30" s="97" t="s">
         <v>137</v>
       </c>
-      <c r="Y30" s="110" t="s">
+      <c r="Y30" s="98" t="s">
         <v>149</v>
       </c>
-      <c r="Z30" s="106" t="s">
+      <c r="Z30" s="95" t="s">
         <v>58</v>
       </c>
       <c r="AA30" s="45" t="s">
@@ -5470,65 +5486,65 @@
       </c>
       <c r="AC30" s="46"/>
       <c r="AD30" s="46"/>
-      <c r="AI30" s="111"/>
-      <c r="AJ30" s="111"/>
-      <c r="AK30" s="106"/>
-      <c r="AL30" s="106"/>
-      <c r="AM30" s="106"/>
-      <c r="AN30" s="106"/>
-      <c r="AO30" s="106"/>
-      <c r="AP30" s="106"/>
-      <c r="AQ30" s="106"/>
-      <c r="AR30" s="106"/>
-      <c r="AS30" s="106"/>
-      <c r="AT30" s="106"/>
-      <c r="AU30" s="106"/>
-      <c r="AV30" s="106"/>
-      <c r="AW30" s="106"/>
-    </row>
-    <row r="31" spans="2:51" s="104" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="102" t="str">
+      <c r="AI30" s="99"/>
+      <c r="AJ30" s="99"/>
+      <c r="AK30" s="95"/>
+      <c r="AL30" s="95"/>
+      <c r="AM30" s="95"/>
+      <c r="AN30" s="95"/>
+      <c r="AO30" s="95"/>
+      <c r="AP30" s="95"/>
+      <c r="AQ30" s="95"/>
+      <c r="AR30" s="95"/>
+      <c r="AS30" s="95"/>
+      <c r="AT30" s="95"/>
+      <c r="AU30" s="95"/>
+      <c r="AV30" s="95"/>
+      <c r="AW30" s="95"/>
+    </row>
+    <row r="31" spans="2:51" s="94" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="93" t="str">
         <f>X29</f>
         <v>DECPOWER</v>
       </c>
-      <c r="C31" s="102" t="s">
+      <c r="C31" s="93" t="s">
         <v>131</v>
       </c>
-      <c r="D31" s="102" t="str">
+      <c r="D31" s="93" t="str">
         <f>X9</f>
         <v>DECELC</v>
       </c>
-      <c r="E31" s="103">
+      <c r="E31" s="119">
         <v>2030</v>
       </c>
-      <c r="F31" s="104">
+      <c r="F31" s="120">
         <v>1</v>
       </c>
-      <c r="G31" s="104">
+      <c r="G31" s="120">
         <v>1</v>
       </c>
-      <c r="H31" s="103">
+      <c r="H31" s="119">
         <v>100</v>
       </c>
-      <c r="I31" s="105">
+      <c r="I31" s="121">
         <v>0</v>
       </c>
-      <c r="J31" s="106">
+      <c r="J31" s="120">
         <v>0</v>
       </c>
-      <c r="K31" s="104">
+      <c r="K31" s="120">
         <v>0</v>
       </c>
-      <c r="L31" s="105">
+      <c r="L31" s="121">
         <v>8.76</v>
       </c>
-      <c r="M31" s="107"/>
-      <c r="N31" s="107"/>
-      <c r="O31" s="105"/>
-      <c r="P31" s="105"/>
-      <c r="Q31" s="105"/>
-      <c r="R31" s="107"/>
-      <c r="S31" s="103"/>
+      <c r="M31" s="122"/>
+      <c r="N31" s="122"/>
+      <c r="O31" s="121"/>
+      <c r="P31" s="121"/>
+      <c r="Q31" s="121"/>
+      <c r="R31" s="122"/>
+      <c r="S31" s="119"/>
       <c r="V31" s="46" t="s">
         <v>169</v>
       </c>
@@ -5539,30 +5555,30 @@
       <c r="Y31" s="46" t="s">
         <v>150</v>
       </c>
-      <c r="Z31" s="106" t="s">
+      <c r="Z31" s="95" t="s">
         <v>58</v>
       </c>
-      <c r="AA31" s="106" t="s">
+      <c r="AA31" s="95" t="s">
         <v>87</v>
       </c>
-      <c r="AB31" s="104" t="s">
+      <c r="AB31" s="94" t="s">
         <v>88</v>
       </c>
-      <c r="AI31" s="111"/>
-      <c r="AJ31" s="111"/>
-      <c r="AK31" s="106"/>
-      <c r="AL31" s="106"/>
-      <c r="AM31" s="106"/>
-      <c r="AN31" s="106"/>
-      <c r="AO31" s="106"/>
-      <c r="AP31" s="106"/>
-      <c r="AQ31" s="106"/>
-      <c r="AR31" s="106"/>
-      <c r="AS31" s="106"/>
-      <c r="AT31" s="106"/>
-      <c r="AU31" s="106"/>
-      <c r="AV31" s="106"/>
-      <c r="AW31" s="106"/>
+      <c r="AI31" s="99"/>
+      <c r="AJ31" s="99"/>
+      <c r="AK31" s="95"/>
+      <c r="AL31" s="95"/>
+      <c r="AM31" s="95"/>
+      <c r="AN31" s="95"/>
+      <c r="AO31" s="95"/>
+      <c r="AP31" s="95"/>
+      <c r="AQ31" s="95"/>
+      <c r="AR31" s="95"/>
+      <c r="AS31" s="95"/>
+      <c r="AT31" s="95"/>
+      <c r="AU31" s="95"/>
+      <c r="AV31" s="95"/>
+      <c r="AW31" s="95"/>
     </row>
     <row r="32" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B32" s="50" t="str">
@@ -5575,37 +5591,37 @@
       <c r="D32" s="50" t="s">
         <v>135</v>
       </c>
-      <c r="E32" s="43">
+      <c r="E32" s="116">
         <v>2030</v>
       </c>
-      <c r="F32" s="46">
+      <c r="F32" s="123">
         <v>0.35</v>
       </c>
-      <c r="G32" s="46">
+      <c r="G32" s="123">
         <v>0.98</v>
       </c>
-      <c r="H32" s="43">
+      <c r="H32" s="116">
         <v>20</v>
       </c>
-      <c r="I32" s="112">
+      <c r="I32" s="124">
         <v>3242</v>
       </c>
-      <c r="J32" s="64">
+      <c r="J32" s="117">
         <v>129.68</v>
       </c>
-      <c r="K32" s="64">
+      <c r="K32" s="117">
         <v>0</v>
       </c>
-      <c r="L32" s="64">
+      <c r="L32" s="117">
         <v>8.76</v>
       </c>
-      <c r="M32" s="67"/>
-      <c r="N32" s="67"/>
-      <c r="O32" s="64"/>
-      <c r="P32" s="64"/>
-      <c r="Q32" s="64"/>
-      <c r="R32" s="67"/>
-      <c r="S32" s="43"/>
+      <c r="M32" s="118"/>
+      <c r="N32" s="118"/>
+      <c r="O32" s="117"/>
+      <c r="P32" s="117"/>
+      <c r="Q32" s="117"/>
+      <c r="R32" s="118"/>
+      <c r="S32" s="116"/>
       <c r="V32" s="45" t="s">
         <v>139</v>
       </c>
@@ -5616,16 +5632,16 @@
       <c r="Y32" s="45" t="s">
         <v>165</v>
       </c>
-      <c r="Z32" s="106" t="s">
+      <c r="Z32" s="95" t="s">
         <v>58</v>
       </c>
-      <c r="AA32" s="106" t="s">
+      <c r="AA32" s="95" t="s">
         <v>87</v>
       </c>
-      <c r="AB32" s="104" t="s">
+      <c r="AB32" s="94" t="s">
         <v>88</v>
       </c>
-      <c r="AD32" s="104"/>
+      <c r="AD32" s="94"/>
       <c r="AI32" s="38"/>
       <c r="AJ32" s="38"/>
       <c r="AK32" s="45"/>
@@ -5642,211 +5658,211 @@
       <c r="AV32" s="45"/>
       <c r="AW32" s="45"/>
     </row>
-    <row r="33" spans="1:49" s="104" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="102" t="str">
+    <row r="33" spans="1:49" s="94" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="93" t="str">
         <f>X29</f>
         <v>DECPOWER</v>
       </c>
-      <c r="C33" s="106" t="s">
+      <c r="C33" s="95" t="s">
         <v>135</v>
       </c>
-      <c r="D33" s="102" t="str">
+      <c r="D33" s="93" t="str">
         <f>X9</f>
         <v>DECELC</v>
       </c>
-      <c r="E33" s="103">
+      <c r="E33" s="119">
         <v>2030</v>
       </c>
-      <c r="F33" s="105">
+      <c r="F33" s="121">
         <v>1</v>
       </c>
-      <c r="G33" s="105">
+      <c r="G33" s="121">
         <v>1</v>
       </c>
-      <c r="H33" s="104">
+      <c r="H33" s="120">
         <v>100</v>
       </c>
-      <c r="I33" s="104">
+      <c r="I33" s="120">
         <v>0</v>
       </c>
-      <c r="J33" s="104">
+      <c r="J33" s="120">
         <v>0</v>
       </c>
-      <c r="K33" s="104">
+      <c r="K33" s="120">
         <v>0</v>
       </c>
-      <c r="L33" s="104">
+      <c r="L33" s="120">
         <v>0</v>
       </c>
-      <c r="M33" s="107"/>
-      <c r="N33" s="107"/>
-      <c r="O33" s="105"/>
-      <c r="P33" s="105"/>
-      <c r="Q33" s="105"/>
-      <c r="R33" s="107"/>
-      <c r="S33" s="103"/>
-      <c r="V33" s="111" t="s">
+      <c r="M33" s="122"/>
+      <c r="N33" s="122"/>
+      <c r="O33" s="121"/>
+      <c r="P33" s="121"/>
+      <c r="Q33" s="121"/>
+      <c r="R33" s="122"/>
+      <c r="S33" s="119"/>
+      <c r="V33" s="99" t="s">
         <v>128</v>
       </c>
-      <c r="W33" s="111"/>
-      <c r="X33" s="106" t="s">
+      <c r="W33" s="99"/>
+      <c r="X33" s="95" t="s">
         <v>152</v>
       </c>
-      <c r="Y33" s="126" t="s">
+      <c r="Y33" s="109" t="s">
         <v>166</v>
       </c>
-      <c r="Z33" s="106" t="s">
+      <c r="Z33" s="95" t="s">
         <v>58</v>
       </c>
-      <c r="AA33" s="106" t="s">
+      <c r="AA33" s="95" t="s">
         <v>87</v>
       </c>
-      <c r="AB33" s="104" t="s">
+      <c r="AB33" s="94" t="s">
         <v>88</v>
       </c>
-      <c r="AC33" s="106"/>
+      <c r="AC33" s="95"/>
       <c r="AD33" s="46"/>
-      <c r="AI33" s="111"/>
-      <c r="AJ33" s="111"/>
-      <c r="AK33" s="106"/>
-      <c r="AL33" s="106"/>
-      <c r="AM33" s="106"/>
-      <c r="AN33" s="106"/>
-      <c r="AO33" s="106"/>
-      <c r="AP33" s="106"/>
-      <c r="AQ33" s="106"/>
-      <c r="AR33" s="106"/>
-      <c r="AS33" s="106"/>
-      <c r="AT33" s="106"/>
-      <c r="AU33" s="106"/>
-      <c r="AV33" s="106"/>
-      <c r="AW33" s="106"/>
-    </row>
-    <row r="34" spans="1:49" s="104" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="102" t="str">
+      <c r="AI33" s="99"/>
+      <c r="AJ33" s="99"/>
+      <c r="AK33" s="95"/>
+      <c r="AL33" s="95"/>
+      <c r="AM33" s="95"/>
+      <c r="AN33" s="95"/>
+      <c r="AO33" s="95"/>
+      <c r="AP33" s="95"/>
+      <c r="AQ33" s="95"/>
+      <c r="AR33" s="95"/>
+      <c r="AS33" s="95"/>
+      <c r="AT33" s="95"/>
+      <c r="AU33" s="95"/>
+      <c r="AV33" s="95"/>
+      <c r="AW33" s="95"/>
+    </row>
+    <row r="34" spans="1:49" s="94" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="93" t="str">
         <f>X21</f>
         <v>Furnace</v>
       </c>
-      <c r="C34" s="102" t="str">
+      <c r="C34" s="93" t="str">
         <f>X9</f>
         <v>DECELC</v>
       </c>
-      <c r="D34" s="102" t="str">
+      <c r="D34" s="93" t="str">
         <f>X12</f>
         <v>DECEHEAT</v>
       </c>
-      <c r="E34" s="103">
+      <c r="E34" s="119">
         <v>2030</v>
       </c>
-      <c r="F34" s="105">
+      <c r="F34" s="121">
         <v>1</v>
       </c>
-      <c r="G34" s="105">
+      <c r="G34" s="121">
         <v>1</v>
       </c>
-      <c r="H34" s="104">
+      <c r="H34" s="120">
         <v>100</v>
       </c>
-      <c r="I34" s="104">
+      <c r="I34" s="120">
         <v>0</v>
       </c>
-      <c r="J34" s="104">
+      <c r="J34" s="120">
         <v>0</v>
       </c>
-      <c r="K34" s="104">
+      <c r="K34" s="120">
         <v>0</v>
       </c>
-      <c r="L34" s="104">
+      <c r="L34" s="120">
         <v>0</v>
       </c>
-      <c r="M34" s="107"/>
-      <c r="N34" s="107"/>
-      <c r="O34" s="105"/>
-      <c r="P34" s="105"/>
-      <c r="Q34" s="105"/>
-      <c r="R34" s="107"/>
-      <c r="S34" s="103"/>
-      <c r="V34" s="111" t="s">
+      <c r="M34" s="122"/>
+      <c r="N34" s="122"/>
+      <c r="O34" s="121"/>
+      <c r="P34" s="121"/>
+      <c r="Q34" s="121"/>
+      <c r="R34" s="122"/>
+      <c r="S34" s="119"/>
+      <c r="V34" s="99" t="s">
         <v>128</v>
       </c>
-      <c r="W34" s="111"/>
-      <c r="X34" s="125" t="s">
+      <c r="W34" s="99"/>
+      <c r="X34" s="108" t="s">
         <v>170</v>
       </c>
-      <c r="Y34" s="126" t="s">
+      <c r="Y34" s="109" t="s">
         <v>171</v>
       </c>
-      <c r="Z34" s="106" t="s">
+      <c r="Z34" s="95" t="s">
         <v>58</v>
       </c>
-      <c r="AA34" s="106" t="s">
+      <c r="AA34" s="95" t="s">
         <v>87</v>
       </c>
-      <c r="AB34" s="104" t="s">
+      <c r="AB34" s="94" t="s">
         <v>88</v>
       </c>
-      <c r="AC34" s="106"/>
-      <c r="AD34" s="106"/>
-      <c r="AI34" s="111"/>
-      <c r="AJ34" s="111"/>
-      <c r="AK34" s="106"/>
-      <c r="AL34" s="106"/>
-      <c r="AM34" s="106"/>
-      <c r="AN34" s="106"/>
-      <c r="AO34" s="106"/>
-      <c r="AP34" s="106"/>
-      <c r="AQ34" s="106"/>
-      <c r="AR34" s="106"/>
-      <c r="AS34" s="106"/>
-      <c r="AT34" s="106"/>
-      <c r="AU34" s="106"/>
-      <c r="AV34" s="106"/>
-      <c r="AW34" s="106"/>
-    </row>
-    <row r="35" spans="1:49" s="104" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="102" t="str">
+      <c r="AC34" s="95"/>
+      <c r="AD34" s="95"/>
+      <c r="AI34" s="99"/>
+      <c r="AJ34" s="99"/>
+      <c r="AK34" s="95"/>
+      <c r="AL34" s="95"/>
+      <c r="AM34" s="95"/>
+      <c r="AN34" s="95"/>
+      <c r="AO34" s="95"/>
+      <c r="AP34" s="95"/>
+      <c r="AQ34" s="95"/>
+      <c r="AR34" s="95"/>
+      <c r="AS34" s="95"/>
+      <c r="AT34" s="95"/>
+      <c r="AU34" s="95"/>
+      <c r="AV34" s="95"/>
+      <c r="AW34" s="95"/>
+    </row>
+    <row r="35" spans="1:49" s="94" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="93" t="str">
         <f>X25</f>
         <v>ELCBoiler</v>
       </c>
-      <c r="C35" s="102" t="str">
+      <c r="C35" s="93" t="str">
         <f>X9</f>
         <v>DECELC</v>
       </c>
-      <c r="D35" s="102" t="str">
+      <c r="D35" s="93" t="str">
         <f>X12</f>
         <v>DECEHEAT</v>
       </c>
-      <c r="E35" s="103">
+      <c r="E35" s="119">
         <v>2030</v>
       </c>
-      <c r="F35" s="105">
+      <c r="F35" s="121">
         <v>1</v>
       </c>
-      <c r="G35" s="105">
+      <c r="G35" s="121">
         <v>1</v>
       </c>
-      <c r="H35" s="103">
+      <c r="H35" s="119">
         <v>100</v>
       </c>
-      <c r="I35" s="105">
+      <c r="I35" s="121">
         <v>0</v>
       </c>
-      <c r="J35" s="105">
+      <c r="J35" s="121">
         <v>0</v>
       </c>
-      <c r="K35" s="105">
+      <c r="K35" s="121">
         <v>0</v>
       </c>
-      <c r="L35" s="105">
+      <c r="L35" s="121">
         <v>0</v>
       </c>
-      <c r="M35" s="107"/>
-      <c r="N35" s="107"/>
-      <c r="O35" s="105"/>
-      <c r="P35" s="105"/>
-      <c r="Q35" s="105"/>
-      <c r="R35" s="107"/>
-      <c r="S35" s="103"/>
+      <c r="M35" s="122"/>
+      <c r="N35" s="122"/>
+      <c r="O35" s="121"/>
+      <c r="P35" s="121"/>
+      <c r="Q35" s="121"/>
+      <c r="R35" s="122"/>
+      <c r="S35" s="119"/>
       <c r="V35" s="45"/>
       <c r="W35" s="45"/>
       <c r="X35" s="45"/>
@@ -5854,21 +5870,21 @@
       <c r="Z35" s="50"/>
       <c r="AA35" s="38"/>
       <c r="AB35" s="38"/>
-      <c r="AC35" s="106"/>
-      <c r="AD35" s="106"/>
-      <c r="AI35" s="111"/>
-      <c r="AJ35" s="111"/>
-      <c r="AK35" s="125"/>
-      <c r="AL35" s="125"/>
-      <c r="AM35" s="106"/>
-      <c r="AN35" s="106"/>
-      <c r="AO35" s="106"/>
-      <c r="AQ35" s="111"/>
-      <c r="AR35" s="111"/>
-      <c r="AS35" s="125"/>
-      <c r="AT35" s="125"/>
-      <c r="AU35" s="106"/>
-      <c r="AV35" s="106"/>
+      <c r="AC35" s="95"/>
+      <c r="AD35" s="95"/>
+      <c r="AI35" s="99"/>
+      <c r="AJ35" s="99"/>
+      <c r="AK35" s="108"/>
+      <c r="AL35" s="108"/>
+      <c r="AM35" s="95"/>
+      <c r="AN35" s="95"/>
+      <c r="AO35" s="95"/>
+      <c r="AQ35" s="99"/>
+      <c r="AR35" s="99"/>
+      <c r="AS35" s="108"/>
+      <c r="AT35" s="108"/>
+      <c r="AU35" s="95"/>
+      <c r="AV35" s="95"/>
     </row>
     <row r="36" spans="1:49" s="46" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B36" s="5" t="str">
@@ -5882,44 +5898,44 @@
       <c r="D36" s="50" t="s">
         <v>153</v>
       </c>
-      <c r="E36" s="43">
+      <c r="E36" s="116">
         <v>2030</v>
       </c>
-      <c r="F36" s="82">
+      <c r="F36" s="113">
         <v>1</v>
       </c>
-      <c r="G36" s="64">
+      <c r="G36" s="117">
         <v>1</v>
       </c>
-      <c r="H36" s="46">
+      <c r="H36" s="123">
         <v>100</v>
       </c>
-      <c r="I36" s="46">
+      <c r="I36" s="123">
         <v>0</v>
       </c>
-      <c r="J36" s="46">
+      <c r="J36" s="123">
         <v>0</v>
       </c>
-      <c r="K36" s="46">
+      <c r="K36" s="123">
         <v>0</v>
       </c>
-      <c r="L36" s="46">
+      <c r="L36" s="123">
         <v>0</v>
       </c>
-      <c r="M36" s="43"/>
-      <c r="N36" s="67"/>
-      <c r="O36" s="43"/>
-      <c r="P36" s="43"/>
-      <c r="Q36" s="43"/>
-      <c r="R36" s="43"/>
-      <c r="S36" s="43"/>
-      <c r="V36" s="114"/>
-      <c r="W36" s="113"/>
-      <c r="X36" s="114"/>
-      <c r="Y36" s="113"/>
-      <c r="Z36" s="119"/>
-      <c r="AA36" s="115"/>
-      <c r="AB36" s="120"/>
+      <c r="M36" s="116"/>
+      <c r="N36" s="118"/>
+      <c r="O36" s="116"/>
+      <c r="P36" s="116"/>
+      <c r="Q36" s="116"/>
+      <c r="R36" s="116"/>
+      <c r="S36" s="116"/>
+      <c r="V36" s="101"/>
+      <c r="W36" s="100"/>
+      <c r="X36" s="101"/>
+      <c r="Y36" s="100"/>
+      <c r="Z36" s="103"/>
+      <c r="AA36" s="102"/>
+      <c r="AB36" s="104"/>
       <c r="AC36" s="45"/>
       <c r="AD36" s="45"/>
       <c r="AI36"/>
@@ -5936,105 +5952,117 @@
       <c r="AU36" s="45"/>
       <c r="AV36" s="45"/>
     </row>
-    <row r="37" spans="1:49" s="113" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="114" t="str">
+    <row r="37" spans="1:49" s="100" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="101" t="str">
         <f>X32</f>
         <v>ETHT</v>
       </c>
-      <c r="C37" s="115" t="str">
+      <c r="C37" s="102" t="str">
         <f>X11</f>
         <v>GEHEAT</v>
       </c>
-      <c r="D37" s="115" t="str">
+      <c r="D37" s="102" t="str">
         <f>X13</f>
         <v>ELCHEAT</v>
       </c>
-      <c r="E37" s="116">
+      <c r="E37" s="125">
         <v>2030</v>
       </c>
-      <c r="F37" s="117">
+      <c r="F37" s="126">
         <v>1</v>
       </c>
-      <c r="G37" s="117">
+      <c r="G37" s="126">
         <v>1</v>
       </c>
-      <c r="H37" s="116">
+      <c r="H37" s="125">
         <v>100</v>
       </c>
-      <c r="I37" s="117">
+      <c r="I37" s="126">
         <v>0</v>
       </c>
-      <c r="J37" s="117">
+      <c r="J37" s="126">
         <v>0</v>
       </c>
-      <c r="K37" s="117">
+      <c r="K37" s="126">
         <v>0</v>
       </c>
-      <c r="L37" s="117">
+      <c r="L37" s="126">
         <v>0</v>
       </c>
-      <c r="N37" s="118"/>
-      <c r="V37" s="106"/>
-      <c r="W37" s="106"/>
-      <c r="X37" s="106"/>
-      <c r="Y37" s="106"/>
-      <c r="Z37" s="106"/>
-      <c r="AA37" s="124"/>
-      <c r="AB37" s="106"/>
-      <c r="AC37" s="114"/>
-      <c r="AD37" s="114"/>
-      <c r="AI37" s="121"/>
-      <c r="AJ37" s="121"/>
-      <c r="AK37" s="122"/>
-      <c r="AL37" s="122"/>
-      <c r="AM37" s="114"/>
-      <c r="AN37" s="114"/>
-      <c r="AO37" s="114"/>
-      <c r="AQ37" s="121"/>
-      <c r="AR37" s="121"/>
-      <c r="AS37" s="122"/>
-      <c r="AT37" s="122"/>
-      <c r="AU37" s="114"/>
-      <c r="AV37" s="114"/>
-    </row>
-    <row r="38" spans="1:49" s="104" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="106" t="str">
+      <c r="M37" s="127"/>
+      <c r="N37" s="128"/>
+      <c r="O37" s="127"/>
+      <c r="P37" s="127"/>
+      <c r="Q37" s="127"/>
+      <c r="R37" s="127"/>
+      <c r="S37" s="127"/>
+      <c r="V37" s="95"/>
+      <c r="W37" s="95"/>
+      <c r="X37" s="95"/>
+      <c r="Y37" s="95"/>
+      <c r="Z37" s="95"/>
+      <c r="AA37" s="107"/>
+      <c r="AB37" s="95"/>
+      <c r="AC37" s="101"/>
+      <c r="AD37" s="101"/>
+      <c r="AI37" s="105"/>
+      <c r="AJ37" s="105"/>
+      <c r="AK37" s="106"/>
+      <c r="AL37" s="106"/>
+      <c r="AM37" s="101"/>
+      <c r="AN37" s="101"/>
+      <c r="AO37" s="101"/>
+      <c r="AQ37" s="105"/>
+      <c r="AR37" s="105"/>
+      <c r="AS37" s="106"/>
+      <c r="AT37" s="106"/>
+      <c r="AU37" s="101"/>
+      <c r="AV37" s="101"/>
+    </row>
+    <row r="38" spans="1:49" s="94" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="95" t="str">
         <f>X32</f>
         <v>ETHT</v>
       </c>
-      <c r="C38" s="102" t="str">
+      <c r="C38" s="93" t="str">
         <f>X12</f>
         <v>DECEHEAT</v>
       </c>
-      <c r="D38" s="102" t="str">
+      <c r="D38" s="93" t="str">
         <f>X13</f>
         <v>ELCHEAT</v>
       </c>
-      <c r="E38" s="103">
+      <c r="E38" s="119">
         <v>2030</v>
       </c>
-      <c r="F38" s="105">
+      <c r="F38" s="121">
         <v>1</v>
       </c>
-      <c r="G38" s="105">
+      <c r="G38" s="121">
         <v>1</v>
       </c>
-      <c r="H38" s="103">
+      <c r="H38" s="119">
         <v>100</v>
       </c>
-      <c r="I38" s="105">
+      <c r="I38" s="121">
         <v>0</v>
       </c>
-      <c r="J38" s="105">
+      <c r="J38" s="121">
         <v>0</v>
       </c>
-      <c r="K38" s="105">
+      <c r="K38" s="121">
         <v>0</v>
       </c>
-      <c r="L38" s="105">
+      <c r="L38" s="121">
         <v>0</v>
       </c>
-      <c r="N38" s="123"/>
+      <c r="M38" s="120"/>
+      <c r="N38" s="129"/>
+      <c r="O38" s="120"/>
+      <c r="P38" s="120"/>
+      <c r="Q38" s="120"/>
+      <c r="R38" s="120"/>
+      <c r="S38" s="120"/>
       <c r="V38" s="45"/>
       <c r="W38" s="45"/>
       <c r="X38" s="45"/>
@@ -6042,21 +6070,21 @@
       <c r="Z38" s="45"/>
       <c r="AA38" s="54"/>
       <c r="AB38" s="45"/>
-      <c r="AC38" s="106"/>
-      <c r="AD38" s="106"/>
-      <c r="AI38" s="111"/>
-      <c r="AJ38" s="111"/>
-      <c r="AK38" s="125"/>
-      <c r="AL38" s="125"/>
-      <c r="AM38" s="106"/>
-      <c r="AN38" s="106"/>
-      <c r="AO38" s="106"/>
-      <c r="AQ38" s="111"/>
-      <c r="AR38" s="111"/>
-      <c r="AS38" s="125"/>
-      <c r="AT38" s="125"/>
-      <c r="AU38" s="106"/>
-      <c r="AV38" s="106"/>
+      <c r="AC38" s="95"/>
+      <c r="AD38" s="95"/>
+      <c r="AI38" s="99"/>
+      <c r="AJ38" s="99"/>
+      <c r="AK38" s="108"/>
+      <c r="AL38" s="108"/>
+      <c r="AM38" s="95"/>
+      <c r="AN38" s="95"/>
+      <c r="AO38" s="95"/>
+      <c r="AQ38" s="99"/>
+      <c r="AR38" s="99"/>
+      <c r="AS38" s="108"/>
+      <c r="AT38" s="108"/>
+      <c r="AU38" s="95"/>
+      <c r="AV38" s="95"/>
     </row>
     <row r="39" spans="1:49" s="46" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B39" s="45" t="str">
@@ -6071,31 +6099,37 @@
         <f>X10</f>
         <v>RNWHEAT</v>
       </c>
-      <c r="E39" s="43">
+      <c r="E39" s="116">
         <v>2030</v>
       </c>
-      <c r="F39" s="82">
+      <c r="F39" s="113">
         <v>1</v>
       </c>
-      <c r="G39" s="64">
+      <c r="G39" s="117">
         <v>1</v>
       </c>
-      <c r="H39" s="46">
+      <c r="H39" s="123">
         <v>100</v>
       </c>
-      <c r="I39" s="46">
+      <c r="I39" s="123">
         <v>0</v>
       </c>
-      <c r="J39" s="46">
+      <c r="J39" s="123">
         <v>0</v>
       </c>
-      <c r="K39" s="46">
+      <c r="K39" s="123">
         <v>0</v>
       </c>
-      <c r="L39" s="46">
+      <c r="L39" s="123">
         <v>0</v>
       </c>
-      <c r="N39" s="65"/>
+      <c r="M39" s="123"/>
+      <c r="N39" s="130"/>
+      <c r="O39" s="123"/>
+      <c r="P39" s="123"/>
+      <c r="Q39" s="123"/>
+      <c r="R39" s="123"/>
+      <c r="S39" s="123"/>
       <c r="V39" s="45"/>
       <c r="W39" s="45"/>
       <c r="X39" s="45"/>
@@ -6132,30 +6166,37 @@
         <f>X10</f>
         <v>RNWHEAT</v>
       </c>
-      <c r="E40" s="43">
+      <c r="E40" s="116">
         <v>2030</v>
       </c>
-      <c r="F40" s="82">
+      <c r="F40" s="113">
         <v>1</v>
       </c>
-      <c r="G40" s="64">
+      <c r="G40" s="117">
         <v>1</v>
       </c>
-      <c r="H40" s="46">
+      <c r="H40" s="123">
         <v>100</v>
       </c>
-      <c r="I40" s="46">
+      <c r="I40" s="123">
         <v>0</v>
       </c>
-      <c r="J40" s="46">
+      <c r="J40" s="123">
         <v>0</v>
       </c>
-      <c r="K40" s="46">
+      <c r="K40" s="123">
         <v>0</v>
       </c>
-      <c r="L40" s="46">
+      <c r="L40" s="123">
         <v>0</v>
       </c>
+      <c r="M40" s="123"/>
+      <c r="N40" s="123"/>
+      <c r="O40" s="123"/>
+      <c r="P40" s="123"/>
+      <c r="Q40" s="123"/>
+      <c r="R40" s="123"/>
+      <c r="S40" s="123"/>
       <c r="V40" s="45"/>
       <c r="W40" s="45"/>
       <c r="X40" s="45"/>
@@ -6192,30 +6233,37 @@
       <c r="D41" s="50" t="s">
         <v>107</v>
       </c>
-      <c r="E41" s="43">
+      <c r="E41" s="116">
         <v>2030</v>
       </c>
-      <c r="F41" s="82">
+      <c r="F41" s="113">
         <v>1</v>
       </c>
-      <c r="G41" s="64">
+      <c r="G41" s="117">
         <v>1</v>
       </c>
-      <c r="H41" s="46">
+      <c r="H41" s="123">
         <v>100</v>
       </c>
-      <c r="I41" s="46">
+      <c r="I41" s="123">
         <v>0</v>
       </c>
-      <c r="J41" s="46">
+      <c r="J41" s="123">
         <v>0</v>
       </c>
-      <c r="K41" s="46">
+      <c r="K41" s="123">
         <v>0</v>
       </c>
-      <c r="L41" s="46">
+      <c r="L41" s="123">
         <v>0</v>
       </c>
+      <c r="M41" s="123"/>
+      <c r="N41" s="123"/>
+      <c r="O41" s="123"/>
+      <c r="P41" s="123"/>
+      <c r="Q41" s="123"/>
+      <c r="R41" s="123"/>
+      <c r="S41" s="123"/>
       <c r="V41" s="45"/>
       <c r="W41" s="45"/>
       <c r="X41" s="45"/>
@@ -6242,16 +6290,21 @@
     </row>
     <row r="42" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A42" s="46"/>
-      <c r="F42" s="66"/>
-      <c r="G42" s="43"/>
-      <c r="H42" s="68"/>
-      <c r="M42" s="46"/>
-      <c r="N42" s="46"/>
-      <c r="O42" s="46"/>
-      <c r="P42" s="46"/>
-      <c r="Q42" s="46"/>
-      <c r="R42" s="46"/>
-      <c r="S42" s="46"/>
+      <c r="E42" s="123"/>
+      <c r="F42" s="131"/>
+      <c r="G42" s="116"/>
+      <c r="H42" s="130"/>
+      <c r="I42" s="123"/>
+      <c r="J42" s="123"/>
+      <c r="K42" s="123"/>
+      <c r="L42" s="123"/>
+      <c r="M42" s="123"/>
+      <c r="N42" s="123"/>
+      <c r="O42" s="123"/>
+      <c r="P42" s="123"/>
+      <c r="Q42" s="123"/>
+      <c r="R42" s="123"/>
+      <c r="S42" s="123"/>
       <c r="AI42"/>
       <c r="AJ42"/>
       <c r="AK42" s="39"/>
@@ -6264,7 +6317,7 @@
     </row>
     <row r="43" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A43" s="46"/>
-      <c r="H43" s="68"/>
+      <c r="H43" s="64"/>
       <c r="M43" s="46"/>
       <c r="N43" s="46"/>
       <c r="O43" s="46"/>
@@ -6283,11 +6336,11 @@
       <c r="AT43" s="39"/>
     </row>
     <row r="44" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="B44" s="69"/>
+      <c r="B44" s="65"/>
       <c r="C44" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="H44" s="68"/>
+      <c r="H44" s="64"/>
       <c r="AI44"/>
       <c r="AJ44"/>
       <c r="AK44" s="39"/>
@@ -6298,11 +6351,11 @@
       <c r="AT44" s="39"/>
     </row>
     <row r="45" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="B45" s="70"/>
+      <c r="B45" s="66"/>
       <c r="C45" s="45" t="s">
         <v>83</v>
       </c>
-      <c r="H45" s="68"/>
+      <c r="H45" s="64"/>
       <c r="AI45"/>
       <c r="AJ45"/>
       <c r="AK45" s="39"/>
@@ -6313,7 +6366,7 @@
       <c r="AT45" s="39"/>
     </row>
     <row r="46" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="H46" s="68"/>
+      <c r="H46" s="64"/>
       <c r="AI46"/>
       <c r="AJ46"/>
       <c r="AK46" s="39"/>
@@ -6415,8 +6468,8 @@
       <c r="AT55" s="39"/>
     </row>
     <row r="56" spans="2:46" x14ac:dyDescent="0.25">
-      <c r="B56" s="72"/>
-      <c r="C56" s="72"/>
+      <c r="B56" s="68"/>
+      <c r="C56" s="68"/>
       <c r="D56"/>
       <c r="E56"/>
       <c r="F56"/>
@@ -6436,17 +6489,17 @@
       <c r="AT56" s="39"/>
     </row>
     <row r="57" spans="2:46" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="73"/>
-      <c r="C57" s="73"/>
-      <c r="D57" s="73"/>
-      <c r="E57" s="73"/>
-      <c r="F57" s="73"/>
-      <c r="G57" s="73"/>
-      <c r="H57" s="73"/>
-      <c r="I57" s="73"/>
-      <c r="J57" s="73"/>
-      <c r="K57" s="73"/>
-      <c r="L57" s="73"/>
+      <c r="B57" s="69"/>
+      <c r="C57" s="69"/>
+      <c r="D57" s="69"/>
+      <c r="E57" s="69"/>
+      <c r="F57" s="69"/>
+      <c r="G57" s="69"/>
+      <c r="H57" s="69"/>
+      <c r="I57" s="69"/>
+      <c r="J57" s="69"/>
+      <c r="K57" s="69"/>
+      <c r="L57" s="69"/>
       <c r="AI57"/>
       <c r="AJ57"/>
       <c r="AK57" s="39"/>
@@ -6702,14 +6755,14 @@
     <row r="71" spans="1:48" x14ac:dyDescent="0.25">
       <c r="B71"/>
       <c r="C71"/>
-      <c r="E71" s="72"/>
-      <c r="F71" s="72"/>
+      <c r="E71" s="68"/>
+      <c r="F71" s="68"/>
       <c r="G71" s="1"/>
       <c r="H71"/>
-      <c r="I71" s="72"/>
+      <c r="I71" s="68"/>
       <c r="J71"/>
       <c r="K71"/>
-      <c r="L71" s="72"/>
+      <c r="L71" s="68"/>
       <c r="AC71" s="46"/>
       <c r="AD71" s="46"/>
       <c r="AE71" s="46"/>
@@ -6724,17 +6777,17 @@
     </row>
     <row r="72" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="45"/>
-      <c r="B72" s="78"/>
-      <c r="C72" s="78"/>
-      <c r="D72" s="78"/>
-      <c r="E72" s="78"/>
-      <c r="F72" s="78"/>
-      <c r="G72" s="78"/>
-      <c r="H72" s="79"/>
-      <c r="I72" s="78"/>
-      <c r="J72" s="78"/>
-      <c r="K72" s="78"/>
-      <c r="L72" s="78"/>
+      <c r="B72" s="74"/>
+      <c r="C72" s="74"/>
+      <c r="D72" s="74"/>
+      <c r="E72" s="74"/>
+      <c r="F72" s="74"/>
+      <c r="G72" s="74"/>
+      <c r="H72" s="75"/>
+      <c r="I72" s="74"/>
+      <c r="J72" s="74"/>
+      <c r="K72" s="74"/>
+      <c r="L72" s="74"/>
       <c r="M72" s="45"/>
       <c r="N72" s="45"/>
       <c r="O72" s="45"/>
@@ -6751,33 +6804,33 @@
       <c r="AB72" s="45"/>
       <c r="AC72" s="45"/>
       <c r="AI72"/>
-      <c r="AJ72" s="79"/>
+      <c r="AJ72" s="75"/>
       <c r="AK72" s="39"/>
       <c r="AL72" s="41"/>
       <c r="AM72" s="45"/>
       <c r="AN72" s="45"/>
       <c r="AQ72"/>
-      <c r="AR72" s="79"/>
+      <c r="AR72" s="75"/>
       <c r="AS72" s="39"/>
       <c r="AT72" s="41"/>
       <c r="AU72" s="45"/>
       <c r="AV72" s="45"/>
     </row>
     <row r="73" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="72"/>
-      <c r="B73" s="80"/>
-      <c r="C73" s="81"/>
-      <c r="D73" s="80"/>
-      <c r="E73" s="80"/>
-      <c r="F73" s="80"/>
-      <c r="G73" s="80"/>
-      <c r="H73" s="79"/>
-      <c r="I73" s="80"/>
-      <c r="J73" s="80"/>
-      <c r="K73" s="81"/>
-      <c r="L73" s="81"/>
-      <c r="M73" s="72"/>
-      <c r="N73" s="72"/>
+      <c r="A73" s="68"/>
+      <c r="B73" s="76"/>
+      <c r="C73" s="77"/>
+      <c r="D73" s="76"/>
+      <c r="E73" s="76"/>
+      <c r="F73" s="76"/>
+      <c r="G73" s="76"/>
+      <c r="H73" s="75"/>
+      <c r="I73" s="76"/>
+      <c r="J73" s="76"/>
+      <c r="K73" s="77"/>
+      <c r="L73" s="77"/>
+      <c r="M73" s="68"/>
+      <c r="N73" s="68"/>
       <c r="O73" s="1"/>
       <c r="P73" s="45"/>
       <c r="Q73" s="45"/>
@@ -6798,21 +6851,21 @@
       <c r="AK73" s="54"/>
     </row>
     <row r="74" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="78"/>
-      <c r="B74" s="80"/>
-      <c r="C74" s="80"/>
-      <c r="D74" s="80"/>
-      <c r="E74" s="80"/>
-      <c r="F74" s="80"/>
-      <c r="G74" s="80"/>
-      <c r="H74" s="79"/>
-      <c r="I74" s="80"/>
-      <c r="J74" s="80"/>
-      <c r="K74" s="80"/>
-      <c r="L74" s="80"/>
-      <c r="M74" s="78"/>
-      <c r="N74" s="78"/>
-      <c r="O74" s="78"/>
+      <c r="A74" s="74"/>
+      <c r="B74" s="76"/>
+      <c r="C74" s="76"/>
+      <c r="D74" s="76"/>
+      <c r="E74" s="76"/>
+      <c r="F74" s="76"/>
+      <c r="G74" s="76"/>
+      <c r="H74" s="75"/>
+      <c r="I74" s="76"/>
+      <c r="J74" s="76"/>
+      <c r="K74" s="76"/>
+      <c r="L74" s="76"/>
+      <c r="M74" s="74"/>
+      <c r="N74" s="74"/>
+      <c r="O74" s="74"/>
       <c r="V74" s="45"/>
       <c r="W74" s="45"/>
       <c r="X74" s="45"/>
@@ -6828,7 +6881,7 @@
       <c r="AK74" s="54"/>
     </row>
     <row r="75" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A75" s="80"/>
+      <c r="A75" s="76"/>
       <c r="B75"/>
       <c r="C75" s="39"/>
       <c r="D75" s="39"/>
@@ -6837,9 +6890,9 @@
       <c r="J75"/>
       <c r="K75" s="39"/>
       <c r="L75" s="39"/>
-      <c r="M75" s="81"/>
-      <c r="N75" s="81"/>
-      <c r="O75" s="80"/>
+      <c r="M75" s="77"/>
+      <c r="N75" s="77"/>
+      <c r="O75" s="76"/>
       <c r="P75" s="46"/>
       <c r="Q75" s="46"/>
       <c r="R75" s="46"/>
@@ -6849,18 +6902,18 @@
       <c r="AK75" s="50"/>
     </row>
     <row r="76" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A76" s="80"/>
+      <c r="A76" s="76"/>
       <c r="B76"/>
       <c r="C76" s="39"/>
       <c r="D76" s="39"/>
-      <c r="H76" s="77"/>
+      <c r="H76" s="73"/>
       <c r="I76"/>
       <c r="J76"/>
       <c r="K76" s="39"/>
       <c r="L76" s="39"/>
-      <c r="M76" s="80"/>
-      <c r="N76" s="80"/>
-      <c r="O76" s="80"/>
+      <c r="M76" s="76"/>
+      <c r="N76" s="76"/>
+      <c r="O76" s="76"/>
       <c r="P76" s="46"/>
       <c r="Q76" s="46"/>
       <c r="R76" s="46"/>

--- a/SubRES_TMPL/SubRES_NewTechs.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CF0000B-F091-4853-8725-B85E8104F935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D357DC3-BD0F-4DF7-A313-1E7E2B8A8D00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PRI_Sector_Fuels" sheetId="6" r:id="rId1"/>
@@ -1125,7 +1125,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V19" authorId="2" shapeId="0" xr:uid="{BAA0F8AB-741B-4302-9E54-000CB5DC4ACF}">
+    <comment ref="AB16" authorId="2" shapeId="0" xr:uid="{5EE58488-723F-4683-9026-2F0EE70F8071}">
       <text>
         <r>
           <rPr>
@@ -1134,17 +1134,8 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Sets declarations are </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>inherited. 
-Allowed Process Sets</t>
+          <t xml:space="preserve">Allowed TsLvl
+</t>
         </r>
         <r>
           <rPr>
@@ -1154,17 +1145,17 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">
-ELE </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>(Thermal Electric Power Plant)</t>
+          <t>ANNUAL</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (Annual level)
+</t>
         </r>
         <r>
           <rPr>
@@ -1174,17 +1165,17 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">
-CHP </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>(Combined Heat and Power)</t>
+          <t>SEASON</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (Seasonal level)
+</t>
         </r>
         <r>
           <rPr>
@@ -1194,17 +1185,17 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">
-STGTSS </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>(Pump Storage)</t>
+          <t>WEEKLY</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (Weekly level)
+</t>
         </r>
         <r>
           <rPr>
@@ -1214,254 +1205,20 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">
-STGIPS</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (Pump Storage IP)</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-PRE </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>(Genric Process/Technology)</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-DMD</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (Demand Device)</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-IMP </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">(Import)
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>EXP</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (Export)</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-MIN </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>(Mining Process)</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-RNW </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>(Renewable Technology)</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-HPL</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (Heating Plant)</t>
+          <t>DAYNITE</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (day and night level)</t>
         </r>
       </text>
     </comment>
-    <comment ref="AB19" authorId="2" shapeId="0" xr:uid="{5EE58488-723F-4683-9026-2F0EE70F8071}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Allowed TsLvl
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>ANNUAL</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (Annual level)
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>SEASON</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (Seasonal level)
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>WEEKLY</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (Weekly level)
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>DAYNITE</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (day and night level)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AC19" authorId="1" shapeId="0" xr:uid="{308E9284-8F99-498B-A3DD-262799AF67EB}">
+    <comment ref="AC16" authorId="1" shapeId="0" xr:uid="{308E9284-8F99-498B-A3DD-262799AF67EB}">
       <text>
         <r>
           <rPr>
@@ -1486,7 +1243,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AD19" authorId="2" shapeId="0" xr:uid="{FD29F772-15B8-47C4-8D7A-88CCF8F71647}">
+    <comment ref="AD16" authorId="2" shapeId="0" xr:uid="{FD29F772-15B8-47C4-8D7A-88CCF8F71647}">
       <text>
         <r>
           <rPr>
@@ -1546,6 +1303,249 @@
           </rPr>
           <t xml:space="preserve">
 YES</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V17" authorId="2" shapeId="0" xr:uid="{BAA0F8AB-741B-4302-9E54-000CB5DC4ACF}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Sets declarations are </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>inherited. 
+Allowed Process Sets</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+ELE </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>(Thermal Electric Power Plant)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+CHP </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>(Combined Heat and Power)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+STGTSS </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>(Pump Storage)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+STGIPS</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (Pump Storage IP)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+PRE </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>(Genric Process/Technology)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+DMD</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (Demand Device)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+IMP </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">(Import)
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>EXP</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (Export)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+MIN </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>(Mining Process)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+RNW </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>(Renewable Technology)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+HPL</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (Heating Plant)</t>
         </r>
       </text>
     </comment>
@@ -1554,7 +1554,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="158">
   <si>
     <t>~FI_T</t>
   </si>
@@ -2006,70 +2006,28 @@
     <t>Bio-Elctricity Generation Technology</t>
   </si>
   <si>
-    <t>Renewable Manufacturing Process Heat Aggregator</t>
-  </si>
-  <si>
     <t>Decentralized Electricity form Solar, Wind and Bio</t>
   </si>
   <si>
-    <t>MANELC_TECH</t>
-  </si>
-  <si>
-    <t>MANELC</t>
-  </si>
-  <si>
     <t>DECPOWER</t>
   </si>
   <si>
-    <t>RNWHEAT</t>
-  </si>
-  <si>
-    <t>RNWTHT</t>
-  </si>
-  <si>
-    <t>Grid electricity-based heat</t>
-  </si>
-  <si>
-    <t>GEHEAT</t>
-  </si>
-  <si>
-    <t>DECEHEAT</t>
-  </si>
-  <si>
-    <t>Decentralized Electricity fbased heat</t>
-  </si>
-  <si>
     <t>Process heat from  renewables-CSP and BIO</t>
   </si>
   <si>
-    <t>ELCHEAT</t>
-  </si>
-  <si>
-    <t>Electricity-based process heat</t>
-  </si>
-  <si>
-    <t>ETHT</t>
-  </si>
-  <si>
-    <t>Electricity-based process heat-aggrigator</t>
-  </si>
-  <si>
-    <t>ELC to MANELC transformation</t>
-  </si>
-  <si>
     <t>DECRHEAT</t>
   </si>
   <si>
-    <t>Renewable Heat Aggrigator from all renewables including elc</t>
-  </si>
-  <si>
-    <t>HEAt</t>
-  </si>
-  <si>
-    <t>PTHT</t>
-  </si>
-  <si>
-    <t>Manufacturing process heat aggrigator</t>
+    <t>ELC_AGG</t>
+  </si>
+  <si>
+    <t>Electricity aggrigator</t>
+  </si>
+  <si>
+    <t>Bioheat and CSP heat aggrigator</t>
+  </si>
+  <si>
+    <t>DECTHT</t>
   </si>
 </sst>
 </file>
@@ -2426,7 +2384,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="132">
+  <cellXfs count="137">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
@@ -2612,7 +2570,6 @@
     <xf numFmtId="0" fontId="31" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="28" fillId="8" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2632,13 +2589,19 @@
     <xf numFmtId="166" fontId="28" fillId="12" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="21" fillId="12" borderId="0" xfId="4" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="29" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="30" fillId="12" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="30" fillId="12" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" xfId="4" applyFont="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="30" fillId="12" borderId="0" xfId="21" applyFont="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="28" fillId="12" borderId="0" xfId="21" applyFont="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="21" fillId="12" borderId="0" xfId="21" applyFont="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="21" fillId="12" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="28" fillId="8" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="28" fillId="8" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="28" fillId="8" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="21" fillId="8" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="16" fillId="8" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="21" fillId="8" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="21" fillId="8" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="30" fillId="8" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="30" fillId="8" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="30" fillId="8" borderId="0" xfId="21" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="28" fillId="8" borderId="0" xfId="21" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="21" fillId="8" borderId="0" xfId="21" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="21" fillId="8" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="22">
     <cellStyle name="20% - Accent5 2" xfId="18" xr:uid="{4C3A48E2-3C46-4D12-9A64-54698D8BF8EE}"/>
@@ -4109,7 +4072,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3360854E-4C4D-467D-BD8A-32231E61C6CE}">
-  <dimension ref="A1:AY148"/>
+  <dimension ref="A1:AY150"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" style="45" customWidth="1"/>
@@ -4145,7 +4108,7 @@
     <col min="45" max="16384" width="8.77734375" style="45"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:31" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:51" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B1" s="44" t="s">
         <v>38</v>
       </c>
@@ -4166,7 +4129,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="2:31" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:51" ht="31.2" x14ac:dyDescent="0.3">
       <c r="B2" s="47" t="s">
         <v>92</v>
       </c>
@@ -4199,7 +4162,7 @@
       <c r="AC2" s="50"/>
       <c r="AD2" s="50"/>
     </row>
-    <row r="3" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:51" x14ac:dyDescent="0.25">
       <c r="V3" s="51" t="s">
         <v>8</v>
       </c>
@@ -4228,7 +4191,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="2:31" ht="22.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:51" ht="22.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="53"/>
       <c r="C4" s="53"/>
       <c r="D4" s="53"/>
@@ -4263,7 +4226,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="2:31" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B5" s="53"/>
       <c r="C5" s="53"/>
       <c r="D5" s="53"/>
@@ -4286,7 +4249,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="6" spans="2:31" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B6" s="53"/>
       <c r="C6" s="53"/>
       <c r="D6" s="53"/>
@@ -4309,7 +4272,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="2:31" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:51" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B7" s="53"/>
       <c r="C7" s="53"/>
       <c r="D7" s="53"/>
@@ -4332,752 +4295,845 @@
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:51" x14ac:dyDescent="0.25">
       <c r="V8" s="50" t="s">
-        <v>139</v>
+        <v>69</v>
       </c>
       <c r="W8" s="50"/>
       <c r="X8" s="50" t="s">
-        <v>167</v>
+        <v>129</v>
       </c>
       <c r="Y8" s="50" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="Z8" s="72" t="s">
         <v>58</v>
       </c>
+      <c r="AA8" s="50"/>
       <c r="AB8" s="72" t="s">
         <v>88</v>
       </c>
       <c r="AE8" s="46"/>
     </row>
-    <row r="9" spans="2:31" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:51" x14ac:dyDescent="0.25">
       <c r="V9" s="50" t="s">
-        <v>69</v>
+        <v>139</v>
       </c>
       <c r="W9" s="50"/>
       <c r="X9" s="50" t="s">
-        <v>129</v>
+        <v>153</v>
       </c>
       <c r="Y9" s="50" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Z9" s="72" t="s">
         <v>58</v>
       </c>
-      <c r="AA9" s="50"/>
       <c r="AB9" s="72" t="s">
         <v>88</v>
       </c>
       <c r="AC9" s="50"/>
       <c r="AD9" s="50"/>
     </row>
-    <row r="10" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="V10" s="45" t="s">
-        <v>139</v>
-      </c>
-      <c r="X10" s="45" t="s">
-        <v>155</v>
-      </c>
-      <c r="Y10" s="45" t="s">
-        <v>168</v>
-      </c>
-      <c r="Z10" s="72" t="s">
-        <v>58</v>
-      </c>
-      <c r="AA10" s="50"/>
-      <c r="AB10" s="72" t="s">
-        <v>88</v>
-      </c>
-      <c r="AC10" s="50"/>
-      <c r="AD10" s="50"/>
-    </row>
-    <row r="11" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="V11" s="45" t="s">
-        <v>139</v>
-      </c>
-      <c r="X11" s="45" t="s">
-        <v>158</v>
-      </c>
-      <c r="Y11" s="45" t="s">
-        <v>157</v>
-      </c>
-      <c r="Z11" s="72" t="s">
-        <v>58</v>
-      </c>
-      <c r="AB11" s="72" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="12" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="V12" s="45" t="s">
-        <v>139</v>
-      </c>
-      <c r="X12" s="45" t="s">
-        <v>159</v>
-      </c>
-      <c r="Y12" s="45" t="s">
-        <v>160</v>
-      </c>
-      <c r="Z12" s="72" t="s">
-        <v>58</v>
-      </c>
-      <c r="AB12" s="72" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="13" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="V13" s="45" t="s">
-        <v>139</v>
-      </c>
-      <c r="X13" s="45" t="s">
-        <v>162</v>
-      </c>
-      <c r="Y13" s="45" t="s">
-        <v>163</v>
-      </c>
-      <c r="Z13" s="72" t="s">
-        <v>58</v>
-      </c>
-      <c r="AB13" s="72" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="14" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="Z14" s="72"/>
+    <row r="10" spans="2:51" x14ac:dyDescent="0.25">
+      <c r="Z10" s="72"/>
+      <c r="AB10" s="72"/>
+    </row>
+    <row r="11" spans="2:51" x14ac:dyDescent="0.25">
+      <c r="Z11" s="72"/>
+      <c r="AB11" s="72"/>
+    </row>
+    <row r="13" spans="2:51" x14ac:dyDescent="0.25">
+      <c r="Z13" s="72"/>
+      <c r="AB13" s="72"/>
+    </row>
+    <row r="14" spans="2:51" x14ac:dyDescent="0.25">
       <c r="AB14" s="72"/>
     </row>
-    <row r="15" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="Z15" s="72"/>
-      <c r="AB15" s="72"/>
-    </row>
-    <row r="16" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="AB16" s="72"/>
-    </row>
-    <row r="17" spans="2:51" x14ac:dyDescent="0.25">
-      <c r="D17" s="55" t="s">
+    <row r="15" spans="2:51" x14ac:dyDescent="0.25">
+      <c r="D15" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="E17" s="55"/>
-      <c r="F17" s="55"/>
-      <c r="H17" s="55"/>
-      <c r="V17" s="49" t="s">
+      <c r="E15" s="55"/>
+      <c r="F15" s="55"/>
+      <c r="H15" s="55"/>
+      <c r="V15" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="W17" s="49"/>
-      <c r="X17" s="50"/>
-      <c r="Y17" s="50"/>
-      <c r="Z17" s="50"/>
+      <c r="W15" s="49"/>
+      <c r="X15" s="50"/>
+      <c r="Y15" s="50"/>
+      <c r="Z15" s="50"/>
+      <c r="AI15"/>
+      <c r="AJ15" s="39"/>
+      <c r="AK15" s="72"/>
+      <c r="AL15" s="72"/>
+      <c r="AM15" s="72"/>
+      <c r="AN15" s="72"/>
+      <c r="AO15" s="72"/>
+      <c r="AP15" s="72"/>
+      <c r="AQ15" s="72"/>
+      <c r="AR15" s="72"/>
+      <c r="AS15" s="72"/>
+      <c r="AT15" s="72"/>
+      <c r="AU15" s="72"/>
+      <c r="AV15" s="72"/>
+      <c r="AW15" s="72"/>
+    </row>
+    <row r="16" spans="2:51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="56" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="E16" s="57" t="s">
+        <v>113</v>
+      </c>
+      <c r="F16" s="57" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" s="57" t="s">
+        <v>34</v>
+      </c>
+      <c r="H16" s="57" t="s">
+        <v>47</v>
+      </c>
+      <c r="I16" s="57" t="s">
+        <v>36</v>
+      </c>
+      <c r="J16" s="59" t="s">
+        <v>5</v>
+      </c>
+      <c r="K16" s="59" t="s">
+        <v>98</v>
+      </c>
+      <c r="L16" s="57" t="s">
+        <v>56</v>
+      </c>
+      <c r="M16" s="59" t="s">
+        <v>103</v>
+      </c>
+      <c r="N16" s="58" t="s">
+        <v>112</v>
+      </c>
+      <c r="O16" s="59" t="s">
+        <v>115</v>
+      </c>
+      <c r="P16" s="59" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q16" s="59" t="s">
+        <v>117</v>
+      </c>
+      <c r="R16" s="59" t="s">
+        <v>118</v>
+      </c>
+      <c r="S16" s="59" t="s">
+        <v>126</v>
+      </c>
+      <c r="V16" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="W16" s="52" t="s">
+        <v>42</v>
+      </c>
+      <c r="X16" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y16" s="51" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z16" s="51" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA16" s="51" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB16" s="51" t="s">
+        <v>20</v>
+      </c>
+      <c r="AC16" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="AD16" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="AI16"/>
+      <c r="AJ16" s="39"/>
+      <c r="AK16" s="72"/>
+      <c r="AL16" s="72"/>
+      <c r="AM16" s="72"/>
+      <c r="AN16" s="72"/>
+      <c r="AO16" s="72"/>
+      <c r="AP16" s="72"/>
+      <c r="AQ16" s="72"/>
+      <c r="AR16" s="72"/>
+      <c r="AS16" s="72"/>
+      <c r="AT16" s="72"/>
+      <c r="AU16" s="72"/>
+      <c r="AV16" s="72"/>
+      <c r="AW16" s="72"/>
+      <c r="AY16" s="46"/>
+    </row>
+    <row r="17" spans="2:51" ht="31.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="E17" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="F17" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="G17" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="H17" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="I17" s="32" t="s">
+        <v>86</v>
+      </c>
+      <c r="J17" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="K17" s="33" t="s">
+        <v>99</v>
+      </c>
+      <c r="L17" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="M17" s="33" t="s">
+        <v>104</v>
+      </c>
+      <c r="N17" s="32" t="s">
+        <v>85</v>
+      </c>
+      <c r="O17" s="33" t="s">
+        <v>114</v>
+      </c>
+      <c r="P17" s="33" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q17" s="33" t="s">
+        <v>114</v>
+      </c>
+      <c r="R17" s="70" t="s">
+        <v>114</v>
+      </c>
+      <c r="S17" s="70" t="s">
+        <v>127</v>
+      </c>
+      <c r="V17" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="W17" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="X17" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y17" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z17" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA17" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB17" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="AC17" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD17" s="31" t="s">
+        <v>31</v>
+      </c>
       <c r="AI17"/>
       <c r="AJ17" s="39"/>
-      <c r="AK17" s="72"/>
-      <c r="AL17" s="72"/>
-      <c r="AM17" s="72"/>
-      <c r="AN17" s="72"/>
-      <c r="AO17" s="72"/>
-      <c r="AP17" s="72"/>
-      <c r="AQ17" s="72"/>
-      <c r="AR17" s="72"/>
-      <c r="AS17" s="72"/>
-      <c r="AT17" s="72"/>
-      <c r="AU17" s="72"/>
-      <c r="AV17" s="72"/>
-      <c r="AW17" s="72"/>
-    </row>
-    <row r="18" spans="2:51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="C18" s="56" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="56" t="s">
-        <v>4</v>
-      </c>
-      <c r="E18" s="57" t="s">
-        <v>113</v>
-      </c>
-      <c r="F18" s="57" t="s">
-        <v>16</v>
-      </c>
-      <c r="G18" s="57" t="s">
-        <v>34</v>
-      </c>
-      <c r="H18" s="57" t="s">
-        <v>47</v>
-      </c>
-      <c r="I18" s="57" t="s">
-        <v>36</v>
-      </c>
-      <c r="J18" s="59" t="s">
-        <v>5</v>
-      </c>
-      <c r="K18" s="59" t="s">
-        <v>98</v>
-      </c>
-      <c r="L18" s="57" t="s">
-        <v>56</v>
-      </c>
-      <c r="M18" s="59" t="s">
-        <v>103</v>
-      </c>
-      <c r="N18" s="58" t="s">
-        <v>112</v>
-      </c>
-      <c r="O18" s="59" t="s">
-        <v>115</v>
-      </c>
-      <c r="P18" s="59" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q18" s="59" t="s">
-        <v>117</v>
-      </c>
-      <c r="R18" s="59" t="s">
-        <v>118</v>
-      </c>
-      <c r="S18" s="59" t="s">
-        <v>126</v>
-      </c>
-      <c r="V18" s="51" t="s">
-        <v>15</v>
-      </c>
-      <c r="W18" s="52" t="s">
-        <v>42</v>
-      </c>
-      <c r="X18" s="51" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y18" s="51" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z18" s="51" t="s">
-        <v>18</v>
-      </c>
-      <c r="AA18" s="50"/>
-      <c r="AB18" s="50"/>
-      <c r="AC18" s="50"/>
-      <c r="AD18" s="50"/>
+      <c r="AY17" s="46"/>
+    </row>
+    <row r="18" spans="2:51" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" s="34"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="35"/>
+      <c r="G18" s="36"/>
+      <c r="H18" s="35" t="s">
+        <v>54</v>
+      </c>
+      <c r="I18" s="35" t="s">
+        <v>111</v>
+      </c>
+      <c r="J18" s="35" t="s">
+        <v>111</v>
+      </c>
+      <c r="K18" s="35" t="s">
+        <v>134</v>
+      </c>
+      <c r="L18" s="36"/>
+      <c r="M18" s="36" t="s">
+        <v>105</v>
+      </c>
+      <c r="N18" s="35"/>
+      <c r="O18" s="36"/>
+      <c r="P18" s="36"/>
+      <c r="Q18" s="36"/>
+      <c r="R18" s="35"/>
+      <c r="S18" s="71"/>
+      <c r="V18" s="31" t="s">
+        <v>81</v>
+      </c>
+      <c r="W18" s="31"/>
+      <c r="X18" s="31"/>
+      <c r="Y18" s="31"/>
+      <c r="Z18" s="31"/>
+      <c r="AA18" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB18" s="31" t="s">
+        <v>88</v>
+      </c>
+      <c r="AC18" s="31"/>
+      <c r="AD18" s="31"/>
       <c r="AI18"/>
       <c r="AJ18" s="39"/>
-      <c r="AK18" s="72"/>
-      <c r="AL18" s="72"/>
-      <c r="AM18" s="72"/>
-      <c r="AN18" s="72"/>
-      <c r="AO18" s="72"/>
-      <c r="AP18" s="72"/>
-      <c r="AQ18" s="72"/>
-      <c r="AR18" s="72"/>
-      <c r="AS18" s="72"/>
-      <c r="AT18" s="72"/>
-      <c r="AU18" s="72"/>
-      <c r="AV18" s="72"/>
-      <c r="AW18" s="72"/>
       <c r="AY18" s="46"/>
     </row>
-    <row r="19" spans="2:51" ht="31.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="32" t="s">
-        <v>48</v>
-      </c>
-      <c r="C19" s="32" t="s">
-        <v>32</v>
-      </c>
-      <c r="D19" s="32" t="s">
-        <v>33</v>
-      </c>
-      <c r="E19" s="32" t="s">
-        <v>54</v>
-      </c>
-      <c r="F19" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="G19" s="33" t="s">
-        <v>49</v>
-      </c>
-      <c r="H19" s="32" t="s">
-        <v>57</v>
-      </c>
-      <c r="I19" s="32" t="s">
-        <v>86</v>
-      </c>
-      <c r="J19" s="33" t="s">
-        <v>37</v>
-      </c>
-      <c r="K19" s="33" t="s">
-        <v>99</v>
-      </c>
-      <c r="L19" s="33" t="s">
-        <v>80</v>
-      </c>
-      <c r="M19" s="33" t="s">
-        <v>104</v>
-      </c>
-      <c r="N19" s="32" t="s">
-        <v>85</v>
-      </c>
-      <c r="O19" s="33" t="s">
-        <v>114</v>
-      </c>
-      <c r="P19" s="33" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q19" s="33" t="s">
-        <v>114</v>
-      </c>
-      <c r="R19" s="70" t="s">
-        <v>114</v>
-      </c>
-      <c r="S19" s="70" t="s">
-        <v>127</v>
-      </c>
-      <c r="V19" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="W19" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="X19" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y19" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z19" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="AA19" s="51" t="s">
-        <v>19</v>
-      </c>
-      <c r="AB19" s="51" t="s">
-        <v>20</v>
-      </c>
-      <c r="AC19" s="51" t="s">
-        <v>21</v>
-      </c>
-      <c r="AD19" s="51" t="s">
-        <v>22</v>
-      </c>
-      <c r="AI19"/>
-      <c r="AJ19" s="39"/>
-      <c r="AY19" s="46"/>
-    </row>
-    <row r="20" spans="2:51" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="C20" s="34"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="35"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="36"/>
-      <c r="H20" s="35" t="s">
-        <v>54</v>
-      </c>
-      <c r="I20" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="J20" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="K20" s="35" t="s">
-        <v>134</v>
-      </c>
-      <c r="L20" s="36"/>
-      <c r="M20" s="36" t="s">
-        <v>105</v>
-      </c>
-      <c r="N20" s="35"/>
-      <c r="O20" s="36"/>
-      <c r="P20" s="36"/>
-      <c r="Q20" s="36"/>
-      <c r="R20" s="35"/>
-      <c r="S20" s="71"/>
-      <c r="V20" s="31" t="s">
+    <row r="19" spans="2:51" s="80" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="80" t="str">
+        <f>X19</f>
+        <v>Furnace</v>
+      </c>
+      <c r="C19" s="80" t="s">
+        <v>69</v>
+      </c>
+      <c r="D19" s="81" t="s">
+        <v>107</v>
+      </c>
+      <c r="E19" s="109">
+        <v>2030</v>
+      </c>
+      <c r="F19" s="110">
+        <v>1</v>
+      </c>
+      <c r="G19" s="110">
+        <v>1</v>
+      </c>
+      <c r="H19" s="109">
+        <v>25</v>
+      </c>
+      <c r="I19" s="110">
         <v>81</v>
       </c>
-      <c r="W20" s="31"/>
-      <c r="X20" s="31"/>
-      <c r="Y20" s="31"/>
-      <c r="Z20" s="31"/>
-      <c r="AA20" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB20" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="AC20" s="31" t="s">
-        <v>52</v>
-      </c>
-      <c r="AD20" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="AI20"/>
-      <c r="AJ20" s="39"/>
-      <c r="AY20" s="46"/>
-    </row>
-    <row r="21" spans="2:51" s="80" customFormat="1" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J19" s="110">
+        <v>0</v>
+      </c>
+      <c r="K19" s="110">
+        <v>0.24</v>
+      </c>
+      <c r="L19" s="110">
+        <v>8.76</v>
+      </c>
+      <c r="M19" s="109"/>
+      <c r="N19" s="110">
+        <v>0.1</v>
+      </c>
+      <c r="O19" s="110">
+        <v>0.15</v>
+      </c>
+      <c r="P19" s="110">
+        <v>0.2</v>
+      </c>
+      <c r="Q19" s="110">
+        <v>0.25</v>
+      </c>
+      <c r="R19" s="110">
+        <v>0.35</v>
+      </c>
+      <c r="S19" s="109"/>
+      <c r="T19" s="82"/>
+      <c r="U19" s="82"/>
+      <c r="V19" s="83" t="s">
+        <v>139</v>
+      </c>
+      <c r="W19" s="83"/>
+      <c r="X19" s="84" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y19" s="85" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z19" s="80" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA19" s="80" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB19" s="86" t="s">
+        <v>88</v>
+      </c>
+      <c r="AC19" s="82"/>
+      <c r="AD19" s="82"/>
+      <c r="AI19" s="87"/>
+      <c r="AJ19" s="88"/>
+      <c r="AY19" s="82"/>
+    </row>
+    <row r="20" spans="2:51" s="72" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="72" t="str">
+        <f>X$20</f>
+        <v>BIOBoiler</v>
+      </c>
+      <c r="C20" s="72" t="str">
+        <f>PRI_Sector_Fuels!P5</f>
+        <v>MANBIOMIN</v>
+      </c>
+      <c r="D20" s="78" t="str">
+        <f>X9</f>
+        <v>DECRHEAT</v>
+      </c>
+      <c r="E20" s="111">
+        <v>2030</v>
+      </c>
+      <c r="F20" s="112">
+        <v>0.7</v>
+      </c>
+      <c r="G20" s="112">
+        <v>0.98</v>
+      </c>
+      <c r="H20" s="111">
+        <v>25</v>
+      </c>
+      <c r="I20" s="112">
+        <v>797.9</v>
+      </c>
+      <c r="J20" s="112">
+        <v>48.48</v>
+      </c>
+      <c r="K20" s="112">
+        <v>3.75</v>
+      </c>
+      <c r="L20" s="112">
+        <v>8.76</v>
+      </c>
+      <c r="M20" s="111"/>
+      <c r="N20" s="113"/>
+      <c r="O20" s="111"/>
+      <c r="P20" s="111"/>
+      <c r="Q20" s="111"/>
+      <c r="R20" s="111"/>
+      <c r="S20" s="111"/>
+      <c r="T20" s="89"/>
+      <c r="U20" s="89"/>
+      <c r="V20" s="79" t="s">
+        <v>139</v>
+      </c>
+      <c r="W20" s="79"/>
+      <c r="X20" s="90" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y20" s="91" t="s">
+        <v>141</v>
+      </c>
+      <c r="Z20" s="72" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA20" s="72" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB20" s="92" t="s">
+        <v>88</v>
+      </c>
+      <c r="AC20" s="89"/>
+      <c r="AD20" s="89"/>
+      <c r="AI20" s="14"/>
+      <c r="AJ20" s="12"/>
+      <c r="AY20" s="89"/>
+    </row>
+    <row r="21" spans="2:51" s="80" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B21" s="80" t="str">
-        <f>X21</f>
-        <v>Furnace</v>
+        <f>X23</f>
+        <v>ELCBoiler</v>
       </c>
       <c r="C21" s="80" t="s">
         <v>69</v>
       </c>
-      <c r="D21" s="81" t="str">
-        <f>X11</f>
-        <v>GEHEAT</v>
-      </c>
-      <c r="E21" s="110">
+      <c r="D21" s="81" t="s">
+        <v>107</v>
+      </c>
+      <c r="E21" s="109">
         <v>2030</v>
       </c>
-      <c r="F21" s="111">
+      <c r="F21" s="110">
+        <v>0.99</v>
+      </c>
+      <c r="G21" s="110">
         <v>1</v>
       </c>
-      <c r="G21" s="111">
-        <v>1</v>
-      </c>
-      <c r="H21" s="110">
+      <c r="H21" s="109">
         <v>25</v>
       </c>
-      <c r="I21" s="111">
-        <v>81</v>
-      </c>
-      <c r="J21" s="111">
-        <v>0</v>
-      </c>
-      <c r="K21" s="111">
-        <v>0.24</v>
-      </c>
-      <c r="L21" s="111">
+      <c r="I21" s="110">
+        <v>112.9</v>
+      </c>
+      <c r="J21" s="110">
+        <v>14.26</v>
+      </c>
+      <c r="K21" s="110">
+        <v>1.22</v>
+      </c>
+      <c r="L21" s="110">
         <v>8.76</v>
       </c>
-      <c r="M21" s="110"/>
-      <c r="N21" s="111">
-        <v>0.1</v>
-      </c>
-      <c r="O21" s="111">
-        <v>0.15</v>
-      </c>
-      <c r="P21" s="111">
-        <v>0.2</v>
-      </c>
-      <c r="Q21" s="111">
-        <v>0.25</v>
-      </c>
-      <c r="R21" s="111">
-        <v>0.35</v>
-      </c>
-      <c r="S21" s="110"/>
+      <c r="M21" s="109"/>
+      <c r="N21" s="114"/>
+      <c r="O21" s="114"/>
+      <c r="P21" s="114"/>
+      <c r="Q21" s="114"/>
+      <c r="R21" s="114"/>
+      <c r="S21" s="109"/>
       <c r="T21" s="82"/>
       <c r="U21" s="82"/>
       <c r="V21" s="83" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="W21" s="83"/>
       <c r="X21" s="84" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="Y21" s="85" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="Z21" s="80" t="s">
         <v>58</v>
       </c>
-      <c r="AA21" s="31" t="s">
+      <c r="AA21" s="80" t="s">
         <v>87</v>
       </c>
-      <c r="AB21" s="31" t="s">
+      <c r="AB21" s="86" t="s">
         <v>88</v>
       </c>
-      <c r="AC21" s="31"/>
-      <c r="AD21" s="31"/>
+      <c r="AC21" s="82"/>
+      <c r="AD21" s="82"/>
       <c r="AI21" s="87"/>
       <c r="AJ21" s="88"/>
       <c r="AY21" s="82"/>
     </row>
-    <row r="22" spans="2:51" s="72" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="72" t="str">
-        <f>X$22</f>
-        <v>BIOBoiler</v>
-      </c>
-      <c r="C22" s="72" t="str">
+    <row r="22" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="45" t="str">
+        <f>X21</f>
+        <v>BIOKiln</v>
+      </c>
+      <c r="C22" s="45" t="str">
         <f>PRI_Sector_Fuels!P5</f>
         <v>MANBIOMIN</v>
       </c>
-      <c r="D22" s="78" t="str">
-        <f>X8</f>
-        <v>DECRHEAT</v>
-      </c>
-      <c r="E22" s="112">
+      <c r="D22" s="50" t="s">
+        <v>108</v>
+      </c>
+      <c r="E22" s="115">
         <v>2030</v>
       </c>
-      <c r="F22" s="113">
-        <v>0.7</v>
-      </c>
-      <c r="G22" s="113">
+      <c r="F22" s="116">
+        <v>0.55600000000000005</v>
+      </c>
+      <c r="G22" s="116">
         <v>0.98</v>
       </c>
-      <c r="H22" s="112">
+      <c r="H22" s="115">
         <v>25</v>
       </c>
-      <c r="I22" s="113">
-        <v>797.9</v>
-      </c>
-      <c r="J22" s="113">
-        <v>48.48</v>
-      </c>
-      <c r="K22" s="113">
-        <v>3.75</v>
-      </c>
-      <c r="L22" s="113">
+      <c r="I22" s="116">
+        <v>297.10000000000002</v>
+      </c>
+      <c r="J22" s="116">
+        <v>4.46</v>
+      </c>
+      <c r="K22" s="116">
+        <v>0.45</v>
+      </c>
+      <c r="L22" s="116">
         <v>8.76</v>
       </c>
-      <c r="M22" s="112"/>
-      <c r="N22" s="114"/>
-      <c r="O22" s="112"/>
-      <c r="P22" s="112"/>
-      <c r="Q22" s="112"/>
-      <c r="R22" s="112"/>
-      <c r="S22" s="112"/>
-      <c r="T22" s="89"/>
-      <c r="U22" s="89"/>
-      <c r="V22" s="79" t="s">
-        <v>139</v>
-      </c>
-      <c r="W22" s="79"/>
-      <c r="X22" s="90" t="s">
-        <v>94</v>
-      </c>
-      <c r="Y22" s="91" t="s">
-        <v>141</v>
-      </c>
-      <c r="Z22" s="72" t="s">
+      <c r="M22" s="115"/>
+      <c r="N22" s="116">
+        <v>0.1</v>
+      </c>
+      <c r="O22" s="116">
+        <v>0.15</v>
+      </c>
+      <c r="P22" s="116">
+        <v>0.2</v>
+      </c>
+      <c r="Q22" s="116">
+        <v>0.25</v>
+      </c>
+      <c r="R22" s="116">
+        <v>0.35</v>
+      </c>
+      <c r="S22" s="115"/>
+      <c r="V22" s="60" t="s">
+        <v>128</v>
+      </c>
+      <c r="W22" s="60"/>
+      <c r="X22" s="61" t="s">
+        <v>96</v>
+      </c>
+      <c r="Y22" s="62" t="s">
+        <v>143</v>
+      </c>
+      <c r="Z22" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="AA22" s="80" t="s">
+      <c r="AA22" s="45" t="s">
         <v>87</v>
       </c>
-      <c r="AB22" s="86" t="s">
+      <c r="AB22" s="63" t="s">
         <v>88</v>
       </c>
-      <c r="AC22" s="82"/>
-      <c r="AD22" s="82"/>
-      <c r="AI22" s="14"/>
-      <c r="AJ22" s="12"/>
-      <c r="AY22" s="89"/>
-    </row>
-    <row r="23" spans="2:51" s="80" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="80" t="str">
-        <f>X25</f>
-        <v>ELCBoiler</v>
-      </c>
-      <c r="C23" s="80" t="s">
-        <v>69</v>
-      </c>
-      <c r="D23" s="81" t="str">
-        <f>X11</f>
-        <v>GEHEAT</v>
-      </c>
-      <c r="E23" s="110">
+      <c r="AI22"/>
+      <c r="AJ22"/>
+      <c r="AK22" s="45"/>
+      <c r="AL22" s="45"/>
+      <c r="AM22" s="45"/>
+      <c r="AN22" s="45"/>
+      <c r="AO22" s="45"/>
+      <c r="AP22" s="45"/>
+      <c r="AQ22" s="45"/>
+      <c r="AR22" s="45"/>
+      <c r="AS22" s="45"/>
+      <c r="AT22" s="45"/>
+      <c r="AU22" s="45"/>
+      <c r="AV22" s="45"/>
+      <c r="AW22" s="45"/>
+    </row>
+    <row r="23" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="50" t="str">
+        <f>X22</f>
+        <v>GASBoiler</v>
+      </c>
+      <c r="C23" s="45" t="str">
+        <f>PRI_Sector_Fuels!P6</f>
+        <v>MANGASMIN</v>
+      </c>
+      <c r="D23" s="50" t="s">
+        <v>107</v>
+      </c>
+      <c r="E23" s="115">
         <v>2030</v>
       </c>
-      <c r="F23" s="111">
+      <c r="F23" s="116">
+        <v>0.75</v>
+      </c>
+      <c r="G23" s="116">
         <v>0.99</v>
       </c>
-      <c r="G23" s="111">
-        <v>1</v>
-      </c>
-      <c r="H23" s="110">
+      <c r="H23" s="115">
         <v>25</v>
       </c>
-      <c r="I23" s="111">
-        <v>112.9</v>
-      </c>
-      <c r="J23" s="111">
-        <v>14.26</v>
-      </c>
-      <c r="K23" s="111">
-        <v>1.22</v>
-      </c>
-      <c r="L23" s="111">
+      <c r="I23" s="116">
+        <v>61.4</v>
+      </c>
+      <c r="J23" s="116">
+        <v>2.57</v>
+      </c>
+      <c r="K23" s="116">
+        <v>1.35</v>
+      </c>
+      <c r="L23" s="116">
         <v>8.76</v>
       </c>
-      <c r="M23" s="110"/>
-      <c r="N23" s="115"/>
+      <c r="M23" s="115"/>
+      <c r="N23" s="117"/>
       <c r="O23" s="115"/>
       <c r="P23" s="115"/>
       <c r="Q23" s="115"/>
       <c r="R23" s="115"/>
-      <c r="S23" s="110"/>
-      <c r="T23" s="82"/>
-      <c r="U23" s="82"/>
-      <c r="V23" s="83" t="s">
-        <v>128</v>
-      </c>
-      <c r="W23" s="83"/>
-      <c r="X23" s="84" t="s">
-        <v>95</v>
-      </c>
-      <c r="Y23" s="85" t="s">
-        <v>142</v>
-      </c>
-      <c r="Z23" s="80" t="s">
+      <c r="S23" s="115"/>
+      <c r="V23" s="60" t="s">
+        <v>139</v>
+      </c>
+      <c r="W23" s="60"/>
+      <c r="X23" s="61" t="s">
+        <v>97</v>
+      </c>
+      <c r="Y23" s="62" t="s">
+        <v>144</v>
+      </c>
+      <c r="Z23" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="AA23" s="72" t="s">
+      <c r="AA23" s="45" t="s">
         <v>87</v>
       </c>
-      <c r="AB23" s="92" t="s">
+      <c r="AB23" s="63" t="s">
         <v>88</v>
       </c>
-      <c r="AC23" s="89"/>
-      <c r="AD23" s="89"/>
-      <c r="AI23" s="87"/>
-      <c r="AJ23" s="88"/>
-      <c r="AY23" s="82"/>
+      <c r="AI23"/>
+      <c r="AJ23"/>
+      <c r="AK23" s="72"/>
+      <c r="AL23" s="72"/>
+      <c r="AM23" s="72"/>
+      <c r="AN23" s="72"/>
+      <c r="AO23" s="72"/>
+      <c r="AP23" s="72"/>
+      <c r="AQ23" s="72"/>
+      <c r="AR23" s="72"/>
+      <c r="AS23" s="72"/>
+      <c r="AT23" s="72"/>
+      <c r="AU23" s="72"/>
+      <c r="AV23" s="72"/>
+      <c r="AW23" s="72"/>
     </row>
     <row r="24" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="45" t="str">
-        <f>X23</f>
-        <v>BIOKiln</v>
+      <c r="B24" s="50" t="str">
+        <f>X25</f>
+        <v>WNDTRBN</v>
       </c>
       <c r="C24" s="45" t="str">
-        <f>PRI_Sector_Fuels!P5</f>
-        <v>MANBIOMIN</v>
+        <f>PRI_Sector_Fuels!D19</f>
+        <v>WIND</v>
       </c>
       <c r="D24" s="50" t="s">
-        <v>108</v>
-      </c>
-      <c r="E24" s="116">
+        <v>130</v>
+      </c>
+      <c r="E24" s="115">
         <v>2030</v>
       </c>
-      <c r="F24" s="117">
-        <v>0.55600000000000005</v>
-      </c>
-      <c r="G24" s="117">
-        <v>0.98</v>
-      </c>
-      <c r="H24" s="116">
+      <c r="F24" s="112">
+        <v>1</v>
+      </c>
+      <c r="G24" s="116">
+        <v>0.97</v>
+      </c>
+      <c r="H24" s="115">
         <v>25</v>
       </c>
-      <c r="I24" s="117">
-        <v>297.10000000000002</v>
-      </c>
-      <c r="J24" s="117">
-        <v>4.46</v>
-      </c>
-      <c r="K24" s="117">
-        <v>0.45</v>
-      </c>
-      <c r="L24" s="117">
+      <c r="I24" s="116">
+        <v>1041</v>
+      </c>
+      <c r="J24" s="116">
+        <v>38</v>
+      </c>
+      <c r="K24" s="116">
+        <v>0</v>
+      </c>
+      <c r="L24" s="116">
         <v>8.76</v>
       </c>
-      <c r="M24" s="116"/>
-      <c r="N24" s="117">
-        <v>0.1</v>
-      </c>
-      <c r="O24" s="117">
-        <v>0.15</v>
-      </c>
-      <c r="P24" s="117">
+      <c r="M24" s="117"/>
+      <c r="N24" s="117"/>
+      <c r="O24" s="116"/>
+      <c r="P24" s="116"/>
+      <c r="Q24" s="116"/>
+      <c r="R24" s="117"/>
+      <c r="S24" s="115">
         <v>0.2</v>
       </c>
-      <c r="Q24" s="117">
-        <v>0.25</v>
-      </c>
-      <c r="R24" s="117">
-        <v>0.35</v>
-      </c>
-      <c r="S24" s="116"/>
       <c r="V24" s="60" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="W24" s="60"/>
       <c r="X24" s="61" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="Y24" s="62" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="Z24" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="AA24" s="80" t="s">
+      <c r="AA24" s="45" t="s">
         <v>87</v>
       </c>
-      <c r="AB24" s="86" t="s">
+      <c r="AB24" s="46" t="s">
         <v>88</v>
       </c>
-      <c r="AC24" s="82"/>
-      <c r="AD24" s="82"/>
       <c r="AI24"/>
       <c r="AJ24"/>
-      <c r="AK24" s="45"/>
-      <c r="AL24" s="45"/>
-      <c r="AM24" s="45"/>
-      <c r="AN24" s="45"/>
-      <c r="AO24" s="45"/>
-      <c r="AP24" s="45"/>
-      <c r="AQ24" s="45"/>
-      <c r="AR24" s="45"/>
-      <c r="AS24" s="45"/>
-      <c r="AT24" s="45"/>
-      <c r="AU24" s="45"/>
-      <c r="AV24" s="45"/>
-      <c r="AW24" s="45"/>
+      <c r="AK24" s="72"/>
+      <c r="AL24" s="72"/>
+      <c r="AM24" s="72"/>
+      <c r="AN24" s="72"/>
+      <c r="AO24" s="72"/>
+      <c r="AP24" s="72"/>
+      <c r="AQ24" s="72"/>
+      <c r="AR24" s="72"/>
+      <c r="AS24" s="72"/>
+      <c r="AT24" s="72"/>
+      <c r="AU24" s="72"/>
+      <c r="AV24" s="72"/>
+      <c r="AW24" s="72"/>
     </row>
     <row r="25" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B25" s="50" t="str">
-        <f>X24</f>
-        <v>GASBoiler</v>
+        <f>X26</f>
+        <v>SOLPV</v>
       </c>
       <c r="C25" s="45" t="str">
-        <f>PRI_Sector_Fuels!P6</f>
-        <v>MANGASMIN</v>
+        <f>PRI_Sector_Fuels!D20</f>
+        <v>SOLAR</v>
       </c>
       <c r="D25" s="50" t="s">
-        <v>107</v>
-      </c>
-      <c r="E25" s="116">
+        <v>131</v>
+      </c>
+      <c r="E25" s="115">
         <v>2030</v>
       </c>
-      <c r="F25" s="117">
-        <v>0.75</v>
-      </c>
-      <c r="G25" s="117">
+      <c r="F25" s="112">
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="G25" s="116">
         <v>0.99</v>
       </c>
-      <c r="H25" s="116">
+      <c r="H25" s="115">
         <v>25</v>
       </c>
-      <c r="I25" s="117">
-        <v>61.4</v>
-      </c>
-      <c r="J25" s="117">
-        <v>2.57</v>
-      </c>
-      <c r="K25" s="117">
-        <v>1.35</v>
-      </c>
-      <c r="L25" s="117">
+      <c r="I25" s="116">
+        <v>691</v>
+      </c>
+      <c r="J25" s="116">
+        <v>6.99</v>
+      </c>
+      <c r="K25" s="116">
+        <v>0</v>
+      </c>
+      <c r="L25" s="116">
         <v>8.76</v>
       </c>
-      <c r="M25" s="116"/>
-      <c r="N25" s="118"/>
+      <c r="M25" s="117"/>
+      <c r="N25" s="117"/>
       <c r="O25" s="116"/>
       <c r="P25" s="116"/>
       <c r="Q25" s="116"/>
-      <c r="R25" s="116"/>
-      <c r="S25" s="116"/>
+      <c r="R25" s="117"/>
+      <c r="S25" s="115">
+        <v>0.3</v>
+      </c>
       <c r="V25" s="60" t="s">
-        <v>139</v>
+        <v>69</v>
       </c>
       <c r="W25" s="60"/>
       <c r="X25" s="61" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="Y25" s="62" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="Z25" s="45" t="s">
         <v>58</v>
@@ -5085,91 +5141,90 @@
       <c r="AA25" s="45" t="s">
         <v>87</v>
       </c>
-      <c r="AB25" s="63" t="s">
+      <c r="AB25" s="46" t="s">
         <v>88</v>
       </c>
       <c r="AI25"/>
       <c r="AJ25"/>
-      <c r="AK25" s="72"/>
-      <c r="AL25" s="72"/>
-      <c r="AM25" s="72"/>
-      <c r="AN25" s="72"/>
-      <c r="AO25" s="72"/>
-      <c r="AP25" s="72"/>
-      <c r="AQ25" s="72"/>
-      <c r="AR25" s="72"/>
-      <c r="AS25" s="72"/>
-      <c r="AT25" s="72"/>
-      <c r="AU25" s="72"/>
-      <c r="AV25" s="72"/>
-      <c r="AW25" s="72"/>
-    </row>
-    <row r="26" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="50" t="str">
-        <f>X27</f>
-        <v>WNDTRBN</v>
-      </c>
-      <c r="C26" s="45" t="str">
-        <f>PRI_Sector_Fuels!D19</f>
-        <v>WIND</v>
-      </c>
-      <c r="D26" s="50" t="s">
-        <v>130</v>
-      </c>
-      <c r="E26" s="116">
+      <c r="AK25" s="45"/>
+      <c r="AL25" s="45"/>
+      <c r="AM25" s="45"/>
+      <c r="AN25" s="45"/>
+      <c r="AO25" s="45"/>
+      <c r="AP25" s="45"/>
+      <c r="AQ25" s="45"/>
+      <c r="AR25" s="45"/>
+      <c r="AS25" s="45"/>
+      <c r="AT25" s="45"/>
+      <c r="AU25" s="45"/>
+      <c r="AV25" s="45"/>
+      <c r="AW25" s="45"/>
+    </row>
+    <row r="26" spans="2:51" s="89" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="78" t="str">
+        <f>X24</f>
+        <v>CSP</v>
+      </c>
+      <c r="C26" s="72" t="str">
+        <f>PRI_Sector_Fuels!D20</f>
+        <v>SOLAR</v>
+      </c>
+      <c r="D26" s="78" t="str">
+        <f>X9</f>
+        <v>DECRHEAT</v>
+      </c>
+      <c r="E26" s="111">
         <v>2030</v>
       </c>
-      <c r="F26" s="113">
+      <c r="F26" s="112">
+        <v>0.4</v>
+      </c>
+      <c r="G26" s="112">
         <v>1</v>
       </c>
-      <c r="G26" s="117">
-        <v>0.97</v>
-      </c>
-      <c r="H26" s="116">
+      <c r="H26" s="111">
         <v>25</v>
       </c>
-      <c r="I26" s="117">
-        <v>1041</v>
-      </c>
-      <c r="J26" s="117">
-        <v>38</v>
-      </c>
-      <c r="K26" s="117">
+      <c r="I26" s="112">
+        <v>3677</v>
+      </c>
+      <c r="J26" s="112">
         <v>0</v>
       </c>
-      <c r="L26" s="117">
+      <c r="K26" s="112">
+        <v>14</v>
+      </c>
+      <c r="L26" s="112">
         <v>8.76</v>
       </c>
-      <c r="M26" s="118"/>
-      <c r="N26" s="118"/>
-      <c r="O26" s="117"/>
-      <c r="P26" s="117"/>
-      <c r="Q26" s="117"/>
-      <c r="R26" s="118"/>
-      <c r="S26" s="116">
-        <v>0.2</v>
-      </c>
-      <c r="V26" s="60" t="s">
-        <v>139</v>
-      </c>
-      <c r="W26" s="60"/>
-      <c r="X26" s="61" t="s">
-        <v>65</v>
-      </c>
-      <c r="Y26" s="62" t="s">
-        <v>145</v>
-      </c>
-      <c r="Z26" s="45" t="s">
+      <c r="M26" s="113"/>
+      <c r="N26" s="113"/>
+      <c r="O26" s="112"/>
+      <c r="P26" s="112"/>
+      <c r="Q26" s="112"/>
+      <c r="R26" s="113"/>
+      <c r="S26" s="111"/>
+      <c r="V26" s="79" t="s">
+        <v>69</v>
+      </c>
+      <c r="W26" s="79"/>
+      <c r="X26" s="90" t="s">
+        <v>90</v>
+      </c>
+      <c r="Y26" s="91" t="s">
+        <v>147</v>
+      </c>
+      <c r="Z26" s="72" t="s">
         <v>58</v>
       </c>
-      <c r="AA26" s="45" t="s">
+      <c r="AA26" s="72" t="s">
         <v>87</v>
       </c>
-      <c r="AB26" s="63" t="s">
+      <c r="AB26" s="89" t="s">
         <v>88</v>
       </c>
-      <c r="AI26"/>
-      <c r="AJ26"/>
+      <c r="AI26" s="14"/>
+      <c r="AJ26" s="14"/>
       <c r="AK26" s="72"/>
       <c r="AL26" s="72"/>
       <c r="AM26" s="72"/>
@@ -5186,58 +5241,53 @@
     </row>
     <row r="27" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B27" s="50" t="str">
-        <f>X28</f>
-        <v>SOLPV</v>
-      </c>
-      <c r="C27" s="45" t="str">
-        <f>PRI_Sector_Fuels!D20</f>
-        <v>SOLAR</v>
-      </c>
+        <f>X22</f>
+        <v>GASBoiler</v>
+      </c>
+      <c r="C27" s="45"/>
       <c r="D27" s="50" t="s">
-        <v>131</v>
-      </c>
-      <c r="E27" s="116">
+        <v>106</v>
+      </c>
+      <c r="E27" s="115">
         <v>2030</v>
       </c>
-      <c r="F27" s="113">
-        <v>0.20499999999999999</v>
-      </c>
-      <c r="G27" s="117">
-        <v>0.99</v>
-      </c>
-      <c r="H27" s="116">
+      <c r="F27" s="112">
+        <v>0.3</v>
+      </c>
+      <c r="G27" s="116">
+        <v>1</v>
+      </c>
+      <c r="H27" s="115">
         <v>25</v>
       </c>
-      <c r="I27" s="117">
-        <v>691</v>
-      </c>
-      <c r="J27" s="117">
-        <v>6.99</v>
-      </c>
-      <c r="K27" s="117">
+      <c r="I27" s="116">
         <v>0</v>
       </c>
-      <c r="L27" s="117">
+      <c r="J27" s="116">
+        <v>0</v>
+      </c>
+      <c r="K27" s="116">
+        <v>0</v>
+      </c>
+      <c r="L27" s="116">
         <v>8.76</v>
       </c>
-      <c r="M27" s="118"/>
-      <c r="N27" s="118"/>
-      <c r="O27" s="117"/>
-      <c r="P27" s="117"/>
-      <c r="Q27" s="117"/>
-      <c r="R27" s="118"/>
-      <c r="S27" s="116">
-        <v>0.3</v>
-      </c>
+      <c r="M27" s="117"/>
+      <c r="N27" s="117"/>
+      <c r="O27" s="116"/>
+      <c r="P27" s="116"/>
+      <c r="Q27" s="116"/>
+      <c r="R27" s="117"/>
+      <c r="S27" s="115"/>
       <c r="V27" s="60" t="s">
         <v>69</v>
       </c>
       <c r="W27" s="60"/>
       <c r="X27" s="61" t="s">
-        <v>89</v>
+        <v>151</v>
       </c>
       <c r="Y27" s="62" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="Z27" s="45" t="s">
         <v>58</v>
@@ -5264,61 +5314,60 @@
       <c r="AV27" s="45"/>
       <c r="AW27" s="45"/>
     </row>
-    <row r="28" spans="2:51" s="89" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="78" t="str">
-        <f>X26</f>
-        <v>CSP</v>
-      </c>
-      <c r="C28" s="72" t="str">
-        <f>PRI_Sector_Fuels!D20</f>
-        <v>SOLAR</v>
-      </c>
-      <c r="D28" s="78" t="str">
+    <row r="28" spans="2:51" s="94" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="93" t="str">
+        <f>X27</f>
+        <v>DECPOWER</v>
+      </c>
+      <c r="C28" s="93" t="s">
+        <v>130</v>
+      </c>
+      <c r="D28" s="93" t="str">
         <f>X8</f>
-        <v>DECRHEAT</v>
-      </c>
-      <c r="E28" s="112">
+        <v>DECELC</v>
+      </c>
+      <c r="E28" s="118">
         <v>2030</v>
       </c>
-      <c r="F28" s="113">
-        <v>0.4</v>
-      </c>
-      <c r="G28" s="113">
+      <c r="F28" s="119">
         <v>1</v>
       </c>
-      <c r="H28" s="112">
-        <v>25</v>
-      </c>
-      <c r="I28" s="113">
-        <v>3677</v>
-      </c>
-      <c r="J28" s="113">
+      <c r="G28" s="119">
+        <v>1</v>
+      </c>
+      <c r="H28" s="118">
+        <v>100</v>
+      </c>
+      <c r="I28" s="120">
         <v>0</v>
       </c>
-      <c r="K28" s="113">
-        <v>14</v>
-      </c>
-      <c r="L28" s="113">
+      <c r="J28" s="119">
+        <v>0</v>
+      </c>
+      <c r="K28" s="119">
+        <v>0</v>
+      </c>
+      <c r="L28" s="120">
         <v>8.76</v>
       </c>
-      <c r="M28" s="114"/>
-      <c r="N28" s="114"/>
-      <c r="O28" s="113"/>
-      <c r="P28" s="113"/>
-      <c r="Q28" s="113"/>
-      <c r="R28" s="114"/>
-      <c r="S28" s="112"/>
-      <c r="V28" s="79" t="s">
+      <c r="M28" s="121"/>
+      <c r="N28" s="121"/>
+      <c r="O28" s="120"/>
+      <c r="P28" s="120"/>
+      <c r="Q28" s="120"/>
+      <c r="R28" s="121"/>
+      <c r="S28" s="118"/>
+      <c r="V28" s="96" t="s">
         <v>69</v>
       </c>
-      <c r="W28" s="79"/>
-      <c r="X28" s="90" t="s">
-        <v>90</v>
-      </c>
-      <c r="Y28" s="91" t="s">
-        <v>147</v>
-      </c>
-      <c r="Z28" s="72" t="s">
+      <c r="W28" s="96"/>
+      <c r="X28" s="97" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y28" s="98" t="s">
+        <v>149</v>
+      </c>
+      <c r="Z28" s="95" t="s">
         <v>58</v>
       </c>
       <c r="AA28" s="45" t="s">
@@ -5327,194 +5376,190 @@
       <c r="AB28" s="46" t="s">
         <v>88</v>
       </c>
-      <c r="AC28" s="46"/>
-      <c r="AD28" s="46"/>
-      <c r="AI28" s="14"/>
-      <c r="AJ28" s="14"/>
-      <c r="AK28" s="72"/>
-      <c r="AL28" s="72"/>
-      <c r="AM28" s="72"/>
-      <c r="AN28" s="72"/>
-      <c r="AO28" s="72"/>
-      <c r="AP28" s="72"/>
-      <c r="AQ28" s="72"/>
-      <c r="AR28" s="72"/>
-      <c r="AS28" s="72"/>
-      <c r="AT28" s="72"/>
-      <c r="AU28" s="72"/>
-      <c r="AV28" s="72"/>
-      <c r="AW28" s="72"/>
-    </row>
-    <row r="29" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="50" t="str">
-        <f>X24</f>
-        <v>GASBoiler</v>
-      </c>
-      <c r="C29" s="45"/>
-      <c r="D29" s="50" t="s">
-        <v>106</v>
-      </c>
-      <c r="E29" s="116">
+      <c r="AI28" s="99"/>
+      <c r="AJ28" s="99"/>
+      <c r="AK28" s="95"/>
+      <c r="AL28" s="95"/>
+      <c r="AM28" s="95"/>
+      <c r="AN28" s="95"/>
+      <c r="AO28" s="95"/>
+      <c r="AP28" s="95"/>
+      <c r="AQ28" s="95"/>
+      <c r="AR28" s="95"/>
+      <c r="AS28" s="95"/>
+      <c r="AT28" s="95"/>
+      <c r="AU28" s="95"/>
+      <c r="AV28" s="95"/>
+      <c r="AW28" s="95"/>
+    </row>
+    <row r="29" spans="2:51" s="94" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="93" t="str">
+        <f>X27</f>
+        <v>DECPOWER</v>
+      </c>
+      <c r="C29" s="93" t="s">
+        <v>131</v>
+      </c>
+      <c r="D29" s="93" t="str">
+        <f>X8</f>
+        <v>DECELC</v>
+      </c>
+      <c r="E29" s="118">
         <v>2030</v>
       </c>
-      <c r="F29" s="113">
-        <v>0.3</v>
-      </c>
-      <c r="G29" s="117">
+      <c r="F29" s="119">
         <v>1</v>
       </c>
-      <c r="H29" s="116">
-        <v>25</v>
-      </c>
-      <c r="I29" s="117">
+      <c r="G29" s="119">
+        <v>1</v>
+      </c>
+      <c r="H29" s="118">
+        <v>100</v>
+      </c>
+      <c r="I29" s="120">
         <v>0</v>
       </c>
-      <c r="J29" s="117">
+      <c r="J29" s="119">
         <v>0</v>
       </c>
-      <c r="K29" s="117">
+      <c r="K29" s="119">
         <v>0</v>
       </c>
-      <c r="L29" s="117">
+      <c r="L29" s="120">
         <v>8.76</v>
       </c>
-      <c r="M29" s="118"/>
-      <c r="N29" s="118"/>
-      <c r="O29" s="117"/>
-      <c r="P29" s="117"/>
-      <c r="Q29" s="117"/>
-      <c r="R29" s="118"/>
-      <c r="S29" s="116"/>
-      <c r="V29" s="60" t="s">
+      <c r="M29" s="121"/>
+      <c r="N29" s="121"/>
+      <c r="O29" s="120"/>
+      <c r="P29" s="120"/>
+      <c r="Q29" s="120"/>
+      <c r="R29" s="121"/>
+      <c r="S29" s="118"/>
+      <c r="V29" s="94" t="s">
         <v>69</v>
       </c>
-      <c r="W29" s="60"/>
-      <c r="X29" s="61" t="s">
+      <c r="X29" s="94" t="s">
         <v>154</v>
       </c>
-      <c r="Y29" s="62" t="s">
-        <v>148</v>
-      </c>
-      <c r="Z29" s="45" t="s">
+      <c r="Y29" s="94" t="s">
+        <v>155</v>
+      </c>
+      <c r="Z29" s="95" t="s">
         <v>58</v>
       </c>
-      <c r="AA29" s="72" t="s">
+      <c r="AA29" s="95" t="s">
         <v>87</v>
       </c>
-      <c r="AB29" s="89" t="s">
+      <c r="AB29" s="94" t="s">
         <v>88</v>
       </c>
-      <c r="AC29" s="89"/>
-      <c r="AD29" s="89"/>
-      <c r="AI29"/>
-      <c r="AJ29"/>
-      <c r="AK29" s="45"/>
-      <c r="AL29" s="45"/>
-      <c r="AM29" s="45"/>
-      <c r="AN29" s="45"/>
-      <c r="AO29" s="45"/>
-      <c r="AP29" s="45"/>
-      <c r="AQ29" s="45"/>
-      <c r="AR29" s="45"/>
-      <c r="AS29" s="45"/>
-      <c r="AT29" s="45"/>
-      <c r="AU29" s="45"/>
-      <c r="AV29" s="45"/>
-      <c r="AW29" s="45"/>
-    </row>
-    <row r="30" spans="2:51" s="94" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="93" t="str">
-        <f>X29</f>
-        <v>DECPOWER</v>
-      </c>
-      <c r="C30" s="93" t="s">
-        <v>130</v>
-      </c>
-      <c r="D30" s="93" t="str">
-        <f>X9</f>
-        <v>DECELC</v>
-      </c>
-      <c r="E30" s="119">
+      <c r="AC29" s="46"/>
+      <c r="AI29" s="99"/>
+      <c r="AJ29" s="99"/>
+      <c r="AK29" s="95"/>
+      <c r="AL29" s="95"/>
+      <c r="AM29" s="95"/>
+      <c r="AN29" s="95"/>
+      <c r="AO29" s="95"/>
+      <c r="AP29" s="95"/>
+      <c r="AQ29" s="95"/>
+      <c r="AR29" s="95"/>
+      <c r="AS29" s="95"/>
+      <c r="AT29" s="95"/>
+      <c r="AU29" s="95"/>
+      <c r="AV29" s="95"/>
+      <c r="AW29" s="95"/>
+    </row>
+    <row r="30" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="50" t="str">
+        <f>X28</f>
+        <v>BIOPOWER</v>
+      </c>
+      <c r="C30" s="50" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30" s="50" t="s">
+        <v>135</v>
+      </c>
+      <c r="E30" s="115">
         <v>2030</v>
       </c>
-      <c r="F30" s="120">
-        <v>1</v>
-      </c>
-      <c r="G30" s="120">
-        <v>1</v>
-      </c>
-      <c r="H30" s="119">
-        <v>100</v>
-      </c>
-      <c r="I30" s="121">
+      <c r="F30" s="122">
+        <v>0.35</v>
+      </c>
+      <c r="G30" s="122">
+        <v>0.98</v>
+      </c>
+      <c r="H30" s="115">
+        <v>20</v>
+      </c>
+      <c r="I30" s="123">
+        <v>3242</v>
+      </c>
+      <c r="J30" s="116">
+        <v>129.68</v>
+      </c>
+      <c r="K30" s="116">
         <v>0</v>
       </c>
-      <c r="J30" s="120">
-        <v>0</v>
-      </c>
-      <c r="K30" s="120">
-        <v>0</v>
-      </c>
-      <c r="L30" s="121">
+      <c r="L30" s="116">
         <v>8.76</v>
       </c>
-      <c r="M30" s="122"/>
-      <c r="N30" s="122"/>
-      <c r="O30" s="121"/>
-      <c r="P30" s="121"/>
-      <c r="Q30" s="121"/>
-      <c r="R30" s="122"/>
-      <c r="S30" s="119"/>
-      <c r="V30" s="96" t="s">
-        <v>69</v>
-      </c>
-      <c r="W30" s="96"/>
-      <c r="X30" s="97" t="s">
-        <v>137</v>
-      </c>
-      <c r="Y30" s="98" t="s">
-        <v>149</v>
+      <c r="M30" s="117"/>
+      <c r="N30" s="117"/>
+      <c r="O30" s="116"/>
+      <c r="P30" s="116"/>
+      <c r="Q30" s="116"/>
+      <c r="R30" s="117"/>
+      <c r="S30" s="115"/>
+      <c r="V30" s="46" t="s">
+        <v>139</v>
+      </c>
+      <c r="X30" s="46" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y30" s="46" t="s">
+        <v>156</v>
       </c>
       <c r="Z30" s="95" t="s">
         <v>58</v>
       </c>
-      <c r="AA30" s="45" t="s">
+      <c r="AA30" s="95" t="s">
         <v>87</v>
       </c>
-      <c r="AB30" s="46" t="s">
+      <c r="AB30" s="94" t="s">
         <v>88</v>
       </c>
-      <c r="AC30" s="46"/>
-      <c r="AD30" s="46"/>
-      <c r="AI30" s="99"/>
-      <c r="AJ30" s="99"/>
-      <c r="AK30" s="95"/>
-      <c r="AL30" s="95"/>
-      <c r="AM30" s="95"/>
-      <c r="AN30" s="95"/>
-      <c r="AO30" s="95"/>
-      <c r="AP30" s="95"/>
-      <c r="AQ30" s="95"/>
-      <c r="AR30" s="95"/>
-      <c r="AS30" s="95"/>
-      <c r="AT30" s="95"/>
-      <c r="AU30" s="95"/>
-      <c r="AV30" s="95"/>
-      <c r="AW30" s="95"/>
+      <c r="AC30" s="94"/>
+      <c r="AI30" s="38"/>
+      <c r="AJ30" s="38"/>
+      <c r="AK30" s="45"/>
+      <c r="AL30" s="45"/>
+      <c r="AM30" s="45"/>
+      <c r="AN30" s="45"/>
+      <c r="AO30" s="45"/>
+      <c r="AP30" s="45"/>
+      <c r="AQ30" s="45"/>
+      <c r="AR30" s="45"/>
+      <c r="AS30" s="45"/>
+      <c r="AT30" s="45"/>
+      <c r="AU30" s="45"/>
+      <c r="AV30" s="45"/>
+      <c r="AW30" s="45"/>
     </row>
     <row r="31" spans="2:51" s="94" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="93" t="str">
-        <f>X29</f>
+      <c r="B31" s="50" t="str">
+        <f>X27</f>
         <v>DECPOWER</v>
       </c>
-      <c r="C31" s="93" t="s">
-        <v>131</v>
+      <c r="C31" s="95" t="s">
+        <v>135</v>
       </c>
       <c r="D31" s="93" t="str">
-        <f>X9</f>
+        <f>X8</f>
         <v>DECELC</v>
       </c>
-      <c r="E31" s="119">
+      <c r="E31" s="118">
         <v>2030</v>
       </c>
       <c r="F31" s="120">
@@ -5526,44 +5571,31 @@
       <c r="H31" s="119">
         <v>100</v>
       </c>
-      <c r="I31" s="121">
+      <c r="I31" s="119">
         <v>0</v>
       </c>
-      <c r="J31" s="120">
+      <c r="J31" s="119">
         <v>0</v>
       </c>
-      <c r="K31" s="120">
+      <c r="K31" s="119">
         <v>0</v>
       </c>
-      <c r="L31" s="121">
-        <v>8.76</v>
-      </c>
-      <c r="M31" s="122"/>
-      <c r="N31" s="122"/>
-      <c r="O31" s="121"/>
-      <c r="P31" s="121"/>
-      <c r="Q31" s="121"/>
-      <c r="R31" s="122"/>
-      <c r="S31" s="119"/>
-      <c r="V31" s="46" t="s">
-        <v>169</v>
-      </c>
+      <c r="L31" s="119">
+        <v>0</v>
+      </c>
+      <c r="M31" s="121"/>
+      <c r="N31" s="121"/>
+      <c r="O31" s="120"/>
+      <c r="P31" s="120"/>
+      <c r="Q31" s="120"/>
+      <c r="R31" s="121"/>
+      <c r="S31" s="118"/>
+      <c r="V31" s="46"/>
       <c r="W31" s="46"/>
-      <c r="X31" s="46" t="s">
-        <v>156</v>
-      </c>
-      <c r="Y31" s="46" t="s">
-        <v>150</v>
-      </c>
-      <c r="Z31" s="95" t="s">
-        <v>58</v>
-      </c>
-      <c r="AA31" s="95" t="s">
-        <v>87</v>
-      </c>
-      <c r="AB31" s="94" t="s">
-        <v>88</v>
-      </c>
+      <c r="X31" s="46"/>
+      <c r="Y31" s="46"/>
+      <c r="Z31" s="95"/>
+      <c r="AD31" s="46"/>
       <c r="AI31" s="99"/>
       <c r="AJ31" s="99"/>
       <c r="AK31" s="95"/>
@@ -5580,147 +5612,109 @@
       <c r="AV31" s="95"/>
       <c r="AW31" s="95"/>
     </row>
-    <row r="32" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:51" s="94" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B32" s="50" t="str">
-        <f>X30</f>
-        <v>BIOPOWER</v>
-      </c>
-      <c r="C32" s="50" t="s">
-        <v>68</v>
-      </c>
-      <c r="D32" s="50" t="s">
-        <v>135</v>
-      </c>
-      <c r="E32" s="116">
+        <f>X29</f>
+        <v>ELC_AGG</v>
+      </c>
+      <c r="C32" s="93" t="str">
+        <f>X8</f>
+        <v>DECELC</v>
+      </c>
+      <c r="D32" s="93" t="s">
+        <v>69</v>
+      </c>
+      <c r="E32" s="118">
         <v>2030</v>
       </c>
-      <c r="F32" s="123">
-        <v>0.35</v>
-      </c>
-      <c r="G32" s="123">
-        <v>0.98</v>
-      </c>
-      <c r="H32" s="116">
-        <v>20</v>
-      </c>
-      <c r="I32" s="124">
-        <v>3242</v>
-      </c>
-      <c r="J32" s="117">
-        <v>129.68</v>
-      </c>
-      <c r="K32" s="117">
+      <c r="F32" s="120">
+        <v>1</v>
+      </c>
+      <c r="G32" s="120">
+        <v>1</v>
+      </c>
+      <c r="H32" s="119">
+        <v>100</v>
+      </c>
+      <c r="I32" s="119">
         <v>0</v>
       </c>
-      <c r="L32" s="117">
-        <v>8.76</v>
-      </c>
-      <c r="M32" s="118"/>
-      <c r="N32" s="118"/>
-      <c r="O32" s="117"/>
-      <c r="P32" s="117"/>
-      <c r="Q32" s="117"/>
-      <c r="R32" s="118"/>
-      <c r="S32" s="116"/>
-      <c r="V32" s="45" t="s">
-        <v>139</v>
-      </c>
-      <c r="W32" s="45"/>
-      <c r="X32" s="45" t="s">
-        <v>164</v>
-      </c>
-      <c r="Y32" s="45" t="s">
-        <v>165</v>
-      </c>
-      <c r="Z32" s="95" t="s">
-        <v>58</v>
-      </c>
-      <c r="AA32" s="95" t="s">
-        <v>87</v>
-      </c>
-      <c r="AB32" s="94" t="s">
-        <v>88</v>
-      </c>
-      <c r="AD32" s="94"/>
-      <c r="AI32" s="38"/>
-      <c r="AJ32" s="38"/>
-      <c r="AK32" s="45"/>
-      <c r="AL32" s="45"/>
-      <c r="AM32" s="45"/>
-      <c r="AN32" s="45"/>
-      <c r="AO32" s="45"/>
-      <c r="AP32" s="45"/>
-      <c r="AQ32" s="45"/>
-      <c r="AR32" s="45"/>
-      <c r="AS32" s="45"/>
-      <c r="AT32" s="45"/>
-      <c r="AU32" s="45"/>
-      <c r="AV32" s="45"/>
-      <c r="AW32" s="45"/>
+      <c r="J32" s="119">
+        <v>0</v>
+      </c>
+      <c r="K32" s="119">
+        <v>0</v>
+      </c>
+      <c r="L32" s="119">
+        <v>0</v>
+      </c>
+      <c r="M32" s="121"/>
+      <c r="N32" s="121"/>
+      <c r="O32" s="120"/>
+      <c r="P32" s="120"/>
+      <c r="Q32" s="120"/>
+      <c r="R32" s="121"/>
+      <c r="S32" s="118"/>
+      <c r="AD32" s="46"/>
+      <c r="AI32" s="99"/>
+      <c r="AJ32" s="99"/>
+      <c r="AK32" s="95"/>
+      <c r="AL32" s="95"/>
+      <c r="AM32" s="95"/>
+      <c r="AN32" s="95"/>
+      <c r="AO32" s="95"/>
+      <c r="AP32" s="95"/>
+      <c r="AQ32" s="95"/>
+      <c r="AR32" s="95"/>
+      <c r="AS32" s="95"/>
+      <c r="AT32" s="95"/>
+      <c r="AU32" s="95"/>
+      <c r="AV32" s="95"/>
+      <c r="AW32" s="95"/>
     </row>
     <row r="33" spans="1:49" s="94" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B33" s="93" t="str">
-        <f>X29</f>
-        <v>DECPOWER</v>
-      </c>
-      <c r="C33" s="95" t="s">
-        <v>135</v>
-      </c>
-      <c r="D33" s="93" t="str">
+        <f>X30</f>
+        <v>DECTHT</v>
+      </c>
+      <c r="C33" s="93" t="str">
         <f>X9</f>
-        <v>DECELC</v>
-      </c>
-      <c r="E33" s="119">
+        <v>DECRHEAT</v>
+      </c>
+      <c r="D33" s="93" t="s">
+        <v>107</v>
+      </c>
+      <c r="E33" s="118">
         <v>2030</v>
       </c>
-      <c r="F33" s="121">
+      <c r="F33" s="120">
         <v>1</v>
       </c>
-      <c r="G33" s="121">
+      <c r="G33" s="120">
         <v>1</v>
       </c>
-      <c r="H33" s="120">
+      <c r="H33" s="119">
         <v>100</v>
       </c>
-      <c r="I33" s="120">
+      <c r="I33" s="119">
         <v>0</v>
       </c>
-      <c r="J33" s="120">
+      <c r="J33" s="119">
         <v>0</v>
       </c>
-      <c r="K33" s="120">
+      <c r="K33" s="119">
         <v>0</v>
       </c>
-      <c r="L33" s="120">
+      <c r="L33" s="119">
         <v>0</v>
       </c>
-      <c r="M33" s="122"/>
-      <c r="N33" s="122"/>
-      <c r="O33" s="121"/>
-      <c r="P33" s="121"/>
-      <c r="Q33" s="121"/>
-      <c r="R33" s="122"/>
-      <c r="S33" s="119"/>
-      <c r="V33" s="99" t="s">
-        <v>128</v>
-      </c>
-      <c r="W33" s="99"/>
-      <c r="X33" s="95" t="s">
-        <v>152</v>
-      </c>
-      <c r="Y33" s="109" t="s">
-        <v>166</v>
-      </c>
-      <c r="Z33" s="95" t="s">
-        <v>58</v>
-      </c>
-      <c r="AA33" s="95" t="s">
-        <v>87</v>
-      </c>
-      <c r="AB33" s="94" t="s">
-        <v>88</v>
-      </c>
-      <c r="AC33" s="95"/>
+      <c r="M33" s="121"/>
+      <c r="N33" s="121"/>
+      <c r="O33" s="120"/>
+      <c r="P33" s="120"/>
+      <c r="Q33" s="120"/>
+      <c r="R33" s="121"/>
+      <c r="S33" s="118"/>
       <c r="AD33" s="46"/>
       <c r="AI33" s="99"/>
       <c r="AJ33" s="99"/>
@@ -5739,70 +5733,20 @@
       <c r="AW33" s="95"/>
     </row>
     <row r="34" spans="1:49" s="94" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="93" t="str">
-        <f>X21</f>
-        <v>Furnace</v>
-      </c>
-      <c r="C34" s="93" t="str">
-        <f>X9</f>
-        <v>DECELC</v>
-      </c>
-      <c r="D34" s="93" t="str">
-        <f>X12</f>
-        <v>DECEHEAT</v>
-      </c>
-      <c r="E34" s="119">
-        <v>2030</v>
-      </c>
-      <c r="F34" s="121">
-        <v>1</v>
-      </c>
-      <c r="G34" s="121">
-        <v>1</v>
-      </c>
-      <c r="H34" s="120">
-        <v>100</v>
-      </c>
-      <c r="I34" s="120">
-        <v>0</v>
-      </c>
-      <c r="J34" s="120">
-        <v>0</v>
-      </c>
-      <c r="K34" s="120">
-        <v>0</v>
-      </c>
-      <c r="L34" s="120">
-        <v>0</v>
-      </c>
-      <c r="M34" s="122"/>
-      <c r="N34" s="122"/>
-      <c r="O34" s="121"/>
-      <c r="P34" s="121"/>
-      <c r="Q34" s="121"/>
-      <c r="R34" s="122"/>
-      <c r="S34" s="119"/>
-      <c r="V34" s="99" t="s">
-        <v>128</v>
-      </c>
-      <c r="W34" s="99"/>
-      <c r="X34" s="108" t="s">
-        <v>170</v>
-      </c>
-      <c r="Y34" s="109" t="s">
-        <v>171</v>
-      </c>
-      <c r="Z34" s="95" t="s">
-        <v>58</v>
-      </c>
-      <c r="AA34" s="95" t="s">
-        <v>87</v>
-      </c>
-      <c r="AB34" s="94" t="s">
-        <v>88</v>
-      </c>
-      <c r="AC34" s="95"/>
-      <c r="AD34" s="95"/>
+      <c r="B34" s="93"/>
+      <c r="C34" s="95"/>
+      <c r="D34" s="93"/>
+      <c r="E34" s="124"/>
+      <c r="F34" s="125"/>
+      <c r="G34" s="125"/>
+      <c r="M34" s="126"/>
+      <c r="N34" s="126"/>
+      <c r="O34" s="125"/>
+      <c r="P34" s="125"/>
+      <c r="Q34" s="125"/>
+      <c r="R34" s="126"/>
+      <c r="S34" s="124"/>
+      <c r="AD34" s="46"/>
       <c r="AI34" s="99"/>
       <c r="AJ34" s="99"/>
       <c r="AK34" s="95"/>
@@ -5820,460 +5764,237 @@
       <c r="AW34" s="95"/>
     </row>
     <row r="35" spans="1:49" s="94" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="93" t="str">
-        <f>X25</f>
-        <v>ELCBoiler</v>
-      </c>
-      <c r="C35" s="93" t="str">
-        <f>X9</f>
-        <v>DECELC</v>
-      </c>
-      <c r="D35" s="93" t="str">
-        <f>X12</f>
-        <v>DECEHEAT</v>
-      </c>
-      <c r="E35" s="119">
-        <v>2030</v>
-      </c>
-      <c r="F35" s="121">
-        <v>1</v>
-      </c>
-      <c r="G35" s="121">
-        <v>1</v>
-      </c>
-      <c r="H35" s="119">
-        <v>100</v>
-      </c>
-      <c r="I35" s="121">
-        <v>0</v>
-      </c>
-      <c r="J35" s="121">
-        <v>0</v>
-      </c>
-      <c r="K35" s="121">
-        <v>0</v>
-      </c>
-      <c r="L35" s="121">
-        <v>0</v>
-      </c>
-      <c r="M35" s="122"/>
-      <c r="N35" s="122"/>
-      <c r="O35" s="121"/>
-      <c r="P35" s="121"/>
-      <c r="Q35" s="121"/>
-      <c r="R35" s="122"/>
-      <c r="S35" s="119"/>
-      <c r="V35" s="45"/>
-      <c r="W35" s="45"/>
-      <c r="X35" s="45"/>
-      <c r="Y35" s="45"/>
-      <c r="Z35" s="50"/>
-      <c r="AA35" s="38"/>
-      <c r="AB35" s="38"/>
-      <c r="AC35" s="95"/>
+      <c r="B35" s="93"/>
+      <c r="C35" s="95"/>
+      <c r="D35" s="93"/>
+      <c r="E35" s="124"/>
+      <c r="F35" s="125"/>
+      <c r="G35" s="125"/>
+      <c r="M35" s="126"/>
+      <c r="N35" s="126"/>
+      <c r="O35" s="125"/>
+      <c r="P35" s="125"/>
+      <c r="Q35" s="125"/>
+      <c r="R35" s="126"/>
+      <c r="S35" s="124"/>
       <c r="AD35" s="95"/>
       <c r="AI35" s="99"/>
       <c r="AJ35" s="99"/>
-      <c r="AK35" s="108"/>
-      <c r="AL35" s="108"/>
+      <c r="AK35" s="95"/>
+      <c r="AL35" s="95"/>
       <c r="AM35" s="95"/>
       <c r="AN35" s="95"/>
       <c r="AO35" s="95"/>
-      <c r="AQ35" s="99"/>
-      <c r="AR35" s="99"/>
-      <c r="AS35" s="108"/>
-      <c r="AT35" s="108"/>
+      <c r="AP35" s="95"/>
+      <c r="AQ35" s="95"/>
+      <c r="AR35" s="95"/>
+      <c r="AS35" s="95"/>
+      <c r="AT35" s="95"/>
       <c r="AU35" s="95"/>
       <c r="AV35" s="95"/>
-    </row>
-    <row r="36" spans="1:49" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="5" t="str">
-        <f>X33</f>
-        <v>MANELC_TECH</v>
-      </c>
-      <c r="C36" s="50" t="str">
-        <f>X9</f>
-        <v>DECELC</v>
-      </c>
-      <c r="D36" s="50" t="s">
-        <v>153</v>
-      </c>
-      <c r="E36" s="116">
-        <v>2030</v>
-      </c>
-      <c r="F36" s="113">
-        <v>1</v>
-      </c>
-      <c r="G36" s="117">
-        <v>1</v>
-      </c>
-      <c r="H36" s="123">
-        <v>100</v>
-      </c>
-      <c r="I36" s="123">
-        <v>0</v>
-      </c>
-      <c r="J36" s="123">
-        <v>0</v>
-      </c>
-      <c r="K36" s="123">
-        <v>0</v>
-      </c>
-      <c r="L36" s="123">
-        <v>0</v>
-      </c>
-      <c r="M36" s="116"/>
-      <c r="N36" s="118"/>
-      <c r="O36" s="116"/>
-      <c r="P36" s="116"/>
-      <c r="Q36" s="116"/>
-      <c r="R36" s="116"/>
-      <c r="S36" s="116"/>
-      <c r="V36" s="101"/>
-      <c r="W36" s="100"/>
-      <c r="X36" s="101"/>
-      <c r="Y36" s="100"/>
-      <c r="Z36" s="103"/>
-      <c r="AA36" s="102"/>
-      <c r="AB36" s="104"/>
-      <c r="AC36" s="45"/>
-      <c r="AD36" s="45"/>
-      <c r="AI36"/>
-      <c r="AJ36"/>
-      <c r="AK36" s="39"/>
-      <c r="AL36" s="39"/>
-      <c r="AM36" s="45"/>
-      <c r="AN36" s="45"/>
-      <c r="AO36" s="45"/>
-      <c r="AQ36"/>
-      <c r="AR36"/>
-      <c r="AS36" s="39"/>
-      <c r="AT36" s="39"/>
-      <c r="AU36" s="45"/>
-      <c r="AV36" s="45"/>
-    </row>
-    <row r="37" spans="1:49" s="100" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="101" t="str">
-        <f>X32</f>
-        <v>ETHT</v>
-      </c>
-      <c r="C37" s="102" t="str">
-        <f>X11</f>
-        <v>GEHEAT</v>
-      </c>
-      <c r="D37" s="102" t="str">
-        <f>X13</f>
-        <v>ELCHEAT</v>
-      </c>
-      <c r="E37" s="125">
-        <v>2030</v>
-      </c>
-      <c r="F37" s="126">
-        <v>1</v>
-      </c>
-      <c r="G37" s="126">
-        <v>1</v>
-      </c>
-      <c r="H37" s="125">
-        <v>100</v>
-      </c>
-      <c r="I37" s="126">
-        <v>0</v>
-      </c>
-      <c r="J37" s="126">
-        <v>0</v>
-      </c>
-      <c r="K37" s="126">
-        <v>0</v>
-      </c>
-      <c r="L37" s="126">
-        <v>0</v>
-      </c>
-      <c r="M37" s="127"/>
-      <c r="N37" s="128"/>
-      <c r="O37" s="127"/>
-      <c r="P37" s="127"/>
-      <c r="Q37" s="127"/>
-      <c r="R37" s="127"/>
-      <c r="S37" s="127"/>
-      <c r="V37" s="95"/>
-      <c r="W37" s="95"/>
-      <c r="X37" s="95"/>
-      <c r="Y37" s="95"/>
-      <c r="Z37" s="95"/>
-      <c r="AA37" s="107"/>
-      <c r="AB37" s="95"/>
-      <c r="AC37" s="101"/>
-      <c r="AD37" s="101"/>
-      <c r="AI37" s="105"/>
-      <c r="AJ37" s="105"/>
-      <c r="AK37" s="106"/>
-      <c r="AL37" s="106"/>
-      <c r="AM37" s="101"/>
-      <c r="AN37" s="101"/>
-      <c r="AO37" s="101"/>
-      <c r="AQ37" s="105"/>
-      <c r="AR37" s="105"/>
-      <c r="AS37" s="106"/>
-      <c r="AT37" s="106"/>
-      <c r="AU37" s="101"/>
-      <c r="AV37" s="101"/>
-    </row>
-    <row r="38" spans="1:49" s="94" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="95" t="str">
-        <f>X32</f>
-        <v>ETHT</v>
-      </c>
-      <c r="C38" s="93" t="str">
-        <f>X12</f>
-        <v>DECEHEAT</v>
-      </c>
-      <c r="D38" s="93" t="str">
-        <f>X13</f>
-        <v>ELCHEAT</v>
-      </c>
-      <c r="E38" s="119">
-        <v>2030</v>
-      </c>
-      <c r="F38" s="121">
-        <v>1</v>
-      </c>
-      <c r="G38" s="121">
-        <v>1</v>
-      </c>
-      <c r="H38" s="119">
-        <v>100</v>
-      </c>
-      <c r="I38" s="121">
-        <v>0</v>
-      </c>
-      <c r="J38" s="121">
-        <v>0</v>
-      </c>
-      <c r="K38" s="121">
-        <v>0</v>
-      </c>
-      <c r="L38" s="121">
-        <v>0</v>
-      </c>
-      <c r="M38" s="120"/>
-      <c r="N38" s="129"/>
-      <c r="O38" s="120"/>
-      <c r="P38" s="120"/>
-      <c r="Q38" s="120"/>
-      <c r="R38" s="120"/>
-      <c r="S38" s="120"/>
-      <c r="V38" s="45"/>
-      <c r="W38" s="45"/>
-      <c r="X38" s="45"/>
-      <c r="Y38" s="45"/>
-      <c r="Z38" s="45"/>
-      <c r="AA38" s="54"/>
-      <c r="AB38" s="45"/>
-      <c r="AC38" s="95"/>
-      <c r="AD38" s="95"/>
-      <c r="AI38" s="99"/>
-      <c r="AJ38" s="99"/>
-      <c r="AK38" s="108"/>
-      <c r="AL38" s="108"/>
-      <c r="AM38" s="95"/>
-      <c r="AN38" s="95"/>
-      <c r="AO38" s="95"/>
-      <c r="AQ38" s="99"/>
-      <c r="AR38" s="99"/>
-      <c r="AS38" s="108"/>
-      <c r="AT38" s="108"/>
-      <c r="AU38" s="95"/>
-      <c r="AV38" s="95"/>
-    </row>
-    <row r="39" spans="1:49" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="45" t="str">
-        <f>X31</f>
-        <v>RNWTHT</v>
-      </c>
-      <c r="C39" s="50" t="str">
-        <f>X13</f>
-        <v>ELCHEAT</v>
-      </c>
-      <c r="D39" s="50" t="str">
-        <f>X10</f>
-        <v>RNWHEAT</v>
-      </c>
-      <c r="E39" s="116">
-        <v>2030</v>
-      </c>
-      <c r="F39" s="113">
-        <v>1</v>
-      </c>
-      <c r="G39" s="117">
-        <v>1</v>
-      </c>
-      <c r="H39" s="123">
-        <v>100</v>
-      </c>
-      <c r="I39" s="123">
-        <v>0</v>
-      </c>
-      <c r="J39" s="123">
-        <v>0</v>
-      </c>
-      <c r="K39" s="123">
-        <v>0</v>
-      </c>
-      <c r="L39" s="123">
-        <v>0</v>
-      </c>
-      <c r="M39" s="123"/>
-      <c r="N39" s="130"/>
-      <c r="O39" s="123"/>
-      <c r="P39" s="123"/>
-      <c r="Q39" s="123"/>
-      <c r="R39" s="123"/>
-      <c r="S39" s="123"/>
-      <c r="V39" s="45"/>
-      <c r="W39" s="45"/>
-      <c r="X39" s="45"/>
-      <c r="Y39" s="45"/>
-      <c r="Z39" s="45"/>
-      <c r="AA39" s="45"/>
-      <c r="AB39" s="45"/>
-      <c r="AC39" s="45"/>
-      <c r="AD39" s="45"/>
-      <c r="AI39"/>
-      <c r="AJ39"/>
-      <c r="AK39" s="39"/>
-      <c r="AL39" s="39"/>
-      <c r="AM39" s="45"/>
-      <c r="AN39" s="45"/>
-      <c r="AO39" s="45"/>
-      <c r="AQ39"/>
-      <c r="AR39"/>
-      <c r="AS39" s="39"/>
-      <c r="AT39" s="39"/>
-      <c r="AU39" s="45"/>
-      <c r="AV39" s="45"/>
-    </row>
-    <row r="40" spans="1:49" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="50" t="str">
-        <f>X31</f>
-        <v>RNWTHT</v>
-      </c>
-      <c r="C40" s="50" t="str">
-        <f>X8</f>
-        <v>DECRHEAT</v>
-      </c>
-      <c r="D40" s="50" t="str">
-        <f>X10</f>
-        <v>RNWHEAT</v>
-      </c>
-      <c r="E40" s="116">
-        <v>2030</v>
-      </c>
-      <c r="F40" s="113">
-        <v>1</v>
-      </c>
-      <c r="G40" s="117">
-        <v>1</v>
-      </c>
-      <c r="H40" s="123">
-        <v>100</v>
-      </c>
-      <c r="I40" s="123">
-        <v>0</v>
-      </c>
-      <c r="J40" s="123">
-        <v>0</v>
-      </c>
-      <c r="K40" s="123">
-        <v>0</v>
-      </c>
-      <c r="L40" s="123">
-        <v>0</v>
-      </c>
-      <c r="M40" s="123"/>
-      <c r="N40" s="123"/>
-      <c r="O40" s="123"/>
-      <c r="P40" s="123"/>
-      <c r="Q40" s="123"/>
-      <c r="R40" s="123"/>
-      <c r="S40" s="123"/>
+      <c r="AW35" s="95"/>
+    </row>
+    <row r="36" spans="1:49" s="94" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="93"/>
+      <c r="C36" s="93"/>
+      <c r="D36" s="93"/>
+      <c r="E36" s="124"/>
+      <c r="F36" s="125"/>
+      <c r="G36" s="125"/>
+      <c r="M36" s="126"/>
+      <c r="N36" s="126"/>
+      <c r="O36" s="125"/>
+      <c r="P36" s="125"/>
+      <c r="Q36" s="125"/>
+      <c r="R36" s="126"/>
+      <c r="S36" s="124"/>
+      <c r="AA36" s="38"/>
+      <c r="AB36" s="38"/>
+      <c r="AC36" s="95"/>
+      <c r="AD36" s="95"/>
+      <c r="AI36" s="99"/>
+      <c r="AJ36" s="99"/>
+      <c r="AK36" s="95"/>
+      <c r="AL36" s="95"/>
+      <c r="AM36" s="95"/>
+      <c r="AN36" s="95"/>
+      <c r="AO36" s="95"/>
+      <c r="AP36" s="95"/>
+      <c r="AQ36" s="95"/>
+      <c r="AR36" s="95"/>
+      <c r="AS36" s="95"/>
+      <c r="AT36" s="95"/>
+      <c r="AU36" s="95"/>
+      <c r="AV36" s="95"/>
+      <c r="AW36" s="95"/>
+    </row>
+    <row r="37" spans="1:49" s="94" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="93"/>
+      <c r="C37" s="93"/>
+      <c r="D37" s="93"/>
+      <c r="E37" s="124"/>
+      <c r="F37" s="125"/>
+      <c r="G37" s="125"/>
+      <c r="H37" s="124"/>
+      <c r="I37" s="125"/>
+      <c r="J37" s="125"/>
+      <c r="K37" s="125"/>
+      <c r="L37" s="125"/>
+      <c r="M37" s="126"/>
+      <c r="N37" s="126"/>
+      <c r="O37" s="125"/>
+      <c r="P37" s="125"/>
+      <c r="Q37" s="125"/>
+      <c r="R37" s="126"/>
+      <c r="S37" s="124"/>
+      <c r="V37" s="45"/>
+      <c r="W37" s="45"/>
+      <c r="X37" s="45"/>
+      <c r="Y37" s="45"/>
+      <c r="Z37" s="50"/>
+      <c r="AA37" s="102"/>
+      <c r="AB37" s="104"/>
+      <c r="AC37" s="45"/>
+      <c r="AD37" s="45"/>
+      <c r="AI37" s="99"/>
+      <c r="AJ37" s="99"/>
+      <c r="AK37" s="107"/>
+      <c r="AL37" s="107"/>
+      <c r="AM37" s="95"/>
+      <c r="AN37" s="95"/>
+      <c r="AO37" s="95"/>
+      <c r="AQ37" s="99"/>
+      <c r="AR37" s="99"/>
+      <c r="AS37" s="107"/>
+      <c r="AT37" s="107"/>
+      <c r="AU37" s="95"/>
+      <c r="AV37" s="95"/>
+    </row>
+    <row r="38" spans="1:49" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="5"/>
+      <c r="C38" s="50"/>
+      <c r="D38" s="50"/>
+      <c r="E38" s="127"/>
+      <c r="F38" s="128"/>
+      <c r="G38" s="129"/>
+      <c r="M38" s="127"/>
+      <c r="N38" s="130"/>
+      <c r="O38" s="127"/>
+      <c r="P38" s="127"/>
+      <c r="Q38" s="127"/>
+      <c r="R38" s="127"/>
+      <c r="S38" s="127"/>
+      <c r="V38" s="101"/>
+      <c r="W38" s="100"/>
+      <c r="X38" s="101"/>
+      <c r="Y38" s="100"/>
+      <c r="Z38" s="103"/>
+      <c r="AA38" s="95"/>
+      <c r="AB38" s="94"/>
+      <c r="AC38" s="94"/>
+      <c r="AD38" s="101"/>
+      <c r="AI38"/>
+      <c r="AJ38"/>
+      <c r="AK38" s="39"/>
+      <c r="AL38" s="39"/>
+      <c r="AM38" s="45"/>
+      <c r="AN38" s="45"/>
+      <c r="AO38" s="45"/>
+      <c r="AQ38"/>
+      <c r="AR38"/>
+      <c r="AS38" s="39"/>
+      <c r="AT38" s="39"/>
+      <c r="AU38" s="45"/>
+      <c r="AV38" s="45"/>
+    </row>
+    <row r="39" spans="1:49" s="100" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="101"/>
+      <c r="C39" s="102"/>
+      <c r="D39" s="102"/>
+      <c r="E39" s="131"/>
+      <c r="F39" s="132"/>
+      <c r="G39" s="132"/>
+      <c r="H39" s="131"/>
+      <c r="I39" s="132"/>
+      <c r="J39" s="132"/>
+      <c r="K39" s="132"/>
+      <c r="L39" s="132"/>
+      <c r="N39" s="133"/>
+      <c r="V39" s="46"/>
+      <c r="W39" s="46"/>
+      <c r="X39" s="46"/>
+      <c r="Y39" s="46"/>
+      <c r="Z39" s="95"/>
+      <c r="AA39" s="95"/>
+      <c r="AB39" s="94"/>
+      <c r="AC39" s="46"/>
+      <c r="AD39" s="95"/>
+      <c r="AI39" s="105"/>
+      <c r="AJ39" s="105"/>
+      <c r="AK39" s="106"/>
+      <c r="AL39" s="106"/>
+      <c r="AM39" s="101"/>
+      <c r="AN39" s="101"/>
+      <c r="AO39" s="101"/>
+      <c r="AQ39" s="105"/>
+      <c r="AR39" s="105"/>
+      <c r="AS39" s="106"/>
+      <c r="AT39" s="106"/>
+      <c r="AU39" s="101"/>
+      <c r="AV39" s="101"/>
+    </row>
+    <row r="40" spans="1:49" s="94" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="95"/>
+      <c r="C40" s="93"/>
+      <c r="D40" s="93"/>
+      <c r="E40" s="124"/>
+      <c r="F40" s="125"/>
+      <c r="G40" s="125"/>
+      <c r="H40" s="124"/>
+      <c r="I40" s="125"/>
+      <c r="J40" s="125"/>
+      <c r="K40" s="125"/>
+      <c r="L40" s="125"/>
+      <c r="N40" s="134"/>
       <c r="V40" s="45"/>
       <c r="W40" s="45"/>
       <c r="X40" s="45"/>
       <c r="Y40" s="45"/>
-      <c r="Z40" s="45"/>
-      <c r="AA40" s="45"/>
-      <c r="AB40" s="45"/>
-      <c r="AC40" s="45"/>
+      <c r="Z40" s="95"/>
+      <c r="AA40" s="95"/>
+      <c r="AC40" s="95"/>
       <c r="AD40" s="45"/>
-      <c r="AE40" s="45"/>
-      <c r="AI40"/>
-      <c r="AJ40"/>
-      <c r="AK40" s="39"/>
-      <c r="AL40" s="39"/>
-      <c r="AM40" s="45"/>
-      <c r="AN40" s="45"/>
-      <c r="AO40" s="45"/>
-      <c r="AQ40"/>
-      <c r="AR40"/>
-      <c r="AS40" s="39"/>
-      <c r="AT40" s="39"/>
-      <c r="AU40" s="45"/>
-      <c r="AV40" s="45"/>
+      <c r="AI40" s="99"/>
+      <c r="AJ40" s="99"/>
+      <c r="AK40" s="107"/>
+      <c r="AL40" s="107"/>
+      <c r="AM40" s="95"/>
+      <c r="AN40" s="95"/>
+      <c r="AO40" s="95"/>
+      <c r="AQ40" s="99"/>
+      <c r="AR40" s="99"/>
+      <c r="AS40" s="107"/>
+      <c r="AT40" s="107"/>
+      <c r="AU40" s="95"/>
+      <c r="AV40" s="95"/>
     </row>
     <row r="41" spans="1:49" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="50" t="str">
-        <f>X34</f>
-        <v>PTHT</v>
-      </c>
-      <c r="C41" s="50" t="str">
-        <f>X10</f>
-        <v>RNWHEAT</v>
-      </c>
-      <c r="D41" s="50" t="s">
-        <v>107</v>
-      </c>
-      <c r="E41" s="116">
-        <v>2030</v>
-      </c>
-      <c r="F41" s="113">
-        <v>1</v>
-      </c>
-      <c r="G41" s="117">
-        <v>1</v>
-      </c>
-      <c r="H41" s="123">
-        <v>100</v>
-      </c>
-      <c r="I41" s="123">
-        <v>0</v>
-      </c>
-      <c r="J41" s="123">
-        <v>0</v>
-      </c>
-      <c r="K41" s="123">
-        <v>0</v>
-      </c>
-      <c r="L41" s="123">
-        <v>0</v>
-      </c>
-      <c r="M41" s="123"/>
-      <c r="N41" s="123"/>
-      <c r="O41" s="123"/>
-      <c r="P41" s="123"/>
-      <c r="Q41" s="123"/>
-      <c r="R41" s="123"/>
-      <c r="S41" s="123"/>
-      <c r="V41" s="45"/>
-      <c r="W41" s="45"/>
-      <c r="X41" s="45"/>
-      <c r="Y41" s="45"/>
-      <c r="Z41" s="45"/>
-      <c r="AA41" s="45"/>
-      <c r="AB41" s="45"/>
-      <c r="AC41" s="45"/>
+      <c r="B41" s="45"/>
+      <c r="C41" s="50"/>
+      <c r="D41" s="50"/>
+      <c r="E41" s="127"/>
+      <c r="F41" s="128"/>
+      <c r="G41" s="129"/>
+      <c r="N41" s="135"/>
+      <c r="V41" s="99"/>
+      <c r="W41" s="99"/>
+      <c r="X41" s="95"/>
+      <c r="Y41" s="108"/>
+      <c r="Z41" s="95"/>
+      <c r="AA41" s="95"/>
+      <c r="AB41" s="94"/>
+      <c r="AC41" s="95"/>
       <c r="AD41" s="45"/>
-      <c r="AE41" s="45"/>
       <c r="AI41"/>
       <c r="AJ41"/>
       <c r="AK41" s="39"/>
@@ -6288,84 +6009,125 @@
       <c r="AU41" s="45"/>
       <c r="AV41" s="45"/>
     </row>
-    <row r="42" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A42" s="46"/>
-      <c r="E42" s="123"/>
-      <c r="F42" s="131"/>
-      <c r="G42" s="116"/>
-      <c r="H42" s="130"/>
-      <c r="I42" s="123"/>
-      <c r="J42" s="123"/>
-      <c r="K42" s="123"/>
-      <c r="L42" s="123"/>
-      <c r="M42" s="123"/>
-      <c r="N42" s="123"/>
-      <c r="O42" s="123"/>
-      <c r="P42" s="123"/>
-      <c r="Q42" s="123"/>
-      <c r="R42" s="123"/>
-      <c r="S42" s="123"/>
+    <row r="42" spans="1:49" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="50"/>
+      <c r="C42" s="50"/>
+      <c r="D42" s="50"/>
+      <c r="E42" s="127"/>
+      <c r="F42" s="128"/>
+      <c r="G42" s="129"/>
+      <c r="V42" s="99"/>
+      <c r="W42" s="99"/>
+      <c r="X42" s="95"/>
+      <c r="Y42" s="108"/>
+      <c r="Z42" s="95"/>
+      <c r="AA42" s="95"/>
+      <c r="AB42" s="94"/>
+      <c r="AC42" s="95"/>
+      <c r="AD42" s="45"/>
+      <c r="AE42" s="45"/>
       <c r="AI42"/>
       <c r="AJ42"/>
       <c r="AK42" s="39"/>
       <c r="AL42" s="39"/>
-      <c r="AP42" s="46"/>
+      <c r="AM42" s="45"/>
+      <c r="AN42" s="45"/>
+      <c r="AO42" s="45"/>
       <c r="AQ42"/>
       <c r="AR42"/>
       <c r="AS42" s="39"/>
       <c r="AT42" s="39"/>
-    </row>
-    <row r="43" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A43" s="46"/>
-      <c r="H43" s="64"/>
-      <c r="M43" s="46"/>
-      <c r="N43" s="46"/>
-      <c r="O43" s="46"/>
-      <c r="P43" s="46"/>
-      <c r="Q43" s="46"/>
-      <c r="R43" s="46"/>
-      <c r="S43" s="46"/>
+      <c r="AU42" s="45"/>
+      <c r="AV42" s="45"/>
+    </row>
+    <row r="43" spans="1:49" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="50"/>
+      <c r="C43" s="50"/>
+      <c r="D43" s="50"/>
+      <c r="E43" s="127"/>
+      <c r="F43" s="128"/>
+      <c r="G43" s="129"/>
+      <c r="V43" s="99"/>
+      <c r="W43" s="99"/>
+      <c r="X43" s="95"/>
+      <c r="Y43" s="108"/>
+      <c r="Z43" s="95"/>
+      <c r="AA43" s="95"/>
+      <c r="AB43" s="94"/>
+      <c r="AC43" s="95"/>
+      <c r="AD43" s="45"/>
+      <c r="AE43" s="45"/>
       <c r="AI43"/>
       <c r="AJ43"/>
       <c r="AK43" s="39"/>
       <c r="AL43" s="39"/>
-      <c r="AP43" s="46"/>
+      <c r="AM43" s="45"/>
+      <c r="AN43" s="45"/>
+      <c r="AO43" s="45"/>
       <c r="AQ43"/>
       <c r="AR43"/>
       <c r="AS43" s="39"/>
       <c r="AT43" s="39"/>
+      <c r="AU43" s="45"/>
+      <c r="AV43" s="45"/>
     </row>
     <row r="44" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="B44" s="65"/>
-      <c r="C44" s="45" t="s">
-        <v>82</v>
-      </c>
-      <c r="H44" s="64"/>
+      <c r="A44" s="46"/>
+      <c r="E44" s="46"/>
+      <c r="F44" s="136"/>
+      <c r="G44" s="127"/>
+      <c r="H44" s="135"/>
+      <c r="I44" s="46"/>
+      <c r="J44" s="46"/>
+      <c r="K44" s="46"/>
+      <c r="L44" s="46"/>
+      <c r="M44" s="46"/>
+      <c r="N44" s="46"/>
+      <c r="O44" s="46"/>
+      <c r="P44" s="46"/>
+      <c r="Q44" s="46"/>
+      <c r="R44" s="46"/>
+      <c r="S44" s="46"/>
+      <c r="V44" s="99"/>
+      <c r="W44" s="99"/>
+      <c r="X44" s="107"/>
+      <c r="Y44" s="108"/>
+      <c r="Z44" s="95"/>
       <c r="AI44"/>
       <c r="AJ44"/>
       <c r="AK44" s="39"/>
       <c r="AL44" s="39"/>
+      <c r="AP44" s="46"/>
       <c r="AQ44"/>
       <c r="AR44"/>
       <c r="AS44" s="39"/>
       <c r="AT44" s="39"/>
     </row>
     <row r="45" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="B45" s="66"/>
-      <c r="C45" s="45" t="s">
-        <v>83</v>
-      </c>
+      <c r="A45" s="46"/>
       <c r="H45" s="64"/>
+      <c r="M45" s="46"/>
+      <c r="N45" s="46"/>
+      <c r="O45" s="46"/>
+      <c r="P45" s="46"/>
+      <c r="Q45" s="46"/>
+      <c r="R45" s="46"/>
+      <c r="S45" s="46"/>
       <c r="AI45"/>
       <c r="AJ45"/>
       <c r="AK45" s="39"/>
       <c r="AL45" s="39"/>
+      <c r="AP45" s="46"/>
       <c r="AQ45"/>
       <c r="AR45"/>
       <c r="AS45" s="39"/>
       <c r="AT45" s="39"/>
     </row>
     <row r="46" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="B46" s="65"/>
+      <c r="C46" s="45" t="s">
+        <v>82</v>
+      </c>
       <c r="H46" s="64"/>
       <c r="AI46"/>
       <c r="AJ46"/>
@@ -6377,6 +6139,11 @@
       <c r="AT46" s="39"/>
     </row>
     <row r="47" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="B47" s="66"/>
+      <c r="C47" s="45" t="s">
+        <v>83</v>
+      </c>
+      <c r="H47" s="64"/>
       <c r="AI47"/>
       <c r="AJ47"/>
       <c r="AK47" s="39"/>
@@ -6387,6 +6154,7 @@
       <c r="AT47" s="39"/>
     </row>
     <row r="48" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="H48" s="64"/>
       <c r="AI48"/>
       <c r="AJ48"/>
       <c r="AK48" s="39"/>
@@ -6397,7 +6165,6 @@
       <c r="AT48" s="39"/>
     </row>
     <row r="49" spans="2:46" x14ac:dyDescent="0.25">
-      <c r="E49" s="43"/>
       <c r="AI49"/>
       <c r="AJ49"/>
       <c r="AK49" s="39"/>
@@ -6418,6 +6185,7 @@
       <c r="AT50" s="39"/>
     </row>
     <row r="51" spans="2:46" x14ac:dyDescent="0.25">
+      <c r="E51" s="43"/>
       <c r="AI51"/>
       <c r="AJ51"/>
       <c r="AK51" s="39"/>
@@ -6468,17 +6236,6 @@
       <c r="AT55" s="39"/>
     </row>
     <row r="56" spans="2:46" x14ac:dyDescent="0.25">
-      <c r="B56" s="68"/>
-      <c r="C56" s="68"/>
-      <c r="D56"/>
-      <c r="E56"/>
-      <c r="F56"/>
-      <c r="G56"/>
-      <c r="H56"/>
-      <c r="I56"/>
-      <c r="J56"/>
-      <c r="K56"/>
-      <c r="L56"/>
       <c r="AI56"/>
       <c r="AJ56"/>
       <c r="AK56" s="39"/>
@@ -6488,18 +6245,7 @@
       <c r="AS56" s="39"/>
       <c r="AT56" s="39"/>
     </row>
-    <row r="57" spans="2:46" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="69"/>
-      <c r="C57" s="69"/>
-      <c r="D57" s="69"/>
-      <c r="E57" s="69"/>
-      <c r="F57" s="69"/>
-      <c r="G57" s="69"/>
-      <c r="H57" s="69"/>
-      <c r="I57" s="69"/>
-      <c r="J57" s="69"/>
-      <c r="K57" s="69"/>
-      <c r="L57" s="69"/>
+    <row r="57" spans="2:46" x14ac:dyDescent="0.25">
       <c r="AI57"/>
       <c r="AJ57"/>
       <c r="AK57" s="39"/>
@@ -6510,10 +6256,10 @@
       <c r="AT57" s="39"/>
     </row>
     <row r="58" spans="2:46" x14ac:dyDescent="0.25">
-      <c r="B58"/>
-      <c r="C58"/>
+      <c r="B58" s="68"/>
+      <c r="C58" s="68"/>
       <c r="D58"/>
-      <c r="E58" s="1"/>
+      <c r="E58"/>
       <c r="F58"/>
       <c r="G58"/>
       <c r="H58"/>
@@ -6530,18 +6276,18 @@
       <c r="AS58" s="39"/>
       <c r="AT58" s="39"/>
     </row>
-    <row r="59" spans="2:46" x14ac:dyDescent="0.25">
-      <c r="B59"/>
-      <c r="C59"/>
-      <c r="D59"/>
-      <c r="E59" s="1"/>
-      <c r="F59"/>
-      <c r="G59"/>
-      <c r="H59"/>
-      <c r="I59"/>
-      <c r="J59"/>
-      <c r="K59"/>
-      <c r="L59"/>
+    <row r="59" spans="2:46" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B59" s="69"/>
+      <c r="C59" s="69"/>
+      <c r="D59" s="69"/>
+      <c r="E59" s="69"/>
+      <c r="F59" s="69"/>
+      <c r="G59" s="69"/>
+      <c r="H59" s="69"/>
+      <c r="I59" s="69"/>
+      <c r="J59" s="69"/>
+      <c r="K59" s="69"/>
+      <c r="L59" s="69"/>
       <c r="AI59"/>
       <c r="AJ59"/>
       <c r="AK59" s="39"/>
@@ -6678,6 +6424,17 @@
       <c r="AT65" s="39"/>
     </row>
     <row r="66" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="B66"/>
+      <c r="C66"/>
+      <c r="D66"/>
+      <c r="E66" s="1"/>
+      <c r="F66"/>
+      <c r="G66"/>
+      <c r="H66"/>
+      <c r="I66"/>
+      <c r="J66"/>
+      <c r="K66"/>
+      <c r="L66"/>
       <c r="AI66"/>
       <c r="AJ66"/>
       <c r="AK66" s="39"/>
@@ -6688,11 +6445,17 @@
       <c r="AT66" s="39"/>
     </row>
     <row r="67" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="V67" s="46"/>
-      <c r="W67" s="46"/>
-      <c r="X67" s="46"/>
-      <c r="Y67" s="46"/>
-      <c r="Z67" s="46"/>
+      <c r="B67"/>
+      <c r="C67"/>
+      <c r="D67"/>
+      <c r="E67" s="1"/>
+      <c r="F67"/>
+      <c r="G67"/>
+      <c r="H67"/>
+      <c r="I67"/>
+      <c r="J67"/>
+      <c r="K67"/>
+      <c r="L67"/>
       <c r="AI67"/>
       <c r="AJ67"/>
       <c r="AK67" s="39"/>
@@ -6703,13 +6466,6 @@
       <c r="AT67" s="39"/>
     </row>
     <row r="68" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="V68" s="46"/>
-      <c r="W68" s="46"/>
-      <c r="X68" s="46"/>
-      <c r="Y68" s="46"/>
-      <c r="Z68" s="46"/>
-      <c r="AA68" s="46"/>
-      <c r="AB68" s="46"/>
       <c r="AI68"/>
       <c r="AJ68"/>
       <c r="AK68" s="39"/>
@@ -6727,7 +6483,6 @@
       <c r="Z69" s="46"/>
       <c r="AA69" s="46"/>
       <c r="AB69" s="46"/>
-      <c r="AC69" s="46"/>
       <c r="AI69"/>
       <c r="AJ69"/>
       <c r="AK69" s="39"/>
@@ -6738,11 +6493,14 @@
       <c r="AT69" s="39"/>
     </row>
     <row r="70" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="V70" s="46"/>
+      <c r="W70" s="46"/>
+      <c r="X70" s="46"/>
+      <c r="Y70" s="46"/>
+      <c r="Z70" s="46"/>
       <c r="AA70" s="46"/>
       <c r="AB70" s="46"/>
       <c r="AC70" s="46"/>
-      <c r="AD70" s="46"/>
-      <c r="AE70" s="46"/>
       <c r="AI70"/>
       <c r="AJ70"/>
       <c r="AK70" s="39"/>
@@ -6753,19 +6511,15 @@
       <c r="AT70" s="39"/>
     </row>
     <row r="71" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="B71"/>
-      <c r="C71"/>
-      <c r="E71" s="68"/>
-      <c r="F71" s="68"/>
-      <c r="G71" s="1"/>
-      <c r="H71"/>
-      <c r="I71" s="68"/>
-      <c r="J71"/>
-      <c r="K71"/>
-      <c r="L71" s="68"/>
+      <c r="V71" s="46"/>
+      <c r="W71" s="46"/>
+      <c r="X71" s="46"/>
+      <c r="Y71" s="46"/>
+      <c r="Z71" s="46"/>
+      <c r="AA71" s="46"/>
+      <c r="AB71" s="46"/>
       <c r="AC71" s="46"/>
       <c r="AD71" s="46"/>
-      <c r="AE71" s="46"/>
       <c r="AI71"/>
       <c r="AJ71"/>
       <c r="AK71" s="39"/>
@@ -6775,97 +6529,61 @@
       <c r="AS71" s="39"/>
       <c r="AT71" s="39"/>
     </row>
-    <row r="72" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="45"/>
-      <c r="B72" s="74"/>
-      <c r="C72" s="74"/>
-      <c r="D72" s="74"/>
-      <c r="E72" s="74"/>
-      <c r="F72" s="74"/>
-      <c r="G72" s="74"/>
-      <c r="H72" s="75"/>
-      <c r="I72" s="74"/>
-      <c r="J72" s="74"/>
-      <c r="K72" s="74"/>
-      <c r="L72" s="74"/>
-      <c r="M72" s="45"/>
-      <c r="N72" s="45"/>
-      <c r="O72" s="45"/>
-      <c r="P72" s="45"/>
-      <c r="Q72" s="45"/>
-      <c r="R72" s="45"/>
-      <c r="S72" s="45"/>
-      <c r="V72" s="45"/>
-      <c r="W72" s="45"/>
-      <c r="X72" s="45"/>
-      <c r="Y72" s="45"/>
-      <c r="Z72" s="45"/>
-      <c r="AA72" s="45"/>
-      <c r="AB72" s="45"/>
-      <c r="AC72" s="45"/>
+    <row r="72" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="AC72" s="46"/>
+      <c r="AD72" s="46"/>
+      <c r="AE72" s="46"/>
       <c r="AI72"/>
-      <c r="AJ72" s="75"/>
+      <c r="AJ72"/>
       <c r="AK72" s="39"/>
-      <c r="AL72" s="41"/>
-      <c r="AM72" s="45"/>
-      <c r="AN72" s="45"/>
+      <c r="AL72" s="39"/>
       <c r="AQ72"/>
-      <c r="AR72" s="75"/>
+      <c r="AR72"/>
       <c r="AS72" s="39"/>
-      <c r="AT72" s="41"/>
-      <c r="AU72" s="45"/>
-      <c r="AV72" s="45"/>
-    </row>
-    <row r="73" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="68"/>
-      <c r="B73" s="76"/>
-      <c r="C73" s="77"/>
-      <c r="D73" s="76"/>
-      <c r="E73" s="76"/>
-      <c r="F73" s="76"/>
-      <c r="G73" s="76"/>
-      <c r="H73" s="75"/>
-      <c r="I73" s="76"/>
-      <c r="J73" s="76"/>
-      <c r="K73" s="77"/>
-      <c r="L73" s="77"/>
-      <c r="M73" s="68"/>
-      <c r="N73" s="68"/>
-      <c r="O73" s="1"/>
-      <c r="P73" s="45"/>
-      <c r="Q73" s="45"/>
-      <c r="R73" s="45"/>
-      <c r="S73" s="45"/>
-      <c r="V73" s="45"/>
-      <c r="W73" s="45"/>
-      <c r="X73" s="45"/>
-      <c r="Y73" s="45"/>
-      <c r="Z73" s="45"/>
-      <c r="AA73" s="45"/>
-      <c r="AB73" s="45"/>
-      <c r="AC73" s="45"/>
-      <c r="AD73" s="45"/>
-      <c r="AE73" s="45"/>
-      <c r="AI73" s="42"/>
-      <c r="AJ73" s="42"/>
-      <c r="AK73" s="54"/>
+      <c r="AT72" s="39"/>
+    </row>
+    <row r="73" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="B73"/>
+      <c r="C73"/>
+      <c r="E73" s="68"/>
+      <c r="F73" s="68"/>
+      <c r="G73" s="1"/>
+      <c r="H73"/>
+      <c r="I73" s="68"/>
+      <c r="J73"/>
+      <c r="K73"/>
+      <c r="L73" s="68"/>
+      <c r="AD73" s="46"/>
+      <c r="AE73" s="46"/>
+      <c r="AI73"/>
+      <c r="AJ73"/>
+      <c r="AK73" s="39"/>
+      <c r="AL73" s="39"/>
+      <c r="AQ73"/>
+      <c r="AR73"/>
+      <c r="AS73" s="39"/>
+      <c r="AT73" s="39"/>
     </row>
     <row r="74" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="74"/>
-      <c r="B74" s="76"/>
-      <c r="C74" s="76"/>
-      <c r="D74" s="76"/>
-      <c r="E74" s="76"/>
-      <c r="F74" s="76"/>
-      <c r="G74" s="76"/>
+      <c r="A74" s="45"/>
+      <c r="B74" s="74"/>
+      <c r="C74" s="74"/>
+      <c r="D74" s="74"/>
+      <c r="E74" s="74"/>
+      <c r="F74" s="74"/>
+      <c r="G74" s="74"/>
       <c r="H74" s="75"/>
-      <c r="I74" s="76"/>
-      <c r="J74" s="76"/>
-      <c r="K74" s="76"/>
-      <c r="L74" s="76"/>
-      <c r="M74" s="74"/>
-      <c r="N74" s="74"/>
-      <c r="O74" s="74"/>
+      <c r="I74" s="74"/>
+      <c r="J74" s="74"/>
+      <c r="K74" s="74"/>
+      <c r="L74" s="74"/>
+      <c r="M74" s="45"/>
+      <c r="N74" s="45"/>
+      <c r="O74" s="45"/>
+      <c r="P74" s="45"/>
+      <c r="Q74" s="45"/>
+      <c r="R74" s="45"/>
+      <c r="S74" s="45"/>
       <c r="V74" s="45"/>
       <c r="W74" s="45"/>
       <c r="X74" s="45"/>
@@ -6875,75 +6593,121 @@
       <c r="AB74" s="45"/>
       <c r="AC74" s="45"/>
       <c r="AD74" s="45"/>
-      <c r="AE74" s="45"/>
-      <c r="AI74" s="42"/>
-      <c r="AJ74" s="42"/>
-      <c r="AK74" s="54"/>
-    </row>
-    <row r="75" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A75" s="76"/>
-      <c r="B75"/>
-      <c r="C75" s="39"/>
-      <c r="D75" s="39"/>
-      <c r="H75"/>
-      <c r="I75"/>
-      <c r="J75"/>
-      <c r="K75" s="39"/>
-      <c r="L75" s="39"/>
-      <c r="M75" s="77"/>
-      <c r="N75" s="77"/>
-      <c r="O75" s="76"/>
-      <c r="P75" s="46"/>
-      <c r="Q75" s="46"/>
-      <c r="R75" s="46"/>
-      <c r="S75" s="46"/>
-      <c r="AI75" s="38"/>
-      <c r="AJ75" s="38"/>
-      <c r="AK75" s="50"/>
-    </row>
-    <row r="76" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A76" s="76"/>
-      <c r="B76"/>
-      <c r="C76" s="39"/>
-      <c r="D76" s="39"/>
-      <c r="H76" s="73"/>
-      <c r="I76"/>
-      <c r="J76"/>
-      <c r="K76" s="39"/>
-      <c r="L76" s="39"/>
-      <c r="M76" s="76"/>
-      <c r="N76" s="76"/>
-      <c r="O76" s="76"/>
-      <c r="P76" s="46"/>
-      <c r="Q76" s="46"/>
-      <c r="R76" s="46"/>
-      <c r="S76" s="46"/>
-      <c r="AI76" s="38"/>
-      <c r="AJ76" s="38"/>
-      <c r="AK76" s="50"/>
+      <c r="AI74"/>
+      <c r="AJ74" s="75"/>
+      <c r="AK74" s="39"/>
+      <c r="AL74" s="41"/>
+      <c r="AM74" s="45"/>
+      <c r="AN74" s="45"/>
+      <c r="AQ74"/>
+      <c r="AR74" s="75"/>
+      <c r="AS74" s="39"/>
+      <c r="AT74" s="41"/>
+      <c r="AU74" s="45"/>
+      <c r="AV74" s="45"/>
+    </row>
+    <row r="75" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="68"/>
+      <c r="B75" s="76"/>
+      <c r="C75" s="77"/>
+      <c r="D75" s="76"/>
+      <c r="E75" s="76"/>
+      <c r="F75" s="76"/>
+      <c r="G75" s="76"/>
+      <c r="H75" s="75"/>
+      <c r="I75" s="76"/>
+      <c r="J75" s="76"/>
+      <c r="K75" s="77"/>
+      <c r="L75" s="77"/>
+      <c r="M75" s="68"/>
+      <c r="N75" s="68"/>
+      <c r="O75" s="1"/>
+      <c r="P75" s="45"/>
+      <c r="Q75" s="45"/>
+      <c r="R75" s="45"/>
+      <c r="S75" s="45"/>
+      <c r="V75" s="45"/>
+      <c r="W75" s="45"/>
+      <c r="X75" s="45"/>
+      <c r="Y75" s="45"/>
+      <c r="Z75" s="45"/>
+      <c r="AA75" s="45"/>
+      <c r="AB75" s="45"/>
+      <c r="AC75" s="45"/>
+      <c r="AD75" s="45"/>
+      <c r="AE75" s="45"/>
+      <c r="AI75" s="42"/>
+      <c r="AJ75" s="42"/>
+      <c r="AK75" s="54"/>
+    </row>
+    <row r="76" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="74"/>
+      <c r="B76" s="76"/>
+      <c r="C76" s="76"/>
+      <c r="D76" s="76"/>
+      <c r="E76" s="76"/>
+      <c r="F76" s="76"/>
+      <c r="G76" s="76"/>
+      <c r="H76" s="75"/>
+      <c r="I76" s="76"/>
+      <c r="J76" s="76"/>
+      <c r="K76" s="76"/>
+      <c r="L76" s="76"/>
+      <c r="M76" s="74"/>
+      <c r="N76" s="74"/>
+      <c r="O76" s="74"/>
+      <c r="V76" s="45"/>
+      <c r="W76" s="45"/>
+      <c r="X76" s="45"/>
+      <c r="Y76" s="45"/>
+      <c r="Z76" s="45"/>
+      <c r="AA76" s="45"/>
+      <c r="AB76" s="45"/>
+      <c r="AC76" s="45"/>
+      <c r="AD76" s="45"/>
+      <c r="AE76" s="45"/>
+      <c r="AI76" s="42"/>
+      <c r="AJ76" s="42"/>
+      <c r="AK76" s="54"/>
     </row>
     <row r="77" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A77"/>
+      <c r="A77" s="76"/>
       <c r="B77"/>
       <c r="C77" s="39"/>
       <c r="D77" s="39"/>
+      <c r="H77"/>
       <c r="I77"/>
       <c r="J77"/>
       <c r="K77" s="39"/>
       <c r="L77" s="39"/>
+      <c r="M77" s="77"/>
+      <c r="N77" s="77"/>
+      <c r="O77" s="76"/>
+      <c r="P77" s="46"/>
+      <c r="Q77" s="46"/>
+      <c r="R77" s="46"/>
+      <c r="S77" s="46"/>
       <c r="AI77" s="38"/>
       <c r="AJ77" s="38"/>
       <c r="AK77" s="50"/>
     </row>
     <row r="78" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A78"/>
+      <c r="A78" s="76"/>
       <c r="B78"/>
       <c r="C78" s="39"/>
       <c r="D78" s="39"/>
+      <c r="H78" s="73"/>
       <c r="I78"/>
       <c r="J78"/>
       <c r="K78" s="39"/>
       <c r="L78" s="39"/>
+      <c r="M78" s="76"/>
+      <c r="N78" s="76"/>
+      <c r="O78" s="76"/>
+      <c r="P78" s="46"/>
+      <c r="Q78" s="46"/>
+      <c r="R78" s="46"/>
+      <c r="S78" s="46"/>
       <c r="AI78" s="38"/>
       <c r="AJ78" s="38"/>
       <c r="AK78" s="50"/>
@@ -6953,12 +6717,10 @@
       <c r="B79"/>
       <c r="C79" s="39"/>
       <c r="D79" s="39"/>
-      <c r="H79" s="46"/>
       <c r="I79"/>
       <c r="J79"/>
       <c r="K79" s="39"/>
       <c r="L79" s="39"/>
-      <c r="O79" s="46"/>
       <c r="AI79" s="38"/>
       <c r="AJ79" s="38"/>
       <c r="AK79" s="50"/>
@@ -6968,12 +6730,10 @@
       <c r="B80"/>
       <c r="C80" s="39"/>
       <c r="D80" s="39"/>
-      <c r="H80" s="46"/>
       <c r="I80"/>
       <c r="J80"/>
       <c r="K80" s="39"/>
       <c r="L80" s="39"/>
-      <c r="O80" s="46"/>
       <c r="AI80" s="38"/>
       <c r="AJ80" s="38"/>
       <c r="AK80" s="50"/>
@@ -7178,10 +6938,12 @@
       <c r="B94"/>
       <c r="C94" s="39"/>
       <c r="D94" s="39"/>
+      <c r="H94" s="46"/>
       <c r="I94"/>
       <c r="J94"/>
       <c r="K94" s="39"/>
       <c r="L94" s="39"/>
+      <c r="O94" s="46"/>
       <c r="AI94" s="38"/>
       <c r="AJ94" s="38"/>
       <c r="AK94" s="50"/>
@@ -7191,10 +6953,12 @@
       <c r="B95"/>
       <c r="C95" s="39"/>
       <c r="D95" s="39"/>
+      <c r="H95" s="46"/>
       <c r="I95"/>
       <c r="J95"/>
       <c r="K95" s="39"/>
       <c r="L95" s="39"/>
+      <c r="O95" s="46"/>
       <c r="AI95" s="38"/>
       <c r="AJ95" s="38"/>
       <c r="AK95" s="50"/>
@@ -7552,22 +7316,38 @@
     </row>
     <row r="123" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A123"/>
+      <c r="B123"/>
+      <c r="C123" s="39"/>
+      <c r="D123" s="39"/>
+      <c r="I123"/>
+      <c r="J123"/>
+      <c r="K123" s="39"/>
+      <c r="L123" s="39"/>
       <c r="AI123" s="38"/>
       <c r="AJ123" s="38"/>
       <c r="AK123" s="50"/>
     </row>
     <row r="124" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A124"/>
+      <c r="B124"/>
+      <c r="C124" s="39"/>
+      <c r="D124" s="39"/>
+      <c r="I124"/>
+      <c r="J124"/>
+      <c r="K124" s="39"/>
+      <c r="L124" s="39"/>
       <c r="AI124" s="38"/>
       <c r="AJ124" s="38"/>
       <c r="AK124" s="50"/>
     </row>
     <row r="125" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A125"/>
       <c r="AI125" s="38"/>
       <c r="AJ125" s="38"/>
       <c r="AK125" s="50"/>
     </row>
     <row r="126" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A126"/>
       <c r="AI126" s="38"/>
       <c r="AJ126" s="38"/>
       <c r="AK126" s="50"/>
@@ -7681,13 +7461,23 @@
       <c r="AI148" s="38"/>
       <c r="AJ148" s="38"/>
       <c r="AK148" s="50"/>
+    </row>
+    <row r="149" spans="35:37" x14ac:dyDescent="0.25">
+      <c r="AI149" s="38"/>
+      <c r="AJ149" s="38"/>
+      <c r="AK149" s="50"/>
+    </row>
+    <row r="150" spans="35:37" x14ac:dyDescent="0.25">
+      <c r="AI150" s="38"/>
+      <c r="AJ150" s="38"/>
+      <c r="AK150" s="50"/>
     </row>
   </sheetData>
   <phoneticPr fontId="24" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="C36" formula="1"/>
+    <ignoredError sqref="B31" formula="1"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId2"/>
 </worksheet>

--- a/SubRES_TMPL/SubRES_NewTechs.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D357DC3-BD0F-4DF7-A313-1E7E2B8A8D00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1237C312-93F3-44F5-817B-1F5D780F271F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5513,7 +5513,7 @@
       <c r="R30" s="117"/>
       <c r="S30" s="115"/>
       <c r="V30" s="46" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="X30" s="46" t="s">
         <v>157</v>

--- a/SubRES_TMPL/SubRES_NewTechs.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1237C312-93F3-44F5-817B-1F5D780F271F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26D917AE-38CE-453F-968C-A0382A2927F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PRI_Sector_Fuels" sheetId="6" r:id="rId1"/>
@@ -4670,7 +4670,7 @@
       <c r="T19" s="82"/>
       <c r="U19" s="82"/>
       <c r="V19" s="83" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="W19" s="83"/>
       <c r="X19" s="84" t="s">
@@ -4966,7 +4966,7 @@
       <c r="R23" s="115"/>
       <c r="S23" s="115"/>
       <c r="V23" s="60" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="W23" s="60"/>
       <c r="X23" s="61" t="s">

--- a/SubRES_TMPL/SubRES_NewTechs.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26D917AE-38CE-453F-968C-A0382A2927F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3A652E6-1773-48BA-A16E-E767465E45CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4087,7 +4087,8 @@
     <col min="10" max="10" width="12.77734375" style="45" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="8.21875" style="45" customWidth="1"/>
     <col min="13" max="13" width="10.21875" style="45" bestFit="1" customWidth="1"/>
-    <col min="14" max="19" width="8.21875" style="45" customWidth="1"/>
+    <col min="14" max="14" width="16.21875" style="45" bestFit="1" customWidth="1"/>
+    <col min="15" max="19" width="8.21875" style="45" customWidth="1"/>
     <col min="20" max="21" width="8.21875" style="46" customWidth="1"/>
     <col min="22" max="22" width="12.77734375" style="45" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="7.21875" style="45" customWidth="1"/>
@@ -4664,7 +4665,7 @@
         <v>0.25</v>
       </c>
       <c r="R19" s="110">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="S19" s="109"/>
       <c r="T19" s="82"/>
@@ -4884,7 +4885,7 @@
         <v>0.25</v>
       </c>
       <c r="R22" s="116">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="S22" s="115"/>
       <c r="V22" s="60" t="s">

--- a/SubRES_TMPL/SubRES_NewTechs.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3A652E6-1773-48BA-A16E-E767465E45CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37320A23-5F55-45FA-B0A8-E9374800D4DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1554,7 +1554,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="157">
   <si>
     <t>~FI_T</t>
   </si>
@@ -1896,9 +1896,6 @@
   </si>
   <si>
     <t>START</t>
-  </si>
-  <si>
-    <t>Bound on new capacity</t>
   </si>
   <si>
     <t>Share-I~UP~UP~2035</t>
@@ -3242,7 +3239,7 @@
         <v>67</v>
       </c>
       <c r="Q6" s="39" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="R6" s="39" t="s">
         <v>58</v>
@@ -3268,7 +3265,7 @@
         <v>72</v>
       </c>
       <c r="Q7" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R7" s="12" t="s">
         <v>58</v>
@@ -3292,10 +3289,10 @@
       </c>
       <c r="O8" s="37"/>
       <c r="P8" s="37" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q8" s="37" t="s">
         <v>120</v>
-      </c>
-      <c r="Q8" s="37" t="s">
-        <v>121</v>
       </c>
       <c r="R8" s="37" t="s">
         <v>58</v>
@@ -3653,10 +3650,10 @@
         <v>64</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="R19" s="38" t="s">
         <v>58</v>
@@ -3699,10 +3696,10 @@
       </c>
       <c r="O20" s="14"/>
       <c r="P20" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q20" s="14" t="s">
         <v>123</v>
-      </c>
-      <c r="Q20" s="14" t="s">
-        <v>124</v>
       </c>
       <c r="R20" s="38" t="s">
         <v>58</v>
@@ -4238,10 +4235,10 @@
         <v>69</v>
       </c>
       <c r="X5" s="45" t="s">
+        <v>130</v>
+      </c>
+      <c r="Y5" s="72" t="s">
         <v>131</v>
-      </c>
-      <c r="Y5" s="72" t="s">
-        <v>132</v>
       </c>
       <c r="Z5" s="72" t="s">
         <v>58</v>
@@ -4261,10 +4258,10 @@
         <v>69</v>
       </c>
       <c r="X6" s="45" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Y6" s="72" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="Z6" s="72" t="s">
         <v>58</v>
@@ -4284,10 +4281,10 @@
         <v>69</v>
       </c>
       <c r="X7" s="45" t="s">
+        <v>134</v>
+      </c>
+      <c r="Y7" s="45" t="s">
         <v>135</v>
-      </c>
-      <c r="Y7" s="45" t="s">
-        <v>136</v>
       </c>
       <c r="Z7" s="72" t="s">
         <v>58</v>
@@ -4302,10 +4299,10 @@
       </c>
       <c r="W8" s="50"/>
       <c r="X8" s="50" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Y8" s="50" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="Z8" s="72" t="s">
         <v>58</v>
@@ -4318,14 +4315,14 @@
     </row>
     <row r="9" spans="2:51" x14ac:dyDescent="0.25">
       <c r="V9" s="50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="W9" s="50"/>
       <c r="X9" s="50" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Y9" s="50" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Z9" s="72" t="s">
         <v>58</v>
@@ -4422,19 +4419,19 @@
         <v>112</v>
       </c>
       <c r="O16" s="59" t="s">
+        <v>114</v>
+      </c>
+      <c r="P16" s="59" t="s">
         <v>115</v>
       </c>
-      <c r="P16" s="59" t="s">
+      <c r="Q16" s="59" t="s">
         <v>116</v>
       </c>
-      <c r="Q16" s="59" t="s">
+      <c r="R16" s="59" t="s">
         <v>117</v>
       </c>
-      <c r="R16" s="59" t="s">
-        <v>118</v>
-      </c>
       <c r="S16" s="59" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="V16" s="51" t="s">
         <v>15</v>
@@ -4520,20 +4517,20 @@
       <c r="N17" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="O17" s="33" t="s">
-        <v>114</v>
-      </c>
-      <c r="P17" s="33" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q17" s="33" t="s">
-        <v>114</v>
-      </c>
-      <c r="R17" s="70" t="s">
-        <v>114</v>
+      <c r="O17" s="32" t="s">
+        <v>85</v>
+      </c>
+      <c r="P17" s="32" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q17" s="32" t="s">
+        <v>85</v>
+      </c>
+      <c r="R17" s="32" t="s">
+        <v>85</v>
       </c>
       <c r="S17" s="70" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="V17" s="31" t="s">
         <v>50</v>
@@ -4585,7 +4582,7 @@
         <v>111</v>
       </c>
       <c r="K18" s="35" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L18" s="36"/>
       <c r="M18" s="36" t="s">
@@ -4671,14 +4668,14 @@
       <c r="T19" s="82"/>
       <c r="U19" s="82"/>
       <c r="V19" s="83" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="W19" s="83"/>
       <c r="X19" s="84" t="s">
         <v>66</v>
       </c>
       <c r="Y19" s="85" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Z19" s="80" t="s">
         <v>58</v>
@@ -4742,14 +4739,14 @@
       <c r="T20" s="89"/>
       <c r="U20" s="89"/>
       <c r="V20" s="79" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="W20" s="79"/>
       <c r="X20" s="90" t="s">
         <v>94</v>
       </c>
       <c r="Y20" s="91" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="Z20" s="72" t="s">
         <v>58</v>
@@ -4811,14 +4808,14 @@
       <c r="T21" s="82"/>
       <c r="U21" s="82"/>
       <c r="V21" s="83" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="W21" s="83"/>
       <c r="X21" s="84" t="s">
         <v>95</v>
       </c>
       <c r="Y21" s="85" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="Z21" s="80" t="s">
         <v>58</v>
@@ -4889,14 +4886,14 @@
       </c>
       <c r="S22" s="115"/>
       <c r="V22" s="60" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="W22" s="60"/>
       <c r="X22" s="61" t="s">
         <v>96</v>
       </c>
       <c r="Y22" s="62" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="Z22" s="45" t="s">
         <v>58</v>
@@ -4967,14 +4964,14 @@
       <c r="R23" s="115"/>
       <c r="S23" s="115"/>
       <c r="V23" s="60" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="W23" s="60"/>
       <c r="X23" s="61" t="s">
         <v>97</v>
       </c>
       <c r="Y23" s="62" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="Z23" s="45" t="s">
         <v>58</v>
@@ -5011,7 +5008,7 @@
         <v>WIND</v>
       </c>
       <c r="D24" s="50" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E24" s="115">
         <v>2030</v>
@@ -5047,14 +5044,14 @@
         <v>0.2</v>
       </c>
       <c r="V24" s="60" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="W24" s="60"/>
       <c r="X24" s="61" t="s">
         <v>65</v>
       </c>
       <c r="Y24" s="62" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Z24" s="45" t="s">
         <v>58</v>
@@ -5091,7 +5088,7 @@
         <v>SOLAR</v>
       </c>
       <c r="D25" s="50" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E25" s="115">
         <v>2030</v>
@@ -5134,7 +5131,7 @@
         <v>89</v>
       </c>
       <c r="Y25" s="62" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Z25" s="45" t="s">
         <v>58</v>
@@ -5213,7 +5210,7 @@
         <v>90</v>
       </c>
       <c r="Y26" s="91" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Z26" s="72" t="s">
         <v>58</v>
@@ -5285,10 +5282,10 @@
       </c>
       <c r="W27" s="60"/>
       <c r="X27" s="61" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Y27" s="62" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="Z27" s="45" t="s">
         <v>58</v>
@@ -5321,7 +5318,7 @@
         <v>DECPOWER</v>
       </c>
       <c r="C28" s="93" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D28" s="93" t="str">
         <f>X8</f>
@@ -5363,10 +5360,10 @@
       </c>
       <c r="W28" s="96"/>
       <c r="X28" s="97" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Y28" s="98" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="Z28" s="95" t="s">
         <v>58</v>
@@ -5399,7 +5396,7 @@
         <v>DECPOWER</v>
       </c>
       <c r="C29" s="93" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D29" s="93" t="str">
         <f>X8</f>
@@ -5440,10 +5437,10 @@
         <v>69</v>
       </c>
       <c r="X29" s="94" t="s">
+        <v>153</v>
+      </c>
+      <c r="Y29" s="94" t="s">
         <v>154</v>
-      </c>
-      <c r="Y29" s="94" t="s">
-        <v>155</v>
       </c>
       <c r="Z29" s="95" t="s">
         <v>58</v>
@@ -5480,7 +5477,7 @@
         <v>68</v>
       </c>
       <c r="D30" s="50" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E30" s="115">
         <v>2030</v>
@@ -5514,13 +5511,13 @@
       <c r="R30" s="117"/>
       <c r="S30" s="115"/>
       <c r="V30" s="46" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="X30" s="46" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y30" s="46" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="Z30" s="95" t="s">
         <v>58</v>
@@ -5554,7 +5551,7 @@
         <v>DECPOWER</v>
       </c>
       <c r="C31" s="95" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D31" s="93" t="str">
         <f>X8</f>

--- a/SubRES_TMPL/SubRES_NewTechs.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37320A23-5F55-45FA-B0A8-E9374800D4DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEA7030D-D1A6-425A-9A27-824493520470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1554,7 +1554,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="163">
   <si>
     <t>~FI_T</t>
   </si>
@@ -2025,6 +2025,24 @@
   </si>
   <si>
     <t>DECTHT</t>
+  </si>
+  <si>
+    <t>BHEAT</t>
+  </si>
+  <si>
+    <t>FHEAT</t>
+  </si>
+  <si>
+    <t>Process heat using boiler</t>
+  </si>
+  <si>
+    <t>Process heat using furnace</t>
+  </si>
+  <si>
+    <t>ELCTHT</t>
+  </si>
+  <si>
+    <t>MANHEAT using Electricity</t>
   </si>
 </sst>
 </file>
@@ -4334,12 +4352,38 @@
       <c r="AD9" s="50"/>
     </row>
     <row r="10" spans="2:51" x14ac:dyDescent="0.25">
-      <c r="Z10" s="72"/>
-      <c r="AB10" s="72"/>
+      <c r="V10" s="45" t="s">
+        <v>138</v>
+      </c>
+      <c r="X10" s="45" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y10" s="45" t="s">
+        <v>159</v>
+      </c>
+      <c r="Z10" s="72" t="s">
+        <v>58</v>
+      </c>
+      <c r="AB10" s="72" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="11" spans="2:51" x14ac:dyDescent="0.25">
-      <c r="Z11" s="72"/>
-      <c r="AB11" s="72"/>
+      <c r="V11" s="45" t="s">
+        <v>138</v>
+      </c>
+      <c r="X11" s="45" t="s">
+        <v>158</v>
+      </c>
+      <c r="Y11" s="45" t="s">
+        <v>160</v>
+      </c>
+      <c r="Z11" s="72" t="s">
+        <v>58</v>
+      </c>
+      <c r="AB11" s="72" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="13" spans="2:51" x14ac:dyDescent="0.25">
       <c r="Z13" s="72"/>
@@ -4621,8 +4665,9 @@
       <c r="C19" s="80" t="s">
         <v>69</v>
       </c>
-      <c r="D19" s="81" t="s">
-        <v>107</v>
+      <c r="D19" s="81" t="str">
+        <f>X11</f>
+        <v>FHEAT</v>
       </c>
       <c r="E19" s="109">
         <v>2030</v>
@@ -4668,7 +4713,7 @@
       <c r="T19" s="82"/>
       <c r="U19" s="82"/>
       <c r="V19" s="83" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="W19" s="83"/>
       <c r="X19" s="84" t="s">
@@ -4771,8 +4816,9 @@
       <c r="C21" s="80" t="s">
         <v>69</v>
       </c>
-      <c r="D21" s="81" t="s">
-        <v>107</v>
+      <c r="D21" s="81" t="str">
+        <f>X10</f>
+        <v>BHEAT</v>
       </c>
       <c r="E21" s="109">
         <v>2030</v>
@@ -4964,7 +5010,7 @@
       <c r="R23" s="115"/>
       <c r="S23" s="115"/>
       <c r="V23" s="60" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="W23" s="60"/>
       <c r="X23" s="61" t="s">
@@ -5588,11 +5634,25 @@
       <c r="Q31" s="120"/>
       <c r="R31" s="121"/>
       <c r="S31" s="118"/>
-      <c r="V31" s="46"/>
+      <c r="V31" s="46" t="s">
+        <v>127</v>
+      </c>
       <c r="W31" s="46"/>
-      <c r="X31" s="46"/>
-      <c r="Y31" s="46"/>
-      <c r="Z31" s="95"/>
+      <c r="X31" s="46" t="s">
+        <v>161</v>
+      </c>
+      <c r="Y31" s="46" t="s">
+        <v>162</v>
+      </c>
+      <c r="Z31" s="95" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA31" s="95" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB31" s="94" t="s">
+        <v>88</v>
+      </c>
       <c r="AD31" s="46"/>
       <c r="AI31" s="99"/>
       <c r="AJ31" s="99"/>
@@ -5731,19 +5791,48 @@
       <c r="AW33" s="95"/>
     </row>
     <row r="34" spans="1:49" s="94" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="93"/>
-      <c r="C34" s="95"/>
-      <c r="D34" s="93"/>
-      <c r="E34" s="124"/>
-      <c r="F34" s="125"/>
-      <c r="G34" s="125"/>
-      <c r="M34" s="126"/>
-      <c r="N34" s="126"/>
-      <c r="O34" s="125"/>
-      <c r="P34" s="125"/>
-      <c r="Q34" s="125"/>
-      <c r="R34" s="126"/>
-      <c r="S34" s="124"/>
+      <c r="B34" s="93" t="str">
+        <f>X31</f>
+        <v>ELCTHT</v>
+      </c>
+      <c r="C34" s="95" t="str">
+        <f>X10</f>
+        <v>BHEAT</v>
+      </c>
+      <c r="D34" s="93" t="s">
+        <v>107</v>
+      </c>
+      <c r="E34" s="118">
+        <v>2030</v>
+      </c>
+      <c r="F34" s="120">
+        <v>1</v>
+      </c>
+      <c r="G34" s="120">
+        <v>1</v>
+      </c>
+      <c r="H34" s="119">
+        <v>100</v>
+      </c>
+      <c r="I34" s="119">
+        <v>0</v>
+      </c>
+      <c r="J34" s="119">
+        <v>0</v>
+      </c>
+      <c r="K34" s="119">
+        <v>0</v>
+      </c>
+      <c r="L34" s="119">
+        <v>0</v>
+      </c>
+      <c r="M34" s="121"/>
+      <c r="N34" s="121"/>
+      <c r="O34" s="120"/>
+      <c r="P34" s="120"/>
+      <c r="Q34" s="120"/>
+      <c r="R34" s="121"/>
+      <c r="S34" s="118"/>
       <c r="AD34" s="46"/>
       <c r="AI34" s="99"/>
       <c r="AJ34" s="99"/>
@@ -5762,19 +5851,48 @@
       <c r="AW34" s="95"/>
     </row>
     <row r="35" spans="1:49" s="94" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="93"/>
-      <c r="C35" s="95"/>
-      <c r="D35" s="93"/>
-      <c r="E35" s="124"/>
-      <c r="F35" s="125"/>
-      <c r="G35" s="125"/>
-      <c r="M35" s="126"/>
-      <c r="N35" s="126"/>
-      <c r="O35" s="125"/>
-      <c r="P35" s="125"/>
-      <c r="Q35" s="125"/>
-      <c r="R35" s="126"/>
-      <c r="S35" s="124"/>
+      <c r="B35" s="93" t="str">
+        <f>X31</f>
+        <v>ELCTHT</v>
+      </c>
+      <c r="C35" s="95" t="str">
+        <f>X11</f>
+        <v>FHEAT</v>
+      </c>
+      <c r="D35" s="93" t="s">
+        <v>107</v>
+      </c>
+      <c r="E35" s="118">
+        <v>2030</v>
+      </c>
+      <c r="F35" s="120">
+        <v>1</v>
+      </c>
+      <c r="G35" s="120">
+        <v>1</v>
+      </c>
+      <c r="H35" s="119">
+        <v>100</v>
+      </c>
+      <c r="I35" s="119">
+        <v>0</v>
+      </c>
+      <c r="J35" s="119">
+        <v>0</v>
+      </c>
+      <c r="K35" s="119">
+        <v>0</v>
+      </c>
+      <c r="L35" s="119">
+        <v>0</v>
+      </c>
+      <c r="M35" s="121"/>
+      <c r="N35" s="121"/>
+      <c r="O35" s="120"/>
+      <c r="P35" s="120"/>
+      <c r="Q35" s="120"/>
+      <c r="R35" s="121"/>
+      <c r="S35" s="118"/>
       <c r="AD35" s="95"/>
       <c r="AI35" s="99"/>
       <c r="AJ35" s="99"/>

--- a/SubRES_TMPL/SubRES_NewTechs.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEA7030D-D1A6-425A-9A27-824493520470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77ECF40F-F9EA-4C77-AFCB-7248A511BBB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PRI_Sector_Fuels" sheetId="6" r:id="rId1"/>
@@ -2042,7 +2042,7 @@
     <t>ELCTHT</t>
   </si>
   <si>
-    <t>MANHEAT using Electricity</t>
+    <t>MANHEAT using Electricity aggrigator</t>
   </si>
 </sst>
 </file>

--- a/SubRES_TMPL/SubRES_NewTechs.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77ECF40F-F9EA-4C77-AFCB-7248A511BBB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PRI_Sector_Fuels" sheetId="6" r:id="rId1"/>

--- a/SubRES_TMPL/SubRES_NewTechs.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77ECF40F-F9EA-4C77-AFCB-7248A511BBB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{417F5034-3B67-4EFF-BD1E-0C9AB5E63F58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PRI_Sector_Fuels" sheetId="6" r:id="rId1"/>
@@ -1554,7 +1554,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="157">
   <si>
     <t>~FI_T</t>
   </si>
@@ -2025,24 +2025,6 @@
   </si>
   <si>
     <t>DECTHT</t>
-  </si>
-  <si>
-    <t>BHEAT</t>
-  </si>
-  <si>
-    <t>FHEAT</t>
-  </si>
-  <si>
-    <t>Process heat using boiler</t>
-  </si>
-  <si>
-    <t>Process heat using furnace</t>
-  </si>
-  <si>
-    <t>ELCTHT</t>
-  </si>
-  <si>
-    <t>MANHEAT using Electricity aggrigator</t>
   </si>
 </sst>
 </file>
@@ -4352,35 +4334,13 @@
       <c r="AD9" s="50"/>
     </row>
     <row r="10" spans="2:51" x14ac:dyDescent="0.25">
-      <c r="V10" s="45" t="s">
-        <v>138</v>
-      </c>
-      <c r="X10" s="45" t="s">
-        <v>157</v>
-      </c>
-      <c r="Y10" s="45" t="s">
-        <v>159</v>
-      </c>
-      <c r="Z10" s="72" t="s">
-        <v>58</v>
-      </c>
+      <c r="Z10" s="72"/>
       <c r="AB10" s="72" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="11" spans="2:51" x14ac:dyDescent="0.25">
-      <c r="V11" s="45" t="s">
-        <v>138</v>
-      </c>
-      <c r="X11" s="45" t="s">
-        <v>158</v>
-      </c>
-      <c r="Y11" s="45" t="s">
-        <v>160</v>
-      </c>
-      <c r="Z11" s="72" t="s">
-        <v>58</v>
-      </c>
+      <c r="Z11" s="72"/>
       <c r="AB11" s="72" t="s">
         <v>88</v>
       </c>
@@ -4665,9 +4625,8 @@
       <c r="C19" s="80" t="s">
         <v>69</v>
       </c>
-      <c r="D19" s="81" t="str">
-        <f>X11</f>
-        <v>FHEAT</v>
+      <c r="D19" s="81" t="s">
+        <v>107</v>
       </c>
       <c r="E19" s="109">
         <v>2030</v>
@@ -4713,7 +4672,7 @@
       <c r="T19" s="82"/>
       <c r="U19" s="82"/>
       <c r="V19" s="83" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="W19" s="83"/>
       <c r="X19" s="84" t="s">
@@ -4816,9 +4775,8 @@
       <c r="C21" s="80" t="s">
         <v>69</v>
       </c>
-      <c r="D21" s="81" t="str">
-        <f>X10</f>
-        <v>BHEAT</v>
+      <c r="D21" s="81" t="s">
+        <v>107</v>
       </c>
       <c r="E21" s="109">
         <v>2030</v>
@@ -5010,7 +4968,7 @@
       <c r="R23" s="115"/>
       <c r="S23" s="115"/>
       <c r="V23" s="60" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="W23" s="60"/>
       <c r="X23" s="61" t="s">
@@ -5634,25 +5592,12 @@
       <c r="Q31" s="120"/>
       <c r="R31" s="121"/>
       <c r="S31" s="118"/>
-      <c r="V31" s="46" t="s">
-        <v>127</v>
-      </c>
+      <c r="V31" s="46"/>
       <c r="W31" s="46"/>
-      <c r="X31" s="46" t="s">
-        <v>161</v>
-      </c>
-      <c r="Y31" s="46" t="s">
-        <v>162</v>
-      </c>
-      <c r="Z31" s="95" t="s">
-        <v>58</v>
-      </c>
-      <c r="AA31" s="95" t="s">
-        <v>87</v>
-      </c>
-      <c r="AB31" s="94" t="s">
-        <v>88</v>
-      </c>
+      <c r="X31" s="46"/>
+      <c r="Y31" s="46"/>
+      <c r="Z31" s="95"/>
+      <c r="AA31" s="95"/>
       <c r="AD31" s="46"/>
       <c r="AI31" s="99"/>
       <c r="AJ31" s="99"/>
@@ -5791,41 +5736,17 @@
       <c r="AW33" s="95"/>
     </row>
     <row r="34" spans="1:49" s="94" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="93" t="str">
-        <f>X31</f>
-        <v>ELCTHT</v>
-      </c>
-      <c r="C34" s="95" t="str">
-        <f>X10</f>
-        <v>BHEAT</v>
-      </c>
-      <c r="D34" s="93" t="s">
-        <v>107</v>
-      </c>
-      <c r="E34" s="118">
-        <v>2030</v>
-      </c>
-      <c r="F34" s="120">
-        <v>1</v>
-      </c>
-      <c r="G34" s="120">
-        <v>1</v>
-      </c>
-      <c r="H34" s="119">
-        <v>100</v>
-      </c>
-      <c r="I34" s="119">
-        <v>0</v>
-      </c>
-      <c r="J34" s="119">
-        <v>0</v>
-      </c>
-      <c r="K34" s="119">
-        <v>0</v>
-      </c>
-      <c r="L34" s="119">
-        <v>0</v>
-      </c>
+      <c r="B34" s="93"/>
+      <c r="C34" s="95"/>
+      <c r="D34" s="93"/>
+      <c r="E34" s="118"/>
+      <c r="F34" s="120"/>
+      <c r="G34" s="120"/>
+      <c r="H34" s="119"/>
+      <c r="I34" s="119"/>
+      <c r="J34" s="119"/>
+      <c r="K34" s="119"/>
+      <c r="L34" s="119"/>
       <c r="M34" s="121"/>
       <c r="N34" s="121"/>
       <c r="O34" s="120"/>
@@ -5851,41 +5772,17 @@
       <c r="AW34" s="95"/>
     </row>
     <row r="35" spans="1:49" s="94" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="93" t="str">
-        <f>X31</f>
-        <v>ELCTHT</v>
-      </c>
-      <c r="C35" s="95" t="str">
-        <f>X11</f>
-        <v>FHEAT</v>
-      </c>
-      <c r="D35" s="93" t="s">
-        <v>107</v>
-      </c>
-      <c r="E35" s="118">
-        <v>2030</v>
-      </c>
-      <c r="F35" s="120">
-        <v>1</v>
-      </c>
-      <c r="G35" s="120">
-        <v>1</v>
-      </c>
-      <c r="H35" s="119">
-        <v>100</v>
-      </c>
-      <c r="I35" s="119">
-        <v>0</v>
-      </c>
-      <c r="J35" s="119">
-        <v>0</v>
-      </c>
-      <c r="K35" s="119">
-        <v>0</v>
-      </c>
-      <c r="L35" s="119">
-        <v>0</v>
-      </c>
+      <c r="B35" s="93"/>
+      <c r="C35" s="95"/>
+      <c r="D35" s="93"/>
+      <c r="E35" s="118"/>
+      <c r="F35" s="120"/>
+      <c r="G35" s="120"/>
+      <c r="H35" s="119"/>
+      <c r="I35" s="119"/>
+      <c r="J35" s="119"/>
+      <c r="K35" s="119"/>
+      <c r="L35" s="119"/>
       <c r="M35" s="121"/>
       <c r="N35" s="121"/>
       <c r="O35" s="120"/>

--- a/SubRES_TMPL/SubRES_NewTechs.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{417F5034-3B67-4EFF-BD1E-0C9AB5E63F58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8629F90D-DFF4-47C8-BA52-1EF25C168459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1554,7 +1554,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="157">
   <si>
     <t>~FI_T</t>
   </si>
@@ -4335,15 +4335,11 @@
     </row>
     <row r="10" spans="2:51" x14ac:dyDescent="0.25">
       <c r="Z10" s="72"/>
-      <c r="AB10" s="72" t="s">
-        <v>88</v>
-      </c>
+      <c r="AB10" s="72"/>
     </row>
     <row r="11" spans="2:51" x14ac:dyDescent="0.25">
       <c r="Z11" s="72"/>
-      <c r="AB11" s="72" t="s">
-        <v>88</v>
-      </c>
+      <c r="AB11" s="72"/>
     </row>
     <row r="13" spans="2:51" x14ac:dyDescent="0.25">
       <c r="Z13" s="72"/>

--- a/SubRES_TMPL/SubRES_NewTechs.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8629F90D-DFF4-47C8-BA52-1EF25C168459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C22E79A6-D2A3-4DB0-B5C9-D1AA8C67E47C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PRI_Sector_Fuels" sheetId="6" r:id="rId1"/>
@@ -5433,16 +5433,17 @@
       <c r="Q29" s="120"/>
       <c r="R29" s="121"/>
       <c r="S29" s="118"/>
-      <c r="V29" s="94" t="s">
+      <c r="V29" s="46" t="s">
         <v>69</v>
       </c>
-      <c r="X29" s="94" t="s">
+      <c r="W29" s="46"/>
+      <c r="X29" s="46" t="s">
         <v>153</v>
       </c>
-      <c r="Y29" s="94" t="s">
+      <c r="Y29" s="46" t="s">
         <v>154</v>
       </c>
-      <c r="Z29" s="95" t="s">
+      <c r="Z29" s="45" t="s">
         <v>58</v>
       </c>
       <c r="AA29" s="95" t="s">
@@ -5624,7 +5625,7 @@
         <v>69</v>
       </c>
       <c r="E32" s="118">
-        <v>2030</v>
+        <v>2022</v>
       </c>
       <c r="F32" s="120">
         <v>1</v>

--- a/SubRES_TMPL/SubRES_NewTechs.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C22E79A6-D2A3-4DB0-B5C9-D1AA8C67E47C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22E9682F-63F2-4C7D-912C-268758273409}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1554,7 +1554,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="155">
   <si>
     <t>~FI_T</t>
   </si>
@@ -2013,12 +2013,6 @@
   </si>
   <si>
     <t>DECRHEAT</t>
-  </si>
-  <si>
-    <t>ELC_AGG</t>
-  </si>
-  <si>
-    <t>Electricity aggrigator</t>
   </si>
   <si>
     <t>Bioheat and CSP heat aggrigator</t>
@@ -4069,7 +4063,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3360854E-4C4D-467D-BD8A-32231E61C6CE}">
-  <dimension ref="A1:AY150"/>
+  <dimension ref="A1:AY149"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" style="45" customWidth="1"/>
@@ -4258,7 +4252,7 @@
         <v>69</v>
       </c>
       <c r="X6" s="45" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Y6" s="72" t="s">
         <v>132</v>
@@ -4618,8 +4612,9 @@
         <f>X19</f>
         <v>Furnace</v>
       </c>
-      <c r="C19" s="80" t="s">
-        <v>69</v>
+      <c r="C19" s="81" t="str">
+        <f>X8</f>
+        <v>DECELC</v>
       </c>
       <c r="D19" s="81" t="s">
         <v>107</v>
@@ -4768,8 +4763,9 @@
         <f>X23</f>
         <v>ELCBoiler</v>
       </c>
-      <c r="C21" s="80" t="s">
-        <v>69</v>
+      <c r="C21" s="81" t="str">
+        <f>X8</f>
+        <v>DECELC</v>
       </c>
       <c r="D21" s="81" t="s">
         <v>107</v>
@@ -5434,16 +5430,16 @@
       <c r="R29" s="121"/>
       <c r="S29" s="118"/>
       <c r="V29" s="46" t="s">
-        <v>69</v>
+        <v>127</v>
       </c>
       <c r="W29" s="46"/>
       <c r="X29" s="46" t="s">
+        <v>154</v>
+      </c>
+      <c r="Y29" s="46" t="s">
         <v>153</v>
       </c>
-      <c r="Y29" s="46" t="s">
-        <v>154</v>
-      </c>
-      <c r="Z29" s="45" t="s">
+      <c r="Z29" s="95" t="s">
         <v>58</v>
       </c>
       <c r="AA29" s="95" t="s">
@@ -5511,24 +5507,9 @@
       <c r="Q30" s="116"/>
       <c r="R30" s="117"/>
       <c r="S30" s="115"/>
-      <c r="V30" s="46" t="s">
-        <v>127</v>
-      </c>
-      <c r="X30" s="46" t="s">
-        <v>156</v>
-      </c>
-      <c r="Y30" s="46" t="s">
-        <v>155</v>
-      </c>
-      <c r="Z30" s="95" t="s">
-        <v>58</v>
-      </c>
-      <c r="AA30" s="95" t="s">
-        <v>87</v>
-      </c>
-      <c r="AB30" s="94" t="s">
-        <v>88</v>
-      </c>
+      <c r="Z30" s="95"/>
+      <c r="AA30" s="95"/>
+      <c r="AB30" s="94"/>
       <c r="AC30" s="94"/>
       <c r="AI30" s="38"/>
       <c r="AJ30" s="38"/>
@@ -5589,12 +5570,6 @@
       <c r="Q31" s="120"/>
       <c r="R31" s="121"/>
       <c r="S31" s="118"/>
-      <c r="V31" s="46"/>
-      <c r="W31" s="46"/>
-      <c r="X31" s="46"/>
-      <c r="Y31" s="46"/>
-      <c r="Z31" s="95"/>
-      <c r="AA31" s="95"/>
       <c r="AD31" s="46"/>
       <c r="AI31" s="99"/>
       <c r="AJ31" s="99"/>
@@ -5613,19 +5588,19 @@
       <c r="AW31" s="95"/>
     </row>
     <row r="32" spans="2:51" s="94" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="50" t="str">
+      <c r="B32" s="93" t="str">
         <f>X29</f>
-        <v>ELC_AGG</v>
+        <v>DECTHT</v>
       </c>
       <c r="C32" s="93" t="str">
-        <f>X8</f>
-        <v>DECELC</v>
+        <f>X9</f>
+        <v>DECRHEAT</v>
       </c>
       <c r="D32" s="93" t="s">
-        <v>69</v>
+        <v>107</v>
       </c>
       <c r="E32" s="118">
-        <v>2022</v>
+        <v>2030</v>
       </c>
       <c r="F32" s="120">
         <v>1</v>
@@ -5673,13 +5648,11 @@
       <c r="AW32" s="95"/>
     </row>
     <row r="33" spans="1:49" s="94" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="93" t="str">
-        <f>X30</f>
-        <v>DECTHT</v>
-      </c>
-      <c r="C33" s="93" t="str">
-        <f>X9</f>
-        <v>DECRHEAT</v>
+      <c r="B33" s="93" t="s">
+        <v>66</v>
+      </c>
+      <c r="C33" s="95" t="s">
+        <v>69</v>
       </c>
       <c r="D33" s="93" t="s">
         <v>107</v>
@@ -5733,17 +5706,39 @@
       <c r="AW33" s="95"/>
     </row>
     <row r="34" spans="1:49" s="94" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="93"/>
-      <c r="C34" s="95"/>
-      <c r="D34" s="93"/>
-      <c r="E34" s="118"/>
-      <c r="F34" s="120"/>
-      <c r="G34" s="120"/>
-      <c r="H34" s="119"/>
-      <c r="I34" s="119"/>
-      <c r="J34" s="119"/>
-      <c r="K34" s="119"/>
-      <c r="L34" s="119"/>
+      <c r="B34" s="93" t="s">
+        <v>97</v>
+      </c>
+      <c r="C34" s="95" t="s">
+        <v>69</v>
+      </c>
+      <c r="D34" s="93" t="s">
+        <v>107</v>
+      </c>
+      <c r="E34" s="118">
+        <v>2030</v>
+      </c>
+      <c r="F34" s="120">
+        <v>1</v>
+      </c>
+      <c r="G34" s="120">
+        <v>1</v>
+      </c>
+      <c r="H34" s="119">
+        <v>100</v>
+      </c>
+      <c r="I34" s="119">
+        <v>0</v>
+      </c>
+      <c r="J34" s="119">
+        <v>0</v>
+      </c>
+      <c r="K34" s="119">
+        <v>0</v>
+      </c>
+      <c r="L34" s="119">
+        <v>0</v>
+      </c>
       <c r="M34" s="121"/>
       <c r="N34" s="121"/>
       <c r="O34" s="120"/>
@@ -5751,7 +5746,9 @@
       <c r="Q34" s="120"/>
       <c r="R34" s="121"/>
       <c r="S34" s="118"/>
-      <c r="AD34" s="46"/>
+      <c r="AA34" s="38"/>
+      <c r="AB34" s="38"/>
+      <c r="AD34" s="95"/>
       <c r="AI34" s="99"/>
       <c r="AJ34" s="99"/>
       <c r="AK34" s="95"/>
@@ -5770,23 +5767,26 @@
     </row>
     <row r="35" spans="1:49" s="94" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B35" s="93"/>
-      <c r="C35" s="95"/>
+      <c r="C35" s="93"/>
       <c r="D35" s="93"/>
-      <c r="E35" s="118"/>
-      <c r="F35" s="120"/>
-      <c r="G35" s="120"/>
-      <c r="H35" s="119"/>
-      <c r="I35" s="119"/>
-      <c r="J35" s="119"/>
-      <c r="K35" s="119"/>
-      <c r="L35" s="119"/>
-      <c r="M35" s="121"/>
-      <c r="N35" s="121"/>
-      <c r="O35" s="120"/>
-      <c r="P35" s="120"/>
-      <c r="Q35" s="120"/>
-      <c r="R35" s="121"/>
-      <c r="S35" s="118"/>
+      <c r="E35" s="124"/>
+      <c r="F35" s="125"/>
+      <c r="G35" s="125"/>
+      <c r="M35" s="126"/>
+      <c r="N35" s="126"/>
+      <c r="O35" s="125"/>
+      <c r="P35" s="125"/>
+      <c r="Q35" s="125"/>
+      <c r="R35" s="126"/>
+      <c r="S35" s="124"/>
+      <c r="V35" s="45"/>
+      <c r="W35" s="45"/>
+      <c r="X35" s="45"/>
+      <c r="Y35" s="45"/>
+      <c r="Z35" s="50"/>
+      <c r="AA35" s="102"/>
+      <c r="AB35" s="104"/>
+      <c r="AC35" s="95"/>
       <c r="AD35" s="95"/>
       <c r="AI35" s="99"/>
       <c r="AJ35" s="99"/>
@@ -5811,6 +5811,11 @@
       <c r="E36" s="124"/>
       <c r="F36" s="125"/>
       <c r="G36" s="125"/>
+      <c r="H36" s="124"/>
+      <c r="I36" s="125"/>
+      <c r="J36" s="125"/>
+      <c r="K36" s="125"/>
+      <c r="L36" s="125"/>
       <c r="M36" s="126"/>
       <c r="N36" s="126"/>
       <c r="O36" s="125"/>
@@ -5818,184 +5823,170 @@
       <c r="Q36" s="125"/>
       <c r="R36" s="126"/>
       <c r="S36" s="124"/>
-      <c r="AA36" s="38"/>
-      <c r="AB36" s="38"/>
-      <c r="AC36" s="95"/>
-      <c r="AD36" s="95"/>
+      <c r="V36" s="101"/>
+      <c r="W36" s="100"/>
+      <c r="X36" s="101"/>
+      <c r="Y36" s="100"/>
+      <c r="Z36" s="103"/>
+      <c r="AA36" s="95"/>
+      <c r="AC36" s="45"/>
+      <c r="AD36" s="45"/>
       <c r="AI36" s="99"/>
       <c r="AJ36" s="99"/>
-      <c r="AK36" s="95"/>
-      <c r="AL36" s="95"/>
+      <c r="AK36" s="107"/>
+      <c r="AL36" s="107"/>
       <c r="AM36" s="95"/>
       <c r="AN36" s="95"/>
       <c r="AO36" s="95"/>
-      <c r="AP36" s="95"/>
-      <c r="AQ36" s="95"/>
-      <c r="AR36" s="95"/>
-      <c r="AS36" s="95"/>
-      <c r="AT36" s="95"/>
+      <c r="AQ36" s="99"/>
+      <c r="AR36" s="99"/>
+      <c r="AS36" s="107"/>
+      <c r="AT36" s="107"/>
       <c r="AU36" s="95"/>
       <c r="AV36" s="95"/>
-      <c r="AW36" s="95"/>
-    </row>
-    <row r="37" spans="1:49" s="94" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="93"/>
-      <c r="C37" s="93"/>
-      <c r="D37" s="93"/>
-      <c r="E37" s="124"/>
-      <c r="F37" s="125"/>
-      <c r="G37" s="125"/>
-      <c r="H37" s="124"/>
-      <c r="I37" s="125"/>
-      <c r="J37" s="125"/>
-      <c r="K37" s="125"/>
-      <c r="L37" s="125"/>
-      <c r="M37" s="126"/>
-      <c r="N37" s="126"/>
-      <c r="O37" s="125"/>
-      <c r="P37" s="125"/>
-      <c r="Q37" s="125"/>
-      <c r="R37" s="126"/>
-      <c r="S37" s="124"/>
-      <c r="V37" s="45"/>
-      <c r="W37" s="45"/>
-      <c r="X37" s="45"/>
-      <c r="Y37" s="45"/>
-      <c r="Z37" s="50"/>
-      <c r="AA37" s="102"/>
-      <c r="AB37" s="104"/>
-      <c r="AC37" s="45"/>
-      <c r="AD37" s="45"/>
-      <c r="AI37" s="99"/>
-      <c r="AJ37" s="99"/>
-      <c r="AK37" s="107"/>
-      <c r="AL37" s="107"/>
-      <c r="AM37" s="95"/>
-      <c r="AN37" s="95"/>
-      <c r="AO37" s="95"/>
-      <c r="AQ37" s="99"/>
-      <c r="AR37" s="99"/>
-      <c r="AS37" s="107"/>
-      <c r="AT37" s="107"/>
-      <c r="AU37" s="95"/>
-      <c r="AV37" s="95"/>
-    </row>
-    <row r="38" spans="1:49" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="5"/>
-      <c r="C38" s="50"/>
-      <c r="D38" s="50"/>
-      <c r="E38" s="127"/>
-      <c r="F38" s="128"/>
-      <c r="G38" s="129"/>
-      <c r="M38" s="127"/>
-      <c r="N38" s="130"/>
-      <c r="O38" s="127"/>
-      <c r="P38" s="127"/>
-      <c r="Q38" s="127"/>
-      <c r="R38" s="127"/>
-      <c r="S38" s="127"/>
-      <c r="V38" s="101"/>
-      <c r="W38" s="100"/>
-      <c r="X38" s="101"/>
-      <c r="Y38" s="100"/>
-      <c r="Z38" s="103"/>
+    </row>
+    <row r="37" spans="1:49" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="5"/>
+      <c r="C37" s="50"/>
+      <c r="D37" s="50"/>
+      <c r="E37" s="127"/>
+      <c r="F37" s="128"/>
+      <c r="G37" s="129"/>
+      <c r="M37" s="127"/>
+      <c r="N37" s="130"/>
+      <c r="O37" s="127"/>
+      <c r="P37" s="127"/>
+      <c r="Q37" s="127"/>
+      <c r="R37" s="127"/>
+      <c r="S37" s="127"/>
+      <c r="Z37" s="95"/>
+      <c r="AA37" s="95"/>
+      <c r="AB37" s="94"/>
+      <c r="AC37" s="94"/>
+      <c r="AD37" s="101"/>
+      <c r="AI37"/>
+      <c r="AJ37"/>
+      <c r="AK37" s="39"/>
+      <c r="AL37" s="39"/>
+      <c r="AM37" s="45"/>
+      <c r="AN37" s="45"/>
+      <c r="AO37" s="45"/>
+      <c r="AQ37"/>
+      <c r="AR37"/>
+      <c r="AS37" s="39"/>
+      <c r="AT37" s="39"/>
+      <c r="AU37" s="45"/>
+      <c r="AV37" s="45"/>
+    </row>
+    <row r="38" spans="1:49" s="100" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="101"/>
+      <c r="C38" s="102"/>
+      <c r="D38" s="102"/>
+      <c r="E38" s="131"/>
+      <c r="F38" s="132"/>
+      <c r="G38" s="132"/>
+      <c r="H38" s="131"/>
+      <c r="I38" s="132"/>
+      <c r="J38" s="132"/>
+      <c r="K38" s="132"/>
+      <c r="L38" s="132"/>
+      <c r="N38" s="133"/>
+      <c r="V38" s="45"/>
+      <c r="W38" s="45"/>
+      <c r="X38" s="45"/>
+      <c r="Y38" s="45"/>
+      <c r="Z38" s="95"/>
       <c r="AA38" s="95"/>
       <c r="AB38" s="94"/>
-      <c r="AC38" s="94"/>
-      <c r="AD38" s="101"/>
-      <c r="AI38"/>
-      <c r="AJ38"/>
-      <c r="AK38" s="39"/>
-      <c r="AL38" s="39"/>
-      <c r="AM38" s="45"/>
-      <c r="AN38" s="45"/>
-      <c r="AO38" s="45"/>
-      <c r="AQ38"/>
-      <c r="AR38"/>
-      <c r="AS38" s="39"/>
-      <c r="AT38" s="39"/>
-      <c r="AU38" s="45"/>
-      <c r="AV38" s="45"/>
-    </row>
-    <row r="39" spans="1:49" s="100" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="101"/>
-      <c r="C39" s="102"/>
-      <c r="D39" s="102"/>
-      <c r="E39" s="131"/>
-      <c r="F39" s="132"/>
-      <c r="G39" s="132"/>
-      <c r="H39" s="131"/>
-      <c r="I39" s="132"/>
-      <c r="J39" s="132"/>
-      <c r="K39" s="132"/>
-      <c r="L39" s="132"/>
-      <c r="N39" s="133"/>
-      <c r="V39" s="46"/>
-      <c r="W39" s="46"/>
-      <c r="X39" s="46"/>
-      <c r="Y39" s="46"/>
+      <c r="AC38" s="46"/>
+      <c r="AD38" s="95"/>
+      <c r="AI38" s="105"/>
+      <c r="AJ38" s="105"/>
+      <c r="AK38" s="106"/>
+      <c r="AL38" s="106"/>
+      <c r="AM38" s="101"/>
+      <c r="AN38" s="101"/>
+      <c r="AO38" s="101"/>
+      <c r="AQ38" s="105"/>
+      <c r="AR38" s="105"/>
+      <c r="AS38" s="106"/>
+      <c r="AT38" s="106"/>
+      <c r="AU38" s="101"/>
+      <c r="AV38" s="101"/>
+    </row>
+    <row r="39" spans="1:49" s="94" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="95"/>
+      <c r="C39" s="93"/>
+      <c r="D39" s="93"/>
+      <c r="E39" s="124"/>
+      <c r="F39" s="125"/>
+      <c r="G39" s="125"/>
+      <c r="H39" s="124"/>
+      <c r="I39" s="125"/>
+      <c r="J39" s="125"/>
+      <c r="K39" s="125"/>
+      <c r="L39" s="125"/>
+      <c r="N39" s="134"/>
+      <c r="V39" s="99"/>
+      <c r="W39" s="99"/>
+      <c r="X39" s="95"/>
+      <c r="Y39" s="108"/>
       <c r="Z39" s="95"/>
       <c r="AA39" s="95"/>
-      <c r="AB39" s="94"/>
-      <c r="AC39" s="46"/>
-      <c r="AD39" s="95"/>
-      <c r="AI39" s="105"/>
-      <c r="AJ39" s="105"/>
-      <c r="AK39" s="106"/>
-      <c r="AL39" s="106"/>
-      <c r="AM39" s="101"/>
-      <c r="AN39" s="101"/>
-      <c r="AO39" s="101"/>
-      <c r="AQ39" s="105"/>
-      <c r="AR39" s="105"/>
-      <c r="AS39" s="106"/>
-      <c r="AT39" s="106"/>
-      <c r="AU39" s="101"/>
-      <c r="AV39" s="101"/>
-    </row>
-    <row r="40" spans="1:49" s="94" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="95"/>
-      <c r="C40" s="93"/>
-      <c r="D40" s="93"/>
-      <c r="E40" s="124"/>
-      <c r="F40" s="125"/>
-      <c r="G40" s="125"/>
-      <c r="H40" s="124"/>
-      <c r="I40" s="125"/>
-      <c r="J40" s="125"/>
-      <c r="K40" s="125"/>
-      <c r="L40" s="125"/>
-      <c r="N40" s="134"/>
-      <c r="V40" s="45"/>
-      <c r="W40" s="45"/>
-      <c r="X40" s="45"/>
-      <c r="Y40" s="45"/>
+      <c r="AC39" s="95"/>
+      <c r="AD39" s="45"/>
+      <c r="AI39" s="99"/>
+      <c r="AJ39" s="99"/>
+      <c r="AK39" s="107"/>
+      <c r="AL39" s="107"/>
+      <c r="AM39" s="95"/>
+      <c r="AN39" s="95"/>
+      <c r="AO39" s="95"/>
+      <c r="AQ39" s="99"/>
+      <c r="AR39" s="99"/>
+      <c r="AS39" s="107"/>
+      <c r="AT39" s="107"/>
+      <c r="AU39" s="95"/>
+      <c r="AV39" s="95"/>
+    </row>
+    <row r="40" spans="1:49" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="45"/>
+      <c r="C40" s="50"/>
+      <c r="D40" s="50"/>
+      <c r="E40" s="127"/>
+      <c r="F40" s="128"/>
+      <c r="G40" s="129"/>
+      <c r="N40" s="135"/>
+      <c r="V40" s="99"/>
+      <c r="W40" s="99"/>
+      <c r="X40" s="95"/>
+      <c r="Y40" s="108"/>
       <c r="Z40" s="95"/>
       <c r="AA40" s="95"/>
+      <c r="AB40" s="94"/>
       <c r="AC40" s="95"/>
       <c r="AD40" s="45"/>
-      <c r="AI40" s="99"/>
-      <c r="AJ40" s="99"/>
-      <c r="AK40" s="107"/>
-      <c r="AL40" s="107"/>
-      <c r="AM40" s="95"/>
-      <c r="AN40" s="95"/>
-      <c r="AO40" s="95"/>
-      <c r="AQ40" s="99"/>
-      <c r="AR40" s="99"/>
-      <c r="AS40" s="107"/>
-      <c r="AT40" s="107"/>
-      <c r="AU40" s="95"/>
-      <c r="AV40" s="95"/>
+      <c r="AI40"/>
+      <c r="AJ40"/>
+      <c r="AK40" s="39"/>
+      <c r="AL40" s="39"/>
+      <c r="AM40" s="45"/>
+      <c r="AN40" s="45"/>
+      <c r="AO40" s="45"/>
+      <c r="AQ40"/>
+      <c r="AR40"/>
+      <c r="AS40" s="39"/>
+      <c r="AT40" s="39"/>
+      <c r="AU40" s="45"/>
+      <c r="AV40" s="45"/>
     </row>
     <row r="41" spans="1:49" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="45"/>
+      <c r="B41" s="50"/>
       <c r="C41" s="50"/>
       <c r="D41" s="50"/>
       <c r="E41" s="127"/>
       <c r="F41" s="128"/>
       <c r="G41" s="129"/>
-      <c r="N41" s="135"/>
       <c r="V41" s="99"/>
       <c r="W41" s="99"/>
       <c r="X41" s="95"/>
@@ -6005,6 +5996,7 @@
       <c r="AB41" s="94"/>
       <c r="AC41" s="95"/>
       <c r="AD41" s="45"/>
+      <c r="AE41" s="45"/>
       <c r="AI41"/>
       <c r="AJ41"/>
       <c r="AK41" s="39"/>
@@ -6028,11 +6020,11 @@
       <c r="G42" s="129"/>
       <c r="V42" s="99"/>
       <c r="W42" s="99"/>
-      <c r="X42" s="95"/>
+      <c r="X42" s="107"/>
       <c r="Y42" s="108"/>
       <c r="Z42" s="95"/>
-      <c r="AA42" s="95"/>
-      <c r="AB42" s="94"/>
+      <c r="AA42" s="45"/>
+      <c r="AB42" s="45"/>
       <c r="AC42" s="95"/>
       <c r="AD42" s="45"/>
       <c r="AE42" s="45"/>
@@ -6050,47 +6042,36 @@
       <c r="AU42" s="45"/>
       <c r="AV42" s="45"/>
     </row>
-    <row r="43" spans="1:49" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="50"/>
-      <c r="C43" s="50"/>
-      <c r="D43" s="50"/>
-      <c r="E43" s="127"/>
-      <c r="F43" s="128"/>
-      <c r="G43" s="129"/>
-      <c r="V43" s="99"/>
-      <c r="W43" s="99"/>
-      <c r="X43" s="95"/>
-      <c r="Y43" s="108"/>
-      <c r="Z43" s="95"/>
-      <c r="AA43" s="95"/>
-      <c r="AB43" s="94"/>
-      <c r="AC43" s="95"/>
-      <c r="AD43" s="45"/>
-      <c r="AE43" s="45"/>
+    <row r="43" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="A43" s="46"/>
+      <c r="E43" s="46"/>
+      <c r="F43" s="136"/>
+      <c r="G43" s="127"/>
+      <c r="H43" s="135"/>
+      <c r="I43" s="46"/>
+      <c r="J43" s="46"/>
+      <c r="K43" s="46"/>
+      <c r="L43" s="46"/>
+      <c r="M43" s="46"/>
+      <c r="N43" s="46"/>
+      <c r="O43" s="46"/>
+      <c r="P43" s="46"/>
+      <c r="Q43" s="46"/>
+      <c r="R43" s="46"/>
+      <c r="S43" s="46"/>
       <c r="AI43"/>
       <c r="AJ43"/>
       <c r="AK43" s="39"/>
       <c r="AL43" s="39"/>
-      <c r="AM43" s="45"/>
-      <c r="AN43" s="45"/>
-      <c r="AO43" s="45"/>
+      <c r="AP43" s="46"/>
       <c r="AQ43"/>
       <c r="AR43"/>
       <c r="AS43" s="39"/>
       <c r="AT43" s="39"/>
-      <c r="AU43" s="45"/>
-      <c r="AV43" s="45"/>
     </row>
     <row r="44" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A44" s="46"/>
-      <c r="E44" s="46"/>
-      <c r="F44" s="136"/>
-      <c r="G44" s="127"/>
-      <c r="H44" s="135"/>
-      <c r="I44" s="46"/>
-      <c r="J44" s="46"/>
-      <c r="K44" s="46"/>
-      <c r="L44" s="46"/>
+      <c r="H44" s="64"/>
       <c r="M44" s="46"/>
       <c r="N44" s="46"/>
       <c r="O44" s="46"/>
@@ -6098,11 +6079,6 @@
       <c r="Q44" s="46"/>
       <c r="R44" s="46"/>
       <c r="S44" s="46"/>
-      <c r="V44" s="99"/>
-      <c r="W44" s="99"/>
-      <c r="X44" s="107"/>
-      <c r="Y44" s="108"/>
-      <c r="Z44" s="95"/>
       <c r="AI44"/>
       <c r="AJ44"/>
       <c r="AK44" s="39"/>
@@ -6114,29 +6090,24 @@
       <c r="AT44" s="39"/>
     </row>
     <row r="45" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A45" s="46"/>
+      <c r="B45" s="65"/>
+      <c r="C45" s="45" t="s">
+        <v>82</v>
+      </c>
       <c r="H45" s="64"/>
-      <c r="M45" s="46"/>
-      <c r="N45" s="46"/>
-      <c r="O45" s="46"/>
-      <c r="P45" s="46"/>
-      <c r="Q45" s="46"/>
-      <c r="R45" s="46"/>
-      <c r="S45" s="46"/>
       <c r="AI45"/>
       <c r="AJ45"/>
       <c r="AK45" s="39"/>
       <c r="AL45" s="39"/>
-      <c r="AP45" s="46"/>
       <c r="AQ45"/>
       <c r="AR45"/>
       <c r="AS45" s="39"/>
       <c r="AT45" s="39"/>
     </row>
     <row r="46" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="B46" s="65"/>
+      <c r="B46" s="66"/>
       <c r="C46" s="45" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H46" s="64"/>
       <c r="AI46"/>
@@ -6149,10 +6120,6 @@
       <c r="AT46" s="39"/>
     </row>
     <row r="47" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="B47" s="66"/>
-      <c r="C47" s="45" t="s">
-        <v>83</v>
-      </c>
       <c r="H47" s="64"/>
       <c r="AI47"/>
       <c r="AJ47"/>
@@ -6164,7 +6131,6 @@
       <c r="AT47" s="39"/>
     </row>
     <row r="48" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="H48" s="64"/>
       <c r="AI48"/>
       <c r="AJ48"/>
       <c r="AK48" s="39"/>
@@ -6185,6 +6151,7 @@
       <c r="AT49" s="39"/>
     </row>
     <row r="50" spans="2:46" x14ac:dyDescent="0.25">
+      <c r="E50" s="43"/>
       <c r="AI50"/>
       <c r="AJ50"/>
       <c r="AK50" s="39"/>
@@ -6195,7 +6162,6 @@
       <c r="AT50" s="39"/>
     </row>
     <row r="51" spans="2:46" x14ac:dyDescent="0.25">
-      <c r="E51" s="43"/>
       <c r="AI51"/>
       <c r="AJ51"/>
       <c r="AK51" s="39"/>
@@ -6256,6 +6222,17 @@
       <c r="AT56" s="39"/>
     </row>
     <row r="57" spans="2:46" x14ac:dyDescent="0.25">
+      <c r="B57" s="68"/>
+      <c r="C57" s="68"/>
+      <c r="D57"/>
+      <c r="E57"/>
+      <c r="F57"/>
+      <c r="G57"/>
+      <c r="H57"/>
+      <c r="I57"/>
+      <c r="J57"/>
+      <c r="K57"/>
+      <c r="L57"/>
       <c r="AI57"/>
       <c r="AJ57"/>
       <c r="AK57" s="39"/>
@@ -6265,18 +6242,18 @@
       <c r="AS57" s="39"/>
       <c r="AT57" s="39"/>
     </row>
-    <row r="58" spans="2:46" x14ac:dyDescent="0.25">
-      <c r="B58" s="68"/>
-      <c r="C58" s="68"/>
-      <c r="D58"/>
-      <c r="E58"/>
-      <c r="F58"/>
-      <c r="G58"/>
-      <c r="H58"/>
-      <c r="I58"/>
-      <c r="J58"/>
-      <c r="K58"/>
-      <c r="L58"/>
+    <row r="58" spans="2:46" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="69"/>
+      <c r="C58" s="69"/>
+      <c r="D58" s="69"/>
+      <c r="E58" s="69"/>
+      <c r="F58" s="69"/>
+      <c r="G58" s="69"/>
+      <c r="H58" s="69"/>
+      <c r="I58" s="69"/>
+      <c r="J58" s="69"/>
+      <c r="K58" s="69"/>
+      <c r="L58" s="69"/>
       <c r="AI58"/>
       <c r="AJ58"/>
       <c r="AK58" s="39"/>
@@ -6286,18 +6263,18 @@
       <c r="AS58" s="39"/>
       <c r="AT58" s="39"/>
     </row>
-    <row r="59" spans="2:46" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="69"/>
-      <c r="C59" s="69"/>
-      <c r="D59" s="69"/>
-      <c r="E59" s="69"/>
-      <c r="F59" s="69"/>
-      <c r="G59" s="69"/>
-      <c r="H59" s="69"/>
-      <c r="I59" s="69"/>
-      <c r="J59" s="69"/>
-      <c r="K59" s="69"/>
-      <c r="L59" s="69"/>
+    <row r="59" spans="2:46" x14ac:dyDescent="0.25">
+      <c r="B59"/>
+      <c r="C59"/>
+      <c r="D59"/>
+      <c r="E59" s="1"/>
+      <c r="F59"/>
+      <c r="G59"/>
+      <c r="H59"/>
+      <c r="I59"/>
+      <c r="J59"/>
+      <c r="K59"/>
+      <c r="L59"/>
       <c r="AI59"/>
       <c r="AJ59"/>
       <c r="AK59" s="39"/>
@@ -6455,17 +6432,13 @@
       <c r="AT66" s="39"/>
     </row>
     <row r="67" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="B67"/>
-      <c r="C67"/>
-      <c r="D67"/>
-      <c r="E67" s="1"/>
-      <c r="F67"/>
-      <c r="G67"/>
-      <c r="H67"/>
-      <c r="I67"/>
-      <c r="J67"/>
-      <c r="K67"/>
-      <c r="L67"/>
+      <c r="V67" s="46"/>
+      <c r="W67" s="46"/>
+      <c r="X67" s="46"/>
+      <c r="Y67" s="46"/>
+      <c r="Z67" s="46"/>
+      <c r="AA67" s="46"/>
+      <c r="AB67" s="46"/>
       <c r="AI67"/>
       <c r="AJ67"/>
       <c r="AK67" s="39"/>
@@ -6476,6 +6449,13 @@
       <c r="AT67" s="39"/>
     </row>
     <row r="68" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="V68" s="46"/>
+      <c r="W68" s="46"/>
+      <c r="X68" s="46"/>
+      <c r="Y68" s="46"/>
+      <c r="Z68" s="46"/>
+      <c r="AA68" s="46"/>
+      <c r="AB68" s="46"/>
       <c r="AI68"/>
       <c r="AJ68"/>
       <c r="AK68" s="39"/>
@@ -6493,6 +6473,7 @@
       <c r="Z69" s="46"/>
       <c r="AA69" s="46"/>
       <c r="AB69" s="46"/>
+      <c r="AC69" s="46"/>
       <c r="AI69"/>
       <c r="AJ69"/>
       <c r="AK69" s="39"/>
@@ -6503,14 +6484,8 @@
       <c r="AT69" s="39"/>
     </row>
     <row r="70" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="V70" s="46"/>
-      <c r="W70" s="46"/>
-      <c r="X70" s="46"/>
-      <c r="Y70" s="46"/>
-      <c r="Z70" s="46"/>
-      <c r="AA70" s="46"/>
-      <c r="AB70" s="46"/>
       <c r="AC70" s="46"/>
+      <c r="AD70" s="46"/>
       <c r="AI70"/>
       <c r="AJ70"/>
       <c r="AK70" s="39"/>
@@ -6521,15 +6496,9 @@
       <c r="AT70" s="39"/>
     </row>
     <row r="71" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="V71" s="46"/>
-      <c r="W71" s="46"/>
-      <c r="X71" s="46"/>
-      <c r="Y71" s="46"/>
-      <c r="Z71" s="46"/>
-      <c r="AA71" s="46"/>
-      <c r="AB71" s="46"/>
       <c r="AC71" s="46"/>
       <c r="AD71" s="46"/>
+      <c r="AE71" s="46"/>
       <c r="AI71"/>
       <c r="AJ71"/>
       <c r="AK71" s="39"/>
@@ -6540,7 +6509,16 @@
       <c r="AT71" s="39"/>
     </row>
     <row r="72" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="AC72" s="46"/>
+      <c r="B72"/>
+      <c r="C72"/>
+      <c r="E72" s="68"/>
+      <c r="F72" s="68"/>
+      <c r="G72" s="1"/>
+      <c r="H72"/>
+      <c r="I72" s="68"/>
+      <c r="J72"/>
+      <c r="K72"/>
+      <c r="L72" s="68"/>
       <c r="AD72" s="46"/>
       <c r="AE72" s="46"/>
       <c r="AI72"/>
@@ -6552,44 +6530,64 @@
       <c r="AS72" s="39"/>
       <c r="AT72" s="39"/>
     </row>
-    <row r="73" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="B73"/>
-      <c r="C73"/>
-      <c r="E73" s="68"/>
-      <c r="F73" s="68"/>
-      <c r="G73" s="1"/>
-      <c r="H73"/>
-      <c r="I73" s="68"/>
-      <c r="J73"/>
-      <c r="K73"/>
-      <c r="L73" s="68"/>
-      <c r="AD73" s="46"/>
-      <c r="AE73" s="46"/>
+    <row r="73" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="45"/>
+      <c r="B73" s="74"/>
+      <c r="C73" s="74"/>
+      <c r="D73" s="74"/>
+      <c r="E73" s="74"/>
+      <c r="F73" s="74"/>
+      <c r="G73" s="74"/>
+      <c r="H73" s="75"/>
+      <c r="I73" s="74"/>
+      <c r="J73" s="74"/>
+      <c r="K73" s="74"/>
+      <c r="L73" s="74"/>
+      <c r="M73" s="45"/>
+      <c r="N73" s="45"/>
+      <c r="O73" s="45"/>
+      <c r="P73" s="45"/>
+      <c r="Q73" s="45"/>
+      <c r="R73" s="45"/>
+      <c r="S73" s="45"/>
+      <c r="V73" s="45"/>
+      <c r="W73" s="45"/>
+      <c r="X73" s="45"/>
+      <c r="Y73" s="45"/>
+      <c r="Z73" s="45"/>
+      <c r="AA73" s="45"/>
+      <c r="AB73" s="45"/>
+      <c r="AC73" s="45"/>
+      <c r="AD73" s="45"/>
       <c r="AI73"/>
-      <c r="AJ73"/>
+      <c r="AJ73" s="75"/>
       <c r="AK73" s="39"/>
-      <c r="AL73" s="39"/>
+      <c r="AL73" s="41"/>
+      <c r="AM73" s="45"/>
+      <c r="AN73" s="45"/>
       <c r="AQ73"/>
-      <c r="AR73"/>
+      <c r="AR73" s="75"/>
       <c r="AS73" s="39"/>
-      <c r="AT73" s="39"/>
+      <c r="AT73" s="41"/>
+      <c r="AU73" s="45"/>
+      <c r="AV73" s="45"/>
     </row>
     <row r="74" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="45"/>
-      <c r="B74" s="74"/>
-      <c r="C74" s="74"/>
-      <c r="D74" s="74"/>
-      <c r="E74" s="74"/>
-      <c r="F74" s="74"/>
-      <c r="G74" s="74"/>
+      <c r="A74" s="68"/>
+      <c r="B74" s="76"/>
+      <c r="C74" s="77"/>
+      <c r="D74" s="76"/>
+      <c r="E74" s="76"/>
+      <c r="F74" s="76"/>
+      <c r="G74" s="76"/>
       <c r="H74" s="75"/>
-      <c r="I74" s="74"/>
-      <c r="J74" s="74"/>
-      <c r="K74" s="74"/>
-      <c r="L74" s="74"/>
-      <c r="M74" s="45"/>
-      <c r="N74" s="45"/>
-      <c r="O74" s="45"/>
+      <c r="I74" s="76"/>
+      <c r="J74" s="76"/>
+      <c r="K74" s="77"/>
+      <c r="L74" s="77"/>
+      <c r="M74" s="68"/>
+      <c r="N74" s="68"/>
+      <c r="O74" s="1"/>
       <c r="P74" s="45"/>
       <c r="Q74" s="45"/>
       <c r="R74" s="45"/>
@@ -6603,23 +6601,15 @@
       <c r="AB74" s="45"/>
       <c r="AC74" s="45"/>
       <c r="AD74" s="45"/>
-      <c r="AI74"/>
-      <c r="AJ74" s="75"/>
-      <c r="AK74" s="39"/>
-      <c r="AL74" s="41"/>
-      <c r="AM74" s="45"/>
-      <c r="AN74" s="45"/>
-      <c r="AQ74"/>
-      <c r="AR74" s="75"/>
-      <c r="AS74" s="39"/>
-      <c r="AT74" s="41"/>
-      <c r="AU74" s="45"/>
-      <c r="AV74" s="45"/>
+      <c r="AE74" s="45"/>
+      <c r="AI74" s="42"/>
+      <c r="AJ74" s="42"/>
+      <c r="AK74" s="54"/>
     </row>
     <row r="75" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="68"/>
+      <c r="A75" s="74"/>
       <c r="B75" s="76"/>
-      <c r="C75" s="77"/>
+      <c r="C75" s="76"/>
       <c r="D75" s="76"/>
       <c r="E75" s="76"/>
       <c r="F75" s="76"/>
@@ -6627,15 +6617,11 @@
       <c r="H75" s="75"/>
       <c r="I75" s="76"/>
       <c r="J75" s="76"/>
-      <c r="K75" s="77"/>
-      <c r="L75" s="77"/>
-      <c r="M75" s="68"/>
-      <c r="N75" s="68"/>
-      <c r="O75" s="1"/>
-      <c r="P75" s="45"/>
-      <c r="Q75" s="45"/>
-      <c r="R75" s="45"/>
-      <c r="S75" s="45"/>
+      <c r="K75" s="76"/>
+      <c r="L75" s="76"/>
+      <c r="M75" s="74"/>
+      <c r="N75" s="74"/>
+      <c r="O75" s="74"/>
       <c r="V75" s="45"/>
       <c r="W75" s="45"/>
       <c r="X75" s="45"/>
@@ -6650,48 +6636,39 @@
       <c r="AJ75" s="42"/>
       <c r="AK75" s="54"/>
     </row>
-    <row r="76" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="74"/>
-      <c r="B76" s="76"/>
-      <c r="C76" s="76"/>
-      <c r="D76" s="76"/>
-      <c r="E76" s="76"/>
-      <c r="F76" s="76"/>
-      <c r="G76" s="76"/>
-      <c r="H76" s="75"/>
-      <c r="I76" s="76"/>
-      <c r="J76" s="76"/>
-      <c r="K76" s="76"/>
-      <c r="L76" s="76"/>
-      <c r="M76" s="74"/>
-      <c r="N76" s="74"/>
-      <c r="O76" s="74"/>
-      <c r="V76" s="45"/>
-      <c r="W76" s="45"/>
-      <c r="X76" s="45"/>
-      <c r="Y76" s="45"/>
-      <c r="Z76" s="45"/>
-      <c r="AA76" s="45"/>
-      <c r="AB76" s="45"/>
-      <c r="AC76" s="45"/>
-      <c r="AD76" s="45"/>
-      <c r="AE76" s="45"/>
-      <c r="AI76" s="42"/>
-      <c r="AJ76" s="42"/>
-      <c r="AK76" s="54"/>
+    <row r="76" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A76" s="76"/>
+      <c r="B76"/>
+      <c r="C76" s="39"/>
+      <c r="D76" s="39"/>
+      <c r="H76"/>
+      <c r="I76"/>
+      <c r="J76"/>
+      <c r="K76" s="39"/>
+      <c r="L76" s="39"/>
+      <c r="M76" s="77"/>
+      <c r="N76" s="77"/>
+      <c r="O76" s="76"/>
+      <c r="P76" s="46"/>
+      <c r="Q76" s="46"/>
+      <c r="R76" s="46"/>
+      <c r="S76" s="46"/>
+      <c r="AI76" s="38"/>
+      <c r="AJ76" s="38"/>
+      <c r="AK76" s="50"/>
     </row>
     <row r="77" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A77" s="76"/>
       <c r="B77"/>
       <c r="C77" s="39"/>
       <c r="D77" s="39"/>
-      <c r="H77"/>
+      <c r="H77" s="73"/>
       <c r="I77"/>
       <c r="J77"/>
       <c r="K77" s="39"/>
       <c r="L77" s="39"/>
-      <c r="M77" s="77"/>
-      <c r="N77" s="77"/>
+      <c r="M77" s="76"/>
+      <c r="N77" s="76"/>
       <c r="O77" s="76"/>
       <c r="P77" s="46"/>
       <c r="Q77" s="46"/>
@@ -6702,22 +6679,14 @@
       <c r="AK77" s="50"/>
     </row>
     <row r="78" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A78" s="76"/>
+      <c r="A78"/>
       <c r="B78"/>
       <c r="C78" s="39"/>
       <c r="D78" s="39"/>
-      <c r="H78" s="73"/>
       <c r="I78"/>
       <c r="J78"/>
       <c r="K78" s="39"/>
       <c r="L78" s="39"/>
-      <c r="M78" s="76"/>
-      <c r="N78" s="76"/>
-      <c r="O78" s="76"/>
-      <c r="P78" s="46"/>
-      <c r="Q78" s="46"/>
-      <c r="R78" s="46"/>
-      <c r="S78" s="46"/>
       <c r="AI78" s="38"/>
       <c r="AJ78" s="38"/>
       <c r="AK78" s="50"/>
@@ -6740,10 +6709,12 @@
       <c r="B80"/>
       <c r="C80" s="39"/>
       <c r="D80" s="39"/>
+      <c r="H80" s="46"/>
       <c r="I80"/>
       <c r="J80"/>
       <c r="K80" s="39"/>
       <c r="L80" s="39"/>
+      <c r="O80" s="46"/>
       <c r="AI80" s="38"/>
       <c r="AJ80" s="38"/>
       <c r="AK80" s="50"/>
@@ -6963,12 +6934,10 @@
       <c r="B95"/>
       <c r="C95" s="39"/>
       <c r="D95" s="39"/>
-      <c r="H95" s="46"/>
       <c r="I95"/>
       <c r="J95"/>
       <c r="K95" s="39"/>
       <c r="L95" s="39"/>
-      <c r="O95" s="46"/>
       <c r="AI95" s="38"/>
       <c r="AJ95" s="38"/>
       <c r="AK95" s="50"/>
@@ -7339,13 +7308,6 @@
     </row>
     <row r="124" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A124"/>
-      <c r="B124"/>
-      <c r="C124" s="39"/>
-      <c r="D124" s="39"/>
-      <c r="I124"/>
-      <c r="J124"/>
-      <c r="K124" s="39"/>
-      <c r="L124" s="39"/>
       <c r="AI124" s="38"/>
       <c r="AJ124" s="38"/>
       <c r="AK124" s="50"/>
@@ -7357,7 +7319,6 @@
       <c r="AK125" s="50"/>
     </row>
     <row r="126" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A126"/>
       <c r="AI126" s="38"/>
       <c r="AJ126" s="38"/>
       <c r="AK126" s="50"/>
@@ -7476,11 +7437,6 @@
       <c r="AI149" s="38"/>
       <c r="AJ149" s="38"/>
       <c r="AK149" s="50"/>
-    </row>
-    <row r="150" spans="35:37" x14ac:dyDescent="0.25">
-      <c r="AI150" s="38"/>
-      <c r="AJ150" s="38"/>
-      <c r="AK150" s="50"/>
     </row>
   </sheetData>
   <phoneticPr fontId="24" type="noConversion"/>

--- a/SubRES_TMPL/SubRES_NewTechs.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22E9682F-63F2-4C7D-912C-268758273409}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB31F9FE-4360-4064-8A6B-010FE2EB66EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1554,7 +1554,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="157">
   <si>
     <t>~FI_T</t>
   </si>
@@ -2019,6 +2019,12 @@
   </si>
   <si>
     <t>DECTHT</t>
+  </si>
+  <si>
+    <t>ELC_AGG</t>
+  </si>
+  <si>
+    <t>Electricity aggrigator</t>
   </si>
 </sst>
 </file>
@@ -2375,7 +2381,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="137">
+  <cellXfs count="138">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
@@ -2593,6 +2599,7 @@
     <xf numFmtId="9" fontId="28" fillId="8" borderId="0" xfId="21" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="21" fillId="8" borderId="0" xfId="21" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="21" fillId="8" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="4" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="22">
     <cellStyle name="20% - Accent5 2" xfId="18" xr:uid="{4C3A48E2-3C46-4D12-9A64-54698D8BF8EE}"/>
@@ -5507,9 +5514,25 @@
       <c r="Q30" s="116"/>
       <c r="R30" s="117"/>
       <c r="S30" s="115"/>
-      <c r="Z30" s="95"/>
-      <c r="AA30" s="95"/>
-      <c r="AB30" s="94"/>
+      <c r="V30" s="94" t="s">
+        <v>69</v>
+      </c>
+      <c r="W30" s="94"/>
+      <c r="X30" s="94" t="s">
+        <v>155</v>
+      </c>
+      <c r="Y30" s="94" t="s">
+        <v>156</v>
+      </c>
+      <c r="Z30" s="95" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA30" s="95" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB30" s="94" t="s">
+        <v>88</v>
+      </c>
       <c r="AC30" s="94"/>
       <c r="AI30" s="38"/>
       <c r="AJ30" s="38"/>
@@ -5766,19 +5789,48 @@
       <c r="AW34" s="95"/>
     </row>
     <row r="35" spans="1:49" s="94" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="93"/>
-      <c r="C35" s="93"/>
-      <c r="D35" s="93"/>
-      <c r="E35" s="124"/>
-      <c r="F35" s="125"/>
-      <c r="G35" s="125"/>
-      <c r="M35" s="126"/>
-      <c r="N35" s="126"/>
-      <c r="O35" s="125"/>
-      <c r="P35" s="125"/>
-      <c r="Q35" s="125"/>
-      <c r="R35" s="126"/>
-      <c r="S35" s="124"/>
+      <c r="B35" s="72" t="str">
+        <f>X30</f>
+        <v>ELC_AGG</v>
+      </c>
+      <c r="C35" s="78" t="str">
+        <f>X8</f>
+        <v>DECELC</v>
+      </c>
+      <c r="D35" s="137" t="s">
+        <v>69</v>
+      </c>
+      <c r="E35" s="124">
+        <v>2022</v>
+      </c>
+      <c r="F35" s="120">
+        <v>1</v>
+      </c>
+      <c r="G35" s="120">
+        <v>1</v>
+      </c>
+      <c r="H35" s="119">
+        <v>100</v>
+      </c>
+      <c r="I35" s="119">
+        <v>0</v>
+      </c>
+      <c r="J35" s="119">
+        <v>0</v>
+      </c>
+      <c r="K35" s="119">
+        <v>0</v>
+      </c>
+      <c r="L35" s="119">
+        <v>0</v>
+      </c>
+      <c r="M35" s="121"/>
+      <c r="N35" s="121"/>
+      <c r="O35" s="120"/>
+      <c r="P35" s="120"/>
+      <c r="Q35" s="120"/>
+      <c r="R35" s="121"/>
+      <c r="S35" s="118"/>
       <c r="V35" s="45"/>
       <c r="W35" s="45"/>
       <c r="X35" s="45"/>

--- a/SubRES_TMPL/SubRES_NewTechs.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB31F9FE-4360-4064-8A6B-010FE2EB66EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{881C639A-A4E9-4D84-B0D2-C7D2D4D4DA4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="21600" windowHeight="11232" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PRI_Sector_Fuels" sheetId="6" r:id="rId1"/>
@@ -1554,7 +1554,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="157">
   <si>
     <t>~FI_T</t>
   </si>
@@ -4259,7 +4259,7 @@
         <v>69</v>
       </c>
       <c r="X6" s="45" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Y6" s="72" t="s">
         <v>132</v>
@@ -5320,8 +5320,9 @@
         <f>X27</f>
         <v>DECPOWER</v>
       </c>
-      <c r="C28" s="93" t="s">
-        <v>129</v>
+      <c r="C28" s="93" t="str">
+        <f>X6</f>
+        <v>WNDELC</v>
       </c>
       <c r="D28" s="93" t="str">
         <f>X8</f>
@@ -5398,8 +5399,9 @@
         <f>X27</f>
         <v>DECPOWER</v>
       </c>
-      <c r="C29" s="93" t="s">
-        <v>130</v>
+      <c r="C29" s="93" t="str">
+        <f>X5</f>
+        <v>SOLELC</v>
       </c>
       <c r="D29" s="93" t="str">
         <f>X8</f>
@@ -5555,8 +5557,9 @@
         <f>X27</f>
         <v>DECPOWER</v>
       </c>
-      <c r="C31" s="95" t="s">
-        <v>134</v>
+      <c r="C31" s="95" t="str">
+        <f>X7</f>
+        <v>BIOELC</v>
       </c>
       <c r="D31" s="93" t="str">
         <f>X8</f>

--- a/SubRES_TMPL/SubRES_NewTechs.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{881C639A-A4E9-4D84-B0D2-C7D2D4D4DA4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34B42AA0-0129-47C8-A678-9396207B797C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="21600" windowHeight="11232" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PRI_Sector_Fuels" sheetId="6" r:id="rId1"/>
@@ -1554,7 +1554,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="158">
   <si>
     <t>~FI_T</t>
   </si>
@@ -2021,10 +2021,13 @@
     <t>DECTHT</t>
   </si>
   <si>
-    <t>ELC_AGG</t>
-  </si>
-  <si>
     <t>Electricity aggrigator</t>
+  </si>
+  <si>
+    <t>MANELC_TECH</t>
+  </si>
+  <si>
+    <t>MANELC</t>
   </si>
 </sst>
 </file>
@@ -5516,15 +5519,15 @@
       <c r="Q30" s="116"/>
       <c r="R30" s="117"/>
       <c r="S30" s="115"/>
-      <c r="V30" s="94" t="s">
-        <v>69</v>
+      <c r="V30" s="72" t="s">
+        <v>127</v>
       </c>
       <c r="W30" s="94"/>
       <c r="X30" s="94" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y30" s="94" t="s">
         <v>155</v>
-      </c>
-      <c r="Y30" s="94" t="s">
-        <v>156</v>
       </c>
       <c r="Z30" s="95" t="s">
         <v>58</v>
@@ -5794,14 +5797,14 @@
     <row r="35" spans="1:49" s="94" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B35" s="72" t="str">
         <f>X30</f>
-        <v>ELC_AGG</v>
+        <v>MANELC_TECH</v>
       </c>
       <c r="C35" s="78" t="str">
         <f>X8</f>
         <v>DECELC</v>
       </c>
       <c r="D35" s="137" t="s">
-        <v>69</v>
+        <v>157</v>
       </c>
       <c r="E35" s="124">
         <v>2022</v>

--- a/SubRES_TMPL/SubRES_NewTechs.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34B42AA0-0129-47C8-A678-9396207B797C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A25A859-9FBE-43A4-975D-22FE599F4824}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PRI_Sector_Fuels" sheetId="6" r:id="rId1"/>
@@ -5748,7 +5748,7 @@
         <v>2030</v>
       </c>
       <c r="F34" s="120">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="G34" s="120">
         <v>1</v>

--- a/SubRES_TMPL/SubRES_NewTechs.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A25A859-9FBE-43A4-975D-22FE599F4824}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F59D916-673C-4EC1-BCC8-35330532C311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5687,36 +5687,65 @@
         <v>107</v>
       </c>
       <c r="E33" s="118">
+        <f>E19</f>
         <v>2030</v>
       </c>
-      <c r="F33" s="120">
+      <c r="F33" s="118">
+        <f t="shared" ref="F33:S33" si="0">F19</f>
         <v>1</v>
       </c>
-      <c r="G33" s="120">
+      <c r="G33" s="118">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H33" s="119">
-        <v>100</v>
-      </c>
-      <c r="I33" s="119">
+      <c r="H33" s="118">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="I33" s="118">
+        <f t="shared" si="0"/>
+        <v>81</v>
+      </c>
+      <c r="J33" s="118">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J33" s="119">
+      <c r="K33" s="118">
+        <f t="shared" si="0"/>
+        <v>0.24</v>
+      </c>
+      <c r="L33" s="118">
+        <f t="shared" si="0"/>
+        <v>8.76</v>
+      </c>
+      <c r="M33" s="118">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K33" s="119">
+      <c r="N33" s="118">
+        <f t="shared" si="0"/>
+        <v>0.1</v>
+      </c>
+      <c r="O33" s="118">
+        <f t="shared" si="0"/>
+        <v>0.15</v>
+      </c>
+      <c r="P33" s="118">
+        <f t="shared" si="0"/>
+        <v>0.2</v>
+      </c>
+      <c r="Q33" s="118">
+        <f t="shared" si="0"/>
+        <v>0.25</v>
+      </c>
+      <c r="R33" s="118">
+        <f t="shared" si="0"/>
+        <v>0.3</v>
+      </c>
+      <c r="S33" s="118">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L33" s="119">
-        <v>0</v>
-      </c>
-      <c r="M33" s="121"/>
-      <c r="N33" s="121"/>
-      <c r="O33" s="120"/>
-      <c r="P33" s="120"/>
-      <c r="Q33" s="120"/>
-      <c r="R33" s="121"/>
-      <c r="S33" s="118"/>
       <c r="AD33" s="46"/>
       <c r="AI33" s="99"/>
       <c r="AJ33" s="99"/>
@@ -5745,36 +5774,65 @@
         <v>107</v>
       </c>
       <c r="E34" s="118">
+        <f>E21</f>
         <v>2030</v>
       </c>
-      <c r="F34" s="120">
+      <c r="F34" s="118">
+        <f t="shared" ref="F34:S34" si="1">F21</f>
         <v>0.99</v>
       </c>
-      <c r="G34" s="120">
+      <c r="G34" s="118">
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="H34" s="119">
-        <v>100</v>
-      </c>
-      <c r="I34" s="119">
+      <c r="H34" s="118">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="I34" s="118">
+        <f t="shared" si="1"/>
+        <v>112.9</v>
+      </c>
+      <c r="J34" s="118">
+        <f t="shared" si="1"/>
+        <v>14.26</v>
+      </c>
+      <c r="K34" s="118">
+        <f t="shared" si="1"/>
+        <v>1.22</v>
+      </c>
+      <c r="L34" s="118">
+        <f t="shared" si="1"/>
+        <v>8.76</v>
+      </c>
+      <c r="M34" s="118">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J34" s="119">
+      <c r="N34" s="118">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K34" s="119">
+      <c r="O34" s="118">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L34" s="119">
+      <c r="P34" s="118">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M34" s="121"/>
-      <c r="N34" s="121"/>
-      <c r="O34" s="120"/>
-      <c r="P34" s="120"/>
-      <c r="Q34" s="120"/>
-      <c r="R34" s="121"/>
-      <c r="S34" s="118"/>
+      <c r="Q34" s="118">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="R34" s="118">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S34" s="118">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="AA34" s="38"/>
       <c r="AB34" s="38"/>
       <c r="AD34" s="95"/>

--- a/SubRES_TMPL/SubRES_NewTechs.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F59D916-673C-4EC1-BCC8-35330532C311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87A6BE40-2075-4F11-B6D4-D720C16142DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PRI_Sector_Fuels" sheetId="6" r:id="rId1"/>
@@ -2039,7 +2039,7 @@
     <numFmt numFmtId="165" formatCode="\Te\x\t"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="32" x14ac:knownFonts="1">
+  <fonts count="30" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -2197,20 +2197,6 @@
     <font>
       <sz val="10"/>
       <color rgb="FF00B0F0"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF00B0F0"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -2384,7 +2370,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="138">
+  <cellXfs count="114">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
@@ -2535,74 +2521,44 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="4" applyFont="1"/>
-    <xf numFmtId="165" fontId="25" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="25" fillId="8" borderId="0" xfId="4" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="25" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="25" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="8" borderId="0" xfId="4" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="16" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="16" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="26" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" xfId="4" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="4" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="0" xfId="4" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="4" applyFont="1"/>
+    <xf numFmtId="165" fontId="28" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="28" fillId="8" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="28" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="28" fillId="8" borderId="0" xfId="4" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="4" applyFont="1"/>
-    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="28" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="28" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="30" fillId="8" borderId="0" xfId="4" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="4" applyFont="1"/>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="30" fillId="8" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="31" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="25" fillId="12" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="25" fillId="12" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="16" fillId="12" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="16" fillId="12" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="16" fillId="12" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" xfId="4" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="21" fillId="12" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="21" fillId="12" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="166" fontId="21" fillId="12" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="28" fillId="12" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" xfId="4" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="28" fillId="12" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="28" fillId="12" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="21" fillId="12" borderId="0" xfId="4" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="29" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="28" fillId="8" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="28" fillId="8" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="28" fillId="8" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="26" fillId="8" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="26" fillId="8" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="26" fillId="8" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="21" fillId="8" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="16" fillId="8" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="21" fillId="8" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="166" fontId="21" fillId="8" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="30" fillId="8" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="30" fillId="8" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="30" fillId="8" borderId="0" xfId="21" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="28" fillId="8" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="28" fillId="8" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="28" fillId="8" borderId="0" xfId="21" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="26" fillId="8" borderId="0" xfId="21" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="21" fillId="8" borderId="0" xfId="21" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="21" fillId="8" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="4" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="22">
     <cellStyle name="20% - Accent5 2" xfId="18" xr:uid="{4C3A48E2-3C46-4D12-9A64-54698D8BF8EE}"/>
@@ -3222,8 +3178,8 @@
       <c r="R5" s="39" t="s">
         <v>58</v>
       </c>
-      <c r="S5" s="12"/>
-      <c r="T5" s="12" t="s">
+      <c r="S5" s="39"/>
+      <c r="T5" s="39" t="s">
         <v>88</v>
       </c>
       <c r="U5" s="12"/>
@@ -3248,8 +3204,8 @@
       <c r="R6" s="39" t="s">
         <v>58</v>
       </c>
-      <c r="S6" s="12"/>
-      <c r="T6" s="12" t="s">
+      <c r="S6" s="39"/>
+      <c r="T6" s="39" t="s">
         <v>88</v>
       </c>
       <c r="U6" s="12"/>
@@ -3261,21 +3217,21 @@
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="14"/>
-      <c r="N7" s="12" t="s">
+      <c r="N7" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="O7" s="12"/>
-      <c r="P7" s="12" t="s">
+      <c r="O7" s="39"/>
+      <c r="P7" s="39" t="s">
         <v>72</v>
       </c>
-      <c r="Q7" s="12" t="s">
+      <c r="Q7" s="39" t="s">
         <v>118</v>
       </c>
-      <c r="R7" s="12" t="s">
+      <c r="R7" s="39" t="s">
         <v>58</v>
       </c>
-      <c r="S7" s="12"/>
-      <c r="T7" s="12" t="s">
+      <c r="S7" s="39"/>
+      <c r="T7" s="39" t="s">
         <v>88</v>
       </c>
       <c r="U7" s="12"/>
@@ -3288,21 +3244,21 @@
       <c r="E8" s="14"/>
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
-      <c r="N8" s="37" t="s">
+      <c r="N8" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="O8" s="37"/>
-      <c r="P8" s="37" t="s">
+      <c r="O8" s="39"/>
+      <c r="P8" s="39" t="s">
         <v>119</v>
       </c>
-      <c r="Q8" s="37" t="s">
+      <c r="Q8" s="39" t="s">
         <v>120</v>
       </c>
-      <c r="R8" s="37" t="s">
+      <c r="R8" s="39" t="s">
         <v>58</v>
       </c>
-      <c r="S8" s="12"/>
-      <c r="T8" s="12" t="s">
+      <c r="S8" s="39"/>
+      <c r="T8" s="39" t="s">
         <v>88</v>
       </c>
       <c r="U8" s="12"/>
@@ -3570,7 +3526,7 @@
         <v>58</v>
       </c>
       <c r="S17" s="38"/>
-      <c r="T17" s="12" t="s">
+      <c r="T17" s="39" t="s">
         <v>88</v>
       </c>
     </row>
@@ -3618,7 +3574,7 @@
         <v>58</v>
       </c>
       <c r="S18" s="38"/>
-      <c r="T18" s="12" t="s">
+      <c r="T18" s="39" t="s">
         <v>88</v>
       </c>
     </row>
@@ -3653,17 +3609,18 @@
       <c r="N19" s="38" t="s">
         <v>64</v>
       </c>
-      <c r="P19" s="1" t="s">
+      <c r="O19" s="38"/>
+      <c r="P19" s="38" t="s">
         <v>121</v>
       </c>
-      <c r="Q19" s="1" t="s">
+      <c r="Q19" s="38" t="s">
         <v>124</v>
       </c>
       <c r="R19" s="38" t="s">
         <v>58</v>
       </c>
       <c r="S19" s="38"/>
-      <c r="T19" s="12" t="s">
+      <c r="T19" s="39" t="s">
         <v>88</v>
       </c>
     </row>
@@ -3698,18 +3655,18 @@
       <c r="N20" s="38" t="s">
         <v>64</v>
       </c>
-      <c r="O20" s="14"/>
-      <c r="P20" s="14" t="s">
+      <c r="O20" s="38"/>
+      <c r="P20" s="38" t="s">
         <v>122</v>
       </c>
-      <c r="Q20" s="14" t="s">
+      <c r="Q20" s="38" t="s">
         <v>123</v>
       </c>
       <c r="R20" s="38" t="s">
         <v>58</v>
       </c>
       <c r="S20" s="38"/>
-      <c r="T20" s="12" t="s">
+      <c r="T20" s="39" t="s">
         <v>88</v>
       </c>
     </row>
@@ -4077,7 +4034,7 @@
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" style="45" customWidth="1"/>
-    <col min="2" max="2" width="12.21875" style="45" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.109375" style="45" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="25.77734375" style="45" customWidth="1"/>
     <col min="4" max="4" width="13.77734375" style="45" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20" style="45" bestFit="1" customWidth="1"/>
@@ -4235,19 +4192,19 @@
       <c r="E5" s="53"/>
       <c r="F5" s="53"/>
       <c r="G5" s="53"/>
-      <c r="V5" s="72" t="s">
+      <c r="V5" s="45" t="s">
         <v>69</v>
       </c>
       <c r="X5" s="45" t="s">
         <v>130</v>
       </c>
-      <c r="Y5" s="72" t="s">
+      <c r="Y5" s="45" t="s">
         <v>131</v>
       </c>
-      <c r="Z5" s="72" t="s">
+      <c r="Z5" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="AB5" s="72" t="s">
+      <c r="AB5" s="45" t="s">
         <v>88</v>
       </c>
     </row>
@@ -4258,19 +4215,19 @@
       <c r="E6" s="53"/>
       <c r="F6" s="53"/>
       <c r="G6" s="53"/>
-      <c r="V6" s="72" t="s">
+      <c r="V6" s="45" t="s">
         <v>69</v>
       </c>
       <c r="X6" s="45" t="s">
         <v>129</v>
       </c>
-      <c r="Y6" s="72" t="s">
+      <c r="Y6" s="45" t="s">
         <v>132</v>
       </c>
-      <c r="Z6" s="72" t="s">
+      <c r="Z6" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="AB6" s="72" t="s">
+      <c r="AB6" s="45" t="s">
         <v>88</v>
       </c>
     </row>
@@ -4290,10 +4247,10 @@
       <c r="Y7" s="45" t="s">
         <v>135</v>
       </c>
-      <c r="Z7" s="72" t="s">
+      <c r="Z7" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="AB7" s="72" t="s">
+      <c r="AB7" s="45" t="s">
         <v>88</v>
       </c>
     </row>
@@ -4308,11 +4265,11 @@
       <c r="Y8" s="50" t="s">
         <v>149</v>
       </c>
-      <c r="Z8" s="72" t="s">
+      <c r="Z8" s="45" t="s">
         <v>58</v>
       </c>
       <c r="AA8" s="50"/>
-      <c r="AB8" s="72" t="s">
+      <c r="AB8" s="45" t="s">
         <v>88</v>
       </c>
       <c r="AE8" s="46"/>
@@ -4328,10 +4285,10 @@
       <c r="Y9" s="50" t="s">
         <v>151</v>
       </c>
-      <c r="Z9" s="72" t="s">
+      <c r="Z9" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="AB9" s="72" t="s">
+      <c r="AB9" s="45" t="s">
         <v>88</v>
       </c>
       <c r="AC9" s="50"/>
@@ -4617,226 +4574,216 @@
       <c r="AJ18" s="39"/>
       <c r="AY18" s="46"/>
     </row>
-    <row r="19" spans="2:51" s="80" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="80" t="str">
+    <row r="19" spans="2:51" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="45" t="str">
         <f>X19</f>
         <v>Furnace</v>
       </c>
-      <c r="C19" s="81" t="str">
+      <c r="C19" s="50" t="str">
         <f>X8</f>
         <v>DECELC</v>
       </c>
-      <c r="D19" s="81" t="s">
+      <c r="D19" s="50" t="s">
         <v>107</v>
       </c>
-      <c r="E19" s="109">
+      <c r="E19" s="96">
         <v>2030</v>
       </c>
-      <c r="F19" s="110">
+      <c r="F19" s="97">
         <v>1</v>
       </c>
-      <c r="G19" s="110">
+      <c r="G19" s="97">
         <v>1</v>
       </c>
-      <c r="H19" s="109">
+      <c r="H19" s="96">
         <v>25</v>
       </c>
-      <c r="I19" s="110">
+      <c r="I19" s="97">
         <v>81</v>
       </c>
-      <c r="J19" s="110">
+      <c r="J19" s="97">
         <v>0</v>
       </c>
-      <c r="K19" s="110">
+      <c r="K19" s="97">
         <v>0.24</v>
       </c>
-      <c r="L19" s="110">
+      <c r="L19" s="97">
         <v>8.76</v>
       </c>
-      <c r="M19" s="109"/>
-      <c r="N19" s="110">
-        <v>0.1</v>
-      </c>
-      <c r="O19" s="110">
-        <v>0.15</v>
-      </c>
-      <c r="P19" s="110">
-        <v>0.2</v>
-      </c>
-      <c r="Q19" s="110">
-        <v>0.25</v>
-      </c>
-      <c r="R19" s="110">
-        <v>0.3</v>
-      </c>
-      <c r="S19" s="109"/>
-      <c r="T19" s="82"/>
-      <c r="U19" s="82"/>
-      <c r="V19" s="83" t="s">
+      <c r="M19" s="96"/>
+      <c r="N19" s="97"/>
+      <c r="O19" s="97"/>
+      <c r="P19" s="97"/>
+      <c r="Q19" s="97"/>
+      <c r="R19" s="97"/>
+      <c r="S19" s="96"/>
+      <c r="T19" s="79"/>
+      <c r="U19" s="79"/>
+      <c r="V19" s="60" t="s">
         <v>127</v>
       </c>
-      <c r="W19" s="83"/>
-      <c r="X19" s="84" t="s">
+      <c r="W19" s="60"/>
+      <c r="X19" s="61" t="s">
         <v>66</v>
       </c>
-      <c r="Y19" s="85" t="s">
+      <c r="Y19" s="62" t="s">
         <v>139</v>
       </c>
-      <c r="Z19" s="80" t="s">
+      <c r="Z19" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="AA19" s="80" t="s">
+      <c r="AA19" s="45" t="s">
         <v>87</v>
       </c>
-      <c r="AB19" s="86" t="s">
+      <c r="AB19" s="63" t="s">
         <v>88</v>
       </c>
-      <c r="AC19" s="82"/>
-      <c r="AD19" s="82"/>
-      <c r="AI19" s="87"/>
-      <c r="AJ19" s="88"/>
-      <c r="AY19" s="82"/>
+      <c r="AC19" s="79"/>
+      <c r="AD19" s="79"/>
+      <c r="AI19" s="80"/>
+      <c r="AJ19" s="81"/>
+      <c r="AY19" s="79"/>
     </row>
     <row r="20" spans="2:51" s="72" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="72" t="str">
+      <c r="B20" s="45" t="str">
         <f>X$20</f>
         <v>BIOBoiler</v>
       </c>
-      <c r="C20" s="72" t="str">
+      <c r="C20" s="45" t="str">
         <f>PRI_Sector_Fuels!P5</f>
         <v>MANBIOMIN</v>
       </c>
-      <c r="D20" s="78" t="str">
+      <c r="D20" s="50" t="str">
         <f>X9</f>
         <v>DECRHEAT</v>
       </c>
-      <c r="E20" s="111">
+      <c r="E20" s="96">
         <v>2030</v>
       </c>
-      <c r="F20" s="112">
+      <c r="F20" s="97">
         <v>0.7</v>
       </c>
-      <c r="G20" s="112">
+      <c r="G20" s="97">
         <v>0.98</v>
       </c>
-      <c r="H20" s="111">
+      <c r="H20" s="96">
         <v>25</v>
       </c>
-      <c r="I20" s="112">
+      <c r="I20" s="97">
         <v>797.9</v>
       </c>
-      <c r="J20" s="112">
+      <c r="J20" s="97">
         <v>48.48</v>
       </c>
-      <c r="K20" s="112">
+      <c r="K20" s="97">
         <v>3.75</v>
       </c>
-      <c r="L20" s="112">
+      <c r="L20" s="97">
         <v>8.76</v>
       </c>
-      <c r="M20" s="111"/>
-      <c r="N20" s="113"/>
-      <c r="O20" s="111"/>
-      <c r="P20" s="111"/>
-      <c r="Q20" s="111"/>
-      <c r="R20" s="111"/>
-      <c r="S20" s="111"/>
-      <c r="T20" s="89"/>
-      <c r="U20" s="89"/>
-      <c r="V20" s="79" t="s">
+      <c r="M20" s="96"/>
+      <c r="N20" s="98"/>
+      <c r="O20" s="96"/>
+      <c r="P20" s="96"/>
+      <c r="Q20" s="96"/>
+      <c r="R20" s="96"/>
+      <c r="S20" s="96"/>
+      <c r="T20" s="82"/>
+      <c r="U20" s="82"/>
+      <c r="V20" s="60" t="s">
         <v>138</v>
       </c>
-      <c r="W20" s="79"/>
-      <c r="X20" s="90" t="s">
+      <c r="W20" s="60"/>
+      <c r="X20" s="61" t="s">
         <v>94</v>
       </c>
-      <c r="Y20" s="91" t="s">
+      <c r="Y20" s="62" t="s">
         <v>140</v>
       </c>
-      <c r="Z20" s="72" t="s">
+      <c r="Z20" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="AA20" s="72" t="s">
+      <c r="AA20" s="45" t="s">
         <v>87</v>
       </c>
-      <c r="AB20" s="92" t="s">
+      <c r="AB20" s="63" t="s">
         <v>88</v>
       </c>
-      <c r="AC20" s="89"/>
-      <c r="AD20" s="89"/>
+      <c r="AC20" s="82"/>
+      <c r="AD20" s="82"/>
       <c r="AI20" s="14"/>
       <c r="AJ20" s="12"/>
-      <c r="AY20" s="89"/>
-    </row>
-    <row r="21" spans="2:51" s="80" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="80" t="str">
+      <c r="AY20" s="82"/>
+    </row>
+    <row r="21" spans="2:51" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="45" t="str">
         <f>X23</f>
         <v>ELCBoiler</v>
       </c>
-      <c r="C21" s="81" t="str">
+      <c r="C21" s="50" t="str">
         <f>X8</f>
         <v>DECELC</v>
       </c>
-      <c r="D21" s="81" t="s">
+      <c r="D21" s="50" t="s">
         <v>107</v>
       </c>
-      <c r="E21" s="109">
+      <c r="E21" s="96">
         <v>2030</v>
       </c>
-      <c r="F21" s="110">
+      <c r="F21" s="97">
         <v>0.99</v>
       </c>
-      <c r="G21" s="110">
+      <c r="G21" s="97">
         <v>1</v>
       </c>
-      <c r="H21" s="109">
+      <c r="H21" s="96">
         <v>25</v>
       </c>
-      <c r="I21" s="110">
+      <c r="I21" s="97">
         <v>112.9</v>
       </c>
-      <c r="J21" s="110">
+      <c r="J21" s="97">
         <v>14.26</v>
       </c>
-      <c r="K21" s="110">
+      <c r="K21" s="97">
         <v>1.22</v>
       </c>
-      <c r="L21" s="110">
+      <c r="L21" s="97">
         <v>8.76</v>
       </c>
-      <c r="M21" s="109"/>
-      <c r="N21" s="114"/>
-      <c r="O21" s="114"/>
-      <c r="P21" s="114"/>
-      <c r="Q21" s="114"/>
-      <c r="R21" s="114"/>
-      <c r="S21" s="109"/>
-      <c r="T21" s="82"/>
-      <c r="U21" s="82"/>
-      <c r="V21" s="83" t="s">
+      <c r="M21" s="96"/>
+      <c r="N21" s="99"/>
+      <c r="O21" s="99"/>
+      <c r="P21" s="99"/>
+      <c r="Q21" s="99"/>
+      <c r="R21" s="99"/>
+      <c r="S21" s="96"/>
+      <c r="T21" s="79"/>
+      <c r="U21" s="79"/>
+      <c r="V21" s="60" t="s">
         <v>127</v>
       </c>
-      <c r="W21" s="83"/>
-      <c r="X21" s="84" t="s">
+      <c r="W21" s="60"/>
+      <c r="X21" s="61" t="s">
         <v>95</v>
       </c>
-      <c r="Y21" s="85" t="s">
+      <c r="Y21" s="62" t="s">
         <v>141</v>
       </c>
-      <c r="Z21" s="80" t="s">
+      <c r="Z21" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="AA21" s="80" t="s">
+      <c r="AA21" s="45" t="s">
         <v>87</v>
       </c>
-      <c r="AB21" s="86" t="s">
+      <c r="AB21" s="63" t="s">
         <v>88</v>
       </c>
-      <c r="AC21" s="82"/>
-      <c r="AD21" s="82"/>
-      <c r="AI21" s="87"/>
-      <c r="AJ21" s="88"/>
-      <c r="AY21" s="82"/>
+      <c r="AC21" s="79"/>
+      <c r="AD21" s="79"/>
+      <c r="AI21" s="80"/>
+      <c r="AJ21" s="81"/>
+      <c r="AY21" s="79"/>
     </row>
     <row r="22" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B22" s="45" t="str">
@@ -4850,47 +4797,37 @@
       <c r="D22" s="50" t="s">
         <v>108</v>
       </c>
-      <c r="E22" s="115">
+      <c r="E22" s="96">
         <v>2030</v>
       </c>
-      <c r="F22" s="116">
+      <c r="F22" s="97">
         <v>0.55600000000000005</v>
       </c>
-      <c r="G22" s="116">
+      <c r="G22" s="97">
         <v>0.98</v>
       </c>
-      <c r="H22" s="115">
+      <c r="H22" s="96">
         <v>25</v>
       </c>
-      <c r="I22" s="116">
+      <c r="I22" s="97">
         <v>297.10000000000002</v>
       </c>
-      <c r="J22" s="116">
+      <c r="J22" s="97">
         <v>4.46</v>
       </c>
-      <c r="K22" s="116">
+      <c r="K22" s="97">
         <v>0.45</v>
       </c>
-      <c r="L22" s="116">
+      <c r="L22" s="97">
         <v>8.76</v>
       </c>
-      <c r="M22" s="115"/>
-      <c r="N22" s="116">
-        <v>0.1</v>
-      </c>
-      <c r="O22" s="116">
-        <v>0.15</v>
-      </c>
-      <c r="P22" s="116">
-        <v>0.2</v>
-      </c>
-      <c r="Q22" s="116">
-        <v>0.25</v>
-      </c>
-      <c r="R22" s="116">
-        <v>0.3</v>
-      </c>
-      <c r="S22" s="115"/>
+      <c r="M22" s="96"/>
+      <c r="N22" s="97"/>
+      <c r="O22" s="97"/>
+      <c r="P22" s="97"/>
+      <c r="Q22" s="97"/>
+      <c r="R22" s="97"/>
+      <c r="S22" s="96"/>
       <c r="V22" s="60" t="s">
         <v>127</v>
       </c>
@@ -4938,37 +4875,37 @@
       <c r="D23" s="50" t="s">
         <v>107</v>
       </c>
-      <c r="E23" s="115">
+      <c r="E23" s="96">
         <v>2030</v>
       </c>
-      <c r="F23" s="116">
+      <c r="F23" s="97">
         <v>0.75</v>
       </c>
-      <c r="G23" s="116">
+      <c r="G23" s="97">
         <v>0.99</v>
       </c>
-      <c r="H23" s="115">
+      <c r="H23" s="96">
         <v>25</v>
       </c>
-      <c r="I23" s="116">
+      <c r="I23" s="97">
         <v>61.4</v>
       </c>
-      <c r="J23" s="116">
+      <c r="J23" s="97">
         <v>2.57</v>
       </c>
-      <c r="K23" s="116">
+      <c r="K23" s="97">
         <v>1.35</v>
       </c>
-      <c r="L23" s="116">
+      <c r="L23" s="97">
         <v>8.76</v>
       </c>
-      <c r="M23" s="115"/>
-      <c r="N23" s="117"/>
-      <c r="O23" s="115"/>
-      <c r="P23" s="115"/>
-      <c r="Q23" s="115"/>
-      <c r="R23" s="115"/>
-      <c r="S23" s="115"/>
+      <c r="M23" s="96"/>
+      <c r="N23" s="98"/>
+      <c r="O23" s="96"/>
+      <c r="P23" s="96"/>
+      <c r="Q23" s="96"/>
+      <c r="R23" s="96"/>
+      <c r="S23" s="96"/>
       <c r="V23" s="60" t="s">
         <v>127</v>
       </c>
@@ -5016,37 +4953,37 @@
       <c r="D24" s="50" t="s">
         <v>129</v>
       </c>
-      <c r="E24" s="115">
+      <c r="E24" s="96">
         <v>2030</v>
       </c>
-      <c r="F24" s="112">
+      <c r="F24" s="97">
         <v>1</v>
       </c>
-      <c r="G24" s="116">
+      <c r="G24" s="97">
         <v>0.97</v>
       </c>
-      <c r="H24" s="115">
+      <c r="H24" s="96">
         <v>25</v>
       </c>
-      <c r="I24" s="116">
+      <c r="I24" s="97">
         <v>1041</v>
       </c>
-      <c r="J24" s="116">
+      <c r="J24" s="97">
         <v>38</v>
       </c>
-      <c r="K24" s="116">
+      <c r="K24" s="97">
         <v>0</v>
       </c>
-      <c r="L24" s="116">
+      <c r="L24" s="97">
         <v>8.76</v>
       </c>
-      <c r="M24" s="117"/>
-      <c r="N24" s="117"/>
-      <c r="O24" s="116"/>
-      <c r="P24" s="116"/>
-      <c r="Q24" s="116"/>
-      <c r="R24" s="117"/>
-      <c r="S24" s="115">
+      <c r="M24" s="98"/>
+      <c r="N24" s="98"/>
+      <c r="O24" s="97"/>
+      <c r="P24" s="97"/>
+      <c r="Q24" s="97"/>
+      <c r="R24" s="98"/>
+      <c r="S24" s="97">
         <v>0.2</v>
       </c>
       <c r="V24" s="60" t="s">
@@ -5096,37 +5033,37 @@
       <c r="D25" s="50" t="s">
         <v>130</v>
       </c>
-      <c r="E25" s="115">
+      <c r="E25" s="96">
         <v>2030</v>
       </c>
-      <c r="F25" s="112">
+      <c r="F25" s="97">
         <v>0.20499999999999999</v>
       </c>
-      <c r="G25" s="116">
+      <c r="G25" s="97">
         <v>0.99</v>
       </c>
-      <c r="H25" s="115">
+      <c r="H25" s="96">
         <v>25</v>
       </c>
-      <c r="I25" s="116">
+      <c r="I25" s="97">
         <v>691</v>
       </c>
-      <c r="J25" s="116">
+      <c r="J25" s="97">
         <v>6.99</v>
       </c>
-      <c r="K25" s="116">
+      <c r="K25" s="97">
         <v>0</v>
       </c>
-      <c r="L25" s="116">
+      <c r="L25" s="97">
         <v>8.76</v>
       </c>
-      <c r="M25" s="117"/>
-      <c r="N25" s="117"/>
-      <c r="O25" s="116"/>
-      <c r="P25" s="116"/>
-      <c r="Q25" s="116"/>
-      <c r="R25" s="117"/>
-      <c r="S25" s="115">
+      <c r="M25" s="98"/>
+      <c r="N25" s="98"/>
+      <c r="O25" s="97"/>
+      <c r="P25" s="97"/>
+      <c r="Q25" s="97"/>
+      <c r="R25" s="98"/>
+      <c r="S25" s="97">
         <v>0.3</v>
       </c>
       <c r="V25" s="60" t="s">
@@ -5164,67 +5101,67 @@
       <c r="AV25" s="45"/>
       <c r="AW25" s="45"/>
     </row>
-    <row r="26" spans="2:51" s="89" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="78" t="str">
+    <row r="26" spans="2:51" s="82" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="50" t="str">
         <f>X24</f>
         <v>CSP</v>
       </c>
-      <c r="C26" s="72" t="str">
+      <c r="C26" s="45" t="str">
         <f>PRI_Sector_Fuels!D20</f>
         <v>SOLAR</v>
       </c>
-      <c r="D26" s="78" t="str">
+      <c r="D26" s="50" t="str">
         <f>X9</f>
         <v>DECRHEAT</v>
       </c>
-      <c r="E26" s="111">
+      <c r="E26" s="96">
         <v>2030</v>
       </c>
-      <c r="F26" s="112">
+      <c r="F26" s="97">
         <v>0.4</v>
       </c>
-      <c r="G26" s="112">
+      <c r="G26" s="97">
         <v>1</v>
       </c>
-      <c r="H26" s="111">
+      <c r="H26" s="96">
         <v>25</v>
       </c>
-      <c r="I26" s="112">
+      <c r="I26" s="97">
         <v>3677</v>
       </c>
-      <c r="J26" s="112">
+      <c r="J26" s="97">
         <v>0</v>
       </c>
-      <c r="K26" s="112">
+      <c r="K26" s="97">
         <v>14</v>
       </c>
-      <c r="L26" s="112">
+      <c r="L26" s="97">
         <v>8.76</v>
       </c>
-      <c r="M26" s="113"/>
-      <c r="N26" s="113"/>
-      <c r="O26" s="112"/>
-      <c r="P26" s="112"/>
-      <c r="Q26" s="112"/>
-      <c r="R26" s="113"/>
-      <c r="S26" s="111"/>
-      <c r="V26" s="79" t="s">
+      <c r="M26" s="98"/>
+      <c r="N26" s="98"/>
+      <c r="O26" s="97"/>
+      <c r="P26" s="97"/>
+      <c r="Q26" s="97"/>
+      <c r="R26" s="98"/>
+      <c r="S26" s="96"/>
+      <c r="V26" s="60" t="s">
         <v>69</v>
       </c>
-      <c r="W26" s="79"/>
-      <c r="X26" s="90" t="s">
+      <c r="W26" s="60"/>
+      <c r="X26" s="61" t="s">
         <v>90</v>
       </c>
-      <c r="Y26" s="91" t="s">
+      <c r="Y26" s="62" t="s">
         <v>146</v>
       </c>
-      <c r="Z26" s="72" t="s">
+      <c r="Z26" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="AA26" s="72" t="s">
+      <c r="AA26" s="45" t="s">
         <v>87</v>
       </c>
-      <c r="AB26" s="89" t="s">
+      <c r="AB26" s="46" t="s">
         <v>88</v>
       </c>
       <c r="AI26" s="14"/>
@@ -5252,37 +5189,39 @@
       <c r="D27" s="50" t="s">
         <v>106</v>
       </c>
-      <c r="E27" s="115">
+      <c r="E27" s="96">
         <v>2030</v>
       </c>
-      <c r="F27" s="112">
+      <c r="F27" s="97">
         <v>0.3</v>
       </c>
-      <c r="G27" s="116">
+      <c r="G27" s="97">
         <v>1</v>
       </c>
-      <c r="H27" s="115">
+      <c r="H27" s="96">
         <v>25</v>
       </c>
-      <c r="I27" s="116">
+      <c r="I27" s="97">
         <v>0</v>
       </c>
-      <c r="J27" s="116">
+      <c r="J27" s="97">
         <v>0</v>
       </c>
-      <c r="K27" s="116">
+      <c r="K27" s="97">
         <v>0</v>
       </c>
-      <c r="L27" s="116">
+      <c r="L27" s="97">
         <v>8.76</v>
       </c>
-      <c r="M27" s="117"/>
-      <c r="N27" s="117"/>
-      <c r="O27" s="116"/>
-      <c r="P27" s="116"/>
-      <c r="Q27" s="116"/>
-      <c r="R27" s="117"/>
-      <c r="S27" s="115"/>
+      <c r="M27" s="98">
+        <v>0.202158</v>
+      </c>
+      <c r="N27" s="98"/>
+      <c r="O27" s="97"/>
+      <c r="P27" s="97"/>
+      <c r="Q27" s="97"/>
+      <c r="R27" s="98"/>
+      <c r="S27" s="96"/>
       <c r="V27" s="60" t="s">
         <v>69</v>
       </c>
@@ -5318,61 +5257,61 @@
       <c r="AV27" s="45"/>
       <c r="AW27" s="45"/>
     </row>
-    <row r="28" spans="2:51" s="94" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="93" t="str">
+    <row r="28" spans="2:51" s="84" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="50" t="str">
         <f>X27</f>
         <v>DECPOWER</v>
       </c>
-      <c r="C28" s="93" t="str">
+      <c r="C28" s="50" t="str">
         <f>X6</f>
         <v>WNDELC</v>
       </c>
-      <c r="D28" s="93" t="str">
+      <c r="D28" s="50" t="str">
         <f>X8</f>
         <v>DECELC</v>
       </c>
-      <c r="E28" s="118">
+      <c r="E28" s="96">
         <v>2030</v>
       </c>
-      <c r="F28" s="119">
+      <c r="F28" s="99">
         <v>1</v>
       </c>
-      <c r="G28" s="119">
+      <c r="G28" s="99">
         <v>1</v>
       </c>
-      <c r="H28" s="118">
+      <c r="H28" s="96">
         <v>100</v>
       </c>
-      <c r="I28" s="120">
+      <c r="I28" s="97">
         <v>0</v>
       </c>
-      <c r="J28" s="119">
+      <c r="J28" s="99">
         <v>0</v>
       </c>
-      <c r="K28" s="119">
+      <c r="K28" s="99">
         <v>0</v>
       </c>
-      <c r="L28" s="120">
+      <c r="L28" s="97">
         <v>8.76</v>
       </c>
-      <c r="M28" s="121"/>
-      <c r="N28" s="121"/>
-      <c r="O28" s="120"/>
-      <c r="P28" s="120"/>
-      <c r="Q28" s="120"/>
-      <c r="R28" s="121"/>
-      <c r="S28" s="118"/>
-      <c r="V28" s="96" t="s">
+      <c r="M28" s="98"/>
+      <c r="N28" s="98"/>
+      <c r="O28" s="97"/>
+      <c r="P28" s="97"/>
+      <c r="Q28" s="97"/>
+      <c r="R28" s="98"/>
+      <c r="S28" s="96"/>
+      <c r="V28" s="60" t="s">
         <v>69</v>
       </c>
-      <c r="W28" s="96"/>
-      <c r="X28" s="97" t="s">
+      <c r="W28" s="60"/>
+      <c r="X28" s="61" t="s">
         <v>136</v>
       </c>
-      <c r="Y28" s="98" t="s">
+      <c r="Y28" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="Z28" s="95" t="s">
+      <c r="Z28" s="45" t="s">
         <v>58</v>
       </c>
       <c r="AA28" s="45" t="s">
@@ -5381,66 +5320,66 @@
       <c r="AB28" s="46" t="s">
         <v>88</v>
       </c>
-      <c r="AI28" s="99"/>
-      <c r="AJ28" s="99"/>
-      <c r="AK28" s="95"/>
-      <c r="AL28" s="95"/>
-      <c r="AM28" s="95"/>
-      <c r="AN28" s="95"/>
-      <c r="AO28" s="95"/>
-      <c r="AP28" s="95"/>
-      <c r="AQ28" s="95"/>
-      <c r="AR28" s="95"/>
-      <c r="AS28" s="95"/>
-      <c r="AT28" s="95"/>
-      <c r="AU28" s="95"/>
-      <c r="AV28" s="95"/>
-      <c r="AW28" s="95"/>
-    </row>
-    <row r="29" spans="2:51" s="94" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="93" t="str">
+      <c r="AI28" s="86"/>
+      <c r="AJ28" s="86"/>
+      <c r="AK28" s="85"/>
+      <c r="AL28" s="85"/>
+      <c r="AM28" s="85"/>
+      <c r="AN28" s="85"/>
+      <c r="AO28" s="85"/>
+      <c r="AP28" s="85"/>
+      <c r="AQ28" s="85"/>
+      <c r="AR28" s="85"/>
+      <c r="AS28" s="85"/>
+      <c r="AT28" s="85"/>
+      <c r="AU28" s="85"/>
+      <c r="AV28" s="85"/>
+      <c r="AW28" s="85"/>
+    </row>
+    <row r="29" spans="2:51" s="84" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="50" t="str">
         <f>X27</f>
         <v>DECPOWER</v>
       </c>
-      <c r="C29" s="93" t="str">
+      <c r="C29" s="50" t="str">
         <f>X5</f>
         <v>SOLELC</v>
       </c>
-      <c r="D29" s="93" t="str">
+      <c r="D29" s="50" t="str">
         <f>X8</f>
         <v>DECELC</v>
       </c>
-      <c r="E29" s="118">
+      <c r="E29" s="96">
         <v>2030</v>
       </c>
-      <c r="F29" s="119">
+      <c r="F29" s="99">
         <v>1</v>
       </c>
-      <c r="G29" s="119">
+      <c r="G29" s="99">
         <v>1</v>
       </c>
-      <c r="H29" s="118">
+      <c r="H29" s="96">
         <v>100</v>
       </c>
-      <c r="I29" s="120">
+      <c r="I29" s="97">
         <v>0</v>
       </c>
-      <c r="J29" s="119">
+      <c r="J29" s="99">
         <v>0</v>
       </c>
-      <c r="K29" s="119">
+      <c r="K29" s="99">
         <v>0</v>
       </c>
-      <c r="L29" s="120">
+      <c r="L29" s="97">
         <v>8.76</v>
       </c>
-      <c r="M29" s="121"/>
-      <c r="N29" s="121"/>
-      <c r="O29" s="120"/>
-      <c r="P29" s="120"/>
-      <c r="Q29" s="120"/>
-      <c r="R29" s="121"/>
-      <c r="S29" s="118"/>
+      <c r="M29" s="98"/>
+      <c r="N29" s="98"/>
+      <c r="O29" s="97"/>
+      <c r="P29" s="97"/>
+      <c r="Q29" s="97"/>
+      <c r="R29" s="98"/>
+      <c r="S29" s="96"/>
       <c r="V29" s="46" t="s">
         <v>127</v>
       </c>
@@ -5451,31 +5390,31 @@
       <c r="Y29" s="46" t="s">
         <v>153</v>
       </c>
-      <c r="Z29" s="95" t="s">
+      <c r="Z29" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="AA29" s="95" t="s">
+      <c r="AA29" s="45" t="s">
         <v>87</v>
       </c>
-      <c r="AB29" s="94" t="s">
+      <c r="AB29" s="46" t="s">
         <v>88</v>
       </c>
       <c r="AC29" s="46"/>
-      <c r="AI29" s="99"/>
-      <c r="AJ29" s="99"/>
-      <c r="AK29" s="95"/>
-      <c r="AL29" s="95"/>
-      <c r="AM29" s="95"/>
-      <c r="AN29" s="95"/>
-      <c r="AO29" s="95"/>
-      <c r="AP29" s="95"/>
-      <c r="AQ29" s="95"/>
-      <c r="AR29" s="95"/>
-      <c r="AS29" s="95"/>
-      <c r="AT29" s="95"/>
-      <c r="AU29" s="95"/>
-      <c r="AV29" s="95"/>
-      <c r="AW29" s="95"/>
+      <c r="AI29" s="86"/>
+      <c r="AJ29" s="86"/>
+      <c r="AK29" s="85"/>
+      <c r="AL29" s="85"/>
+      <c r="AM29" s="85"/>
+      <c r="AN29" s="85"/>
+      <c r="AO29" s="85"/>
+      <c r="AP29" s="85"/>
+      <c r="AQ29" s="85"/>
+      <c r="AR29" s="85"/>
+      <c r="AS29" s="85"/>
+      <c r="AT29" s="85"/>
+      <c r="AU29" s="85"/>
+      <c r="AV29" s="85"/>
+      <c r="AW29" s="85"/>
     </row>
     <row r="30" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B30" s="50" t="str">
@@ -5488,57 +5427,56 @@
       <c r="D30" s="50" t="s">
         <v>134</v>
       </c>
-      <c r="E30" s="115">
+      <c r="E30" s="96">
         <v>2030</v>
       </c>
-      <c r="F30" s="122">
+      <c r="F30" s="99">
         <v>0.35</v>
       </c>
-      <c r="G30" s="122">
+      <c r="G30" s="99">
         <v>0.98</v>
       </c>
-      <c r="H30" s="115">
+      <c r="H30" s="96">
         <v>20</v>
       </c>
-      <c r="I30" s="123">
+      <c r="I30" s="100">
         <v>3242</v>
       </c>
-      <c r="J30" s="116">
+      <c r="J30" s="97">
         <v>129.68</v>
       </c>
-      <c r="K30" s="116">
+      <c r="K30" s="97">
         <v>0</v>
       </c>
-      <c r="L30" s="116">
+      <c r="L30" s="97">
         <v>8.76</v>
       </c>
-      <c r="M30" s="117"/>
-      <c r="N30" s="117"/>
-      <c r="O30" s="116"/>
-      <c r="P30" s="116"/>
-      <c r="Q30" s="116"/>
-      <c r="R30" s="117"/>
-      <c r="S30" s="115"/>
-      <c r="V30" s="72" t="s">
+      <c r="M30" s="98"/>
+      <c r="N30" s="98"/>
+      <c r="O30" s="97"/>
+      <c r="P30" s="97"/>
+      <c r="Q30" s="97"/>
+      <c r="R30" s="98"/>
+      <c r="S30" s="96"/>
+      <c r="V30" s="45" t="s">
         <v>127</v>
       </c>
-      <c r="W30" s="94"/>
-      <c r="X30" s="94" t="s">
+      <c r="X30" s="46" t="s">
         <v>156</v>
       </c>
-      <c r="Y30" s="94" t="s">
+      <c r="Y30" s="46" t="s">
         <v>155</v>
       </c>
-      <c r="Z30" s="95" t="s">
+      <c r="Z30" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="AA30" s="95" t="s">
+      <c r="AA30" s="45" t="s">
         <v>87</v>
       </c>
-      <c r="AB30" s="94" t="s">
+      <c r="AB30" s="46" t="s">
         <v>88</v>
       </c>
-      <c r="AC30" s="94"/>
+      <c r="AC30" s="84"/>
       <c r="AI30" s="38"/>
       <c r="AJ30" s="38"/>
       <c r="AK30" s="45"/>
@@ -5555,431 +5493,389 @@
       <c r="AV30" s="45"/>
       <c r="AW30" s="45"/>
     </row>
-    <row r="31" spans="2:51" s="94" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:51" s="84" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B31" s="50" t="str">
         <f>X27</f>
         <v>DECPOWER</v>
       </c>
-      <c r="C31" s="95" t="str">
+      <c r="C31" s="45" t="str">
         <f>X7</f>
         <v>BIOELC</v>
       </c>
-      <c r="D31" s="93" t="str">
+      <c r="D31" s="50" t="str">
         <f>X8</f>
         <v>DECELC</v>
       </c>
-      <c r="E31" s="118">
+      <c r="E31" s="96">
         <v>2030</v>
       </c>
-      <c r="F31" s="120">
+      <c r="F31" s="97">
         <v>1</v>
       </c>
-      <c r="G31" s="120">
+      <c r="G31" s="97">
         <v>1</v>
       </c>
-      <c r="H31" s="119">
+      <c r="H31" s="99">
         <v>100</v>
       </c>
-      <c r="I31" s="119">
+      <c r="I31" s="99">
         <v>0</v>
       </c>
-      <c r="J31" s="119">
+      <c r="J31" s="99">
         <v>0</v>
       </c>
-      <c r="K31" s="119">
+      <c r="K31" s="99">
         <v>0</v>
       </c>
-      <c r="L31" s="119">
+      <c r="L31" s="99">
         <v>0</v>
       </c>
-      <c r="M31" s="121"/>
-      <c r="N31" s="121"/>
-      <c r="O31" s="120"/>
-      <c r="P31" s="120"/>
-      <c r="Q31" s="120"/>
-      <c r="R31" s="121"/>
-      <c r="S31" s="118"/>
+      <c r="M31" s="98"/>
+      <c r="N31" s="98"/>
+      <c r="O31" s="97"/>
+      <c r="P31" s="97"/>
+      <c r="Q31" s="97"/>
+      <c r="R31" s="98"/>
+      <c r="S31" s="96"/>
       <c r="AD31" s="46"/>
-      <c r="AI31" s="99"/>
-      <c r="AJ31" s="99"/>
-      <c r="AK31" s="95"/>
-      <c r="AL31" s="95"/>
-      <c r="AM31" s="95"/>
-      <c r="AN31" s="95"/>
-      <c r="AO31" s="95"/>
-      <c r="AP31" s="95"/>
-      <c r="AQ31" s="95"/>
-      <c r="AR31" s="95"/>
-      <c r="AS31" s="95"/>
-      <c r="AT31" s="95"/>
-      <c r="AU31" s="95"/>
-      <c r="AV31" s="95"/>
-      <c r="AW31" s="95"/>
-    </row>
-    <row r="32" spans="2:51" s="94" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="93" t="str">
+      <c r="AI31" s="86"/>
+      <c r="AJ31" s="86"/>
+      <c r="AK31" s="85"/>
+      <c r="AL31" s="85"/>
+      <c r="AM31" s="85"/>
+      <c r="AN31" s="85"/>
+      <c r="AO31" s="85"/>
+      <c r="AP31" s="85"/>
+      <c r="AQ31" s="85"/>
+      <c r="AR31" s="85"/>
+      <c r="AS31" s="85"/>
+      <c r="AT31" s="85"/>
+      <c r="AU31" s="85"/>
+      <c r="AV31" s="85"/>
+      <c r="AW31" s="85"/>
+    </row>
+    <row r="32" spans="2:51" s="84" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="50" t="str">
         <f>X29</f>
         <v>DECTHT</v>
       </c>
-      <c r="C32" s="93" t="str">
+      <c r="C32" s="50" t="str">
         <f>X9</f>
         <v>DECRHEAT</v>
       </c>
-      <c r="D32" s="93" t="s">
+      <c r="D32" s="50" t="s">
         <v>107</v>
       </c>
-      <c r="E32" s="118">
+      <c r="E32" s="96">
         <v>2030</v>
       </c>
-      <c r="F32" s="120">
+      <c r="F32" s="97">
         <v>1</v>
       </c>
-      <c r="G32" s="120">
+      <c r="G32" s="97">
         <v>1</v>
       </c>
-      <c r="H32" s="119">
+      <c r="H32" s="99">
         <v>100</v>
       </c>
-      <c r="I32" s="119">
+      <c r="I32" s="99">
         <v>0</v>
       </c>
-      <c r="J32" s="119">
+      <c r="J32" s="99">
         <v>0</v>
       </c>
-      <c r="K32" s="119">
+      <c r="K32" s="99">
         <v>0</v>
       </c>
-      <c r="L32" s="119">
+      <c r="L32" s="99">
         <v>0</v>
       </c>
-      <c r="M32" s="121"/>
-      <c r="N32" s="121"/>
-      <c r="O32" s="120"/>
-      <c r="P32" s="120"/>
-      <c r="Q32" s="120"/>
-      <c r="R32" s="121"/>
-      <c r="S32" s="118"/>
+      <c r="M32" s="98"/>
+      <c r="N32" s="98"/>
+      <c r="O32" s="97"/>
+      <c r="P32" s="97"/>
+      <c r="Q32" s="97"/>
+      <c r="R32" s="98"/>
+      <c r="S32" s="96"/>
       <c r="AD32" s="46"/>
-      <c r="AI32" s="99"/>
-      <c r="AJ32" s="99"/>
-      <c r="AK32" s="95"/>
-      <c r="AL32" s="95"/>
-      <c r="AM32" s="95"/>
-      <c r="AN32" s="95"/>
-      <c r="AO32" s="95"/>
-      <c r="AP32" s="95"/>
-      <c r="AQ32" s="95"/>
-      <c r="AR32" s="95"/>
-      <c r="AS32" s="95"/>
-      <c r="AT32" s="95"/>
-      <c r="AU32" s="95"/>
-      <c r="AV32" s="95"/>
-      <c r="AW32" s="95"/>
-    </row>
-    <row r="33" spans="1:49" s="94" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="93" t="s">
+      <c r="AI32" s="86"/>
+      <c r="AJ32" s="86"/>
+      <c r="AK32" s="85"/>
+      <c r="AL32" s="85"/>
+      <c r="AM32" s="85"/>
+      <c r="AN32" s="85"/>
+      <c r="AO32" s="85"/>
+      <c r="AP32" s="85"/>
+      <c r="AQ32" s="85"/>
+      <c r="AR32" s="85"/>
+      <c r="AS32" s="85"/>
+      <c r="AT32" s="85"/>
+      <c r="AU32" s="85"/>
+      <c r="AV32" s="85"/>
+      <c r="AW32" s="85"/>
+    </row>
+    <row r="33" spans="1:49" s="84" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="50" t="s">
         <v>66</v>
       </c>
-      <c r="C33" s="95" t="s">
+      <c r="C33" s="45" t="s">
         <v>69</v>
       </c>
-      <c r="D33" s="93" t="s">
+      <c r="D33" s="50" t="s">
         <v>107</v>
       </c>
-      <c r="E33" s="118">
+      <c r="E33" s="96">
         <f>E19</f>
         <v>2030</v>
       </c>
-      <c r="F33" s="118">
+      <c r="F33" s="96">
         <f t="shared" ref="F33:S33" si="0">F19</f>
         <v>1</v>
       </c>
-      <c r="G33" s="118">
+      <c r="G33" s="96">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H33" s="118">
+      <c r="H33" s="96">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="I33" s="118">
+      <c r="I33" s="96">
         <f t="shared" si="0"/>
         <v>81</v>
       </c>
-      <c r="J33" s="118">
+      <c r="J33" s="96">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K33" s="118">
+      <c r="K33" s="96">
         <f t="shared" si="0"/>
         <v>0.24</v>
       </c>
-      <c r="L33" s="118">
+      <c r="L33" s="96">
         <f t="shared" si="0"/>
         <v>8.76</v>
       </c>
-      <c r="M33" s="118">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N33" s="118">
-        <f t="shared" si="0"/>
-        <v>0.1</v>
-      </c>
-      <c r="O33" s="118">
-        <f t="shared" si="0"/>
-        <v>0.15</v>
-      </c>
-      <c r="P33" s="118">
-        <f t="shared" si="0"/>
-        <v>0.2</v>
-      </c>
-      <c r="Q33" s="118">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
-      </c>
-      <c r="R33" s="118">
-        <f t="shared" si="0"/>
-        <v>0.3</v>
-      </c>
-      <c r="S33" s="118">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="M33" s="96"/>
+      <c r="N33" s="97"/>
+      <c r="O33" s="97"/>
+      <c r="P33" s="97"/>
+      <c r="Q33" s="97"/>
+      <c r="R33" s="97"/>
+      <c r="S33" s="97"/>
       <c r="AD33" s="46"/>
-      <c r="AI33" s="99"/>
-      <c r="AJ33" s="99"/>
-      <c r="AK33" s="95"/>
-      <c r="AL33" s="95"/>
-      <c r="AM33" s="95"/>
-      <c r="AN33" s="95"/>
-      <c r="AO33" s="95"/>
-      <c r="AP33" s="95"/>
-      <c r="AQ33" s="95"/>
-      <c r="AR33" s="95"/>
-      <c r="AS33" s="95"/>
-      <c r="AT33" s="95"/>
-      <c r="AU33" s="95"/>
-      <c r="AV33" s="95"/>
-      <c r="AW33" s="95"/>
-    </row>
-    <row r="34" spans="1:49" s="94" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="93" t="s">
+      <c r="AI33" s="86"/>
+      <c r="AJ33" s="86"/>
+      <c r="AK33" s="85"/>
+      <c r="AL33" s="85"/>
+      <c r="AM33" s="85"/>
+      <c r="AN33" s="85"/>
+      <c r="AO33" s="85"/>
+      <c r="AP33" s="85"/>
+      <c r="AQ33" s="85"/>
+      <c r="AR33" s="85"/>
+      <c r="AS33" s="85"/>
+      <c r="AT33" s="85"/>
+      <c r="AU33" s="85"/>
+      <c r="AV33" s="85"/>
+      <c r="AW33" s="85"/>
+    </row>
+    <row r="34" spans="1:49" s="84" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="50" t="s">
         <v>97</v>
       </c>
-      <c r="C34" s="95" t="s">
+      <c r="C34" s="45" t="s">
         <v>69</v>
       </c>
-      <c r="D34" s="93" t="s">
+      <c r="D34" s="50" t="s">
         <v>107</v>
       </c>
-      <c r="E34" s="118">
+      <c r="E34" s="96">
         <f>E21</f>
         <v>2030</v>
       </c>
-      <c r="F34" s="118">
+      <c r="F34" s="96">
         <f t="shared" ref="F34:S34" si="1">F21</f>
         <v>0.99</v>
       </c>
-      <c r="G34" s="118">
+      <c r="G34" s="96">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="H34" s="118">
+      <c r="H34" s="96">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="I34" s="118">
+      <c r="I34" s="96">
         <f t="shared" si="1"/>
         <v>112.9</v>
       </c>
-      <c r="J34" s="118">
+      <c r="J34" s="96">
         <f t="shared" si="1"/>
         <v>14.26</v>
       </c>
-      <c r="K34" s="118">
+      <c r="K34" s="96">
         <f t="shared" si="1"/>
         <v>1.22</v>
       </c>
-      <c r="L34" s="118">
+      <c r="L34" s="96">
         <f t="shared" si="1"/>
         <v>8.76</v>
       </c>
-      <c r="M34" s="118">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N34" s="118">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="O34" s="118">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P34" s="118">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q34" s="118">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="R34" s="118">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="S34" s="118">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="M34" s="96"/>
+      <c r="N34" s="97"/>
+      <c r="O34" s="97"/>
+      <c r="P34" s="97"/>
+      <c r="Q34" s="97"/>
+      <c r="R34" s="97"/>
+      <c r="S34" s="97"/>
       <c r="AA34" s="38"/>
       <c r="AB34" s="38"/>
-      <c r="AD34" s="95"/>
-      <c r="AI34" s="99"/>
-      <c r="AJ34" s="99"/>
-      <c r="AK34" s="95"/>
-      <c r="AL34" s="95"/>
-      <c r="AM34" s="95"/>
-      <c r="AN34" s="95"/>
-      <c r="AO34" s="95"/>
-      <c r="AP34" s="95"/>
-      <c r="AQ34" s="95"/>
-      <c r="AR34" s="95"/>
-      <c r="AS34" s="95"/>
-      <c r="AT34" s="95"/>
-      <c r="AU34" s="95"/>
-      <c r="AV34" s="95"/>
-      <c r="AW34" s="95"/>
-    </row>
-    <row r="35" spans="1:49" s="94" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="72" t="str">
+      <c r="AD34" s="85"/>
+      <c r="AI34" s="86"/>
+      <c r="AJ34" s="86"/>
+      <c r="AK34" s="85"/>
+      <c r="AL34" s="85"/>
+      <c r="AM34" s="85"/>
+      <c r="AN34" s="85"/>
+      <c r="AO34" s="85"/>
+      <c r="AP34" s="85"/>
+      <c r="AQ34" s="85"/>
+      <c r="AR34" s="85"/>
+      <c r="AS34" s="85"/>
+      <c r="AT34" s="85"/>
+      <c r="AU34" s="85"/>
+      <c r="AV34" s="85"/>
+      <c r="AW34" s="85"/>
+    </row>
+    <row r="35" spans="1:49" s="84" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="45" t="str">
         <f>X30</f>
         <v>MANELC_TECH</v>
       </c>
-      <c r="C35" s="78" t="str">
+      <c r="C35" s="50" t="str">
         <f>X8</f>
         <v>DECELC</v>
       </c>
-      <c r="D35" s="137" t="s">
+      <c r="D35" s="50" t="s">
         <v>157</v>
       </c>
-      <c r="E35" s="124">
+      <c r="E35" s="104">
         <v>2022</v>
       </c>
-      <c r="F35" s="120">
+      <c r="F35" s="97">
         <v>1</v>
       </c>
-      <c r="G35" s="120">
+      <c r="G35" s="97">
         <v>1</v>
       </c>
-      <c r="H35" s="119">
+      <c r="H35" s="99">
         <v>100</v>
       </c>
-      <c r="I35" s="119">
+      <c r="I35" s="99">
         <v>0</v>
       </c>
-      <c r="J35" s="119">
+      <c r="J35" s="99">
         <v>0</v>
       </c>
-      <c r="K35" s="119">
+      <c r="K35" s="99">
         <v>0</v>
       </c>
-      <c r="L35" s="119">
+      <c r="L35" s="99">
         <v>0</v>
       </c>
-      <c r="M35" s="121"/>
-      <c r="N35" s="121"/>
-      <c r="O35" s="120"/>
-      <c r="P35" s="120"/>
-      <c r="Q35" s="120"/>
-      <c r="R35" s="121"/>
-      <c r="S35" s="118"/>
+      <c r="M35" s="98"/>
+      <c r="N35" s="98"/>
+      <c r="O35" s="97"/>
+      <c r="P35" s="97"/>
+      <c r="Q35" s="97"/>
+      <c r="R35" s="98"/>
+      <c r="S35" s="96"/>
       <c r="V35" s="45"/>
       <c r="W35" s="45"/>
       <c r="X35" s="45"/>
       <c r="Y35" s="45"/>
       <c r="Z35" s="50"/>
-      <c r="AA35" s="102"/>
-      <c r="AB35" s="104"/>
-      <c r="AC35" s="95"/>
-      <c r="AD35" s="95"/>
-      <c r="AI35" s="99"/>
-      <c r="AJ35" s="99"/>
-      <c r="AK35" s="95"/>
-      <c r="AL35" s="95"/>
-      <c r="AM35" s="95"/>
-      <c r="AN35" s="95"/>
-      <c r="AO35" s="95"/>
-      <c r="AP35" s="95"/>
-      <c r="AQ35" s="95"/>
-      <c r="AR35" s="95"/>
-      <c r="AS35" s="95"/>
-      <c r="AT35" s="95"/>
-      <c r="AU35" s="95"/>
-      <c r="AV35" s="95"/>
-      <c r="AW35" s="95"/>
-    </row>
-    <row r="36" spans="1:49" s="94" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="93"/>
-      <c r="C36" s="93"/>
-      <c r="D36" s="93"/>
-      <c r="E36" s="124"/>
-      <c r="F36" s="125"/>
-      <c r="G36" s="125"/>
-      <c r="H36" s="124"/>
-      <c r="I36" s="125"/>
-      <c r="J36" s="125"/>
-      <c r="K36" s="125"/>
-      <c r="L36" s="125"/>
-      <c r="M36" s="126"/>
-      <c r="N36" s="126"/>
-      <c r="O36" s="125"/>
-      <c r="P36" s="125"/>
-      <c r="Q36" s="125"/>
-      <c r="R36" s="126"/>
-      <c r="S36" s="124"/>
-      <c r="V36" s="101"/>
-      <c r="W36" s="100"/>
-      <c r="X36" s="101"/>
-      <c r="Y36" s="100"/>
-      <c r="Z36" s="103"/>
-      <c r="AA36" s="95"/>
+      <c r="AA35" s="89"/>
+      <c r="AB35" s="91"/>
+      <c r="AC35" s="85"/>
+      <c r="AD35" s="85"/>
+      <c r="AI35" s="86"/>
+      <c r="AJ35" s="86"/>
+      <c r="AK35" s="85"/>
+      <c r="AL35" s="85"/>
+      <c r="AM35" s="85"/>
+      <c r="AN35" s="85"/>
+      <c r="AO35" s="85"/>
+      <c r="AP35" s="85"/>
+      <c r="AQ35" s="85"/>
+      <c r="AR35" s="85"/>
+      <c r="AS35" s="85"/>
+      <c r="AT35" s="85"/>
+      <c r="AU35" s="85"/>
+      <c r="AV35" s="85"/>
+      <c r="AW35" s="85"/>
+    </row>
+    <row r="36" spans="1:49" s="84" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="83"/>
+      <c r="C36" s="83"/>
+      <c r="D36" s="83"/>
+      <c r="E36" s="101"/>
+      <c r="F36" s="102"/>
+      <c r="G36" s="102"/>
+      <c r="H36" s="101"/>
+      <c r="I36" s="102"/>
+      <c r="J36" s="102"/>
+      <c r="K36" s="102"/>
+      <c r="L36" s="102"/>
+      <c r="M36" s="103"/>
+      <c r="N36" s="103"/>
+      <c r="O36" s="102"/>
+      <c r="P36" s="102"/>
+      <c r="Q36" s="102"/>
+      <c r="R36" s="103"/>
+      <c r="S36" s="101"/>
+      <c r="V36" s="88"/>
+      <c r="W36" s="87"/>
+      <c r="X36" s="88"/>
+      <c r="Y36" s="87"/>
+      <c r="Z36" s="90"/>
+      <c r="AA36" s="85"/>
       <c r="AC36" s="45"/>
       <c r="AD36" s="45"/>
-      <c r="AI36" s="99"/>
-      <c r="AJ36" s="99"/>
-      <c r="AK36" s="107"/>
-      <c r="AL36" s="107"/>
-      <c r="AM36" s="95"/>
-      <c r="AN36" s="95"/>
-      <c r="AO36" s="95"/>
-      <c r="AQ36" s="99"/>
-      <c r="AR36" s="99"/>
-      <c r="AS36" s="107"/>
-      <c r="AT36" s="107"/>
-      <c r="AU36" s="95"/>
-      <c r="AV36" s="95"/>
+      <c r="AI36" s="86"/>
+      <c r="AJ36" s="86"/>
+      <c r="AK36" s="94"/>
+      <c r="AL36" s="94"/>
+      <c r="AM36" s="85"/>
+      <c r="AN36" s="85"/>
+      <c r="AO36" s="85"/>
+      <c r="AQ36" s="86"/>
+      <c r="AR36" s="86"/>
+      <c r="AS36" s="94"/>
+      <c r="AT36" s="94"/>
+      <c r="AU36" s="85"/>
+      <c r="AV36" s="85"/>
     </row>
     <row r="37" spans="1:49" s="46" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B37" s="5"/>
       <c r="C37" s="50"/>
       <c r="D37" s="50"/>
-      <c r="E37" s="127"/>
-      <c r="F37" s="128"/>
-      <c r="G37" s="129"/>
-      <c r="M37" s="127"/>
-      <c r="N37" s="130"/>
-      <c r="O37" s="127"/>
-      <c r="P37" s="127"/>
-      <c r="Q37" s="127"/>
-      <c r="R37" s="127"/>
-      <c r="S37" s="127"/>
-      <c r="Z37" s="95"/>
-      <c r="AA37" s="95"/>
-      <c r="AB37" s="94"/>
-      <c r="AC37" s="94"/>
-      <c r="AD37" s="101"/>
+      <c r="E37" s="104"/>
+      <c r="F37" s="105"/>
+      <c r="G37" s="106"/>
+      <c r="M37" s="104"/>
+      <c r="N37" s="107"/>
+      <c r="O37" s="104"/>
+      <c r="P37" s="104"/>
+      <c r="Q37" s="104"/>
+      <c r="R37" s="104"/>
+      <c r="S37" s="104"/>
+      <c r="Z37" s="85"/>
+      <c r="AA37" s="85"/>
+      <c r="AB37" s="84"/>
+      <c r="AC37" s="84"/>
+      <c r="AD37" s="88"/>
       <c r="AI37"/>
       <c r="AJ37"/>
       <c r="AK37" s="39"/>
@@ -5994,93 +5890,93 @@
       <c r="AU37" s="45"/>
       <c r="AV37" s="45"/>
     </row>
-    <row r="38" spans="1:49" s="100" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="101"/>
-      <c r="C38" s="102"/>
-      <c r="D38" s="102"/>
-      <c r="E38" s="131"/>
-      <c r="F38" s="132"/>
-      <c r="G38" s="132"/>
-      <c r="H38" s="131"/>
-      <c r="I38" s="132"/>
-      <c r="J38" s="132"/>
-      <c r="K38" s="132"/>
-      <c r="L38" s="132"/>
-      <c r="N38" s="133"/>
+    <row r="38" spans="1:49" s="87" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="88"/>
+      <c r="C38" s="89"/>
+      <c r="D38" s="89"/>
+      <c r="E38" s="108"/>
+      <c r="F38" s="109"/>
+      <c r="G38" s="109"/>
+      <c r="H38" s="108"/>
+      <c r="I38" s="109"/>
+      <c r="J38" s="109"/>
+      <c r="K38" s="109"/>
+      <c r="L38" s="109"/>
+      <c r="N38" s="110"/>
       <c r="V38" s="45"/>
       <c r="W38" s="45"/>
       <c r="X38" s="45"/>
       <c r="Y38" s="45"/>
-      <c r="Z38" s="95"/>
-      <c r="AA38" s="95"/>
-      <c r="AB38" s="94"/>
+      <c r="Z38" s="85"/>
+      <c r="AA38" s="85"/>
+      <c r="AB38" s="84"/>
       <c r="AC38" s="46"/>
-      <c r="AD38" s="95"/>
-      <c r="AI38" s="105"/>
-      <c r="AJ38" s="105"/>
-      <c r="AK38" s="106"/>
-      <c r="AL38" s="106"/>
-      <c r="AM38" s="101"/>
-      <c r="AN38" s="101"/>
-      <c r="AO38" s="101"/>
-      <c r="AQ38" s="105"/>
-      <c r="AR38" s="105"/>
-      <c r="AS38" s="106"/>
-      <c r="AT38" s="106"/>
-      <c r="AU38" s="101"/>
-      <c r="AV38" s="101"/>
-    </row>
-    <row r="39" spans="1:49" s="94" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="95"/>
-      <c r="C39" s="93"/>
-      <c r="D39" s="93"/>
-      <c r="E39" s="124"/>
-      <c r="F39" s="125"/>
-      <c r="G39" s="125"/>
-      <c r="H39" s="124"/>
-      <c r="I39" s="125"/>
-      <c r="J39" s="125"/>
-      <c r="K39" s="125"/>
-      <c r="L39" s="125"/>
-      <c r="N39" s="134"/>
-      <c r="V39" s="99"/>
-      <c r="W39" s="99"/>
-      <c r="X39" s="95"/>
-      <c r="Y39" s="108"/>
-      <c r="Z39" s="95"/>
-      <c r="AA39" s="95"/>
-      <c r="AC39" s="95"/>
+      <c r="AD38" s="85"/>
+      <c r="AI38" s="92"/>
+      <c r="AJ38" s="92"/>
+      <c r="AK38" s="93"/>
+      <c r="AL38" s="93"/>
+      <c r="AM38" s="88"/>
+      <c r="AN38" s="88"/>
+      <c r="AO38" s="88"/>
+      <c r="AQ38" s="92"/>
+      <c r="AR38" s="92"/>
+      <c r="AS38" s="93"/>
+      <c r="AT38" s="93"/>
+      <c r="AU38" s="88"/>
+      <c r="AV38" s="88"/>
+    </row>
+    <row r="39" spans="1:49" s="84" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="85"/>
+      <c r="C39" s="83"/>
+      <c r="D39" s="83"/>
+      <c r="E39" s="101"/>
+      <c r="F39" s="102"/>
+      <c r="G39" s="102"/>
+      <c r="H39" s="101"/>
+      <c r="I39" s="102"/>
+      <c r="J39" s="102"/>
+      <c r="K39" s="102"/>
+      <c r="L39" s="102"/>
+      <c r="N39" s="111"/>
+      <c r="V39" s="86"/>
+      <c r="W39" s="86"/>
+      <c r="X39" s="85"/>
+      <c r="Y39" s="95"/>
+      <c r="Z39" s="85"/>
+      <c r="AA39" s="85"/>
+      <c r="AC39" s="85"/>
       <c r="AD39" s="45"/>
-      <c r="AI39" s="99"/>
-      <c r="AJ39" s="99"/>
-      <c r="AK39" s="107"/>
-      <c r="AL39" s="107"/>
-      <c r="AM39" s="95"/>
-      <c r="AN39" s="95"/>
-      <c r="AO39" s="95"/>
-      <c r="AQ39" s="99"/>
-      <c r="AR39" s="99"/>
-      <c r="AS39" s="107"/>
-      <c r="AT39" s="107"/>
-      <c r="AU39" s="95"/>
-      <c r="AV39" s="95"/>
+      <c r="AI39" s="86"/>
+      <c r="AJ39" s="86"/>
+      <c r="AK39" s="94"/>
+      <c r="AL39" s="94"/>
+      <c r="AM39" s="85"/>
+      <c r="AN39" s="85"/>
+      <c r="AO39" s="85"/>
+      <c r="AQ39" s="86"/>
+      <c r="AR39" s="86"/>
+      <c r="AS39" s="94"/>
+      <c r="AT39" s="94"/>
+      <c r="AU39" s="85"/>
+      <c r="AV39" s="85"/>
     </row>
     <row r="40" spans="1:49" s="46" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B40" s="45"/>
       <c r="C40" s="50"/>
       <c r="D40" s="50"/>
-      <c r="E40" s="127"/>
-      <c r="F40" s="128"/>
-      <c r="G40" s="129"/>
-      <c r="N40" s="135"/>
-      <c r="V40" s="99"/>
-      <c r="W40" s="99"/>
-      <c r="X40" s="95"/>
-      <c r="Y40" s="108"/>
-      <c r="Z40" s="95"/>
-      <c r="AA40" s="95"/>
-      <c r="AB40" s="94"/>
-      <c r="AC40" s="95"/>
+      <c r="E40" s="104"/>
+      <c r="F40" s="105"/>
+      <c r="G40" s="106"/>
+      <c r="N40" s="112"/>
+      <c r="V40" s="86"/>
+      <c r="W40" s="86"/>
+      <c r="X40" s="85"/>
+      <c r="Y40" s="95"/>
+      <c r="Z40" s="85"/>
+      <c r="AA40" s="85"/>
+      <c r="AB40" s="84"/>
+      <c r="AC40" s="85"/>
       <c r="AD40" s="45"/>
       <c r="AI40"/>
       <c r="AJ40"/>
@@ -6100,17 +5996,17 @@
       <c r="B41" s="50"/>
       <c r="C41" s="50"/>
       <c r="D41" s="50"/>
-      <c r="E41" s="127"/>
-      <c r="F41" s="128"/>
-      <c r="G41" s="129"/>
-      <c r="V41" s="99"/>
-      <c r="W41" s="99"/>
-      <c r="X41" s="95"/>
-      <c r="Y41" s="108"/>
-      <c r="Z41" s="95"/>
-      <c r="AA41" s="95"/>
-      <c r="AB41" s="94"/>
-      <c r="AC41" s="95"/>
+      <c r="E41" s="104"/>
+      <c r="F41" s="105"/>
+      <c r="G41" s="106"/>
+      <c r="V41" s="86"/>
+      <c r="W41" s="86"/>
+      <c r="X41" s="85"/>
+      <c r="Y41" s="95"/>
+      <c r="Z41" s="85"/>
+      <c r="AA41" s="85"/>
+      <c r="AB41" s="84"/>
+      <c r="AC41" s="85"/>
       <c r="AD41" s="45"/>
       <c r="AE41" s="45"/>
       <c r="AI41"/>
@@ -6131,17 +6027,17 @@
       <c r="B42" s="50"/>
       <c r="C42" s="50"/>
       <c r="D42" s="50"/>
-      <c r="E42" s="127"/>
-      <c r="F42" s="128"/>
-      <c r="G42" s="129"/>
-      <c r="V42" s="99"/>
-      <c r="W42" s="99"/>
-      <c r="X42" s="107"/>
-      <c r="Y42" s="108"/>
-      <c r="Z42" s="95"/>
+      <c r="E42" s="104"/>
+      <c r="F42" s="105"/>
+      <c r="G42" s="106"/>
+      <c r="V42" s="86"/>
+      <c r="W42" s="86"/>
+      <c r="X42" s="94"/>
+      <c r="Y42" s="95"/>
+      <c r="Z42" s="85"/>
       <c r="AA42" s="45"/>
       <c r="AB42" s="45"/>
-      <c r="AC42" s="95"/>
+      <c r="AC42" s="85"/>
       <c r="AD42" s="45"/>
       <c r="AE42" s="45"/>
       <c r="AI42"/>
@@ -6161,9 +6057,9 @@
     <row r="43" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A43" s="46"/>
       <c r="E43" s="46"/>
-      <c r="F43" s="136"/>
-      <c r="G43" s="127"/>
-      <c r="H43" s="135"/>
+      <c r="F43" s="113"/>
+      <c r="G43" s="104"/>
+      <c r="H43" s="112"/>
       <c r="I43" s="46"/>
       <c r="J43" s="46"/>
       <c r="K43" s="46"/>

--- a/SubRES_TMPL/SubRES_NewTechs.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87A6BE40-2075-4F11-B6D4-D720C16142DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PRI_Sector_Fuels" sheetId="6" r:id="rId1"/>
@@ -5629,7 +5629,7 @@
         <v>2030</v>
       </c>
       <c r="F33" s="96">
-        <f t="shared" ref="F33:S33" si="0">F19</f>
+        <f t="shared" ref="F33:L33" si="0">F19</f>
         <v>1</v>
       </c>
       <c r="G33" s="96">
@@ -5695,7 +5695,7 @@
         <v>2030</v>
       </c>
       <c r="F34" s="96">
-        <f t="shared" ref="F34:S34" si="1">F21</f>
+        <f t="shared" ref="F34:L34" si="1">F21</f>
         <v>0.99</v>
       </c>
       <c r="G34" s="96">

--- a/SubRES_TMPL/SubRES_NewTechs.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87A6BE40-2075-4F11-B6D4-D720C16142DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72F3ED84-B139-4629-8EF7-E9F8E3AFE51E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PRI_Sector_Fuels" sheetId="6" r:id="rId1"/>
@@ -1554,7 +1554,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="158">
   <si>
     <t>~FI_T</t>
   </si>
@@ -2370,7 +2370,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="114">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
@@ -2502,7 +2502,6 @@
     <xf numFmtId="0" fontId="21" fillId="10" borderId="0" xfId="4" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="22" fillId="8" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="20" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4030,7 +4029,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3360854E-4C4D-467D-BD8A-32231E61C6CE}">
-  <dimension ref="A1:AY149"/>
+  <dimension ref="A1:AY146"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" style="45" customWidth="1"/>
@@ -4295,19 +4294,19 @@
       <c r="AD9" s="50"/>
     </row>
     <row r="10" spans="2:51" x14ac:dyDescent="0.25">
-      <c r="Z10" s="72"/>
-      <c r="AB10" s="72"/>
+      <c r="Z10" s="71"/>
+      <c r="AB10" s="71"/>
     </row>
     <row r="11" spans="2:51" x14ac:dyDescent="0.25">
-      <c r="Z11" s="72"/>
-      <c r="AB11" s="72"/>
+      <c r="Z11" s="71"/>
+      <c r="AB11" s="71"/>
     </row>
     <row r="13" spans="2:51" x14ac:dyDescent="0.25">
-      <c r="Z13" s="72"/>
-      <c r="AB13" s="72"/>
+      <c r="Z13" s="71"/>
+      <c r="AB13" s="71"/>
     </row>
     <row r="14" spans="2:51" x14ac:dyDescent="0.25">
-      <c r="AB14" s="72"/>
+      <c r="AB14" s="71"/>
     </row>
     <row r="15" spans="2:51" x14ac:dyDescent="0.25">
       <c r="D15" s="55" t="s">
@@ -4325,19 +4324,19 @@
       <c r="Z15" s="50"/>
       <c r="AI15"/>
       <c r="AJ15" s="39"/>
-      <c r="AK15" s="72"/>
-      <c r="AL15" s="72"/>
-      <c r="AM15" s="72"/>
-      <c r="AN15" s="72"/>
-      <c r="AO15" s="72"/>
-      <c r="AP15" s="72"/>
-      <c r="AQ15" s="72"/>
-      <c r="AR15" s="72"/>
-      <c r="AS15" s="72"/>
-      <c r="AT15" s="72"/>
-      <c r="AU15" s="72"/>
-      <c r="AV15" s="72"/>
-      <c r="AW15" s="72"/>
+      <c r="AK15" s="71"/>
+      <c r="AL15" s="71"/>
+      <c r="AM15" s="71"/>
+      <c r="AN15" s="71"/>
+      <c r="AO15" s="71"/>
+      <c r="AP15" s="71"/>
+      <c r="AQ15" s="71"/>
+      <c r="AR15" s="71"/>
+      <c r="AS15" s="71"/>
+      <c r="AT15" s="71"/>
+      <c r="AU15" s="71"/>
+      <c r="AV15" s="71"/>
+      <c r="AW15" s="71"/>
     </row>
     <row r="16" spans="2:51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="56" t="s">
@@ -4423,19 +4422,19 @@
       </c>
       <c r="AI16"/>
       <c r="AJ16" s="39"/>
-      <c r="AK16" s="72"/>
-      <c r="AL16" s="72"/>
-      <c r="AM16" s="72"/>
-      <c r="AN16" s="72"/>
-      <c r="AO16" s="72"/>
-      <c r="AP16" s="72"/>
-      <c r="AQ16" s="72"/>
-      <c r="AR16" s="72"/>
-      <c r="AS16" s="72"/>
-      <c r="AT16" s="72"/>
-      <c r="AU16" s="72"/>
-      <c r="AV16" s="72"/>
-      <c r="AW16" s="72"/>
+      <c r="AK16" s="71"/>
+      <c r="AL16" s="71"/>
+      <c r="AM16" s="71"/>
+      <c r="AN16" s="71"/>
+      <c r="AO16" s="71"/>
+      <c r="AP16" s="71"/>
+      <c r="AQ16" s="71"/>
+      <c r="AR16" s="71"/>
+      <c r="AS16" s="71"/>
+      <c r="AT16" s="71"/>
+      <c r="AU16" s="71"/>
+      <c r="AV16" s="71"/>
+      <c r="AW16" s="71"/>
       <c r="AY16" s="46"/>
     </row>
     <row r="17" spans="2:51" ht="31.8" thickBot="1" x14ac:dyDescent="0.3">
@@ -4490,7 +4489,7 @@
       <c r="R17" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="S17" s="70" t="s">
+      <c r="S17" s="69" t="s">
         <v>126</v>
       </c>
       <c r="V17" s="31" t="s">
@@ -4554,7 +4553,7 @@
       <c r="P18" s="36"/>
       <c r="Q18" s="36"/>
       <c r="R18" s="35"/>
-      <c r="S18" s="71"/>
+      <c r="S18" s="70"/>
       <c r="V18" s="31" t="s">
         <v>81</v>
       </c>
@@ -4574,7 +4573,7 @@
       <c r="AJ18" s="39"/>
       <c r="AY18" s="46"/>
     </row>
-    <row r="19" spans="2:51" s="78" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:51" s="77" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B19" s="45" t="str">
         <f>X19</f>
         <v>Furnace</v>
@@ -4586,39 +4585,39 @@
       <c r="D19" s="50" t="s">
         <v>107</v>
       </c>
-      <c r="E19" s="96">
+      <c r="E19" s="95">
         <v>2030</v>
       </c>
-      <c r="F19" s="97">
+      <c r="F19" s="96">
         <v>1</v>
       </c>
-      <c r="G19" s="97">
+      <c r="G19" s="96">
         <v>1</v>
       </c>
-      <c r="H19" s="96">
+      <c r="H19" s="95">
         <v>25</v>
       </c>
-      <c r="I19" s="97">
+      <c r="I19" s="96">
         <v>81</v>
       </c>
-      <c r="J19" s="97">
+      <c r="J19" s="96">
         <v>0</v>
       </c>
-      <c r="K19" s="97">
+      <c r="K19" s="96">
         <v>0.24</v>
       </c>
-      <c r="L19" s="97">
+      <c r="L19" s="96">
         <v>8.76</v>
       </c>
-      <c r="M19" s="96"/>
-      <c r="N19" s="97"/>
-      <c r="O19" s="97"/>
-      <c r="P19" s="97"/>
-      <c r="Q19" s="97"/>
-      <c r="R19" s="97"/>
-      <c r="S19" s="96"/>
-      <c r="T19" s="79"/>
-      <c r="U19" s="79"/>
+      <c r="M19" s="95"/>
+      <c r="N19" s="96"/>
+      <c r="O19" s="96"/>
+      <c r="P19" s="96"/>
+      <c r="Q19" s="96"/>
+      <c r="R19" s="96"/>
+      <c r="S19" s="95"/>
+      <c r="T19" s="78"/>
+      <c r="U19" s="78"/>
       <c r="V19" s="60" t="s">
         <v>127</v>
       </c>
@@ -4638,13 +4637,13 @@
       <c r="AB19" s="63" t="s">
         <v>88</v>
       </c>
-      <c r="AC19" s="79"/>
-      <c r="AD19" s="79"/>
-      <c r="AI19" s="80"/>
-      <c r="AJ19" s="81"/>
-      <c r="AY19" s="79"/>
-    </row>
-    <row r="20" spans="2:51" s="72" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC19" s="78"/>
+      <c r="AD19" s="78"/>
+      <c r="AI19" s="79"/>
+      <c r="AJ19" s="80"/>
+      <c r="AY19" s="78"/>
+    </row>
+    <row r="20" spans="2:51" s="71" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B20" s="45" t="str">
         <f>X$20</f>
         <v>BIOBoiler</v>
@@ -4657,39 +4656,39 @@
         <f>X9</f>
         <v>DECRHEAT</v>
       </c>
-      <c r="E20" s="96">
+      <c r="E20" s="95">
         <v>2030</v>
       </c>
-      <c r="F20" s="97">
+      <c r="F20" s="96">
         <v>0.7</v>
       </c>
-      <c r="G20" s="97">
+      <c r="G20" s="96">
         <v>0.98</v>
       </c>
-      <c r="H20" s="96">
+      <c r="H20" s="95">
         <v>25</v>
       </c>
-      <c r="I20" s="97">
+      <c r="I20" s="96">
         <v>797.9</v>
       </c>
-      <c r="J20" s="97">
+      <c r="J20" s="96">
         <v>48.48</v>
       </c>
-      <c r="K20" s="97">
+      <c r="K20" s="96">
         <v>3.75</v>
       </c>
-      <c r="L20" s="97">
+      <c r="L20" s="96">
         <v>8.76</v>
       </c>
-      <c r="M20" s="96"/>
-      <c r="N20" s="98"/>
-      <c r="O20" s="96"/>
-      <c r="P20" s="96"/>
-      <c r="Q20" s="96"/>
-      <c r="R20" s="96"/>
-      <c r="S20" s="96"/>
-      <c r="T20" s="82"/>
-      <c r="U20" s="82"/>
+      <c r="M20" s="95"/>
+      <c r="N20" s="97"/>
+      <c r="O20" s="95"/>
+      <c r="P20" s="95"/>
+      <c r="Q20" s="95"/>
+      <c r="R20" s="95"/>
+      <c r="S20" s="95"/>
+      <c r="T20" s="81"/>
+      <c r="U20" s="81"/>
       <c r="V20" s="60" t="s">
         <v>138</v>
       </c>
@@ -4709,57 +4708,56 @@
       <c r="AB20" s="63" t="s">
         <v>88</v>
       </c>
-      <c r="AC20" s="82"/>
-      <c r="AD20" s="82"/>
+      <c r="AC20" s="81"/>
+      <c r="AD20" s="81"/>
       <c r="AI20" s="14"/>
       <c r="AJ20" s="12"/>
-      <c r="AY20" s="82"/>
-    </row>
-    <row r="21" spans="2:51" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AY20" s="81"/>
+    </row>
+    <row r="21" spans="2:51" s="77" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B21" s="45" t="str">
         <f>X23</f>
         <v>ELCBoiler</v>
       </c>
-      <c r="C21" s="50" t="str">
-        <f>X8</f>
-        <v>DECELC</v>
+      <c r="C21" s="50" t="s">
+        <v>128</v>
       </c>
       <c r="D21" s="50" t="s">
         <v>107</v>
       </c>
-      <c r="E21" s="96">
+      <c r="E21" s="95">
         <v>2030</v>
       </c>
-      <c r="F21" s="97">
+      <c r="F21" s="96">
         <v>0.99</v>
       </c>
-      <c r="G21" s="97">
+      <c r="G21" s="96">
         <v>1</v>
       </c>
-      <c r="H21" s="96">
+      <c r="H21" s="95">
         <v>25</v>
       </c>
-      <c r="I21" s="97">
+      <c r="I21" s="96">
         <v>112.9</v>
       </c>
-      <c r="J21" s="97">
+      <c r="J21" s="96">
         <v>14.26</v>
       </c>
-      <c r="K21" s="97">
+      <c r="K21" s="96">
         <v>1.22</v>
       </c>
-      <c r="L21" s="97">
+      <c r="L21" s="96">
         <v>8.76</v>
       </c>
-      <c r="M21" s="96"/>
-      <c r="N21" s="99"/>
-      <c r="O21" s="99"/>
-      <c r="P21" s="99"/>
-      <c r="Q21" s="99"/>
-      <c r="R21" s="99"/>
-      <c r="S21" s="96"/>
-      <c r="T21" s="79"/>
-      <c r="U21" s="79"/>
+      <c r="M21" s="95"/>
+      <c r="N21" s="98"/>
+      <c r="O21" s="98"/>
+      <c r="P21" s="98"/>
+      <c r="Q21" s="98"/>
+      <c r="R21" s="98"/>
+      <c r="S21" s="95"/>
+      <c r="T21" s="78"/>
+      <c r="U21" s="78"/>
       <c r="V21" s="60" t="s">
         <v>127</v>
       </c>
@@ -4779,11 +4777,11 @@
       <c r="AB21" s="63" t="s">
         <v>88</v>
       </c>
-      <c r="AC21" s="79"/>
-      <c r="AD21" s="79"/>
-      <c r="AI21" s="80"/>
-      <c r="AJ21" s="81"/>
-      <c r="AY21" s="79"/>
+      <c r="AC21" s="78"/>
+      <c r="AD21" s="78"/>
+      <c r="AI21" s="79"/>
+      <c r="AJ21" s="80"/>
+      <c r="AY21" s="78"/>
     </row>
     <row r="22" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B22" s="45" t="str">
@@ -4797,37 +4795,37 @@
       <c r="D22" s="50" t="s">
         <v>108</v>
       </c>
-      <c r="E22" s="96">
+      <c r="E22" s="95">
         <v>2030</v>
       </c>
-      <c r="F22" s="97">
+      <c r="F22" s="96">
         <v>0.55600000000000005</v>
       </c>
-      <c r="G22" s="97">
+      <c r="G22" s="96">
         <v>0.98</v>
       </c>
-      <c r="H22" s="96">
+      <c r="H22" s="95">
         <v>25</v>
       </c>
-      <c r="I22" s="97">
+      <c r="I22" s="96">
         <v>297.10000000000002</v>
       </c>
-      <c r="J22" s="97">
+      <c r="J22" s="96">
         <v>4.46</v>
       </c>
-      <c r="K22" s="97">
+      <c r="K22" s="96">
         <v>0.45</v>
       </c>
-      <c r="L22" s="97">
+      <c r="L22" s="96">
         <v>8.76</v>
       </c>
-      <c r="M22" s="96"/>
-      <c r="N22" s="97"/>
-      <c r="O22" s="97"/>
-      <c r="P22" s="97"/>
-      <c r="Q22" s="97"/>
-      <c r="R22" s="97"/>
-      <c r="S22" s="96"/>
+      <c r="M22" s="95"/>
+      <c r="N22" s="96"/>
+      <c r="O22" s="96"/>
+      <c r="P22" s="96"/>
+      <c r="Q22" s="96"/>
+      <c r="R22" s="96"/>
+      <c r="S22" s="95"/>
       <c r="V22" s="60" t="s">
         <v>127</v>
       </c>
@@ -4875,37 +4873,37 @@
       <c r="D23" s="50" t="s">
         <v>107</v>
       </c>
-      <c r="E23" s="96">
+      <c r="E23" s="95">
         <v>2030</v>
       </c>
-      <c r="F23" s="97">
+      <c r="F23" s="96">
         <v>0.75</v>
       </c>
-      <c r="G23" s="97">
+      <c r="G23" s="96">
         <v>0.99</v>
       </c>
-      <c r="H23" s="96">
+      <c r="H23" s="95">
         <v>25</v>
       </c>
-      <c r="I23" s="97">
+      <c r="I23" s="96">
         <v>61.4</v>
       </c>
-      <c r="J23" s="97">
+      <c r="J23" s="96">
         <v>2.57</v>
       </c>
-      <c r="K23" s="97">
+      <c r="K23" s="96">
         <v>1.35</v>
       </c>
-      <c r="L23" s="97">
+      <c r="L23" s="96">
         <v>8.76</v>
       </c>
-      <c r="M23" s="96"/>
-      <c r="N23" s="98"/>
-      <c r="O23" s="96"/>
-      <c r="P23" s="96"/>
-      <c r="Q23" s="96"/>
-      <c r="R23" s="96"/>
-      <c r="S23" s="96"/>
+      <c r="M23" s="95"/>
+      <c r="N23" s="97"/>
+      <c r="O23" s="95"/>
+      <c r="P23" s="95"/>
+      <c r="Q23" s="95"/>
+      <c r="R23" s="95"/>
+      <c r="S23" s="95"/>
       <c r="V23" s="60" t="s">
         <v>127</v>
       </c>
@@ -4927,19 +4925,19 @@
       </c>
       <c r="AI23"/>
       <c r="AJ23"/>
-      <c r="AK23" s="72"/>
-      <c r="AL23" s="72"/>
-      <c r="AM23" s="72"/>
-      <c r="AN23" s="72"/>
-      <c r="AO23" s="72"/>
-      <c r="AP23" s="72"/>
-      <c r="AQ23" s="72"/>
-      <c r="AR23" s="72"/>
-      <c r="AS23" s="72"/>
-      <c r="AT23" s="72"/>
-      <c r="AU23" s="72"/>
-      <c r="AV23" s="72"/>
-      <c r="AW23" s="72"/>
+      <c r="AK23" s="71"/>
+      <c r="AL23" s="71"/>
+      <c r="AM23" s="71"/>
+      <c r="AN23" s="71"/>
+      <c r="AO23" s="71"/>
+      <c r="AP23" s="71"/>
+      <c r="AQ23" s="71"/>
+      <c r="AR23" s="71"/>
+      <c r="AS23" s="71"/>
+      <c r="AT23" s="71"/>
+      <c r="AU23" s="71"/>
+      <c r="AV23" s="71"/>
+      <c r="AW23" s="71"/>
     </row>
     <row r="24" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B24" s="50" t="str">
@@ -4953,37 +4951,37 @@
       <c r="D24" s="50" t="s">
         <v>129</v>
       </c>
-      <c r="E24" s="96">
+      <c r="E24" s="95">
         <v>2030</v>
       </c>
-      <c r="F24" s="97">
+      <c r="F24" s="96">
         <v>1</v>
       </c>
-      <c r="G24" s="97">
+      <c r="G24" s="96">
         <v>0.97</v>
       </c>
-      <c r="H24" s="96">
+      <c r="H24" s="95">
         <v>25</v>
       </c>
-      <c r="I24" s="97">
+      <c r="I24" s="96">
         <v>1041</v>
       </c>
-      <c r="J24" s="97">
+      <c r="J24" s="96">
         <v>38</v>
       </c>
-      <c r="K24" s="97">
+      <c r="K24" s="96">
         <v>0</v>
       </c>
-      <c r="L24" s="97">
+      <c r="L24" s="96">
         <v>8.76</v>
       </c>
-      <c r="M24" s="98"/>
-      <c r="N24" s="98"/>
-      <c r="O24" s="97"/>
-      <c r="P24" s="97"/>
-      <c r="Q24" s="97"/>
-      <c r="R24" s="98"/>
-      <c r="S24" s="97">
+      <c r="M24" s="97"/>
+      <c r="N24" s="97"/>
+      <c r="O24" s="96"/>
+      <c r="P24" s="96"/>
+      <c r="Q24" s="96"/>
+      <c r="R24" s="97"/>
+      <c r="S24" s="96">
         <v>0.2</v>
       </c>
       <c r="V24" s="60" t="s">
@@ -5007,19 +5005,19 @@
       </c>
       <c r="AI24"/>
       <c r="AJ24"/>
-      <c r="AK24" s="72"/>
-      <c r="AL24" s="72"/>
-      <c r="AM24" s="72"/>
-      <c r="AN24" s="72"/>
-      <c r="AO24" s="72"/>
-      <c r="AP24" s="72"/>
-      <c r="AQ24" s="72"/>
-      <c r="AR24" s="72"/>
-      <c r="AS24" s="72"/>
-      <c r="AT24" s="72"/>
-      <c r="AU24" s="72"/>
-      <c r="AV24" s="72"/>
-      <c r="AW24" s="72"/>
+      <c r="AK24" s="71"/>
+      <c r="AL24" s="71"/>
+      <c r="AM24" s="71"/>
+      <c r="AN24" s="71"/>
+      <c r="AO24" s="71"/>
+      <c r="AP24" s="71"/>
+      <c r="AQ24" s="71"/>
+      <c r="AR24" s="71"/>
+      <c r="AS24" s="71"/>
+      <c r="AT24" s="71"/>
+      <c r="AU24" s="71"/>
+      <c r="AV24" s="71"/>
+      <c r="AW24" s="71"/>
     </row>
     <row r="25" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B25" s="50" t="str">
@@ -5033,37 +5031,37 @@
       <c r="D25" s="50" t="s">
         <v>130</v>
       </c>
-      <c r="E25" s="96">
+      <c r="E25" s="95">
         <v>2030</v>
       </c>
-      <c r="F25" s="97">
+      <c r="F25" s="96">
         <v>0.20499999999999999</v>
       </c>
-      <c r="G25" s="97">
+      <c r="G25" s="96">
         <v>0.99</v>
       </c>
-      <c r="H25" s="96">
+      <c r="H25" s="95">
         <v>25</v>
       </c>
-      <c r="I25" s="97">
+      <c r="I25" s="96">
         <v>691</v>
       </c>
-      <c r="J25" s="97">
+      <c r="J25" s="96">
         <v>6.99</v>
       </c>
-      <c r="K25" s="97">
+      <c r="K25" s="96">
         <v>0</v>
       </c>
-      <c r="L25" s="97">
+      <c r="L25" s="96">
         <v>8.76</v>
       </c>
-      <c r="M25" s="98"/>
-      <c r="N25" s="98"/>
-      <c r="O25" s="97"/>
-      <c r="P25" s="97"/>
-      <c r="Q25" s="97"/>
-      <c r="R25" s="98"/>
-      <c r="S25" s="97">
+      <c r="M25" s="97"/>
+      <c r="N25" s="97"/>
+      <c r="O25" s="96"/>
+      <c r="P25" s="96"/>
+      <c r="Q25" s="96"/>
+      <c r="R25" s="97"/>
+      <c r="S25" s="96">
         <v>0.3</v>
       </c>
       <c r="V25" s="60" t="s">
@@ -5101,7 +5099,7 @@
       <c r="AV25" s="45"/>
       <c r="AW25" s="45"/>
     </row>
-    <row r="26" spans="2:51" s="82" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:51" s="81" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B26" s="50" t="str">
         <f>X24</f>
         <v>CSP</v>
@@ -5114,37 +5112,37 @@
         <f>X9</f>
         <v>DECRHEAT</v>
       </c>
-      <c r="E26" s="96">
+      <c r="E26" s="95">
         <v>2030</v>
       </c>
-      <c r="F26" s="97">
+      <c r="F26" s="96">
         <v>0.4</v>
       </c>
-      <c r="G26" s="97">
+      <c r="G26" s="96">
         <v>1</v>
       </c>
-      <c r="H26" s="96">
+      <c r="H26" s="95">
         <v>25</v>
       </c>
-      <c r="I26" s="97">
+      <c r="I26" s="96">
         <v>3677</v>
       </c>
-      <c r="J26" s="97">
+      <c r="J26" s="96">
         <v>0</v>
       </c>
-      <c r="K26" s="97">
+      <c r="K26" s="96">
         <v>14</v>
       </c>
-      <c r="L26" s="97">
+      <c r="L26" s="96">
         <v>8.76</v>
       </c>
-      <c r="M26" s="98"/>
-      <c r="N26" s="98"/>
-      <c r="O26" s="97"/>
-      <c r="P26" s="97"/>
-      <c r="Q26" s="97"/>
-      <c r="R26" s="98"/>
-      <c r="S26" s="96"/>
+      <c r="M26" s="97"/>
+      <c r="N26" s="97"/>
+      <c r="O26" s="96"/>
+      <c r="P26" s="96"/>
+      <c r="Q26" s="96"/>
+      <c r="R26" s="97"/>
+      <c r="S26" s="95"/>
       <c r="V26" s="60" t="s">
         <v>69</v>
       </c>
@@ -5166,19 +5164,19 @@
       </c>
       <c r="AI26" s="14"/>
       <c r="AJ26" s="14"/>
-      <c r="AK26" s="72"/>
-      <c r="AL26" s="72"/>
-      <c r="AM26" s="72"/>
-      <c r="AN26" s="72"/>
-      <c r="AO26" s="72"/>
-      <c r="AP26" s="72"/>
-      <c r="AQ26" s="72"/>
-      <c r="AR26" s="72"/>
-      <c r="AS26" s="72"/>
-      <c r="AT26" s="72"/>
-      <c r="AU26" s="72"/>
-      <c r="AV26" s="72"/>
-      <c r="AW26" s="72"/>
+      <c r="AK26" s="71"/>
+      <c r="AL26" s="71"/>
+      <c r="AM26" s="71"/>
+      <c r="AN26" s="71"/>
+      <c r="AO26" s="71"/>
+      <c r="AP26" s="71"/>
+      <c r="AQ26" s="71"/>
+      <c r="AR26" s="71"/>
+      <c r="AS26" s="71"/>
+      <c r="AT26" s="71"/>
+      <c r="AU26" s="71"/>
+      <c r="AV26" s="71"/>
+      <c r="AW26" s="71"/>
     </row>
     <row r="27" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B27" s="50" t="str">
@@ -5189,39 +5187,39 @@
       <c r="D27" s="50" t="s">
         <v>106</v>
       </c>
-      <c r="E27" s="96">
+      <c r="E27" s="95">
         <v>2030</v>
       </c>
-      <c r="F27" s="97">
+      <c r="F27" s="96">
         <v>0.3</v>
       </c>
-      <c r="G27" s="97">
+      <c r="G27" s="96">
         <v>1</v>
       </c>
-      <c r="H27" s="96">
+      <c r="H27" s="95">
         <v>25</v>
       </c>
-      <c r="I27" s="97">
+      <c r="I27" s="96">
         <v>0</v>
       </c>
-      <c r="J27" s="97">
+      <c r="J27" s="96">
         <v>0</v>
       </c>
-      <c r="K27" s="97">
+      <c r="K27" s="96">
         <v>0</v>
       </c>
-      <c r="L27" s="97">
+      <c r="L27" s="96">
         <v>8.76</v>
       </c>
-      <c r="M27" s="98">
+      <c r="M27" s="97">
         <v>0.202158</v>
       </c>
-      <c r="N27" s="98"/>
-      <c r="O27" s="97"/>
-      <c r="P27" s="97"/>
-      <c r="Q27" s="97"/>
-      <c r="R27" s="98"/>
-      <c r="S27" s="96"/>
+      <c r="N27" s="97"/>
+      <c r="O27" s="96"/>
+      <c r="P27" s="96"/>
+      <c r="Q27" s="96"/>
+      <c r="R27" s="97"/>
+      <c r="S27" s="95"/>
       <c r="V27" s="60" t="s">
         <v>69</v>
       </c>
@@ -5257,7 +5255,7 @@
       <c r="AV27" s="45"/>
       <c r="AW27" s="45"/>
     </row>
-    <row r="28" spans="2:51" s="84" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:51" s="83" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B28" s="50" t="str">
         <f>X27</f>
         <v>DECPOWER</v>
@@ -5270,37 +5268,37 @@
         <f>X8</f>
         <v>DECELC</v>
       </c>
-      <c r="E28" s="96">
+      <c r="E28" s="95">
         <v>2030</v>
       </c>
-      <c r="F28" s="99">
+      <c r="F28" s="98">
         <v>1</v>
       </c>
-      <c r="G28" s="99">
+      <c r="G28" s="98">
         <v>1</v>
       </c>
-      <c r="H28" s="96">
+      <c r="H28" s="95">
         <v>100</v>
       </c>
-      <c r="I28" s="97">
+      <c r="I28" s="96">
         <v>0</v>
       </c>
-      <c r="J28" s="99">
+      <c r="J28" s="98">
         <v>0</v>
       </c>
-      <c r="K28" s="99">
+      <c r="K28" s="98">
         <v>0</v>
       </c>
-      <c r="L28" s="97">
+      <c r="L28" s="96">
         <v>8.76</v>
       </c>
-      <c r="M28" s="98"/>
-      <c r="N28" s="98"/>
-      <c r="O28" s="97"/>
-      <c r="P28" s="97"/>
-      <c r="Q28" s="97"/>
-      <c r="R28" s="98"/>
-      <c r="S28" s="96"/>
+      <c r="M28" s="97"/>
+      <c r="N28" s="97"/>
+      <c r="O28" s="96"/>
+      <c r="P28" s="96"/>
+      <c r="Q28" s="96"/>
+      <c r="R28" s="97"/>
+      <c r="S28" s="95"/>
       <c r="V28" s="60" t="s">
         <v>69</v>
       </c>
@@ -5320,23 +5318,23 @@
       <c r="AB28" s="46" t="s">
         <v>88</v>
       </c>
-      <c r="AI28" s="86"/>
-      <c r="AJ28" s="86"/>
-      <c r="AK28" s="85"/>
-      <c r="AL28" s="85"/>
-      <c r="AM28" s="85"/>
-      <c r="AN28" s="85"/>
-      <c r="AO28" s="85"/>
-      <c r="AP28" s="85"/>
-      <c r="AQ28" s="85"/>
-      <c r="AR28" s="85"/>
-      <c r="AS28" s="85"/>
-      <c r="AT28" s="85"/>
-      <c r="AU28" s="85"/>
-      <c r="AV28" s="85"/>
-      <c r="AW28" s="85"/>
-    </row>
-    <row r="29" spans="2:51" s="84" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AI28" s="85"/>
+      <c r="AJ28" s="85"/>
+      <c r="AK28" s="84"/>
+      <c r="AL28" s="84"/>
+      <c r="AM28" s="84"/>
+      <c r="AN28" s="84"/>
+      <c r="AO28" s="84"/>
+      <c r="AP28" s="84"/>
+      <c r="AQ28" s="84"/>
+      <c r="AR28" s="84"/>
+      <c r="AS28" s="84"/>
+      <c r="AT28" s="84"/>
+      <c r="AU28" s="84"/>
+      <c r="AV28" s="84"/>
+      <c r="AW28" s="84"/>
+    </row>
+    <row r="29" spans="2:51" s="83" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B29" s="50" t="str">
         <f>X27</f>
         <v>DECPOWER</v>
@@ -5349,37 +5347,37 @@
         <f>X8</f>
         <v>DECELC</v>
       </c>
-      <c r="E29" s="96">
+      <c r="E29" s="95">
         <v>2030</v>
       </c>
-      <c r="F29" s="99">
+      <c r="F29" s="98">
         <v>1</v>
       </c>
-      <c r="G29" s="99">
+      <c r="G29" s="98">
         <v>1</v>
       </c>
-      <c r="H29" s="96">
+      <c r="H29" s="95">
         <v>100</v>
       </c>
-      <c r="I29" s="97">
+      <c r="I29" s="96">
         <v>0</v>
       </c>
-      <c r="J29" s="99">
+      <c r="J29" s="98">
         <v>0</v>
       </c>
-      <c r="K29" s="99">
+      <c r="K29" s="98">
         <v>0</v>
       </c>
-      <c r="L29" s="97">
+      <c r="L29" s="96">
         <v>8.76</v>
       </c>
-      <c r="M29" s="98"/>
-      <c r="N29" s="98"/>
-      <c r="O29" s="97"/>
-      <c r="P29" s="97"/>
-      <c r="Q29" s="97"/>
-      <c r="R29" s="98"/>
-      <c r="S29" s="96"/>
+      <c r="M29" s="97"/>
+      <c r="N29" s="97"/>
+      <c r="O29" s="96"/>
+      <c r="P29" s="96"/>
+      <c r="Q29" s="96"/>
+      <c r="R29" s="97"/>
+      <c r="S29" s="95"/>
       <c r="V29" s="46" t="s">
         <v>127</v>
       </c>
@@ -5400,21 +5398,21 @@
         <v>88</v>
       </c>
       <c r="AC29" s="46"/>
-      <c r="AI29" s="86"/>
-      <c r="AJ29" s="86"/>
-      <c r="AK29" s="85"/>
-      <c r="AL29" s="85"/>
-      <c r="AM29" s="85"/>
-      <c r="AN29" s="85"/>
-      <c r="AO29" s="85"/>
-      <c r="AP29" s="85"/>
-      <c r="AQ29" s="85"/>
-      <c r="AR29" s="85"/>
-      <c r="AS29" s="85"/>
-      <c r="AT29" s="85"/>
-      <c r="AU29" s="85"/>
-      <c r="AV29" s="85"/>
-      <c r="AW29" s="85"/>
+      <c r="AI29" s="85"/>
+      <c r="AJ29" s="85"/>
+      <c r="AK29" s="84"/>
+      <c r="AL29" s="84"/>
+      <c r="AM29" s="84"/>
+      <c r="AN29" s="84"/>
+      <c r="AO29" s="84"/>
+      <c r="AP29" s="84"/>
+      <c r="AQ29" s="84"/>
+      <c r="AR29" s="84"/>
+      <c r="AS29" s="84"/>
+      <c r="AT29" s="84"/>
+      <c r="AU29" s="84"/>
+      <c r="AV29" s="84"/>
+      <c r="AW29" s="84"/>
     </row>
     <row r="30" spans="2:51" s="46" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B30" s="50" t="str">
@@ -5427,37 +5425,37 @@
       <c r="D30" s="50" t="s">
         <v>134</v>
       </c>
-      <c r="E30" s="96">
+      <c r="E30" s="95">
         <v>2030</v>
       </c>
-      <c r="F30" s="99">
+      <c r="F30" s="98">
         <v>0.35</v>
       </c>
-      <c r="G30" s="99">
+      <c r="G30" s="98">
         <v>0.98</v>
       </c>
-      <c r="H30" s="96">
+      <c r="H30" s="95">
         <v>20</v>
       </c>
-      <c r="I30" s="100">
+      <c r="I30" s="99">
         <v>3242</v>
       </c>
-      <c r="J30" s="97">
+      <c r="J30" s="96">
         <v>129.68</v>
       </c>
-      <c r="K30" s="97">
+      <c r="K30" s="96">
         <v>0</v>
       </c>
-      <c r="L30" s="97">
+      <c r="L30" s="96">
         <v>8.76</v>
       </c>
-      <c r="M30" s="98"/>
-      <c r="N30" s="98"/>
-      <c r="O30" s="97"/>
-      <c r="P30" s="97"/>
-      <c r="Q30" s="97"/>
-      <c r="R30" s="98"/>
-      <c r="S30" s="96"/>
+      <c r="M30" s="97"/>
+      <c r="N30" s="97"/>
+      <c r="O30" s="96"/>
+      <c r="P30" s="96"/>
+      <c r="Q30" s="96"/>
+      <c r="R30" s="97"/>
+      <c r="S30" s="95"/>
       <c r="V30" s="45" t="s">
         <v>127</v>
       </c>
@@ -5476,7 +5474,7 @@
       <c r="AB30" s="46" t="s">
         <v>88</v>
       </c>
-      <c r="AC30" s="84"/>
+      <c r="AC30" s="83"/>
       <c r="AI30" s="38"/>
       <c r="AJ30" s="38"/>
       <c r="AK30" s="45"/>
@@ -5493,7 +5491,7 @@
       <c r="AV30" s="45"/>
       <c r="AW30" s="45"/>
     </row>
-    <row r="31" spans="2:51" s="84" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:51" s="83" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B31" s="50" t="str">
         <f>X27</f>
         <v>DECPOWER</v>
@@ -5506,55 +5504,55 @@
         <f>X8</f>
         <v>DECELC</v>
       </c>
-      <c r="E31" s="96">
+      <c r="E31" s="95">
         <v>2030</v>
       </c>
-      <c r="F31" s="97">
+      <c r="F31" s="96">
         <v>1</v>
       </c>
-      <c r="G31" s="97">
+      <c r="G31" s="96">
         <v>1</v>
       </c>
-      <c r="H31" s="99">
+      <c r="H31" s="98">
         <v>100</v>
       </c>
-      <c r="I31" s="99">
+      <c r="I31" s="98">
         <v>0</v>
       </c>
-      <c r="J31" s="99">
+      <c r="J31" s="98">
         <v>0</v>
       </c>
-      <c r="K31" s="99">
+      <c r="K31" s="98">
         <v>0</v>
       </c>
-      <c r="L31" s="99">
+      <c r="L31" s="98">
         <v>0</v>
       </c>
-      <c r="M31" s="98"/>
-      <c r="N31" s="98"/>
-      <c r="O31" s="97"/>
-      <c r="P31" s="97"/>
-      <c r="Q31" s="97"/>
-      <c r="R31" s="98"/>
-      <c r="S31" s="96"/>
+      <c r="M31" s="97"/>
+      <c r="N31" s="97"/>
+      <c r="O31" s="96"/>
+      <c r="P31" s="96"/>
+      <c r="Q31" s="96"/>
+      <c r="R31" s="97"/>
+      <c r="S31" s="95"/>
       <c r="AD31" s="46"/>
-      <c r="AI31" s="86"/>
-      <c r="AJ31" s="86"/>
-      <c r="AK31" s="85"/>
-      <c r="AL31" s="85"/>
-      <c r="AM31" s="85"/>
-      <c r="AN31" s="85"/>
-      <c r="AO31" s="85"/>
-      <c r="AP31" s="85"/>
-      <c r="AQ31" s="85"/>
-      <c r="AR31" s="85"/>
-      <c r="AS31" s="85"/>
-      <c r="AT31" s="85"/>
-      <c r="AU31" s="85"/>
-      <c r="AV31" s="85"/>
-      <c r="AW31" s="85"/>
-    </row>
-    <row r="32" spans="2:51" s="84" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AI31" s="85"/>
+      <c r="AJ31" s="85"/>
+      <c r="AK31" s="84"/>
+      <c r="AL31" s="84"/>
+      <c r="AM31" s="84"/>
+      <c r="AN31" s="84"/>
+      <c r="AO31" s="84"/>
+      <c r="AP31" s="84"/>
+      <c r="AQ31" s="84"/>
+      <c r="AR31" s="84"/>
+      <c r="AS31" s="84"/>
+      <c r="AT31" s="84"/>
+      <c r="AU31" s="84"/>
+      <c r="AV31" s="84"/>
+      <c r="AW31" s="84"/>
+    </row>
+    <row r="32" spans="2:51" s="83" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B32" s="50" t="str">
         <f>X29</f>
         <v>DECTHT</v>
@@ -5566,55 +5564,55 @@
       <c r="D32" s="50" t="s">
         <v>107</v>
       </c>
-      <c r="E32" s="96">
+      <c r="E32" s="95">
         <v>2030</v>
       </c>
-      <c r="F32" s="97">
+      <c r="F32" s="96">
         <v>1</v>
       </c>
-      <c r="G32" s="97">
+      <c r="G32" s="96">
         <v>1</v>
       </c>
-      <c r="H32" s="99">
+      <c r="H32" s="98">
         <v>100</v>
       </c>
-      <c r="I32" s="99">
+      <c r="I32" s="98">
         <v>0</v>
       </c>
-      <c r="J32" s="99">
+      <c r="J32" s="98">
         <v>0</v>
       </c>
-      <c r="K32" s="99">
+      <c r="K32" s="98">
         <v>0</v>
       </c>
-      <c r="L32" s="99">
+      <c r="L32" s="98">
         <v>0</v>
       </c>
-      <c r="M32" s="98"/>
-      <c r="N32" s="98"/>
-      <c r="O32" s="97"/>
-      <c r="P32" s="97"/>
-      <c r="Q32" s="97"/>
-      <c r="R32" s="98"/>
-      <c r="S32" s="96"/>
+      <c r="M32" s="97"/>
+      <c r="N32" s="97"/>
+      <c r="O32" s="96"/>
+      <c r="P32" s="96"/>
+      <c r="Q32" s="96"/>
+      <c r="R32" s="97"/>
+      <c r="S32" s="95"/>
       <c r="AD32" s="46"/>
-      <c r="AI32" s="86"/>
-      <c r="AJ32" s="86"/>
-      <c r="AK32" s="85"/>
-      <c r="AL32" s="85"/>
-      <c r="AM32" s="85"/>
-      <c r="AN32" s="85"/>
-      <c r="AO32" s="85"/>
-      <c r="AP32" s="85"/>
-      <c r="AQ32" s="85"/>
-      <c r="AR32" s="85"/>
-      <c r="AS32" s="85"/>
-      <c r="AT32" s="85"/>
-      <c r="AU32" s="85"/>
-      <c r="AV32" s="85"/>
-      <c r="AW32" s="85"/>
-    </row>
-    <row r="33" spans="1:49" s="84" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AI32" s="85"/>
+      <c r="AJ32" s="85"/>
+      <c r="AK32" s="84"/>
+      <c r="AL32" s="84"/>
+      <c r="AM32" s="84"/>
+      <c r="AN32" s="84"/>
+      <c r="AO32" s="84"/>
+      <c r="AP32" s="84"/>
+      <c r="AQ32" s="84"/>
+      <c r="AR32" s="84"/>
+      <c r="AS32" s="84"/>
+      <c r="AT32" s="84"/>
+      <c r="AU32" s="84"/>
+      <c r="AV32" s="84"/>
+      <c r="AW32" s="84"/>
+    </row>
+    <row r="33" spans="1:49" s="83" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B33" s="50" t="s">
         <v>66</v>
       </c>
@@ -5624,63 +5622,63 @@
       <c r="D33" s="50" t="s">
         <v>107</v>
       </c>
-      <c r="E33" s="96">
+      <c r="E33" s="95">
         <f>E19</f>
         <v>2030</v>
       </c>
-      <c r="F33" s="96">
+      <c r="F33" s="95">
         <f t="shared" ref="F33:L33" si="0">F19</f>
         <v>1</v>
       </c>
-      <c r="G33" s="96">
+      <c r="G33" s="95">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H33" s="96">
+      <c r="H33" s="95">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="I33" s="96">
+      <c r="I33" s="95">
         <f t="shared" si="0"/>
         <v>81</v>
       </c>
-      <c r="J33" s="96">
+      <c r="J33" s="95">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K33" s="96">
+      <c r="K33" s="95">
         <f t="shared" si="0"/>
         <v>0.24</v>
       </c>
-      <c r="L33" s="96">
+      <c r="L33" s="95">
         <f t="shared" si="0"/>
         <v>8.76</v>
       </c>
-      <c r="M33" s="96"/>
-      <c r="N33" s="97"/>
-      <c r="O33" s="97"/>
-      <c r="P33" s="97"/>
-      <c r="Q33" s="97"/>
-      <c r="R33" s="97"/>
-      <c r="S33" s="97"/>
+      <c r="M33" s="95"/>
+      <c r="N33" s="96"/>
+      <c r="O33" s="96"/>
+      <c r="P33" s="96"/>
+      <c r="Q33" s="96"/>
+      <c r="R33" s="96"/>
+      <c r="S33" s="96"/>
       <c r="AD33" s="46"/>
-      <c r="AI33" s="86"/>
-      <c r="AJ33" s="86"/>
-      <c r="AK33" s="85"/>
-      <c r="AL33" s="85"/>
-      <c r="AM33" s="85"/>
-      <c r="AN33" s="85"/>
-      <c r="AO33" s="85"/>
-      <c r="AP33" s="85"/>
-      <c r="AQ33" s="85"/>
-      <c r="AR33" s="85"/>
-      <c r="AS33" s="85"/>
-      <c r="AT33" s="85"/>
-      <c r="AU33" s="85"/>
-      <c r="AV33" s="85"/>
-      <c r="AW33" s="85"/>
-    </row>
-    <row r="34" spans="1:49" s="84" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AI33" s="85"/>
+      <c r="AJ33" s="85"/>
+      <c r="AK33" s="84"/>
+      <c r="AL33" s="84"/>
+      <c r="AM33" s="84"/>
+      <c r="AN33" s="84"/>
+      <c r="AO33" s="84"/>
+      <c r="AP33" s="84"/>
+      <c r="AQ33" s="84"/>
+      <c r="AR33" s="84"/>
+      <c r="AS33" s="84"/>
+      <c r="AT33" s="84"/>
+      <c r="AU33" s="84"/>
+      <c r="AV33" s="84"/>
+      <c r="AW33" s="84"/>
+    </row>
+    <row r="34" spans="1:49" s="83" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B34" s="50" t="s">
         <v>97</v>
       </c>
@@ -5690,65 +5688,65 @@
       <c r="D34" s="50" t="s">
         <v>107</v>
       </c>
-      <c r="E34" s="96">
+      <c r="E34" s="95">
         <f>E21</f>
         <v>2030</v>
       </c>
-      <c r="F34" s="96">
+      <c r="F34" s="95">
         <f t="shared" ref="F34:L34" si="1">F21</f>
         <v>0.99</v>
       </c>
-      <c r="G34" s="96">
+      <c r="G34" s="95">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="H34" s="96">
+      <c r="H34" s="95">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="I34" s="96">
+      <c r="I34" s="95">
         <f t="shared" si="1"/>
         <v>112.9</v>
       </c>
-      <c r="J34" s="96">
+      <c r="J34" s="95">
         <f t="shared" si="1"/>
         <v>14.26</v>
       </c>
-      <c r="K34" s="96">
+      <c r="K34" s="95">
         <f t="shared" si="1"/>
         <v>1.22</v>
       </c>
-      <c r="L34" s="96">
+      <c r="L34" s="95">
         <f t="shared" si="1"/>
         <v>8.76</v>
       </c>
-      <c r="M34" s="96"/>
-      <c r="N34" s="97"/>
-      <c r="O34" s="97"/>
-      <c r="P34" s="97"/>
-      <c r="Q34" s="97"/>
-      <c r="R34" s="97"/>
-      <c r="S34" s="97"/>
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="96"/>
+      <c r="P34" s="96"/>
+      <c r="Q34" s="96"/>
+      <c r="R34" s="96"/>
+      <c r="S34" s="96"/>
       <c r="AA34" s="38"/>
       <c r="AB34" s="38"/>
-      <c r="AD34" s="85"/>
-      <c r="AI34" s="86"/>
-      <c r="AJ34" s="86"/>
-      <c r="AK34" s="85"/>
-      <c r="AL34" s="85"/>
-      <c r="AM34" s="85"/>
-      <c r="AN34" s="85"/>
-      <c r="AO34" s="85"/>
-      <c r="AP34" s="85"/>
-      <c r="AQ34" s="85"/>
-      <c r="AR34" s="85"/>
-      <c r="AS34" s="85"/>
-      <c r="AT34" s="85"/>
-      <c r="AU34" s="85"/>
-      <c r="AV34" s="85"/>
-      <c r="AW34" s="85"/>
-    </row>
-    <row r="35" spans="1:49" s="84" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AD34" s="84"/>
+      <c r="AI34" s="85"/>
+      <c r="AJ34" s="85"/>
+      <c r="AK34" s="84"/>
+      <c r="AL34" s="84"/>
+      <c r="AM34" s="84"/>
+      <c r="AN34" s="84"/>
+      <c r="AO34" s="84"/>
+      <c r="AP34" s="84"/>
+      <c r="AQ34" s="84"/>
+      <c r="AR34" s="84"/>
+      <c r="AS34" s="84"/>
+      <c r="AT34" s="84"/>
+      <c r="AU34" s="84"/>
+      <c r="AV34" s="84"/>
+      <c r="AW34" s="84"/>
+    </row>
+    <row r="35" spans="1:49" s="83" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B35" s="45" t="str">
         <f>X30</f>
         <v>MANELC_TECH</v>
@@ -5760,122 +5758,122 @@
       <c r="D35" s="50" t="s">
         <v>157</v>
       </c>
-      <c r="E35" s="104">
+      <c r="E35" s="103">
         <v>2022</v>
       </c>
-      <c r="F35" s="97">
+      <c r="F35" s="96">
         <v>1</v>
       </c>
-      <c r="G35" s="97">
+      <c r="G35" s="96">
         <v>1</v>
       </c>
-      <c r="H35" s="99">
+      <c r="H35" s="98">
         <v>100</v>
       </c>
-      <c r="I35" s="99">
+      <c r="I35" s="98">
         <v>0</v>
       </c>
-      <c r="J35" s="99">
+      <c r="J35" s="98">
         <v>0</v>
       </c>
-      <c r="K35" s="99">
+      <c r="K35" s="98">
         <v>0</v>
       </c>
-      <c r="L35" s="99">
+      <c r="L35" s="98">
         <v>0</v>
       </c>
-      <c r="M35" s="98"/>
-      <c r="N35" s="98"/>
-      <c r="O35" s="97"/>
-      <c r="P35" s="97"/>
-      <c r="Q35" s="97"/>
-      <c r="R35" s="98"/>
-      <c r="S35" s="96"/>
+      <c r="M35" s="97"/>
+      <c r="N35" s="97"/>
+      <c r="O35" s="96"/>
+      <c r="P35" s="96"/>
+      <c r="Q35" s="96"/>
+      <c r="R35" s="97"/>
+      <c r="S35" s="95"/>
       <c r="V35" s="45"/>
       <c r="W35" s="45"/>
       <c r="X35" s="45"/>
       <c r="Y35" s="45"/>
       <c r="Z35" s="50"/>
-      <c r="AA35" s="89"/>
-      <c r="AB35" s="91"/>
-      <c r="AC35" s="85"/>
-      <c r="AD35" s="85"/>
-      <c r="AI35" s="86"/>
-      <c r="AJ35" s="86"/>
-      <c r="AK35" s="85"/>
-      <c r="AL35" s="85"/>
-      <c r="AM35" s="85"/>
-      <c r="AN35" s="85"/>
-      <c r="AO35" s="85"/>
-      <c r="AP35" s="85"/>
-      <c r="AQ35" s="85"/>
-      <c r="AR35" s="85"/>
-      <c r="AS35" s="85"/>
-      <c r="AT35" s="85"/>
-      <c r="AU35" s="85"/>
-      <c r="AV35" s="85"/>
-      <c r="AW35" s="85"/>
-    </row>
-    <row r="36" spans="1:49" s="84" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="83"/>
-      <c r="C36" s="83"/>
-      <c r="D36" s="83"/>
-      <c r="E36" s="101"/>
-      <c r="F36" s="102"/>
-      <c r="G36" s="102"/>
-      <c r="H36" s="101"/>
-      <c r="I36" s="102"/>
-      <c r="J36" s="102"/>
-      <c r="K36" s="102"/>
-      <c r="L36" s="102"/>
-      <c r="M36" s="103"/>
-      <c r="N36" s="103"/>
-      <c r="O36" s="102"/>
-      <c r="P36" s="102"/>
-      <c r="Q36" s="102"/>
-      <c r="R36" s="103"/>
-      <c r="S36" s="101"/>
-      <c r="V36" s="88"/>
-      <c r="W36" s="87"/>
-      <c r="X36" s="88"/>
-      <c r="Y36" s="87"/>
-      <c r="Z36" s="90"/>
-      <c r="AA36" s="85"/>
+      <c r="AA35" s="88"/>
+      <c r="AB35" s="90"/>
+      <c r="AC35" s="84"/>
+      <c r="AD35" s="84"/>
+      <c r="AI35" s="85"/>
+      <c r="AJ35" s="85"/>
+      <c r="AK35" s="84"/>
+      <c r="AL35" s="84"/>
+      <c r="AM35" s="84"/>
+      <c r="AN35" s="84"/>
+      <c r="AO35" s="84"/>
+      <c r="AP35" s="84"/>
+      <c r="AQ35" s="84"/>
+      <c r="AR35" s="84"/>
+      <c r="AS35" s="84"/>
+      <c r="AT35" s="84"/>
+      <c r="AU35" s="84"/>
+      <c r="AV35" s="84"/>
+      <c r="AW35" s="84"/>
+    </row>
+    <row r="36" spans="1:49" s="83" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="82"/>
+      <c r="C36" s="82"/>
+      <c r="D36" s="82"/>
+      <c r="E36" s="100"/>
+      <c r="F36" s="101"/>
+      <c r="G36" s="101"/>
+      <c r="H36" s="100"/>
+      <c r="I36" s="101"/>
+      <c r="J36" s="101"/>
+      <c r="K36" s="101"/>
+      <c r="L36" s="101"/>
+      <c r="M36" s="102"/>
+      <c r="N36" s="102"/>
+      <c r="O36" s="101"/>
+      <c r="P36" s="101"/>
+      <c r="Q36" s="101"/>
+      <c r="R36" s="102"/>
+      <c r="S36" s="100"/>
+      <c r="V36" s="87"/>
+      <c r="W36" s="86"/>
+      <c r="X36" s="87"/>
+      <c r="Y36" s="86"/>
+      <c r="Z36" s="89"/>
+      <c r="AA36" s="84"/>
       <c r="AC36" s="45"/>
       <c r="AD36" s="45"/>
-      <c r="AI36" s="86"/>
-      <c r="AJ36" s="86"/>
-      <c r="AK36" s="94"/>
-      <c r="AL36" s="94"/>
-      <c r="AM36" s="85"/>
-      <c r="AN36" s="85"/>
-      <c r="AO36" s="85"/>
-      <c r="AQ36" s="86"/>
-      <c r="AR36" s="86"/>
-      <c r="AS36" s="94"/>
-      <c r="AT36" s="94"/>
-      <c r="AU36" s="85"/>
-      <c r="AV36" s="85"/>
+      <c r="AI36" s="85"/>
+      <c r="AJ36" s="85"/>
+      <c r="AK36" s="93"/>
+      <c r="AL36" s="93"/>
+      <c r="AM36" s="84"/>
+      <c r="AN36" s="84"/>
+      <c r="AO36" s="84"/>
+      <c r="AQ36" s="85"/>
+      <c r="AR36" s="85"/>
+      <c r="AS36" s="93"/>
+      <c r="AT36" s="93"/>
+      <c r="AU36" s="84"/>
+      <c r="AV36" s="84"/>
     </row>
     <row r="37" spans="1:49" s="46" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B37" s="5"/>
       <c r="C37" s="50"/>
       <c r="D37" s="50"/>
-      <c r="E37" s="104"/>
-      <c r="F37" s="105"/>
-      <c r="G37" s="106"/>
-      <c r="M37" s="104"/>
-      <c r="N37" s="107"/>
-      <c r="O37" s="104"/>
-      <c r="P37" s="104"/>
-      <c r="Q37" s="104"/>
-      <c r="R37" s="104"/>
-      <c r="S37" s="104"/>
-      <c r="Z37" s="85"/>
-      <c r="AA37" s="85"/>
-      <c r="AB37" s="84"/>
-      <c r="AC37" s="84"/>
-      <c r="AD37" s="88"/>
+      <c r="E37" s="103"/>
+      <c r="F37" s="104"/>
+      <c r="G37" s="105"/>
+      <c r="M37" s="103"/>
+      <c r="N37" s="106"/>
+      <c r="O37" s="103"/>
+      <c r="P37" s="103"/>
+      <c r="Q37" s="103"/>
+      <c r="R37" s="103"/>
+      <c r="S37" s="103"/>
+      <c r="Z37" s="84"/>
+      <c r="AA37" s="84"/>
+      <c r="AB37" s="83"/>
+      <c r="AC37" s="83"/>
+      <c r="AD37" s="87"/>
       <c r="AI37"/>
       <c r="AJ37"/>
       <c r="AK37" s="39"/>
@@ -5890,93 +5888,93 @@
       <c r="AU37" s="45"/>
       <c r="AV37" s="45"/>
     </row>
-    <row r="38" spans="1:49" s="87" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="88"/>
-      <c r="C38" s="89"/>
-      <c r="D38" s="89"/>
-      <c r="E38" s="108"/>
-      <c r="F38" s="109"/>
-      <c r="G38" s="109"/>
-      <c r="H38" s="108"/>
-      <c r="I38" s="109"/>
-      <c r="J38" s="109"/>
-      <c r="K38" s="109"/>
-      <c r="L38" s="109"/>
-      <c r="N38" s="110"/>
+    <row r="38" spans="1:49" s="86" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="87"/>
+      <c r="C38" s="88"/>
+      <c r="D38" s="88"/>
+      <c r="E38" s="107"/>
+      <c r="F38" s="108"/>
+      <c r="G38" s="108"/>
+      <c r="H38" s="107"/>
+      <c r="I38" s="108"/>
+      <c r="J38" s="108"/>
+      <c r="K38" s="108"/>
+      <c r="L38" s="108"/>
+      <c r="N38" s="109"/>
       <c r="V38" s="45"/>
       <c r="W38" s="45"/>
       <c r="X38" s="45"/>
       <c r="Y38" s="45"/>
-      <c r="Z38" s="85"/>
-      <c r="AA38" s="85"/>
-      <c r="AB38" s="84"/>
+      <c r="Z38" s="84"/>
+      <c r="AA38" s="84"/>
+      <c r="AB38" s="83"/>
       <c r="AC38" s="46"/>
-      <c r="AD38" s="85"/>
-      <c r="AI38" s="92"/>
-      <c r="AJ38" s="92"/>
-      <c r="AK38" s="93"/>
-      <c r="AL38" s="93"/>
-      <c r="AM38" s="88"/>
-      <c r="AN38" s="88"/>
-      <c r="AO38" s="88"/>
-      <c r="AQ38" s="92"/>
-      <c r="AR38" s="92"/>
-      <c r="AS38" s="93"/>
-      <c r="AT38" s="93"/>
-      <c r="AU38" s="88"/>
-      <c r="AV38" s="88"/>
-    </row>
-    <row r="39" spans="1:49" s="84" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="85"/>
-      <c r="C39" s="83"/>
-      <c r="D39" s="83"/>
-      <c r="E39" s="101"/>
-      <c r="F39" s="102"/>
-      <c r="G39" s="102"/>
-      <c r="H39" s="101"/>
-      <c r="I39" s="102"/>
-      <c r="J39" s="102"/>
-      <c r="K39" s="102"/>
-      <c r="L39" s="102"/>
-      <c r="N39" s="111"/>
-      <c r="V39" s="86"/>
-      <c r="W39" s="86"/>
-      <c r="X39" s="85"/>
-      <c r="Y39" s="95"/>
-      <c r="Z39" s="85"/>
-      <c r="AA39" s="85"/>
-      <c r="AC39" s="85"/>
+      <c r="AD38" s="84"/>
+      <c r="AI38" s="91"/>
+      <c r="AJ38" s="91"/>
+      <c r="AK38" s="92"/>
+      <c r="AL38" s="92"/>
+      <c r="AM38" s="87"/>
+      <c r="AN38" s="87"/>
+      <c r="AO38" s="87"/>
+      <c r="AQ38" s="91"/>
+      <c r="AR38" s="91"/>
+      <c r="AS38" s="92"/>
+      <c r="AT38" s="92"/>
+      <c r="AU38" s="87"/>
+      <c r="AV38" s="87"/>
+    </row>
+    <row r="39" spans="1:49" s="83" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="84"/>
+      <c r="C39" s="82"/>
+      <c r="D39" s="82"/>
+      <c r="E39" s="100"/>
+      <c r="F39" s="101"/>
+      <c r="G39" s="101"/>
+      <c r="H39" s="100"/>
+      <c r="I39" s="101"/>
+      <c r="J39" s="101"/>
+      <c r="K39" s="101"/>
+      <c r="L39" s="101"/>
+      <c r="N39" s="110"/>
+      <c r="V39" s="85"/>
+      <c r="W39" s="85"/>
+      <c r="X39" s="84"/>
+      <c r="Y39" s="94"/>
+      <c r="Z39" s="84"/>
+      <c r="AA39" s="84"/>
+      <c r="AC39" s="84"/>
       <c r="AD39" s="45"/>
-      <c r="AI39" s="86"/>
-      <c r="AJ39" s="86"/>
-      <c r="AK39" s="94"/>
-      <c r="AL39" s="94"/>
-      <c r="AM39" s="85"/>
-      <c r="AN39" s="85"/>
-      <c r="AO39" s="85"/>
-      <c r="AQ39" s="86"/>
-      <c r="AR39" s="86"/>
-      <c r="AS39" s="94"/>
-      <c r="AT39" s="94"/>
-      <c r="AU39" s="85"/>
-      <c r="AV39" s="85"/>
+      <c r="AI39" s="85"/>
+      <c r="AJ39" s="85"/>
+      <c r="AK39" s="93"/>
+      <c r="AL39" s="93"/>
+      <c r="AM39" s="84"/>
+      <c r="AN39" s="84"/>
+      <c r="AO39" s="84"/>
+      <c r="AQ39" s="85"/>
+      <c r="AR39" s="85"/>
+      <c r="AS39" s="93"/>
+      <c r="AT39" s="93"/>
+      <c r="AU39" s="84"/>
+      <c r="AV39" s="84"/>
     </row>
     <row r="40" spans="1:49" s="46" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B40" s="45"/>
       <c r="C40" s="50"/>
       <c r="D40" s="50"/>
-      <c r="E40" s="104"/>
-      <c r="F40" s="105"/>
-      <c r="G40" s="106"/>
-      <c r="N40" s="112"/>
-      <c r="V40" s="86"/>
-      <c r="W40" s="86"/>
-      <c r="X40" s="85"/>
-      <c r="Y40" s="95"/>
-      <c r="Z40" s="85"/>
-      <c r="AA40" s="85"/>
-      <c r="AB40" s="84"/>
-      <c r="AC40" s="85"/>
+      <c r="E40" s="103"/>
+      <c r="F40" s="104"/>
+      <c r="G40" s="105"/>
+      <c r="N40" s="111"/>
+      <c r="V40" s="85"/>
+      <c r="W40" s="85"/>
+      <c r="X40" s="84"/>
+      <c r="Y40" s="94"/>
+      <c r="Z40" s="84"/>
+      <c r="AA40" s="84"/>
+      <c r="AB40" s="83"/>
+      <c r="AC40" s="84"/>
       <c r="AD40" s="45"/>
       <c r="AI40"/>
       <c r="AJ40"/>
@@ -5996,17 +5994,17 @@
       <c r="B41" s="50"/>
       <c r="C41" s="50"/>
       <c r="D41" s="50"/>
-      <c r="E41" s="104"/>
-      <c r="F41" s="105"/>
-      <c r="G41" s="106"/>
-      <c r="V41" s="86"/>
-      <c r="W41" s="86"/>
-      <c r="X41" s="85"/>
-      <c r="Y41" s="95"/>
-      <c r="Z41" s="85"/>
-      <c r="AA41" s="85"/>
-      <c r="AB41" s="84"/>
-      <c r="AC41" s="85"/>
+      <c r="E41" s="103"/>
+      <c r="F41" s="104"/>
+      <c r="G41" s="105"/>
+      <c r="V41" s="85"/>
+      <c r="W41" s="85"/>
+      <c r="X41" s="84"/>
+      <c r="Y41" s="94"/>
+      <c r="Z41" s="84"/>
+      <c r="AA41" s="84"/>
+      <c r="AB41" s="83"/>
+      <c r="AC41" s="84"/>
       <c r="AD41" s="45"/>
       <c r="AE41" s="45"/>
       <c r="AI41"/>
@@ -6027,17 +6025,17 @@
       <c r="B42" s="50"/>
       <c r="C42" s="50"/>
       <c r="D42" s="50"/>
-      <c r="E42" s="104"/>
-      <c r="F42" s="105"/>
-      <c r="G42" s="106"/>
-      <c r="V42" s="86"/>
-      <c r="W42" s="86"/>
-      <c r="X42" s="94"/>
-      <c r="Y42" s="95"/>
-      <c r="Z42" s="85"/>
+      <c r="E42" s="103"/>
+      <c r="F42" s="104"/>
+      <c r="G42" s="105"/>
+      <c r="V42" s="85"/>
+      <c r="W42" s="85"/>
+      <c r="X42" s="93"/>
+      <c r="Y42" s="94"/>
+      <c r="Z42" s="84"/>
       <c r="AA42" s="45"/>
       <c r="AB42" s="45"/>
-      <c r="AC42" s="85"/>
+      <c r="AC42" s="84"/>
       <c r="AD42" s="45"/>
       <c r="AE42" s="45"/>
       <c r="AI42"/>
@@ -6057,9 +6055,9 @@
     <row r="43" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A43" s="46"/>
       <c r="E43" s="46"/>
-      <c r="F43" s="113"/>
-      <c r="G43" s="104"/>
-      <c r="H43" s="112"/>
+      <c r="F43" s="112"/>
+      <c r="G43" s="103"/>
+      <c r="H43" s="111"/>
       <c r="I43" s="46"/>
       <c r="J43" s="46"/>
       <c r="K43" s="46"/>
@@ -6254,18 +6252,18 @@
       <c r="AS57" s="39"/>
       <c r="AT57" s="39"/>
     </row>
-    <row r="58" spans="2:46" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="69"/>
-      <c r="C58" s="69"/>
-      <c r="D58" s="69"/>
-      <c r="E58" s="69"/>
-      <c r="F58" s="69"/>
-      <c r="G58" s="69"/>
-      <c r="H58" s="69"/>
-      <c r="I58" s="69"/>
-      <c r="J58" s="69"/>
-      <c r="K58" s="69"/>
-      <c r="L58" s="69"/>
+    <row r="58" spans="2:46" x14ac:dyDescent="0.25">
+      <c r="B58"/>
+      <c r="C58"/>
+      <c r="D58"/>
+      <c r="E58" s="1"/>
+      <c r="F58"/>
+      <c r="G58"/>
+      <c r="H58"/>
+      <c r="I58"/>
+      <c r="J58"/>
+      <c r="K58"/>
+      <c r="L58"/>
       <c r="AI58"/>
       <c r="AJ58"/>
       <c r="AK58" s="39"/>
@@ -6381,17 +6379,13 @@
       <c r="AT63" s="39"/>
     </row>
     <row r="64" spans="2:46" x14ac:dyDescent="0.25">
-      <c r="B64"/>
-      <c r="C64"/>
-      <c r="D64"/>
-      <c r="E64" s="1"/>
-      <c r="F64"/>
-      <c r="G64"/>
-      <c r="H64"/>
-      <c r="I64"/>
-      <c r="J64"/>
-      <c r="K64"/>
-      <c r="L64"/>
+      <c r="V64" s="46"/>
+      <c r="W64" s="46"/>
+      <c r="X64" s="46"/>
+      <c r="Y64" s="46"/>
+      <c r="Z64" s="46"/>
+      <c r="AA64" s="46"/>
+      <c r="AB64" s="46"/>
       <c r="AI64"/>
       <c r="AJ64"/>
       <c r="AK64" s="39"/>
@@ -6402,17 +6396,13 @@
       <c r="AT64" s="39"/>
     </row>
     <row r="65" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="B65"/>
-      <c r="C65"/>
-      <c r="D65"/>
-      <c r="E65" s="1"/>
-      <c r="F65"/>
-      <c r="G65"/>
-      <c r="H65"/>
-      <c r="I65"/>
-      <c r="J65"/>
-      <c r="K65"/>
-      <c r="L65"/>
+      <c r="V65" s="46"/>
+      <c r="W65" s="46"/>
+      <c r="X65" s="46"/>
+      <c r="Y65" s="46"/>
+      <c r="Z65" s="46"/>
+      <c r="AA65" s="46"/>
+      <c r="AB65" s="46"/>
       <c r="AI65"/>
       <c r="AJ65"/>
       <c r="AK65" s="39"/>
@@ -6423,17 +6413,14 @@
       <c r="AT65" s="39"/>
     </row>
     <row r="66" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="B66"/>
-      <c r="C66"/>
-      <c r="D66"/>
-      <c r="E66" s="1"/>
-      <c r="F66"/>
-      <c r="G66"/>
-      <c r="H66"/>
-      <c r="I66"/>
-      <c r="J66"/>
-      <c r="K66"/>
-      <c r="L66"/>
+      <c r="V66" s="46"/>
+      <c r="W66" s="46"/>
+      <c r="X66" s="46"/>
+      <c r="Y66" s="46"/>
+      <c r="Z66" s="46"/>
+      <c r="AA66" s="46"/>
+      <c r="AB66" s="46"/>
+      <c r="AC66" s="46"/>
       <c r="AI66"/>
       <c r="AJ66"/>
       <c r="AK66" s="39"/>
@@ -6444,13 +6431,8 @@
       <c r="AT66" s="39"/>
     </row>
     <row r="67" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="V67" s="46"/>
-      <c r="W67" s="46"/>
-      <c r="X67" s="46"/>
-      <c r="Y67" s="46"/>
-      <c r="Z67" s="46"/>
-      <c r="AA67" s="46"/>
-      <c r="AB67" s="46"/>
+      <c r="AC67" s="46"/>
+      <c r="AD67" s="46"/>
       <c r="AI67"/>
       <c r="AJ67"/>
       <c r="AK67" s="39"/>
@@ -6461,13 +6443,9 @@
       <c r="AT67" s="39"/>
     </row>
     <row r="68" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="V68" s="46"/>
-      <c r="W68" s="46"/>
-      <c r="X68" s="46"/>
-      <c r="Y68" s="46"/>
-      <c r="Z68" s="46"/>
-      <c r="AA68" s="46"/>
-      <c r="AB68" s="46"/>
+      <c r="AC68" s="46"/>
+      <c r="AD68" s="46"/>
+      <c r="AE68" s="46"/>
       <c r="AI68"/>
       <c r="AJ68"/>
       <c r="AK68" s="39"/>
@@ -6478,14 +6456,18 @@
       <c r="AT68" s="39"/>
     </row>
     <row r="69" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="V69" s="46"/>
-      <c r="W69" s="46"/>
-      <c r="X69" s="46"/>
-      <c r="Y69" s="46"/>
-      <c r="Z69" s="46"/>
-      <c r="AA69" s="46"/>
-      <c r="AB69" s="46"/>
-      <c r="AC69" s="46"/>
+      <c r="B69"/>
+      <c r="C69"/>
+      <c r="E69" s="68"/>
+      <c r="F69" s="68"/>
+      <c r="G69" s="1"/>
+      <c r="H69"/>
+      <c r="I69" s="68"/>
+      <c r="J69"/>
+      <c r="K69"/>
+      <c r="L69" s="68"/>
+      <c r="AD69" s="46"/>
+      <c r="AE69" s="46"/>
       <c r="AI69"/>
       <c r="AJ69"/>
       <c r="AK69" s="39"/>
@@ -6495,197 +6477,191 @@
       <c r="AS69" s="39"/>
       <c r="AT69" s="39"/>
     </row>
-    <row r="70" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="AC70" s="46"/>
-      <c r="AD70" s="46"/>
+    <row r="70" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="45"/>
+      <c r="B70" s="73"/>
+      <c r="C70" s="73"/>
+      <c r="D70" s="73"/>
+      <c r="E70" s="73"/>
+      <c r="F70" s="73"/>
+      <c r="G70" s="73"/>
+      <c r="H70" s="74"/>
+      <c r="I70" s="73"/>
+      <c r="J70" s="73"/>
+      <c r="K70" s="73"/>
+      <c r="L70" s="73"/>
+      <c r="M70" s="45"/>
+      <c r="N70" s="45"/>
+      <c r="O70" s="45"/>
+      <c r="P70" s="45"/>
+      <c r="Q70" s="45"/>
+      <c r="R70" s="45"/>
+      <c r="S70" s="45"/>
+      <c r="V70" s="45"/>
+      <c r="W70" s="45"/>
+      <c r="X70" s="45"/>
+      <c r="Y70" s="45"/>
+      <c r="Z70" s="45"/>
+      <c r="AA70" s="45"/>
+      <c r="AB70" s="45"/>
+      <c r="AC70" s="45"/>
+      <c r="AD70" s="45"/>
       <c r="AI70"/>
-      <c r="AJ70"/>
+      <c r="AJ70" s="74"/>
       <c r="AK70" s="39"/>
-      <c r="AL70" s="39"/>
+      <c r="AL70" s="41"/>
+      <c r="AM70" s="45"/>
+      <c r="AN70" s="45"/>
       <c r="AQ70"/>
-      <c r="AR70"/>
+      <c r="AR70" s="74"/>
       <c r="AS70" s="39"/>
-      <c r="AT70" s="39"/>
-    </row>
-    <row r="71" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="AC71" s="46"/>
-      <c r="AD71" s="46"/>
-      <c r="AE71" s="46"/>
-      <c r="AI71"/>
-      <c r="AJ71"/>
-      <c r="AK71" s="39"/>
-      <c r="AL71" s="39"/>
-      <c r="AQ71"/>
-      <c r="AR71"/>
-      <c r="AS71" s="39"/>
-      <c r="AT71" s="39"/>
-    </row>
-    <row r="72" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="B72"/>
-      <c r="C72"/>
-      <c r="E72" s="68"/>
-      <c r="F72" s="68"/>
-      <c r="G72" s="1"/>
-      <c r="H72"/>
-      <c r="I72" s="68"/>
-      <c r="J72"/>
-      <c r="K72"/>
-      <c r="L72" s="68"/>
-      <c r="AD72" s="46"/>
-      <c r="AE72" s="46"/>
-      <c r="AI72"/>
-      <c r="AJ72"/>
-      <c r="AK72" s="39"/>
-      <c r="AL72" s="39"/>
-      <c r="AQ72"/>
-      <c r="AR72"/>
-      <c r="AS72" s="39"/>
-      <c r="AT72" s="39"/>
-    </row>
-    <row r="73" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="45"/>
-      <c r="B73" s="74"/>
-      <c r="C73" s="74"/>
-      <c r="D73" s="74"/>
-      <c r="E73" s="74"/>
-      <c r="F73" s="74"/>
-      <c r="G73" s="74"/>
-      <c r="H73" s="75"/>
-      <c r="I73" s="74"/>
-      <c r="J73" s="74"/>
-      <c r="K73" s="74"/>
-      <c r="L73" s="74"/>
-      <c r="M73" s="45"/>
-      <c r="N73" s="45"/>
-      <c r="O73" s="45"/>
-      <c r="P73" s="45"/>
-      <c r="Q73" s="45"/>
-      <c r="R73" s="45"/>
-      <c r="S73" s="45"/>
-      <c r="V73" s="45"/>
-      <c r="W73" s="45"/>
-      <c r="X73" s="45"/>
-      <c r="Y73" s="45"/>
-      <c r="Z73" s="45"/>
-      <c r="AA73" s="45"/>
-      <c r="AB73" s="45"/>
-      <c r="AC73" s="45"/>
-      <c r="AD73" s="45"/>
-      <c r="AI73"/>
-      <c r="AJ73" s="75"/>
-      <c r="AK73" s="39"/>
-      <c r="AL73" s="41"/>
-      <c r="AM73" s="45"/>
-      <c r="AN73" s="45"/>
-      <c r="AQ73"/>
-      <c r="AR73" s="75"/>
-      <c r="AS73" s="39"/>
-      <c r="AT73" s="41"/>
-      <c r="AU73" s="45"/>
-      <c r="AV73" s="45"/>
-    </row>
-    <row r="74" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="68"/>
-      <c r="B74" s="76"/>
-      <c r="C74" s="77"/>
-      <c r="D74" s="76"/>
-      <c r="E74" s="76"/>
-      <c r="F74" s="76"/>
-      <c r="G74" s="76"/>
-      <c r="H74" s="75"/>
-      <c r="I74" s="76"/>
-      <c r="J74" s="76"/>
-      <c r="K74" s="77"/>
-      <c r="L74" s="77"/>
-      <c r="M74" s="68"/>
-      <c r="N74" s="68"/>
-      <c r="O74" s="1"/>
-      <c r="P74" s="45"/>
-      <c r="Q74" s="45"/>
-      <c r="R74" s="45"/>
-      <c r="S74" s="45"/>
-      <c r="V74" s="45"/>
-      <c r="W74" s="45"/>
-      <c r="X74" s="45"/>
-      <c r="Y74" s="45"/>
-      <c r="Z74" s="45"/>
-      <c r="AA74" s="45"/>
-      <c r="AB74" s="45"/>
-      <c r="AC74" s="45"/>
-      <c r="AD74" s="45"/>
-      <c r="AE74" s="45"/>
-      <c r="AI74" s="42"/>
-      <c r="AJ74" s="42"/>
-      <c r="AK74" s="54"/>
-    </row>
-    <row r="75" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="74"/>
-      <c r="B75" s="76"/>
-      <c r="C75" s="76"/>
-      <c r="D75" s="76"/>
-      <c r="E75" s="76"/>
-      <c r="F75" s="76"/>
-      <c r="G75" s="76"/>
-      <c r="H75" s="75"/>
-      <c r="I75" s="76"/>
-      <c r="J75" s="76"/>
-      <c r="K75" s="76"/>
-      <c r="L75" s="76"/>
-      <c r="M75" s="74"/>
-      <c r="N75" s="74"/>
-      <c r="O75" s="74"/>
-      <c r="V75" s="45"/>
-      <c r="W75" s="45"/>
-      <c r="X75" s="45"/>
-      <c r="Y75" s="45"/>
-      <c r="Z75" s="45"/>
-      <c r="AA75" s="45"/>
-      <c r="AB75" s="45"/>
-      <c r="AC75" s="45"/>
-      <c r="AD75" s="45"/>
-      <c r="AE75" s="45"/>
-      <c r="AI75" s="42"/>
-      <c r="AJ75" s="42"/>
-      <c r="AK75" s="54"/>
+      <c r="AT70" s="41"/>
+      <c r="AU70" s="45"/>
+      <c r="AV70" s="45"/>
+    </row>
+    <row r="71" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="68"/>
+      <c r="B71" s="75"/>
+      <c r="C71" s="76"/>
+      <c r="D71" s="75"/>
+      <c r="E71" s="75"/>
+      <c r="F71" s="75"/>
+      <c r="G71" s="75"/>
+      <c r="H71" s="74"/>
+      <c r="I71" s="75"/>
+      <c r="J71" s="75"/>
+      <c r="K71" s="76"/>
+      <c r="L71" s="76"/>
+      <c r="M71" s="68"/>
+      <c r="N71" s="68"/>
+      <c r="O71" s="1"/>
+      <c r="P71" s="45"/>
+      <c r="Q71" s="45"/>
+      <c r="R71" s="45"/>
+      <c r="S71" s="45"/>
+      <c r="V71" s="45"/>
+      <c r="W71" s="45"/>
+      <c r="X71" s="45"/>
+      <c r="Y71" s="45"/>
+      <c r="Z71" s="45"/>
+      <c r="AA71" s="45"/>
+      <c r="AB71" s="45"/>
+      <c r="AC71" s="45"/>
+      <c r="AD71" s="45"/>
+      <c r="AE71" s="45"/>
+      <c r="AI71" s="42"/>
+      <c r="AJ71" s="42"/>
+      <c r="AK71" s="54"/>
+    </row>
+    <row r="72" spans="1:48" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="73"/>
+      <c r="B72" s="75"/>
+      <c r="C72" s="75"/>
+      <c r="D72" s="75"/>
+      <c r="E72" s="75"/>
+      <c r="F72" s="75"/>
+      <c r="G72" s="75"/>
+      <c r="H72" s="74"/>
+      <c r="I72" s="75"/>
+      <c r="J72" s="75"/>
+      <c r="K72" s="75"/>
+      <c r="L72" s="75"/>
+      <c r="M72" s="73"/>
+      <c r="N72" s="73"/>
+      <c r="O72" s="73"/>
+      <c r="V72" s="45"/>
+      <c r="W72" s="45"/>
+      <c r="X72" s="45"/>
+      <c r="Y72" s="45"/>
+      <c r="Z72" s="45"/>
+      <c r="AA72" s="45"/>
+      <c r="AB72" s="45"/>
+      <c r="AC72" s="45"/>
+      <c r="AD72" s="45"/>
+      <c r="AE72" s="45"/>
+      <c r="AI72" s="42"/>
+      <c r="AJ72" s="42"/>
+      <c r="AK72" s="54"/>
+    </row>
+    <row r="73" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A73" s="75"/>
+      <c r="B73"/>
+      <c r="C73" s="39"/>
+      <c r="D73" s="39"/>
+      <c r="H73"/>
+      <c r="I73"/>
+      <c r="J73"/>
+      <c r="K73" s="39"/>
+      <c r="L73" s="39"/>
+      <c r="M73" s="76"/>
+      <c r="N73" s="76"/>
+      <c r="O73" s="75"/>
+      <c r="P73" s="46"/>
+      <c r="Q73" s="46"/>
+      <c r="R73" s="46"/>
+      <c r="S73" s="46"/>
+      <c r="AI73" s="38"/>
+      <c r="AJ73" s="38"/>
+      <c r="AK73" s="50"/>
+    </row>
+    <row r="74" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A74" s="75"/>
+      <c r="B74"/>
+      <c r="C74" s="39"/>
+      <c r="D74" s="39"/>
+      <c r="H74" s="72"/>
+      <c r="I74"/>
+      <c r="J74"/>
+      <c r="K74" s="39"/>
+      <c r="L74" s="39"/>
+      <c r="M74" s="75"/>
+      <c r="N74" s="75"/>
+      <c r="O74" s="75"/>
+      <c r="P74" s="46"/>
+      <c r="Q74" s="46"/>
+      <c r="R74" s="46"/>
+      <c r="S74" s="46"/>
+      <c r="AI74" s="38"/>
+      <c r="AJ74" s="38"/>
+      <c r="AK74" s="50"/>
+    </row>
+    <row r="75" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A75"/>
+      <c r="B75"/>
+      <c r="C75" s="39"/>
+      <c r="D75" s="39"/>
+      <c r="I75"/>
+      <c r="J75"/>
+      <c r="K75" s="39"/>
+      <c r="L75" s="39"/>
+      <c r="AI75" s="38"/>
+      <c r="AJ75" s="38"/>
+      <c r="AK75" s="50"/>
     </row>
     <row r="76" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A76" s="76"/>
+      <c r="A76"/>
       <c r="B76"/>
       <c r="C76" s="39"/>
       <c r="D76" s="39"/>
-      <c r="H76"/>
       <c r="I76"/>
       <c r="J76"/>
       <c r="K76" s="39"/>
       <c r="L76" s="39"/>
-      <c r="M76" s="77"/>
-      <c r="N76" s="77"/>
-      <c r="O76" s="76"/>
-      <c r="P76" s="46"/>
-      <c r="Q76" s="46"/>
-      <c r="R76" s="46"/>
-      <c r="S76" s="46"/>
       <c r="AI76" s="38"/>
       <c r="AJ76" s="38"/>
       <c r="AK76" s="50"/>
     </row>
     <row r="77" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A77" s="76"/>
+      <c r="A77"/>
       <c r="B77"/>
       <c r="C77" s="39"/>
       <c r="D77" s="39"/>
-      <c r="H77" s="73"/>
+      <c r="H77" s="46"/>
       <c r="I77"/>
       <c r="J77"/>
       <c r="K77" s="39"/>
       <c r="L77" s="39"/>
-      <c r="M77" s="76"/>
-      <c r="N77" s="76"/>
-      <c r="O77" s="76"/>
-      <c r="P77" s="46"/>
-      <c r="Q77" s="46"/>
-      <c r="R77" s="46"/>
-      <c r="S77" s="46"/>
+      <c r="O77" s="46"/>
       <c r="AI77" s="38"/>
       <c r="AJ77" s="38"/>
       <c r="AK77" s="50"/>
@@ -6695,10 +6671,12 @@
       <c r="B78"/>
       <c r="C78" s="39"/>
       <c r="D78" s="39"/>
+      <c r="H78" s="46"/>
       <c r="I78"/>
       <c r="J78"/>
       <c r="K78" s="39"/>
       <c r="L78" s="39"/>
+      <c r="O78" s="46"/>
       <c r="AI78" s="38"/>
       <c r="AJ78" s="38"/>
       <c r="AK78" s="50"/>
@@ -6708,10 +6686,12 @@
       <c r="B79"/>
       <c r="C79" s="39"/>
       <c r="D79" s="39"/>
+      <c r="H79" s="46"/>
       <c r="I79"/>
       <c r="J79"/>
       <c r="K79" s="39"/>
       <c r="L79" s="39"/>
+      <c r="O79" s="46"/>
       <c r="AI79" s="38"/>
       <c r="AJ79" s="38"/>
       <c r="AK79" s="50"/>
@@ -6901,12 +6881,10 @@
       <c r="B92"/>
       <c r="C92" s="39"/>
       <c r="D92" s="39"/>
-      <c r="H92" s="46"/>
       <c r="I92"/>
       <c r="J92"/>
       <c r="K92" s="39"/>
       <c r="L92" s="39"/>
-      <c r="O92" s="46"/>
       <c r="AI92" s="38"/>
       <c r="AJ92" s="38"/>
       <c r="AK92" s="50"/>
@@ -6916,12 +6894,10 @@
       <c r="B93"/>
       <c r="C93" s="39"/>
       <c r="D93" s="39"/>
-      <c r="H93" s="46"/>
       <c r="I93"/>
       <c r="J93"/>
       <c r="K93" s="39"/>
       <c r="L93" s="39"/>
-      <c r="O93" s="46"/>
       <c r="AI93" s="38"/>
       <c r="AJ93" s="38"/>
       <c r="AK93" s="50"/>
@@ -6931,12 +6907,10 @@
       <c r="B94"/>
       <c r="C94" s="39"/>
       <c r="D94" s="39"/>
-      <c r="H94" s="46"/>
       <c r="I94"/>
       <c r="J94"/>
       <c r="K94" s="39"/>
       <c r="L94" s="39"/>
-      <c r="O94" s="46"/>
       <c r="AI94" s="38"/>
       <c r="AJ94" s="38"/>
       <c r="AK94" s="50"/>
@@ -7281,51 +7255,27 @@
     </row>
     <row r="121" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A121"/>
-      <c r="B121"/>
-      <c r="C121" s="39"/>
-      <c r="D121" s="39"/>
-      <c r="I121"/>
-      <c r="J121"/>
-      <c r="K121" s="39"/>
-      <c r="L121" s="39"/>
       <c r="AI121" s="38"/>
       <c r="AJ121" s="38"/>
       <c r="AK121" s="50"/>
     </row>
     <row r="122" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A122"/>
-      <c r="B122"/>
-      <c r="C122" s="39"/>
-      <c r="D122" s="39"/>
-      <c r="I122"/>
-      <c r="J122"/>
-      <c r="K122" s="39"/>
-      <c r="L122" s="39"/>
       <c r="AI122" s="38"/>
       <c r="AJ122" s="38"/>
       <c r="AK122" s="50"/>
     </row>
     <row r="123" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A123"/>
-      <c r="B123"/>
-      <c r="C123" s="39"/>
-      <c r="D123" s="39"/>
-      <c r="I123"/>
-      <c r="J123"/>
-      <c r="K123" s="39"/>
-      <c r="L123" s="39"/>
       <c r="AI123" s="38"/>
       <c r="AJ123" s="38"/>
       <c r="AK123" s="50"/>
     </row>
     <row r="124" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A124"/>
       <c r="AI124" s="38"/>
       <c r="AJ124" s="38"/>
       <c r="AK124" s="50"/>
     </row>
     <row r="125" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A125"/>
       <c r="AI125" s="38"/>
       <c r="AJ125" s="38"/>
       <c r="AK125" s="50"/>
@@ -7434,21 +7384,6 @@
       <c r="AI146" s="38"/>
       <c r="AJ146" s="38"/>
       <c r="AK146" s="50"/>
-    </row>
-    <row r="147" spans="35:37" x14ac:dyDescent="0.25">
-      <c r="AI147" s="38"/>
-      <c r="AJ147" s="38"/>
-      <c r="AK147" s="50"/>
-    </row>
-    <row r="148" spans="35:37" x14ac:dyDescent="0.25">
-      <c r="AI148" s="38"/>
-      <c r="AJ148" s="38"/>
-      <c r="AK148" s="50"/>
-    </row>
-    <row r="149" spans="35:37" x14ac:dyDescent="0.25">
-      <c r="AI149" s="38"/>
-      <c r="AJ149" s="38"/>
-      <c r="AK149" s="50"/>
     </row>
   </sheetData>
   <phoneticPr fontId="24" type="noConversion"/>
